--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -2,16 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="題庫" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,10 +16,8 @@
   <fonts count="3">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -45,18 +38,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8E0F0"/>
+        <fgColor rgb="FFE8E0F0"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -83,9 +70,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -200,72 +186,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -321,7 +249,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -330,13 +258,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -370,17 +298,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -435,8 +352,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -446,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X96"/>
+  <dimension ref="A1:X107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -665,14 +580,38 @@
           <t>血漿約占全血 55%，以水為主，含蛋白質與電解質。</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>「約占 55%」「水與溶質」：血液分成液體和血球兩部分，這裡在問液體那一半。</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>血液離心後會分成上層液體和下層血球嗎？→ 上層那層以水為主、帶有蛋白質與電解質的液體叫什麼？→ 它是細胞，還是液體？</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>以水為主、約占全血 55% 的液體部分，就是「血漿」。</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>血漿＝血液的液體部分，約 55%，以水為主；其餘是血球。</t>
+        </is>
+      </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
@@ -743,14 +682,38 @@
           <t>血清是凝血後的液體，缺少纖維蛋白原等凝血蛋白。</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>「血清」「血漿」「缺少」：兩者差在有沒有經過凝血。</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>血清是血液凝固之前還是之後得到的液體？→ 凝血時會把哪一類蛋白質用掉，變成血塊？→ 用掉的那類蛋白質，血清裡還會有嗎？</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>血清是凝血後的液體，凝血蛋白已被用掉，所以缺少「纖維蛋白原等凝血蛋白」。</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>血清＝血漿 − 纖維蛋白原等凝血蛋白（凝血時被用掉）。</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="inlineStr"/>
-      <c r="W3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -821,14 +784,38 @@
           <t>成熟紅血球無核、呈雙凹圓盤狀，利於攜氧。</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>「成熟紅血球」「特徵」：想想紅血球的外形和有沒有細胞核。</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>紅血球的工作是吞細菌、做抗體，還是攜氧？→ 成熟紅血球還保留細胞核嗎？→ 它的形狀是什麼樣子，才方便攜氧？</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>成熟紅血球沒有核、形狀像兩面凹的圓盤，所以選「無核、雙凹圓盤狀」。</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>成熟紅血球＝無核＋雙凹圓盤→專心攜氧。</t>
+        </is>
+      </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
@@ -899,14 +886,38 @@
           <t>白血球具細胞核，負責免疫與防禦。</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>「血球」「免疫防禦」：先分清楚三種血球各自的工作。</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>紅血球主要負責什麼？→ 血小板主要負責什麼？→ 剩下哪一種血球有細胞核、負責對抗外來入侵？</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>負責免疫與防禦的是有細胞核的「白血球」。</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>紅血球→攜氧；白血球→防禦；血小板→止血。</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
@@ -977,14 +988,38 @@
           <t>血小板先形成初步栓子，之後由纖維蛋白網加強。</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>「血小板」「止血」「第一個」：問的是止血最早的那一步。</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>血管破了，最先趕到破口的是哪種成分？→ 它們到了之後會黏在傷口並聚在一起嗎？→ 聚在一起先形成的是穩固血塊，還是初步的栓子？</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>血小板會先黏附並聚集，因此第一步是「黏附並聚集形成初步栓子」。</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>止血順序：血小板栓子（先、鬆）→ 纖維蛋白網（後、穩）。</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="3" t="inlineStr"/>
-      <c r="W6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1055,14 +1090,38 @@
           <t>成人由紅骨髓持續進行造血。</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>「成人」「最主要」「造血器官」：要選成人時期，不是胚胎時期。</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>卵黃囊、肝臟、脾臟是胚胎時期還是成人時期的造血地點？→ 出生後長大，造血工作交給哪裡？→ 那是骨頭裡哪一種骨髓？</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>成人由骨頭裡的紅骨髓持續造血，所以答案是「紅骨髓」。</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>成人造血＝紅骨髓；卵黃囊、肝、脾＝胚胎時期。</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
-      <c r="V7" s="3" t="inlineStr"/>
-      <c r="W7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1133,14 +1192,38 @@
           <t>血比容過高會使血液黏滯度大幅上升，增加心臟唧血阻力。</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>「血比容 65%」「心臟負荷變大」：血球比例太高，血液性質會改變。</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>血比容升高代表血液中哪種成分變多？→ 血球變多，血液會變得比較稀還是比較黏稠？→ 血越黏，心臟把血打出去會更省力還是更費力？</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>血球太多讓血液變黏，心臟更難推動，所以是「血液黏滯度上升，唧血阻力增加」。</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>血比容↑→ 黏滯度↑→ 唧血阻力↑→ 心臟負荷↑。</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1211,14 +1294,38 @@
           <t>這是血清；它是凝血後的液體，纖維蛋白原等凝血蛋白已被消耗。</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>「未加入抗凝劑」「凝固後」「上清液」：這是凝血後才得到的液體。</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>沒加抗凝劑讓血液凝固後，上面的淡黃色液體叫血漿還是血清？→ 凝固的過程中消耗掉哪一類蛋白質？→ 所以它和血漿相比少了什麼？</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>這液體是血清，凝血時已用掉「纖維蛋白原等凝血蛋白」。</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>凝固後的上清液＝血清＝血漿少了凝血蛋白。</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="inlineStr"/>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1289,14 +1396,38 @@
           <t>嗜鹼性球含肝素與組織胺；嗜酸性球則有抗過敏作用，兩者最容易混淆。</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>「陷阱題」「過敏」「配對正確」：嗜鹼性球和嗜酸性球最容易搞混。</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>哪一種白血球裡面含有肝素與組織胺？→ 嗜酸性球是釋放組織胺，還是有抗過敏作用？→ 製造抗體、形成纖維蛋白網是這些細胞的工作嗎？</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>含肝素與組織胺的是嗜鹼性球，所以正確配對是「嗜鹼性球—含肝素與組織胺」。</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>嗜鹼＝肝素＋組織胺；嗜酸＝抗過敏，別弄反。</t>
+        </is>
+      </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1367,14 +1498,38 @@
           <t>凝血酶促使纖維蛋白原形成纖維蛋白網，強化原本的血小板栓子。</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>「鬆散栓子」「之後」「穩固」：問止血的下一步，要讓血塊變牢。</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>血小板栓子形成後，要靠什麼把它綁牢？→ 血漿裡哪種蛋白質會變成細絲網？→ 凝血酶把它轉成什麼？</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>凝血酶讓纖維蛋白原變成網子加固栓子，所以是「纖維蛋白原形成纖維蛋白網」。</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>血小板栓子（鬆）＋纖維蛋白網（牢）＝穩固血塊。</t>
+        </is>
+      </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1445,14 +1600,38 @@
           <t>成人由紅骨髓持續造血；胚胎造血依序經過卵黃囊、肝臟、脾臟與骨髓。</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>「陷阱題」「造血器官演變」：要分清胚胎時期和成人時期。</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>胚胎造血依序經過哪些地方？→ 卵黃囊、肝、脾是出生前還是出生後的造血處？→ 成人長期負責造血的是哪裡？</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>胚胎依序由卵黃囊、肝、脾到骨髓，成人則是「成人終身主要由紅骨髓造血」。</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>造血順序：卵黃囊→肝→脾→骨髓；成人＝紅骨髓。</t>
+        </is>
+      </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>血液的組成圖卡</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-composition-v1/index.html</t>
+        </is>
+      </c>
       <c r="X12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1523,10 +1702,26 @@
           <t>成人紅血球主要由紅骨髓（如頭蓋骨、胸骨、肋骨等）中的幹細胞分化生成，進入血液前會失去細胞核，呈現無核之雙凹圓盤狀。</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>「成人紅血球」「生成」「成熟釋入血液」：同時問地點和外形。</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>成人造血在紅骨髓還是黃骨髓？→ 紅血球進入血液前，會失去什麼構造？→ 失去後它的形狀是什麼樣子？</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>紅血球在紅骨髓生成，釋出前失去細胞核，所以是「紅骨髓；無細胞核的雙凹圓盤狀細胞」。</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>紅血球：紅骨髓出生→丟掉細胞核→雙凹圓盤。</t>
+        </is>
+      </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr"/>
@@ -1601,10 +1796,26 @@
           <t>當組織缺氧時，腎臟近腎絲球器受到刺激釋放紅血球生成因子，將血漿中的紅血球生成素原活化為紅血球生成素（EPO），隨血流至紅骨髓加速造血。</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>「缺氧」「腎臟」「紅血球生成」：腎臟是感應缺氧、啟動造血的器官。</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>組織缺氧時，腎臟會先釋放什麼因子？→ 這個因子把血漿中的哪個前身物質活化？→ 活化後的激素叫什麼，會去紅骨髓加速造血？</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>腎臟放出紅血球生成因子，活化成 EPO，所以是「釋放紅血球生成因子，使血漿中紅血球生成素原轉變為紅血球生成素（EPO）」。</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>缺氧→腎臟放紅血球生成因子→EPO 原變 EPO→紅骨髓造血。</t>
+        </is>
+      </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr"/>
@@ -1679,10 +1890,26 @@
           <t>血紅素含有 4 個含鐵血基質，每分子可攜帶 4 個氧分子；二氧化碳在血液中以碳酸氫根（HCO3⁻）形式運送占 70%（經紅血球內碳酸酐酶 CA 催化），23% 與球蛋白結合，7% 直接溶於血漿。</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>「攜氧」「二氧化碳運輸」「正確」：要記得數字：每分子帶幾個氧、CO₂ 各途徑占多少。</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>一個血紅素有幾個含鐵血基質，可以帶幾個氧？→ 氧是跟鐵結合，還是跟球蛋白結合？→ CO₂ 的 70%、23%、7% 各是哪種形式？</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>CO₂ 大多在紅血球內轉成碳酸氫根，所以正確的是「血液中 70% 的二氧化碳係轉化為碳酸氫根（HCO3⁻）形式運送」。</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>血紅素 4 鐵帶 4 氧；CO₂＝70% HCO₃⁻＋23% 球蛋白＋7% 溶血漿。</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr"/>
@@ -1757,10 +1984,26 @@
           <t>老化紅血球細胞膜彈性喪失且變脆，通過脾臟與肝臟之竇狀微血管（sinusoidal capillary）細胞間孔隙時擠壓破裂，由網狀內皮細胞（巨噬細胞）吞噬分解。</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>「老化紅血球」「在何處」「吞噬」：老紅血球變脆，會卡在窄縫被清掉。</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>老化紅血球的細胞膜變得更有彈性還是更脆？→ 它要擠過哪兩個器官的竇狀微血管小孔？→ 擠破後由哪種細胞吞掉？</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>老紅血球在脾與肝的窄縫擠破後被巨噬細胞吞噬，所以是「脾臟與肝臟的竇狀微血管」。</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>老紅血球變脆→脾、肝竇狀微血管擠破→巨噬細胞吞掉。</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="3" t="inlineStr"/>
@@ -1835,10 +2078,26 @@
           <t>血紅素分解時，血球素（Globin）降解為胺基酸回收；鐵質（Fe）運回骨髓再利用；血基質（Heme）轉化為脂溶性膽紅素，於肝臟經尿苷酸轉移酶轉化為結合態膽紅素隨膽汁排入腸道。</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>「血紅素成分」「回收與代謝路徑」：血紅素拆成三部分，各有去處。</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>血球素（Globin）拆解後變成什麼？→ 鐵會被排掉還是送回骨髓？→ 血基質（Heme）變成什麼，經肝臟處理後從哪裡排出？</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>血基質變成膽紅素，肝臟結合後進膽汁，所以是「血基質（Heme）轉化為膽紅素，經肝臟結合後隨膽汁排入腸道」。</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>球蛋白→胺基酸；鐵→回骨髓；血基質→膽紅素→肝→膽汁→腸道。</t>
+        </is>
+      </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="3" t="inlineStr"/>
@@ -1913,10 +2172,26 @@
           <t>鐵是血紅素血基質中心的 Fe²⁺；維生素 B₁₂ 與葉酸是細胞分裂所需，B₁₂ 吸收需要胃分泌的內在因子；刺激造血的 EPO 則來自腎臟。</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>「原料」「配對正確」：逐一核對每種物質真正的角色。</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>血紅素中心的金屬離子是哪一種？→ 內在因子是胃分泌還是腎臟分泌？→ 刺激紅骨髓造血的 EPO 來自哪裡？</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>血基質中心是 Fe²⁺ 負責結合氧，所以正確的是「鐵：血紅素中心的 Fe²⁺，負責結合氧」。</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>鐵＝血紅素中心 Fe²⁺；內在因子＝胃；EPO＝腎臟。</t>
+        </is>
+      </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr"/>
@@ -1991,10 +2266,26 @@
           <t>紅血球增加、攜氧恢復後，組織不再缺氧，腎臟 EPO 分泌減少，造血速度回到平常；多出的紅血球隨壽命到期被清除，血比容逐漸恢復，這就是負回饋。</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>「回到平地」「血比容恢復正常」：刺激消失後，調節會往回拉。</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>回到平地後，組織還缺氧嗎？→ 不缺氧時，腎臟分泌的 EPO 會增加還是減少？→ 造血變慢、多的紅血球到期被清除，這叫什麼回饋？</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>缺氧解除使 EPO 減少，造血回到平常，所以是「缺氧解除，腎臟分泌的 EPO 減少，造血速度回到平常（負回饋）」。</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>缺氧→EPO↑→紅血球↑→不缺氧→EPO↓＝負回饋。</t>
+        </is>
+      </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" s="3" t="inlineStr"/>
@@ -2069,10 +2360,26 @@
           <t>胃壁細胞分泌內在因子（Intrinsic factor），與維生素 B₁₂ 結合後才能在迴腸被吸收；B₁₂ 讓紅血球母細胞能正常複製 DNA 與分裂。</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>「維生素 B₁₂」「迴腸被吸收」「幫忙」：B₁₂ 需要一個搭檔才能被吸收。</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>B₁₂ 需要跟哪一種物質結合才能在迴腸吸收？→ 這種物質是哪個器官分泌的？→ 是胃裡的哪一種細胞？</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>B₁₂ 要和胃分泌的內在因子結合才能吸收，所以是「胃壁細胞分泌的內在因子」。</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>內在因子（胃壁細胞）＋B₁₂→迴腸吸收→紅血球母細胞分裂。</t>
+        </is>
+      </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr"/>
@@ -2147,10 +2454,26 @@
           <t>高山大氣壓低導致高空低氧，引發身體組織缺氧（Hypoxia），刺激腎臟釋放 EPO 隨血流至紅骨髓，加速幹細胞分化生成紅血球，使血比容（Hct）與攜氧能力代償性提高。</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>「高山」「45% 上升至 55%」「正確順序」：從缺氧一路推到造血。</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>高山空氣氧少，身體組織會怎樣？→ 哪個器官感應到缺氧並增加 EPO？→ EPO 送到哪裡去加速製造紅血球，讓血比容上升？</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>順序是缺氧→腎臟 EPO→紅骨髓造血，所以是「高山低氧壓 → 組織缺氧 → 腎臟釋放 EPO 增加 → 刺激紅骨髓造血 → 血比容上升」。</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>低氧→組織缺氧→腎 EPO↑→紅骨髓造血→血比容↑。</t>
+        </is>
+      </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr"/>
@@ -2225,10 +2548,26 @@
           <t>血基質轉成膽紅素，隨膽汁排入腸道，經腸道細菌作用形成尿膽素原與糞膽素原；糞膽素原使糞便呈黃褐色。</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>「糞便」「黃褐色」「紅血球分解後」：顏色來自血基質的代謝產物。</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>血基質分解後先變成什麼？→ 它隨膽汁進入腸道後，被腸道細菌轉成哪些物質？→ 其中哪一個讓糞便呈黃褐色？</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>膽紅素在腸道變成糞膽素原，使糞便變色，所以是「膽紅素在腸道轉變成的糞膽素原」。</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>血基質→膽紅素→腸道細菌→糞膽素原＝糞便黃褐色。</t>
+        </is>
+      </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr"/>
@@ -2303,10 +2642,26 @@
           <t>男性 RBC 約 540 萬/mm³、Hb 16 g/dl；女性約 480 萬/mm³、Hb 14 g/dl。男性數值較高，主要因為基礎代謝率較高、需氧較多。</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>「男性比女性高」「依本教材」「主要原因」：從需氧多少去想。</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>男性 RBC 約 540 萬、Hb 16；女性約 480 萬、Hb 14，誰比較高？→ 身體需要的氧越多，紅血球需要越多還是越少？→ 哪一個選項說明男性需氧較多？</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>男性基礎代謝率較高、需氧較多，所以是「男性的基礎代謝率較高」。</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>男 RBC 540 萬、Hb 16 &gt; 女 480 萬、Hb 14→代謝高、需氧多。</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr"/>
@@ -2381,14 +2736,38 @@
           <t>血紅素的含鐵血基質可與氧氣可逆結合。</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>「成熟紅血球」「攜帶氧氣」「分子」：找紅血球裡會和氧結合的分子。</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>紅血球裡最多的蛋白質是什麼？→ 它的哪個部分含鐵？→ 含鐵的部分能不能和氧可逆結合？</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>紅血球靠含鐵血基質的「血紅素」攜氧。</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>血紅素＝紅血球的攜氧分子（鐵和氧可逆結合）。</t>
+        </is>
+      </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="inlineStr"/>
-      <c r="V24" s="3" t="inlineStr"/>
-      <c r="W24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2459,14 +2838,38 @@
           <t>超過 98% 的氧氣與血紅素結合。</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>「大部分」「氧氣」「形式」：比較溶在血漿和結合血紅素哪個多。</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>氧直接溶在血漿裡的量多還是少？→ 紅血球裡哪個分子專門抓氧？→ 超過 98% 的氧是靠哪種方式運送？</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>超過 98% 的氧是「與血紅素結合」運送。</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>氧氣：＞98% 與血紅素結合；溶在血漿的很少。</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr"/>
       <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="inlineStr"/>
-      <c r="W25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2537,14 +2940,38 @@
           <t>紅血球內的碳酸酐酶協助 CO₂ 轉為 HCO₃⁻。</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>「約 70%」「二氧化碳」：70% 這個數字對應 CO₂ 最主要的運送形式。</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>CO₂ 進入紅血球後，哪個酵素會幫它轉換？→ 轉換後變成哪一種離子？→ 占 70% 的就是這種形式嗎？</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>紅血球的碳酸酐酶把 CO₂ 轉成「碳酸氫根 HCO₃⁻」運送。</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>CO₂ 70%＝碳酸氫根 HCO₃⁻（靠碳酸酐酶）。</t>
+        </is>
+      </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="inlineStr"/>
-      <c r="W26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2615,14 +3042,38 @@
           <t>腎臟感受低氧後以 EPO 刺激紅骨髓造血。</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>「組織缺氧」「分泌 EPO」：要記住 EPO 是哪個器官放出的。</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>缺氧時，哪個器官能感受到低氧？→ 它會放出什麼激素？→ 這激素再去刺激哪裡造血？</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>感受低氧並分泌 EPO 刺激紅骨髓的器官是「腎臟」。</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>缺氧→腎臟→EPO→紅骨髓造血。</t>
+        </is>
+      </c>
       <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2693,14 +3144,38 @@
           <t>血基質中心是 Fe²⁺，負責與氧氣可逆結合，所以鐵是製造血紅素的必要原料。</t>
         </is>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="3" t="inlineStr"/>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>「血基質中心」「礦物質」：血基質中心的金屬負責抓住氧。</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>血紅素靠血基質的哪個離子與氧結合？→ 這個離子寫作 Fe²⁺，是哪一種元素？→ 所以製造血紅素一定要有它嗎？</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>血基質中心是 Fe²⁺，所以需要的礦物質是「鐵」。</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>血基質中心＝Fe²⁺＝鐵→負責抓氧。</t>
+        </is>
+      </c>
       <c r="T28" s="3" t="inlineStr"/>
       <c r="U28" s="3" t="inlineStr"/>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2771,14 +3246,38 @@
           <t>胃壁細胞分泌的內在因子與維生素 B₁₂ 結合後，才能在迴腸被吸收；B₁₂ 是紅血球母細胞分裂所需。</t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>「維生素 B₁₂」「迴腸」「胃分泌」：B₁₂ 要靠胃的一種物質幫忙吸收。</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>B₁₂ 在哪裡被吸收？→ 它需要先跟什麼物質結合？→ 那是胃壁細胞分泌的哪一種因子？</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>胃壁細胞分泌的「內在因子」與 B₁₂ 結合後，才能在迴腸吸收。</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>B₁₂＋內在因子（胃）→迴腸吸收。</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr"/>
       <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2849,14 +3348,38 @@
           <t>鐵是血紅素血基質中心的 Fe²⁺；鐵攝取不足時血紅素合成減少，血液能攜帶的氧也跟著變少。</t>
         </is>
       </c>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>「很少吃含鐵的食物」「最直接受影響」：鐵是血紅素的原料。</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>鐵在紅血球的哪個分子裡？→ 鐵不夠時，這個分子會做得多還是少？→ 它少了，血液能帶的氧會怎樣？</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>鐵不足使血紅素做得少，所以是「血紅素合成減少，血液攜氧能力下降」。</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>鐵↓→血紅素↓→攜氧能力↓。</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr"/>
       <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2927,14 +3450,38 @@
           <t>CO₂ 運送三大途徑：70% 經紅血球內碳酸酐酶（CA，反應加速 250 倍）轉化為 HCO₃⁻ 於血漿運送；23% 與血紅素球蛋白結合；7% 溶於血漿。</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>「二氧化碳」「紅血球與血漿」「轉化」：想 CO₂ 在紅血球內怎麼變身。</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>CO₂ 最主要（70%）的運送方式是溶在血漿、和鐵結合，還是轉成 HCO₃⁻？→ 碳酸酐酶在紅血球內還是血漿中，是加快還是減慢反應？→ CO₂ 加水先變 H₂CO₃，再解離成什麼？</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>70% 的 CO₂ 在紅血球內經碳酸酐酶轉成 HCO₃⁻，所以是「約 70% 的 CO₂ 在紅血球內經碳酸酐酶（CA）催化生成 H₂CO₃，再解離為 HCO₃⁻ 進入血漿運送」。</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>CO₂：70% 經 CA→H₂CO₃→HCO₃⁻；23% 結合球蛋白；7% 溶血漿。</t>
+        </is>
+      </c>
       <c r="T31" s="3" t="inlineStr"/>
       <c r="U31" s="3" t="inlineStr"/>
-      <c r="V31" s="3" t="inlineStr"/>
-      <c r="W31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
@@ -3005,14 +3552,38 @@
           <t>血紅素與氧是可逆結合：在氧分壓高的肺泡結合，在氧分壓低的組織解離，把氧送到需要的地方。</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>「肺泡結合」「肌肉解離」：同一個血紅素，在不同地方行為不同。</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>血紅素和氧的結合是固定的還是可逆的？→ 肺泡和運動中的肌肉，哪邊氧分壓高？→ 氧分壓高時結合、低時會怎樣？</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>肺泡氧多就結合、肌肉氧少就放出，原因是「肺泡氧分壓高、肌肉組織氧分壓低」。</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>氧分壓高（肺）→結合；氧分壓低（組織）→解離釋氧。</t>
+        </is>
+      </c>
       <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="3" t="inlineStr"/>
-      <c r="W32" s="3" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
@@ -3083,14 +3654,38 @@
           <t>組織缺氧刺激腎臟釋放紅血球生成因子，將血漿中的紅血球生成素原轉化為 EPO，EPO 作用於紅骨髓刺激幹細胞分化生成紅血球。</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>「海拔 3,500 公尺」「低氧」「紅血球生成」：從缺氧推到腎臟與骨髓。</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>高山低氧，最先感受到的是組織缺氧嗎？→ 哪個器官會放出紅血球生成因子，把 EPO 原轉成 EPO？→ EPO 最後作用在哪裡造血？</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>缺氧讓腎臟啟動 EPO 刺激骨髓，所以是「組織缺氧刺激腎臟釋放紅血球生成因子，使血漿 EPO 原轉化為 EPO 刺激骨髓造血」。</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>低氧→腎臟紅血球生成因子→EPO 原變 EPO→骨髓造血。</t>
+        </is>
+      </c>
       <c r="T33" s="3" t="inlineStr"/>
       <c r="U33" s="3" t="inlineStr"/>
-      <c r="V33" s="3" t="inlineStr"/>
-      <c r="W33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
@@ -3161,14 +3756,38 @@
           <t>老化紅血球分解後，血球素變成胺基酸、鐵運回紅骨髓再利用，血基質則轉成膽紅素隨膽汁排出。</t>
         </is>
       </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>「約 120 天」「分解」「鐵最後」：只追蹤鐵這一個成分的去處。</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>紅血球分解後，血紅素會拆成哪幾部分？→ 鐵是珍貴原料，會被丟掉還是回收？→ 回收的鐵要送去哪裡再做新的血紅素？</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>鐵會回收利用，所以是「被回收運回紅骨髓，用來製造新的血紅素」。</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>老紅血球：鐵→回紅骨髓再用；血基質→膽紅素；球蛋白→胺基酸。</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
-      <c r="W34" s="3" t="inlineStr"/>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>血液氣體運送圖卡</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-gas-transport-v2/index.html</t>
+        </is>
+      </c>
       <c r="X34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
@@ -3239,14 +3858,38 @@
           <t>血管痙攣是第一道防線：先縮小破口、降低局部血流量。</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>「剛受傷時」「最先」：問的是止血三步驟裡的第一步。</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>止血有哪三個步驟？→ 血管壁有平滑肌，受傷當下它能立刻做什麼動作？→ 破口縮小、血流變少，靠的是收縮還是擴張？</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>血管受傷的第一道防線是先縮小破口，所以答案是「血管痙攣收縮」。</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>止血第一步＝血管痙攣（縮小破口、減少血流）；擴張只會讓血流更多。</t>
+        </is>
+      </c>
       <c r="T35" s="3" t="inlineStr"/>
       <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
@@ -3317,14 +3960,38 @@
           <t>內皮受損會露出下層膠原纖維，血小板在此黏附、活化並招募同伴。</t>
         </is>
       </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>「血小板」「先附著」「受傷後暴露」：找血管內皮底下原本藏著的結構。</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>血管內皮受損後，底下會露出什麼纖維？→ 血小板碰到這種纖維會做什麼？→ 黏附後再招募同伴，就形成什麼？</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>內皮破了露出下層「膠原纖維」，血小板在此黏附、活化，形成初步栓子。</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>內皮破→露出膠原纖維→血小板黏附、活化、招募同伴→血小板栓子。</t>
+        </is>
+      </c>
       <c r="T36" s="3" t="inlineStr"/>
       <c r="U36" s="3" t="inlineStr"/>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
@@ -3395,14 +4062,38 @@
           <t>內外在路徑的重點是匯流：活化因子 X 後進入共同路徑。</t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>「內在與外在」「最後匯入」「共同步驟」：問兩條路徑在哪裡會合。</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>內在、外在路徑是兩條不同的起點，對嗎？→ 兩條路最後都會去活化哪一個凝血因子？→ 活化它之後進入的是哪一段路徑？</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>兩條路徑的重點是匯流，答案是「活化因子 X，進入共同路徑」。</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>內在路徑＋外在路徑 → 活化因子 X → 共同路徑。</t>
+        </is>
+      </c>
       <c r="T37" s="3" t="inlineStr"/>
       <c r="U37" s="3" t="inlineStr"/>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
@@ -3473,14 +4164,38 @@
           <t>凝血酶將可溶性的纖維蛋白原轉為不溶性的纖維蛋白，形成固定血塊的網。</t>
         </is>
       </c>
-      <c r="P38" s="3" t="inlineStr"/>
-      <c r="Q38" s="3" t="inlineStr"/>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>「凝血酶」「轉變成纖維蛋白網」：找纖維蛋白的前身。</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>纖維蛋白是溶在血漿裡，還是不溶的網？→ 它的可溶性前身，名字和它長得很像的是哪一個？→ 凝血酶負責把誰切成纖維蛋白？</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>凝血酶把可溶的「纖維蛋白原（Fibrinogen）」轉成不溶的纖維蛋白網。</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>凝血酶：纖維蛋白原（可溶）→ 纖維蛋白（不溶的網，固定血塊）。</t>
+        </is>
+      </c>
       <c r="T38" s="3" t="inlineStr"/>
       <c r="U38" s="3" t="inlineStr"/>
-      <c r="V38" s="3" t="inlineStr"/>
-      <c r="W38" s="3" t="inlineStr"/>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
@@ -3551,14 +4266,38 @@
           <t>維生素 K 與肝臟共同參與 II、VII、IX、X 等凝血因子的合成。</t>
         </is>
       </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>「維生素 K」「肝臟製造」「凝血因子」：要背出特定四個因子的編號。</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>題目問的是凝血因子，選項中哪些根本不是凝血因子？→ 剩下兩組羅馬數字，哪一組是維生素 K 參與合成的？→ 記得是 2、7、9、10 這四個嗎？</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>維生素 K 與肝臟共同參與合成的凝血因子是「II、VII、IX、X」。</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>維生素 K 因子＝II、VII、IX、X（口訣：2、7、9、10）。</t>
+        </is>
+      </c>
       <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
@@ -3629,14 +4368,38 @@
           <t>纖溶是在需要止血的任務完成後，清除舊血塊並恢復血流。</t>
         </is>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>「組織修復後」「tPA」「纖溶系統」：止血任務完成後，要處理什麼？</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>修復完成後，原本的血塊還需要留著嗎？→ 「纖溶」字面上是溶解什麼？→ 所以 tPA 啟動纖溶，是要讓血塊變多還是被清掉？</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>纖溶是任務完成後清除舊血塊、恢復血流，目的是「分解不再需要的纖維蛋白血塊」。</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>凝血＝把洞補起來；纖溶（tPA）＝修好後把血塊清掉、恢復血流。</t>
+        </is>
+      </c>
       <c r="T40" s="3" t="inlineStr"/>
       <c r="U40" s="3" t="inlineStr"/>
-      <c r="V40" s="3" t="inlineStr"/>
-      <c r="W40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3707,14 +4470,38 @@
           <t>鈣離子（因子 IV）是凝血路徑必需的輔因子；EDTA 或檸檬酸鹽會螯合 Ca²⁺，使凝血無法進行，所以常用於抗凝試管。</t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>「EDTA」「不會凝固」：抗凝試管的關鍵在於拿走凝血必需的某種離子。</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>凝血路徑中有哪一種離子是必需的輔因子（因子 IV）？→ EDTA 的作用是「螯合」，也就是把什麼抓走？→ 沒有這個輔因子，凝血還能進行嗎？</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>EDTA 把鈣抓走，凝血就停住，答案是「EDTA 螯合血漿中的鈣離子（Ca²⁺），凝血反應無法進行」。</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>Ca²⁺＝因子 IV，凝血必需；EDTA／檸檬酸鹽抓走 Ca²⁺ → 血不凝。</t>
+        </is>
+      </c>
       <c r="T41" s="3" t="inlineStr"/>
       <c r="U41" s="3" t="inlineStr"/>
-      <c r="V41" s="3" t="inlineStr"/>
-      <c r="W41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3785,14 +4572,38 @@
           <t>血液凝固時，纖維蛋白原轉化為不溶性纖維蛋白網並包覆血球。凝塊收縮擠出的黃色液體即為「血清」，血清與血漿的差異即為缺乏參與凝血的蛋白質（如纖維蛋白原）。</t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr"/>
-      <c r="R42" s="3" t="inlineStr"/>
-      <c r="S42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>「未加抗凝劑」「完全凝固」「血清」：血清是凝血「之後」剩下的液體。</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>血液凝固時，哪一種蛋白質被轉成纖維蛋白網？→ 這張網連同血球變成凝塊後，還會留在上層液體裡嗎？→ 所以血清比血漿少了哪一類蛋白質？</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>凝血時纖維蛋白原已用掉，所以血清「缺乏纖維蛋白原（Fibrinogen）等參與凝血反應之蛋白質」。</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>血漿 − 凝血蛋白（纖維蛋白原等）＝血清。</t>
+        </is>
+      </c>
       <c r="T42" s="3" t="inlineStr"/>
       <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3863,14 +4674,38 @@
           <t>血小板栓子較疏鬆；凝血反應生成凝血酶，將纖維蛋白原轉為纖維蛋白網，把栓子固定成緊密血塊。</t>
         </is>
       </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
-      <c r="S43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>「血塊變得牢固」：血小板栓子本身較疏鬆，是誰把它固定住？</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>血小板栓子是緊密還是疏鬆？→ 凝血反應產生的凝血酶，會把纖維蛋白原變成什麼？→ 這張網對血小板栓子有什麼作用？</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>讓血塊牢固的是「凝血酶把纖維蛋白原轉成纖維蛋白網，固定血小板栓子」。</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>血小板栓子＝疏鬆的塞子；纖維蛋白網＝把塞子綁牢的網。</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3941,14 +4776,38 @@
           <t>止血三階段順序為：1. 血管痙攣（平滑肌收縮）；2. 血小板栓塞（黏附膠原纖維、釋放 ADP/TXA2 形成疏鬆栓子）；3. 血液凝固（內外在路徑生成致活素，催化凝血酶原形成凝血酶，將纖維蛋白原轉為纖維蛋白網）。</t>
         </is>
       </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
-      <c r="S44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>「止血三階段」「順序」：要依序排出血管、血小板、凝血三步。</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>血管受傷當下，平滑肌最先做什麼？→ 接著血小板在膠原纖維上做什麼、形成什麼樣的栓子？→ 最後凝血酶產生什麼，把栓子變緊密？</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>正確順序是「血管痙攣 → 血小板黏附變形並聚集形成疏鬆栓子 → 凝血級聯反應生成凝血酶並形成緊密纖維蛋白網」。</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>止血三步：血管痙攣 → 血小板栓子（疏鬆）→ 凝血（纖維蛋白網，緊密）。</t>
+        </is>
+      </c>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
@@ -4019,14 +4878,38 @@
           <t>肝素（由肥胖細胞與嗜鹼性球分泌）可增強抗凝血酶 III 的活性，是體內的「煞車」；其他選項都是促進凝血的步驟。</t>
         </is>
       </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>「沒有受傷時」「防止血管內凝血」：要找的是抗凝的「煞車」，不是促凝的油門。</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>四個選項中，哪些是在推動凝血？→ 剩下哪一個是讓凝血變慢的物質？→ 肝素是增強誰的活性來抗凝？</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>其他選項都在促進凝血，體內的煞車是「肝素增強抗凝血酶 III 的活性」。</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>肝素（肥胖細胞、嗜鹼性球分泌）＋抗凝血酶 III＝體內防凝血的煞車。</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr"/>
       <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>止血機制與凝血圖卡</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemostasis-mechanisms-v2/index.html</t>
+        </is>
+      </c>
       <c r="X45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
@@ -4097,14 +4980,38 @@
           <t>心包腔位於漿膜心包壁層與臟層之間，內含有少許心包液（Pericardial fluid），可防止心臟跳動時產生的膜面摩擦。</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
-      <c r="S46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>「含有心包液」「減少摩擦」：找壁層與臟層之間的那個空間。</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>漿膜心包分成哪兩層？→ 兩層之間的空隙叫什麼？→ 空隙裡的少量液體能發揮什麼作用？</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>壁層與臟層之間的「心包腔（Pericardial cavity）」含心包液，可減少膜面摩擦。</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>心包腔＝壁層與臟層間的空隙，內含心包液 → 潤滑、減少摩擦。</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr"/>
       <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
@@ -4172,17 +5079,41 @@
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>心肌層（Myocardium）構成心臟壁的主體，負責心臟強採收縮以打出血液。</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr"/>
-      <c r="Q47" s="3" t="inlineStr"/>
-      <c r="R47" s="3" t="inlineStr"/>
-      <c r="S47" s="3" t="inlineStr"/>
+          <t>心肌層（Myocardium）構成心臟壁的主體，負責心臟強力收縮以打出血液。</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>「心肌細胞組成」「最厚」「負責收縮」：看名字裡有「肌」的那一層。</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>心臟壁由內到外是哪三層？→ 哪一層的名字直接帶著「肌」字？→ 負責收縮、把血打出去的應該是哪一層？</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>構成心臟壁主體、負責收縮的是「心肌層（Myocardium）」。</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>心臟壁三層：心內膜（內）→ 心肌層（中、最厚、收縮）→ 心外膜（外）。</t>
+        </is>
+      </c>
       <c r="T47" s="3" t="inlineStr"/>
       <c r="U47" s="3" t="inlineStr"/>
-      <c r="V47" s="3" t="inlineStr"/>
-      <c r="W47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
@@ -4253,14 +5184,38 @@
           <t>左心室工作量最大、需克服全身體循環的高阻力，因此左心室的心肌層最厚（約為右心室的 3 倍）。</t>
         </is>
       </c>
-      <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="3" t="inlineStr"/>
-      <c r="R48" s="3" t="inlineStr"/>
-      <c r="S48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>「心肌層最厚」：肌肉越厚，代表那個腔室工作量越大。</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>心房和心室，誰要把血打得比較遠？→ 左、右心室分別把血送到哪裡？→ 哪一個要克服全身體循環的高阻力？</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>送血到全身、工作量最大的是「左心室」，所以它的心肌層最厚。</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
+          <t>左心室最厚（約右心室 3 倍）＝要推動全身體循環。</t>
+        </is>
+      </c>
       <c r="T48" s="3" t="inlineStr"/>
       <c r="U48" s="3" t="inlineStr"/>
-      <c r="V48" s="3" t="inlineStr"/>
-      <c r="W48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
@@ -4331,14 +5286,38 @@
           <t>右房室瓣為三尖瓣（Tricuspid valve），其游離端經由腱索（Chordae tendineae）連接至心室壁的乳頭肌（Papillary muscle），防止瓣膜翻入心房。</t>
         </is>
       </c>
-      <c r="P49" s="3" t="inlineStr"/>
-      <c r="Q49" s="3" t="inlineStr"/>
-      <c r="R49" s="3" t="inlineStr"/>
-      <c r="S49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>「右心房與右心室之間」「防止倒翻」：先認瓣膜名稱，再找拉住它的構造。</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>右側房室瓣有幾片瓣葉、叫什麼名字？→ 瓣膜的游離端連著哪一種細繩狀構造？→ 這些細繩又固定在心室壁的哪種肌肉上？</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>右房室瓣是三尖瓣，靠腱索連到乳頭肌防止翻入心房，答案是「三尖瓣；腱索與乳頭肌」。</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>右三左二：右房室瓣＝三尖瓣；腱索＋乳頭肌＝拉住瓣膜不倒翻。</t>
+        </is>
+      </c>
       <c r="T49" s="3" t="inlineStr"/>
       <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="3" t="inlineStr"/>
-      <c r="W49" s="3" t="inlineStr"/>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
@@ -4409,14 +5388,38 @@
           <t>左冠狀動脈（LCA）分支出的前室間枝（Anterior interventricular branch，又稱左前降支 LAD）主要供應兩心室前壁與心室間隔。</t>
         </is>
       </c>
-      <c r="P50" s="3" t="inlineStr"/>
-      <c r="Q50" s="3" t="inlineStr"/>
-      <c r="R50" s="3" t="inlineStr"/>
-      <c r="S50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>「左心室前壁」「心室間隔前 2/3」：找走在心臟前面的那條冠狀動脈分枝。</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>供應前壁的血管，應該來自左冠狀動脈還是右冠狀動脈？→ 左冠狀動脈的兩條分枝，哪一條沿前室間溝往下走？→ 它的另一個名字是什麼？</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>供應前壁與間隔前 2/3 的是「左冠狀動脈前室間枝（前降支）」。</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>前室間枝（前降支，LAD）＝左冠狀動脈分枝，管兩心室前壁與間隔前 2/3。</t>
+        </is>
+      </c>
       <c r="T50" s="3" t="inlineStr"/>
       <c r="U50" s="3" t="inlineStr"/>
-      <c r="V50" s="3" t="inlineStr"/>
-      <c r="W50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
@@ -4487,14 +5490,38 @@
           <t>竇房結（Sinoatrial node; SA node）具有最高自發去極化速率（70~80次/分），為心臟正常的節律點。</t>
         </is>
       </c>
-      <c r="P51" s="3" t="inlineStr"/>
-      <c r="Q51" s="3" t="inlineStr"/>
-      <c r="R51" s="3" t="inlineStr"/>
-      <c r="S51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>「節律點」「右心房壁」：找自發去極化最快的那個構造。</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>傳導系統中誰的自發去極化速率最高？→ 它每分鐘約 70～80 次，位在右心房壁上嗎？→ 心跳由誰最先發出訊號？</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>自發去極化最快、位於右心房壁的是「竇房結（SA node）」，它是正常節律點。</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>竇房結（SA node）＝節律點（70～80 次／分），心跳從這裡開始。</t>
+        </is>
+      </c>
       <c r="T51" s="3" t="inlineStr"/>
       <c r="U51" s="3" t="inlineStr"/>
-      <c r="V51" s="3" t="inlineStr"/>
-      <c r="W51" s="3" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
@@ -4565,14 +5592,38 @@
           <t>左冠狀動脈的前室間枝走在前室間溝，供應兩心室前壁與心室間隔前 2/3；心大靜脈與它伴行。</t>
         </is>
       </c>
-      <c r="P52" s="3" t="inlineStr"/>
-      <c r="Q52" s="3" t="inlineStr"/>
-      <c r="R52" s="3" t="inlineStr"/>
-      <c r="S52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>「前面」「左右心室之間的溝」「供應左心室前壁」：溝的位置決定血管名稱。</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>左右心室在前面交界的那條溝叫什麼？→ 走在這條溝裡的動脈，是哪一條冠狀動脈的分枝？→ 它還有什麼別名？</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>走在前室間溝、供應左心室前壁的是「左冠狀動脈前室間枝（前降支）」。</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>前室間溝＝前室間枝（前降支）＋心大靜脈伴行。</t>
+        </is>
+      </c>
       <c r="T52" s="3" t="inlineStr"/>
       <c r="U52" s="3" t="inlineStr"/>
-      <c r="V52" s="3" t="inlineStr"/>
-      <c r="W52" s="3" t="inlineStr"/>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
@@ -4643,14 +5694,38 @@
           <t>二尖瓣位於左心房與左心室之間；心室收縮時關閉，並由腱索與乳頭肌拉住，防止血液倒流回左心房。</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr"/>
-      <c r="Q53" s="3" t="inlineStr"/>
-      <c r="R53" s="3" t="inlineStr"/>
-      <c r="S53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>「左心室」「倒流回左心房」：找左心房與左心室之間的那扇門。</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>左心房和左心室之間的瓣膜，是房室瓣還是半月瓣？→ 左側房室瓣有幾片瓣葉？→ 心室收縮時它要打開還是關緊？</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>防止血液從左心室倒流回左心房的是「二尖瓣（僧帽瓣）」。</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>左房室＝二尖瓣（僧帽瓣）；右房室＝三尖瓣；心室收縮時兩者都關。</t>
+        </is>
+      </c>
       <c r="T53" s="3" t="inlineStr"/>
       <c r="U53" s="3" t="inlineStr"/>
-      <c r="V53" s="3" t="inlineStr"/>
-      <c r="W53" s="3" t="inlineStr"/>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
@@ -4721,14 +5796,38 @@
           <t>漿膜心包的壁層與臟層之間是心包腔，內含少量心包液，能潤滑膜面、減少心臟跳動時的摩擦。</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr"/>
-      <c r="Q54" s="3" t="inlineStr"/>
-      <c r="R54" s="3" t="inlineStr"/>
-      <c r="S54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>「不會和周圍組織摩擦」：想想哪個構造裡有液體可以潤滑。</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>心臟外面包著哪一層膜？→ 這層膜的壁層和臟層之間有什麼空間？→ 空間裡的液體能發揮什麼作用？</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>壁層與臟層間的心包腔含少量心包液，靠的是「心包腔內的心包液潤滑」。</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>心包液＝心臟的潤滑油，減少跳動時的摩擦。</t>
+        </is>
+      </c>
       <c r="T54" s="3" t="inlineStr"/>
       <c r="U54" s="3" t="inlineStr"/>
-      <c r="V54" s="3" t="inlineStr"/>
-      <c r="W54" s="3" t="inlineStr"/>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
@@ -4799,14 +5898,38 @@
           <t>衝動經過房室結時傳導最慢，產生約 0.1 秒的延遲，讓心房先把血液擠進心室，心室再收縮。</t>
         </is>
       </c>
-      <c r="P55" s="3" t="inlineStr"/>
-      <c r="Q55" s="3" t="inlineStr"/>
-      <c r="R55" s="3" t="inlineStr"/>
-      <c r="S55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>「心室要稍等一下」「延遲」：找傳導最慢的那一站。</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>電衝動從竇房結出發後，下一站是哪裡？→ 傳導系統中哪一站的速度最慢？→ 這段約 0.1 秒的延遲有什麼好處？</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>衝動在「房室結（AV node）」傳得最慢，延遲約 0.1 秒，讓心房先把血擠進心室。</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>房室結＝傳導慢車站（約 0.1 秒），讓心房先收縮、心室後收縮。</t>
+        </is>
+      </c>
       <c r="T55" s="3" t="inlineStr"/>
       <c r="U55" s="3" t="inlineStr"/>
-      <c r="V55" s="3" t="inlineStr"/>
-      <c r="W55" s="3" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4877,14 +6000,38 @@
           <t>左心室負責把血液打入主動脈送到全身（體循環），需克服的阻力最大，所以心肌層最厚。</t>
         </is>
       </c>
-      <c r="P56" s="3" t="inlineStr"/>
-      <c r="Q56" s="3" t="inlineStr"/>
-      <c r="R56" s="3" t="inlineStr"/>
-      <c r="S56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>「左心室」「3 倍厚」「原因」：肌肉厚度和工作量有關。</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>左心室把血打到哪一條大動脈？→ 那條血管把血送往全身還是只到肺？→ 送全身要克服的阻力大還是小？</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>左心室負責體循環，要克服較大阻力，所以是「左心室要把血液打到全身，阻力較大」。</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>左心室送全身（阻力大）→ 肌肉最厚；右心室只送到肺 → 較薄。</t>
+        </is>
+      </c>
       <c r="T56" s="3" t="inlineStr"/>
       <c r="U56" s="3" t="inlineStr"/>
-      <c r="V56" s="3" t="inlineStr"/>
-      <c r="W56" s="3" t="inlineStr"/>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>心臟構造與解剖生理圖卡</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+        </is>
+      </c>
       <c r="X56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4955,14 +6102,38 @@
           <t>左、右冠狀動脈環繞心臟表面，供應心肌養分與氧氣。</t>
         </is>
       </c>
-      <c r="P57" s="3" t="inlineStr"/>
-      <c r="Q57" s="3" t="inlineStr"/>
-      <c r="R57" s="3" t="inlineStr"/>
-      <c r="S57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>「心臟肌肉自己」「養分與氧氣」：心腔裡流過的血不直接養心肌，要找專屬血管。</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>心肌需要自己的血管供應氧氣嗎？→ 環繞在心臟表面、像皇冠一樣的動脈叫什麼？→ 它分成左、右兩條嗎？</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>環繞心臟表面、供應心肌養分與氧氣的是「冠狀動脈」。</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>冠狀動脈（左、右）＝心肌自己的供血管。</t>
+        </is>
+      </c>
       <c r="T57" s="3" t="inlineStr"/>
       <c r="U57" s="3" t="inlineStr"/>
-      <c r="V57" s="3" t="inlineStr"/>
-      <c r="W57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
@@ -5033,14 +6204,38 @@
           <t>冠狀動脈開口位於升主動脈基部、主動脈瓣上方的主動脈竇。</t>
         </is>
       </c>
-      <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="3" t="inlineStr"/>
-      <c r="R58" s="3" t="inlineStr"/>
-      <c r="S58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>「冠狀動脈」「從哪裡發出」：找主動脈最起始的那一段。</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>血液離開左心室後，最先進入的是哪一段主動脈？→ 主動脈瓣上方有個膨大的主動脈竇嗎？→ 冠狀動脈的開口就在這裡的哪個位置？</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>冠狀動脈開口在主動脈瓣上方的主動脈竇，也就是「升主動脈基部（主動脈瓣上方）」。</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>冠狀動脈起點＝升主動脈基部（主動脈瓣上方、主動脈竇）。</t>
+        </is>
+      </c>
       <c r="T58" s="3" t="inlineStr"/>
       <c r="U58" s="3" t="inlineStr"/>
-      <c r="V58" s="3" t="inlineStr"/>
-      <c r="W58" s="3" t="inlineStr"/>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
@@ -5111,14 +6306,38 @@
           <t>左冠狀動脈分為前室間枝（走前室間溝）與迴旋枝（沿冠狀溝繞到後方）。</t>
         </is>
       </c>
-      <c r="P59" s="3" t="inlineStr"/>
-      <c r="Q59" s="3" t="inlineStr"/>
-      <c r="R59" s="3" t="inlineStr"/>
-      <c r="S59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>「左冠狀動脈」「兩條主要分支」：一條往前走、一條往後繞。</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>左冠狀動脈哪一條分支沿前室間溝往下走？→ 另一條沿冠狀溝繞到心臟後方的叫什麼？→ 兩條合起來是哪一組？</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>左冠狀動脈分為往前的前室間枝與往後繞的迴旋枝，答案是「前室間枝與迴旋枝」。</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>左冠＝前室間枝（往前下）＋迴旋枝（繞後）；右冠＝邊緣枝＋後室間枝。</t>
+        </is>
+      </c>
       <c r="T59" s="3" t="inlineStr"/>
       <c r="U59" s="3" t="inlineStr"/>
-      <c r="V59" s="3" t="inlineStr"/>
-      <c r="W59" s="3" t="inlineStr"/>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
@@ -5189,14 +6408,38 @@
           <t>右冠狀動脈發出邊緣枝（供應右心室）與後室間枝（供應兩心室後壁）。</t>
         </is>
       </c>
-      <c r="P60" s="3" t="inlineStr"/>
-      <c r="Q60" s="3" t="inlineStr"/>
-      <c r="R60" s="3" t="inlineStr"/>
-      <c r="S60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>「右冠狀動脈」「兩條主要分支」：一條供應右心室邊緣，一條走後室間溝。</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>供應右心室的那條分支叫什麼？→ 走在心臟後面、兩心室之間溝裡的分支叫什麼？→ 前室間枝、迴旋枝是左邊還是右邊的？</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>右冠狀動脈發出供應右心室的邊緣枝與後室間枝，答案是「邊緣枝與後室間枝」。</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>右冠＝邊緣枝（右心室）＋後室間枝（兩心室後壁）。</t>
+        </is>
+      </c>
       <c r="T60" s="3" t="inlineStr"/>
       <c r="U60" s="3" t="inlineStr"/>
-      <c r="V60" s="3" t="inlineStr"/>
-      <c r="W60" s="3" t="inlineStr"/>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
@@ -5267,14 +6510,38 @@
           <t>心大靜脈、心中靜脈匯入冠狀靜脈竇，再注入右心房。</t>
         </is>
       </c>
-      <c r="P61" s="3" t="inlineStr"/>
-      <c r="Q61" s="3" t="inlineStr"/>
-      <c r="R61" s="3" t="inlineStr"/>
-      <c r="S61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>「缺氧血」「先匯集」「再流回右心房」：找心臟靜脈的集合處。</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>心大靜脈、心中靜脈收集的是心肌用過的血嗎？→ 它們先匯入哪一條大的靜脈通道？→ 這條通道再把血注入哪一個腔室？</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>心大、心中靜脈先匯入「冠狀靜脈竇」，再注入右心房。</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>心大靜脈＋心中靜脈 → 冠狀靜脈竇 → 右心房。</t>
+        </is>
+      </c>
       <c r="T61" s="3" t="inlineStr"/>
       <c r="U61" s="3" t="inlineStr"/>
-      <c r="V61" s="3" t="inlineStr"/>
-      <c r="W61" s="3" t="inlineStr"/>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
@@ -5345,14 +6612,38 @@
           <t>收縮期心肌擠壓血管；舒張期心肌放鬆，血液才大量流進冠狀動脈。</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="3" t="inlineStr"/>
-      <c r="R62" s="3" t="inlineStr"/>
-      <c r="S62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>「左心室的心肌」「什麼時候得到血流」：想想收縮時心肌對血管做了什麼。</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>心室收縮時，心肌會對穿行其中的血管造成什麼影響？→ 血管被擠壓時，血流得進去嗎？→ 那心肌什麼時候放鬆、血管才張開？</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>收縮時血管被擠壓，放鬆時血才大量流入，所以是「心室舒張期」。</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>冠狀血流：收縮期被擠（少）；舒張期放鬆（多）。</t>
+        </is>
+      </c>
       <c r="T62" s="3" t="inlineStr"/>
       <c r="U62" s="3" t="inlineStr"/>
-      <c r="V62" s="3" t="inlineStr"/>
-      <c r="W62" s="3" t="inlineStr"/>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
@@ -5423,14 +6714,38 @@
           <t>心室收縮時心肌擠壓穿行其中的血管，血流減少；舒張時血管張開，血流才充足。</t>
         </is>
       </c>
-      <c r="P63" s="3" t="inlineStr"/>
-      <c r="Q63" s="3" t="inlineStr"/>
-      <c r="R63" s="3" t="inlineStr"/>
-      <c r="S63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>「捏住水管」「放開後才流得動」：把手換成心肌，水管換成冠狀動脈。</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>比喻中捏住水管的手，對應心臟的什麼動作？→ 心室收縮時，穿行在心肌裡的血管會怎樣？→ 什麼時候血管張開、血流才順？</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>收縮像捏水管、舒張像放手，最像「心室收縮時心肌擠壓血管，舒張時血流才順暢」。</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>收縮＝捏住水管（血少）；舒張＝放開水管（血多）。</t>
+        </is>
+      </c>
       <c r="T63" s="3" t="inlineStr"/>
       <c r="U63" s="3" t="inlineStr"/>
-      <c r="V63" s="3" t="inlineStr"/>
-      <c r="W63" s="3" t="inlineStr"/>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
@@ -5501,14 +6816,38 @@
           <t>冠狀血流主要發生在舒張期；心跳變快時舒張期縮短最多，心肌灌流時間也跟著變少。</t>
         </is>
       </c>
-      <c r="P64" s="3" t="inlineStr"/>
-      <c r="Q64" s="3" t="inlineStr"/>
-      <c r="R64" s="3" t="inlineStr"/>
-      <c r="S64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>「心跳變得很快」「得到血液的時間」：冠狀血流主要發生在哪一期？</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>冠狀血流主要在收縮期還是舒張期？→ 心跳變快時，收縮期和舒張期哪一個縮短最多？→ 那心肌灌流的時間會變多還是變少？</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>心跳加快時舒張期縮短最多，所以「舒張期變短，灌流時間減少」。</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>心跳快 → 舒張期縮最多 → 冠狀灌流時間變少。</t>
+        </is>
+      </c>
       <c r="T64" s="3" t="inlineStr"/>
       <c r="U64" s="3" t="inlineStr"/>
-      <c r="V64" s="3" t="inlineStr"/>
-      <c r="W64" s="3" t="inlineStr"/>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
@@ -5579,14 +6918,38 @@
           <t>前室間枝是左冠狀動脈的分支，走在前室間溝，供應兩心室前壁與心室間隔前 2/3。</t>
         </is>
       </c>
-      <c r="P65" s="3" t="inlineStr"/>
-      <c r="Q65" s="3" t="inlineStr"/>
-      <c r="R65" s="3" t="inlineStr"/>
-      <c r="S65" s="3" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>「前面」「左右心室之間的溝」「動脈」：溝的名字就藏著血管名字。</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>左右心室在前面交界的溝叫什麼？→ 走在這條溝裡的是動脈還是靜脈？→ 這條動脈叫前室間枝還是後室間枝？</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>走在前室間溝裡的動脈是左冠狀動脈的分支「前室間枝」。</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>前室間溝＝前室間枝；後室間溝＝後室間枝（名稱跟著溝走）。</t>
+        </is>
+      </c>
       <c r="T65" s="3" t="inlineStr"/>
       <c r="U65" s="3" t="inlineStr"/>
-      <c r="V65" s="3" t="inlineStr"/>
-      <c r="W65" s="3" t="inlineStr"/>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
@@ -5657,14 +7020,38 @@
           <t>心大靜脈與前室間枝伴行於前室間溝；心中靜脈與後室間枝伴行於後室間溝。</t>
         </is>
       </c>
-      <c r="P66" s="3" t="inlineStr"/>
-      <c r="Q66" s="3" t="inlineStr"/>
-      <c r="R66" s="3" t="inlineStr"/>
-      <c r="S66" s="3" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>「與前室間枝並行」「前室間溝」「靜脈」：動脈和靜脈在同一條溝裡伴行。</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>前室間溝裡除了前室間枝，還有哪一條靜脈？→ 心中靜脈伴行的是前室間枝還是後室間枝？→ 所以走前面的靜脈是哪一條？</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>與前室間枝一起走在前室間溝的靜脈是「心大靜脈」。</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
+          <t>前溝：前室間枝＋心大靜脈；後溝：後室間枝＋心中靜脈。</t>
+        </is>
+      </c>
       <c r="T66" s="3" t="inlineStr"/>
       <c r="U66" s="3" t="inlineStr"/>
-      <c r="V66" s="3" t="inlineStr"/>
-      <c r="W66" s="3" t="inlineStr"/>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
@@ -5735,14 +7122,38 @@
           <t>心肌安靜時已抓取約 70% 的氧，很難再多抓；需氧增加時主要靠冠狀動脈擴張、增加血流。</t>
         </is>
       </c>
-      <c r="P67" s="3" t="inlineStr"/>
-      <c r="Q67" s="3" t="inlineStr"/>
-      <c r="R67" s="3" t="inlineStr"/>
-      <c r="S67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>「需要更多氧氣」「主要靠什麼方法」：先想心肌能不能再多抓氧。</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>心肌安靜時已經抓取血液中約多少的氧？→ 還能從血中再多抓很多嗎？→ 抓不了更多，就只能讓流過的血量怎麼變？</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>心肌已抓約 70% 的氧、難再多抓，所以靠「冠狀動脈擴張，增加血流量」。</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>心肌取氧已約 70% → 需氧增加時靠冠狀動脈擴張、增加血流。</t>
+        </is>
+      </c>
       <c r="T67" s="3" t="inlineStr"/>
       <c r="U67" s="3" t="inlineStr"/>
-      <c r="V67" s="3" t="inlineStr"/>
-      <c r="W67" s="3" t="inlineStr"/>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>心臟血液供應（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/coronary-circulation-v1/index.html</t>
+        </is>
+      </c>
       <c r="X67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
@@ -5813,14 +7224,38 @@
           <t>竇房結（SA node）位於右心房壁近上腔靜脈開口處，具有最高的自發去極化頻率（每分鐘約 70~80 次），主導正常心跳節律，故稱為節律點。</t>
         </is>
       </c>
-      <c r="P68" s="3" t="inlineStr"/>
-      <c r="Q68" s="3" t="inlineStr"/>
-      <c r="R68" s="3" t="inlineStr"/>
-      <c r="S68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>「節律點（Pacemaker）」「右心房…近上腔靜脈開口」：要找心跳的起點。</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>心跳的電訊號由誰最先自己發出？→ 傳導系統中哪個構造自發去極化的頻率最高？→ 位在右心房、靠近上腔靜脈開口的那個「結」叫什麼？</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>位在右心房近上腔靜脈開口、頻率最高而主導心跳的是「竇房結（SA node）」。</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>竇房結＝節律點（右心房、近上腔靜脈）；頻率最高的帶頭跑。</t>
+        </is>
+      </c>
       <c r="T68" s="3" t="inlineStr"/>
       <c r="U68" s="3" t="inlineStr"/>
-      <c r="V68" s="3" t="inlineStr"/>
-      <c r="W68" s="3" t="inlineStr"/>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
@@ -5891,14 +7326,38 @@
           <t>正常人竇房結每分鐘自發興奮約 70~80 次，此為正常竇性節律（Sinus rhythm）的基本頻率。</t>
         </is>
       </c>
-      <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr"/>
-      <c r="R69" s="3" t="inlineStr"/>
-      <c r="S69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>「竇房結」「安靜休息」「每分鐘」：問的是正常竇性節律的頻率。</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>竇房結是節律點，它的頻率就決定了什麼？→ 安靜時正常人一分鐘大約心跳幾下？→ 哪個範圍最接近安靜時的正常心跳？</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>竇房結在安靜時每分鐘自發興奮約「70~80 次」，就是正常竇性節律。</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>竇房結＝節律點＝每分鐘約 70~80 次（正常竇性節律）。</t>
+        </is>
+      </c>
       <c r="T69" s="3" t="inlineStr"/>
       <c r="U69" s="3" t="inlineStr"/>
-      <c r="V69" s="3" t="inlineStr"/>
-      <c r="W69" s="3" t="inlineStr"/>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
@@ -5969,14 +7428,38 @@
           <t>衝動行經房室結（AV node）時傳導速度最慢（產生約 0.1 秒以上的生理延遲），能確保心房完全收縮擠血入心室後，心室才開始收縮。</t>
         </is>
       </c>
-      <c r="P70" s="3" t="inlineStr"/>
-      <c r="Q70" s="3" t="inlineStr"/>
-      <c r="R70" s="3" t="inlineStr"/>
-      <c r="S70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>「最慢」「生理延遲的功能」：要同時答出位置和用途。</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>電衝動從心房要進入心室，中間要經過哪個關卡？→ 在這個關卡慢下來約 0.1 秒以上，心房可以趁機做什麼？→ 這樣心室開始收縮前會先裝滿血嗎？</t>
+        </is>
+      </c>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>房室結傳導最慢，延遲讓心房先把血擠進心室，所以選「房室結（AV node）；使心房有時間將血液擠入心室」。</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t>房室結＝最慢的關卡；延遲 → 心房先擠血 → 心室再收縮。</t>
+        </is>
+      </c>
       <c r="T70" s="3" t="inlineStr"/>
       <c r="U70" s="3" t="inlineStr"/>
-      <c r="V70" s="3" t="inlineStr"/>
-      <c r="W70" s="3" t="inlineStr"/>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
@@ -6047,14 +7530,38 @@
           <t>由房室結發出的傳導纖維稱為房室束（Atrioventricular bundle），又稱希氏束（Bundle of His），是衝動由心房傳入心室間隔的通道。</t>
         </is>
       </c>
-      <c r="P71" s="3" t="inlineStr"/>
-      <c r="Q71" s="3" t="inlineStr"/>
-      <c r="R71" s="3" t="inlineStr"/>
-      <c r="S71" s="3" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>「穿過絕緣纖維環」「由房室結傳向心室間隔」：找房室結之後的那一段。</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>心房與心室之間有絕緣纖維環，電訊號要靠什麼通道過去？→ 從房室結發出、往心室間隔頂端走的纖維束叫什麼？→ 這條纖維束還有哪個別名？</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>由房室結發出、穿過絕緣環通往心室間隔的是「房室束（希氏束 / Bundle of His）」。</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>房室結 → 房室束（希氏束）→ 心室間隔；衝動由心房進入心室的通道。</t>
+        </is>
+      </c>
       <c r="T71" s="3" t="inlineStr"/>
       <c r="U71" s="3" t="inlineStr"/>
-      <c r="V71" s="3" t="inlineStr"/>
-      <c r="W71" s="3" t="inlineStr"/>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
@@ -6125,14 +7632,38 @@
           <t>浦金埃氏纖維（傳導性肌纖維）直徑粗，電衝動傳導速度居全系統之冠（最快），能使衝動快速傳遍整個心室。</t>
         </is>
       </c>
-      <c r="P72" s="3" t="inlineStr"/>
-      <c r="Q72" s="3" t="inlineStr"/>
-      <c r="R72" s="3" t="inlineStr"/>
-      <c r="S72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>「傳導速度最快」：找直徑粗、負責把衝動傳遍心室的纖維。</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>傳導系統裡哪裡最慢？（先排除它）→ 哪一種纖維直徑最粗、傳得最快？→ 誰負責讓衝動一下子傳遍整個心室？</t>
+        </is>
+      </c>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>直徑粗、能讓衝動快速傳遍心室的是「浦金埃氏纖維（Purkinje fibers）」。</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t>最慢＝房室結；最快＝浦金埃氏纖維（直徑粗，快速傳遍心室）。</t>
+        </is>
+      </c>
       <c r="T72" s="3" t="inlineStr"/>
       <c r="U72" s="3" t="inlineStr"/>
-      <c r="V72" s="3" t="inlineStr"/>
-      <c r="W72" s="3" t="inlineStr"/>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
@@ -6203,14 +7734,38 @@
           <t>心臟肌肉具自律性，不需神經直接刺激即可自發收縮；自主神經系統僅負責調節心跳速率與收縮強度，不直接啟動收縮。</t>
         </is>
       </c>
-      <c r="P73" s="3" t="inlineStr"/>
-      <c r="Q73" s="3" t="inlineStr"/>
-      <c r="R73" s="3" t="inlineStr"/>
-      <c r="S73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>「自律性」「自主神經」：分清誰負責啟動、誰負責調節。</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>心肌有自律性，代表不需要神經刺激也能怎樣？→ 那自主神經在心臟扮演的是「啟動」還是「調節」？→ 它調節的是哪兩件事？</t>
+        </is>
+      </c>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>心臟自己會收縮，自主神經只做調整，所以「自主神經只會調節心跳速率與收縮力，不會引發心臟收縮」。</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>心臟自律性＝自己會跳；自主神經＝只調快慢與力量，不負責啟動。</t>
+        </is>
+      </c>
       <c r="T73" s="3" t="inlineStr"/>
       <c r="U73" s="3" t="inlineStr"/>
-      <c r="V73" s="3" t="inlineStr"/>
-      <c r="W73" s="3" t="inlineStr"/>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
@@ -6281,14 +7836,38 @@
           <t>交感神經末梢釋放正腎上腺素（Norepinephrine），作用於心臟傳導系統與心肌，使心跳速率及收縮強度增加以因應運動需求。</t>
         </is>
       </c>
-      <c r="P74" s="3" t="inlineStr"/>
-      <c r="Q74" s="3" t="inlineStr"/>
-      <c r="R74" s="3" t="inlineStr"/>
-      <c r="S74" s="3" t="inlineStr"/>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>「交感神經」「神經末梢釋放」「增加心跳」：找交感神經的化學傳遞物質。</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>長跑時是哪一種神經被啟動來加快心跳？→ 交感神經末梢釋放的物質是什麼？→ 它讓心跳速率和收縮強度如何改變？</t>
+        </is>
+      </c>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>交感神經末梢釋放「正腎上腺素（Norepinephrine）」，使心跳變快、收縮變強。</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>交感＝正腎上腺素 → 心跳快、力量強；副交感＝乙醯膽鹼 → 心跳慢。</t>
+        </is>
+      </c>
       <c r="T74" s="3" t="inlineStr"/>
       <c r="U74" s="3" t="inlineStr"/>
-      <c r="V74" s="3" t="inlineStr"/>
-      <c r="W74" s="3" t="inlineStr"/>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
@@ -6359,14 +7938,38 @@
           <t>情緒緊張、憤怒或生理緊迫會刺激延腦心跳加速中樞，使交感神經興奮並釋放腎上腺素/正腎上腺素，增加竇房結放電頻率使心跳加快。</t>
         </is>
       </c>
-      <c r="P75" s="3" t="inlineStr"/>
-      <c r="Q75" s="3" t="inlineStr"/>
-      <c r="R75" s="3" t="inlineStr"/>
-      <c r="S75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>「極度緊張」「心跳很快」：緊張時是哪一套神經在作用。</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>緊張、憤怒時，延腦的心跳加速中樞會被刺激嗎？→ 這個中樞是透過交感還是副交感神經作用？→ 這套神經讓竇房結放電變快還是變慢？</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>緊張時交感神經興奮，使竇房結放電加快，所以是「交感神經系統」。</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>緊張、運動＝交感興奮 → 竇房結放電快 → 心跳加快。</t>
+        </is>
+      </c>
       <c r="T75" s="3" t="inlineStr"/>
       <c r="U75" s="3" t="inlineStr"/>
-      <c r="V75" s="3" t="inlineStr"/>
-      <c r="W75" s="3" t="inlineStr"/>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
@@ -6437,14 +8040,38 @@
           <t>體溫升高（如發燒或激烈運動）能使竇房結與房室結細胞自發產生動作電位的速率加快，進而使心跳速率上升。</t>
         </is>
       </c>
-      <c r="P76" s="3" t="inlineStr"/>
-      <c r="Q76" s="3" t="inlineStr"/>
-      <c r="R76" s="3" t="inlineStr"/>
-      <c r="S76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>「體溫升高」「心跳變快」：想體溫對節律細胞本身的影響。</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>心跳速率是由哪些節律細胞發出衝動決定的？→ 體溫升高時，這些細胞自發產生動作電位的速率會怎麼變？→ 發出衝動變快，心跳會跟著怎樣？</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>體溫升高使竇房結與房室結放電變快，所以「體溫升高會直接刺激竇房結與房室結，使其發出衝動的速率加快」。</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>體溫↑ → 竇房結、房室結放電↑ → 心跳↑。</t>
+        </is>
+      </c>
       <c r="T76" s="3" t="inlineStr"/>
       <c r="U76" s="3" t="inlineStr"/>
-      <c r="V76" s="3" t="inlineStr"/>
-      <c r="W76" s="3" t="inlineStr"/>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
@@ -6515,14 +8142,38 @@
           <t>副交感神經（迷走神經）末梢釋放乙醯膽鹼（Acetylcholine），能降低竇房結與房室結的興奮性，使心跳速率減慢、心跳平緩。</t>
         </is>
       </c>
-      <c r="P77" s="3" t="inlineStr"/>
-      <c r="Q77" s="3" t="inlineStr"/>
-      <c r="R77" s="3" t="inlineStr"/>
-      <c r="S77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>「迷走神經（副交感神經）」「乙醯膽鹼」：副交感讓心臟放慢。</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>靜坐、入睡時是交感還是副交感較活躍？→ 乙醯膽鹼讓竇房結與房室結的興奮性升高還是降低？→ 興奮性降低，心跳速率與收縮強度會怎樣？</t>
+        </is>
+      </c>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>乙醯膽鹼降低節律點的興奮性，所以「使心跳速率減慢，收縮強度減弱」。</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>副交感（迷走神經）＝乙醯膽鹼 → 心跳慢、收縮弱；休息時的煞車。</t>
+        </is>
+      </c>
       <c r="T77" s="3" t="inlineStr"/>
       <c r="U77" s="3" t="inlineStr"/>
-      <c r="V77" s="3" t="inlineStr"/>
-      <c r="W77" s="3" t="inlineStr"/>
+      <c r="V77" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W77" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
@@ -6593,14 +8244,38 @@
           <t>節律細胞（如竇房結）具有「自發性（Automaticity）」，在沒有外來神經刺激下，細胞膜能自動且有節律地去極化產生動作電位，維持離體心臟跳動。</t>
         </is>
       </c>
-      <c r="P78" s="3" t="inlineStr"/>
-      <c r="Q78" s="3" t="inlineStr"/>
-      <c r="R78" s="3" t="inlineStr"/>
-      <c r="S78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>「離體蛙心」「沒有任何神經連接」「仍能節律跳動」：心臟能自己跳的特性。</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>沒有神經刺激，心臟的電訊號從哪裡來？→ 竇房結細胞膜能不能自己有節律地去極化？→ 這種「自己發動」的特性叫什麼？</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>不靠神經也能自己有節律地產生動作電位，這就是「自發性/自律性（Automaticity）」。</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="inlineStr">
+        <is>
+          <t>離體心臟還會跳＝自律性；節律細胞自己去極化，不需神經。</t>
+        </is>
+      </c>
       <c r="T78" s="3" t="inlineStr"/>
       <c r="U78" s="3" t="inlineStr"/>
-      <c r="V78" s="3" t="inlineStr"/>
-      <c r="W78" s="3" t="inlineStr"/>
+      <c r="V78" s="3" t="inlineStr">
+        <is>
+          <t>心臟的傳導系統（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-conduction-v2/index.html</t>
+        </is>
+      </c>
       <c r="X78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
@@ -6671,14 +8346,38 @@
           <t>房室瓣是二尖瓣（左）與三尖瓣（右）；主動脈瓣與肺動脈瓣則合稱半月瓣。</t>
         </is>
       </c>
-      <c r="P79" s="3" t="inlineStr"/>
-      <c r="Q79" s="3" t="inlineStr"/>
-      <c r="R79" s="3" t="inlineStr"/>
-      <c r="S79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>「房室瓣」三個字：房＝心房、室＝心室，指的是心房與心室之間的門。</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>房室瓣位在心臟的哪兩個腔室之間？→ 左邊、右邊各有一個，名字分別是什麼？→ 主動脈瓣、肺動脈瓣位在心室和哪裡之間？</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>心房與心室之間的兩個瓣膜，就是「二尖瓣與三尖瓣」。</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr">
+        <is>
+          <t>房室瓣＝二尖瓣（左）＋三尖瓣（右）；半月瓣＝主動脈瓣＋肺動脈瓣。</t>
+        </is>
+      </c>
       <c r="T79" s="3" t="inlineStr"/>
       <c r="U79" s="3" t="inlineStr"/>
-      <c r="V79" s="3" t="inlineStr"/>
-      <c r="W79" s="3" t="inlineStr"/>
+      <c r="V79" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W79" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
@@ -6749,14 +8448,38 @@
           <t>約 70~80% 的血液在心房收縮前就被動流入心室；心房收縮只補入最後約 20~30%。</t>
         </is>
       </c>
-      <c r="P80" s="3" t="inlineStr"/>
-      <c r="Q80" s="3" t="inlineStr"/>
-      <c r="R80" s="3" t="inlineStr"/>
-      <c r="S80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>「大部分」「怎麼進入心室」：想想被動充血與心房收縮各占多少。</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>心房收縮前，房室瓣是開還是關？→ 這時血液靠什麼流進心室？→ 心房收縮只補了多少？</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>大部分血液在心房收縮前順著壓力差自己流入，所以選「心房還沒收縮前，就順著壓力差自己流入」。</t>
+        </is>
+      </c>
+      <c r="S80" s="3" t="inlineStr">
+        <is>
+          <t>心室充血：約 70~80% 被動流入，心房收縮只補最後約 20~30%。</t>
+        </is>
+      </c>
       <c r="T80" s="3" t="inlineStr"/>
       <c r="U80" s="3" t="inlineStr"/>
-      <c r="V80" s="3" t="inlineStr"/>
-      <c r="W80" s="3" t="inlineStr"/>
+      <c r="V80" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
@@ -6827,14 +8550,38 @@
           <t>心室開始收縮、壓力高過心房時，房室瓣關閉，發出低沉的第一心音。</t>
         </is>
       </c>
-      <c r="P81" s="3" t="inlineStr"/>
-      <c r="Q81" s="3" t="inlineStr"/>
-      <c r="R81" s="3" t="inlineStr"/>
-      <c r="S81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>「第一心音」「關閉」：心音是瓣膜關上的聲音。</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>S1 出現在心室收縮的開頭還是結尾？→ 心室一收縮，哪一組瓣膜會被壓力推上？→ 那是心房與心室之間的門，還是動脈端的門？</t>
+        </is>
+      </c>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>心室開始收縮時關上的是房室瓣，所以 S1 是「房室瓣關閉」的聲音。</t>
+        </is>
+      </c>
+      <c r="S81" s="3" t="inlineStr">
+        <is>
+          <t>S1＝房室瓣關（收縮開始）；S2＝半月瓣關（舒張開始）。</t>
+        </is>
+      </c>
       <c r="T81" s="3" t="inlineStr"/>
       <c r="U81" s="3" t="inlineStr"/>
-      <c r="V81" s="3" t="inlineStr"/>
-      <c r="W81" s="3" t="inlineStr"/>
+      <c r="V81" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W81" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
@@ -6905,14 +8652,38 @@
           <t>心室開始舒張、壓力低於動脈時，半月瓣關閉，發出較清脆的第二心音。</t>
         </is>
       </c>
-      <c r="P82" s="3" t="inlineStr"/>
-      <c r="Q82" s="3" t="inlineStr"/>
-      <c r="R82" s="3" t="inlineStr"/>
-      <c r="S82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>「第二心音」「關閉」：想想心室射完血、開始放鬆的那一刻。</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>心室開始舒張時，心室壓力會比動脈高還是低？→ 動脈裡的血想往回流時，哪一組瓣膜會關上？→ 這組瓣膜的名稱是什麼？</t>
+        </is>
+      </c>
+      <c r="R82" s="3" t="inlineStr">
+        <is>
+          <t>心室舒張、壓力低於動脈時，半月瓣被推上，所以 S2 是「半月瓣關閉」。</t>
+        </is>
+      </c>
+      <c r="S82" s="3" t="inlineStr">
+        <is>
+          <t>S2＝半月瓣關閉，聲音清脆較短，代表心室舒張期開始。</t>
+        </is>
+      </c>
       <c r="T82" s="3" t="inlineStr"/>
       <c r="U82" s="3" t="inlineStr"/>
-      <c r="V82" s="3" t="inlineStr"/>
-      <c r="W82" s="3" t="inlineStr"/>
+      <c r="V82" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W82" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
@@ -6983,14 +8754,38 @@
           <t>這時房室瓣已關、半月瓣還沒開，血液進不來也出不去，心室容積不變、壓力快速上升。</t>
         </is>
       </c>
-      <c r="P83" s="3" t="inlineStr"/>
-      <c r="Q83" s="3" t="inlineStr"/>
-      <c r="R83" s="3" t="inlineStr"/>
-      <c r="S83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>「等容」：等＝不變，容＝心室的容積。</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>等容收縮期時，房室瓣是開是關？半月瓣呢？→ 四個瓣膜都關著，血能進出嗎？→ 心室裡的血量會不會改變？</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>四個瓣膜都關著、血進不來也出不去，所以「等容」是「四個瓣膜都關著，心室裡的血量不變」。</t>
+        </is>
+      </c>
+      <c r="S83" s="3" t="inlineStr">
+        <is>
+          <t>等容＝四門全關、容積不變；等容收縮時壓力上升，等容舒張時壓力下降。</t>
+        </is>
+      </c>
       <c r="T83" s="3" t="inlineStr"/>
       <c r="U83" s="3" t="inlineStr"/>
-      <c r="V83" s="3" t="inlineStr"/>
-      <c r="W83" s="3" t="inlineStr"/>
+      <c r="V83" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W83" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
@@ -7061,14 +8856,38 @@
           <t>心搏量是心室每次收縮射出的血量，安靜時約 70 ml。</t>
         </is>
       </c>
-      <c r="P84" s="3" t="inlineStr"/>
-      <c r="Q84" s="3" t="inlineStr"/>
-      <c r="R84" s="3" t="inlineStr"/>
-      <c r="S84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>「心搏量」：搏＝心臟跳一下。</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>心臟跳一下，心室做了什麼？→ 射出去的血是充滿時的總量，還是扣掉剩下的量？→ 每分鐘的總量叫什麼？</t>
+        </is>
+      </c>
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>心搏量是「心室每收縮一次射出的血量」，安靜時約 70 ml。</t>
+        </is>
+      </c>
+      <c r="S84" s="3" t="inlineStr">
+        <is>
+          <t>心搏量＝每跳一下射出的血（約 70 ml）；心輸出量＝心搏量 × 心率。</t>
+        </is>
+      </c>
       <c r="T84" s="3" t="inlineStr"/>
       <c r="U84" s="3" t="inlineStr"/>
-      <c r="V84" s="3" t="inlineStr"/>
-      <c r="W84" s="3" t="inlineStr"/>
+      <c r="V84" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W84" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
@@ -7139,14 +8958,38 @@
           <t>S1 是心室開始收縮、房室瓣關閉的聲音，標誌心室收縮期開始。</t>
         </is>
       </c>
-      <c r="P85" s="3" t="inlineStr"/>
-      <c r="Q85" s="3" t="inlineStr"/>
-      <c r="R85" s="3" t="inlineStr"/>
-      <c r="S85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>「第一聲」「噗」：先判斷這是 S1 還是 S2。</t>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>噗－通的第一聲是 S1 還是 S2？→ S1 是哪一組瓣膜關上？→ 房室瓣關上時，心室正要開始收縮還是舒張？</t>
+        </is>
+      </c>
+      <c r="R85" s="3" t="inlineStr">
+        <is>
+          <t>第一聲「噗」是 S1，房室瓣關閉，代表心室「開始收縮」。</t>
+        </is>
+      </c>
+      <c r="S85" s="3" t="inlineStr">
+        <is>
+          <t>噗（S1）→ 心室開始收縮；通（S2）→ 心室開始舒張。</t>
+        </is>
+      </c>
       <c r="T85" s="3" t="inlineStr"/>
       <c r="U85" s="3" t="inlineStr"/>
-      <c r="V85" s="3" t="inlineStr"/>
-      <c r="W85" s="3" t="inlineStr"/>
+      <c r="V85" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W85" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
@@ -7217,14 +9060,38 @@
           <t>心跳變快時，收縮時間只稍縮短，被壓縮最多的是舒張（充血）時間。</t>
         </is>
       </c>
-      <c r="P86" s="3" t="inlineStr"/>
-      <c r="Q86" s="3" t="inlineStr"/>
-      <c r="R86" s="3" t="inlineStr"/>
-      <c r="S86" s="3" t="inlineStr"/>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>「心跳加快」「縮短最多」：比較收縮期與舒張期誰比較能被壓縮。</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>心跳從 75 變 150，一次心跳的時間變長還是變短？→ 心室收縮所需的時間能縮短很多嗎？→ 那被擠壓掉的主要是哪一段？</t>
+        </is>
+      </c>
+      <c r="R86" s="3" t="inlineStr">
+        <is>
+          <t>收縮時間變化不大，被壓縮最多的是「心室舒張（充血）的時間」。</t>
+        </is>
+      </c>
+      <c r="S86" s="3" t="inlineStr">
+        <is>
+          <t>心跳越快，舒張期縮得最多，心室充血與冠狀灌流的時間都變少。</t>
+        </is>
+      </c>
       <c r="T86" s="3" t="inlineStr"/>
       <c r="U86" s="3" t="inlineStr"/>
-      <c r="V86" s="3" t="inlineStr"/>
-      <c r="W86" s="3" t="inlineStr"/>
+      <c r="V86" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W86" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
@@ -7295,14 +9162,38 @@
           <t>心搏量 = EDV − ESV = 130 − 60 = 70 ml。</t>
         </is>
       </c>
-      <c r="P87" s="3" t="inlineStr"/>
-      <c r="Q87" s="3" t="inlineStr"/>
-      <c r="R87" s="3" t="inlineStr"/>
-      <c r="S87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>「充滿時 130 ml」「剩 60 ml」「心搏量」：用減法。</t>
+        </is>
+      </c>
+      <c r="Q87" s="3" t="inlineStr">
+        <is>
+          <t>心室充滿時的血量叫什麼？→ 射完血剩下的量叫什麼？→ 真正射出去的量要怎麼算？</t>
+        </is>
+      </c>
+      <c r="R87" s="3" t="inlineStr">
+        <is>
+          <t>130 − 60 = 70，所以心搏量是「70 ml」。</t>
+        </is>
+      </c>
+      <c r="S87" s="3" t="inlineStr">
+        <is>
+          <t>心搏量 = EDV（充滿）− ESV（剩下）= 130 − 60 = 70 ml。</t>
+        </is>
+      </c>
       <c r="T87" s="3" t="inlineStr"/>
       <c r="U87" s="3" t="inlineStr"/>
-      <c r="V87" s="3" t="inlineStr"/>
-      <c r="W87" s="3" t="inlineStr"/>
+      <c r="V87" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W87" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
@@ -7373,14 +9264,38 @@
           <t>70 次/分 × 70 ml = 4,900 ml/分（約 4.9 公升）。</t>
         </is>
       </c>
-      <c r="P88" s="3" t="inlineStr"/>
-      <c r="Q88" s="3" t="inlineStr"/>
-      <c r="R88" s="3" t="inlineStr"/>
-      <c r="S88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>「每分鐘 70 次」「心搏量 70 ml」「每分鐘打出多少血」：這是心輸出量。</t>
+        </is>
+      </c>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>每分鐘打出的血量叫什麼？→ 它等於哪兩個數相乘？→ 70 × 70 是多少？</t>
+        </is>
+      </c>
+      <c r="R88" s="3" t="inlineStr">
+        <is>
+          <t>70 次/分 × 70 ml = 4,900 ml，所以選「約 4,900 ml」。</t>
+        </is>
+      </c>
+      <c r="S88" s="3" t="inlineStr">
+        <is>
+          <t>心輸出量 = 心率 × 心搏量，安靜時約 5 公升／分。</t>
+        </is>
+      </c>
       <c r="T88" s="3" t="inlineStr"/>
       <c r="U88" s="3" t="inlineStr"/>
-      <c r="V88" s="3" t="inlineStr"/>
-      <c r="W88" s="3" t="inlineStr"/>
+      <c r="V88" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W88" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
@@ -7451,14 +9366,38 @@
           <t>射血期半月瓣打開，心室把血推進動脈，動脈壁被撐開，就是摸到的脈搏。</t>
         </is>
       </c>
-      <c r="P89" s="3" t="inlineStr"/>
-      <c r="Q89" s="3" t="inlineStr"/>
-      <c r="R89" s="3" t="inlineStr"/>
-      <c r="S89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>「脈搏跳一下」「把血推進動脈」：想想哪個時期半月瓣打開。</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>血液要進入動脈，哪一組瓣膜必須打開？→ 半月瓣在哪個時期打開？→ 動脈被推進來的血撐開，手腕就摸到什麼？</t>
+        </is>
+      </c>
+      <c r="R89" s="3" t="inlineStr">
+        <is>
+          <t>半月瓣打開、心室把血推進動脈的是「心室射血期」，這就是摸到的脈搏。</t>
+        </is>
+      </c>
+      <c r="S89" s="3" t="inlineStr">
+        <is>
+          <t>脈搏來自心室射血：半月瓣打開，血液把動脈壁撐開。</t>
+        </is>
+      </c>
       <c r="T89" s="3" t="inlineStr"/>
       <c r="U89" s="3" t="inlineStr"/>
-      <c r="V89" s="3" t="inlineStr"/>
-      <c r="W89" s="3" t="inlineStr"/>
+      <c r="V89" s="3" t="inlineStr">
+        <is>
+          <t>心動週期（圖像強化版）</t>
+        </is>
+      </c>
+      <c r="W89" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-cycle-v2/index.html</t>
+        </is>
+      </c>
       <c r="X89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
@@ -7529,14 +9468,38 @@
           <t>P 波反映心房去極化（電活動）；心房收縮是其後的機械反應，所以 P 波不等於心房收縮本身。</t>
         </is>
       </c>
-      <c r="P90" s="3" t="inlineStr"/>
-      <c r="Q90" s="3" t="inlineStr"/>
-      <c r="R90" s="3" t="inlineStr"/>
-      <c r="S90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>「P 波」「電活動」：題目問的是電訊號，不是收縮動作。</t>
+        </is>
+      </c>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>P 波是心電圖第一個波，對應心房還是心室？→ ECG 記錄的是電活動還是機械動作？→ 心房被電訊號啟動的過程叫什麼？</t>
+        </is>
+      </c>
+      <c r="R90" s="3" t="inlineStr">
+        <is>
+          <t>P 波反映心房的電活動，也就是「心房去極化」；收縮是之後的機械反應。</t>
+        </is>
+      </c>
+      <c r="S90" s="3" t="inlineStr">
+        <is>
+          <t>P 波＝心房去極化（電）；心房收縮（機械）在其後，兩者不相等。</t>
+        </is>
+      </c>
       <c r="T90" s="3" t="inlineStr"/>
       <c r="U90" s="3" t="inlineStr"/>
-      <c r="V90" s="3" t="inlineStr"/>
-      <c r="W90" s="3" t="inlineStr"/>
+      <c r="V90" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W90" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
@@ -7607,14 +9570,38 @@
           <t>T 波反映心室再極化，也就是心室肌細胞恢復靜止膜電位的過程。</t>
         </is>
       </c>
-      <c r="P91" s="3" t="inlineStr"/>
-      <c r="Q91" s="3" t="inlineStr"/>
-      <c r="R91" s="3" t="inlineStr"/>
-      <c r="S91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>「T 波」：QRS 之後的圓鈍波，想心室的下一步。</t>
+        </is>
+      </c>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>QRS 代表心室去極化，之後心室細胞要做什麼？→ 細胞恢復靜止膜電位的過程叫什麼？→ 所以 T 波反映哪裡的這個過程？</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr">
+        <is>
+          <t>T 波反映心室肌細胞恢復靜止膜電位，也就是「心室再極化」。</t>
+        </is>
+      </c>
+      <c r="S91" s="3" t="inlineStr">
+        <is>
+          <t>T 波＝心室再極化（心室細胞回到靜止膜電位）。</t>
+        </is>
+      </c>
       <c r="T91" s="3" t="inlineStr"/>
       <c r="U91" s="3" t="inlineStr"/>
-      <c r="V91" s="3" t="inlineStr"/>
-      <c r="W91" s="3" t="inlineStr"/>
+      <c r="V91" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W91" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
@@ -7685,14 +9672,38 @@
           <t>心率變快時 PR 與 QRS 幾乎不變、QT 只稍縮短，縮短最多的是 T 波結束到下一個 QRS 之間的心室舒張期。</t>
         </is>
       </c>
-      <c r="P92" s="3" t="inlineStr"/>
-      <c r="Q92" s="3" t="inlineStr"/>
-      <c r="R92" s="3" t="inlineStr"/>
-      <c r="S92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>「心率 75 拉到 150」「縮短最多」：比較 R-R 內各段誰變化最大。</t>
+        </is>
+      </c>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>心率變快時，PR 與 QRS 會明顯改變嗎？→ QT 是大幅縮短還是只稍縮短？→ 那被擠掉最多時間的是 T 波後的哪一段？</t>
+        </is>
+      </c>
+      <c r="R92" s="3" t="inlineStr">
+        <is>
+          <t>PR、QRS 幾乎不變、QT 只稍縮短，縮短最多的是「T 波結束到下一個 QRS 之間（心室舒張期）」。</t>
+        </is>
+      </c>
+      <c r="S92" s="3" t="inlineStr">
+        <is>
+          <t>心率↑ → 主要犧牲舒張期；PR、QRS 幾乎不變，QT 稍短。</t>
+        </is>
+      </c>
       <c r="T92" s="3" t="inlineStr"/>
       <c r="U92" s="3" t="inlineStr"/>
-      <c r="V92" s="3" t="inlineStr"/>
-      <c r="W92" s="3" t="inlineStr"/>
+      <c r="V92" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W92" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
@@ -7763,14 +9774,38 @@
           <t>P 波是心房去極化的電訊號，心房收縮（機械活動）通常緊接在後；要區分電活動與機械活動。</t>
         </is>
       </c>
-      <c r="P93" s="3" t="inlineStr"/>
-      <c r="Q93" s="3" t="inlineStr"/>
-      <c r="R93" s="3" t="inlineStr"/>
-      <c r="S93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>「P 波就是心房收縮」：要分清電活動與機械活動。</t>
+        </is>
+      </c>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>ECG 上的 P 波是電訊號還是肌肉動作？→ 心房先有電訊號，還是先收縮？→ 所以修正時要怎麼說明兩者的先後？</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="inlineStr">
+        <is>
+          <t>P 波是電訊號，收縮緊接在後，最合宜的修正是「P 波是心房去極化，收縮通常在其後發生」。</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>先電後動：P 波（心房去極化）→ 心房收縮。</t>
+        </is>
+      </c>
       <c r="T93" s="3" t="inlineStr"/>
       <c r="U93" s="3" t="inlineStr"/>
-      <c r="V93" s="3" t="inlineStr"/>
-      <c r="W93" s="3" t="inlineStr"/>
+      <c r="V93" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W93" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
@@ -7841,14 +9876,38 @@
           <t>心房再極化與 QRS 同時發生，但心室肌量大、QRS 振幅大，心房再極化的小訊號被遮蔽。</t>
         </is>
       </c>
-      <c r="P94" s="3" t="inlineStr"/>
-      <c r="Q94" s="3" t="inlineStr"/>
-      <c r="R94" s="3" t="inlineStr"/>
-      <c r="S94" s="3" t="inlineStr"/>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>「看不到」「心房再極化波」：想它發生的時間跟什麼重疊。</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>心房再極化大約和心電圖哪一個波同時發生？→ 心室肌量大，那個波的振幅是大還是小？→ 小訊號碰上同時期的大訊號，會怎樣？</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>心房再極化與 QRS 同時發生，小訊號「常被同時期較大的 QRS 波群遮蔽」。</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="inlineStr">
+        <is>
+          <t>心房再極化＝藏在 QRS 裡（心室肌量大、QRS 大，把它蓋住）。</t>
+        </is>
+      </c>
       <c r="T94" s="3" t="inlineStr"/>
       <c r="U94" s="3" t="inlineStr"/>
-      <c r="V94" s="3" t="inlineStr"/>
-      <c r="W94" s="3" t="inlineStr"/>
+      <c r="V94" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W94" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
@@ -7919,14 +9978,38 @@
           <t>T 波是心室再極化的電訊號（心室細胞恢復靜止膜電位）；心室收縮與放鬆是機械活動，要區分電活動與機械活動。</t>
         </is>
       </c>
-      <c r="P95" s="3" t="inlineStr"/>
-      <c r="Q95" s="3" t="inlineStr"/>
-      <c r="R95" s="3" t="inlineStr"/>
-      <c r="S95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>「T 波就是心室收縮結束」：又是電活動和機械活動混為一談。</t>
+        </is>
+      </c>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>ECG 上的 T 波記錄的是電訊號還是收縮動作？→ T 波代表心室細胞在做什麼（去極化或再極化）？→ 收縮與放鬆屬於電活動還是機械活動？</t>
+        </is>
+      </c>
+      <c r="R95" s="3" t="inlineStr">
+        <is>
+          <t>T 波是電訊號而非動作本身，最合宜的修正是「T 波是心室再極化的電訊號，不是收縮動作本身」。</t>
+        </is>
+      </c>
+      <c r="S95" s="3" t="inlineStr">
+        <is>
+          <t>T 波＝心室再極化（電）；收縮、放鬆＝機械活動，兩者要分開。</t>
+        </is>
+      </c>
       <c r="T95" s="3" t="inlineStr"/>
       <c r="U95" s="3" t="inlineStr"/>
-      <c r="V95" s="3" t="inlineStr"/>
-      <c r="W95" s="3" t="inlineStr"/>
+      <c r="V95" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W95" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
@@ -7997,15 +10080,1007 @@
           <t>標準十二導程使用 10 個電極（四肢 4、胸前 6），組合出 12 個觀測角度（導程）。</t>
         </is>
       </c>
-      <c r="P96" s="3" t="inlineStr"/>
-      <c r="Q96" s="3" t="inlineStr"/>
-      <c r="R96" s="3" t="inlineStr"/>
-      <c r="S96" s="3" t="inlineStr"/>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>「12 導程」：導程是觀測角度，不等於貼片數。</t>
+        </is>
+      </c>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>標準十二導程實際用幾個電極？（四肢幾個、胸前幾個）→ 這些電極組合起來，能得到幾個觀測角度？→ 所以「12」指的是電極數還是角度數？</t>
+        </is>
+      </c>
+      <c r="R96" s="3" t="inlineStr">
+        <is>
+          <t>10 個電極組合出 12 個角度，所以是「由 10 個電極建立的 12 個觀測角度」。</t>
+        </is>
+      </c>
+      <c r="S96" s="3" t="inlineStr">
+        <is>
+          <t>12 導程＝12 個角度；10 個電極＝四肢 4 ＋胸前 6。</t>
+        </is>
+      </c>
       <c r="T96" s="3" t="inlineStr"/>
       <c r="U96" s="3" t="inlineStr"/>
-      <c r="V96" s="3" t="inlineStr"/>
-      <c r="W96" s="3" t="inlineStr"/>
+      <c r="V96" s="3" t="inlineStr">
+        <is>
+          <t>心電圖基礎與心率調控</t>
+        </is>
+      </c>
+      <c r="W96" s="3" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/ecg-basics-v1/index.html</t>
+        </is>
+      </c>
       <c r="X96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>正常節律最常從哪裡開始？</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>房室結</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>浦金氏纖維</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>希氏束</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>竇房結</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>竇房結是正常心跳最早規律發出電訊號的節律點。</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>「正常節律」「從哪裡開始」：找心跳電訊號的起點。</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>心跳的電訊號有一個最早的發出點嗎？→ 它規律發出訊號，所以被稱為什麼？→ 這個節律點是哪一個「結」？</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>正常心跳最早規律發出電訊號的節律點是「竇房結」。</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>竇房結＝起點（節律點）→ 房室結 → 希氏束 → 浦金氏纖維。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>P 波代表什麼？</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>心房再極化</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>心室去極化</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>心室再極化</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>心房去極化</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>4</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>P 波反映心房去極化的電性活動。</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>「P 波」：心電圖第一個波，想它對應心臟哪一部分。</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>心跳的電訊號最先傳遍的是心房還是心室？→ 訊號傳開時，細胞是在去極化還是再極化？→ 所以第一個小波 P 波代表什麼？</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>P 波反映的是心房細胞被電訊號啟動，也就是「心房去極化」。</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>P 波＝心房去極化；QRS＝心室去極化；T 波＝心室再極化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>房室結暫緩的意義？</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>讓心房先送血入心室</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>停止電傳導</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>讓半月瓣先關閉</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>讓心室先收縮</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>房室結暫緩讓心房先完成收縮與心室充血，再由心室收縮。</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>「房室結」「暫緩」：想訊號慢下來時，心房可以趁機做什麼。</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>訊號在房室結停頓一下，心房和心室誰先收縮？→ 心房收縮是要把血送去哪裡？→ 先讓心室裝滿血，再收縮，有什麼好處？</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>房室結暫緩讓心房先完成收縮、心室先充血，所以意義是「讓心房先送血入心室」。</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>房室結暫緩＝心房先送血 → 心室裝滿 → 心室再收縮。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>哪個路徑快速把訊號送到心室？</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>希氏束、束支與浦金氏纖維</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>冠狀動脈</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>房室瓣</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>上腔靜脈</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>訊號離開房室結後，經希氏束、左右束支與浦金氏纖維快速傳到心室。</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>「快速」「送到心室」：找房室結之後的傳導路徑。</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>訊號離開房室結後，先進入哪一束？→ 接著分成左右兩條什麼？→ 最後由哪種纖維把訊號快速散到整個心室？</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>訊號經「希氏束、束支與浦金氏纖維」快速傳到心室。</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>房室結 → 希氏束 → 左右束支 → 浦金氏纖維 → 心室。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>QRS 主要代表？</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>心室去極化</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>心室再極化</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>心房再極化</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>心房去極化</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>QRS 複合波主要反映心室去極化。</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>「QRS」：心電圖中最高、最尖的那組波。</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>P 波代表心房，那 QRS 對應的是心房還是心室？→ 這時心室細胞是被啟動（去極化）還是在恢復（再極化）？→ 所以 QRS 主要代表什麼？</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>QRS 複合波主要反映「心室去極化」。</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>P＝心房去極化；QRS＝心室去極化；T＝心室再極化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>心室工作心肌在 phase 2 高原期，哪一項敘述正確？</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>所有離子通道都關閉</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>L 型 Ca²⁺ 通道造成 Ca²⁺ 內流，與 K⁺ 外流暫時平衡</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>只有 Na⁺ 大量內流，沒有 K⁺ 外流</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Cl⁻ 是唯一流動的離子</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Phase 2 時 L 型 Ca²⁺ 通道開啟；Ca²⁺ 內流與 K⁺ 外流暫時平衡，形成高原期。</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>「phase 2」「高原期」：電位維持平平，代表進出的電荷互相抵消。</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>高原期電位為什麼能維持一段時間不下降？→ 這時哪一種通道打開，讓什麼離子流進來？→ 同時有什麼離子流出去，兩者達到暫時平衡？</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>高原期是鈣進、鉀出暫時平衡，所以選「L 型 Ca²⁺ 通道造成 Ca²⁺ 內流，與 K⁺ 外流暫時平衡」。</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Phase 2 高原期＝L 型 Ca²⁺ 內流 ⇄ K⁺ 外流，暫時平衡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-case-q01</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>【生活情境】運動時心率加快，最直接的電性改變是？</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>T 波消失</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>竇房結放電變快</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>房室結停止傳導</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>浦金氏纖維傳導停止</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>運動時竇房結放電頻率增加，所以心率加快。</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>「心率加快」「最直接的電性改變」：心率由節律點決定。</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>心率是由誰發出訊號的快慢決定？→ 運動時這個節律點放電頻率會增加還是減少？→ 放電變快，心率就會怎樣？</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>運動時竇房結放電頻率增加，心率跟著加快，所以是「竇房結放電變快」。</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>心率快慢＝竇房結放電快慢；運動 → 放電↑ → 心率↑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-case-q02</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>【實驗觀察】心房先於心室收縮，最能解釋的是？</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>浦金氏纖維消失</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>房室結暫緩</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>半月瓣先開啟</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>瓣膜發出電訊號</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>2</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>房室結的短暫延遲讓心房有時間先完成送血入心室。</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>「心房先於心室收縮」：想是什麼讓訊號在中間停一下。</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>訊號從心房到心室，中間要經過哪個關卡？→ 在那裡是加速還是短暫延遲？→ 延遲讓誰有時間先完成送血？</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>房室結的短暫延遲讓心房先送血入心室，所以最能解釋的是「房室結暫緩」。</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>心房先、心室後＝房室結暫緩（短暫延遲）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-case-q03</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>9</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>【模型觀察】心房到心室的關鍵電性關卡是？</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>冠狀動脈</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>主動脈瓣</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>房室結</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>心包膜</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>3</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>房室結位於心房與心室交界，是正常傳導的關鍵暫緩處。</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>「心房到心室」「電性關卡」：找位在房室交界、負責傳電的構造。</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>選項中哪些是血管、瓣膜或外膜，而不是傳電構造？→ 位在心房與心室交界、會傳電的是哪一個？→ 它還會讓訊號短暫停一下嗎？</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>位在心房與心室交界、正常傳導的關鍵暫緩處是「房室結」。</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>房室結＝心房到心室的電性關卡（交界處暫緩）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-case-q04</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>10</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>【生理判讀】QRS 後緩緩回到基線的 T 波表示？</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>心房再極化</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>心房去極化</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>心室再極化</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>心室去極化</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>3</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>T 波反映心室再極化，也就是心室肌細胞回復電性狀態。</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>「QRS 後」「回到基線」「T 波」：想心室被啟動之後的下一步。</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>QRS 代表心室去極化，接下來心室細胞要做什麼？→ 細胞回復電性狀態叫去極化還是再極化？→ 所以 T 波代表哪裡的哪個過程？</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>T 波表示心室肌細胞回復電性狀態，也就是「心室再極化」。</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>QRS＝心室去極化（啟動）→ T 波＝心室再極化（回復）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>cardiac-electrical-case-q05</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>心臟構造</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>11</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>【生理判讀】心室工作心肌處於高原期時，ECG 大致對應哪個區段？</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>下一個 P 波</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>QRS 複合波</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>ST 間段</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>P 波</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>3</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>心室多數細胞處於 phase 2 高原期時，ECG 大致呈近等電位的 ST 間段。</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>「高原期」「ECG 區段」：電位維持平平，對應圖上平平的一段。</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>高原期時心室多數細胞的電位是持續改變還是維持平平？→ ECG 在 QRS 之後、T 波之前有一段近乎平的區段叫什麼？→ 平平的電位對應平平的線嗎？</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>心室多數細胞在 phase 2 高原期時，ECG 大致呈近等電位的「ST 間段」。</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Phase 2 高原期 ≈ ST 間段（近等電位，平平一段）。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8013,7 +11088,7 @@
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8023,7 +11098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8277,16 +11352,28 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>心臟的電性活動</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜html/心臟電性活動.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>95 題</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>106 題</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>供應左心室前壁及心室間隔前 2/3 血液的主要冠狀動脈分枝為何？</t>
+          <t>供應左、右心室前壁及心室間隔前 2/3 血液的主要冠狀動脈分枝為何？</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>左冠狀動脈（LCA）分支出的前室間枝（Anterior interventricular branch，又稱左前降支 LAD）主要供應兩心室前壁與心室間隔。</t>
+          <t>左冠狀動脈（LCA）分支出的前室間枝（Anterior interventricular branch，又稱左前降支 LAD）主要供應左、右心室前壁與心室間隔。</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>「左心室前壁」「心室間隔前 2/3」：找走在心臟前面的那條冠狀動脈分枝。</t>
+          <t>「左、右心室前壁」「心室間隔前 2/3」：找走在心臟前面的那條冠狀動脈分枝。</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>前室間枝（前降支，LAD）＝左冠狀動脈分枝，管兩心室前壁與間隔前 2/3。</t>
+          <t>前室間枝（前降支，LAD）＝左冠狀動脈分枝，管左、右心室前壁與間隔前 2/3。</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>【模型觀察】心臟模型前面、左右心室之間的溝裡有一條動脈，負責供應左心室前壁。它是？</t>
+          <t>【模型觀察】心臟模型前面、左右心室之間的溝裡有一條動脈，負責供應左、右心室前壁。它是？</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>左冠狀動脈的前室間枝走在前室間溝，供應兩心室前壁與心室間隔前 2/3；心大靜脈與它伴行。</t>
+          <t>左冠狀動脈的前室間枝走在前室間溝，供應左、右心室前壁與心室間隔前 2/3；心大靜脈與它伴行。</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>「前面」「左右心室之間的溝」「供應左心室前壁」：溝的位置決定血管名稱。</t>
+          <t>「前面」「左右心室之間的溝」「供應左、右心室前壁」：溝的位置決定血管名稱。</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>走在前室間溝、供應左心室前壁的是「左冠狀動脈前室間枝（前降支）」。</t>
+          <t>走在前室間溝、供應左、右心室前壁的是「左冠狀動脈前室間枝（前降支）」。</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>心臟傳導系統由特化心肌組織構成，其中位於右心房後壁近上腔靜脈開口下方、被稱為正常心跳「節律點（Pacemaker）」的構造為何？</t>
+          <t>心臟傳導系統由特化心肌組織構成，其中位於右心房壁近上腔靜脈開口下方、被稱為正常心跳「節律點（Pacemaker）」的構造為何？</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -5004,12 +5004,12 @@
       <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr"/>
@@ -5106,12 +5106,12 @@
       <c r="U47" s="3" t="inlineStr"/>
       <c r="V47" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr"/>
@@ -5208,12 +5208,12 @@
       <c r="U48" s="3" t="inlineStr"/>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr"/>
@@ -5310,12 +5310,12 @@
       <c r="U49" s="3" t="inlineStr"/>
       <c r="V49" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr"/>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>左冠狀動脈（LCA）分支出的前室間枝（Anterior interventricular branch，又稱左前降支 LAD）主要供應左、右心室前壁與心室間隔。</t>
+          <t>左冠狀動脈（LCA）分支出的前室間枝（Anterior interventricular branch，又稱左前降支 LAD）主要供應左、右心室前壁及心室間隔前 2/3。</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -5412,12 +5412,12 @@
       <c r="U50" s="3" t="inlineStr"/>
       <c r="V50" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr"/>
@@ -5514,12 +5514,12 @@
       <c r="U51" s="3" t="inlineStr"/>
       <c r="V51" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr"/>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>左冠狀動脈的前室間枝走在前室間溝，供應左、右心室前壁與心室間隔前 2/3；心大靜脈與它伴行。</t>
+          <t>左冠狀動脈的前室間枝走在前室間溝，供應左、右心室前壁及心室間隔前 2/3；心大靜脈與它伴行。</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5616,12 +5616,12 @@
       <c r="U52" s="3" t="inlineStr"/>
       <c r="V52" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       <c r="U53" s="3" t="inlineStr"/>
       <c r="V53" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr"/>
@@ -5820,12 +5820,12 @@
       <c r="U54" s="3" t="inlineStr"/>
       <c r="V54" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr"/>
@@ -5922,12 +5922,12 @@
       <c r="U55" s="3" t="inlineStr"/>
       <c r="V55" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr"/>
@@ -6024,12 +6024,12 @@
       <c r="U56" s="3" t="inlineStr"/>
       <c r="V56" s="3" t="inlineStr">
         <is>
-          <t>心臟構造與解剖生理圖卡</t>
+          <t>心臟構造與解剖生理圖卡（圖像強化版）</t>
         </is>
       </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v1/index.html</t>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/heart-structure-v2/index.html</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr"/>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X107"/>
+  <dimension ref="A1:X162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11082,6 +11082,5616 @@
         </is>
       </c>
     </row>
+    <row r="108" ht="134" hidden="0" customHeight="1">
+      <c r="A108" s="3"/>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>血液離開心臟後的正確順序為何？</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>微血管→動脈→靜脈</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>靜脈→微血管→動脈</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>動脈→微血管→靜脈</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>動脈→靜脈→微血管</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
+          <t>動脈帶離心臟，微血管交換物質，靜脈送回心臟。</t>
+        </is>
+      </c>
+      <c r="P108" s="5" t="inlineStr">
+        <is>
+          <t>「離心、交換、回心」：先找離開心臟的血管，再找交換的位置。</t>
+        </is>
+      </c>
+      <c r="Q108" s="5" t="inlineStr">
+        <is>
+          <t>離開心臟先進哪類血管？→ 在哪裡交換物質？→ 交換後由哪類血管回心？</t>
+        </is>
+      </c>
+      <c r="R108" s="5" t="inlineStr">
+        <is>
+          <t>選擇「動脈→微血管→靜脈」。動脈帶離心臟，微血管交換物質，靜脈送回心臟。</t>
+        </is>
+      </c>
+      <c r="S108" s="5" t="inlineStr">
+        <is>
+          <t>動脈帶離心臟，微血管交換物質，靜脈送回心臟。</t>
+        </is>
+      </c>
+      <c r="T108" s="3"/>
+      <c r="U108" s="3"/>
+      <c r="V108" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W108" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X108" s="3"/>
+    </row>
+    <row r="109" ht="134" hidden="0" customHeight="1">
+      <c r="A109" s="3"/>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>哪一層血管壁直接接觸血液？</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>內膜</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>中膜</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>基底膜外層</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>外膜</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" s="5" t="inlineStr">
+        <is>
+          <t>內膜的內皮直接接觸血液；中膜含平滑肌，外膜在最外側。</t>
+        </is>
+      </c>
+      <c r="P109" s="5" t="inlineStr">
+        <is>
+          <t>「直接接觸血液、最內側」：想想哪一層位在管腔最內側。</t>
+        </is>
+      </c>
+      <c r="Q109" s="5" t="inlineStr">
+        <is>
+          <t>血液流在管腔內嗎？→ 哪一膜位於管腔最內側？→ 中膜與外膜會直接接觸血液嗎？</t>
+        </is>
+      </c>
+      <c r="R109" s="5" t="inlineStr">
+        <is>
+          <t>選擇「內膜」。內膜的內皮直接接觸血液；中膜含平滑肌，外膜在最外側。</t>
+        </is>
+      </c>
+      <c r="S109" s="5" t="inlineStr">
+        <is>
+          <t>內膜的內皮直接接觸血液；中膜含平滑肌，外膜在最外側。</t>
+        </is>
+      </c>
+      <c r="T109" s="3"/>
+      <c r="U109" s="3"/>
+      <c r="V109" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W109" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X109" s="3"/>
+    </row>
+    <row r="110" ht="134" hidden="0" customHeight="1">
+      <c r="A110" s="3"/>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>哪一類血管的中膜最發達？</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>所有血管相同</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>動脈</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
+          <t>動脈的中膜通常最發達，有助承受高壓及調節管徑。</t>
+        </is>
+      </c>
+      <c r="P110" s="5" t="inlineStr">
+        <is>
+          <t>「中膜、承受高壓」：它必須承受離開心臟時較高的壓力。</t>
+        </is>
+      </c>
+      <c r="Q110" s="5" t="inlineStr">
+        <is>
+          <t>剛離開心臟的血液壓力較高嗎？→ 哪類血管需要較厚的平滑肌與彈性纖維？</t>
+        </is>
+      </c>
+      <c r="R110" s="5" t="inlineStr">
+        <is>
+          <t>選擇「動脈」。動脈的中膜通常最發達，有助承受高壓及調節管徑。</t>
+        </is>
+      </c>
+      <c r="S110" s="5" t="inlineStr">
+        <is>
+          <t>動脈的中膜通常最發達，有助承受高壓及調節管徑。</t>
+        </is>
+      </c>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W110" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X110" s="3"/>
+    </row>
+    <row r="111" ht="134" hidden="0" customHeight="1">
+      <c r="A111" s="3"/>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>最適合物質交換的血管構造是？</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>單向瓣膜</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>單層內皮細胞管壁</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>厚的平滑肌層</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>寬大的管腔</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
+          <t>微血管主要由單層內皮與基底膜構成，薄壁縮短交換距離。</t>
+        </is>
+      </c>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>「交換、薄壁、短距離」：交換距離越短越容易進行。</t>
+        </is>
+      </c>
+      <c r="Q111" s="5" t="inlineStr">
+        <is>
+          <t>交換物質需要跨過管壁嗎？→ 管壁厚還是薄較容易交換？→ 哪個選項描述薄壁？</t>
+        </is>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
+        <is>
+          <t>選擇「單層內皮細胞管壁」。微血管主要由單層內皮與基底膜構成，薄壁縮短交換距離。</t>
+        </is>
+      </c>
+      <c r="S111" s="5" t="inlineStr">
+        <is>
+          <t>微血管主要由單層內皮與基底膜構成，薄壁縮短交換距離。</t>
+        </is>
+      </c>
+      <c r="T111" s="3"/>
+      <c r="U111" s="3"/>
+      <c r="V111" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W111" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X111" s="3"/>
+    </row>
+    <row r="112" ht="134" hidden="0" customHeight="1">
+      <c r="A112" s="3"/>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>靜脈回流時，何者可防止下肢血液逆流？</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>外膜</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>彈性纖維</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>靜脈瓣膜</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>微血管前括約肌</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O112" s="5" t="inlineStr">
+        <is>
+          <t>靜脈瓣膜可減少逆流；骨骼肌擠壓靜脈可協助回流。</t>
+        </is>
+      </c>
+      <c r="P112" s="5" t="inlineStr">
+        <is>
+          <t>「下肢、逆流、單向門」：這是血管內像單向門的構造。</t>
+        </is>
+      </c>
+      <c r="Q112" s="5" t="inlineStr">
+        <is>
+          <t>下肢血液回心時可能向下倒流嗎？→ 哪個構造像只能向心臟開啟的門？</t>
+        </is>
+      </c>
+      <c r="R112" s="5" t="inlineStr">
+        <is>
+          <t>選擇「靜脈瓣膜」。靜脈瓣膜可減少逆流；骨骼肌擠壓靜脈可協助回流。</t>
+        </is>
+      </c>
+      <c r="S112" s="5" t="inlineStr">
+        <is>
+          <t>靜脈瓣膜可減少逆流；骨骼肌擠壓靜脈可協助回流。</t>
+        </is>
+      </c>
+      <c r="T112" s="3"/>
+      <c r="U112" s="3"/>
+      <c r="V112" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W112" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X112" s="3"/>
+    </row>
+    <row r="113" ht="134" hidden="0" customHeight="1">
+      <c r="A113" s="3"/>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>哪一段血管的總截面積最大？</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>大靜脈</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>小動脈</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>大動脈</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>微血管單根很細但數目多，總截面積最大。</t>
+        </is>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>「總截面積、很多細管」：它由非常多條極細的小管組成。</t>
+        </is>
+      </c>
+      <c r="Q113" s="5" t="inlineStr">
+        <is>
+          <t>題目問單根管徑還是所有血管加總的面積？→ 哪類血管雖細但數目最多？</t>
+        </is>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>選擇「微血管」。微血管單根很細但數目多，總截面積最大。</t>
+        </is>
+      </c>
+      <c r="S113" s="5" t="inlineStr">
+        <is>
+          <t>微血管單根很細但數目多，總截面積最大。</t>
+        </is>
+      </c>
+      <c r="T113" s="3"/>
+      <c r="U113" s="3"/>
+      <c r="V113" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W113" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X113" s="3"/>
+    </row>
+    <row r="114" ht="134" hidden="0" customHeight="1">
+      <c r="A114" s="3"/>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-case-q01</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】厚壁、管腔較圓的血管最可能是？</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>淋巴管</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>動脈</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
+          <t>動脈的中膜較發達，模型中的厚壁與較圓管腔符合動脈。</t>
+        </is>
+      </c>
+      <c r="P114" s="5" t="inlineStr">
+        <is>
+          <t>「厚壁、圓管腔、中膜」：比較中膜厚度與管腔形狀。</t>
+        </is>
+      </c>
+      <c r="Q114" s="5" t="inlineStr">
+        <is>
+          <t>厚壁需要較多平滑肌與彈性纖維嗎？→ 這是哪類承受高壓血管的特徵？</t>
+        </is>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
+        <is>
+          <t>選擇「動脈」。動脈的中膜較發達，模型中的厚壁與較圓管腔符合動脈。</t>
+        </is>
+      </c>
+      <c r="S114" s="5" t="inlineStr">
+        <is>
+          <t>動脈的中膜較發達，模型中的厚壁與較圓管腔符合動脈。</t>
+        </is>
+      </c>
+      <c r="T114" s="3"/>
+      <c r="U114" s="3"/>
+      <c r="V114" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W114" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X114" s="3"/>
+    </row>
+    <row r="115" ht="134" hidden="0" customHeight="1">
+      <c r="A115" s="3"/>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-case-q02</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】慢跑時，小腿肌肉可幫助哪種血管回流？</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>小動脈</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>動脈</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" s="5" t="inlineStr">
+        <is>
+          <t>小腿肌肉幫浦配合靜脈瓣膜，協助下肢靜脈回流。</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>「小腿肌肉、回流」：想想瓣膜與肌肉幫浦一起作用的血管。</t>
+        </is>
+      </c>
+      <c r="Q115" s="5" t="inlineStr">
+        <is>
+          <t>肌肉收縮會擠壓周圍血管嗎？→ 哪類血管配合瓣膜把血液送回心臟？</t>
+        </is>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>選擇「靜脈」。小腿肌肉幫浦配合靜脈瓣膜，協助下肢靜脈回流。</t>
+        </is>
+      </c>
+      <c r="S115" s="5" t="inlineStr">
+        <is>
+          <t>小腿肌肉幫浦配合靜脈瓣膜，協助下肢靜脈回流。</t>
+        </is>
+      </c>
+      <c r="T115" s="3"/>
+      <c r="U115" s="3"/>
+      <c r="V115" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W115" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X115" s="3"/>
+    </row>
+    <row r="116" ht="134" hidden="0" customHeight="1">
+      <c r="A116" s="3"/>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-case-q03</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】血流最慢、交換最充分的位置是？</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>小動脈</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>主動脈</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>微血管網</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>腔靜脈</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
+          <t>微血管網總截面積最大、平均流速最慢，有利充分交換。</t>
+        </is>
+      </c>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>「血流最慢、總截面積最大」：找總截面積最大的血管區段。</t>
+        </is>
+      </c>
+      <c r="Q116" s="5" t="inlineStr">
+        <is>
+          <t>總流量相近時，總截面積增加會讓流速快還是慢？→ 哪個網絡面積最大？</t>
+        </is>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>選擇「微血管網」。微血管網總截面積最大、平均流速最慢，有利充分交換。</t>
+        </is>
+      </c>
+      <c r="S116" s="5" t="inlineStr">
+        <is>
+          <t>微血管網總截面積最大、平均流速最慢，有利充分交換。</t>
+        </is>
+      </c>
+      <c r="T116" s="3"/>
+      <c r="U116" s="3"/>
+      <c r="V116" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W116" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X116" s="3"/>
+    </row>
+    <row r="117" ht="134" hidden="0" customHeight="1">
+      <c r="A117" s="3"/>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-case-q04</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】紅血球單列通過最符合哪種血管？</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>小靜脈</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>大動脈</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" s="5" t="inlineStr">
+        <is>
+          <t>微血管管腔極細，紅血球常以單列通過。</t>
+        </is>
+      </c>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>「紅血球單列、細小管腔」：這種血管的管腔最細，管壁也最薄。</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr">
+        <is>
+          <t>單列通過表示管腔寬還是細？→ 哪種血管既細又只有薄壁？</t>
+        </is>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>選擇「微血管」。微血管管腔極細，紅血球常以單列通過。</t>
+        </is>
+      </c>
+      <c r="S117" s="5" t="inlineStr">
+        <is>
+          <t>微血管管腔極細，紅血球常以單列通過。</t>
+        </is>
+      </c>
+      <c r="T117" s="3"/>
+      <c r="U117" s="3"/>
+      <c r="V117" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X117" s="3"/>
+    </row>
+    <row r="118" ht="134" hidden="0" customHeight="1">
+      <c r="A118" s="3"/>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>blood-vessels-case-q05</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】橡皮管回彈能幫助哪種血管維持血流？</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>靜脈瓣膜</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>小靜脈</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>大動脈</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O118" s="5" t="inlineStr">
+        <is>
+          <t>大動脈射血時擴張、舒張時回彈，可緩衝間歇射血並維持血流。</t>
+        </is>
+      </c>
+      <c r="P118" s="5" t="inlineStr">
+        <is>
+          <t>「回彈、射血緩衝」：想想能儲存射血壓力的血管。</t>
+        </is>
+      </c>
+      <c r="Q118" s="5" t="inlineStr">
+        <is>
+          <t>射血時哪種血管先擴張？→ 心室舒張時哪種血管的回彈可維持血流？</t>
+        </is>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>選擇「大動脈」。大動脈射血時擴張、舒張時回彈，可緩衝間歇射血並維持血流。</t>
+        </is>
+      </c>
+      <c r="S118" s="5" t="inlineStr">
+        <is>
+          <t>大動脈射血時擴張、舒張時回彈，可緩衝間歇射血並維持血流。</t>
+        </is>
+      </c>
+      <c r="T118" s="3"/>
+      <c r="U118" s="3"/>
+      <c r="V118" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="W118" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X118" s="3"/>
+    </row>
+    <row r="119" ht="134" hidden="0" customHeight="1">
+      <c r="A119" s="3"/>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>體循環由哪個心室出發、回到哪個心房？</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>左心房→右心室</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>左心室→右心房</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>右心房→左心室</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>右心室→左心房</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" s="5" t="inlineStr">
+        <is>
+          <t>體循環由左心室出發，經全身交換後回到右心房。</t>
+        </is>
+      </c>
+      <c r="P119" s="5" t="inlineStr">
+        <is>
+          <t>「體循環、主動脈、腔靜脈」：想想主動脈由哪個心室發出。</t>
+        </is>
+      </c>
+      <c r="Q119" s="5" t="inlineStr">
+        <is>
+          <t>主動脈從哪個心室出發？→ 全身交換後的血液經腔靜脈回到哪個心房？</t>
+        </is>
+      </c>
+      <c r="R119" s="5" t="inlineStr">
+        <is>
+          <t>選擇「左心室→右心房」。體循環由左心室出發，經全身交換後回到右心房。</t>
+        </is>
+      </c>
+      <c r="S119" s="5" t="inlineStr">
+        <is>
+          <t>體循環由左心室出發，經全身交換後回到右心房。</t>
+        </is>
+      </c>
+      <c r="T119" s="3"/>
+      <c r="U119" s="3"/>
+      <c r="V119" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W119" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X119" s="3"/>
+    </row>
+    <row r="120" ht="134" hidden="0" customHeight="1">
+      <c r="A120" s="3"/>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈與肺靜脈的血液配對何者正確？</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>都攜帶缺氧血</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>都攜帶充氧血</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈缺氧、肺靜脈充氧</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈充氧、肺靜脈缺氧</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O120" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈攜帶缺氧血到肺；肺靜脈攜帶換氧後的充氧血回左心房。</t>
+        </is>
+      </c>
+      <c r="P120" s="5" t="inlineStr">
+        <is>
+          <t>「肺動脈、肺靜脈、換氧前後」：肺循環在肺泡旁換氧。</t>
+        </is>
+      </c>
+      <c r="Q120" s="5" t="inlineStr">
+        <is>
+          <t>到肺泡前的血液缺氧還是充氧？→ 換氧後經肺靜脈返回的血液含氧量如何？</t>
+        </is>
+      </c>
+      <c r="R120" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肺動脈缺氧、肺靜脈充氧」。肺動脈攜帶缺氧血到肺；肺靜脈攜帶換氧後的充氧血回左心房。</t>
+        </is>
+      </c>
+      <c r="S120" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈攜帶缺氧血到肺；肺靜脈攜帶換氧後的充氧血回左心房。</t>
+        </is>
+      </c>
+      <c r="T120" s="3"/>
+      <c r="U120" s="3"/>
+      <c r="V120" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W120" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X120" s="3"/>
+    </row>
+    <row r="121" ht="134" hidden="0" customHeight="1">
+      <c r="A121" s="3"/>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>體循環與肺循環的總血流量關係為何？</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>兩者相同</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>隨呼吸完全改變</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>體循環較大</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>肺循環較大</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="5" t="inlineStr">
+        <is>
+          <t>肺循環與體循環串聯，正常平衡時兩者總血流量相同。</t>
+        </is>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>「串聯、總血流量」：兩個循環是串聯的迴路。</t>
+        </is>
+      </c>
+      <c r="Q121" s="5" t="inlineStr">
+        <is>
+          <t>血液是否接著走過肺循環與體循環？→ 若兩者流量長期不同，會在某處累積嗎？</t>
+        </is>
+      </c>
+      <c r="R121" s="5" t="inlineStr">
+        <is>
+          <t>選擇「兩者相同」。肺循環與體循環串聯，正常平衡時兩者總血流量相同。</t>
+        </is>
+      </c>
+      <c r="S121" s="5" t="inlineStr">
+        <is>
+          <t>肺循環與體循環串聯，正常平衡時兩者總血流量相同。</t>
+        </is>
+      </c>
+      <c r="T121" s="3"/>
+      <c r="U121" s="3"/>
+      <c r="V121" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W121" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X121" s="3"/>
+    </row>
+    <row r="122" ht="134" hidden="0" customHeight="1">
+      <c r="A122" s="3"/>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>消化道吸收的養分先由何者送進肝臟？</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>下腔靜脈</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>肝靜脈</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>肝動脈</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>肝門靜脈</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O122" s="5" t="inlineStr">
+        <is>
+          <t>消化道吸收的養分經肝門靜脈先進入肝臟，再由肝靜脈離開。</t>
+        </is>
+      </c>
+      <c r="P122" s="5" t="inlineStr">
+        <is>
+          <t>「消化道、先進肝臟」：先區分：這段血管是從消化道進入肝臟，還是離開肝臟。</t>
+        </is>
+      </c>
+      <c r="Q122" s="5" t="inlineStr">
+        <is>
+          <t>題目要找進肝臟還是離開肝臟的血管？→ 哪條靜脈連接消化道與肝臟？</t>
+        </is>
+      </c>
+      <c r="R122" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肝門靜脈」。消化道吸收的養分經肝門靜脈先進入肝臟，再由肝靜脈離開。</t>
+        </is>
+      </c>
+      <c r="S122" s="5" t="inlineStr">
+        <is>
+          <t>消化道吸收的養分經肝門靜脈先進入肝臟，再由肝靜脈離開。</t>
+        </is>
+      </c>
+      <c r="T122" s="3"/>
+      <c r="U122" s="3"/>
+      <c r="V122" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W122" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X122" s="3"/>
+    </row>
+    <row r="123" ht="134" hidden="0" customHeight="1">
+      <c r="A123" s="3"/>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>冠狀動脈直接分支自何處？</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>上腔靜脈</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>升主動脈根部</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈幹</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>左心房</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>左、右冠狀動脈直接分支自升主動脈根部，供應心肌。</t>
+        </is>
+      </c>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>「冠狀動脈、起點」：找左心室射出的血液剛離開心臟的位置。</t>
+        </is>
+      </c>
+      <c r="Q123" s="5" t="inlineStr">
+        <is>
+          <t>冠狀動脈要把充氧血送給心肌嗎？→ 左心室剛射出的血液先進入哪條大血管？</t>
+        </is>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>選擇「升主動脈根部」。左、右冠狀動脈直接分支自升主動脈根部，供應心肌。</t>
+        </is>
+      </c>
+      <c r="S123" s="5" t="inlineStr">
+        <is>
+          <t>左、右冠狀動脈直接分支自升主動脈根部，供應心肌。</t>
+        </is>
+      </c>
+      <c r="T123" s="3"/>
+      <c r="U123" s="3"/>
+      <c r="V123" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W123" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X123" s="3"/>
+    </row>
+    <row r="124" ht="134" hidden="0" customHeight="1">
+      <c r="A124" s="3"/>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>胎兒時連接肺動脈幹與主動脈的是？</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>卵圓孔</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>臍靜脈</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>動脈導管</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>靜脈導管</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O124" s="5" t="inlineStr">
+        <is>
+          <t>動脈導管連接肺動脈幹與主動脈；卵圓孔連接兩個心房。</t>
+        </is>
+      </c>
+      <c r="P124" s="5" t="inlineStr">
+        <is>
+          <t>「胎兒、兩條大動脈間的旁路」：它是連接兩條大動脈的短路構造。</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>題目連接的是心房還是大動脈？→ 哪個導管連接肺動脈幹與主動脈？</t>
+        </is>
+      </c>
+      <c r="R124" s="5" t="inlineStr">
+        <is>
+          <t>選擇「動脈導管」。動脈導管連接肺動脈幹與主動脈；卵圓孔連接兩個心房。</t>
+        </is>
+      </c>
+      <c r="S124" s="5" t="inlineStr">
+        <is>
+          <t>動脈導管連接肺動脈幹與主動脈；卵圓孔連接兩個心房。</t>
+        </is>
+      </c>
+      <c r="T124" s="3"/>
+      <c r="U124" s="3"/>
+      <c r="V124" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W124" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X124" s="3"/>
+    </row>
+    <row r="125" ht="134" hidden="0" customHeight="1">
+      <c r="A125" s="3"/>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-case-q01</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】腳趾血液回心後，下一個換氧位置是？</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>肺泡周圍微血管</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>肝臟微血管</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>手掌微血管</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>冠狀微血管</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" s="5" t="inlineStr">
+        <is>
+          <t>全身缺氧血回到右心後，經肺動脈到肺泡周圍微血管換氧。</t>
+        </is>
+      </c>
+      <c r="P125" s="5" t="inlineStr">
+        <is>
+          <t>「腳趾回心、下一次換氧」：缺氧血先回右心，再由肺動脈送往哪裡？</t>
+        </is>
+      </c>
+      <c r="Q125" s="5" t="inlineStr">
+        <is>
+          <t>全身回流的缺氧血先到右心嗎？→ 右心室再把血液送到哪裡吸收氧氣？</t>
+        </is>
+      </c>
+      <c r="R125" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肺泡周圍微血管」。全身缺氧血回到右心後，經肺動脈到肺泡周圍微血管換氧。</t>
+        </is>
+      </c>
+      <c r="S125" s="5" t="inlineStr">
+        <is>
+          <t>全身缺氧血回到右心後，經肺動脈到肺泡周圍微血管換氧。</t>
+        </is>
+      </c>
+      <c r="T125" s="3"/>
+      <c r="U125" s="3"/>
+      <c r="V125" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W125" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X125" s="3"/>
+    </row>
+    <row r="126" ht="134" hidden="0" customHeight="1">
+      <c r="A126" s="3"/>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-case-q02</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】午餐吸收的養分先送到哪個器官？</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>腎臟</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>肺臟</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>心肌</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O126" s="5" t="inlineStr">
+        <is>
+          <t>消化道吸收的養分先經肝門靜脈送入肝臟處理。</t>
+        </is>
+      </c>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>「午餐養分、肝門脈」：回想消化道與全身循環之間的特殊路線。</t>
+        </is>
+      </c>
+      <c r="Q126" s="5" t="inlineStr">
+        <is>
+          <t>消化道吸收的養分會先經肝門靜脈嗎？→ 這條血管先送到哪個器官？</t>
+        </is>
+      </c>
+      <c r="R126" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肝臟」。消化道吸收的養分先經肝門靜脈送入肝臟處理。</t>
+        </is>
+      </c>
+      <c r="S126" s="5" t="inlineStr">
+        <is>
+          <t>消化道吸收的養分先經肝門靜脈送入肝臟處理。</t>
+        </is>
+      </c>
+      <c r="T126" s="3"/>
+      <c r="U126" s="3"/>
+      <c r="V126" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W126" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X126" s="3"/>
+    </row>
+    <row r="127" ht="134" hidden="0" customHeight="1">
+      <c r="A127" s="3"/>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-case-q03</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】滋養心肌的專屬循環稱為？</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>體循環</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>冠狀循環</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>肝門脈循環</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>肺循環</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>冠狀循環由冠狀動脈供應心肌，靜脈血經冠狀靜脈竇回右心房。</t>
+        </is>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>「心肌本身、專屬供血」：找從升主動脈根部出發的支線。</t>
+        </is>
+      </c>
+      <c r="Q127" s="5" t="inlineStr">
+        <is>
+          <t>心腔內有血就能取代心肌自己的血液供應嗎？→ 哪條循環從升主動脈根部供應心肌？</t>
+        </is>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
+        <is>
+          <t>選擇「冠狀循環」。冠狀循環由冠狀動脈供應心肌，靜脈血經冠狀靜脈竇回右心房。</t>
+        </is>
+      </c>
+      <c r="S127" s="5" t="inlineStr">
+        <is>
+          <t>冠狀循環由冠狀動脈供應心肌，靜脈血經冠狀靜脈竇回右心房。</t>
+        </is>
+      </c>
+      <c r="T127" s="3"/>
+      <c r="U127" s="3"/>
+      <c r="V127" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W127" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X127" s="3"/>
+    </row>
+    <row r="128" ht="134" hidden="0" customHeight="1">
+      <c r="A128" s="3"/>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-case-q04</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】哪個循環壓力較低以保護肺泡？</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>肝門脈循環</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>體循環</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>肺循環</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>冠狀循環</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O128" s="5" t="inlineStr">
+        <is>
+          <t>肺循環壓力與阻力較低，有助保護薄的肺泡微血管。</t>
+        </is>
+      </c>
+      <c r="P128" s="5" t="inlineStr">
+        <is>
+          <t>「保護肺泡、低阻力」：比較肺與全身迴路的阻力。</t>
+        </is>
+      </c>
+      <c r="Q128" s="5" t="inlineStr">
+        <is>
+          <t>全身迴路與肺迴路哪個阻力較低？→ 薄的肺泡微血管需要較高還是較低壓力？</t>
+        </is>
+      </c>
+      <c r="R128" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肺循環」。肺循環壓力與阻力較低，有助保護薄的肺泡微血管。</t>
+        </is>
+      </c>
+      <c r="S128" s="5" t="inlineStr">
+        <is>
+          <t>肺循環壓力與阻力較低，有助保護薄的肺泡微血管。</t>
+        </is>
+      </c>
+      <c r="T128" s="3"/>
+      <c r="U128" s="3"/>
+      <c r="V128" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W128" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X128" s="3"/>
+    </row>
+    <row r="129" ht="134" hidden="0" customHeight="1">
+      <c r="A129" s="3"/>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>circulation-routes-case-q05</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】出生後動脈導管閉鎖會形成？</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>動脈韌帶</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>卵圓窩</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>冠狀靜脈竇</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>靜脈韌帶</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="5" t="inlineStr">
+        <is>
+          <t>動脈導管出生後閉鎖形成動脈韌帶；卵圓孔則留下卵圓窩。</t>
+        </is>
+      </c>
+      <c r="P129" s="5" t="inlineStr">
+        <is>
+          <t>「動脈導管、出生後遺跡」：回想它原本連接肺動脈幹與主動脈；出生後這條旁路不再需要。</t>
+        </is>
+      </c>
+      <c r="Q129" s="5" t="inlineStr">
+        <is>
+          <t>肺開始換氣後還需要這條繞肺旁路嗎？→ 動脈導管閉鎖後留下哪種韌帶？</t>
+        </is>
+      </c>
+      <c r="R129" s="5" t="inlineStr">
+        <is>
+          <t>選擇「動脈韌帶」。動脈導管出生後閉鎖形成動脈韌帶；卵圓孔則留下卵圓窩。</t>
+        </is>
+      </c>
+      <c r="S129" s="5" t="inlineStr">
+        <is>
+          <t>動脈導管出生後閉鎖形成動脈韌帶；卵圓孔則留下卵圓窩。</t>
+        </is>
+      </c>
+      <c r="T129" s="3"/>
+      <c r="U129" s="3"/>
+      <c r="V129" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="W129" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/circulation-routes-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X129" s="3"/>
+    </row>
+    <row r="130" ht="150" hidden="0" customHeight="1">
+      <c r="A130" s="3"/>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-foundation-1</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>血壓升高後，壓力受器反射的方向是？</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>只增加腎素</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>交感上升、心率上升</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>受器完全停止放電</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>交感下降、心率下降</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O130" s="5" t="inlineStr">
+        <is>
+          <t>伸展增加使受器放電增加，經延腦使心率及血管收縮作用下降。</t>
+        </is>
+      </c>
+      <c r="P130" s="5" t="inlineStr">
+        <is>
+          <t>「血壓升高、伸展、負回饋」：先比較血壓與受器伸展。</t>
+        </is>
+      </c>
+      <c r="Q130" s="5" t="inlineStr">
+        <is>
+          <t>伸展增加會使受器放電增加嗎？→ 延腦整合後要降低還是加強交感作用？→ 心率如何變？</t>
+        </is>
+      </c>
+      <c r="R130" s="5" t="inlineStr">
+        <is>
+          <t>選擇「交感下降、心率下降」。伸展增加使受器放電增加，經延腦使心率及血管收縮作用下降。</t>
+        </is>
+      </c>
+      <c r="S130" s="5" t="inlineStr">
+        <is>
+          <t>伸展增加使受器放電增加，經延腦使心率及血管收縮作用下降。</t>
+        </is>
+      </c>
+      <c r="T130" s="3"/>
+      <c r="U130" s="3"/>
+      <c r="V130" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W130" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X130" s="3"/>
+    </row>
+    <row r="131" ht="150" hidden="0" customHeight="1">
+      <c r="A131" s="3"/>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-foundation-2</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>化學受器主要感測哪一組變化？</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>淋巴瓣膜開關</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>O₂、CO₂、H⁺</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>紅血球形狀、血小板數</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>血管長度、體重</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" s="5" t="inlineStr">
+        <is>
+          <t>化學受器監測氣體與酸鹼變化，不是血管長度。</t>
+        </is>
+      </c>
+      <c r="P131" s="5" t="inlineStr">
+        <is>
+          <t>「氣體、酸鹼、化學訊號」：分清機械伸展與化學訊號。</t>
+        </is>
+      </c>
+      <c r="Q131" s="5" t="inlineStr">
+        <is>
+          <t>受器監測的是機械伸展還是血中化學成分？→ 氧氣、二氧化碳與氫離子屬哪一類？</t>
+        </is>
+      </c>
+      <c r="R131" s="5" t="inlineStr">
+        <is>
+          <t>選擇「O₂、CO₂、H⁺」。化學受器監測氣體與酸鹼變化，不是血管長度。</t>
+        </is>
+      </c>
+      <c r="S131" s="5" t="inlineStr">
+        <is>
+          <t>化學受器監測氣體與酸鹼變化，不是血管長度。</t>
+        </is>
+      </c>
+      <c r="T131" s="3"/>
+      <c r="U131" s="3"/>
+      <c r="V131" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W131" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X131" s="3"/>
+    </row>
+    <row r="132" ht="150" hidden="0" customHeight="1">
+      <c r="A132" s="3"/>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-foundation-3</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>腎素主要由哪裡釋放？</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>腦下垂體後葉</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>肝臟肝細胞</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>腎臟近腎絲球細胞</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>心房肌細胞</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O132" s="5" t="inlineStr">
+        <is>
+          <t>腎臟釋放腎素；肝臟提供血管張力素原。</t>
+        </is>
+      </c>
+      <c r="P132" s="5" t="inlineStr">
+        <is>
+          <t>「腎素、RAAS 起點」：回想 RAAS 最前端。</t>
+        </is>
+      </c>
+      <c r="Q132" s="5" t="inlineStr">
+        <is>
+          <t>RAAS 起點要釋放的是腎素還是醛固酮？→ 腎臟哪類細胞負責釋放腎素？</t>
+        </is>
+      </c>
+      <c r="R132" s="5" t="inlineStr">
+        <is>
+          <t>選擇「腎臟近腎絲球細胞」。腎臟釋放腎素；肝臟提供血管張力素原。</t>
+        </is>
+      </c>
+      <c r="S132" s="5" t="inlineStr">
+        <is>
+          <t>腎臟釋放腎素；肝臟提供血管張力素原。</t>
+        </is>
+      </c>
+      <c r="T132" s="3"/>
+      <c r="U132" s="3"/>
+      <c r="V132" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W132" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X132" s="3"/>
+    </row>
+    <row r="133" ht="150" hidden="0" customHeight="1">
+      <c r="A133" s="3"/>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-foundation-4</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>ADH 對腎臟的主要作用是？</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>增加水再吸收</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>阻止所有鈉再吸收</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>直接製造紅血球</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>製造血管張力素原</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" s="5" t="inlineStr">
+        <is>
+          <t>ADH 促進集合管水再吸收，減少水分流失。</t>
+        </is>
+      </c>
+      <c r="P133" s="5" t="inlineStr">
+        <is>
+          <t>「ADH、水再吸收」：看水分留在體內或尿中。</t>
+        </is>
+      </c>
+      <c r="Q133" s="5" t="inlineStr">
+        <is>
+          <t>ADH 使水留在體內還是排到尿中？→ 集合管的水再吸收因此增加還是減少？</t>
+        </is>
+      </c>
+      <c r="R133" s="5" t="inlineStr">
+        <is>
+          <t>選擇「增加水再吸收」。ADH 促進集合管水再吸收，減少水分流失。</t>
+        </is>
+      </c>
+      <c r="S133" s="5" t="inlineStr">
+        <is>
+          <t>ADH 促進集合管水再吸收，減少水分流失。</t>
+        </is>
+      </c>
+      <c r="T133" s="3"/>
+      <c r="U133" s="3"/>
+      <c r="V133" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W133" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X133" s="3"/>
+    </row>
+    <row r="134" ht="150" hidden="0" customHeight="1">
+      <c r="A134" s="3"/>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-foundation-5</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>ANP 的主要方向是？</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>增加腎素釋放</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>直接增加血比容</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>增加保鈉留水</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>促進排鈉排水</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O134" s="5" t="inlineStr">
+        <is>
+          <t>ANP 協助排出鈉與水，與保留體液方向相對。</t>
+        </is>
+      </c>
+      <c r="P134" s="5" t="inlineStr">
+        <is>
+          <t>「ANP、排鈉排水」：把它與 RAAS 對照。</t>
+        </is>
+      </c>
+      <c r="Q134" s="5" t="inlineStr">
+        <is>
+          <t>心房伸展反映體液增加嗎？→ ANP 要協助保留還是排出鈉與水？</t>
+        </is>
+      </c>
+      <c r="R134" s="5" t="inlineStr">
+        <is>
+          <t>選擇「促進排鈉排水」。ANP 協助排出鈉與水，與保留體液方向相對。</t>
+        </is>
+      </c>
+      <c r="S134" s="5" t="inlineStr">
+        <is>
+          <t>ANP 協助排出鈉與水，與保留體液方向相對。</t>
+        </is>
+      </c>
+      <c r="T134" s="3"/>
+      <c r="U134" s="3"/>
+      <c r="V134" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W134" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X134" s="3"/>
+    </row>
+    <row r="135" ht="150" hidden="0" customHeight="1">
+      <c r="A135" s="3"/>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-foundation-6</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>其他條件固定，CO 與 TPR 都增加，MAP 趨勢為何？</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>必定不變</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>必定為零</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" s="5" t="inlineStr">
+        <is>
+          <t>在此近似模型中，兩者增加使 MAP 增加。</t>
+        </is>
+      </c>
+      <c r="P135" s="5" t="inlineStr">
+        <is>
+          <t>「CO、TPR、乘積」：使用兩個變因的乘積。</t>
+        </is>
+      </c>
+      <c r="Q135" s="5" t="inlineStr">
+        <is>
+          <t>MAP 近似哪兩個變因的乘積？→ 兩個因子都增加，乘積會增加還是減少？</t>
+        </is>
+      </c>
+      <c r="R135" s="5" t="inlineStr">
+        <is>
+          <t>選擇「增加」。在此近似模型中，兩者增加使 MAP 增加。</t>
+        </is>
+      </c>
+      <c r="S135" s="5" t="inlineStr">
+        <is>
+          <t>在此近似模型中，兩者增加使 MAP 增加。</t>
+        </is>
+      </c>
+      <c r="T135" s="3"/>
+      <c r="U135" s="3"/>
+      <c r="V135" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W135" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X135" s="3"/>
+    </row>
+    <row r="136" ht="150" hidden="0" customHeight="1">
+      <c r="A136" s="3"/>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-case-1</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】站起時血壓短暫下降，壓力受器反射會如何回應？</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>迷走增加，使心率更慢</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>受器放電增加</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>交感增加，協助血壓回升</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>ANP 是唯一即時反應</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O136" s="5" t="inlineStr">
+        <is>
+          <t>血壓下降使受器放電減少，反射性增加交感作用。</t>
+        </is>
+      </c>
+      <c r="P136" s="5" t="inlineStr">
+        <is>
+          <t>「站起、血壓下降、反射」：比較低血壓時的放電方向。</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr">
+        <is>
+          <t>血壓下降使壓力受器伸展與放電增多還是減少？→ 交感反應要怎樣協助血壓回升？</t>
+        </is>
+      </c>
+      <c r="R136" s="5" t="inlineStr">
+        <is>
+          <t>選擇「交感增加，協助血壓回升」。血壓下降使受器放電減少，反射性增加交感作用。</t>
+        </is>
+      </c>
+      <c r="S136" s="5" t="inlineStr">
+        <is>
+          <t>血壓下降使受器放電減少，反射性增加交感作用。</t>
+        </is>
+      </c>
+      <c r="T136" s="3"/>
+      <c r="U136" s="3"/>
+      <c r="V136" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W136" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X136" s="3"/>
+    </row>
+    <row r="137" ht="150" hidden="0" customHeight="1">
+      <c r="A137" s="3"/>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-case-2</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】動脈血 O₂ 降低且 CO₂、H⁺ 增加，哪種受器最直接感測？</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>化學受器</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>淋巴瓣膜</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>腎集合管</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>心房伸展受器</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" s="5" t="inlineStr">
+        <is>
+          <t>氣體與酸鹼變化屬化學受器刺激，不把一般運動等同這個模型。</t>
+        </is>
+      </c>
+      <c r="P137" s="5" t="inlineStr">
+        <is>
+          <t>「O₂ 下降、CO₂ 與 H⁺ 增加」：辨識刺激類型。</t>
+        </is>
+      </c>
+      <c r="Q137" s="5" t="inlineStr">
+        <is>
+          <t>刺激是管壁伸展還是氣體與酸鹼變化？→ 哪種受器直接監測這些化學變化？</t>
+        </is>
+      </c>
+      <c r="R137" s="5" t="inlineStr">
+        <is>
+          <t>選擇「化學受器」。氣體與酸鹼變化屬化學受器刺激，不把一般運動等同這個模型。</t>
+        </is>
+      </c>
+      <c r="S137" s="5" t="inlineStr">
+        <is>
+          <t>氣體與酸鹼變化屬化學受器刺激，不把一般運動等同這個模型。</t>
+        </is>
+      </c>
+      <c r="T137" s="3"/>
+      <c r="U137" s="3"/>
+      <c r="V137" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W137" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X137" s="3"/>
+    </row>
+    <row r="138" ht="150" hidden="0" customHeight="1">
+      <c r="A138" s="3"/>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-case-3</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】腎灌流下降後，RAAS 的第一個釋放步驟是？</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>肝臟釋放醛固酮</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>心房釋放 ACE</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>後葉釋放血管張力素原</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>腎臟釋放腎素</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O138" s="5" t="inlineStr">
+        <is>
+          <t>腎素作用於血管張力素原，後續形成 II。</t>
+        </is>
+      </c>
+      <c r="P138" s="5" t="inlineStr">
+        <is>
+          <t>「腎灌流下降、第一步」：從反應鏈起點找。</t>
+        </is>
+      </c>
+      <c r="Q138" s="5" t="inlineStr">
+        <is>
+          <t>先啟動 RAAS 的訊號是什麼？→ 腎臟最先釋放腎素還是直接釋放醛固酮？</t>
+        </is>
+      </c>
+      <c r="R138" s="5" t="inlineStr">
+        <is>
+          <t>選擇「腎臟釋放腎素」。腎素作用於血管張力素原，後續形成 II。</t>
+        </is>
+      </c>
+      <c r="S138" s="5" t="inlineStr">
+        <is>
+          <t>腎素作用於血管張力素原，後續形成 II。</t>
+        </is>
+      </c>
+      <c r="T138" s="3"/>
+      <c r="U138" s="3"/>
+      <c r="V138" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W138" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X138" s="3"/>
+    </row>
+    <row r="139" ht="150" hidden="0" customHeight="1">
+      <c r="A139" s="3"/>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-case-4</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】心房伸展增加後，哪個作用有助降低過多血容量？</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>腎素必定增加</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>ANP 促進排鈉排水</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮增加鈉保留</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>ADH 增加水保留</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" s="5" t="inlineStr">
+        <is>
+          <t>ANP 是心房來源的排鈉胜肽。</t>
+        </is>
+      </c>
+      <c r="P139" s="5" t="inlineStr">
+        <is>
+          <t>「心房伸展、降低過多血容量」：比較保留與排出兩個方向。</t>
+        </is>
+      </c>
+      <c r="Q139" s="5" t="inlineStr">
+        <is>
+          <t>要減少血容量，應保留還是排出鈉水？→ 哪個心房來源激素促進排出？</t>
+        </is>
+      </c>
+      <c r="R139" s="5" t="inlineStr">
+        <is>
+          <t>選擇「ANP 促進排鈉排水」。ANP 是心房來源的排鈉胜肽。</t>
+        </is>
+      </c>
+      <c r="S139" s="5" t="inlineStr">
+        <is>
+          <t>ANP 是心房來源的排鈉胜肽。</t>
+        </is>
+      </c>
+      <c r="T139" s="3"/>
+      <c r="U139" s="3"/>
+      <c r="V139" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W139" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X139" s="3"/>
+    </row>
+    <row r="140" ht="182" hidden="0" customHeight="1">
+      <c r="A140" s="3"/>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-regulation-case-5</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】動脈血壓短暫上升，使頸動脈竇伸展增加，壓力受器反射的方向為何？</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>受器放電停止，血管持續收縮</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>受器放電增加，交感作用增加</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>受器放電增加，心率下降</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>受器放電減少，心率增加</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" s="5" t="inlineStr">
+        <is>
+          <t>血壓升高使壓力受器放電增加，延腦整合後降低交感、增加心臟迷走作用，使心率下降並促進小動脈舒張。</t>
+        </is>
+      </c>
+      <c r="P140" s="5" t="inlineStr">
+        <is>
+          <t>「頸動脈竇、伸展增加」：先比較伸展與受器放電，再追蹤負回饋的方向。</t>
+        </is>
+      </c>
+      <c r="Q140" s="5" t="inlineStr">
+        <is>
+          <t>血壓上升會使受器放電增加還是減少？→ 負回饋會讓交感與心率上升還是下降？</t>
+        </is>
+      </c>
+      <c r="R140" s="5" t="inlineStr">
+        <is>
+          <t>選擇「受器放電增加，心率下降」。血壓升高使壓力受器放電增加，延腦整合後降低交感、增加心臟迷走作用，使心率下降並促進小動脈舒張。</t>
+        </is>
+      </c>
+      <c r="S140" s="5" t="inlineStr">
+        <is>
+          <t>血壓升高使壓力受器放電增加，延腦整合後降低交感、增加心臟迷走作用，使心率下降並促進小動脈舒張。</t>
+        </is>
+      </c>
+      <c r="T140" s="3"/>
+      <c r="U140" s="3"/>
+      <c r="V140" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="W140" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-regulation-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X140" s="3"/>
+    </row>
+    <row r="141" ht="134" hidden="0" customHeight="1">
+      <c r="A141" s="3"/>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-foundation-1</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>淋巴直接由哪一種液體進入淋巴微管形成？</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>組織液</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>細胞內液</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>尿液</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>動脈內全部血液</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" s="5" t="inlineStr">
+        <is>
+          <t>組織液進入淋巴微管後稱為淋巴。</t>
+        </is>
+      </c>
+      <c r="P141" s="5" t="inlineStr">
+        <is>
+          <t>「組織間隙、淋巴微管」：看液體位於哪個空間。</t>
+        </is>
+      </c>
+      <c r="Q141" s="5" t="inlineStr">
+        <is>
+          <t>液體原本位在細胞內還是組織間隙？→ 進入淋巴微管後改稱什麼？</t>
+        </is>
+      </c>
+      <c r="R141" s="5" t="inlineStr">
+        <is>
+          <t>選擇「組織液」。組織液進入淋巴微管後稱為淋巴。</t>
+        </is>
+      </c>
+      <c r="S141" s="5" t="inlineStr">
+        <is>
+          <t>組織液進入淋巴微管後稱為淋巴。</t>
+        </is>
+      </c>
+      <c r="T141" s="3"/>
+      <c r="U141" s="3"/>
+      <c r="V141" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W141" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X141" s="3"/>
+    </row>
+    <row r="142" ht="134" hidden="0" customHeight="1">
+      <c r="A142" s="3"/>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-foundation-2</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>健康淋巴的敘述何者合理？</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>完全不含任何蛋白質</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>必定含大量紅血球</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>組成在所有部位完全相同</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>可含蛋白質，通常無紅血球</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" s="5" t="inlineStr">
+        <is>
+          <t>淋巴回收水與蛋白質，組成因部位不同。</t>
+        </is>
+      </c>
+      <c r="P142" s="5" t="inlineStr">
+        <is>
+          <t>「蛋白質、紅血球、部位差異」：回想回收的內容與區域差異。</t>
+        </is>
+      </c>
+      <c r="Q142" s="5" t="inlineStr">
+        <is>
+          <t>淋巴會回收組織液中的蛋白質嗎？→ 健康淋巴通常有大量紅血球嗎？→ 組成是否因部位而異？</t>
+        </is>
+      </c>
+      <c r="R142" s="5" t="inlineStr">
+        <is>
+          <t>選擇「可含蛋白質，通常無紅血球」。淋巴回收水與蛋白質，組成因部位不同。</t>
+        </is>
+      </c>
+      <c r="S142" s="5" t="inlineStr">
+        <is>
+          <t>淋巴回收水與蛋白質，組成因部位不同。</t>
+        </is>
+      </c>
+      <c r="T142" s="3"/>
+      <c r="U142" s="3"/>
+      <c r="V142" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W142" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X142" s="3"/>
+    </row>
+    <row r="143" ht="134" hidden="0" customHeight="1">
+      <c r="A143" s="3"/>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-foundation-3</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>何者不是淋巴前進的直接動力？</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>呼吸壓差</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>左心室直接泵入淋巴管</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>骨骼肌擠壓</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>集淋巴管壁收縮</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統沒有由左心室直接泵送的中央泵。</t>
+        </is>
+      </c>
+      <c r="P143" s="5" t="inlineStr">
+        <is>
+          <t>「不是動力、血管與淋巴管」：分清血管與淋巴管。</t>
+        </is>
+      </c>
+      <c r="Q143" s="5" t="inlineStr">
+        <is>
+          <t>骨骼肌、管壁收縮與呼吸壓差能推進淋巴嗎？→ 左心室是否直接把血液泵入淋巴管？</t>
+        </is>
+      </c>
+      <c r="R143" s="5" t="inlineStr">
+        <is>
+          <t>選擇「左心室直接泵入淋巴管」。淋巴系統沒有由左心室直接泵送的中央泵。</t>
+        </is>
+      </c>
+      <c r="S143" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統沒有由左心室直接泵送的中央泵。</t>
+        </is>
+      </c>
+      <c r="T143" s="3"/>
+      <c r="U143" s="3"/>
+      <c r="V143" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W143" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X143" s="3"/>
+    </row>
+    <row r="144" ht="134" hidden="0" customHeight="1">
+      <c r="A144" s="3"/>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-foundation-4</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>左下肢的淋巴最後主要經哪條管？</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>主動脈</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>胸管</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>右淋巴管</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" s="5" t="inlineStr">
+        <is>
+          <t>兩側下肢皆屬胸管引流範圍。</t>
+        </is>
+      </c>
+      <c r="P144" s="5" t="inlineStr">
+        <is>
+          <t>「左下肢、引流區域」：先判斷是否屬右上方區域。</t>
+        </is>
+      </c>
+      <c r="Q144" s="5" t="inlineStr">
+        <is>
+          <t>胸管收集兩側下肢嗎？→ 左下肢屬右上方小區域還是胸管的大區域？</t>
+        </is>
+      </c>
+      <c r="R144" s="5" t="inlineStr">
+        <is>
+          <t>選擇「胸管」。兩側下肢皆屬胸管引流範圍。</t>
+        </is>
+      </c>
+      <c r="S144" s="5" t="inlineStr">
+        <is>
+          <t>兩側下肢皆屬胸管引流範圍。</t>
+        </is>
+      </c>
+      <c r="T144" s="3"/>
+      <c r="U144" s="3"/>
+      <c r="V144" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W144" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X144" s="3"/>
+    </row>
+    <row r="145" ht="134" hidden="0" customHeight="1">
+      <c r="A145" s="3"/>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-foundation-5</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>哪個區域主要由右淋巴管引流？</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>右上肢</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>左上肢</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>右下肢</t>
+        </is>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>腹部</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" s="5" t="inlineStr">
+        <is>
+          <t>它引流右頭頸、右上肢和右胸部。</t>
+        </is>
+      </c>
+      <c r="P145" s="5" t="inlineStr">
+        <is>
+          <t>「右淋巴管、右上方區域」：右淋巴管不是整個右半身。</t>
+        </is>
+      </c>
+      <c r="Q145" s="5" t="inlineStr">
+        <is>
+          <t>右淋巴管引流整個右半身嗎？→ 右上肢與右下肢，哪個才屬它的範圍？</t>
+        </is>
+      </c>
+      <c r="R145" s="5" t="inlineStr">
+        <is>
+          <t>選擇「右上肢」。它引流右頭頸、右上肢和右胸部。</t>
+        </is>
+      </c>
+      <c r="S145" s="5" t="inlineStr">
+        <is>
+          <t>它引流右頭頸、右上肢和右胸部。</t>
+        </is>
+      </c>
+      <c r="T145" s="3"/>
+      <c r="U145" s="3"/>
+      <c r="V145" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W145" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X145" s="3"/>
+    </row>
+    <row r="146" ht="134" hidden="0" customHeight="1">
+      <c r="A146" s="3"/>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-foundation-6</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>淋巴結的流入與流出順序為？</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>輸出管→淋巴結→輸入管</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>胸管→紅血球→脾臟</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>動脈→淋巴結→主動脈</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>輸入管→淋巴結→輸出管</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" s="5" t="inlineStr">
+        <is>
+          <t>輸入帶入、輸出帶離；淋巴結過濾淋巴。</t>
+        </is>
+      </c>
+      <c r="P146" s="5" t="inlineStr">
+        <is>
+          <t>「輸入、淋巴結、輸出」：由管名判斷方向。</t>
+        </is>
+      </c>
+      <c r="Q146" s="5" t="inlineStr">
+        <is>
+          <t>哪種管把淋巴帶入淋巴結？→ 過濾後由哪種管帶離？</t>
+        </is>
+      </c>
+      <c r="R146" s="5" t="inlineStr">
+        <is>
+          <t>選擇「輸入管→淋巴結→輸出管」。輸入帶入、輸出帶離；淋巴結過濾淋巴。</t>
+        </is>
+      </c>
+      <c r="S146" s="5" t="inlineStr">
+        <is>
+          <t>輸入帶入、輸出帶離；淋巴結過濾淋巴。</t>
+        </is>
+      </c>
+      <c r="T146" s="3"/>
+      <c r="U146" s="3"/>
+      <c r="V146" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W146" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X146" s="3"/>
+    </row>
+    <row r="147" ht="134" hidden="0" customHeight="1">
+      <c r="A147" s="3"/>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-case-1</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】散步時腿部肌肉反覆收縮，如何幫助淋巴回流？</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>直接把淋巴變成紅血球</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>擠壓淋巴管，瓣膜減少倒流</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>取代所有管壁活動</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>使所有瓣膜永久關閉</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" s="5" t="inlineStr">
+        <is>
+          <t>肌肉擠壓提供動力，瓣膜支持單向流動。</t>
+        </is>
+      </c>
+      <c r="P147" s="5" t="inlineStr">
+        <is>
+          <t>「肌肉擠壓、瓣膜防倒流」：分開推進與防倒流功能。</t>
+        </is>
+      </c>
+      <c r="Q147" s="5" t="inlineStr">
+        <is>
+          <t>肌肉收縮提供推力嗎？→ 瓣膜負責製造淋巴還是減少倒流？</t>
+        </is>
+      </c>
+      <c r="R147" s="5" t="inlineStr">
+        <is>
+          <t>選擇「擠壓淋巴管，瓣膜減少倒流」。肌肉擠壓提供動力，瓣膜支持單向流動。</t>
+        </is>
+      </c>
+      <c r="S147" s="5" t="inlineStr">
+        <is>
+          <t>肌肉擠壓提供動力，瓣膜支持單向流動。</t>
+        </is>
+      </c>
+      <c r="T147" s="3"/>
+      <c r="U147" s="3"/>
+      <c r="V147" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W147" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X147" s="3"/>
+    </row>
+    <row r="148" ht="134" hidden="0" customHeight="1">
+      <c r="A148" s="3"/>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-case-2</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】追蹤右手的淋巴，主要回到哪裡？</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>主動脈→右心室</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>肺動脈→左心房</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>右淋巴管→右靜脈角</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>胸管→左靜脈角</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" s="5" t="inlineStr">
+        <is>
+          <t>右上肢屬右淋巴管引流區。</t>
+        </is>
+      </c>
+      <c r="P148" s="5" t="inlineStr">
+        <is>
+          <t>「人體右手、右靜脈角」：確認人體本身的右側。</t>
+        </is>
+      </c>
+      <c r="Q148" s="5" t="inlineStr">
+        <is>
+          <t>右手屬哪條淋巴管的引流區？→ 那條管最後匯入左還是右靜脈角？</t>
+        </is>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>選擇「右淋巴管→右靜脈角」。右上肢屬右淋巴管引流區。</t>
+        </is>
+      </c>
+      <c r="S148" s="5" t="inlineStr">
+        <is>
+          <t>右上肢屬右淋巴管引流區。</t>
+        </is>
+      </c>
+      <c r="T148" s="3"/>
+      <c r="U148" s="3"/>
+      <c r="V148" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W148" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X148" s="3"/>
+    </row>
+    <row r="149" ht="134" hidden="0" customHeight="1">
+      <c r="A149" s="3"/>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-case-3</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】右腳的淋巴應走哪個主要路徑？</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>胸管→左靜脈角</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>直接進左心室</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>右淋巴管→右靜脈角</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>右上肢→右淋巴管</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" s="5" t="inlineStr">
+        <is>
+          <t>兩側下肢均由胸管回流。</t>
+        </is>
+      </c>
+      <c r="P149" s="5" t="inlineStr">
+        <is>
+          <t>「右腳、兩側下肢」：別把右側所有部位歸同一管。</t>
+        </is>
+      </c>
+      <c r="Q149" s="5" t="inlineStr">
+        <is>
+          <t>右腳是否位在右上方引流區？→ 兩側下肢的淋巴主要經哪條管、哪個靜脈角？</t>
+        </is>
+      </c>
+      <c r="R149" s="5" t="inlineStr">
+        <is>
+          <t>選擇「胸管→左靜脈角」。兩側下肢均由胸管回流。</t>
+        </is>
+      </c>
+      <c r="S149" s="5" t="inlineStr">
+        <is>
+          <t>兩側下肢均由胸管回流。</t>
+        </is>
+      </c>
+      <c r="T149" s="3"/>
+      <c r="U149" s="3"/>
+      <c r="V149" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W149" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X149" s="3"/>
+    </row>
+    <row r="150" ht="134" hidden="0" customHeight="1">
+      <c r="A150" s="3"/>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-case-4</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】吸氣時胸腔壓降低，對淋巴回流有何作用？</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>由肺直接製造淋巴球</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>使淋巴必定逆流</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>讓瓣膜失去作用</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>壓差有助向胸腔回流</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" s="5" t="inlineStr">
+        <is>
+          <t>呼吸造成的壓差支持回流，配合瓣膜維持方向。</t>
+        </is>
+      </c>
+      <c r="P150" s="5" t="inlineStr">
+        <is>
+          <t>「吸氣、胸腔壓降低」：觀察胸腹的壓力方向。</t>
+        </is>
+      </c>
+      <c r="Q150" s="5" t="inlineStr">
+        <is>
+          <t>胸腔壓降低會產生朝胸腔的壓差嗎？→ 配合瓣膜，這個壓差如何幫助回流？</t>
+        </is>
+      </c>
+      <c r="R150" s="5" t="inlineStr">
+        <is>
+          <t>選擇「壓差有助向胸腔回流」。呼吸造成的壓差支持回流，配合瓣膜維持方向。</t>
+        </is>
+      </c>
+      <c r="S150" s="5" t="inlineStr">
+        <is>
+          <t>呼吸造成的壓差支持回流，配合瓣膜維持方向。</t>
+        </is>
+      </c>
+      <c r="T150" s="3"/>
+      <c r="U150" s="3"/>
+      <c r="V150" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W150" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X150" s="3"/>
+    </row>
+    <row r="151" ht="134" hidden="0" customHeight="1">
+      <c r="A151" s="3"/>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>lymphatic-system-case-5</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】T 淋巴球前驅細胞主要在哪裡成熟？</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>右淋巴管</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>胸腺</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>脾臟</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>淋巴結</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在胸腺成熟，B 細胞在骨髓成熟。</t>
+        </is>
+      </c>
+      <c r="P151" s="5" t="inlineStr">
+        <is>
+          <t>「T 淋巴球、成熟而非活化」：區分成熟與免疫活化。</t>
+        </is>
+      </c>
+      <c r="Q151" s="5" t="inlineStr">
+        <is>
+          <t>題目問細胞成熟還是免疫活化？→ T 細胞與 B 細胞的成熟場所是否相同？</t>
+        </is>
+      </c>
+      <c r="R151" s="5" t="inlineStr">
+        <is>
+          <t>選擇「胸腺」。T 細胞在胸腺成熟，B 細胞在骨髓成熟。</t>
+        </is>
+      </c>
+      <c r="S151" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在胸腺成熟，B 細胞在骨髓成熟。</t>
+        </is>
+      </c>
+      <c r="T151" s="3"/>
+      <c r="U151" s="3"/>
+      <c r="V151" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="W151" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphatic-system-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X151" s="3"/>
+    </row>
+    <row r="152" ht="118" hidden="0" customHeight="1">
+      <c r="A152" s="3"/>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-foundation-1</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>固定壓差，阻力變成兩倍，流量如何改變？</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>變成四倍</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>變成兩倍</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>變成一半</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O152" s="5" t="inlineStr">
+        <is>
+          <t>Q = ΔP／R；固定分子，分母加倍使 Q 減半。</t>
+        </is>
+      </c>
+      <c r="P152" s="5" t="inlineStr">
+        <is>
+          <t>「固定壓差、阻力加倍」：流量與阻力是何種關係？</t>
+        </is>
+      </c>
+      <c r="Q152" s="5" t="inlineStr">
+        <is>
+          <t>Q = ΔP／R 中哪個量固定？→ 分母加倍、分子不變，流量變為多少？</t>
+        </is>
+      </c>
+      <c r="R152" s="5" t="inlineStr">
+        <is>
+          <t>選擇「變成一半」。Q = ΔP／R；固定分子，分母加倍使 Q 減半。</t>
+        </is>
+      </c>
+      <c r="S152" s="5" t="inlineStr">
+        <is>
+          <t>Q = ΔP／R；固定分子，分母加倍使 Q 減半。</t>
+        </is>
+      </c>
+      <c r="T152" s="3"/>
+      <c r="U152" s="3"/>
+      <c r="V152" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W152" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X152" s="3"/>
+    </row>
+    <row r="153" ht="118" hidden="0" customHeight="1">
+      <c r="A153" s="3"/>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-foundation-2</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>理想圓管模型中，半徑加倍，阻力變為？</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>1／16</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>16 倍</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>2 倍</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>1／2</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" s="5" t="inlineStr">
+        <is>
+          <t>R 與 r⁴ 成反比；2⁴ = 16。</t>
+        </is>
+      </c>
+      <c r="P153" s="5" t="inlineStr">
+        <is>
+          <t>「半徑加倍、四次方反比」：先算半徑的四次方。</t>
+        </is>
+      </c>
+      <c r="Q153" s="5" t="inlineStr">
+        <is>
+          <t>2 的四次方是多少？→ 阻力與半徑四次方成反比，阻力應乘以還是除以 16？</t>
+        </is>
+      </c>
+      <c r="R153" s="5" t="inlineStr">
+        <is>
+          <t>選擇「1／16」。R 與 r⁴ 成反比；2⁴ = 16。</t>
+        </is>
+      </c>
+      <c r="S153" s="5" t="inlineStr">
+        <is>
+          <t>R 與 r⁴ 成反比；2⁴ = 16。</t>
+        </is>
+      </c>
+      <c r="T153" s="3"/>
+      <c r="U153" s="3"/>
+      <c r="V153" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W153" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X153" s="3"/>
+    </row>
+    <row r="154" ht="118" hidden="0" customHeight="1">
+      <c r="A154" s="3"/>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-foundation-3</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>血比容描述哪個比例？</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>血漿蛋白／血漿</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>全部白血球／全血</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>血小板數／紅血球數</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>紅血球體積／全血體積</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" s="5" t="inlineStr">
+        <is>
+          <t>血比容測紅血球佔全血體積比例。</t>
+        </is>
+      </c>
+      <c r="P154" s="5" t="inlineStr">
+        <is>
+          <t>「血比容、體積比例」：注意分子是什麼。</t>
+        </is>
+      </c>
+      <c r="Q154" s="5" t="inlineStr">
+        <is>
+          <t>分子是紅血球體積還是所有血球數？→ 分母是血漿還是全血體積？</t>
+        </is>
+      </c>
+      <c r="R154" s="5" t="inlineStr">
+        <is>
+          <t>選擇「紅血球體積／全血體積」。血比容測紅血球佔全血體積比例。</t>
+        </is>
+      </c>
+      <c r="S154" s="5" t="inlineStr">
+        <is>
+          <t>血比容測紅血球佔全血體積比例。</t>
+        </is>
+      </c>
+      <c r="T154" s="3"/>
+      <c r="U154" s="3"/>
+      <c r="V154" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W154" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X154" s="3"/>
+    </row>
+    <row r="155" ht="118" hidden="0" customHeight="1">
+      <c r="A155" s="3"/>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-foundation-4</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>總流量相同時，哪一處因總截面積大而平均流速慢？</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>單一主動脈</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>微血管床</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>所有位置必定相同</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>單一小動脈</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
+          <t>微血管數目多，總截面積大，平均速度低。</t>
+        </is>
+      </c>
+      <c r="P155" s="5" t="inlineStr">
+        <is>
+          <t>「總流量相同、總截面積」：比較整組血管，不是單一管徑。</t>
+        </is>
+      </c>
+      <c r="Q155" s="5" t="inlineStr">
+        <is>
+          <t>平均流速 v = Q／A 嗎？→ 很多微血管的面積加總後變大，速度如何變？</t>
+        </is>
+      </c>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>選擇「微血管床」。微血管數目多，總截面積大，平均速度低。</t>
+        </is>
+      </c>
+      <c r="S155" s="5" t="inlineStr">
+        <is>
+          <t>微血管數目多，總截面積大，平均速度低。</t>
+        </is>
+      </c>
+      <c r="T155" s="3"/>
+      <c r="U155" s="3"/>
+      <c r="V155" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W155" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X155" s="3"/>
+    </row>
+    <row r="156" ht="118" hidden="0" customHeight="1">
+      <c r="A156" s="3"/>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-foundation-5</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>理想層流中何處速度較快？</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>整個截面完全一樣</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>只有出口</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>管中央</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>緊貼管壁</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O156" s="5" t="inlineStr">
+        <is>
+          <t>管中央較快，靠近管壁較慢。</t>
+        </is>
+      </c>
+      <c r="P156" s="5" t="inlineStr">
+        <is>
+          <t>「理想層流、管中央」：回想流層與管壁的關係。</t>
+        </is>
+      </c>
+      <c r="Q156" s="5" t="inlineStr">
+        <is>
+          <t>緊貼管壁的流層受阻較大嗎？→ 管中央與管壁哪裡較快？</t>
+        </is>
+      </c>
+      <c r="R156" s="5" t="inlineStr">
+        <is>
+          <t>選擇「管中央」。管中央較快，靠近管壁較慢。</t>
+        </is>
+      </c>
+      <c r="S156" s="5" t="inlineStr">
+        <is>
+          <t>管中央較快，靠近管壁較慢。</t>
+        </is>
+      </c>
+      <c r="T156" s="3"/>
+      <c r="U156" s="3"/>
+      <c r="V156" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W156" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X156" s="3"/>
+    </row>
+    <row r="157" ht="166" hidden="0" customHeight="1">
+      <c r="A157" s="3"/>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-foundation-6</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>靜息模型血壓 120／80，脈壓與估算 MAP 為？</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>40、約 93 mmHg</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>80、約 93 mmHg</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>40、約 100 mmHg</t>
+        </is>
+      </c>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>120、約 80 mmHg</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
+          <t>PP = 120 − 80 = 40 mmHg；MAP ≈ 80 + 40／3 ≈ 93 mmHg，不是收縮壓與舒張壓的簡單算術平均。</t>
+        </is>
+      </c>
+      <c r="P157" s="5" t="inlineStr">
+        <is>
+          <t>「120／80、脈壓、MAP」：先相減，再使用舒張壓加三分之一脈壓。</t>
+        </is>
+      </c>
+      <c r="Q157" s="5" t="inlineStr">
+        <is>
+          <t>120 − 80 等於多少？→ 舒張壓加三分之一脈壓為多少？→ 是否等於兩個壓力的簡單平均？</t>
+        </is>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>選擇「40、約 93 mmHg」。PP = 120 − 80 = 40 mmHg；MAP ≈ 80 + 40／3 ≈ 93 mmHg，不是收縮壓與舒張壓的簡單算術平均。</t>
+        </is>
+      </c>
+      <c r="S157" s="5" t="inlineStr">
+        <is>
+          <t>PP = 120 − 80 = 40 mmHg；MAP ≈ 80 + 40／3 ≈ 93 mmHg，不是收縮壓與舒張壓的簡單算術平均。</t>
+        </is>
+      </c>
+      <c r="T157" s="3"/>
+      <c r="U157" s="3"/>
+      <c r="V157" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W157" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X157" s="3"/>
+    </row>
+    <row r="158" ht="118" hidden="0" customHeight="1">
+      <c r="A158" s="3"/>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-case-1</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】紅血球體積比例升高，其他條件固定，流量傾向？</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>必定不變</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>必定增加16倍</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" s="5" t="inlineStr">
+        <is>
+          <t>黏度與阻力通常增加，固定壓差時流量減少。</t>
+        </is>
+      </c>
+      <c r="P158" s="5" t="inlineStr">
+        <is>
+          <t>「血比容升高、黏度、阻力」：串連血比容、黏度、阻力。</t>
+        </is>
+      </c>
+      <c r="Q158" s="5" t="inlineStr">
+        <is>
+          <t>紅血球體積比例升高，黏度通常如何變？→ 阻力增加、壓差固定時流量如何變？</t>
+        </is>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>選擇「減少」。黏度與阻力通常增加，固定壓差時流量減少。</t>
+        </is>
+      </c>
+      <c r="S158" s="5" t="inlineStr">
+        <is>
+          <t>黏度與阻力通常增加，固定壓差時流量減少。</t>
+        </is>
+      </c>
+      <c r="T158" s="3"/>
+      <c r="U158" s="3"/>
+      <c r="V158" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W158" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X158" s="3"/>
+    </row>
+    <row r="159" ht="118" hidden="0" customHeight="1">
+      <c r="A159" s="3"/>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-case-2</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】理想圓管半徑減半，固定其他條件，阻力為？</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>1／2</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>16 倍</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>2 倍</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>1／16</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>R ∝ 1／r⁴；半徑減半使 R 增加16倍。</t>
+        </is>
+      </c>
+      <c r="P159" s="5" t="inlineStr">
+        <is>
+          <t>「半徑減半、阻力反比四次方」：倒數再取四次方。</t>
+        </is>
+      </c>
+      <c r="Q159" s="5" t="inlineStr">
+        <is>
+          <t>半徑變為一半，四次方變為多少？→ 取倒數後阻力變為幾倍？</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>選擇「16 倍」。R ∝ 1／r⁴；半徑減半使 R 增加16倍。</t>
+        </is>
+      </c>
+      <c r="S159" s="5" t="inlineStr">
+        <is>
+          <t>R ∝ 1／r⁴；半徑減半使 R 增加16倍。</t>
+        </is>
+      </c>
+      <c r="T159" s="3"/>
+      <c r="U159" s="3"/>
+      <c r="V159" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W159" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X159" s="3"/>
+    </row>
+    <row r="160" ht="118" hidden="0" customHeight="1">
+      <c r="A160" s="3"/>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-case-3</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】分支總截面積加倍，總流量不變，平均流速為？</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>十六倍</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>四倍</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>一半</t>
+        </is>
+      </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>兩倍</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O160" s="5" t="inlineStr">
+        <is>
+          <t>流量固定、總截面積加倍使平均流速減半。</t>
+        </is>
+      </c>
+      <c r="P160" s="5" t="inlineStr">
+        <is>
+          <t>「分支總截面積加倍、Q 固定」：使用 v = Q／A。</t>
+        </is>
+      </c>
+      <c r="Q160" s="5" t="inlineStr">
+        <is>
+          <t>用的是單根面積還是分支總面積？→ v = Q／A 的分母加倍時，平均速度如何變？</t>
+        </is>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>選擇「一半」。流量固定、總截面積加倍使平均流速減半。</t>
+        </is>
+      </c>
+      <c r="S160" s="5" t="inlineStr">
+        <is>
+          <t>流量固定、總截面積加倍使平均流速減半。</t>
+        </is>
+      </c>
+      <c r="T160" s="3"/>
+      <c r="U160" s="3"/>
+      <c r="V160" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W160" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X160" s="3"/>
+    </row>
+    <row r="161" ht="118" hidden="0" customHeight="1">
+      <c r="A161" s="3"/>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-case-4</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】管路突然變徑且速度升高，哪種流動較可能出現？</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>擾流</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>所有流層同速</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="inlineStr">
+        <is>
+          <t>必定完全靜止</t>
+        </is>
+      </c>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>只能保持理想層流</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" s="5" t="inlineStr">
+        <is>
+          <t>高速與幾何變化會增加擾流的可能；擾流的流線不像層流那樣平順。</t>
+        </is>
+      </c>
+      <c r="P161" s="5" t="inlineStr">
+        <is>
+          <t>「突然變徑、高速、流線」：觀察流線是否仍然平順。</t>
+        </is>
+      </c>
+      <c r="Q161" s="5" t="inlineStr">
+        <is>
+          <t>理想層流的流線平順嗎？→ 高速與幾何變化會使擾流更容易還是更不容易出現？</t>
+        </is>
+      </c>
+      <c r="R161" s="5" t="inlineStr">
+        <is>
+          <t>選擇「擾流」。高速與幾何變化會增加擾流的可能；擾流的流線不像層流那樣平順。</t>
+        </is>
+      </c>
+      <c r="S161" s="5" t="inlineStr">
+        <is>
+          <t>高速與幾何變化會增加擾流的可能；擾流的流線不像層流那樣平順。</t>
+        </is>
+      </c>
+      <c r="T161" s="3"/>
+      <c r="U161" s="3"/>
+      <c r="V161" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W161" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X161" s="3"/>
+    </row>
+    <row r="162" ht="118" hidden="0" customHeight="1">
+      <c r="A162" s="3"/>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>hemodynamics-case-5</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】TPR 固定，CO 減少，MAP 趨勢如何？</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>變成收縮壓加舒張壓</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>必定不變</t>
+        </is>
+      </c>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O162" s="5" t="inlineStr">
+        <is>
+          <t>忽略右心房壓的模型中，CO 減少使 MAP 下降。</t>
+        </is>
+      </c>
+      <c r="P162" s="5" t="inlineStr">
+        <is>
+          <t>「TPR 固定、CO 減少」：用 MAP ≈ CO × TPR。</t>
+        </is>
+      </c>
+      <c r="Q162" s="5" t="inlineStr">
+        <is>
+          <t>MAP ≈ CO × TPR 中哪個因子固定？→ 另一個因子減少，乘積如何變？</t>
+        </is>
+      </c>
+      <c r="R162" s="5" t="inlineStr">
+        <is>
+          <t>選擇「下降」。忽略右心房壓的模型中，CO 減少使 MAP 下降。</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr">
+        <is>
+          <t>忽略右心房壓的模型中，CO 減少使 MAP 下降。</t>
+        </is>
+      </c>
+      <c r="T162" s="3"/>
+      <c r="U162" s="3"/>
+      <c r="V162" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="W162" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/hemodynamics-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X162" s="3"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="M2:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -11098,7 +16708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11369,7 +16979,67 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>106 題</t>
+          <t>161 題</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" hidden="0" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>血管構造解析</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜public/materials/blood-vessels-v1/index.html（已登錄、待部署）；6 先備＋5 情境；單元＝次單元＝血管構造解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" hidden="0" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>循環路線</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜public/materials/circulation-routes-v1/index.html（已登錄、待部署）；6 先備＋5 情境；單元＝次單元＝循環路線</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" hidden="0" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>血壓的調控</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜public/materials/blood-pressure-regulation-v1/index.html（已登錄、待部署）；6 先備＋5 情境；單元＝次單元＝血壓的調控</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" hidden="0" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜public/materials/lymphatic-system-v1/index.html（已登錄、待部署）；6 先備＋5 情境；單元＝次單元＝淋巴系統</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" hidden="0" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>血液動力學</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜public/materials/hemodynamics-v1/index.html（已登錄、待部署）；6 先備＋5 情境；單元＝次單元＝血液動力學</t>
         </is>
       </c>
     </row>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X162"/>
+  <dimension ref="A1:X228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16692,6 +16692,6738 @@
       </c>
       <c r="X162" s="3"/>
     </row>
+    <row r="163" ht="150" hidden="0" customHeight="1">
+      <c r="A163" s="3"/>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>CO＝？</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>每搏量÷心率</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>血壓×阻力</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>心率×每搏量</t>
+        </is>
+      </c>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>心率＋每搏量</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O163" s="5" t="inlineStr">
+        <is>
+          <t>CO＝HR×SV，表示一側心室每分鐘射出的血量。</t>
+        </is>
+      </c>
+      <c r="P163" s="5" t="inlineStr">
+        <is>
+          <t>「心輸出量＝心率×每搏量」：回想每分鐘的搏動次數與每次射出的血量。</t>
+        </is>
+      </c>
+      <c r="Q163" s="5" t="inlineStr">
+        <is>
+          <t>回想每分鐘的搏動次數與每次射出的血量。 → 回到「心輸出量＝心率×每搏量」比較：一側心室每分鐘射出的血量</t>
+        </is>
+      </c>
+      <c r="R163" s="5" t="inlineStr">
+        <is>
+          <t>選擇「心率×每搏量」。CO＝HR×SV，表示一側心室每分鐘射出的血量。</t>
+        </is>
+      </c>
+      <c r="S163" s="5" t="inlineStr">
+        <is>
+          <t>CO＝HR×SV，表示一側心室每分鐘射出的血量。</t>
+        </is>
+      </c>
+      <c r="T163" s="3"/>
+      <c r="U163" s="3"/>
+      <c r="V163" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W163" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X163" s="3"/>
+    </row>
+    <row r="164" ht="150" hidden="0" customHeight="1">
+      <c r="A164" s="3"/>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>EDV 120、ESV 50 mL，SV？</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>120 mL</t>
+        </is>
+      </c>
+      <c r="L164" s="5" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" s="5" t="inlineStr">
+        <is>
+          <t>SV＝EDV−ESV＝120−50＝70 mL。</t>
+        </is>
+      </c>
+      <c r="P164" s="5" t="inlineStr">
+        <is>
+          <t>「每搏量＝EDV−ESV」：用舒張末期容積減去收縮末期容積。</t>
+        </is>
+      </c>
+      <c r="Q164" s="5" t="inlineStr">
+        <is>
+          <t>用舒張末期容積減去收縮末期容積。 → 回到「每搏量＝EDV−ESV」比較：EDV 約 120 mL、ESV 約 50 mL → SV 約 70 mL</t>
+        </is>
+      </c>
+      <c r="R164" s="5" t="inlineStr">
+        <is>
+          <t>選擇「70」。SV＝EDV−ESV＝120−50＝70 mL。</t>
+        </is>
+      </c>
+      <c r="S164" s="5" t="inlineStr">
+        <is>
+          <t>SV＝EDV−ESV＝120−50＝70 mL。</t>
+        </is>
+      </c>
+      <c r="T164" s="3"/>
+      <c r="U164" s="3"/>
+      <c r="V164" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W164" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X164" s="3"/>
+    </row>
+    <row r="165" ht="182" hidden="0" customHeight="1">
+      <c r="A165" s="3"/>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>生理範圍內前負荷增加，收縮力？</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="inlineStr">
+        <is>
+          <t>減弱</t>
+        </is>
+      </c>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>增強</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O165" s="5" t="inlineStr">
+        <is>
+          <t>生理範圍內，前負荷增加使心肌拉長，依 Frank-Starling 收縮增強。</t>
+        </is>
+      </c>
+      <c r="P165" s="5" t="inlineStr">
+        <is>
+          <t>「前負荷與 Frank-Starling 定律」：注意生理範圍內心肌拉長與收縮的關係。</t>
+        </is>
+      </c>
+      <c r="Q165" s="5" t="inlineStr">
+        <is>
+          <t>注意生理範圍內心肌拉長與收縮的關係。 → 回到「前負荷與 Frank-Starling 定律」比較：前負荷＝收縮前心室被血液撐開的程度（EDV）</t>
+        </is>
+      </c>
+      <c r="R165" s="5" t="inlineStr">
+        <is>
+          <t>選擇「增強」。生理範圍內，前負荷增加使心肌拉長，依 Frank-Starling 收縮增強。</t>
+        </is>
+      </c>
+      <c r="S165" s="5" t="inlineStr">
+        <is>
+          <t>生理範圍內，前負荷增加使心肌拉長，依 Frank-Starling 收縮增強。</t>
+        </is>
+      </c>
+      <c r="T165" s="3"/>
+      <c r="U165" s="3"/>
+      <c r="V165" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W165" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X165" s="3"/>
+    </row>
+    <row r="166" ht="182" hidden="0" customHeight="1">
+      <c r="A166" s="3"/>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>交感對心臟？</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>只作用於血管</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>心率與收縮力增加</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="inlineStr">
+        <is>
+          <t>使心臟停止</t>
+        </is>
+      </c>
+      <c r="L166" s="5" t="inlineStr">
+        <is>
+          <t>心率下降</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" s="5" t="inlineStr">
+        <is>
+          <t>交感作用使心率與收縮力增加。</t>
+        </is>
+      </c>
+      <c r="P166" s="5" t="inlineStr">
+        <is>
+          <t>「收縮力」：比較交感作用對心率與收縮力的方向。</t>
+        </is>
+      </c>
+      <c r="Q166" s="5" t="inlineStr">
+        <is>
+          <t>比較交感作用對心率與收縮力的方向。 → 回到「收縮力」比較：相同前負荷下，交感神經（正腎上腺素）與腎上腺素使收縮力增強 → SV↑、ESV↓</t>
+        </is>
+      </c>
+      <c r="R166" s="5" t="inlineStr">
+        <is>
+          <t>選擇「心率與收縮力增加」。交感作用使心率與收縮力增加。</t>
+        </is>
+      </c>
+      <c r="S166" s="5" t="inlineStr">
+        <is>
+          <t>交感作用使心率與收縮力增加。</t>
+        </is>
+      </c>
+      <c r="T166" s="3"/>
+      <c r="U166" s="3"/>
+      <c r="V166" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W166" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X166" s="3"/>
+    </row>
+    <row r="167" ht="134" hidden="0" customHeight="1">
+      <c r="A167" s="3"/>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>迷走神經對心臟？</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>增加心率</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
+        <is>
+          <t>增加後負荷</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="inlineStr">
+        <is>
+          <t>降低心率</t>
+        </is>
+      </c>
+      <c r="L167" s="5" t="inlineStr">
+        <is>
+          <t>增加收縮力</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" s="5" t="inlineStr">
+        <is>
+          <t>迷走神經以乙醯膽鹼降低心率。</t>
+        </is>
+      </c>
+      <c r="P167" s="5" t="inlineStr">
+        <is>
+          <t>「自主神經與心率」：回想安靜時迷走神經的作用。</t>
+        </is>
+      </c>
+      <c r="Q167" s="5" t="inlineStr">
+        <is>
+          <t>回想安靜時迷走神經的作用。 → 回到「自主神經與心率」比較：交感使心率↑</t>
+        </is>
+      </c>
+      <c r="R167" s="5" t="inlineStr">
+        <is>
+          <t>選擇「降低心率」。迷走神經以乙醯膽鹼降低心率。</t>
+        </is>
+      </c>
+      <c r="S167" s="5" t="inlineStr">
+        <is>
+          <t>迷走神經以乙醯膽鹼降低心率。</t>
+        </is>
+      </c>
+      <c r="T167" s="3"/>
+      <c r="U167" s="3"/>
+      <c r="V167" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W167" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X167" s="3"/>
+    </row>
+    <row r="168" ht="134" hidden="0" customHeight="1">
+      <c r="A168" s="3"/>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>後負荷指？</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>心室射血要克服的動脈壓力</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>心房壓力</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="inlineStr">
+        <is>
+          <t>心率</t>
+        </is>
+      </c>
+      <c r="L168" s="5" t="inlineStr">
+        <is>
+          <t>舒張末期容積</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" s="5" t="inlineStr">
+        <is>
+          <t>後負荷是心室射血必須克服的動脈壓力。</t>
+        </is>
+      </c>
+      <c r="P168" s="5" t="inlineStr">
+        <is>
+          <t>「後負荷」：分清射血前的充血與射血時要克服的壓力。</t>
+        </is>
+      </c>
+      <c r="Q168" s="5" t="inlineStr">
+        <is>
+          <t>分清射血前的充血與射血時要克服的壓力。 → 回到「後負荷」比較：心室射血必須克服的動脈壓力</t>
+        </is>
+      </c>
+      <c r="R168" s="5" t="inlineStr">
+        <is>
+          <t>選擇「心室射血要克服的動脈壓力」。後負荷是心室射血必須克服的動脈壓力。</t>
+        </is>
+      </c>
+      <c r="S168" s="5" t="inlineStr">
+        <is>
+          <t>後負荷是心室射血必須克服的動脈壓力。</t>
+        </is>
+      </c>
+      <c r="T168" s="3"/>
+      <c r="U168" s="3"/>
+      <c r="V168" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W168" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X168" s="3"/>
+    </row>
+    <row r="169" ht="150" hidden="0" customHeight="1">
+      <c r="A169" s="3"/>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-case-q01</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】慢跑時心率 70→140、SV 70→100 mL，CO 約？</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>7 L/min</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="inlineStr">
+        <is>
+          <t>4.9 L/min</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="inlineStr">
+        <is>
+          <t>9.8 L/min</t>
+        </is>
+      </c>
+      <c r="L169" s="5" t="inlineStr">
+        <is>
+          <t>14 L/min</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O169" s="5" t="inlineStr">
+        <is>
+          <t>140×100＝14000 mL/min＝14 L/min。</t>
+        </is>
+      </c>
+      <c r="P169" s="5" t="inlineStr">
+        <is>
+          <t>「心輸出量＝心率×每搏量」：先乘心率與每搏量，再將 mL 換成 L。</t>
+        </is>
+      </c>
+      <c r="Q169" s="5" t="inlineStr">
+        <is>
+          <t>先乘心率與每搏量，再將 mL 換成 L。 → 回到「心輸出量＝心率×每搏量」比較：一側心室每分鐘射出的血量</t>
+        </is>
+      </c>
+      <c r="R169" s="5" t="inlineStr">
+        <is>
+          <t>選擇「14 L/min」。140×100＝14000 mL/min＝14 L/min。</t>
+        </is>
+      </c>
+      <c r="S169" s="5" t="inlineStr">
+        <is>
+          <t>140×100＝14000 mL/min＝14 L/min。</t>
+        </is>
+      </c>
+      <c r="T169" s="3"/>
+      <c r="U169" s="3"/>
+      <c r="V169" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W169" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X169" s="3"/>
+    </row>
+    <row r="170" ht="182" hidden="0" customHeight="1">
+      <c r="A170" s="3"/>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-case-q02</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】平躺抬腿使回心血量增加，下一次 SV？</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="inlineStr">
+        <is>
+          <t>變為零</t>
+        </is>
+      </c>
+      <c r="L170" s="5" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" s="5" t="inlineStr">
+        <is>
+          <t>回心血量增加使 EDV 增加，生理範圍內 SV 增加。</t>
+        </is>
+      </c>
+      <c r="P170" s="5" t="inlineStr">
+        <is>
+          <t>「前負荷與 Frank-Starling 定律」：把回心血量、EDV 與 Frank-Starling 連起來。</t>
+        </is>
+      </c>
+      <c r="Q170" s="5" t="inlineStr">
+        <is>
+          <t>把回心血量、EDV 與 Frank-Starling 連起來。 → 回到「前負荷與 Frank-Starling 定律」比較：前負荷＝收縮前心室被血液撐開的程度（EDV）</t>
+        </is>
+      </c>
+      <c r="R170" s="5" t="inlineStr">
+        <is>
+          <t>選擇「增加」。回心血量增加使 EDV 增加，生理範圍內 SV 增加。</t>
+        </is>
+      </c>
+      <c r="S170" s="5" t="inlineStr">
+        <is>
+          <t>回心血量增加使 EDV 增加，生理範圍內 SV 增加。</t>
+        </is>
+      </c>
+      <c r="T170" s="3"/>
+      <c r="U170" s="3"/>
+      <c r="V170" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W170" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X170" s="3"/>
+    </row>
+    <row r="171" ht="198" hidden="0" customHeight="1">
+      <c r="A171" s="3"/>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-case-q03</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】交感作用使收縮力增強，ESV？</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>等於 EDV</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="L171" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" s="5" t="inlineStr">
+        <is>
+          <t>相同前負荷下收縮力增強，射出較多血，ESV 減少。</t>
+        </is>
+      </c>
+      <c r="P171" s="5" t="inlineStr">
+        <is>
+          <t>「收縮力」：收縮更強時，收縮末期留下的血量較多還是較少？</t>
+        </is>
+      </c>
+      <c r="Q171" s="5" t="inlineStr">
+        <is>
+          <t>收縮更強時，收縮末期留下的血量較多還是較少？ → 回到「收縮力」比較：相同前負荷下，交感神經（正腎上腺素）與腎上腺素使收縮力增強 → SV↑、ESV↓</t>
+        </is>
+      </c>
+      <c r="R171" s="5" t="inlineStr">
+        <is>
+          <t>選擇「減少」。相同前負荷下收縮力增強，射出較多血，ESV 減少。</t>
+        </is>
+      </c>
+      <c r="S171" s="5" t="inlineStr">
+        <is>
+          <t>相同前負荷下收縮力增強，射出較多血，ESV 減少。</t>
+        </is>
+      </c>
+      <c r="T171" s="3"/>
+      <c r="U171" s="3"/>
+      <c r="V171" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W171" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X171" s="3"/>
+    </row>
+    <row r="172" ht="134" hidden="0" customHeight="1">
+      <c r="A172" s="3"/>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-case-q04</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】主動脈壓升高、其他不變，SV？</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="L172" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" s="5" t="inlineStr">
+        <is>
+          <t>主動脈壓升高使後負荷增加，其他條件不變時 SV 傾向減少。</t>
+        </is>
+      </c>
+      <c r="P172" s="5" t="inlineStr">
+        <is>
+          <t>「後負荷」：其他條件固定，心室要克服的壓力增加。</t>
+        </is>
+      </c>
+      <c r="Q172" s="5" t="inlineStr">
+        <is>
+          <t>其他條件固定，心室要克服的壓力增加。 → 回到「後負荷」比較：心室射血必須克服的動脈壓力</t>
+        </is>
+      </c>
+      <c r="R172" s="5" t="inlineStr">
+        <is>
+          <t>選擇「減少」。主動脈壓升高使後負荷增加，其他條件不變時 SV 傾向減少。</t>
+        </is>
+      </c>
+      <c r="S172" s="5" t="inlineStr">
+        <is>
+          <t>主動脈壓升高使後負荷增加，其他條件不變時 SV 傾向減少。</t>
+        </is>
+      </c>
+      <c r="T172" s="3"/>
+      <c r="U172" s="3"/>
+      <c r="V172" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W172" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X172" s="3"/>
+    </row>
+    <row r="173" ht="134" hidden="0" customHeight="1">
+      <c r="A173" s="3"/>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>cardiac-output-case-q05</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】心率極快時心室充血時間？</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>與心率無關</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>減少，EDV 可能下降</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O173" s="5" t="inlineStr">
+        <is>
+          <t>心率極快使舒張期縮短，充血時間減少，EDV 可能下降。</t>
+        </is>
+      </c>
+      <c r="P173" s="5" t="inlineStr">
+        <is>
+          <t>「自主神經與心率」：心率變快時，每次舒張可用的時間會變短。</t>
+        </is>
+      </c>
+      <c r="Q173" s="5" t="inlineStr">
+        <is>
+          <t>心率變快時，每次舒張可用的時間會變短。 → 回到「自主神經與心率」比較：交感使心率↑</t>
+        </is>
+      </c>
+      <c r="R173" s="5" t="inlineStr">
+        <is>
+          <t>選擇「減少，EDV 可能下降」。心率極快使舒張期縮短，充血時間減少，EDV 可能下降。</t>
+        </is>
+      </c>
+      <c r="S173" s="5" t="inlineStr">
+        <is>
+          <t>心率極快使舒張期縮短，充血時間減少，EDV 可能下降。</t>
+        </is>
+      </c>
+      <c r="T173" s="3"/>
+      <c r="U173" s="3"/>
+      <c r="V173" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="W173" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X173" s="3"/>
+    </row>
+    <row r="174" ht="150" hidden="0" customHeight="1">
+      <c r="A174" s="3"/>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>聽診法常量？</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>頸動脈</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>肱動脈</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="inlineStr">
+        <is>
+          <t>股動脈</t>
+        </is>
+      </c>
+      <c r="L174" s="5" t="inlineStr">
+        <is>
+          <t>橈動脈</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O174" s="5" t="inlineStr">
+        <is>
+          <t>聽診法在肘窩的肱動脈聽取血流聲音。</t>
+        </is>
+      </c>
+      <c r="P174" s="5" t="inlineStr">
+        <is>
+          <t>「聽診法原理」：找肘窩聽診器對應的動脈。</t>
+        </is>
+      </c>
+      <c r="Q174" s="5" t="inlineStr">
+        <is>
+          <t>找肘窩聽診器對應的動脈。 → 回到「聽診法原理」比較：壓脈帶加壓阻斷肱動脈血流，再緩慢放氣，聽血流恢復的聲音</t>
+        </is>
+      </c>
+      <c r="R174" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肱動脈」。聽診法在肘窩的肱動脈聽取血流聲音。</t>
+        </is>
+      </c>
+      <c r="S174" s="5" t="inlineStr">
+        <is>
+          <t>聽診法在肘窩的肱動脈聽取血流聲音。</t>
+        </is>
+      </c>
+      <c r="T174" s="3"/>
+      <c r="U174" s="3"/>
+      <c r="V174" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W174" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X174" s="3"/>
+    </row>
+    <row r="175" ht="150" hidden="0" customHeight="1">
+      <c r="A175" s="3"/>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>柯氏音來自？</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>呼吸聲</t>
+        </is>
+      </c>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>壓脈帶漏氣</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="inlineStr">
+        <is>
+          <t>血液斷續通過受壓動脈的亂流</t>
+        </is>
+      </c>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>瓣膜關閉</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" s="5" t="inlineStr">
+        <is>
+          <t>柯氏音由血液斷續衝過被壓窄動脈形成的亂流產生。</t>
+        </is>
+      </c>
+      <c r="P175" s="5" t="inlineStr">
+        <is>
+          <t>「柯氏音」：想想血液衝過受壓管腔時的流動。</t>
+        </is>
+      </c>
+      <c r="Q175" s="5" t="inlineStr">
+        <is>
+          <t>想想血液衝過受壓管腔時的流動。 → 回到「柯氏音」比較：血液斷續衝過被壓窄的動脈形成亂流所產生</t>
+        </is>
+      </c>
+      <c r="R175" s="5" t="inlineStr">
+        <is>
+          <t>選擇「血液斷續通過受壓動脈的亂流」。柯氏音由血液斷續衝過被壓窄動脈形成的亂流產生。</t>
+        </is>
+      </c>
+      <c r="S175" s="5" t="inlineStr">
+        <is>
+          <t>柯氏音由血液斷續衝過被壓窄動脈形成的亂流產生。</t>
+        </is>
+      </c>
+      <c r="T175" s="3"/>
+      <c r="U175" s="3"/>
+      <c r="V175" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W175" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X175" s="3"/>
+    </row>
+    <row r="176" ht="150" hidden="0" customHeight="1">
+      <c r="A176" s="3"/>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>第一個柯氏音＝？</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>收縮壓</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>脈壓</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>平均動脈壓</t>
+        </is>
+      </c>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>舒張壓</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O176" s="5" t="inlineStr">
+        <is>
+          <t>放氣時第一個規律柯氏音的壓力是收縮壓。</t>
+        </is>
+      </c>
+      <c r="P176" s="5" t="inlineStr">
+        <is>
+          <t>「收縮壓」：對照壓脈帶放氣時聲音剛出現的時刻。</t>
+        </is>
+      </c>
+      <c r="Q176" s="5" t="inlineStr">
+        <is>
+          <t>對照壓脈帶放氣時聲音剛出現的時刻。 → 回到「收縮壓」比較：第一個規律柯氏音出現時的壓力</t>
+        </is>
+      </c>
+      <c r="R176" s="5" t="inlineStr">
+        <is>
+          <t>選擇「收縮壓」。放氣時第一個規律柯氏音的壓力是收縮壓。</t>
+        </is>
+      </c>
+      <c r="S176" s="5" t="inlineStr">
+        <is>
+          <t>放氣時第一個規律柯氏音的壓力是收縮壓。</t>
+        </is>
+      </c>
+      <c r="T176" s="3"/>
+      <c r="U176" s="3"/>
+      <c r="V176" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W176" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X176" s="3"/>
+    </row>
+    <row r="177" ht="150" hidden="0" customHeight="1">
+      <c r="A177" s="3"/>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>柯氏音消失＝？</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>脈壓</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>心率</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="inlineStr">
+        <is>
+          <t>收縮壓</t>
+        </is>
+      </c>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>舒張壓</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O177" s="5" t="inlineStr">
+        <is>
+          <t>柯氏音消失時的壓力是舒張壓。</t>
+        </is>
+      </c>
+      <c r="P177" s="5" t="inlineStr">
+        <is>
+          <t>「舒張壓」：對照血流變平順後聲音的變化。</t>
+        </is>
+      </c>
+      <c r="Q177" s="5" t="inlineStr">
+        <is>
+          <t>對照血流變平順後聲音的變化。 → 回到「舒張壓」比較：柯氏音消失時的壓力</t>
+        </is>
+      </c>
+      <c r="R177" s="5" t="inlineStr">
+        <is>
+          <t>選擇「舒張壓」。柯氏音消失時的壓力是舒張壓。</t>
+        </is>
+      </c>
+      <c r="S177" s="5" t="inlineStr">
+        <is>
+          <t>柯氏音消失時的壓力是舒張壓。</t>
+        </is>
+      </c>
+      <c r="T177" s="3"/>
+      <c r="U177" s="3"/>
+      <c r="V177" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W177" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X177" s="3"/>
+    </row>
+    <row r="178" ht="166" hidden="0" customHeight="1">
+      <c r="A178" s="3"/>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>手臂位置？</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>垂到地面</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>與心臟同高</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>高於頭部</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" s="5" t="inlineStr">
+        <is>
+          <t>手臂應與心臟同高，以避免高度影響讀值。</t>
+        </is>
+      </c>
+      <c r="P178" s="5" t="inlineStr">
+        <is>
+          <t>「測量步驟」：比較手臂高度與心臟高度。</t>
+        </is>
+      </c>
+      <c r="Q178" s="5" t="inlineStr">
+        <is>
+          <t>比較手臂高度與心臟高度。 → 回到「測量步驟」比較：坐姿休息、手臂與心臟同高、壓脈帶寬度合適、聽診器放肘窩肱動脈</t>
+        </is>
+      </c>
+      <c r="R178" s="5" t="inlineStr">
+        <is>
+          <t>選擇「與心臟同高」。手臂應與心臟同高，以避免高度影響讀值。</t>
+        </is>
+      </c>
+      <c r="S178" s="5" t="inlineStr">
+        <is>
+          <t>手臂應與心臟同高，以避免高度影響讀值。</t>
+        </is>
+      </c>
+      <c r="T178" s="3"/>
+      <c r="U178" s="3"/>
+      <c r="V178" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W178" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X178" s="3"/>
+    </row>
+    <row r="179" ht="150" hidden="0" customHeight="1">
+      <c r="A179" s="3"/>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>血壓 120/80 mmHg 的脈壓？</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>200 mmHg</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" s="5" t="inlineStr">
+        <is>
+          <t>脈壓＝120−80＝40 mmHg。</t>
+        </is>
+      </c>
+      <c r="P179" s="5" t="inlineStr">
+        <is>
+          <t>「判讀與換算」：用收縮壓減舒張壓。</t>
+        </is>
+      </c>
+      <c r="Q179" s="5" t="inlineStr">
+        <is>
+          <t>用收縮壓減舒張壓。 → 回到「判讀與換算」比較：120／80 → 脈壓 40、MAP≈80＋40÷3≈93 mmHg（連結血液動力學）</t>
+        </is>
+      </c>
+      <c r="R179" s="5" t="inlineStr">
+        <is>
+          <t>選擇「40」。脈壓＝120−80＝40 mmHg。</t>
+        </is>
+      </c>
+      <c r="S179" s="5" t="inlineStr">
+        <is>
+          <t>脈壓＝120−80＝40 mmHg。</t>
+        </is>
+      </c>
+      <c r="T179" s="3"/>
+      <c r="U179" s="3"/>
+      <c r="V179" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W179" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X179" s="3"/>
+    </row>
+    <row r="180" ht="150" hidden="0" customHeight="1">
+      <c r="A180" s="3"/>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-case-q01</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】加壓到 150 無聲，放氣到 118 開始聽到規律聲，76 消失，記錄為？</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>「118/76 mmHg」</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t>「118/150 mmHg」</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="inlineStr">
+        <is>
+          <t>「76/118 mmHg」</t>
+        </is>
+      </c>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>「150/76 mmHg」</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" s="5" t="inlineStr">
+        <is>
+          <t>第一聲在 118、消失在 76，記為 118/76 mmHg。</t>
+        </is>
+      </c>
+      <c r="P180" s="5" t="inlineStr">
+        <is>
+          <t>「收縮壓」：記錄聲音開始與消失的壓力，不是最高加壓值。</t>
+        </is>
+      </c>
+      <c r="Q180" s="5" t="inlineStr">
+        <is>
+          <t>記錄聲音開始與消失的壓力，不是最高加壓值。 → 回到「收縮壓」比較：第一個規律柯氏音出現時的壓力</t>
+        </is>
+      </c>
+      <c r="R180" s="5" t="inlineStr">
+        <is>
+          <t>選擇「「118/76 mmHg」」。第一聲在 118、消失在 76，記為 118/76 mmHg。</t>
+        </is>
+      </c>
+      <c r="S180" s="5" t="inlineStr">
+        <is>
+          <t>第一聲在 118、消失在 76，記為 118/76 mmHg。</t>
+        </is>
+      </c>
+      <c r="T180" s="3"/>
+      <c r="U180" s="3"/>
+      <c r="V180" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W180" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X180" s="3"/>
+    </row>
+    <row r="181" ht="150" hidden="0" customHeight="1">
+      <c r="A181" s="3"/>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-case-q02</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】壓力介於收縮壓與舒張壓之間，肱動脈血流？</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>完全平順</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>倒流</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="inlineStr">
+        <is>
+          <t>完全停止</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>只在收縮期斷續衝過</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" s="5" t="inlineStr">
+        <is>
+          <t>壓脈帶壓力介於兩者時，只有收縮期血液能斷續衝過。</t>
+        </is>
+      </c>
+      <c r="P181" s="5" t="inlineStr">
+        <is>
+          <t>「柯氏音」：收縮時的壓力才能衝過壓脈帶。</t>
+        </is>
+      </c>
+      <c r="Q181" s="5" t="inlineStr">
+        <is>
+          <t>收縮時的壓力才能衝過壓脈帶。 → 回到「柯氏音」比較：血液斷續衝過被壓窄的動脈形成亂流所產生</t>
+        </is>
+      </c>
+      <c r="R181" s="5" t="inlineStr">
+        <is>
+          <t>選擇「只在收縮期斷續衝過」。壓脈帶壓力介於兩者時，只有收縮期血液能斷續衝過。</t>
+        </is>
+      </c>
+      <c r="S181" s="5" t="inlineStr">
+        <is>
+          <t>壓脈帶壓力介於兩者時，只有收縮期血液能斷續衝過。</t>
+        </is>
+      </c>
+      <c r="T181" s="3"/>
+      <c r="U181" s="3"/>
+      <c r="V181" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W181" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X181" s="3"/>
+    </row>
+    <row r="182" ht="166" hidden="0" customHeight="1">
+      <c r="A182" s="3"/>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-case-q03</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】手臂舉得比心臟高，讀值？</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>偏低</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="inlineStr">
+        <is>
+          <t>無法測量</t>
+        </is>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>偏高</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O182" s="5" t="inlineStr">
+        <is>
+          <t>手臂高於心臟時讀值偏低，低於心臟則偏高。</t>
+        </is>
+      </c>
+      <c r="P182" s="5" t="inlineStr">
+        <is>
+          <t>「判讀與換算」：對照節點 6 的手臂高度與讀值。</t>
+        </is>
+      </c>
+      <c r="Q182" s="5" t="inlineStr">
+        <is>
+          <t>對照節點 6 的手臂高度與讀值。 → 回到「判讀與換算」比較：120／80 → 脈壓 40、MAP≈80＋40÷3≈93 mmHg（連結血液動力學）</t>
+        </is>
+      </c>
+      <c r="R182" s="5" t="inlineStr">
+        <is>
+          <t>選擇「偏低」。手臂高於心臟時讀值偏低，低於心臟則偏高。</t>
+        </is>
+      </c>
+      <c r="S182" s="5" t="inlineStr">
+        <is>
+          <t>手臂高於心臟時讀值偏低，低於心臟則偏高。</t>
+        </is>
+      </c>
+      <c r="T182" s="3"/>
+      <c r="U182" s="3"/>
+      <c r="V182" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W182" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X182" s="3"/>
+    </row>
+    <row r="183" ht="182" hidden="0" customHeight="1">
+      <c r="A183" s="3"/>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-case-q04</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】放氣太快可能？</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>聽到心音</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>壓脈帶破裂</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="inlineStr">
+        <is>
+          <t>錯過第一聲而判讀不準</t>
+        </is>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>讓血壓真的升高</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O183" s="5" t="inlineStr">
+        <is>
+          <t>放氣太快可能錯過第一聲，造成判讀不準。</t>
+        </is>
+      </c>
+      <c r="P183" s="5" t="inlineStr">
+        <is>
+          <t>「測量步驟」：第一聲只在放氣過程中的特定壓力出現。</t>
+        </is>
+      </c>
+      <c r="Q183" s="5" t="inlineStr">
+        <is>
+          <t>第一聲只在放氣過程中的特定壓力出現。 → 回到「測量步驟」比較：坐姿休息、手臂與心臟同高、壓脈帶寬度合適、聽診器放肘窩肱動脈</t>
+        </is>
+      </c>
+      <c r="R183" s="5" t="inlineStr">
+        <is>
+          <t>選擇「錯過第一聲而判讀不準」。放氣太快可能錯過第一聲，造成判讀不準。</t>
+        </is>
+      </c>
+      <c r="S183" s="5" t="inlineStr">
+        <is>
+          <t>放氣太快可能錯過第一聲，造成判讀不準。</t>
+        </is>
+      </c>
+      <c r="T183" s="3"/>
+      <c r="U183" s="3"/>
+      <c r="V183" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W183" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X183" s="3"/>
+    </row>
+    <row r="184" ht="182" hidden="0" customHeight="1">
+      <c r="A184" s="3"/>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>blood-pressure-measurement-case-q05</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】量得 120/80 mmHg，MAP 約？</t>
+        </is>
+      </c>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="inlineStr">
+        <is>
+          <t>200 mmHg</t>
+        </is>
+      </c>
+      <c r="L184" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" s="5" t="inlineStr">
+        <is>
+          <t>MAP≈80＋(120−80)÷3≈93 mmHg。</t>
+        </is>
+      </c>
+      <c r="P184" s="5" t="inlineStr">
+        <is>
+          <t>「判讀與換算」：先算脈壓，再將三分之一加到舒張壓。</t>
+        </is>
+      </c>
+      <c r="Q184" s="5" t="inlineStr">
+        <is>
+          <t>先算脈壓，再將三分之一加到舒張壓。 → 回到「判讀與換算」比較：120／80 → 脈壓 40、MAP≈80＋40÷3≈93 mmHg（連結血液動力學）</t>
+        </is>
+      </c>
+      <c r="R184" s="5" t="inlineStr">
+        <is>
+          <t>選擇「93」。MAP≈80＋(120−80)÷3≈93 mmHg。</t>
+        </is>
+      </c>
+      <c r="S184" s="5" t="inlineStr">
+        <is>
+          <t>MAP≈80＋(120−80)÷3≈93 mmHg。</t>
+        </is>
+      </c>
+      <c r="T184" s="3"/>
+      <c r="U184" s="3"/>
+      <c r="V184" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="W184" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X184" s="3"/>
+    </row>
+    <row r="185" ht="166" hidden="0" customHeight="1">
+      <c r="A185" s="3"/>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>最主要交換方式？</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>胞吞</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>過濾</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="inlineStr">
+        <is>
+          <t>主動運輸</t>
+        </is>
+      </c>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>擴散</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O185" s="5" t="inlineStr">
+        <is>
+          <t>O₂、CO₂、葡萄糖等順濃度梯度擴散，是最主要交換方式。</t>
+        </is>
+      </c>
+      <c r="P185" s="5" t="inlineStr">
+        <is>
+          <t>「擴散」：想想物質順濃度梯度移動的方式。</t>
+        </is>
+      </c>
+      <c r="Q185" s="5" t="inlineStr">
+        <is>
+          <t>想想物質順濃度梯度移動的方式。 → 回到「擴散」比較：O₂、CO₂、葡萄糖等順濃度梯度通過管壁，是最主要的交換方式</t>
+        </is>
+      </c>
+      <c r="R185" s="5" t="inlineStr">
+        <is>
+          <t>選擇「擴散」。O₂、CO₂、葡萄糖等順濃度梯度擴散，是最主要交換方式。</t>
+        </is>
+      </c>
+      <c r="S185" s="5" t="inlineStr">
+        <is>
+          <t>O₂、CO₂、葡萄糖等順濃度梯度擴散，是最主要交換方式。</t>
+        </is>
+      </c>
+      <c r="T185" s="3"/>
+      <c r="U185" s="3"/>
+      <c r="V185" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W185" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X185" s="3"/>
+    </row>
+    <row r="186" ht="134" hidden="0" customHeight="1">
+      <c r="A186" s="3"/>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>推出液體的力？</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="inlineStr">
+        <is>
+          <t>淋巴壓</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>微血管靜水壓</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="inlineStr">
+        <is>
+          <t>大氣壓</t>
+        </is>
+      </c>
+      <c r="L186" s="5" t="inlineStr">
+        <is>
+          <t>膠體滲透壓</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O186" s="5" t="inlineStr">
+        <is>
+          <t>微血管靜水壓把液體推出血管。</t>
+        </is>
+      </c>
+      <c r="P186" s="5" t="inlineStr">
+        <is>
+          <t>「微血管靜水壓」：哪個力把液體從血管推出？</t>
+        </is>
+      </c>
+      <c r="Q186" s="5" t="inlineStr">
+        <is>
+          <t>哪個力把液體從血管推出？ → 回到「微血管靜水壓」比較：血壓把液體推出血管</t>
+        </is>
+      </c>
+      <c r="R186" s="5" t="inlineStr">
+        <is>
+          <t>選擇「微血管靜水壓」。微血管靜水壓把液體推出血管。</t>
+        </is>
+      </c>
+      <c r="S186" s="5" t="inlineStr">
+        <is>
+          <t>微血管靜水壓把液體推出血管。</t>
+        </is>
+      </c>
+      <c r="T186" s="3"/>
+      <c r="U186" s="3"/>
+      <c r="V186" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W186" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X186" s="3"/>
+    </row>
+    <row r="187" ht="134" hidden="0" customHeight="1">
+      <c r="A187" s="3"/>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>拉回液體的力？</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>心臟收縮</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="inlineStr">
+        <is>
+          <t>血漿膠體滲透壓</t>
+        </is>
+      </c>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>微血管靜水壓</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O187" s="5" t="inlineStr">
+        <is>
+          <t>血漿膠體滲透壓把液體拉回血管。</t>
+        </is>
+      </c>
+      <c r="P187" s="5" t="inlineStr">
+        <is>
+          <t>「血漿膠體滲透壓」：哪個力把液體拉回血管？</t>
+        </is>
+      </c>
+      <c r="Q187" s="5" t="inlineStr">
+        <is>
+          <t>哪個力把液體拉回血管？ → 回到「血漿膠體滲透壓」比較：主要由白蛋白形成，把液體拉回血管</t>
+        </is>
+      </c>
+      <c r="R187" s="5" t="inlineStr">
+        <is>
+          <t>選擇「血漿膠體滲透壓」。血漿膠體滲透壓把液體拉回血管。</t>
+        </is>
+      </c>
+      <c r="S187" s="5" t="inlineStr">
+        <is>
+          <t>血漿膠體滲透壓把液體拉回血管。</t>
+        </is>
+      </c>
+      <c r="T187" s="3"/>
+      <c r="U187" s="3"/>
+      <c r="V187" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W187" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X187" s="3"/>
+    </row>
+    <row r="188" ht="134" hidden="0" customHeight="1">
+      <c r="A188" s="3"/>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>膠體滲透壓主要來自？</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>白蛋白</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>鈉離子</t>
+        </is>
+      </c>
+      <c r="L188" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" s="5" t="inlineStr">
+        <is>
+          <t>膠體滲透壓主要由不易通過管壁的白蛋白形成。</t>
+        </is>
+      </c>
+      <c r="P188" s="5" t="inlineStr">
+        <is>
+          <t>「血漿膠體滲透壓」：找血漿內不易通過管壁的蛋白質。</t>
+        </is>
+      </c>
+      <c r="Q188" s="5" t="inlineStr">
+        <is>
+          <t>找血漿內不易通過管壁的蛋白質。 → 回到「血漿膠體滲透壓」比較：主要由白蛋白形成，把液體拉回血管</t>
+        </is>
+      </c>
+      <c r="R188" s="5" t="inlineStr">
+        <is>
+          <t>選擇「白蛋白」。膠體滲透壓主要由不易通過管壁的白蛋白形成。</t>
+        </is>
+      </c>
+      <c r="S188" s="5" t="inlineStr">
+        <is>
+          <t>膠體滲透壓主要由不易通過管壁的白蛋白形成。</t>
+        </is>
+      </c>
+      <c r="T188" s="3"/>
+      <c r="U188" s="3"/>
+      <c r="V188" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W188" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X188" s="3"/>
+    </row>
+    <row r="189" ht="134" hidden="0" customHeight="1">
+      <c r="A189" s="3"/>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>動脈端淨移動？</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>不移動</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>進入淋巴結</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="inlineStr">
+        <is>
+          <t>回收入血管</t>
+        </is>
+      </c>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>濾出到組織間隙</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O189" s="5" t="inlineStr">
+        <is>
+          <t>模型動脈端靜水壓大於膠體滲透壓，液體淨濾出。</t>
+        </is>
+      </c>
+      <c r="P189" s="5" t="inlineStr">
+        <is>
+          <t>「淨過濾」：比較動脈端 35 與 25 mmHg。</t>
+        </is>
+      </c>
+      <c r="Q189" s="5" t="inlineStr">
+        <is>
+          <t>比較動脈端 35 與 25 mmHg。 → 回到「淨過濾」比較：動脈端淨濾出、靜脈端淨回收（模型數字同實驗室）</t>
+        </is>
+      </c>
+      <c r="R189" s="5" t="inlineStr">
+        <is>
+          <t>選擇「濾出到組織間隙」。模型動脈端靜水壓大於膠體滲透壓，液體淨濾出。</t>
+        </is>
+      </c>
+      <c r="S189" s="5" t="inlineStr">
+        <is>
+          <t>模型動脈端靜水壓大於膠體滲透壓，液體淨濾出。</t>
+        </is>
+      </c>
+      <c r="T189" s="3"/>
+      <c r="U189" s="3"/>
+      <c r="V189" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W189" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X189" s="3"/>
+    </row>
+    <row r="190" ht="150" hidden="0" customHeight="1">
+      <c r="A190" s="3"/>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>多出的組織液由何回收？</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="inlineStr">
+        <is>
+          <t>肺泡</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>淋巴管</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>腎小管</t>
+        </is>
+      </c>
+      <c r="L190" s="5" t="inlineStr">
+        <is>
+          <t>動脈</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O190" s="5" t="inlineStr">
+        <is>
+          <t>多出的組織液由淋巴管回收並送回靜脈。</t>
+        </is>
+      </c>
+      <c r="P190" s="5" t="inlineStr">
+        <is>
+          <t>「淋巴回收」：濾出略多於回收，多出的液體如何回靜脈？</t>
+        </is>
+      </c>
+      <c r="Q190" s="5" t="inlineStr">
+        <is>
+          <t>濾出略多於回收，多出的液體如何回靜脈？ → 回到「淋巴回收」比較：濾出略多於回收，多出的組織液由淋巴送回靜脈</t>
+        </is>
+      </c>
+      <c r="R190" s="5" t="inlineStr">
+        <is>
+          <t>選擇「淋巴管」。多出的組織液由淋巴管回收並送回靜脈。</t>
+        </is>
+      </c>
+      <c r="S190" s="5" t="inlineStr">
+        <is>
+          <t>多出的組織液由淋巴管回收並送回靜脈。</t>
+        </is>
+      </c>
+      <c r="T190" s="3"/>
+      <c r="U190" s="3"/>
+      <c r="V190" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W190" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X190" s="3"/>
+    </row>
+    <row r="191" ht="134" hidden="0" customHeight="1">
+      <c r="A191" s="3"/>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-case-q01</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】動脈端靜水壓 35、膠體滲透壓 25，淨過濾壓？</t>
+        </is>
+      </c>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>向外 60</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>0 mmHg</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="inlineStr">
+        <is>
+          <t>向外 10</t>
+        </is>
+      </c>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>向內 10</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O191" s="5" t="inlineStr">
+        <is>
+          <t>35−25＝10 mmHg，淨方向向外。</t>
+        </is>
+      </c>
+      <c r="P191" s="5" t="inlineStr">
+        <is>
+          <t>「淨過濾」：用向外的 35 減向內的 25。</t>
+        </is>
+      </c>
+      <c r="Q191" s="5" t="inlineStr">
+        <is>
+          <t>用向外的 35 減向內的 25。 → 回到「淨過濾」比較：動脈端淨濾出、靜脈端淨回收（模型數字同實驗室）</t>
+        </is>
+      </c>
+      <c r="R191" s="5" t="inlineStr">
+        <is>
+          <t>選擇「向外 10」。35−25＝10 mmHg，淨方向向外。</t>
+        </is>
+      </c>
+      <c r="S191" s="5" t="inlineStr">
+        <is>
+          <t>35−25＝10 mmHg，淨方向向外。</t>
+        </is>
+      </c>
+      <c r="T191" s="3"/>
+      <c r="U191" s="3"/>
+      <c r="V191" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W191" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X191" s="3"/>
+    </row>
+    <row r="192" ht="150" hidden="0" customHeight="1">
+      <c r="A192" s="3"/>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-case-q02</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】靜脈端靜水壓 18、膠體滲透壓 25，液體？</t>
+        </is>
+      </c>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>淨回收</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>不移動</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>全部進淋巴</t>
+        </is>
+      </c>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>淨濾出</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" s="5" t="inlineStr">
+        <is>
+          <t>18 小於 25 mmHg，向內的力較大，液體淨回收。</t>
+        </is>
+      </c>
+      <c r="P192" s="5" t="inlineStr">
+        <is>
+          <t>「淨過濾」：比較向外 18 與向內 25，哪個較大？</t>
+        </is>
+      </c>
+      <c r="Q192" s="5" t="inlineStr">
+        <is>
+          <t>比較向外 18 與向內 25，哪個較大？ → 回到「淨過濾」比較：動脈端淨濾出、靜脈端淨回收（模型數字同實驗室）</t>
+        </is>
+      </c>
+      <c r="R192" s="5" t="inlineStr">
+        <is>
+          <t>選擇「淨回收」。18 小於 25 mmHg，向內的力較大，液體淨回收。</t>
+        </is>
+      </c>
+      <c r="S192" s="5" t="inlineStr">
+        <is>
+          <t>18 小於 25 mmHg，向內的力較大，液體淨回收。</t>
+        </is>
+      </c>
+      <c r="T192" s="3"/>
+      <c r="U192" s="3"/>
+      <c r="V192" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W192" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X192" s="3"/>
+    </row>
+    <row r="193" ht="150" hidden="0" customHeight="1">
+      <c r="A193" s="3"/>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-case-q03</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】血漿白蛋白減少，回收入血管的液體？</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>全部回收</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>減少，組織液增加</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O193" s="5" t="inlineStr">
+        <is>
+          <t>白蛋白減少使膠體滲透壓減少，回收液體減少、組織液增加。</t>
+        </is>
+      </c>
+      <c r="P193" s="5" t="inlineStr">
+        <is>
+          <t>「血漿膠體滲透壓」：白蛋白減少時，拉回液體的力會怎麼變？</t>
+        </is>
+      </c>
+      <c r="Q193" s="5" t="inlineStr">
+        <is>
+          <t>白蛋白減少時，拉回液體的力會怎麼變？ → 回到「血漿膠體滲透壓」比較：主要由白蛋白形成，把液體拉回血管</t>
+        </is>
+      </c>
+      <c r="R193" s="5" t="inlineStr">
+        <is>
+          <t>選擇「減少，組織液增加」。白蛋白減少使膠體滲透壓減少，回收液體減少、組織液增加。</t>
+        </is>
+      </c>
+      <c r="S193" s="5" t="inlineStr">
+        <is>
+          <t>白蛋白減少使膠體滲透壓減少，回收液體減少、組織液增加。</t>
+        </is>
+      </c>
+      <c r="T193" s="3"/>
+      <c r="U193" s="3"/>
+      <c r="V193" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W193" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X193" s="3"/>
+    </row>
+    <row r="194" ht="134" hidden="0" customHeight="1">
+      <c r="A194" s="3"/>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-case-q04</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】久站時下肢微血管靜水壓升高，組織液生成？</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="L194" s="5" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O194" s="5" t="inlineStr">
+        <is>
+          <t>下肢靜水壓升高使推出液體的力增加，組織液生成增加。</t>
+        </is>
+      </c>
+      <c r="P194" s="5" t="inlineStr">
+        <is>
+          <t>「微血管靜水壓」：推出液體的靜水壓增加。</t>
+        </is>
+      </c>
+      <c r="Q194" s="5" t="inlineStr">
+        <is>
+          <t>推出液體的靜水壓增加。 → 回到「微血管靜水壓」比較：血壓把液體推出血管</t>
+        </is>
+      </c>
+      <c r="R194" s="5" t="inlineStr">
+        <is>
+          <t>選擇「增加」。下肢靜水壓升高使推出液體的力增加，組織液生成增加。</t>
+        </is>
+      </c>
+      <c r="S194" s="5" t="inlineStr">
+        <is>
+          <t>下肢靜水壓升高使推出液體的力增加，組織液生成增加。</t>
+        </is>
+      </c>
+      <c r="T194" s="3"/>
+      <c r="U194" s="3"/>
+      <c r="V194" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W194" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X194" s="3"/>
+    </row>
+    <row r="195" ht="166" hidden="0" customHeight="1">
+      <c r="A195" s="3"/>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>capillary-exchange-case-q05</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】運動時肌肉產生較多 CO₂，主要以何方式進入微血管？</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>過濾</t>
+        </is>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>主動運輸</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="inlineStr">
+        <is>
+          <t>擴散</t>
+        </is>
+      </c>
+      <c r="L195" s="5" t="inlineStr">
+        <is>
+          <t>胞吞</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O195" s="5" t="inlineStr">
+        <is>
+          <t>肌肉內 CO₂ 濃度增加，順濃度梯度擴散到微血管。</t>
+        </is>
+      </c>
+      <c r="P195" s="5" t="inlineStr">
+        <is>
+          <t>「擴散」：肌肉內 CO₂ 較多，順濃度梯度移動。</t>
+        </is>
+      </c>
+      <c r="Q195" s="5" t="inlineStr">
+        <is>
+          <t>肌肉內 CO₂ 較多，順濃度梯度移動。 → 回到「擴散」比較：O₂、CO₂、葡萄糖等順濃度梯度通過管壁，是最主要的交換方式</t>
+        </is>
+      </c>
+      <c r="R195" s="5" t="inlineStr">
+        <is>
+          <t>選擇「擴散」。肌肉內 CO₂ 濃度增加，順濃度梯度擴散到微血管。</t>
+        </is>
+      </c>
+      <c r="S195" s="5" t="inlineStr">
+        <is>
+          <t>肌肉內 CO₂ 濃度增加，順濃度梯度擴散到微血管。</t>
+        </is>
+      </c>
+      <c r="T195" s="3"/>
+      <c r="U195" s="3"/>
+      <c r="V195" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="W195" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X195" s="3"/>
+    </row>
+    <row r="196" ht="182" hidden="0" customHeight="1">
+      <c r="A196" s="3"/>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>直接由主動脈弓發出的是？</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>頭臂幹</t>
+        </is>
+      </c>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>右頸總動脈</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="inlineStr">
+        <is>
+          <t>肱動脈</t>
+        </is>
+      </c>
+      <c r="L196" s="5" t="inlineStr">
+        <is>
+          <t>右鎖骨下動脈</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" s="5" t="inlineStr">
+        <is>
+          <t>頭臂幹直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
+        </is>
+      </c>
+      <c r="P196" s="5" t="inlineStr">
+        <is>
+          <t>「主動脈弓三分支」：分清主動脈弓直接分支與頭臂幹的分支。</t>
+        </is>
+      </c>
+      <c r="Q196" s="5" t="inlineStr">
+        <is>
+          <t>分清主動脈弓直接分支與頭臂幹的分支。 → 回到「主動脈弓三分支」比較：頭臂幹（再分右頸總、右鎖骨下）、左頸總動脈、左鎖骨下動脈</t>
+        </is>
+      </c>
+      <c r="R196" s="5" t="inlineStr">
+        <is>
+          <t>選擇「頭臂幹」。頭臂幹直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
+        </is>
+      </c>
+      <c r="S196" s="5" t="inlineStr">
+        <is>
+          <t>頭臂幹直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
+        </is>
+      </c>
+      <c r="T196" s="3"/>
+      <c r="U196" s="3"/>
+      <c r="V196" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W196" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X196" s="3"/>
+    </row>
+    <row r="197" ht="134" hidden="0" customHeight="1">
+      <c r="A197" s="3"/>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>上肢動脈順序？</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="inlineStr">
+        <is>
+          <t>肱→腋→橈</t>
+        </is>
+      </c>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t>橈→肱→腋</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="inlineStr">
+        <is>
+          <t>腋→鎖骨下→肱</t>
+        </is>
+      </c>
+      <c r="L197" s="5" t="inlineStr">
+        <is>
+          <t>鎖骨下→腋→肱→橈、尺</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O197" s="5" t="inlineStr">
+        <is>
+          <t>上肢動脈由鎖骨下、腋、肱，接到橈與尺動脈。</t>
+        </is>
+      </c>
+      <c r="P197" s="5" t="inlineStr">
+        <is>
+          <t>「上肢動脈」：由軀幹走向手指，按血管位置排序。</t>
+        </is>
+      </c>
+      <c r="Q197" s="5" t="inlineStr">
+        <is>
+          <t>由軀幹走向手指，按血管位置排序。 → 回到「上肢動脈」比較：鎖骨下 → 腋 → 肱 → 橈、尺動脈</t>
+        </is>
+      </c>
+      <c r="R197" s="5" t="inlineStr">
+        <is>
+          <t>選擇「鎖骨下→腋→肱→橈、尺」。上肢動脈由鎖骨下、腋、肱，接到橈與尺動脈。</t>
+        </is>
+      </c>
+      <c r="S197" s="5" t="inlineStr">
+        <is>
+          <t>上肢動脈由鎖骨下、腋、肱，接到橈與尺動脈。</t>
+        </is>
+      </c>
+      <c r="T197" s="3"/>
+      <c r="U197" s="3"/>
+      <c r="V197" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W197" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X197" s="3"/>
+    </row>
+    <row r="198" ht="150" hidden="0" customHeight="1">
+      <c r="A198" s="3"/>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>腹主動脈的成對分支？</t>
+        </is>
+      </c>
+      <c r="I198" s="5" t="inlineStr">
+        <is>
+          <t>上腸繫膜動脈</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="inlineStr">
+        <is>
+          <t>腎動脈</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="inlineStr">
+        <is>
+          <t>下腸繫膜動脈</t>
+        </is>
+      </c>
+      <c r="L198" s="5" t="inlineStr">
+        <is>
+          <t>腹腔幹</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" s="5" t="inlineStr">
+        <is>
+          <t>左右腎動脈是腹主動脈的成對分支。</t>
+        </is>
+      </c>
+      <c r="P198" s="5" t="inlineStr">
+        <is>
+          <t>「腹主動脈分支」：成對表示左、右各有一條。</t>
+        </is>
+      </c>
+      <c r="Q198" s="5" t="inlineStr">
+        <is>
+          <t>成對表示左、右各有一條。 → 回到「腹主動脈分支」比較：不成對的腹腔幹（胃、肝、脾）、上腸繫膜、下腸繫膜動脈</t>
+        </is>
+      </c>
+      <c r="R198" s="5" t="inlineStr">
+        <is>
+          <t>選擇「腎動脈」。左右腎動脈是腹主動脈的成對分支。</t>
+        </is>
+      </c>
+      <c r="S198" s="5" t="inlineStr">
+        <is>
+          <t>左右腎動脈是腹主動脈的成對分支。</t>
+        </is>
+      </c>
+      <c r="T198" s="3"/>
+      <c r="U198" s="3"/>
+      <c r="V198" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W198" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X198" s="3"/>
+    </row>
+    <row r="199" ht="134" hidden="0" customHeight="1">
+      <c r="A199" s="3"/>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>下肢動脈順序？</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>膕→股→髂外</t>
+        </is>
+      </c>
+      <c r="J199" s="5" t="inlineStr">
+        <is>
+          <t>髂外→膕→股</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="inlineStr">
+        <is>
+          <t>髂外→股→膕</t>
+        </is>
+      </c>
+      <c r="L199" s="5" t="inlineStr">
+        <is>
+          <t>股→髂外→膕</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O199" s="5" t="inlineStr">
+        <is>
+          <t>下肢動脈由髂外到股，再到膝後的膕動脈。</t>
+        </is>
+      </c>
+      <c r="P199" s="5" t="inlineStr">
+        <is>
+          <t>「下肢動脈」：由骨盆往膝後追蹤動脈。</t>
+        </is>
+      </c>
+      <c r="Q199" s="5" t="inlineStr">
+        <is>
+          <t>由骨盆往膝後追蹤動脈。 → 回到「下肢動脈」比較：髂總 → 髂外 → 股 → 膕 → 脛前、脛後</t>
+        </is>
+      </c>
+      <c r="R199" s="5" t="inlineStr">
+        <is>
+          <t>選擇「髂外→股→膕」。下肢動脈由髂外到股，再到膝後的膕動脈。</t>
+        </is>
+      </c>
+      <c r="S199" s="5" t="inlineStr">
+        <is>
+          <t>下肢動脈由髂外到股，再到膝後的膕動脈。</t>
+        </is>
+      </c>
+      <c r="T199" s="3"/>
+      <c r="U199" s="3"/>
+      <c r="V199" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W199" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X199" s="3"/>
+    </row>
+    <row r="200" ht="150" hidden="0" customHeight="1">
+      <c r="A200" s="3"/>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>上腔靜脈收集？</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="inlineStr">
+        <is>
+          <t>頭頸與上肢</t>
+        </is>
+      </c>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>腹部器官</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="inlineStr">
+        <is>
+          <t>心肌</t>
+        </is>
+      </c>
+      <c r="L200" s="5" t="inlineStr">
+        <is>
+          <t>下肢</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" s="5" t="inlineStr">
+        <is>
+          <t>上腔靜脈收集頭頸與上肢的血液。</t>
+        </is>
+      </c>
+      <c r="P200" s="5" t="inlineStr">
+        <is>
+          <t>「主要靜脈」：上腔靜脈收集橫膈以上的主要回流。</t>
+        </is>
+      </c>
+      <c r="Q200" s="5" t="inlineStr">
+        <is>
+          <t>上腔靜脈收集橫膈以上的主要回流。 → 回到「主要靜脈」比較：上腔靜脈收集頭頸與上肢（左右頭臂靜脈匯合）</t>
+        </is>
+      </c>
+      <c r="R200" s="5" t="inlineStr">
+        <is>
+          <t>選擇「頭頸與上肢」。上腔靜脈收集頭頸與上肢的血液。</t>
+        </is>
+      </c>
+      <c r="S200" s="5" t="inlineStr">
+        <is>
+          <t>上腔靜脈收集頭頸與上肢的血液。</t>
+        </is>
+      </c>
+      <c r="T200" s="3"/>
+      <c r="U200" s="3"/>
+      <c r="V200" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W200" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X200" s="3"/>
+    </row>
+    <row r="201" ht="134" hidden="0" customHeight="1">
+      <c r="A201" s="3"/>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>人體最長的靜脈？</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
+          <t>股靜脈</t>
+        </is>
+      </c>
+      <c r="J201" s="5" t="inlineStr">
+        <is>
+          <t>頸內靜脈</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="inlineStr">
+        <is>
+          <t>肘正中靜脈</t>
+        </is>
+      </c>
+      <c r="L201" s="5" t="inlineStr">
+        <is>
+          <t>大隱靜脈</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O201" s="5" t="inlineStr">
+        <is>
+          <t>大隱靜脈是人體最長的靜脈。</t>
+        </is>
+      </c>
+      <c r="P201" s="5" t="inlineStr">
+        <is>
+          <t>「主要靜脈」：回想下肢的長淺層靜脈。</t>
+        </is>
+      </c>
+      <c r="Q201" s="5" t="inlineStr">
+        <is>
+          <t>回想下肢的長淺層靜脈。 → 回到「主要靜脈」比較：上腔靜脈收集頭頸與上肢（左右頭臂靜脈匯合）</t>
+        </is>
+      </c>
+      <c r="R201" s="5" t="inlineStr">
+        <is>
+          <t>選擇「大隱靜脈」。大隱靜脈是人體最長的靜脈。</t>
+        </is>
+      </c>
+      <c r="S201" s="5" t="inlineStr">
+        <is>
+          <t>大隱靜脈是人體最長的靜脈。</t>
+        </is>
+      </c>
+      <c r="T201" s="3"/>
+      <c r="U201" s="3"/>
+      <c r="V201" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W201" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X201" s="3"/>
+    </row>
+    <row r="202" ht="134" hidden="0" customHeight="1">
+      <c r="A202" s="3"/>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-case-q01</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>【生活情境】手腕拇指側摸脈搏，是哪條動脈？</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>肱動脈</t>
+        </is>
+      </c>
+      <c r="J202" s="5" t="inlineStr">
+        <is>
+          <t>橈動脈</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="inlineStr">
+        <is>
+          <t>頸動脈</t>
+        </is>
+      </c>
+      <c r="L202" s="5" t="inlineStr">
+        <is>
+          <t>尺動脈</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O202" s="5" t="inlineStr">
+        <is>
+          <t>手腕拇指側可摸到橈動脈脈搏。</t>
+        </is>
+      </c>
+      <c r="P202" s="5" t="inlineStr">
+        <is>
+          <t>「上肢動脈」：拇指側對應橈骨一側。</t>
+        </is>
+      </c>
+      <c r="Q202" s="5" t="inlineStr">
+        <is>
+          <t>拇指側對應橈骨一側。 → 回到「上肢動脈」比較：鎖骨下 → 腋 → 肱 → 橈、尺動脈</t>
+        </is>
+      </c>
+      <c r="R202" s="5" t="inlineStr">
+        <is>
+          <t>選擇「橈動脈」。手腕拇指側可摸到橈動脈脈搏。</t>
+        </is>
+      </c>
+      <c r="S202" s="5" t="inlineStr">
+        <is>
+          <t>手腕拇指側可摸到橈動脈脈搏。</t>
+        </is>
+      </c>
+      <c r="T202" s="3"/>
+      <c r="U202" s="3"/>
+      <c r="V202" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W202" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X202" s="3"/>
+    </row>
+    <row r="203" ht="134" hidden="0" customHeight="1">
+      <c r="A203" s="3"/>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-case-q02</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】抽血常選肘窩哪條淺靜脈？</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>頸外靜脈</t>
+        </is>
+      </c>
+      <c r="J203" s="5" t="inlineStr">
+        <is>
+          <t>股靜脈</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="inlineStr">
+        <is>
+          <t>肘正中靜脈</t>
+        </is>
+      </c>
+      <c r="L203" s="5" t="inlineStr">
+        <is>
+          <t>大隱靜脈</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O203" s="5" t="inlineStr">
+        <is>
+          <t>肘正中靜脈是肘窩常用的淺靜脈。</t>
+        </is>
+      </c>
+      <c r="P203" s="5" t="inlineStr">
+        <is>
+          <t>「主要靜脈」：找肘窩的淺層靜脈名稱。</t>
+        </is>
+      </c>
+      <c r="Q203" s="5" t="inlineStr">
+        <is>
+          <t>找肘窩的淺層靜脈名稱。 → 回到「主要靜脈」比較：上腔靜脈收集頭頸與上肢（左右頭臂靜脈匯合）</t>
+        </is>
+      </c>
+      <c r="R203" s="5" t="inlineStr">
+        <is>
+          <t>選擇「肘正中靜脈」。肘正中靜脈是肘窩常用的淺靜脈。</t>
+        </is>
+      </c>
+      <c r="S203" s="5" t="inlineStr">
+        <is>
+          <t>肘正中靜脈是肘窩常用的淺靜脈。</t>
+        </is>
+      </c>
+      <c r="T203" s="3"/>
+      <c r="U203" s="3"/>
+      <c r="V203" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W203" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X203" s="3"/>
+    </row>
+    <row r="204" ht="150" hidden="0" customHeight="1">
+      <c r="A204" s="3"/>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-case-q03</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】右手臂的血液由主動脈弓出發的路徑？</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="inlineStr">
+        <is>
+          <t>頭臂幹→右鎖骨下→腋→肱</t>
+        </is>
+      </c>
+      <c r="J204" s="5" t="inlineStr">
+        <is>
+          <t>右頸總→腋→肱</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="inlineStr">
+        <is>
+          <t>腹腔幹→腋→肱</t>
+        </is>
+      </c>
+      <c r="L204" s="5" t="inlineStr">
+        <is>
+          <t>左鎖骨下→腋→肱</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" s="5" t="inlineStr">
+        <is>
+          <t>右上肢由頭臂幹經右鎖骨下、腋、肱動脈供血。</t>
+        </is>
+      </c>
+      <c r="P204" s="5" t="inlineStr">
+        <is>
+          <t>「主動脈弓三分支」：人體右側先經頭臂幹。</t>
+        </is>
+      </c>
+      <c r="Q204" s="5" t="inlineStr">
+        <is>
+          <t>人體右側先經頭臂幹。 → 回到「主動脈弓三分支」比較：頭臂幹（再分右頸總、右鎖骨下）、左頸總動脈、左鎖骨下動脈</t>
+        </is>
+      </c>
+      <c r="R204" s="5" t="inlineStr">
+        <is>
+          <t>選擇「頭臂幹→右鎖骨下→腋→肱」。右上肢由頭臂幹經右鎖骨下、腋、肱動脈供血。</t>
+        </is>
+      </c>
+      <c r="S204" s="5" t="inlineStr">
+        <is>
+          <t>右上肢由頭臂幹經右鎖骨下、腋、肱動脈供血。</t>
+        </is>
+      </c>
+      <c r="T204" s="3"/>
+      <c r="U204" s="3"/>
+      <c r="V204" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W204" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X204" s="3"/>
+    </row>
+    <row r="205" ht="134" hidden="0" customHeight="1">
+      <c r="A205" s="3"/>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-case-q04</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】左腳靜脈血回心的路徑？</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>大隱靜脈→肺靜脈→左心房</t>
+        </is>
+      </c>
+      <c r="J205" s="5" t="inlineStr">
+        <is>
+          <t>膕靜脈→主動脈→右心房</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="inlineStr">
+        <is>
+          <t>股靜脈→上腔靜脈→左心房</t>
+        </is>
+      </c>
+      <c r="L205" s="5" t="inlineStr">
+        <is>
+          <t>股靜脈→髂外→髂總→下腔靜脈→右心房</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O205" s="5" t="inlineStr">
+        <is>
+          <t>下肢靜脈經股、髂外、髂總、下腔靜脈回右心房。</t>
+        </is>
+      </c>
+      <c r="P205" s="5" t="inlineStr">
+        <is>
+          <t>「主要靜脈」：腳的回流經下腔靜脈進右心房。</t>
+        </is>
+      </c>
+      <c r="Q205" s="5" t="inlineStr">
+        <is>
+          <t>腳的回流經下腔靜脈進右心房。 → 回到「主要靜脈」比較：上腔靜脈收集頭頸與上肢（左右頭臂靜脈匯合）</t>
+        </is>
+      </c>
+      <c r="R205" s="5" t="inlineStr">
+        <is>
+          <t>選擇「股靜脈→髂外→髂總→下腔靜脈→右心房」。下肢靜脈經股、髂外、髂總、下腔靜脈回右心房。</t>
+        </is>
+      </c>
+      <c r="S205" s="5" t="inlineStr">
+        <is>
+          <t>下肢靜脈經股、髂外、髂總、下腔靜脈回右心房。</t>
+        </is>
+      </c>
+      <c r="T205" s="3"/>
+      <c r="U205" s="3"/>
+      <c r="V205" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W205" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X205" s="3"/>
+    </row>
+    <row r="206" ht="166" hidden="0" customHeight="1">
+      <c r="A206" s="3"/>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>major-vessels-case-q05</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>心臟II</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】腹腔幹主要供應？</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>腎臟</t>
+        </is>
+      </c>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t>胃、肝、脾等上腹部器官</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="inlineStr">
+        <is>
+          <t>大腦</t>
+        </is>
+      </c>
+      <c r="L206" s="5" t="inlineStr">
+        <is>
+          <t>下肢</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" s="5" t="inlineStr">
+        <is>
+          <t>腹腔幹供應胃、肝、脾等上腹部器官。</t>
+        </is>
+      </c>
+      <c r="P206" s="5" t="inlineStr">
+        <is>
+          <t>「腹主動脈分支」：對照腹腔幹與腎動脈的供應部位。</t>
+        </is>
+      </c>
+      <c r="Q206" s="5" t="inlineStr">
+        <is>
+          <t>對照腹腔幹與腎動脈的供應部位。 → 回到「腹主動脈分支」比較：不成對的腹腔幹（胃、肝、脾）、上腸繫膜、下腸繫膜動脈</t>
+        </is>
+      </c>
+      <c r="R206" s="5" t="inlineStr">
+        <is>
+          <t>選擇「胃、肝、脾等上腹部器官」。腹腔幹供應胃、肝、脾等上腹部器官。</t>
+        </is>
+      </c>
+      <c r="S206" s="5" t="inlineStr">
+        <is>
+          <t>腹腔幹供應胃、肝、脾等上腹部器官。</t>
+        </is>
+      </c>
+      <c r="T206" s="3"/>
+      <c r="U206" s="3"/>
+      <c r="V206" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="W206" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X206" s="3"/>
+    </row>
+    <row r="207" ht="134" hidden="0" customHeight="1">
+      <c r="A207" s="3"/>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>血型由何決定？</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>血漿顏色</t>
+        </is>
+      </c>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>血小板形狀</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>紅血球表面抗原</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>白血球數目</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" s="5" t="inlineStr">
+        <is>
+          <t>血型由紅血球表面抗原（凝集原）決定。</t>
+        </is>
+      </c>
+      <c r="P207" s="5" t="inlineStr">
+        <is>
+          <t>「血型與紅血球抗原」：看紅血球表面，而非血漿顏色。</t>
+        </is>
+      </c>
+      <c r="Q207" s="5" t="inlineStr">
+        <is>
+          <t>看紅血球表面，而非血漿顏色。 → 回到「血型與紅血球抗原」比較：血型由紅血球表面抗原（凝集原）決定</t>
+        </is>
+      </c>
+      <c r="R207" s="5" t="inlineStr">
+        <is>
+          <t>選擇「紅血球表面抗原」。血型由紅血球表面抗原（凝集原）決定。</t>
+        </is>
+      </c>
+      <c r="S207" s="5" t="inlineStr">
+        <is>
+          <t>血型由紅血球表面抗原（凝集原）決定。</t>
+        </is>
+      </c>
+      <c r="T207" s="3"/>
+      <c r="U207" s="3"/>
+      <c r="V207" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W207" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X207" s="3"/>
+    </row>
+    <row r="208" ht="134" hidden="0" customHeight="1">
+      <c r="A208" s="3"/>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>A 型血漿中的抗體？</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>抗 B</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>抗 A 與抗 B</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="inlineStr">
+        <is>
+          <t>抗 A</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" s="5" t="inlineStr">
+        <is>
+          <t>A 型有 A 抗原與抗 B 抗體。</t>
+        </is>
+      </c>
+      <c r="P208" s="5" t="inlineStr">
+        <is>
+          <t>「ABO 系統」：A 型具有 A 抗原，血漿抗體對應哪個另一種抗原？</t>
+        </is>
+      </c>
+      <c r="Q208" s="5" t="inlineStr">
+        <is>
+          <t>A 型具有 A 抗原，血漿抗體對應哪個另一種抗原？ → 回到「ABO 系統」比較：A 型有 A 抗原、抗 B 抗體</t>
+        </is>
+      </c>
+      <c r="R208" s="5" t="inlineStr">
+        <is>
+          <t>選擇「抗 B」。A 型有 A 抗原與抗 B 抗體。</t>
+        </is>
+      </c>
+      <c r="S208" s="5" t="inlineStr">
+        <is>
+          <t>A 型有 A 抗原與抗 B 抗體。</t>
+        </is>
+      </c>
+      <c r="T208" s="3"/>
+      <c r="U208" s="3"/>
+      <c r="V208" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W208" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X208" s="3"/>
+    </row>
+    <row r="209" ht="118" hidden="0" customHeight="1">
+      <c r="A209" s="3"/>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>O 型紅血球的抗原？</t>
+        </is>
+      </c>
+      <c r="I209" s="5" t="inlineStr">
+        <is>
+          <t>只有 B</t>
+        </is>
+      </c>
+      <c r="J209" s="5" t="inlineStr">
+        <is>
+          <t>A 與 B</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="inlineStr">
+        <is>
+          <t>只有 A</t>
+        </is>
+      </c>
+      <c r="L209" s="5" t="inlineStr">
+        <is>
+          <t>無 A 也無 B</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O209" s="5" t="inlineStr">
+        <is>
+          <t>O 型紅血球無 A、B 抗原。</t>
+        </is>
+      </c>
+      <c r="P209" s="5" t="inlineStr">
+        <is>
+          <t>「ABO 系統」：O 型在 ABO 系統中不帶哪兩種抗原？</t>
+        </is>
+      </c>
+      <c r="Q209" s="5" t="inlineStr">
+        <is>
+          <t>O 型在 ABO 系統中不帶哪兩種抗原？ → 回到「ABO 系統」比較：A 型有 A 抗原、抗 B 抗體</t>
+        </is>
+      </c>
+      <c r="R209" s="5" t="inlineStr">
+        <is>
+          <t>選擇「無 A 也無 B」。O 型紅血球無 A、B 抗原。</t>
+        </is>
+      </c>
+      <c r="S209" s="5" t="inlineStr">
+        <is>
+          <t>O 型紅血球無 A、B 抗原。</t>
+        </is>
+      </c>
+      <c r="T209" s="3"/>
+      <c r="U209" s="3"/>
+      <c r="V209" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W209" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X209" s="3"/>
+    </row>
+    <row r="210" ht="118" hidden="0" customHeight="1">
+      <c r="A210" s="3"/>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>AB 型血漿中的抗體？</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>抗 B</t>
+        </is>
+      </c>
+      <c r="J210" s="5" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="inlineStr">
+        <is>
+          <t>抗 A 與抗 B</t>
+        </is>
+      </c>
+      <c r="L210" s="5" t="inlineStr">
+        <is>
+          <t>抗 A</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O210" s="5" t="inlineStr">
+        <is>
+          <t>AB 型有 A、B 抗原，血漿無對應的抗 A、抗 B 抗體。</t>
+        </is>
+      </c>
+      <c r="P210" s="5" t="inlineStr">
+        <is>
+          <t>「ABO 系統」：AB 型同時具有 A 與 B 抗原。</t>
+        </is>
+      </c>
+      <c r="Q210" s="5" t="inlineStr">
+        <is>
+          <t>AB 型同時具有 A 與 B 抗原。 → 回到「ABO 系統」比較：A 型有 A 抗原、抗 B 抗體</t>
+        </is>
+      </c>
+      <c r="R210" s="5" t="inlineStr">
+        <is>
+          <t>選擇「無」。AB 型有 A、B 抗原，血漿無對應的抗 A、抗 B 抗體。</t>
+        </is>
+      </c>
+      <c r="S210" s="5" t="inlineStr">
+        <is>
+          <t>AB 型有 A、B 抗原，血漿無對應的抗 A、抗 B 抗體。</t>
+        </is>
+      </c>
+      <c r="T210" s="3"/>
+      <c r="U210" s="3"/>
+      <c r="V210" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W210" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X210" s="3"/>
+    </row>
+    <row r="211" ht="118" hidden="0" customHeight="1">
+      <c r="A211" s="3"/>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>Rh 陽性指？</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>無 D 抗原</t>
+        </is>
+      </c>
+      <c r="J211" s="5" t="inlineStr">
+        <is>
+          <t>有 A 抗原</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="inlineStr">
+        <is>
+          <t>有 D 抗原</t>
+        </is>
+      </c>
+      <c r="L211" s="5" t="inlineStr">
+        <is>
+          <t>有抗 D 抗體</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O211" s="5" t="inlineStr">
+        <is>
+          <t>具有 D 抗原為 Rh 陽性。</t>
+        </is>
+      </c>
+      <c r="P211" s="5" t="inlineStr">
+        <is>
+          <t>「Rh 系統」：Rh 系統的關鍵是 D 抗原。</t>
+        </is>
+      </c>
+      <c r="Q211" s="5" t="inlineStr">
+        <is>
+          <t>Rh 系統的關鍵是 D 抗原。 → 回到「Rh 系統」比較：有 D 抗原為 Rh 陽性</t>
+        </is>
+      </c>
+      <c r="R211" s="5" t="inlineStr">
+        <is>
+          <t>選擇「有 D 抗原」。具有 D 抗原為 Rh 陽性。</t>
+        </is>
+      </c>
+      <c r="S211" s="5" t="inlineStr">
+        <is>
+          <t>具有 D 抗原為 Rh 陽性。</t>
+        </is>
+      </c>
+      <c r="T211" s="3"/>
+      <c r="U211" s="3"/>
+      <c r="V211" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W211" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X211" s="3"/>
+    </row>
+    <row r="212" ht="134" hidden="0" customHeight="1">
+      <c r="A212" s="3"/>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>凝集反應是？</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>抗原與對應抗體結合使紅血球聚集</t>
+        </is>
+      </c>
+      <c r="J212" s="5" t="inlineStr">
+        <is>
+          <t>紅血球攜帶氧氣</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="inlineStr">
+        <is>
+          <t>白血球吞噬細菌</t>
+        </is>
+      </c>
+      <c r="L212" s="5" t="inlineStr">
+        <is>
+          <t>血小板形成血栓</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" s="5" t="inlineStr">
+        <is>
+          <t>抗原與對應抗體結合，使紅血球黏聚而發生凝集。</t>
+        </is>
+      </c>
+      <c r="P212" s="5" t="inlineStr">
+        <is>
+          <t>「凝集反應」：分清紅血球凝集與血小板作用。</t>
+        </is>
+      </c>
+      <c r="Q212" s="5" t="inlineStr">
+        <is>
+          <t>分清紅血球凝集與血小板作用。 → 回到「凝集反應」比較：抗原遇對應抗體，紅血球黏聚，進而破壞</t>
+        </is>
+      </c>
+      <c r="R212" s="5" t="inlineStr">
+        <is>
+          <t>選擇「抗原與對應抗體結合使紅血球聚集」。抗原與對應抗體結合，使紅血球黏聚而發生凝集。</t>
+        </is>
+      </c>
+      <c r="S212" s="5" t="inlineStr">
+        <is>
+          <t>抗原與對應抗體結合，使紅血球黏聚而發生凝集。</t>
+        </is>
+      </c>
+      <c r="T212" s="3"/>
+      <c r="U212" s="3"/>
+      <c r="V212" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W212" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X212" s="3"/>
+    </row>
+    <row r="213" ht="150" hidden="0" customHeight="1">
+      <c r="A213" s="3"/>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-case-q01</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】抗 A 凝集、抗 B 不凝集，ABO 血型？</t>
+        </is>
+      </c>
+      <c r="I213" s="5" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="J213" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L213" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" s="5" t="inlineStr">
+        <is>
+          <t>抗 A 凝集、抗 B 不凝集表示有 A、無 B 抗原，是 A 型。</t>
+        </is>
+      </c>
+      <c r="P213" s="5" t="inlineStr">
+        <is>
+          <t>「血型鑑定」：凝集表示玻片抗體找到對應抗原。</t>
+        </is>
+      </c>
+      <c r="Q213" s="5" t="inlineStr">
+        <is>
+          <t>凝集表示玻片抗體找到對應抗原。 → 回到「血型鑑定」比較：分別加入抗 A、抗 B、抗 D 血清，看是否凝集</t>
+        </is>
+      </c>
+      <c r="R213" s="5" t="inlineStr">
+        <is>
+          <t>選擇「A」。抗 A 凝集、抗 B 不凝集表示有 A、無 B 抗原，是 A 型。</t>
+        </is>
+      </c>
+      <c r="S213" s="5" t="inlineStr">
+        <is>
+          <t>抗 A 凝集、抗 B 不凝集表示有 A、無 B 抗原，是 A 型。</t>
+        </is>
+      </c>
+      <c r="T213" s="3"/>
+      <c r="U213" s="3"/>
+      <c r="V213" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W213" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X213" s="3"/>
+    </row>
+    <row r="214" ht="166" hidden="0" customHeight="1">
+      <c r="A214" s="3"/>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-case-q02</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>【實驗觀察】抗 A、抗 B 都不凝集？</t>
+        </is>
+      </c>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J214" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="L214" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O214" s="5" t="inlineStr">
+        <is>
+          <t>抗 A、抗 B 都不凝集表示無 A、B 抗原，是 O 型。</t>
+        </is>
+      </c>
+      <c r="P214" s="5" t="inlineStr">
+        <is>
+          <t>「血型鑑定」：兩種 ABO 血清都不凝集，表示哪兩種抗原都沒有？</t>
+        </is>
+      </c>
+      <c r="Q214" s="5" t="inlineStr">
+        <is>
+          <t>兩種 ABO 血清都不凝集，表示哪兩種抗原都沒有？ → 回到「血型鑑定」比較：分別加入抗 A、抗 B、抗 D 血清，看是否凝集</t>
+        </is>
+      </c>
+      <c r="R214" s="5" t="inlineStr">
+        <is>
+          <t>選擇「O」。抗 A、抗 B 都不凝集表示無 A、B 抗原，是 O 型。</t>
+        </is>
+      </c>
+      <c r="S214" s="5" t="inlineStr">
+        <is>
+          <t>抗 A、抗 B 都不凝集表示無 A、B 抗原，是 O 型。</t>
+        </is>
+      </c>
+      <c r="T214" s="3"/>
+      <c r="U214" s="3"/>
+      <c r="V214" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W214" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X214" s="3"/>
+    </row>
+    <row r="215" ht="150" hidden="0" customHeight="1">
+      <c r="A215" s="3"/>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-case-q03</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】B 型受血者輸入 A 型紅血球會？</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>受血者變成 A 型</t>
+        </is>
+      </c>
+      <c r="J215" s="5" t="inlineStr">
+        <is>
+          <t>輸入的血漿使受血者紅血球增加</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="inlineStr">
+        <is>
+          <t>受血者的抗 A 抗體使輸入紅血球凝集</t>
+        </is>
+      </c>
+      <c r="L215" s="5" t="inlineStr">
+        <is>
+          <t>完全沒有反應</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O215" s="5" t="inlineStr">
+        <is>
+          <t>B 型血漿中的抗 A 抗體與輸入 A 型紅血球抗原結合，造成凝集。</t>
+        </is>
+      </c>
+      <c r="P215" s="5" t="inlineStr">
+        <is>
+          <t>「凝集反應」：B 型血漿有抗 A 抗體，輸入的是 A 型紅血球。</t>
+        </is>
+      </c>
+      <c r="Q215" s="5" t="inlineStr">
+        <is>
+          <t>B 型血漿有抗 A 抗體，輸入的是 A 型紅血球。 → 回到「凝集反應」比較：抗原遇對應抗體，紅血球黏聚，進而破壞</t>
+        </is>
+      </c>
+      <c r="R215" s="5" t="inlineStr">
+        <is>
+          <t>選擇「受血者的抗 A 抗體使輸入紅血球凝集」。B 型血漿中的抗 A 抗體與輸入 A 型紅血球抗原結合，造成凝集。</t>
+        </is>
+      </c>
+      <c r="S215" s="5" t="inlineStr">
+        <is>
+          <t>B 型血漿中的抗 A 抗體與輸入 A 型紅血球抗原結合，造成凝集。</t>
+        </is>
+      </c>
+      <c r="T215" s="3"/>
+      <c r="U215" s="3"/>
+      <c r="V215" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W215" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X215" s="3"/>
+    </row>
+    <row r="216" ht="118" hidden="0" customHeight="1">
+      <c r="A216" s="3"/>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-case-q04</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】Rh 陰性者第一次接觸 Rh 陽性血，抗 D 抗體？</t>
+        </is>
+      </c>
+      <c r="I216" s="5" t="inlineStr">
+        <is>
+          <t>接觸後才逐漸產生</t>
+        </is>
+      </c>
+      <c r="J216" s="5" t="inlineStr">
+        <is>
+          <t>永遠不會產生</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="inlineStr">
+        <is>
+          <t>會轉成 Rh 陽性</t>
+        </is>
+      </c>
+      <c r="L216" s="5" t="inlineStr">
+        <is>
+          <t>出生就大量存在</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O216" s="5" t="inlineStr">
+        <is>
+          <t>Rh 陰性者通常不天生帶抗 D，接觸 Rh 陽性血後才逐漸產生。</t>
+        </is>
+      </c>
+      <c r="P216" s="5" t="inlineStr">
+        <is>
+          <t>「Rh 系統」：Rh 陰性通常不天生帶抗 D。</t>
+        </is>
+      </c>
+      <c r="Q216" s="5" t="inlineStr">
+        <is>
+          <t>Rh 陰性通常不天生帶抗 D。 → 回到「Rh 系統」比較：有 D 抗原為 Rh 陽性</t>
+        </is>
+      </c>
+      <c r="R216" s="5" t="inlineStr">
+        <is>
+          <t>選擇「接觸後才逐漸產生」。Rh 陰性者通常不天生帶抗 D，接觸 Rh 陽性血後才逐漸產生。</t>
+        </is>
+      </c>
+      <c r="S216" s="5" t="inlineStr">
+        <is>
+          <t>Rh 陰性者通常不天生帶抗 D，接觸 Rh 陽性血後才逐漸產生。</t>
+        </is>
+      </c>
+      <c r="T216" s="3"/>
+      <c r="U216" s="3"/>
+      <c r="V216" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W216" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X216" s="3"/>
+    </row>
+    <row r="217" ht="134" hidden="0" customHeight="1">
+      <c r="A217" s="3"/>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>blood-types-case-q05</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】O 型紅血球傳統稱萬能捐血者，原因？</t>
+        </is>
+      </c>
+      <c r="I217" s="5" t="inlineStr">
+        <is>
+          <t>含最多血紅素</t>
+        </is>
+      </c>
+      <c r="J217" s="5" t="inlineStr">
+        <is>
+          <t>不含 D 抗原</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="inlineStr">
+        <is>
+          <t>血漿中沒有抗體</t>
+        </is>
+      </c>
+      <c r="L217" s="5" t="inlineStr">
+        <is>
+          <t>紅血球上沒有 A 與 B 抗原</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O217" s="5" t="inlineStr">
+        <is>
+          <t>傳統用語來自 O 型紅血球無 A、B 抗原；輸血仍以同型為原則。</t>
+        </is>
+      </c>
+      <c r="P217" s="5" t="inlineStr">
+        <is>
+          <t>「輸血原則」：注意這是 ABO 紅血球抗原的傳統用語。</t>
+        </is>
+      </c>
+      <c r="Q217" s="5" t="inlineStr">
+        <is>
+          <t>注意這是 ABO 紅血球抗原的傳統用語。 → 回到「輸血原則」比較：以同型輸血為原則</t>
+        </is>
+      </c>
+      <c r="R217" s="5" t="inlineStr">
+        <is>
+          <t>選擇「紅血球上沒有 A 與 B 抗原」。傳統用語來自 O 型紅血球無 A、B 抗原；輸血仍以同型為原則。</t>
+        </is>
+      </c>
+      <c r="S217" s="5" t="inlineStr">
+        <is>
+          <t>傳統用語來自 O 型紅血球無 A、B 抗原；輸血仍以同型為原則。</t>
+        </is>
+      </c>
+      <c r="T217" s="3"/>
+      <c r="U217" s="3"/>
+      <c r="V217" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="W217" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X217" s="3"/>
+    </row>
+    <row r="218" ht="134" hidden="0" customHeight="1">
+      <c r="A218" s="3"/>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>初級淋巴器官是？</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>扁桃腺與闌尾</t>
+        </is>
+      </c>
+      <c r="J218" s="5" t="inlineStr">
+        <is>
+          <t>骨髓與胸腺</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="inlineStr">
+        <is>
+          <t>肝臟與腎臟</t>
+        </is>
+      </c>
+      <c r="L218" s="5" t="inlineStr">
+        <is>
+          <t>淋巴結與脾臟</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" s="5" t="inlineStr">
+        <is>
+          <t>骨髓與胸腺是初級淋巴器官，負責生成與成熟。</t>
+        </is>
+      </c>
+      <c r="P218" s="5" t="inlineStr">
+        <is>
+          <t>「初級與次級」：初級器官負責生成與成熟。</t>
+        </is>
+      </c>
+      <c r="Q218" s="5" t="inlineStr">
+        <is>
+          <t>初級器官負責生成與成熟。 → 回到「初級與次級」比較：初級（骨髓、胸腺）負責淋巴球生成與成熟</t>
+        </is>
+      </c>
+      <c r="R218" s="5" t="inlineStr">
+        <is>
+          <t>選擇「骨髓與胸腺」。骨髓與胸腺是初級淋巴器官，負責生成與成熟。</t>
+        </is>
+      </c>
+      <c r="S218" s="5" t="inlineStr">
+        <is>
+          <t>骨髓與胸腺是初級淋巴器官，負責生成與成熟。</t>
+        </is>
+      </c>
+      <c r="T218" s="3"/>
+      <c r="U218" s="3"/>
+      <c r="V218" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W218" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X218" s="3"/>
+    </row>
+    <row r="219" ht="134" hidden="0" customHeight="1">
+      <c r="A219" s="3"/>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在何處成熟？</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>淋巴結</t>
+        </is>
+      </c>
+      <c r="J219" s="5" t="inlineStr">
+        <is>
+          <t>扁桃腺</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="inlineStr">
+        <is>
+          <t>胸腺</t>
+        </is>
+      </c>
+      <c r="L219" s="5" t="inlineStr">
+        <is>
+          <t>脾臟</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O219" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在胸腺成熟。</t>
+        </is>
+      </c>
+      <c r="P219" s="5" t="inlineStr">
+        <is>
+          <t>「胸腺」：T 細胞與 B 細胞的成熟位置不同。</t>
+        </is>
+      </c>
+      <c r="Q219" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞與 B 細胞的成熟位置不同。 → 回到「胸腺」比較：位於胸骨後方、縱膈前上部</t>
+        </is>
+      </c>
+      <c r="R219" s="5" t="inlineStr">
+        <is>
+          <t>選擇「胸腺」。T 細胞在胸腺成熟。</t>
+        </is>
+      </c>
+      <c r="S219" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在胸腺成熟。</t>
+        </is>
+      </c>
+      <c r="T219" s="3"/>
+      <c r="U219" s="3"/>
+      <c r="V219" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W219" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X219" s="3"/>
+    </row>
+    <row r="220" ht="134" hidden="0" customHeight="1">
+      <c r="A220" s="3"/>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>人體最大的淋巴器官？</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>脾臟</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="inlineStr">
+        <is>
+          <t>淋巴結</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="inlineStr">
+        <is>
+          <t>扁桃腺</t>
+        </is>
+      </c>
+      <c r="L220" s="5" t="inlineStr">
+        <is>
+          <t>胸腺</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" s="5" t="inlineStr">
+        <is>
+          <t>脾臟位於左上腹，是最大的淋巴器官。</t>
+        </is>
+      </c>
+      <c r="P220" s="5" t="inlineStr">
+        <is>
+          <t>「脾臟」：比較胸腺、脾臟與單個淋巴結。</t>
+        </is>
+      </c>
+      <c r="Q220" s="5" t="inlineStr">
+        <is>
+          <t>比較胸腺、脾臟與單個淋巴結。 → 回到「脾臟」比較：位於左上腹，是最大的淋巴器官</t>
+        </is>
+      </c>
+      <c r="R220" s="5" t="inlineStr">
+        <is>
+          <t>選擇「脾臟」。脾臟位於左上腹，是最大的淋巴器官。</t>
+        </is>
+      </c>
+      <c r="S220" s="5" t="inlineStr">
+        <is>
+          <t>脾臟位於左上腹，是最大的淋巴器官。</t>
+        </is>
+      </c>
+      <c r="T220" s="3"/>
+      <c r="U220" s="3"/>
+      <c r="V220" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W220" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X220" s="3"/>
+    </row>
+    <row r="221" ht="134" hidden="0" customHeight="1">
+      <c r="A221" s="3"/>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>脾臟清除老舊紅血球主要在？</t>
+        </is>
+      </c>
+      <c r="I221" s="5" t="inlineStr">
+        <is>
+          <t>皮質</t>
+        </is>
+      </c>
+      <c r="J221" s="5" t="inlineStr">
+        <is>
+          <t>副皮質</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="inlineStr">
+        <is>
+          <t>白髓</t>
+        </is>
+      </c>
+      <c r="L221" s="5" t="inlineStr">
+        <is>
+          <t>紅髓</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O221" s="5" t="inlineStr">
+        <is>
+          <t>紅髓過濾血液並清除老舊紅血球。</t>
+        </is>
+      </c>
+      <c r="P221" s="5" t="inlineStr">
+        <is>
+          <t>「脾臟」：分清脾臟白髓與紅髓。</t>
+        </is>
+      </c>
+      <c r="Q221" s="5" t="inlineStr">
+        <is>
+          <t>分清脾臟白髓與紅髓。 → 回到「脾臟」比較：位於左上腹，是最大的淋巴器官</t>
+        </is>
+      </c>
+      <c r="R221" s="5" t="inlineStr">
+        <is>
+          <t>選擇「紅髓」。紅髓過濾血液並清除老舊紅血球。</t>
+        </is>
+      </c>
+      <c r="S221" s="5" t="inlineStr">
+        <is>
+          <t>紅髓過濾血液並清除老舊紅血球。</t>
+        </is>
+      </c>
+      <c r="T221" s="3"/>
+      <c r="U221" s="3"/>
+      <c r="V221" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W221" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X221" s="3"/>
+    </row>
+    <row r="222" ht="150" hidden="0" customHeight="1">
+      <c r="A222" s="3"/>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>腭扁桃腺位於？</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="inlineStr">
+        <is>
+          <t>左上腹</t>
+        </is>
+      </c>
+      <c r="J222" s="5" t="inlineStr">
+        <is>
+          <t>口咽兩側</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>腋窩</t>
+        </is>
+      </c>
+      <c r="L222" s="5" t="inlineStr">
+        <is>
+          <t>胸骨後方</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" s="5" t="inlineStr">
+        <is>
+          <t>腭扁桃腺位於口咽兩側。</t>
+        </is>
+      </c>
+      <c r="P222" s="5" t="inlineStr">
+        <is>
+          <t>「扁桃腺」：找口咽入口兩側的淋巴組織。</t>
+        </is>
+      </c>
+      <c r="Q222" s="5" t="inlineStr">
+        <is>
+          <t>找口咽入口兩側的淋巴組織。 → 回到「扁桃腺」比較：咽扁桃腺、腭扁桃腺、舌扁桃腺環繞咽部，形成入口防線</t>
+        </is>
+      </c>
+      <c r="R222" s="5" t="inlineStr">
+        <is>
+          <t>選擇「口咽兩側」。腭扁桃腺位於口咽兩側。</t>
+        </is>
+      </c>
+      <c r="S222" s="5" t="inlineStr">
+        <is>
+          <t>腭扁桃腺位於口咽兩側。</t>
+        </is>
+      </c>
+      <c r="T222" s="3"/>
+      <c r="U222" s="3"/>
+      <c r="V222" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W222" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X222" s="3"/>
+    </row>
+    <row r="223" ht="166" hidden="0" customHeight="1">
+      <c r="A223" s="3"/>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>培氏斑位於？</t>
+        </is>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="J223" s="5" t="inlineStr">
+        <is>
+          <t>氣管</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="inlineStr">
+        <is>
+          <t>小腸迴腸黏膜</t>
+        </is>
+      </c>
+      <c r="L223" s="5" t="inlineStr">
+        <is>
+          <t>胃壁</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O223" s="5" t="inlineStr">
+        <is>
+          <t>培氏斑位於小腸迴腸黏膜。</t>
+        </is>
+      </c>
+      <c r="P223" s="5" t="inlineStr">
+        <is>
+          <t>「黏膜相關淋巴組織」：培氏斑是消化道黏膜的淋巴組織。</t>
+        </is>
+      </c>
+      <c r="Q223" s="5" t="inlineStr">
+        <is>
+          <t>培氏斑是消化道黏膜的淋巴組織。 → 回到「黏膜相關淋巴組織」比較：散布在消化道、呼吸道黏膜，如小腸迴腸的培氏斑、闌尾</t>
+        </is>
+      </c>
+      <c r="R223" s="5" t="inlineStr">
+        <is>
+          <t>選擇「小腸迴腸黏膜」。培氏斑位於小腸迴腸黏膜。</t>
+        </is>
+      </c>
+      <c r="S223" s="5" t="inlineStr">
+        <is>
+          <t>培氏斑位於小腸迴腸黏膜。</t>
+        </is>
+      </c>
+      <c r="T223" s="3"/>
+      <c r="U223" s="3"/>
+      <c r="V223" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W223" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X223" s="3"/>
+    </row>
+    <row r="224" ht="134" hidden="0" customHeight="1">
+      <c r="A224" s="3"/>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-case-q01</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】脾臟與淋巴結的過濾對象？</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>脾臟過濾血液，淋巴結過濾淋巴</t>
+        </is>
+      </c>
+      <c r="J224" s="5" t="inlineStr">
+        <is>
+          <t>兩者都過濾尿液</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="inlineStr">
+        <is>
+          <t>脾臟過濾淋巴，淋巴結過濾血液</t>
+        </is>
+      </c>
+      <c r="L224" s="5" t="inlineStr">
+        <is>
+          <t>兩者都過濾淋巴</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" s="5" t="inlineStr">
+        <is>
+          <t>脾臟過濾血液，淋巴結過濾淋巴。</t>
+        </is>
+      </c>
+      <c r="P224" s="5" t="inlineStr">
+        <is>
+          <t>「初級與次級」：分清血液過濾與淋巴過濾。</t>
+        </is>
+      </c>
+      <c r="Q224" s="5" t="inlineStr">
+        <is>
+          <t>分清血液過濾與淋巴過濾。 → 回到「初級與次級」比較：初級（骨髓、胸腺）負責淋巴球生成與成熟</t>
+        </is>
+      </c>
+      <c r="R224" s="5" t="inlineStr">
+        <is>
+          <t>選擇「脾臟過濾血液，淋巴結過濾淋巴」。脾臟過濾血液，淋巴結過濾淋巴。</t>
+        </is>
+      </c>
+      <c r="S224" s="5" t="inlineStr">
+        <is>
+          <t>脾臟過濾血液，淋巴結過濾淋巴。</t>
+        </is>
+      </c>
+      <c r="T224" s="3"/>
+      <c r="U224" s="3"/>
+      <c r="V224" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W224" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X224" s="3"/>
+    </row>
+    <row r="225" ht="134" hidden="0" customHeight="1">
+      <c r="A225" s="3"/>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-case-q02</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】成年後胸腺的變化？</t>
+        </is>
+      </c>
+      <c r="I225" s="5" t="inlineStr">
+        <is>
+          <t>變成脾臟</t>
+        </is>
+      </c>
+      <c r="J225" s="5" t="inlineStr">
+        <is>
+          <t>停止所有功能並消失</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="inlineStr">
+        <is>
+          <t>持續變大</t>
+        </is>
+      </c>
+      <c r="L225" s="5" t="inlineStr">
+        <is>
+          <t>逐漸退化並被脂肪取代</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O225" s="5" t="inlineStr">
+        <is>
+          <t>胸腺青春期後逐漸退化，被脂肪組織取代。</t>
+        </is>
+      </c>
+      <c r="P225" s="5" t="inlineStr">
+        <is>
+          <t>「胸腺」：回想胸腺在青春期後的變化。</t>
+        </is>
+      </c>
+      <c r="Q225" s="5" t="inlineStr">
+        <is>
+          <t>回想胸腺在青春期後的變化。 → 回到「胸腺」比較：位於胸骨後方、縱膈前上部</t>
+        </is>
+      </c>
+      <c r="R225" s="5" t="inlineStr">
+        <is>
+          <t>選擇「逐漸退化並被脂肪取代」。胸腺青春期後逐漸退化，被脂肪組織取代。</t>
+        </is>
+      </c>
+      <c r="S225" s="5" t="inlineStr">
+        <is>
+          <t>胸腺青春期後逐漸退化，被脂肪組織取代。</t>
+        </is>
+      </c>
+      <c r="T225" s="3"/>
+      <c r="U225" s="3"/>
+      <c r="V225" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W225" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X225" s="3"/>
+    </row>
+    <row r="226" ht="150" hidden="0" customHeight="1">
+      <c r="A226" s="3"/>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-case-q03</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】經口鼻進入的病原，最先遇到咽部哪一圈淋巴組織？</t>
+        </is>
+      </c>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>胸腺</t>
+        </is>
+      </c>
+      <c r="J226" s="5" t="inlineStr">
+        <is>
+          <t>扁桃腺</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="inlineStr">
+        <is>
+          <t>骨髓</t>
+        </is>
+      </c>
+      <c r="L226" s="5" t="inlineStr">
+        <is>
+          <t>脾臟</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O226" s="5" t="inlineStr">
+        <is>
+          <t>扁桃腺環繞咽部，形成入口防線。</t>
+        </is>
+      </c>
+      <c r="P226" s="5" t="inlineStr">
+        <is>
+          <t>「扁桃腺」：經口鼻進入先到咽部入口。</t>
+        </is>
+      </c>
+      <c r="Q226" s="5" t="inlineStr">
+        <is>
+          <t>經口鼻進入先到咽部入口。 → 回到「扁桃腺」比較：咽扁桃腺、腭扁桃腺、舌扁桃腺環繞咽部，形成入口防線</t>
+        </is>
+      </c>
+      <c r="R226" s="5" t="inlineStr">
+        <is>
+          <t>選擇「扁桃腺」。扁桃腺環繞咽部，形成入口防線。</t>
+        </is>
+      </c>
+      <c r="S226" s="5" t="inlineStr">
+        <is>
+          <t>扁桃腺環繞咽部，形成入口防線。</t>
+        </is>
+      </c>
+      <c r="T226" s="3"/>
+      <c r="U226" s="3"/>
+      <c r="V226" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W226" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X226" s="3"/>
+    </row>
+    <row r="227" ht="134" hidden="0" customHeight="1">
+      <c r="A227" s="3"/>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-case-q04</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>【模型觀察】脾臟白髓的主要功能？</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>製造尿液</t>
+        </is>
+      </c>
+      <c r="J227" s="5" t="inlineStr">
+        <is>
+          <t>分泌胰島素</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="inlineStr">
+        <is>
+          <t>淋巴球參與免疫反應</t>
+        </is>
+      </c>
+      <c r="L227" s="5" t="inlineStr">
+        <is>
+          <t>儲存膽汁</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O227" s="5" t="inlineStr">
+        <is>
+          <t>白髓富含淋巴球，參與免疫反應。</t>
+        </is>
+      </c>
+      <c r="P227" s="5" t="inlineStr">
+        <is>
+          <t>「脾臟」：白髓富含淋巴球。</t>
+        </is>
+      </c>
+      <c r="Q227" s="5" t="inlineStr">
+        <is>
+          <t>白髓富含淋巴球。 → 回到「脾臟」比較：位於左上腹，是最大的淋巴器官</t>
+        </is>
+      </c>
+      <c r="R227" s="5" t="inlineStr">
+        <is>
+          <t>選擇「淋巴球參與免疫反應」。白髓富含淋巴球，參與免疫反應。</t>
+        </is>
+      </c>
+      <c r="S227" s="5" t="inlineStr">
+        <is>
+          <t>白髓富含淋巴球，參與免疫反應。</t>
+        </is>
+      </c>
+      <c r="T227" s="3"/>
+      <c r="U227" s="3"/>
+      <c r="V227" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W227" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X227" s="3"/>
+    </row>
+    <row r="228" ht="166" hidden="0" customHeight="1">
+      <c r="A228" s="3"/>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>lymphoid-organs-case-q05</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>【生理判讀】小腸黏膜的培氏斑屬於？</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>黏膜相關淋巴組織（次級淋巴器官）</t>
+        </is>
+      </c>
+      <c r="J228" s="5" t="inlineStr">
+        <is>
+          <t>內分泌腺</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="inlineStr">
+        <is>
+          <t>消化腺</t>
+        </is>
+      </c>
+      <c r="L228" s="5" t="inlineStr">
+        <is>
+          <t>初級淋巴器官</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" s="5" t="inlineStr">
+        <is>
+          <t>培氏斑是黏膜相關淋巴組織，屬次級淋巴器官。</t>
+        </is>
+      </c>
+      <c r="P228" s="5" t="inlineStr">
+        <is>
+          <t>「黏膜相關淋巴組織」：分清成熟淋巴球與遇見抗原的位置。</t>
+        </is>
+      </c>
+      <c r="Q228" s="5" t="inlineStr">
+        <is>
+          <t>分清成熟淋巴球與遇見抗原的位置。 → 回到「黏膜相關淋巴組織」比較：散布在消化道、呼吸道黏膜，如小腸迴腸的培氏斑、闌尾</t>
+        </is>
+      </c>
+      <c r="R228" s="5" t="inlineStr">
+        <is>
+          <t>選擇「黏膜相關淋巴組織（次級淋巴器官）」。培氏斑是黏膜相關淋巴組織，屬次級淋巴器官。</t>
+        </is>
+      </c>
+      <c r="S228" s="5" t="inlineStr">
+        <is>
+          <t>培氏斑是黏膜相關淋巴組織，屬次級淋巴器官。</t>
+        </is>
+      </c>
+      <c r="T228" s="3"/>
+      <c r="U228" s="3"/>
+      <c r="V228" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="W228" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X228" s="3"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="M2:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -16708,7 +23440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16979,7 +23711,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>161 題</t>
+          <t>227 題</t>
         </is>
       </c>
     </row>
@@ -17040,6 +23772,78 @@
       <c r="B28" s="5" t="inlineStr">
         <is>
           <t>11 題｜public/materials/hemodynamics-v1/index.html（已登錄、待部署）；6 先備＋5 情境；單元＝次單元＝血液動力學</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" hidden="0" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>心輸出量的調節</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/cardiac-output-v1/index.html；單元：心臟II；6 先備＋5 情境</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" hidden="0" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>血壓測量</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-pressure-measurement-v1/index.html；單元：心臟II；6 先備＋5 情境</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" hidden="0" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>微血管物質交換與組織液</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/capillary-exchange-v1/index.html；單元：心臟II；6 先備＋5 情境</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" hidden="0" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>全身主要動脈與靜脈</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/major-vessels-v1/index.html；單元：心臟II；6 先備＋5 情境</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" hidden="0" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>血型與輸血</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/blood-types-v1/index.html；單元：血液；6 先備＋5 情境</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" hidden="0" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>淋巴器官</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html；單元：淋巴系統；6 先備＋5 情境</t>
         </is>
       </c>
     </row>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -20095,7 +20095,7 @@
       </c>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>頭臂幹</t>
+          <t>頭臂動脈</t>
         </is>
       </c>
       <c r="J196" s="5" t="inlineStr">
@@ -20123,27 +20123,27 @@
       </c>
       <c r="O196" s="5" t="inlineStr">
         <is>
-          <t>頭臂幹直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
+          <t>頭臂動脈直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
         </is>
       </c>
       <c r="P196" s="5" t="inlineStr">
         <is>
-          <t>「主動脈弓三分支」：分清主動脈弓直接分支與頭臂幹的分支。</t>
+          <t>「主動脈弓三分支」：分清主動脈弓直接分支與頭臂動脈的分支。</t>
         </is>
       </c>
       <c r="Q196" s="5" t="inlineStr">
         <is>
-          <t>分清主動脈弓直接分支與頭臂幹的分支。 → 回到「主動脈弓三分支」比較：頭臂幹（再分右頸總、右鎖骨下）、左頸總動脈、左鎖骨下動脈</t>
+          <t>分清主動脈弓直接分支與頭臂動脈的分支。 → 回到「主動脈弓三分支」比較：頭臂動脈（再分右頸總、右鎖骨下）、左頸總動脈、左鎖骨下動脈</t>
         </is>
       </c>
       <c r="R196" s="5" t="inlineStr">
         <is>
-          <t>選擇「頭臂幹」。頭臂幹直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
+          <t>選擇「頭臂動脈」。頭臂動脈直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
         </is>
       </c>
       <c r="S196" s="5" t="inlineStr">
         <is>
-          <t>頭臂幹直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
+          <t>頭臂動脈直接由主動脈弓分出，再分為右頸總與右鎖骨下動脈。</t>
         </is>
       </c>
       <c r="T196" s="3"/>
@@ -20911,7 +20911,7 @@
       </c>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>頭臂幹→右鎖骨下→腋→肱</t>
+          <t>頭臂動脈→右鎖骨下→腋→肱</t>
         </is>
       </c>
       <c r="J204" s="5" t="inlineStr">
@@ -20939,27 +20939,27 @@
       </c>
       <c r="O204" s="5" t="inlineStr">
         <is>
-          <t>右上肢由頭臂幹經右鎖骨下、腋、肱動脈供血。</t>
+          <t>右上肢由頭臂動脈經右鎖骨下、腋、肱動脈供血。</t>
         </is>
       </c>
       <c r="P204" s="5" t="inlineStr">
         <is>
-          <t>「主動脈弓三分支」：人體右側先經頭臂幹。</t>
+          <t>「主動脈弓三分支」：人體右側先經頭臂動脈。</t>
         </is>
       </c>
       <c r="Q204" s="5" t="inlineStr">
         <is>
-          <t>人體右側先經頭臂幹。 → 回到「主動脈弓三分支」比較：頭臂幹（再分右頸總、右鎖骨下）、左頸總動脈、左鎖骨下動脈</t>
+          <t>人體右側先經頭臂動脈。 → 回到「主動脈弓三分支」比較：頭臂動脈（再分右頸總、右鎖骨下）、左頸總動脈、左鎖骨下動脈</t>
         </is>
       </c>
       <c r="R204" s="5" t="inlineStr">
         <is>
-          <t>選擇「頭臂幹→右鎖骨下→腋→肱」。右上肢由頭臂幹經右鎖骨下、腋、肱動脈供血。</t>
+          <t>選擇「頭臂動脈→右鎖骨下→腋→肱」。右上肢由頭臂動脈經右鎖骨下、腋、肱動脈供血。</t>
         </is>
       </c>
       <c r="S204" s="5" t="inlineStr">
         <is>
-          <t>右上肢由頭臂幹經右鎖骨下、腋、肱動脈供血。</t>
+          <t>右上肢由頭臂動脈經右鎖骨下、腋、肱動脈供血。</t>
         </is>
       </c>
       <c r="T204" s="3"/>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -16729,7 +16729,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>每搏量÷心率</t>
+          <t>心搏量÷心率</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
@@ -16739,12 +16739,12 @@
       </c>
       <c r="K163" s="5" t="inlineStr">
         <is>
-          <t>心率×每搏量</t>
+          <t>心率×心搏量</t>
         </is>
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>心率＋每搏量</t>
+          <t>心率＋心搏量</t>
         </is>
       </c>
       <c r="M163" s="3" t="inlineStr">
@@ -16762,17 +16762,17 @@
       </c>
       <c r="P163" s="5" t="inlineStr">
         <is>
-          <t>「心輸出量＝心率×每搏量」：回想每分鐘的搏動次數與每次射出的血量。</t>
+          <t>「心輸出量＝心率×心搏量」：回想每分鐘的搏動次數與每次射出的血量。</t>
         </is>
       </c>
       <c r="Q163" s="5" t="inlineStr">
         <is>
-          <t>回想每分鐘的搏動次數與每次射出的血量。 → 回到「心輸出量＝心率×每搏量」比較：一側心室每分鐘射出的血量</t>
+          <t>回想每分鐘的搏動次數與每次射出的血量。 → 回到「心輸出量＝心率×心搏量」比較：一側心室每分鐘射出的血量</t>
         </is>
       </c>
       <c r="R163" s="5" t="inlineStr">
         <is>
-          <t>選擇「心率×每搏量」。CO＝HR×SV，表示一側心室每分鐘射出的血量。</t>
+          <t>選擇「心率×心搏量」。CO＝HR×SV，表示一側心室每分鐘射出的血量。</t>
         </is>
       </c>
       <c r="S163" s="5" t="inlineStr">
@@ -16864,12 +16864,12 @@
       </c>
       <c r="P164" s="5" t="inlineStr">
         <is>
-          <t>「每搏量＝EDV−ESV」：用舒張末期容積減去收縮末期容積。</t>
+          <t>「心搏量＝EDV−ESV」：用舒張末期容積減去收縮末期容積。</t>
         </is>
       </c>
       <c r="Q164" s="5" t="inlineStr">
         <is>
-          <t>用舒張末期容積減去收縮末期容積。 → 回到「每搏量＝EDV−ESV」比較：EDV 約 120 mL、ESV 約 50 mL → SV 約 70 mL</t>
+          <t>用舒張末期容積減去收縮末期容積。 → 回到「心搏量＝EDV−ESV」比較：EDV 約 120 mL、ESV 約 50 mL → SV 約 70 mL</t>
         </is>
       </c>
       <c r="R164" s="5" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="P169" s="5" t="inlineStr">
         <is>
-          <t>「心輸出量＝心率×每搏量」：先乘心率與每搏量，再將 mL 換成 L。</t>
+          <t>「心輸出量＝心率×心搏量」：先乘心率與心搏量，再將 mL 換成 L。</t>
         </is>
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>先乘心率與每搏量，再將 mL 換成 L。 → 回到「心輸出量＝心率×每搏量」比較：一側心室每分鐘射出的血量</t>
+          <t>先乘心率與心搏量，再將 mL 換成 L。 → 回到「心輸出量＝心率×心搏量」比較：一側心室每分鐘射出的血量</t>
         </is>
       </c>
       <c r="R169" s="5" t="inlineStr">

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X228"/>
+  <dimension ref="A1:X250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23424,6 +23424,2250 @@
       </c>
       <c r="X228" s="3"/>
     </row>
+    <row r="229" ht="216" hidden="0" customHeight="1">
+      <c r="A229" s="3"/>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>抗生素能選擇性作用於細菌、較少傷害人體細胞，主要與下列哪一項差異有關？</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>細菌有粒線體</t>
+        </is>
+      </c>
+      <c r="J229" s="5" t="inlineStr">
+        <is>
+          <t>細菌的核糖體是 70S，人類是 80S</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="inlineStr">
+        <is>
+          <t>細菌有核膜</t>
+        </is>
+      </c>
+      <c r="L229" s="5" t="inlineStr">
+        <is>
+          <t>細菌有溶小體</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O229" s="5" t="inlineStr">
+        <is>
+          <t>細菌沒有核膜和膜狀胞器，核糖體是 70S；抗生素打 30S 或 50S 次單元，不太影響人的 80S 核糖體。</t>
+        </is>
+      </c>
+      <c r="P229" s="5" t="inlineStr">
+        <is>
+          <t>「細菌是原核細胞」：比較細菌和人的核糖體大小。</t>
+        </is>
+      </c>
+      <c r="Q229" s="5" t="inlineStr">
+        <is>
+          <t>比較細菌和人的核糖體大小。 → 回到「細菌是原核細胞」比較：細菌沒有細胞核和膜狀胞器，核糖體也和人不同，這些差異就是抗生素能「只打細菌」的原因。</t>
+        </is>
+      </c>
+      <c r="R229" s="5" t="inlineStr">
+        <is>
+          <t>選擇「細菌的核糖體是 70S，人類是 80S」。細菌沒有核膜和膜狀胞器，核糖體是 70S；抗生素打 30S 或 50S 次單元，不太影響人的 80S 核糖體。</t>
+        </is>
+      </c>
+      <c r="S229" s="5" t="inlineStr">
+        <is>
+          <t>細菌沒有核膜和膜狀胞器，核糖體是 70S；抗生素打 30S 或 50S 次單元，不太影響人的 80S 核糖體。</t>
+        </is>
+      </c>
+      <c r="T229" s="3"/>
+      <c r="U229" s="3"/>
+      <c r="V229" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W229" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X229" s="3"/>
+    </row>
+    <row r="230" ht="182" hidden="0" customHeight="1">
+      <c r="A230" s="3"/>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>下列哪一種微生物沒有細胞壁，因此青黴素類抗生素對它無效？</t>
+        </is>
+      </c>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>大腸桿菌</t>
+        </is>
+      </c>
+      <c r="J230" s="5" t="inlineStr">
+        <is>
+          <t>黴漿菌</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="inlineStr">
+        <is>
+          <t>結核桿菌</t>
+        </is>
+      </c>
+      <c r="L230" s="5" t="inlineStr">
+        <is>
+          <t>金黃色葡萄球菌</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O230" s="5" t="inlineStr">
+        <is>
+          <t>青黴素類抑制細胞壁合成；黴漿菌和脲原體沒有細胞壁，所以無效。</t>
+        </is>
+      </c>
+      <c r="P230" s="5" t="inlineStr">
+        <is>
+          <t>「細胞壁決定很多事」：青黴素類的目標是什麼構造？</t>
+        </is>
+      </c>
+      <c r="Q230" s="5" t="inlineStr">
+        <is>
+          <t>青黴素類的目標是什麼構造？ → 回到「細胞壁決定很多事」比較：細胞壁的種類決定染色結果、毒素種類，以及哪些抗生素有效。</t>
+        </is>
+      </c>
+      <c r="R230" s="5" t="inlineStr">
+        <is>
+          <t>選擇「黴漿菌」。青黴素類抑制細胞壁合成；黴漿菌和脲原體沒有細胞壁，所以無效。</t>
+        </is>
+      </c>
+      <c r="S230" s="5" t="inlineStr">
+        <is>
+          <t>青黴素類抑制細胞壁合成；黴漿菌和脲原體沒有細胞壁，所以無效。</t>
+        </is>
+      </c>
+      <c r="T230" s="3"/>
+      <c r="U230" s="3"/>
+      <c r="V230" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W230" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X230" s="3"/>
+    </row>
+    <row r="231" ht="233" hidden="0" customHeight="1">
+      <c r="A231" s="3"/>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>有關內毒素的敘述，何者正確？</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>成分是脂多糖，耐熱</t>
+        </is>
+      </c>
+      <c r="J231" s="5" t="inlineStr">
+        <is>
+          <t>可以製成類毒素疫苗</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="inlineStr">
+        <is>
+          <t>主要由革蘭氏陽性菌分泌</t>
+        </is>
+      </c>
+      <c r="L231" s="5" t="inlineStr">
+        <is>
+          <t>化學本質是蛋白質</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" s="5" t="inlineStr">
+        <is>
+          <t>內毒素是陰性菌外膜的脂多糖，耐熱、毒性較弱，無法做成類毒素；其他三個選項描述的是外毒素。</t>
+        </is>
+      </c>
+      <c r="P231" s="5" t="inlineStr">
+        <is>
+          <t>「細菌的武器：外毒素與內毒素」：內毒素在陰性菌的哪一層？</t>
+        </is>
+      </c>
+      <c r="Q231" s="5" t="inlineStr">
+        <is>
+          <t>內毒素在陰性菌的哪一層？ → 回到「細菌的武器：外毒素與內毒素」比較：外毒素是活菌分泌的蛋白質，量少但毒性強；內毒素是陰性菌外膜的脂多糖，菌體破裂才釋出。</t>
+        </is>
+      </c>
+      <c r="R231" s="5" t="inlineStr">
+        <is>
+          <t>選擇「成分是脂多糖，耐熱」。內毒素是陰性菌外膜的脂多糖，耐熱、毒性較弱，無法做成類毒素；其他三個選項描述的是外毒素。</t>
+        </is>
+      </c>
+      <c r="S231" s="5" t="inlineStr">
+        <is>
+          <t>內毒素是陰性菌外膜的脂多糖，耐熱、毒性較弱，無法做成類毒素；其他三個選項描述的是外毒素。</t>
+        </is>
+      </c>
+      <c r="T231" s="3"/>
+      <c r="U231" s="3"/>
+      <c r="V231" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W231" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X231" s="3"/>
+    </row>
+    <row r="232" ht="233" hidden="0" customHeight="1">
+      <c r="A232" s="3"/>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>預防醫院內交叉感染，最簡單也最有效的措施是：</t>
+        </is>
+      </c>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>全面禁止訪客</t>
+        </is>
+      </c>
+      <c r="J232" s="5" t="inlineStr">
+        <is>
+          <t>每位病人都使用預防性抗生素</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="inlineStr">
+        <is>
+          <t>落實手部衛生</t>
+        </is>
+      </c>
+      <c r="L232" s="5" t="inlineStr">
+        <is>
+          <t>每天用紫外線照射病房</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O232" s="5" t="inlineStr">
+        <is>
+          <t>院內感染以接觸傳播最常見，醫護人員的手是主要媒介，手部衛生是切斷傳播最有效的方法。</t>
+        </is>
+      </c>
+      <c r="P232" s="5" t="inlineStr">
+        <is>
+          <t>「感染怎麼發生，又怎麼傳出去」：院內感染最常見的傳播途徑是什麼？</t>
+        </is>
+      </c>
+      <c r="Q232" s="5" t="inlineStr">
+        <is>
+          <t>院內感染最常見的傳播途徑是什麼？ → 回到「感染怎麼發生，又怎麼傳出去」比較：感染鏈有六個環節，切斷任何一環就能阻止傳播；在醫院裡最容易切斷的是「手」。</t>
+        </is>
+      </c>
+      <c r="R232" s="5" t="inlineStr">
+        <is>
+          <t>選擇「落實手部衛生」。院內感染以接觸傳播最常見，醫護人員的手是主要媒介，手部衛生是切斷傳播最有效的方法。</t>
+        </is>
+      </c>
+      <c r="S232" s="5" t="inlineStr">
+        <is>
+          <t>院內感染以接觸傳播最常見，醫護人員的手是主要媒介，手部衛生是切斷傳播最有效的方法。</t>
+        </is>
+      </c>
+      <c r="T232" s="3"/>
+      <c r="U232" s="3"/>
+      <c r="V232" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W232" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X232" s="3"/>
+    </row>
+    <row r="233" ht="250" hidden="0" customHeight="1">
+      <c r="A233" s="3"/>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>下列哪一種方法能殺死細菌內孢子而達到滅菌？</t>
+        </is>
+      </c>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>75% 酒精擦拭</t>
+        </is>
+      </c>
+      <c r="J233" s="5" t="inlineStr">
+        <is>
+          <t>煮沸 10 分鐘</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="inlineStr">
+        <is>
+          <t>高壓蒸氣 121℃、15 分鐘</t>
+        </is>
+      </c>
+      <c r="L233" s="5" t="inlineStr">
+        <is>
+          <t>優碘消毒</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O233" s="5" t="inlineStr">
+        <is>
+          <t>滅菌要殺死包括孢子在內的所有微生物；酒精、煮沸、優碘都無法可靠地殺死孢子。</t>
+        </is>
+      </c>
+      <c r="P233" s="5" t="inlineStr">
+        <is>
+          <t>「消毒與滅菌：殺到什麼程度？」：滅菌的定義是連什麼都要殺死？</t>
+        </is>
+      </c>
+      <c r="Q233" s="5" t="inlineStr">
+        <is>
+          <t>滅菌的定義是連什麼都要殺死？ → 回到「消毒與滅菌：殺到什麼程度？」比較：滅菌要連細菌孢子都殺死；消毒只殺死大部分病原。物品要處理到什麼程度，看它會接觸身體哪裡。</t>
+        </is>
+      </c>
+      <c r="R233" s="5" t="inlineStr">
+        <is>
+          <t>選擇「高壓蒸氣 121℃、15 分鐘」。滅菌要殺死包括孢子在內的所有微生物；酒精、煮沸、優碘都無法可靠地殺死孢子。</t>
+        </is>
+      </c>
+      <c r="S233" s="5" t="inlineStr">
+        <is>
+          <t>滅菌要殺死包括孢子在內的所有微生物；酒精、煮沸、優碘都無法可靠地殺死孢子。</t>
+        </is>
+      </c>
+      <c r="T233" s="3"/>
+      <c r="U233" s="3"/>
+      <c r="V233" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W233" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X233" s="3"/>
+    </row>
+    <row r="234" ht="199" hidden="0" customHeight="1">
+      <c r="A234" s="3"/>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>喹諾酮類抗生素（如 ciprofloxacin）的作用機轉是：</t>
+        </is>
+      </c>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>抑制 DNA 旋轉酶</t>
+        </is>
+      </c>
+      <c r="J234" s="5" t="inlineStr">
+        <is>
+          <t>與 30S 核糖體結合</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="inlineStr">
+        <is>
+          <t>抑制葉酸合成</t>
+        </is>
+      </c>
+      <c r="L234" s="5" t="inlineStr">
+        <is>
+          <t>抑制細胞壁合成</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" s="5" t="inlineStr">
+        <is>
+          <t>喹諾酮類抑制 DNA 旋轉酶（與拓樸異構酶 IV），使細菌的 DNA 無法複製。</t>
+        </is>
+      </c>
+      <c r="P234" s="5" t="inlineStr">
+        <is>
+          <t>「抗生素打哪裡？細菌怎麼抗藥？」：它影響的是細菌複製哪一種分子？</t>
+        </is>
+      </c>
+      <c r="Q234" s="5" t="inlineStr">
+        <is>
+          <t>它影響的是細菌複製哪一種分子？ → 回到「抗生素打哪裡？細菌怎麼抗藥？」比較：抗生素攻擊細菌特有的構造；細菌則用四種方法對抗藥物。</t>
+        </is>
+      </c>
+      <c r="R234" s="5" t="inlineStr">
+        <is>
+          <t>選擇「抑制 DNA 旋轉酶」。喹諾酮類抑制 DNA 旋轉酶（與拓樸異構酶 IV），使細菌的 DNA 無法複製。</t>
+        </is>
+      </c>
+      <c r="S234" s="5" t="inlineStr">
+        <is>
+          <t>喹諾酮類抑制 DNA 旋轉酶（與拓樸異構酶 IV），使細菌的 DNA 無法複製。</t>
+        </is>
+      </c>
+      <c r="T234" s="3"/>
+      <c r="U234" s="3"/>
+      <c r="V234" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W234" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X234" s="3"/>
+    </row>
+    <row r="235" ht="233" hidden="0" customHeight="1">
+      <c r="A235" s="3"/>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-case-q01</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>【第 3 天】王先生的燒傷傷口流出藍綠色的膿，培養出需氧的革蘭氏陰性桿菌。最可能是哪一種菌？</t>
+        </is>
+      </c>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>化膿性鏈球菌</t>
+        </is>
+      </c>
+      <c r="J235" s="5" t="inlineStr">
+        <is>
+          <t>破傷風桿菌</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="inlineStr">
+        <is>
+          <t>金黃色葡萄球菌</t>
+        </is>
+      </c>
+      <c r="L235" s="5" t="inlineStr">
+        <is>
+          <t>綠膿桿菌</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O235" s="5" t="inlineStr">
+        <is>
+          <t>綠膿桿菌是需氧的陰性桿菌，會產生藍綠色的綠膿素，喜歡潮濕環境，是燒燙傷病人常見的感染菌。金黃色葡萄球菌和鏈球菌是陽性球菌。</t>
+        </is>
+      </c>
+      <c r="P235" s="5" t="inlineStr">
+        <is>
+          <t>「感染怎麼發生，又怎麼傳出去」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q235" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「感染怎麼發生，又怎麼傳出去」比較：感染鏈有六個環節，切斷任何一環就能阻止傳播；在醫院裡最容易切斷的是「手」。</t>
+        </is>
+      </c>
+      <c r="R235" s="5" t="inlineStr">
+        <is>
+          <t>選擇「綠膿桿菌」。綠膿桿菌是需氧的陰性桿菌，會產生藍綠色的綠膿素，喜歡潮濕環境，是燒燙傷病人常見的感染菌。金黃色葡萄球菌和鏈球菌是陽性球菌。</t>
+        </is>
+      </c>
+      <c r="S235" s="5" t="inlineStr">
+        <is>
+          <t>綠膿桿菌是需氧的陰性桿菌，會產生藍綠色的綠膿素，喜歡潮濕環境，是燒燙傷病人常見的感染菌。金黃色葡萄球菌和鏈球菌是陽性球菌。</t>
+        </is>
+      </c>
+      <c r="T235" s="3"/>
+      <c r="U235" s="3"/>
+      <c r="V235" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W235" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X235" s="3"/>
+    </row>
+    <row r="236" ht="250" hidden="0" customHeight="1">
+      <c r="A236" s="3"/>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-case-q02</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>【第 3 天晚上】王先生體溫 39.5℃、血壓 85/50 mmHg。造成這個狀況的主要毒力因子是：</t>
+        </is>
+      </c>
+      <c r="I236" s="5" t="inlineStr">
+        <is>
+          <t>莢膜</t>
+        </is>
+      </c>
+      <c r="J236" s="5" t="inlineStr">
+        <is>
+          <t>外毒素直接破壞神經</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="inlineStr">
+        <is>
+          <t>陰性菌的內毒素（脂多糖）引起全身發炎與休克</t>
+        </is>
+      </c>
+      <c r="L236" s="5" t="inlineStr">
+        <is>
+          <t>類毒素</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O236" s="5" t="inlineStr">
+        <is>
+          <t>脂多糖的脂質 A 刺激巨噬細胞釋放大量發炎物質，造成發燒、血管擴張、血壓下降，也就是敗血性休克。</t>
+        </is>
+      </c>
+      <c r="P236" s="5" t="inlineStr">
+        <is>
+          <t>「細菌的武器：外毒素與內毒素」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q236" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「細菌的武器：外毒素與內毒素」比較：外毒素是活菌分泌的蛋白質，量少但毒性強；內毒素是陰性菌外膜的脂多糖，菌體破裂才釋出。</t>
+        </is>
+      </c>
+      <c r="R236" s="5" t="inlineStr">
+        <is>
+          <t>選擇「陰性菌的內毒素（脂多糖）引起全身發炎與休克」。脂多糖的脂質 A 刺激巨噬細胞釋放大量發炎物質，造成發燒、血管擴張、血壓下降，也就是敗血性休克。</t>
+        </is>
+      </c>
+      <c r="S236" s="5" t="inlineStr">
+        <is>
+          <t>脂多糖的脂質 A 刺激巨噬細胞釋放大量發炎物質，造成發燒、血管擴張、血壓下降，也就是敗血性休克。</t>
+        </is>
+      </c>
+      <c r="T236" s="3"/>
+      <c r="U236" s="3"/>
+      <c r="V236" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W236" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X236" s="3"/>
+    </row>
+    <row r="237" ht="250" hidden="0" customHeight="1">
+      <c r="A237" s="3"/>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-case-q03</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>【第 4 天】隔壁床的病人也驗出同一種菌。最可能的傳播途徑，以及最優先的處置是：</t>
+        </is>
+      </c>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>空氣傳播，應改住負壓隔離病房</t>
+        </is>
+      </c>
+      <c r="J237" s="5" t="inlineStr">
+        <is>
+          <t>經醫護人員的手與共用器材接觸傳播，落實手部衛生與器材專用</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="inlineStr">
+        <is>
+          <t>經食物傳播，應停止送餐</t>
+        </is>
+      </c>
+      <c r="L237" s="5" t="inlineStr">
+        <is>
+          <t>病人自己免疫力低下，和傳播無關</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O237" s="5" t="inlineStr">
+        <is>
+          <t>綠膿桿菌在醫院主要靠接觸傳播。手部衛生和器材專用可以切斷傳播途徑，這是感染鏈中最容易介入的一環。</t>
+        </is>
+      </c>
+      <c r="P237" s="5" t="inlineStr">
+        <is>
+          <t>「感染怎麼發生，又怎麼傳出去」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q237" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「感染怎麼發生，又怎麼傳出去」比較：感染鏈有六個環節，切斷任何一環就能阻止傳播；在醫院裡最容易切斷的是「手」。</t>
+        </is>
+      </c>
+      <c r="R237" s="5" t="inlineStr">
+        <is>
+          <t>選擇「經醫護人員的手與共用器材接觸傳播，落實手部衛生與器材專用」。綠膿桿菌在醫院主要靠接觸傳播。手部衛生和器材專用可以切斷傳播途徑，這是感染鏈中最容易介入的一環。</t>
+        </is>
+      </c>
+      <c r="S237" s="5" t="inlineStr">
+        <is>
+          <t>綠膿桿菌在醫院主要靠接觸傳播。手部衛生和器材專用可以切斷傳播途徑，這是感染鏈中最容易介入的一環。</t>
+        </is>
+      </c>
+      <c r="T237" s="3"/>
+      <c r="U237" s="3"/>
+      <c r="V237" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W237" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X237" s="3"/>
+    </row>
+    <row r="238" ht="267" hidden="0" customHeight="1">
+      <c r="A238" s="3"/>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-case-q04</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="inlineStr">
+        <is>
+          <t>【第 5 天】王先生換藥時使用的鑷子和剪刀，用完後應該怎麼處理？</t>
+        </is>
+      </c>
+      <c r="I238" s="5" t="inlineStr">
+        <is>
+          <t>清潔後以高壓蒸氣滅菌</t>
+        </is>
+      </c>
+      <c r="J238" s="5" t="inlineStr">
+        <is>
+          <t>用清水沖洗晾乾</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="inlineStr">
+        <is>
+          <t>做低層次消毒</t>
+        </is>
+      </c>
+      <c r="L238" s="5" t="inlineStr">
+        <is>
+          <t>用 75% 酒精擦拭即可</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" s="5" t="inlineStr">
+        <is>
+          <t>換藥器械會接觸燒傷創面的組織，屬於重要物品，必須清潔後滅菌。酒精和低層次消毒都殺不死孢子。</t>
+        </is>
+      </c>
+      <c r="P238" s="5" t="inlineStr">
+        <is>
+          <t>「消毒與滅菌：殺到什麼程度？」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q238" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「消毒與滅菌：殺到什麼程度？」比較：滅菌要連細菌孢子都殺死；消毒只殺死大部分病原。物品要處理到什麼程度，看它會接觸身體哪裡。</t>
+        </is>
+      </c>
+      <c r="R238" s="5" t="inlineStr">
+        <is>
+          <t>選擇「清潔後以高壓蒸氣滅菌」。換藥器械會接觸燒傷創面的組織，屬於重要物品，必須清潔後滅菌。酒精和低層次消毒都殺不死孢子。</t>
+        </is>
+      </c>
+      <c r="S238" s="5" t="inlineStr">
+        <is>
+          <t>換藥器械會接觸燒傷創面的組織，屬於重要物品，必須清潔後滅菌。酒精和低層次消毒都殺不死孢子。</t>
+        </is>
+      </c>
+      <c r="T238" s="3"/>
+      <c r="U238" s="3"/>
+      <c r="V238" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W238" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X238" s="3"/>
+    </row>
+    <row r="239" ht="284" hidden="0" customHeight="1">
+      <c r="A239" s="3"/>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>micro-bacteria-review-case-q05</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>【第 10 天】王先生使用廣效抗生素一週後，開始嚴重水瀉。最需要懷疑的是：</t>
+        </is>
+      </c>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>病毒性腸胃炎</t>
+        </is>
+      </c>
+      <c r="J239" s="5" t="inlineStr">
+        <is>
+          <t>對抗生素過敏</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="inlineStr">
+        <is>
+          <t>綠膿桿菌腸炎</t>
+        </is>
+      </c>
+      <c r="L239" s="5" t="inlineStr">
+        <is>
+          <t>抗生素破壞腸道正常菌叢，困難梭菌過度生長</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O239" s="5" t="inlineStr">
+        <is>
+          <t>廣效抗生素殺死腸道正常菌叢，困難梭菌趁機增生，產生毒素造成偽膜性結腸炎。它會形成孢子，酒精殺不死，照護時要用肥皂和清水洗手（接回節點 05）。</t>
+        </is>
+      </c>
+      <c r="P239" s="5" t="inlineStr">
+        <is>
+          <t>「抗生素打哪裡？細菌怎麼抗藥？」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q239" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「抗生素打哪裡？細菌怎麼抗藥？」比較：抗生素攻擊細菌特有的構造；細菌則用四種方法對抗藥物。</t>
+        </is>
+      </c>
+      <c r="R239" s="5" t="inlineStr">
+        <is>
+          <t>選擇「抗生素破壞腸道正常菌叢，困難梭菌過度生長」。廣效抗生素殺死腸道正常菌叢，困難梭菌趁機增生，產生毒素造成偽膜性結腸炎。它會形成孢子，酒精殺不死，照護時要用肥皂和清水洗手（接回節點 05）。</t>
+        </is>
+      </c>
+      <c r="S239" s="5" t="inlineStr">
+        <is>
+          <t>廣效抗生素殺死腸道正常菌叢，困難梭菌趁機增生，產生毒素造成偽膜性結腸炎。它會形成孢子，酒精殺不死，照護時要用肥皂和清水洗手（接回節點 05）。</t>
+        </is>
+      </c>
+      <c r="T239" s="3"/>
+      <c r="U239" s="3"/>
+      <c r="V239" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="W239" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X239" s="3"/>
+    </row>
+    <row r="240" ht="216" hidden="0" customHeight="1">
+      <c r="A240" s="3"/>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-foundation-q01</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H240" s="5" t="inlineStr">
+        <is>
+          <t>下列哪一項是先天免疫的特性？</t>
+        </is>
+      </c>
+      <c r="I240" s="5" t="inlineStr">
+        <is>
+          <t>具有專一性</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="inlineStr">
+        <is>
+          <t>第二次接觸時反應更強</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="inlineStr">
+        <is>
+          <t>出生就具備，反應快但沒有記憶</t>
+        </is>
+      </c>
+      <c r="L240" s="5" t="inlineStr">
+        <is>
+          <t>由漿細胞負責</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O240" s="5" t="inlineStr">
+        <is>
+          <t>先天免疫出生就有、反應快、沒有專一性也沒有記憶；專一性、記憶、漿細胞都屬於後天免疫。</t>
+        </is>
+      </c>
+      <c r="P240" s="5" t="inlineStr">
+        <is>
+          <t>「先天免疫與後天免疫」：先天免疫有沒有「記憶」？</t>
+        </is>
+      </c>
+      <c r="Q240" s="5" t="inlineStr">
+        <is>
+          <t>先天免疫有沒有「記憶」？ → 回到「先天免疫與後天免疫」比較：先天免疫出生就有、反應快但沒有專一性；後天免疫要接觸過抗原才建立，有專一性和記憶。</t>
+        </is>
+      </c>
+      <c r="R240" s="5" t="inlineStr">
+        <is>
+          <t>選擇「出生就具備，反應快但沒有記憶」。先天免疫出生就有、反應快、沒有專一性也沒有記憶；專一性、記憶、漿細胞都屬於後天免疫。</t>
+        </is>
+      </c>
+      <c r="S240" s="5" t="inlineStr">
+        <is>
+          <t>先天免疫出生就有、反應快、沒有專一性也沒有記憶；專一性、記憶、漿細胞都屬於後天免疫。</t>
+        </is>
+      </c>
+      <c r="T240" s="3"/>
+      <c r="U240" s="3"/>
+      <c r="V240" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W240" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X240" s="3"/>
+    </row>
+    <row r="241" ht="233" hidden="0" customHeight="1">
+      <c r="A241" s="3"/>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-foundation-q02</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>母親是 B 型肝炎帶原者，新生兒出生後立即注射 B 型肝炎免疫球蛋白（HBIG）。這屬於哪一種免疫？</t>
+        </is>
+      </c>
+      <c r="I241" s="5" t="inlineStr">
+        <is>
+          <t>人工主動免疫</t>
+        </is>
+      </c>
+      <c r="J241" s="5" t="inlineStr">
+        <is>
+          <t>天然被動免疫</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="inlineStr">
+        <is>
+          <t>人工被動免疫</t>
+        </is>
+      </c>
+      <c r="L241" s="5" t="inlineStr">
+        <is>
+          <t>天然主動免疫</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O241" s="5" t="inlineStr">
+        <is>
+          <t>HBIG 是現成的抗體，用注射的方式給予，所以是人工被動免疫；同時打的 B 型肝炎疫苗則是人工主動免疫。</t>
+        </is>
+      </c>
+      <c r="P241" s="5" t="inlineStr">
+        <is>
+          <t>「主動免疫與被動免疫」：HBIG 裡裝的是現成的抗體嗎？</t>
+        </is>
+      </c>
+      <c r="Q241" s="5" t="inlineStr">
+        <is>
+          <t>HBIG 裡裝的是現成的抗體嗎？ → 回到「主動免疫與被動免疫」比較：主動免疫是自己的身體製造抗體和記憶細胞，慢但持久；被動免疫是接受現成的抗體，快但短暫。</t>
+        </is>
+      </c>
+      <c r="R241" s="5" t="inlineStr">
+        <is>
+          <t>選擇「人工被動免疫」。HBIG 是現成的抗體，用注射的方式給予，所以是人工被動免疫；同時打的 B 型肝炎疫苗則是人工主動免疫。</t>
+        </is>
+      </c>
+      <c r="S241" s="5" t="inlineStr">
+        <is>
+          <t>HBIG 是現成的抗體，用注射的方式給予，所以是人工被動免疫；同時打的 B 型肝炎疫苗則是人工主動免疫。</t>
+        </is>
+      </c>
+      <c r="T241" s="3"/>
+      <c r="U241" s="3"/>
+      <c r="V241" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W241" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X241" s="3"/>
+    </row>
+    <row r="242" ht="199" hidden="0" customHeight="1">
+      <c r="A242" s="3"/>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-foundation-q03</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="inlineStr">
+        <is>
+          <t>負責製造並分泌抗體的細胞是：</t>
+        </is>
+      </c>
+      <c r="I242" s="5" t="inlineStr">
+        <is>
+          <t>巨噬細胞</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="inlineStr">
+        <is>
+          <t>嗜中性球</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞</t>
+        </is>
+      </c>
+      <c r="L242" s="5" t="inlineStr">
+        <is>
+          <t>漿細胞</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O242" s="5" t="inlineStr">
+        <is>
+          <t>B 細胞活化後分化成漿細胞，由漿細胞大量分泌抗體。</t>
+        </is>
+      </c>
+      <c r="P242" s="5" t="inlineStr">
+        <is>
+          <t>「免疫細胞與淋巴器官」：B 細胞活化後會分化成什麼？</t>
+        </is>
+      </c>
+      <c r="Q242" s="5" t="inlineStr">
+        <is>
+          <t>B 細胞活化後會分化成什麼？ → 回到「免疫細胞與淋巴器官」比較：所有免疫細胞都來自骨髓的造血幹細胞，分成骨髓系和淋巴系兩大家族。</t>
+        </is>
+      </c>
+      <c r="R242" s="5" t="inlineStr">
+        <is>
+          <t>選擇「漿細胞」。B 細胞活化後分化成漿細胞，由漿細胞大量分泌抗體。</t>
+        </is>
+      </c>
+      <c r="S242" s="5" t="inlineStr">
+        <is>
+          <t>B 細胞活化後分化成漿細胞，由漿細胞大量分泌抗體。</t>
+        </is>
+      </c>
+      <c r="T242" s="3"/>
+      <c r="U242" s="3"/>
+      <c r="V242" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W242" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X242" s="3"/>
+    </row>
+    <row r="243" ht="250" hidden="0" customHeight="1">
+      <c r="A243" s="3"/>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-foundation-q04</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>有關抗原與抗體的敘述，何者正確？</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="inlineStr">
+        <is>
+          <t>一個抗原只能被一種抗體結合</t>
+        </is>
+      </c>
+      <c r="J243" s="5" t="inlineStr">
+        <is>
+          <t>抗體是外來物質，抗原是身體製造的蛋白質</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="inlineStr">
+        <is>
+          <t>A 型血的人，紅血球上有 A 抗原，血漿中有抗 B 抗體</t>
+        </is>
+      </c>
+      <c r="L243" s="5" t="inlineStr">
+        <is>
+          <t>抗原一定是致病的細菌或病毒</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O243" s="5" t="inlineStr">
+        <is>
+          <t>抗原是被辨認的物質，抗體是自己的漿細胞製造的；抗原不一定有害；一個抗原有多個決定位，可以被多種抗體結合。</t>
+        </is>
+      </c>
+      <c r="P243" s="5" t="inlineStr">
+        <is>
+          <t>「抗原與抗體：誰是鎖？誰是鑰匙？」：鎖和鑰匙，各自是誰做的？</t>
+        </is>
+      </c>
+      <c r="Q243" s="5" t="inlineStr">
+        <is>
+          <t>鎖和鑰匙，各自是誰做的？ → 回到「抗原與抗體：誰是鎖？誰是鑰匙？」比較：抗原是引起免疫反應、被辨認的那一方（鎖）；抗體是身體做出來、去辨認抗原的蛋白質（鑰匙）。</t>
+        </is>
+      </c>
+      <c r="R243" s="5" t="inlineStr">
+        <is>
+          <t>選擇「A 型血的人，紅血球上有 A 抗原，血漿中有抗 B 抗體」。抗原是被辨認的物質，抗體是自己的漿細胞製造的；抗原不一定有害；一個抗原有多個決定位，可以被多種抗體結合。</t>
+        </is>
+      </c>
+      <c r="S243" s="5" t="inlineStr">
+        <is>
+          <t>抗原是被辨認的物質，抗體是自己的漿細胞製造的；抗原不一定有害；一個抗原有多個決定位，可以被多種抗體結合。</t>
+        </is>
+      </c>
+      <c r="T243" s="3"/>
+      <c r="U243" s="3"/>
+      <c r="V243" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W243" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X243" s="3"/>
+    </row>
+    <row r="244" ht="216" hidden="0" customHeight="1">
+      <c r="A244" s="3"/>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-foundation-q05</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="inlineStr">
+        <is>
+          <t>初次免疫反應最早出現、分子量最大的抗體是：</t>
+        </is>
+      </c>
+      <c r="I244" s="5" t="inlineStr">
+        <is>
+          <t>IgG</t>
+        </is>
+      </c>
+      <c r="J244" s="5" t="inlineStr">
+        <is>
+          <t>IgA</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="inlineStr">
+        <is>
+          <t>IgE</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O244" s="5" t="inlineStr">
+        <is>
+          <t>IgM 是五聚體，分子最大，是初次反應最先出現的抗體。</t>
+        </is>
+      </c>
+      <c r="P244" s="5" t="inlineStr">
+        <is>
+          <t>「五種抗體的不同」：哪一種抗體是五聚體？</t>
+        </is>
+      </c>
+      <c r="Q244" s="5" t="inlineStr">
+        <is>
+          <t>哪一種抗體是五聚體？ → 回到「五種抗體的不同」比較：五種抗體的差別在 Fc 部分，因此結構、分布和工作都不同；血中含量由多到少是 G、A、M、D、E。</t>
+        </is>
+      </c>
+      <c r="R244" s="5" t="inlineStr">
+        <is>
+          <t>選擇「IgM」。IgM 是五聚體，分子最大，是初次反應最先出現的抗體。</t>
+        </is>
+      </c>
+      <c r="S244" s="5" t="inlineStr">
+        <is>
+          <t>IgM 是五聚體，分子最大，是初次反應最先出現的抗體。</t>
+        </is>
+      </c>
+      <c r="T244" s="3"/>
+      <c r="U244" s="3"/>
+      <c r="V244" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W244" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X244" s="3"/>
+    </row>
+    <row r="245" ht="250" hidden="0" customHeight="1">
+      <c r="A245" s="3"/>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-foundation-q06</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>能直接殺死被病毒感染細胞的是：</t>
+        </is>
+      </c>
+      <c r="I245" s="5" t="inlineStr">
+        <is>
+          <t>CD8 毒殺型 T 細胞</t>
+        </is>
+      </c>
+      <c r="J245" s="5" t="inlineStr">
+        <is>
+          <t>B 細胞</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="inlineStr">
+        <is>
+          <t>肥大細胞</t>
+        </is>
+      </c>
+      <c r="L245" s="5" t="inlineStr">
+        <is>
+          <t>CD4 輔助型 T 細胞</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" s="5" t="inlineStr">
+        <is>
+          <t>CD8 毒殺型 T 細胞辨認第一類 MHC 上的病毒抗原片段，直接讓被感染的細胞凋亡；CD4 負責指揮。</t>
+        </is>
+      </c>
+      <c r="P245" s="5" t="inlineStr">
+        <is>
+          <t>「T 細胞：指揮官與殺手」：指揮官和殺手，哪一個動手？</t>
+        </is>
+      </c>
+      <c r="Q245" s="5" t="inlineStr">
+        <is>
+          <t>指揮官和殺手，哪一個動手？ → 回到「T 細胞：指揮官與殺手」比較：T 細胞在胸腺成熟，只辨認「被呈現在細胞表面」的抗原片段，負責指揮免疫反應和直接殺死被感染的細胞。</t>
+        </is>
+      </c>
+      <c r="R245" s="5" t="inlineStr">
+        <is>
+          <t>選擇「CD8 毒殺型 T 細胞」。CD8 毒殺型 T 細胞辨認第一類 MHC 上的病毒抗原片段，直接讓被感染的細胞凋亡；CD4 負責指揮。</t>
+        </is>
+      </c>
+      <c r="S245" s="5" t="inlineStr">
+        <is>
+          <t>CD8 毒殺型 T 細胞辨認第一類 MHC 上的病毒抗原片段，直接讓被感染的細胞凋亡；CD4 負責指揮。</t>
+        </is>
+      </c>
+      <c r="T245" s="3"/>
+      <c r="U245" s="3"/>
+      <c r="V245" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W245" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X245" s="3"/>
+    </row>
+    <row r="246" ht="250" hidden="0" customHeight="1">
+      <c r="A246" s="3"/>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-case-q01</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="inlineStr">
+        <is>
+          <t>【出生】小安的臍帶血檢驗發現有對抗麻疹的抗體。這些抗體最可能是：</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="inlineStr">
+        <is>
+          <t>經母乳得到的 IgA</t>
+        </is>
+      </c>
+      <c r="J246" s="5" t="inlineStr">
+        <is>
+          <t>小安自己製造的 IgG</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="inlineStr">
+        <is>
+          <t>小安自己製造的 IgM</t>
+        </is>
+      </c>
+      <c r="L246" s="5" t="inlineStr">
+        <is>
+          <t>經胎盤從媽媽來的 IgG，屬天然被動免疫</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O246" s="5" t="inlineStr">
+        <is>
+          <t>IgG 是唯一能通過胎盤的抗體，屬天然被動免疫，約在 6 個月內逐漸消失。若臍帶血中特定 IgM 偏高，表示胎兒在子宮內受到感染。</t>
+        </is>
+      </c>
+      <c r="P246" s="5" t="inlineStr">
+        <is>
+          <t>「五種抗體的不同」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q246" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「五種抗體的不同」比較：五種抗體的差別在 Fc 部分，因此結構、分布和工作都不同；血中含量由多到少是 G、A、M、D、E。</t>
+        </is>
+      </c>
+      <c r="R246" s="5" t="inlineStr">
+        <is>
+          <t>選擇「經胎盤從媽媽來的 IgG，屬天然被動免疫」。IgG 是唯一能通過胎盤的抗體，屬天然被動免疫，約在 6 個月內逐漸消失。若臍帶血中特定 IgM 偏高，表示胎兒在子宮內受到感染。</t>
+        </is>
+      </c>
+      <c r="S246" s="5" t="inlineStr">
+        <is>
+          <t>IgG 是唯一能通過胎盤的抗體，屬天然被動免疫，約在 6 個月內逐漸消失。若臍帶血中特定 IgM 偏高，表示胎兒在子宮內受到感染。</t>
+        </is>
+      </c>
+      <c r="T246" s="3"/>
+      <c r="U246" s="3"/>
+      <c r="V246" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W246" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X246" s="3"/>
+    </row>
+    <row r="247" ht="250" hidden="0" customHeight="1">
+      <c r="A247" s="3"/>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-case-q02</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>【第 1 週】媽媽餵小安喝初乳。初乳中保護小安腸道黏膜的主要抗體是：</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="inlineStr">
+        <is>
+          <t>IgE</t>
+        </is>
+      </c>
+      <c r="J247" s="5" t="inlineStr">
+        <is>
+          <t>IgG</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="inlineStr">
+        <is>
+          <t>分泌型 IgA</t>
+        </is>
+      </c>
+      <c r="L247" s="5" t="inlineStr">
+        <is>
+          <t>IgM</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O247" s="5" t="inlineStr">
+        <is>
+          <t>分泌型 IgA 存在初乳和各種黏膜分泌物中，保護腸道和呼吸道黏膜；屬天然被動免疫。</t>
+        </is>
+      </c>
+      <c r="P247" s="5" t="inlineStr">
+        <is>
+          <t>「五種抗體的不同」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q247" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「五種抗體的不同」比較：五種抗體的差別在 Fc 部分，因此結構、分布和工作都不同；血中含量由多到少是 G、A、M、D、E。</t>
+        </is>
+      </c>
+      <c r="R247" s="5" t="inlineStr">
+        <is>
+          <t>選擇「分泌型 IgA」。分泌型 IgA 存在初乳和各種黏膜分泌物中，保護腸道和呼吸道黏膜；屬天然被動免疫。</t>
+        </is>
+      </c>
+      <c r="S247" s="5" t="inlineStr">
+        <is>
+          <t>分泌型 IgA 存在初乳和各種黏膜分泌物中，保護腸道和呼吸道黏膜；屬天然被動免疫。</t>
+        </is>
+      </c>
+      <c r="T247" s="3"/>
+      <c r="U247" s="3"/>
+      <c r="V247" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W247" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X247" s="3"/>
+    </row>
+    <row r="248" ht="335" hidden="0" customHeight="1">
+      <c r="A248" s="3"/>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-case-q03</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>【產後】媽媽是 A 型血，產後大出血需要輸血。如果誤輸了 B 型血，會發生什麼事？</t>
+        </is>
+      </c>
+      <c r="I248" s="5" t="inlineStr">
+        <is>
+          <t>媽媽紅血球上的 B 抗原和輸入的抗 A 抗體結合</t>
+        </is>
+      </c>
+      <c r="J248" s="5" t="inlineStr">
+        <is>
+          <t>媽媽血漿中的抗 B 抗體結合輸入紅血球上的 B 抗原，造成凝集與溶血</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="inlineStr">
+        <is>
+          <t>不會有反應，因為紅血球不是病菌</t>
+        </is>
+      </c>
+      <c r="L248" s="5" t="inlineStr">
+        <is>
+          <t>媽媽要一週後才會開始產生抗體</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O248" s="5" t="inlineStr">
+        <is>
+          <t>A 型的人紅血球上是 A 抗原、血漿中本來就有抗 B 抗體（主要是 IgM）。輸入的 B 型紅血球帶有 B 抗原，會立刻被抗 B 抗體結合，引起凝集並活化補體造成溶血。</t>
+        </is>
+      </c>
+      <c r="P248" s="5" t="inlineStr">
+        <is>
+          <t>「抗原與抗體：誰是鎖？誰是鑰匙？」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q248" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「抗原與抗體：誰是鎖？誰是鑰匙？」比較：抗原是引起免疫反應、被辨認的那一方（鎖）；抗體是身體做出來、去辨認抗原的蛋白質（鑰匙）。</t>
+        </is>
+      </c>
+      <c r="R248" s="5" t="inlineStr">
+        <is>
+          <t>選擇「媽媽血漿中的抗 B 抗體結合輸入紅血球上的 B 抗原，造成凝集與溶血」。A 型的人紅血球上是 A 抗原、血漿中本來就有抗 B 抗體（主要是 IgM）。輸入的 B 型紅血球帶有 B 抗原，會立刻被抗 B 抗體結合，引起凝集並活化補體造成溶血。</t>
+        </is>
+      </c>
+      <c r="S248" s="5" t="inlineStr">
+        <is>
+          <t>A 型的人紅血球上是 A 抗原、血漿中本來就有抗 B 抗體（主要是 IgM）。輸入的 B 型紅血球帶有 B 抗原，會立刻被抗 B 抗體結合，引起凝集並活化補體造成溶血。</t>
+        </is>
+      </c>
+      <c r="T248" s="3"/>
+      <c r="U248" s="3"/>
+      <c r="V248" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W248" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X248" s="3"/>
+    </row>
+    <row r="249" ht="267" hidden="0" customHeight="1">
+      <c r="A249" s="3"/>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-case-q04</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>【1 個月】小安出生時打了第一劑 B 型肝炎疫苗，一個月後打第二劑。第二劑後的抗體反應會：</t>
+        </is>
+      </c>
+      <c r="I249" s="5" t="inlineStr">
+        <is>
+          <t>比較慢，且以 IgM 為主</t>
+        </is>
+      </c>
+      <c r="J249" s="5" t="inlineStr">
+        <is>
+          <t>更快、更多，以 IgG 為主，因為已有記憶細胞</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="inlineStr">
+        <is>
+          <t>不會產生抗體，因為第一劑已經用完</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="inlineStr">
+        <is>
+          <t>和第一劑完全相同</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" s="5" t="inlineStr">
+        <is>
+          <t>第一劑留下記憶 B 細胞，第二劑引發再次反應：潛伏期短、抗體量多、以 IgG 為主、維持更久。這就是疫苗需要追加劑的原因。</t>
+        </is>
+      </c>
+      <c r="P249" s="5" t="inlineStr">
+        <is>
+          <t>「抗體的結構與功能：B 細胞的工作」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q249" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「抗體的結構與功能：B 細胞的工作」比較：B 細胞遇到抗原後，在輔助型 T 細胞幫助下增殖，分化成製造抗體的漿細胞和留下來的記憶 B 細胞。</t>
+        </is>
+      </c>
+      <c r="R249" s="5" t="inlineStr">
+        <is>
+          <t>選擇「更快、更多，以 IgG 為主，因為已有記憶細胞」。第一劑留下記憶 B 細胞，第二劑引發再次反應：潛伏期短、抗體量多、以 IgG 為主、維持更久。這就是疫苗需要追加劑的原因。</t>
+        </is>
+      </c>
+      <c r="S249" s="5" t="inlineStr">
+        <is>
+          <t>第一劑留下記憶 B 細胞，第二劑引發再次反應：潛伏期短、抗體量多、以 IgG 為主、維持更久。這就是疫苗需要追加劑的原因。</t>
+        </is>
+      </c>
+      <c r="T249" s="3"/>
+      <c r="U249" s="3"/>
+      <c r="V249" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W249" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X249" s="3"/>
+    </row>
+    <row r="250" ht="267" hidden="0" customHeight="1">
+      <c r="A250" s="3"/>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>immuno-concepts-review-case-q05</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>單選</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="inlineStr">
+        <is>
+          <t>【同病房】同病房的另一個寶寶出生後反覆發生嚴重的病毒和黴菌感染，檢查發現胸腺發育不全。最主要受影響的是：</t>
+        </is>
+      </c>
+      <c r="I250" s="5" t="inlineStr">
+        <is>
+          <t>嗜中性球的數量</t>
+        </is>
+      </c>
+      <c r="J250" s="5" t="inlineStr">
+        <is>
+          <t>皮膚屏障</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="inlineStr">
+        <is>
+          <t>補體系統</t>
+        </is>
+      </c>
+      <c r="L250" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞成熟與細胞性免疫</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O250" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在胸腺成熟。胸腺發育不全會使 T 細胞缺乏，細胞性免疫低下；因為 B 細胞也需要輔助型 T 細胞幫忙，抗體反應也會變差。</t>
+        </is>
+      </c>
+      <c r="P250" s="5" t="inlineStr">
+        <is>
+          <t>「T 細胞：指揮官與殺手」：回到對應節點重讀臨床連結，再判斷一次。</t>
+        </is>
+      </c>
+      <c r="Q250" s="5" t="inlineStr">
+        <is>
+          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「T 細胞：指揮官與殺手」比較：T 細胞在胸腺成熟，只辨認「被呈現在細胞表面」的抗原片段，負責指揮免疫反應和直接殺死被感染的細胞。</t>
+        </is>
+      </c>
+      <c r="R250" s="5" t="inlineStr">
+        <is>
+          <t>選擇「T 細胞成熟與細胞性免疫」。T 細胞在胸腺成熟。胸腺發育不全會使 T 細胞缺乏，細胞性免疫低下；因為 B 細胞也需要輔助型 T 細胞幫忙，抗體反應也會變差。</t>
+        </is>
+      </c>
+      <c r="S250" s="5" t="inlineStr">
+        <is>
+          <t>T 細胞在胸腺成熟。胸腺發育不全會使 T 細胞缺乏，細胞性免疫低下；因為 B 細胞也需要輔助型 T 細胞幫忙，抗體反應也會變差。</t>
+        </is>
+      </c>
+      <c r="T250" s="3"/>
+      <c r="U250" s="3"/>
+      <c r="V250" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="W250" s="5" t="inlineStr">
+        <is>
+          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
+        </is>
+      </c>
+      <c r="X250" s="3"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="M2:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -23440,7 +25684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23847,6 +26091,42 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="46" hidden="0" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>細菌怎麼害人，我們怎麼對付它</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html；單元＝次單元＝細菌怎麼害人，我們怎麼對付它；6 先備＋5 情境；教師核可 2026-10-11，待部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="46" hidden="0" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>從小安的第一年認識免疫</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html；單元＝次單元＝從小安的第一年認識免疫；6 先備＋5 情境；教師核可 2026-10-11，待部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="46" hidden="0" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>合計（2026-10-11）</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>249 題（既有 227＋本次 22）；前方歷史合計列保留不改</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X250"/>
+  <dimension ref="A1:X228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23424,2250 +23424,6 @@
       </c>
       <c r="X228" s="3"/>
     </row>
-    <row r="229" ht="216" hidden="0" customHeight="1">
-      <c r="A229" s="3"/>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-foundation-q01</t>
-        </is>
-      </c>
-      <c r="C229" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D229" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr">
-        <is>
-          <t>抗生素能選擇性作用於細菌、較少傷害人體細胞，主要與下列哪一項差異有關？</t>
-        </is>
-      </c>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>細菌有粒線體</t>
-        </is>
-      </c>
-      <c r="J229" s="5" t="inlineStr">
-        <is>
-          <t>細菌的核糖體是 70S，人類是 80S</t>
-        </is>
-      </c>
-      <c r="K229" s="5" t="inlineStr">
-        <is>
-          <t>細菌有核膜</t>
-        </is>
-      </c>
-      <c r="L229" s="5" t="inlineStr">
-        <is>
-          <t>細菌有溶小體</t>
-        </is>
-      </c>
-      <c r="M229" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N229" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O229" s="5" t="inlineStr">
-        <is>
-          <t>細菌沒有核膜和膜狀胞器，核糖體是 70S；抗生素打 30S 或 50S 次單元，不太影響人的 80S 核糖體。</t>
-        </is>
-      </c>
-      <c r="P229" s="5" t="inlineStr">
-        <is>
-          <t>「細菌是原核細胞」：比較細菌和人的核糖體大小。</t>
-        </is>
-      </c>
-      <c r="Q229" s="5" t="inlineStr">
-        <is>
-          <t>比較細菌和人的核糖體大小。 → 回到「細菌是原核細胞」比較：細菌沒有細胞核和膜狀胞器，核糖體也和人不同，這些差異就是抗生素能「只打細菌」的原因。</t>
-        </is>
-      </c>
-      <c r="R229" s="5" t="inlineStr">
-        <is>
-          <t>選擇「細菌的核糖體是 70S，人類是 80S」。細菌沒有核膜和膜狀胞器，核糖體是 70S；抗生素打 30S 或 50S 次單元，不太影響人的 80S 核糖體。</t>
-        </is>
-      </c>
-      <c r="S229" s="5" t="inlineStr">
-        <is>
-          <t>細菌沒有核膜和膜狀胞器，核糖體是 70S；抗生素打 30S 或 50S 次單元，不太影響人的 80S 核糖體。</t>
-        </is>
-      </c>
-      <c r="T229" s="3"/>
-      <c r="U229" s="3"/>
-      <c r="V229" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W229" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X229" s="3"/>
-    </row>
-    <row r="230" ht="182" hidden="0" customHeight="1">
-      <c r="A230" s="3"/>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-foundation-q02</t>
-        </is>
-      </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D230" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H230" s="5" t="inlineStr">
-        <is>
-          <t>下列哪一種微生物沒有細胞壁，因此青黴素類抗生素對它無效？</t>
-        </is>
-      </c>
-      <c r="I230" s="5" t="inlineStr">
-        <is>
-          <t>大腸桿菌</t>
-        </is>
-      </c>
-      <c r="J230" s="5" t="inlineStr">
-        <is>
-          <t>黴漿菌</t>
-        </is>
-      </c>
-      <c r="K230" s="5" t="inlineStr">
-        <is>
-          <t>結核桿菌</t>
-        </is>
-      </c>
-      <c r="L230" s="5" t="inlineStr">
-        <is>
-          <t>金黃色葡萄球菌</t>
-        </is>
-      </c>
-      <c r="M230" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N230" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O230" s="5" t="inlineStr">
-        <is>
-          <t>青黴素類抑制細胞壁合成；黴漿菌和脲原體沒有細胞壁，所以無效。</t>
-        </is>
-      </c>
-      <c r="P230" s="5" t="inlineStr">
-        <is>
-          <t>「細胞壁決定很多事」：青黴素類的目標是什麼構造？</t>
-        </is>
-      </c>
-      <c r="Q230" s="5" t="inlineStr">
-        <is>
-          <t>青黴素類的目標是什麼構造？ → 回到「細胞壁決定很多事」比較：細胞壁的種類決定染色結果、毒素種類，以及哪些抗生素有效。</t>
-        </is>
-      </c>
-      <c r="R230" s="5" t="inlineStr">
-        <is>
-          <t>選擇「黴漿菌」。青黴素類抑制細胞壁合成；黴漿菌和脲原體沒有細胞壁，所以無效。</t>
-        </is>
-      </c>
-      <c r="S230" s="5" t="inlineStr">
-        <is>
-          <t>青黴素類抑制細胞壁合成；黴漿菌和脲原體沒有細胞壁，所以無效。</t>
-        </is>
-      </c>
-      <c r="T230" s="3"/>
-      <c r="U230" s="3"/>
-      <c r="V230" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W230" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X230" s="3"/>
-    </row>
-    <row r="231" ht="233" hidden="0" customHeight="1">
-      <c r="A231" s="3"/>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-foundation-q03</t>
-        </is>
-      </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D231" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="inlineStr">
-        <is>
-          <t>有關內毒素的敘述，何者正確？</t>
-        </is>
-      </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>成分是脂多糖，耐熱</t>
-        </is>
-      </c>
-      <c r="J231" s="5" t="inlineStr">
-        <is>
-          <t>可以製成類毒素疫苗</t>
-        </is>
-      </c>
-      <c r="K231" s="5" t="inlineStr">
-        <is>
-          <t>主要由革蘭氏陽性菌分泌</t>
-        </is>
-      </c>
-      <c r="L231" s="5" t="inlineStr">
-        <is>
-          <t>化學本質是蛋白質</t>
-        </is>
-      </c>
-      <c r="M231" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N231" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O231" s="5" t="inlineStr">
-        <is>
-          <t>內毒素是陰性菌外膜的脂多糖，耐熱、毒性較弱，無法做成類毒素；其他三個選項描述的是外毒素。</t>
-        </is>
-      </c>
-      <c r="P231" s="5" t="inlineStr">
-        <is>
-          <t>「細菌的武器：外毒素與內毒素」：內毒素在陰性菌的哪一層？</t>
-        </is>
-      </c>
-      <c r="Q231" s="5" t="inlineStr">
-        <is>
-          <t>內毒素在陰性菌的哪一層？ → 回到「細菌的武器：外毒素與內毒素」比較：外毒素是活菌分泌的蛋白質，量少但毒性強；內毒素是陰性菌外膜的脂多糖，菌體破裂才釋出。</t>
-        </is>
-      </c>
-      <c r="R231" s="5" t="inlineStr">
-        <is>
-          <t>選擇「成分是脂多糖，耐熱」。內毒素是陰性菌外膜的脂多糖，耐熱、毒性較弱，無法做成類毒素；其他三個選項描述的是外毒素。</t>
-        </is>
-      </c>
-      <c r="S231" s="5" t="inlineStr">
-        <is>
-          <t>內毒素是陰性菌外膜的脂多糖，耐熱、毒性較弱，無法做成類毒素；其他三個選項描述的是外毒素。</t>
-        </is>
-      </c>
-      <c r="T231" s="3"/>
-      <c r="U231" s="3"/>
-      <c r="V231" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W231" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X231" s="3"/>
-    </row>
-    <row r="232" ht="233" hidden="0" customHeight="1">
-      <c r="A232" s="3"/>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-foundation-q04</t>
-        </is>
-      </c>
-      <c r="C232" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D232" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H232" s="5" t="inlineStr">
-        <is>
-          <t>預防醫院內交叉感染，最簡單也最有效的措施是：</t>
-        </is>
-      </c>
-      <c r="I232" s="5" t="inlineStr">
-        <is>
-          <t>全面禁止訪客</t>
-        </is>
-      </c>
-      <c r="J232" s="5" t="inlineStr">
-        <is>
-          <t>每位病人都使用預防性抗生素</t>
-        </is>
-      </c>
-      <c r="K232" s="5" t="inlineStr">
-        <is>
-          <t>落實手部衛生</t>
-        </is>
-      </c>
-      <c r="L232" s="5" t="inlineStr">
-        <is>
-          <t>每天用紫外線照射病房</t>
-        </is>
-      </c>
-      <c r="M232" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N232" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O232" s="5" t="inlineStr">
-        <is>
-          <t>院內感染以接觸傳播最常見，醫護人員的手是主要媒介，手部衛生是切斷傳播最有效的方法。</t>
-        </is>
-      </c>
-      <c r="P232" s="5" t="inlineStr">
-        <is>
-          <t>「感染怎麼發生，又怎麼傳出去」：院內感染最常見的傳播途徑是什麼？</t>
-        </is>
-      </c>
-      <c r="Q232" s="5" t="inlineStr">
-        <is>
-          <t>院內感染最常見的傳播途徑是什麼？ → 回到「感染怎麼發生，又怎麼傳出去」比較：感染鏈有六個環節，切斷任何一環就能阻止傳播；在醫院裡最容易切斷的是「手」。</t>
-        </is>
-      </c>
-      <c r="R232" s="5" t="inlineStr">
-        <is>
-          <t>選擇「落實手部衛生」。院內感染以接觸傳播最常見，醫護人員的手是主要媒介，手部衛生是切斷傳播最有效的方法。</t>
-        </is>
-      </c>
-      <c r="S232" s="5" t="inlineStr">
-        <is>
-          <t>院內感染以接觸傳播最常見，醫護人員的手是主要媒介，手部衛生是切斷傳播最有效的方法。</t>
-        </is>
-      </c>
-      <c r="T232" s="3"/>
-      <c r="U232" s="3"/>
-      <c r="V232" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W232" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X232" s="3"/>
-    </row>
-    <row r="233" ht="250" hidden="0" customHeight="1">
-      <c r="A233" s="3"/>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-foundation-q05</t>
-        </is>
-      </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>下列哪一種方法能殺死細菌內孢子而達到滅菌？</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>75% 酒精擦拭</t>
-        </is>
-      </c>
-      <c r="J233" s="5" t="inlineStr">
-        <is>
-          <t>煮沸 10 分鐘</t>
-        </is>
-      </c>
-      <c r="K233" s="5" t="inlineStr">
-        <is>
-          <t>高壓蒸氣 121℃、15 分鐘</t>
-        </is>
-      </c>
-      <c r="L233" s="5" t="inlineStr">
-        <is>
-          <t>優碘消毒</t>
-        </is>
-      </c>
-      <c r="M233" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N233" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O233" s="5" t="inlineStr">
-        <is>
-          <t>滅菌要殺死包括孢子在內的所有微生物；酒精、煮沸、優碘都無法可靠地殺死孢子。</t>
-        </is>
-      </c>
-      <c r="P233" s="5" t="inlineStr">
-        <is>
-          <t>「消毒與滅菌：殺到什麼程度？」：滅菌的定義是連什麼都要殺死？</t>
-        </is>
-      </c>
-      <c r="Q233" s="5" t="inlineStr">
-        <is>
-          <t>滅菌的定義是連什麼都要殺死？ → 回到「消毒與滅菌：殺到什麼程度？」比較：滅菌要連細菌孢子都殺死；消毒只殺死大部分病原。物品要處理到什麼程度，看它會接觸身體哪裡。</t>
-        </is>
-      </c>
-      <c r="R233" s="5" t="inlineStr">
-        <is>
-          <t>選擇「高壓蒸氣 121℃、15 分鐘」。滅菌要殺死包括孢子在內的所有微生物；酒精、煮沸、優碘都無法可靠地殺死孢子。</t>
-        </is>
-      </c>
-      <c r="S233" s="5" t="inlineStr">
-        <is>
-          <t>滅菌要殺死包括孢子在內的所有微生物；酒精、煮沸、優碘都無法可靠地殺死孢子。</t>
-        </is>
-      </c>
-      <c r="T233" s="3"/>
-      <c r="U233" s="3"/>
-      <c r="V233" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W233" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X233" s="3"/>
-    </row>
-    <row r="234" ht="199" hidden="0" customHeight="1">
-      <c r="A234" s="3"/>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-foundation-q06</t>
-        </is>
-      </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H234" s="5" t="inlineStr">
-        <is>
-          <t>喹諾酮類抗生素（如 ciprofloxacin）的作用機轉是：</t>
-        </is>
-      </c>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>抑制 DNA 旋轉酶</t>
-        </is>
-      </c>
-      <c r="J234" s="5" t="inlineStr">
-        <is>
-          <t>與 30S 核糖體結合</t>
-        </is>
-      </c>
-      <c r="K234" s="5" t="inlineStr">
-        <is>
-          <t>抑制葉酸合成</t>
-        </is>
-      </c>
-      <c r="L234" s="5" t="inlineStr">
-        <is>
-          <t>抑制細胞壁合成</t>
-        </is>
-      </c>
-      <c r="M234" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N234" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O234" s="5" t="inlineStr">
-        <is>
-          <t>喹諾酮類抑制 DNA 旋轉酶（與拓樸異構酶 IV），使細菌的 DNA 無法複製。</t>
-        </is>
-      </c>
-      <c r="P234" s="5" t="inlineStr">
-        <is>
-          <t>「抗生素打哪裡？細菌怎麼抗藥？」：它影響的是細菌複製哪一種分子？</t>
-        </is>
-      </c>
-      <c r="Q234" s="5" t="inlineStr">
-        <is>
-          <t>它影響的是細菌複製哪一種分子？ → 回到「抗生素打哪裡？細菌怎麼抗藥？」比較：抗生素攻擊細菌特有的構造；細菌則用四種方法對抗藥物。</t>
-        </is>
-      </c>
-      <c r="R234" s="5" t="inlineStr">
-        <is>
-          <t>選擇「抑制 DNA 旋轉酶」。喹諾酮類抑制 DNA 旋轉酶（與拓樸異構酶 IV），使細菌的 DNA 無法複製。</t>
-        </is>
-      </c>
-      <c r="S234" s="5" t="inlineStr">
-        <is>
-          <t>喹諾酮類抑制 DNA 旋轉酶（與拓樸異構酶 IV），使細菌的 DNA 無法複製。</t>
-        </is>
-      </c>
-      <c r="T234" s="3"/>
-      <c r="U234" s="3"/>
-      <c r="V234" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W234" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X234" s="3"/>
-    </row>
-    <row r="235" ht="233" hidden="0" customHeight="1">
-      <c r="A235" s="3"/>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-case-q01</t>
-        </is>
-      </c>
-      <c r="C235" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D235" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="inlineStr">
-        <is>
-          <t>【第 3 天】王先生的燒傷傷口流出藍綠色的膿，培養出需氧的革蘭氏陰性桿菌。最可能是哪一種菌？</t>
-        </is>
-      </c>
-      <c r="I235" s="5" t="inlineStr">
-        <is>
-          <t>化膿性鏈球菌</t>
-        </is>
-      </c>
-      <c r="J235" s="5" t="inlineStr">
-        <is>
-          <t>破傷風桿菌</t>
-        </is>
-      </c>
-      <c r="K235" s="5" t="inlineStr">
-        <is>
-          <t>金黃色葡萄球菌</t>
-        </is>
-      </c>
-      <c r="L235" s="5" t="inlineStr">
-        <is>
-          <t>綠膿桿菌</t>
-        </is>
-      </c>
-      <c r="M235" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N235" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O235" s="5" t="inlineStr">
-        <is>
-          <t>綠膿桿菌是需氧的陰性桿菌，會產生藍綠色的綠膿素，喜歡潮濕環境，是燒燙傷病人常見的感染菌。金黃色葡萄球菌和鏈球菌是陽性球菌。</t>
-        </is>
-      </c>
-      <c r="P235" s="5" t="inlineStr">
-        <is>
-          <t>「感染怎麼發生，又怎麼傳出去」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q235" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「感染怎麼發生，又怎麼傳出去」比較：感染鏈有六個環節，切斷任何一環就能阻止傳播；在醫院裡最容易切斷的是「手」。</t>
-        </is>
-      </c>
-      <c r="R235" s="5" t="inlineStr">
-        <is>
-          <t>選擇「綠膿桿菌」。綠膿桿菌是需氧的陰性桿菌，會產生藍綠色的綠膿素，喜歡潮濕環境，是燒燙傷病人常見的感染菌。金黃色葡萄球菌和鏈球菌是陽性球菌。</t>
-        </is>
-      </c>
-      <c r="S235" s="5" t="inlineStr">
-        <is>
-          <t>綠膿桿菌是需氧的陰性桿菌，會產生藍綠色的綠膿素，喜歡潮濕環境，是燒燙傷病人常見的感染菌。金黃色葡萄球菌和鏈球菌是陽性球菌。</t>
-        </is>
-      </c>
-      <c r="T235" s="3"/>
-      <c r="U235" s="3"/>
-      <c r="V235" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W235" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X235" s="3"/>
-    </row>
-    <row r="236" ht="250" hidden="0" customHeight="1">
-      <c r="A236" s="3"/>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-case-q02</t>
-        </is>
-      </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H236" s="5" t="inlineStr">
-        <is>
-          <t>【第 3 天晚上】王先生體溫 39.5℃、血壓 85/50 mmHg。造成這個狀況的主要毒力因子是：</t>
-        </is>
-      </c>
-      <c r="I236" s="5" t="inlineStr">
-        <is>
-          <t>莢膜</t>
-        </is>
-      </c>
-      <c r="J236" s="5" t="inlineStr">
-        <is>
-          <t>外毒素直接破壞神經</t>
-        </is>
-      </c>
-      <c r="K236" s="5" t="inlineStr">
-        <is>
-          <t>陰性菌的內毒素（脂多糖）引起全身發炎與休克</t>
-        </is>
-      </c>
-      <c r="L236" s="5" t="inlineStr">
-        <is>
-          <t>類毒素</t>
-        </is>
-      </c>
-      <c r="M236" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N236" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O236" s="5" t="inlineStr">
-        <is>
-          <t>脂多糖的脂質 A 刺激巨噬細胞釋放大量發炎物質，造成發燒、血管擴張、血壓下降，也就是敗血性休克。</t>
-        </is>
-      </c>
-      <c r="P236" s="5" t="inlineStr">
-        <is>
-          <t>「細菌的武器：外毒素與內毒素」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q236" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「細菌的武器：外毒素與內毒素」比較：外毒素是活菌分泌的蛋白質，量少但毒性強；內毒素是陰性菌外膜的脂多糖，菌體破裂才釋出。</t>
-        </is>
-      </c>
-      <c r="R236" s="5" t="inlineStr">
-        <is>
-          <t>選擇「陰性菌的內毒素（脂多糖）引起全身發炎與休克」。脂多糖的脂質 A 刺激巨噬細胞釋放大量發炎物質，造成發燒、血管擴張、血壓下降，也就是敗血性休克。</t>
-        </is>
-      </c>
-      <c r="S236" s="5" t="inlineStr">
-        <is>
-          <t>脂多糖的脂質 A 刺激巨噬細胞釋放大量發炎物質，造成發燒、血管擴張、血壓下降，也就是敗血性休克。</t>
-        </is>
-      </c>
-      <c r="T236" s="3"/>
-      <c r="U236" s="3"/>
-      <c r="V236" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W236" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X236" s="3"/>
-    </row>
-    <row r="237" ht="250" hidden="0" customHeight="1">
-      <c r="A237" s="3"/>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-case-q03</t>
-        </is>
-      </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="inlineStr">
-        <is>
-          <t>【第 4 天】隔壁床的病人也驗出同一種菌。最可能的傳播途徑，以及最優先的處置是：</t>
-        </is>
-      </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>空氣傳播，應改住負壓隔離病房</t>
-        </is>
-      </c>
-      <c r="J237" s="5" t="inlineStr">
-        <is>
-          <t>經醫護人員的手與共用器材接觸傳播，落實手部衛生與器材專用</t>
-        </is>
-      </c>
-      <c r="K237" s="5" t="inlineStr">
-        <is>
-          <t>經食物傳播，應停止送餐</t>
-        </is>
-      </c>
-      <c r="L237" s="5" t="inlineStr">
-        <is>
-          <t>病人自己免疫力低下，和傳播無關</t>
-        </is>
-      </c>
-      <c r="M237" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N237" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O237" s="5" t="inlineStr">
-        <is>
-          <t>綠膿桿菌在醫院主要靠接觸傳播。手部衛生和器材專用可以切斷傳播途徑，這是感染鏈中最容易介入的一環。</t>
-        </is>
-      </c>
-      <c r="P237" s="5" t="inlineStr">
-        <is>
-          <t>「感染怎麼發生，又怎麼傳出去」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q237" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「感染怎麼發生，又怎麼傳出去」比較：感染鏈有六個環節，切斷任何一環就能阻止傳播；在醫院裡最容易切斷的是「手」。</t>
-        </is>
-      </c>
-      <c r="R237" s="5" t="inlineStr">
-        <is>
-          <t>選擇「經醫護人員的手與共用器材接觸傳播，落實手部衛生與器材專用」。綠膿桿菌在醫院主要靠接觸傳播。手部衛生和器材專用可以切斷傳播途徑，這是感染鏈中最容易介入的一環。</t>
-        </is>
-      </c>
-      <c r="S237" s="5" t="inlineStr">
-        <is>
-          <t>綠膿桿菌在醫院主要靠接觸傳播。手部衛生和器材專用可以切斷傳播途徑，這是感染鏈中最容易介入的一環。</t>
-        </is>
-      </c>
-      <c r="T237" s="3"/>
-      <c r="U237" s="3"/>
-      <c r="V237" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W237" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X237" s="3"/>
-    </row>
-    <row r="238" ht="267" hidden="0" customHeight="1">
-      <c r="A238" s="3"/>
-      <c r="B238" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-case-q04</t>
-        </is>
-      </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H238" s="5" t="inlineStr">
-        <is>
-          <t>【第 5 天】王先生換藥時使用的鑷子和剪刀，用完後應該怎麼處理？</t>
-        </is>
-      </c>
-      <c r="I238" s="5" t="inlineStr">
-        <is>
-          <t>清潔後以高壓蒸氣滅菌</t>
-        </is>
-      </c>
-      <c r="J238" s="5" t="inlineStr">
-        <is>
-          <t>用清水沖洗晾乾</t>
-        </is>
-      </c>
-      <c r="K238" s="5" t="inlineStr">
-        <is>
-          <t>做低層次消毒</t>
-        </is>
-      </c>
-      <c r="L238" s="5" t="inlineStr">
-        <is>
-          <t>用 75% 酒精擦拭即可</t>
-        </is>
-      </c>
-      <c r="M238" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N238" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O238" s="5" t="inlineStr">
-        <is>
-          <t>換藥器械會接觸燒傷創面的組織，屬於重要物品，必須清潔後滅菌。酒精和低層次消毒都殺不死孢子。</t>
-        </is>
-      </c>
-      <c r="P238" s="5" t="inlineStr">
-        <is>
-          <t>「消毒與滅菌：殺到什麼程度？」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q238" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「消毒與滅菌：殺到什麼程度？」比較：滅菌要連細菌孢子都殺死；消毒只殺死大部分病原。物品要處理到什麼程度，看它會接觸身體哪裡。</t>
-        </is>
-      </c>
-      <c r="R238" s="5" t="inlineStr">
-        <is>
-          <t>選擇「清潔後以高壓蒸氣滅菌」。換藥器械會接觸燒傷創面的組織，屬於重要物品，必須清潔後滅菌。酒精和低層次消毒都殺不死孢子。</t>
-        </is>
-      </c>
-      <c r="S238" s="5" t="inlineStr">
-        <is>
-          <t>換藥器械會接觸燒傷創面的組織，屬於重要物品，必須清潔後滅菌。酒精和低層次消毒都殺不死孢子。</t>
-        </is>
-      </c>
-      <c r="T238" s="3"/>
-      <c r="U238" s="3"/>
-      <c r="V238" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W238" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X238" s="3"/>
-    </row>
-    <row r="239" ht="284" hidden="0" customHeight="1">
-      <c r="A239" s="3"/>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>micro-bacteria-review-case-q05</t>
-        </is>
-      </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="inlineStr">
-        <is>
-          <t>【第 10 天】王先生使用廣效抗生素一週後，開始嚴重水瀉。最需要懷疑的是：</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>病毒性腸胃炎</t>
-        </is>
-      </c>
-      <c r="J239" s="5" t="inlineStr">
-        <is>
-          <t>對抗生素過敏</t>
-        </is>
-      </c>
-      <c r="K239" s="5" t="inlineStr">
-        <is>
-          <t>綠膿桿菌腸炎</t>
-        </is>
-      </c>
-      <c r="L239" s="5" t="inlineStr">
-        <is>
-          <t>抗生素破壞腸道正常菌叢，困難梭菌過度生長</t>
-        </is>
-      </c>
-      <c r="M239" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N239" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O239" s="5" t="inlineStr">
-        <is>
-          <t>廣效抗生素殺死腸道正常菌叢，困難梭菌趁機增生，產生毒素造成偽膜性結腸炎。它會形成孢子，酒精殺不死，照護時要用肥皂和清水洗手（接回節點 05）。</t>
-        </is>
-      </c>
-      <c r="P239" s="5" t="inlineStr">
-        <is>
-          <t>「抗生素打哪裡？細菌怎麼抗藥？」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q239" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「抗生素打哪裡？細菌怎麼抗藥？」比較：抗生素攻擊細菌特有的構造；細菌則用四種方法對抗藥物。</t>
-        </is>
-      </c>
-      <c r="R239" s="5" t="inlineStr">
-        <is>
-          <t>選擇「抗生素破壞腸道正常菌叢，困難梭菌過度生長」。廣效抗生素殺死腸道正常菌叢，困難梭菌趁機增生，產生毒素造成偽膜性結腸炎。它會形成孢子，酒精殺不死，照護時要用肥皂和清水洗手（接回節點 05）。</t>
-        </is>
-      </c>
-      <c r="S239" s="5" t="inlineStr">
-        <is>
-          <t>廣效抗生素殺死腸道正常菌叢，困難梭菌趁機增生，產生毒素造成偽膜性結腸炎。它會形成孢子，酒精殺不死，照護時要用肥皂和清水洗手（接回節點 05）。</t>
-        </is>
-      </c>
-      <c r="T239" s="3"/>
-      <c r="U239" s="3"/>
-      <c r="V239" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="W239" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X239" s="3"/>
-    </row>
-    <row r="240" ht="216" hidden="0" customHeight="1">
-      <c r="A240" s="3"/>
-      <c r="B240" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-foundation-q01</t>
-        </is>
-      </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H240" s="5" t="inlineStr">
-        <is>
-          <t>下列哪一項是先天免疫的特性？</t>
-        </is>
-      </c>
-      <c r="I240" s="5" t="inlineStr">
-        <is>
-          <t>具有專一性</t>
-        </is>
-      </c>
-      <c r="J240" s="5" t="inlineStr">
-        <is>
-          <t>第二次接觸時反應更強</t>
-        </is>
-      </c>
-      <c r="K240" s="5" t="inlineStr">
-        <is>
-          <t>出生就具備，反應快但沒有記憶</t>
-        </is>
-      </c>
-      <c r="L240" s="5" t="inlineStr">
-        <is>
-          <t>由漿細胞負責</t>
-        </is>
-      </c>
-      <c r="M240" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N240" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O240" s="5" t="inlineStr">
-        <is>
-          <t>先天免疫出生就有、反應快、沒有專一性也沒有記憶；專一性、記憶、漿細胞都屬於後天免疫。</t>
-        </is>
-      </c>
-      <c r="P240" s="5" t="inlineStr">
-        <is>
-          <t>「先天免疫與後天免疫」：先天免疫有沒有「記憶」？</t>
-        </is>
-      </c>
-      <c r="Q240" s="5" t="inlineStr">
-        <is>
-          <t>先天免疫有沒有「記憶」？ → 回到「先天免疫與後天免疫」比較：先天免疫出生就有、反應快但沒有專一性；後天免疫要接觸過抗原才建立，有專一性和記憶。</t>
-        </is>
-      </c>
-      <c r="R240" s="5" t="inlineStr">
-        <is>
-          <t>選擇「出生就具備，反應快但沒有記憶」。先天免疫出生就有、反應快、沒有專一性也沒有記憶；專一性、記憶、漿細胞都屬於後天免疫。</t>
-        </is>
-      </c>
-      <c r="S240" s="5" t="inlineStr">
-        <is>
-          <t>先天免疫出生就有、反應快、沒有專一性也沒有記憶；專一性、記憶、漿細胞都屬於後天免疫。</t>
-        </is>
-      </c>
-      <c r="T240" s="3"/>
-      <c r="U240" s="3"/>
-      <c r="V240" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W240" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X240" s="3"/>
-    </row>
-    <row r="241" ht="233" hidden="0" customHeight="1">
-      <c r="A241" s="3"/>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-foundation-q02</t>
-        </is>
-      </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H241" s="5" t="inlineStr">
-        <is>
-          <t>母親是 B 型肝炎帶原者，新生兒出生後立即注射 B 型肝炎免疫球蛋白（HBIG）。這屬於哪一種免疫？</t>
-        </is>
-      </c>
-      <c r="I241" s="5" t="inlineStr">
-        <is>
-          <t>人工主動免疫</t>
-        </is>
-      </c>
-      <c r="J241" s="5" t="inlineStr">
-        <is>
-          <t>天然被動免疫</t>
-        </is>
-      </c>
-      <c r="K241" s="5" t="inlineStr">
-        <is>
-          <t>人工被動免疫</t>
-        </is>
-      </c>
-      <c r="L241" s="5" t="inlineStr">
-        <is>
-          <t>天然主動免疫</t>
-        </is>
-      </c>
-      <c r="M241" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N241" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O241" s="5" t="inlineStr">
-        <is>
-          <t>HBIG 是現成的抗體，用注射的方式給予，所以是人工被動免疫；同時打的 B 型肝炎疫苗則是人工主動免疫。</t>
-        </is>
-      </c>
-      <c r="P241" s="5" t="inlineStr">
-        <is>
-          <t>「主動免疫與被動免疫」：HBIG 裡裝的是現成的抗體嗎？</t>
-        </is>
-      </c>
-      <c r="Q241" s="5" t="inlineStr">
-        <is>
-          <t>HBIG 裡裝的是現成的抗體嗎？ → 回到「主動免疫與被動免疫」比較：主動免疫是自己的身體製造抗體和記憶細胞，慢但持久；被動免疫是接受現成的抗體，快但短暫。</t>
-        </is>
-      </c>
-      <c r="R241" s="5" t="inlineStr">
-        <is>
-          <t>選擇「人工被動免疫」。HBIG 是現成的抗體，用注射的方式給予，所以是人工被動免疫；同時打的 B 型肝炎疫苗則是人工主動免疫。</t>
-        </is>
-      </c>
-      <c r="S241" s="5" t="inlineStr">
-        <is>
-          <t>HBIG 是現成的抗體，用注射的方式給予，所以是人工被動免疫；同時打的 B 型肝炎疫苗則是人工主動免疫。</t>
-        </is>
-      </c>
-      <c r="T241" s="3"/>
-      <c r="U241" s="3"/>
-      <c r="V241" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W241" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X241" s="3"/>
-    </row>
-    <row r="242" ht="199" hidden="0" customHeight="1">
-      <c r="A242" s="3"/>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-foundation-q03</t>
-        </is>
-      </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H242" s="5" t="inlineStr">
-        <is>
-          <t>負責製造並分泌抗體的細胞是：</t>
-        </is>
-      </c>
-      <c r="I242" s="5" t="inlineStr">
-        <is>
-          <t>巨噬細胞</t>
-        </is>
-      </c>
-      <c r="J242" s="5" t="inlineStr">
-        <is>
-          <t>嗜中性球</t>
-        </is>
-      </c>
-      <c r="K242" s="5" t="inlineStr">
-        <is>
-          <t>T 細胞</t>
-        </is>
-      </c>
-      <c r="L242" s="5" t="inlineStr">
-        <is>
-          <t>漿細胞</t>
-        </is>
-      </c>
-      <c r="M242" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N242" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O242" s="5" t="inlineStr">
-        <is>
-          <t>B 細胞活化後分化成漿細胞，由漿細胞大量分泌抗體。</t>
-        </is>
-      </c>
-      <c r="P242" s="5" t="inlineStr">
-        <is>
-          <t>「免疫細胞與淋巴器官」：B 細胞活化後會分化成什麼？</t>
-        </is>
-      </c>
-      <c r="Q242" s="5" t="inlineStr">
-        <is>
-          <t>B 細胞活化後會分化成什麼？ → 回到「免疫細胞與淋巴器官」比較：所有免疫細胞都來自骨髓的造血幹細胞，分成骨髓系和淋巴系兩大家族。</t>
-        </is>
-      </c>
-      <c r="R242" s="5" t="inlineStr">
-        <is>
-          <t>選擇「漿細胞」。B 細胞活化後分化成漿細胞，由漿細胞大量分泌抗體。</t>
-        </is>
-      </c>
-      <c r="S242" s="5" t="inlineStr">
-        <is>
-          <t>B 細胞活化後分化成漿細胞，由漿細胞大量分泌抗體。</t>
-        </is>
-      </c>
-      <c r="T242" s="3"/>
-      <c r="U242" s="3"/>
-      <c r="V242" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W242" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X242" s="3"/>
-    </row>
-    <row r="243" ht="250" hidden="0" customHeight="1">
-      <c r="A243" s="3"/>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-foundation-q04</t>
-        </is>
-      </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="inlineStr">
-        <is>
-          <t>有關抗原與抗體的敘述，何者正確？</t>
-        </is>
-      </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>一個抗原只能被一種抗體結合</t>
-        </is>
-      </c>
-      <c r="J243" s="5" t="inlineStr">
-        <is>
-          <t>抗體是外來物質，抗原是身體製造的蛋白質</t>
-        </is>
-      </c>
-      <c r="K243" s="5" t="inlineStr">
-        <is>
-          <t>A 型血的人，紅血球上有 A 抗原，血漿中有抗 B 抗體</t>
-        </is>
-      </c>
-      <c r="L243" s="5" t="inlineStr">
-        <is>
-          <t>抗原一定是致病的細菌或病毒</t>
-        </is>
-      </c>
-      <c r="M243" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N243" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O243" s="5" t="inlineStr">
-        <is>
-          <t>抗原是被辨認的物質，抗體是自己的漿細胞製造的；抗原不一定有害；一個抗原有多個決定位，可以被多種抗體結合。</t>
-        </is>
-      </c>
-      <c r="P243" s="5" t="inlineStr">
-        <is>
-          <t>「抗原與抗體：誰是鎖？誰是鑰匙？」：鎖和鑰匙，各自是誰做的？</t>
-        </is>
-      </c>
-      <c r="Q243" s="5" t="inlineStr">
-        <is>
-          <t>鎖和鑰匙，各自是誰做的？ → 回到「抗原與抗體：誰是鎖？誰是鑰匙？」比較：抗原是引起免疫反應、被辨認的那一方（鎖）；抗體是身體做出來、去辨認抗原的蛋白質（鑰匙）。</t>
-        </is>
-      </c>
-      <c r="R243" s="5" t="inlineStr">
-        <is>
-          <t>選擇「A 型血的人，紅血球上有 A 抗原，血漿中有抗 B 抗體」。抗原是被辨認的物質，抗體是自己的漿細胞製造的；抗原不一定有害；一個抗原有多個決定位，可以被多種抗體結合。</t>
-        </is>
-      </c>
-      <c r="S243" s="5" t="inlineStr">
-        <is>
-          <t>抗原是被辨認的物質，抗體是自己的漿細胞製造的；抗原不一定有害；一個抗原有多個決定位，可以被多種抗體結合。</t>
-        </is>
-      </c>
-      <c r="T243" s="3"/>
-      <c r="U243" s="3"/>
-      <c r="V243" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W243" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X243" s="3"/>
-    </row>
-    <row r="244" ht="216" hidden="0" customHeight="1">
-      <c r="A244" s="3"/>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-foundation-q05</t>
-        </is>
-      </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H244" s="5" t="inlineStr">
-        <is>
-          <t>初次免疫反應最早出現、分子量最大的抗體是：</t>
-        </is>
-      </c>
-      <c r="I244" s="5" t="inlineStr">
-        <is>
-          <t>IgG</t>
-        </is>
-      </c>
-      <c r="J244" s="5" t="inlineStr">
-        <is>
-          <t>IgA</t>
-        </is>
-      </c>
-      <c r="K244" s="5" t="inlineStr">
-        <is>
-          <t>IgM</t>
-        </is>
-      </c>
-      <c r="L244" s="5" t="inlineStr">
-        <is>
-          <t>IgE</t>
-        </is>
-      </c>
-      <c r="M244" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N244" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O244" s="5" t="inlineStr">
-        <is>
-          <t>IgM 是五聚體，分子最大，是初次反應最先出現的抗體。</t>
-        </is>
-      </c>
-      <c r="P244" s="5" t="inlineStr">
-        <is>
-          <t>「五種抗體的不同」：哪一種抗體是五聚體？</t>
-        </is>
-      </c>
-      <c r="Q244" s="5" t="inlineStr">
-        <is>
-          <t>哪一種抗體是五聚體？ → 回到「五種抗體的不同」比較：五種抗體的差別在 Fc 部分，因此結構、分布和工作都不同；血中含量由多到少是 G、A、M、D、E。</t>
-        </is>
-      </c>
-      <c r="R244" s="5" t="inlineStr">
-        <is>
-          <t>選擇「IgM」。IgM 是五聚體，分子最大，是初次反應最先出現的抗體。</t>
-        </is>
-      </c>
-      <c r="S244" s="5" t="inlineStr">
-        <is>
-          <t>IgM 是五聚體，分子最大，是初次反應最先出現的抗體。</t>
-        </is>
-      </c>
-      <c r="T244" s="3"/>
-      <c r="U244" s="3"/>
-      <c r="V244" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W244" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X244" s="3"/>
-    </row>
-    <row r="245" ht="250" hidden="0" customHeight="1">
-      <c r="A245" s="3"/>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-foundation-q06</t>
-        </is>
-      </c>
-      <c r="C245" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D245" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="inlineStr">
-        <is>
-          <t>能直接殺死被病毒感染細胞的是：</t>
-        </is>
-      </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>CD8 毒殺型 T 細胞</t>
-        </is>
-      </c>
-      <c r="J245" s="5" t="inlineStr">
-        <is>
-          <t>B 細胞</t>
-        </is>
-      </c>
-      <c r="K245" s="5" t="inlineStr">
-        <is>
-          <t>肥大細胞</t>
-        </is>
-      </c>
-      <c r="L245" s="5" t="inlineStr">
-        <is>
-          <t>CD4 輔助型 T 細胞</t>
-        </is>
-      </c>
-      <c r="M245" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N245" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O245" s="5" t="inlineStr">
-        <is>
-          <t>CD8 毒殺型 T 細胞辨認第一類 MHC 上的病毒抗原片段，直接讓被感染的細胞凋亡；CD4 負責指揮。</t>
-        </is>
-      </c>
-      <c r="P245" s="5" t="inlineStr">
-        <is>
-          <t>「T 細胞：指揮官與殺手」：指揮官和殺手，哪一個動手？</t>
-        </is>
-      </c>
-      <c r="Q245" s="5" t="inlineStr">
-        <is>
-          <t>指揮官和殺手，哪一個動手？ → 回到「T 細胞：指揮官與殺手」比較：T 細胞在胸腺成熟，只辨認「被呈現在細胞表面」的抗原片段，負責指揮免疫反應和直接殺死被感染的細胞。</t>
-        </is>
-      </c>
-      <c r="R245" s="5" t="inlineStr">
-        <is>
-          <t>選擇「CD8 毒殺型 T 細胞」。CD8 毒殺型 T 細胞辨認第一類 MHC 上的病毒抗原片段，直接讓被感染的細胞凋亡；CD4 負責指揮。</t>
-        </is>
-      </c>
-      <c r="S245" s="5" t="inlineStr">
-        <is>
-          <t>CD8 毒殺型 T 細胞辨認第一類 MHC 上的病毒抗原片段，直接讓被感染的細胞凋亡；CD4 負責指揮。</t>
-        </is>
-      </c>
-      <c r="T245" s="3"/>
-      <c r="U245" s="3"/>
-      <c r="V245" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W245" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X245" s="3"/>
-    </row>
-    <row r="246" ht="250" hidden="0" customHeight="1">
-      <c r="A246" s="3"/>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-case-q01</t>
-        </is>
-      </c>
-      <c r="C246" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H246" s="5" t="inlineStr">
-        <is>
-          <t>【出生】小安的臍帶血檢驗發現有對抗麻疹的抗體。這些抗體最可能是：</t>
-        </is>
-      </c>
-      <c r="I246" s="5" t="inlineStr">
-        <is>
-          <t>經母乳得到的 IgA</t>
-        </is>
-      </c>
-      <c r="J246" s="5" t="inlineStr">
-        <is>
-          <t>小安自己製造的 IgG</t>
-        </is>
-      </c>
-      <c r="K246" s="5" t="inlineStr">
-        <is>
-          <t>小安自己製造的 IgM</t>
-        </is>
-      </c>
-      <c r="L246" s="5" t="inlineStr">
-        <is>
-          <t>經胎盤從媽媽來的 IgG，屬天然被動免疫</t>
-        </is>
-      </c>
-      <c r="M246" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N246" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O246" s="5" t="inlineStr">
-        <is>
-          <t>IgG 是唯一能通過胎盤的抗體，屬天然被動免疫，約在 6 個月內逐漸消失。若臍帶血中特定 IgM 偏高，表示胎兒在子宮內受到感染。</t>
-        </is>
-      </c>
-      <c r="P246" s="5" t="inlineStr">
-        <is>
-          <t>「五種抗體的不同」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q246" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「五種抗體的不同」比較：五種抗體的差別在 Fc 部分，因此結構、分布和工作都不同；血中含量由多到少是 G、A、M、D、E。</t>
-        </is>
-      </c>
-      <c r="R246" s="5" t="inlineStr">
-        <is>
-          <t>選擇「經胎盤從媽媽來的 IgG，屬天然被動免疫」。IgG 是唯一能通過胎盤的抗體，屬天然被動免疫，約在 6 個月內逐漸消失。若臍帶血中特定 IgM 偏高，表示胎兒在子宮內受到感染。</t>
-        </is>
-      </c>
-      <c r="S246" s="5" t="inlineStr">
-        <is>
-          <t>IgG 是唯一能通過胎盤的抗體，屬天然被動免疫，約在 6 個月內逐漸消失。若臍帶血中特定 IgM 偏高，表示胎兒在子宮內受到感染。</t>
-        </is>
-      </c>
-      <c r="T246" s="3"/>
-      <c r="U246" s="3"/>
-      <c r="V246" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W246" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X246" s="3"/>
-    </row>
-    <row r="247" ht="250" hidden="0" customHeight="1">
-      <c r="A247" s="3"/>
-      <c r="B247" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-case-q02</t>
-        </is>
-      </c>
-      <c r="C247" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D247" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H247" s="5" t="inlineStr">
-        <is>
-          <t>【第 1 週】媽媽餵小安喝初乳。初乳中保護小安腸道黏膜的主要抗體是：</t>
-        </is>
-      </c>
-      <c r="I247" s="5" t="inlineStr">
-        <is>
-          <t>IgE</t>
-        </is>
-      </c>
-      <c r="J247" s="5" t="inlineStr">
-        <is>
-          <t>IgG</t>
-        </is>
-      </c>
-      <c r="K247" s="5" t="inlineStr">
-        <is>
-          <t>分泌型 IgA</t>
-        </is>
-      </c>
-      <c r="L247" s="5" t="inlineStr">
-        <is>
-          <t>IgM</t>
-        </is>
-      </c>
-      <c r="M247" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N247" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O247" s="5" t="inlineStr">
-        <is>
-          <t>分泌型 IgA 存在初乳和各種黏膜分泌物中，保護腸道和呼吸道黏膜；屬天然被動免疫。</t>
-        </is>
-      </c>
-      <c r="P247" s="5" t="inlineStr">
-        <is>
-          <t>「五種抗體的不同」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q247" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「五種抗體的不同」比較：五種抗體的差別在 Fc 部分，因此結構、分布和工作都不同；血中含量由多到少是 G、A、M、D、E。</t>
-        </is>
-      </c>
-      <c r="R247" s="5" t="inlineStr">
-        <is>
-          <t>選擇「分泌型 IgA」。分泌型 IgA 存在初乳和各種黏膜分泌物中，保護腸道和呼吸道黏膜；屬天然被動免疫。</t>
-        </is>
-      </c>
-      <c r="S247" s="5" t="inlineStr">
-        <is>
-          <t>分泌型 IgA 存在初乳和各種黏膜分泌物中，保護腸道和呼吸道黏膜；屬天然被動免疫。</t>
-        </is>
-      </c>
-      <c r="T247" s="3"/>
-      <c r="U247" s="3"/>
-      <c r="V247" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W247" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X247" s="3"/>
-    </row>
-    <row r="248" ht="335" hidden="0" customHeight="1">
-      <c r="A248" s="3"/>
-      <c r="B248" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-case-q03</t>
-        </is>
-      </c>
-      <c r="C248" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H248" s="5" t="inlineStr">
-        <is>
-          <t>【產後】媽媽是 A 型血，產後大出血需要輸血。如果誤輸了 B 型血，會發生什麼事？</t>
-        </is>
-      </c>
-      <c r="I248" s="5" t="inlineStr">
-        <is>
-          <t>媽媽紅血球上的 B 抗原和輸入的抗 A 抗體結合</t>
-        </is>
-      </c>
-      <c r="J248" s="5" t="inlineStr">
-        <is>
-          <t>媽媽血漿中的抗 B 抗體結合輸入紅血球上的 B 抗原，造成凝集與溶血</t>
-        </is>
-      </c>
-      <c r="K248" s="5" t="inlineStr">
-        <is>
-          <t>不會有反應，因為紅血球不是病菌</t>
-        </is>
-      </c>
-      <c r="L248" s="5" t="inlineStr">
-        <is>
-          <t>媽媽要一週後才會開始產生抗體</t>
-        </is>
-      </c>
-      <c r="M248" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N248" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O248" s="5" t="inlineStr">
-        <is>
-          <t>A 型的人紅血球上是 A 抗原、血漿中本來就有抗 B 抗體（主要是 IgM）。輸入的 B 型紅血球帶有 B 抗原，會立刻被抗 B 抗體結合，引起凝集並活化補體造成溶血。</t>
-        </is>
-      </c>
-      <c r="P248" s="5" t="inlineStr">
-        <is>
-          <t>「抗原與抗體：誰是鎖？誰是鑰匙？」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q248" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「抗原與抗體：誰是鎖？誰是鑰匙？」比較：抗原是引起免疫反應、被辨認的那一方（鎖）；抗體是身體做出來、去辨認抗原的蛋白質（鑰匙）。</t>
-        </is>
-      </c>
-      <c r="R248" s="5" t="inlineStr">
-        <is>
-          <t>選擇「媽媽血漿中的抗 B 抗體結合輸入紅血球上的 B 抗原，造成凝集與溶血」。A 型的人紅血球上是 A 抗原、血漿中本來就有抗 B 抗體（主要是 IgM）。輸入的 B 型紅血球帶有 B 抗原，會立刻被抗 B 抗體結合，引起凝集並活化補體造成溶血。</t>
-        </is>
-      </c>
-      <c r="S248" s="5" t="inlineStr">
-        <is>
-          <t>A 型的人紅血球上是 A 抗原、血漿中本來就有抗 B 抗體（主要是 IgM）。輸入的 B 型紅血球帶有 B 抗原，會立刻被抗 B 抗體結合，引起凝集並活化補體造成溶血。</t>
-        </is>
-      </c>
-      <c r="T248" s="3"/>
-      <c r="U248" s="3"/>
-      <c r="V248" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W248" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X248" s="3"/>
-    </row>
-    <row r="249" ht="267" hidden="0" customHeight="1">
-      <c r="A249" s="3"/>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-case-q04</t>
-        </is>
-      </c>
-      <c r="C249" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H249" s="5" t="inlineStr">
-        <is>
-          <t>【1 個月】小安出生時打了第一劑 B 型肝炎疫苗，一個月後打第二劑。第二劑後的抗體反應會：</t>
-        </is>
-      </c>
-      <c r="I249" s="5" t="inlineStr">
-        <is>
-          <t>比較慢，且以 IgM 為主</t>
-        </is>
-      </c>
-      <c r="J249" s="5" t="inlineStr">
-        <is>
-          <t>更快、更多，以 IgG 為主，因為已有記憶細胞</t>
-        </is>
-      </c>
-      <c r="K249" s="5" t="inlineStr">
-        <is>
-          <t>不會產生抗體，因為第一劑已經用完</t>
-        </is>
-      </c>
-      <c r="L249" s="5" t="inlineStr">
-        <is>
-          <t>和第一劑完全相同</t>
-        </is>
-      </c>
-      <c r="M249" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N249" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O249" s="5" t="inlineStr">
-        <is>
-          <t>第一劑留下記憶 B 細胞，第二劑引發再次反應：潛伏期短、抗體量多、以 IgG 為主、維持更久。這就是疫苗需要追加劑的原因。</t>
-        </is>
-      </c>
-      <c r="P249" s="5" t="inlineStr">
-        <is>
-          <t>「抗體的結構與功能：B 細胞的工作」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q249" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「抗體的結構與功能：B 細胞的工作」比較：B 細胞遇到抗原後，在輔助型 T 細胞幫助下增殖，分化成製造抗體的漿細胞和留下來的記憶 B 細胞。</t>
-        </is>
-      </c>
-      <c r="R249" s="5" t="inlineStr">
-        <is>
-          <t>選擇「更快、更多，以 IgG 為主，因為已有記憶細胞」。第一劑留下記憶 B 細胞，第二劑引發再次反應：潛伏期短、抗體量多、以 IgG 為主、維持更久。這就是疫苗需要追加劑的原因。</t>
-        </is>
-      </c>
-      <c r="S249" s="5" t="inlineStr">
-        <is>
-          <t>第一劑留下記憶 B 細胞，第二劑引發再次反應：潛伏期短、抗體量多、以 IgG 為主、維持更久。這就是疫苗需要追加劑的原因。</t>
-        </is>
-      </c>
-      <c r="T249" s="3"/>
-      <c r="U249" s="3"/>
-      <c r="V249" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W249" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X249" s="3"/>
-    </row>
-    <row r="250" ht="267" hidden="0" customHeight="1">
-      <c r="A250" s="3"/>
-      <c r="B250" s="4" t="inlineStr">
-        <is>
-          <t>immuno-concepts-review-case-q05</t>
-        </is>
-      </c>
-      <c r="C250" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>單選</t>
-        </is>
-      </c>
-      <c r="H250" s="5" t="inlineStr">
-        <is>
-          <t>【同病房】同病房的另一個寶寶出生後反覆發生嚴重的病毒和黴菌感染，檢查發現胸腺發育不全。最主要受影響的是：</t>
-        </is>
-      </c>
-      <c r="I250" s="5" t="inlineStr">
-        <is>
-          <t>嗜中性球的數量</t>
-        </is>
-      </c>
-      <c r="J250" s="5" t="inlineStr">
-        <is>
-          <t>皮膚屏障</t>
-        </is>
-      </c>
-      <c r="K250" s="5" t="inlineStr">
-        <is>
-          <t>補體系統</t>
-        </is>
-      </c>
-      <c r="L250" s="5" t="inlineStr">
-        <is>
-          <t>T 細胞成熟與細胞性免疫</t>
-        </is>
-      </c>
-      <c r="M250" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N250" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O250" s="5" t="inlineStr">
-        <is>
-          <t>T 細胞在胸腺成熟。胸腺發育不全會使 T 細胞缺乏，細胞性免疫低下；因為 B 細胞也需要輔助型 T 細胞幫忙，抗體反應也會變差。</t>
-        </is>
-      </c>
-      <c r="P250" s="5" t="inlineStr">
-        <is>
-          <t>「T 細胞：指揮官與殺手」：回到對應節點重讀臨床連結，再判斷一次。</t>
-        </is>
-      </c>
-      <c r="Q250" s="5" t="inlineStr">
-        <is>
-          <t>回到對應節點重讀臨床連結，再判斷一次。 → 回到「T 細胞：指揮官與殺手」比較：T 細胞在胸腺成熟，只辨認「被呈現在細胞表面」的抗原片段，負責指揮免疫反應和直接殺死被感染的細胞。</t>
-        </is>
-      </c>
-      <c r="R250" s="5" t="inlineStr">
-        <is>
-          <t>選擇「T 細胞成熟與細胞性免疫」。T 細胞在胸腺成熟。胸腺發育不全會使 T 細胞缺乏，細胞性免疫低下；因為 B 細胞也需要輔助型 T 細胞幫忙，抗體反應也會變差。</t>
-        </is>
-      </c>
-      <c r="S250" s="5" t="inlineStr">
-        <is>
-          <t>T 細胞在胸腺成熟。胸腺發育不全會使 T 細胞缺乏，細胞性免疫低下；因為 B 細胞也需要輔助型 T 細胞幫忙，抗體反應也會變差。</t>
-        </is>
-      </c>
-      <c r="T250" s="3"/>
-      <c r="U250" s="3"/>
-      <c r="V250" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="W250" s="5" t="inlineStr">
-        <is>
-          <t>https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html</t>
-        </is>
-      </c>
-      <c r="X250" s="3"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="M2:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -25684,7 +23440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -26091,42 +23847,6 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="46" hidden="0" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>細菌怎麼害人，我們怎麼對付它</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/micro-bacteria-review-v1/index.html；單元＝次單元＝細菌怎麼害人，我們怎麼對付它；6 先備＋5 情境；教師核可 2026-10-11，待部署</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="46" hidden="0" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>從小安的第一年認識免疫</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/immuno-concepts-review-v1/index.html；單元＝次單元＝從小安的第一年認識免疫；6 先備＋5 情境；教師核可 2026-10-11，待部署</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="46" hidden="0" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>合計（2026-10-11）</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>249 題（既有 227＋本次 22）；前方歷史合計列保留不改</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X228"/>
+  <dimension ref="A1:X305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23424,6 +23424,5242 @@
       </c>
       <c r="X228" s="3"/>
     </row>
+    <row r="229" ht="166" customHeight="1">
+      <c r="A229" s="3"/>
+      <c r="B229" s="4" t="str">
+        <v>airway-structure-foundation-q01</v>
+      </c>
+      <c r="C229" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D229" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G229" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H229" s="5" t="str">
+        <v>鼻咽與口咽的分界參考構造？</v>
+      </c>
+      <c r="I229" s="5" t="str">
+        <v>軟腭</v>
+      </c>
+      <c r="J229" s="5" t="str">
+        <v>會厭</v>
+      </c>
+      <c r="K229" s="5" t="str">
+        <v>聲帶</v>
+      </c>
+      <c r="L229" s="5" t="str">
+        <v>環狀軟骨</v>
+      </c>
+      <c r="M229" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N229" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" s="5" t="str">
+        <v>軟腭是區分鼻咽與口咽的參考邊界。</v>
+      </c>
+      <c r="P229" s="5" t="str">
+        <v>比較鼻腔後方與口腔後方的分界。</v>
+      </c>
+      <c r="Q229" s="5" t="str">
+        <v>比較鼻腔後方與口腔後方的分界。 → 鼻咽與口咽的分界參考構造？</v>
+      </c>
+      <c r="R229" s="5" t="str">
+        <v>選擇「軟腭」。軟腭是區分鼻咽與口咽的參考邊界。</v>
+      </c>
+      <c r="S229" s="5" t="str">
+        <v>軟腭是區分鼻咽與口咽的參考邊界。</v>
+      </c>
+      <c r="T229" s="3" t="str">
+        <v>pharynx-divisions；AB-05_13 p.3–5</v>
+      </c>
+      <c r="U229" s="3"/>
+      <c r="V229" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W229" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X229" s="3"/>
+    </row>
+    <row r="230" ht="166" customHeight="1">
+      <c r="A230" s="3"/>
+      <c r="B230" s="4" t="str">
+        <v>airway-structure-foundation-q02</v>
+      </c>
+      <c r="C230" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D230" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F230" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G230" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H230" s="5" t="str">
+        <v>耳咽管連通哪兩處？</v>
+      </c>
+      <c r="I230" s="5" t="str">
+        <v>口咽與外耳道</v>
+      </c>
+      <c r="J230" s="5" t="str">
+        <v>鼻咽與中耳</v>
+      </c>
+      <c r="K230" s="5" t="str">
+        <v>喉咽與中耳</v>
+      </c>
+      <c r="L230" s="5" t="str">
+        <v>鼻腔與內耳</v>
+      </c>
+      <c r="M230" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N230" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O230" s="5" t="str">
+        <v>耳咽管開口在鼻咽，連通中耳；它不連到外耳道。</v>
+      </c>
+      <c r="P230" s="5" t="str">
+        <v>從鼓膜兩側的壓力平衡思考通路。</v>
+      </c>
+      <c r="Q230" s="5" t="str">
+        <v>從鼓膜兩側的壓力平衡思考通路。 → 耳咽管連通哪兩處？</v>
+      </c>
+      <c r="R230" s="5" t="str">
+        <v>選擇「鼻咽與中耳」。耳咽管開口在鼻咽，連通中耳；它不連到外耳道。</v>
+      </c>
+      <c r="S230" s="5" t="str">
+        <v>耳咽管開口在鼻咽，連通中耳；它不連到外耳道。</v>
+      </c>
+      <c r="T230" s="3" t="str">
+        <v>auditory-tube；p.3–4</v>
+      </c>
+      <c r="U230" s="3"/>
+      <c r="V230" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W230" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X230" s="3"/>
+    </row>
+    <row r="231" ht="166" customHeight="1">
+      <c r="A231" s="3"/>
+      <c r="B231" s="4" t="str">
+        <v>airway-structure-foundation-q03</v>
+      </c>
+      <c r="C231" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D231" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F231" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G231" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H231" s="5" t="str">
+        <v>喉結由哪塊軟骨形成？</v>
+      </c>
+      <c r="I231" s="5" t="str">
+        <v>環狀軟骨</v>
+      </c>
+      <c r="J231" s="5" t="str">
+        <v>會厭軟骨</v>
+      </c>
+      <c r="K231" s="5" t="str">
+        <v>甲狀軟骨</v>
+      </c>
+      <c r="L231" s="5" t="str">
+        <v>杓狀軟骨</v>
+      </c>
+      <c r="M231" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N231" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O231" s="5" t="str">
+        <v>甲狀軟骨形成喉結；它屬於單一的喉軟骨。</v>
+      </c>
+      <c r="P231" s="5" t="str">
+        <v>找出構成頸前突出輪廓的單一軟骨。</v>
+      </c>
+      <c r="Q231" s="5" t="str">
+        <v>找出構成頸前突出輪廓的單一軟骨。 → 喉結由哪塊軟骨形成？</v>
+      </c>
+      <c r="R231" s="5" t="str">
+        <v>選擇「甲狀軟骨」。甲狀軟骨形成喉結；它屬於單一的喉軟骨。</v>
+      </c>
+      <c r="S231" s="5" t="str">
+        <v>甲狀軟骨形成喉結；它屬於單一的喉軟骨。</v>
+      </c>
+      <c r="T231" s="3" t="str">
+        <v>laryngeal-cartilage；p.4–5, 20–21</v>
+      </c>
+      <c r="U231" s="3"/>
+      <c r="V231" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W231" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X231" s="3"/>
+    </row>
+    <row r="232" ht="166" customHeight="1">
+      <c r="A232" s="3"/>
+      <c r="B232" s="4" t="str">
+        <v>airway-structure-foundation-q04</v>
+      </c>
+      <c r="C232" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D232" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F232" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G232" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H232" s="5" t="str">
+        <v>與聲帶相連、參與發聲的成對軟骨？</v>
+      </c>
+      <c r="I232" s="5" t="str">
+        <v>甲狀軟骨</v>
+      </c>
+      <c r="J232" s="5" t="str">
+        <v>會厭軟骨</v>
+      </c>
+      <c r="K232" s="5" t="str">
+        <v>環狀軟骨</v>
+      </c>
+      <c r="L232" s="5" t="str">
+        <v>杓狀軟骨</v>
+      </c>
+      <c r="M232" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N232" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O232" s="5" t="str">
+        <v>杓狀軟骨與聲帶相連並參與發聲；會厭主要保護吞嚥時的喉入口。</v>
+      </c>
+      <c r="P232" s="5" t="str">
+        <v>區分發聲連接構造與吞嚥保護構造。</v>
+      </c>
+      <c r="Q232" s="5" t="str">
+        <v>區分發聲連接構造與吞嚥保護構造。 → 與聲帶相連、參與發聲的成對軟骨？</v>
+      </c>
+      <c r="R232" s="5" t="str">
+        <v>選擇「杓狀軟骨」。杓狀軟骨與聲帶相連並參與發聲；會厭主要保護吞嚥時的喉入口。</v>
+      </c>
+      <c r="S232" s="5" t="str">
+        <v>杓狀軟骨與聲帶相連並參與發聲；會厭主要保護吞嚥時的喉入口。</v>
+      </c>
+      <c r="T232" s="3" t="str">
+        <v>laryngeal-cartilage；p.4–5, 20–21</v>
+      </c>
+      <c r="U232" s="3"/>
+      <c r="V232" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W232" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X232" s="3"/>
+    </row>
+    <row r="233" ht="166" customHeight="1">
+      <c r="A233" s="3"/>
+      <c r="B233" s="4" t="str">
+        <v>airway-structure-foundation-q05</v>
+      </c>
+      <c r="C233" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D233" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F233" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G233" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H233" s="5" t="str">
+        <v>氣管內襯的上皮？</v>
+      </c>
+      <c r="I233" s="5" t="str">
+        <v>偽複層纖毛柱狀上皮</v>
+      </c>
+      <c r="J233" s="5" t="str">
+        <v>單層鱗狀上皮</v>
+      </c>
+      <c r="K233" s="5" t="str">
+        <v>複層鱗狀上皮</v>
+      </c>
+      <c r="L233" s="5" t="str">
+        <v>單層立方上皮</v>
+      </c>
+      <c r="M233" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" s="5" t="str">
+        <v>氣管內襯偽複層纖毛柱狀上皮；纖毛與杯狀細胞的黏液協同清潔空氣。</v>
+      </c>
+      <c r="P233" s="5" t="str">
+        <v>想想黏液要靠什麼構造往外移動。</v>
+      </c>
+      <c r="Q233" s="5" t="str">
+        <v>想想黏液要靠什麼構造往外移動。 → 氣管內襯的上皮？</v>
+      </c>
+      <c r="R233" s="5" t="str">
+        <v>選擇「偽複層纖毛柱狀上皮」。氣管內襯偽複層纖毛柱狀上皮；纖毛與杯狀細胞的黏液協同清潔空氣。</v>
+      </c>
+      <c r="S233" s="5" t="str">
+        <v>氣管內襯偽複層纖毛柱狀上皮；纖毛與杯狀細胞的黏液協同清潔空氣。</v>
+      </c>
+      <c r="T233" s="3" t="str">
+        <v>trachea；p.8–10</v>
+      </c>
+      <c r="U233" s="3"/>
+      <c r="V233" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W233" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X233" s="3"/>
+    </row>
+    <row r="234" ht="166" customHeight="1">
+      <c r="A234" s="3"/>
+      <c r="B234" s="4" t="str">
+        <v>airway-structure-foundation-q06</v>
+      </c>
+      <c r="C234" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D234" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F234" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G234" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H234" s="5" t="str">
+        <v>右主支氣管與左主支氣管相比？</v>
+      </c>
+      <c r="I234" s="5" t="str">
+        <v>較長、較窄且較水平</v>
+      </c>
+      <c r="J234" s="5" t="str">
+        <v>較短、較寬且較垂直</v>
+      </c>
+      <c r="K234" s="5" t="str">
+        <v>較短、較窄且較水平</v>
+      </c>
+      <c r="L234" s="5" t="str">
+        <v>兩側完全相同</v>
+      </c>
+      <c r="M234" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N234" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O234" s="5" t="str">
+        <v>右主支氣管較短、較寬且較垂直，與中線的夾角較小。</v>
+      </c>
+      <c r="P234" s="5" t="str">
+        <v>從管徑、長度與中線夾角比較兩側。</v>
+      </c>
+      <c r="Q234" s="5" t="str">
+        <v>從管徑、長度與中線夾角比較兩側。 → 右主支氣管與左主支氣管相比？</v>
+      </c>
+      <c r="R234" s="5" t="str">
+        <v>選擇「較短、較寬且較垂直」。右主支氣管較短、較寬且較垂直，與中線的夾角較小。</v>
+      </c>
+      <c r="S234" s="5" t="str">
+        <v>右主支氣管較短、較寬且較垂直，與中線的夾角較小。</v>
+      </c>
+      <c r="T234" s="3" t="str">
+        <v>right-left-main-bronchi、bronchial-tree、airway-histology；AB-05_13 p.10–11</v>
+      </c>
+      <c r="U234" s="3"/>
+      <c r="V234" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W234" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X234" s="3"/>
+    </row>
+    <row r="235" ht="166" customHeight="1">
+      <c r="A235" s="3"/>
+      <c r="B235" s="4" t="str">
+        <v>airway-structure-case-q01</v>
+      </c>
+      <c r="C235" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D235" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F235" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G235" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H235" s="5" t="str">
+        <v>【生活情境】搭飛機下降時耳朵悶脹，吞口水後改善，是哪個構造平衡了中耳壓力？</v>
+      </c>
+      <c r="I235" s="5" t="str">
+        <v>氣管</v>
+      </c>
+      <c r="J235" s="5" t="str">
+        <v>會厭</v>
+      </c>
+      <c r="K235" s="5" t="str">
+        <v>耳咽管</v>
+      </c>
+      <c r="L235" s="5" t="str">
+        <v>鼻腔</v>
+      </c>
+      <c r="M235" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N235" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O235" s="5" t="str">
+        <v>耳咽管連通鼻咽與中耳，使鼓膜兩側壓力較能平衡。</v>
+      </c>
+      <c r="P235" s="5" t="str">
+        <v>吞嚥後耳悶改善，先找連通中耳的通道。</v>
+      </c>
+      <c r="Q235" s="5" t="str">
+        <v>吞嚥後耳悶改善，先找連通中耳的通道。 → 【生活情境】搭飛機下降時耳朵悶脹，吞口水後改善，是哪個構造平衡了中耳壓力？</v>
+      </c>
+      <c r="R235" s="5" t="str">
+        <v>選擇「耳咽管」。耳咽管連通鼻咽與中耳，使鼓膜兩側壓力較能平衡。</v>
+      </c>
+      <c r="S235" s="5" t="str">
+        <v>耳咽管連通鼻咽與中耳，使鼓膜兩側壓力較能平衡。</v>
+      </c>
+      <c r="T235" s="3" t="str">
+        <v>auditory-tube；p.3–4</v>
+      </c>
+      <c r="U235" s="3"/>
+      <c r="V235" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W235" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X235" s="3"/>
+    </row>
+    <row r="236" ht="166" customHeight="1">
+      <c r="A236" s="3"/>
+      <c r="B236" s="4" t="str">
+        <v>airway-structure-case-q02</v>
+      </c>
+      <c r="C236" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D236" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F236" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G236" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H236" s="5" t="str">
+        <v>【生理判讀】吞嚥時食物沒有誤入氣管，主要因為？</v>
+      </c>
+      <c r="I236" s="5" t="str">
+        <v>聲帶完全打開</v>
+      </c>
+      <c r="J236" s="5" t="str">
+        <v>氣管軟骨環關閉</v>
+      </c>
+      <c r="K236" s="5" t="str">
+        <v>耳咽管關閉</v>
+      </c>
+      <c r="L236" s="5" t="str">
+        <v>喉上提、會厭蓋住喉入口</v>
+      </c>
+      <c r="M236" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N236" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O236" s="5" t="str">
+        <v>吞嚥時喉上提，會厭蓋住喉入口，防止食物誤入氣管。</v>
+      </c>
+      <c r="P236" s="5" t="str">
+        <v>觀察吞嚥時喉的位置與入口如何改變。</v>
+      </c>
+      <c r="Q236" s="5" t="str">
+        <v>觀察吞嚥時喉的位置與入口如何改變。 → 【生理判讀】吞嚥時食物沒有誤入氣管，主要因為？</v>
+      </c>
+      <c r="R236" s="5" t="str">
+        <v>選擇「喉上提、會厭蓋住喉入口」。吞嚥時喉上提，會厭蓋住喉入口，防止食物誤入氣管。</v>
+      </c>
+      <c r="S236" s="5" t="str">
+        <v>吞嚥時喉上提，會厭蓋住喉入口，防止食物誤入氣管。</v>
+      </c>
+      <c r="T236" s="3" t="str">
+        <v>laryngeal-cartilage；p.4–5, 20–21</v>
+      </c>
+      <c r="U236" s="3"/>
+      <c r="V236" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W236" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X236" s="3"/>
+    </row>
+    <row r="237" ht="166" customHeight="1">
+      <c r="A237" s="3"/>
+      <c r="B237" s="4" t="str">
+        <v>airway-structure-case-q03</v>
+      </c>
+      <c r="C237" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D237" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F237" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G237" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H237" s="5" t="str">
+        <v>【模型觀察】氣管 C 形軟骨環的缺口朝向？</v>
+      </c>
+      <c r="I237" s="5" t="str">
+        <v>後方的食道</v>
+      </c>
+      <c r="J237" s="5" t="str">
+        <v>前方的胸骨</v>
+      </c>
+      <c r="K237" s="5" t="str">
+        <v>左側的心臟</v>
+      </c>
+      <c r="L237" s="5" t="str">
+        <v>右側的肺</v>
+      </c>
+      <c r="M237" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N237" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" s="5" t="str">
+        <v>氣管在食道前方，C 形軟骨環的缺口朝向後方食道。</v>
+      </c>
+      <c r="P237" s="5" t="str">
+        <v>先確認氣管與食道的前後位置。</v>
+      </c>
+      <c r="Q237" s="5" t="str">
+        <v>先確認氣管與食道的前後位置。 → 【模型觀察】氣管 C 形軟骨環的缺口朝向？</v>
+      </c>
+      <c r="R237" s="5" t="str">
+        <v>選擇「後方的食道」。氣管在食道前方，C 形軟骨環的缺口朝向後方食道。</v>
+      </c>
+      <c r="S237" s="5" t="str">
+        <v>氣管在食道前方，C 形軟骨環的缺口朝向後方食道。</v>
+      </c>
+      <c r="T237" s="3" t="str">
+        <v>trachea；p.8–10</v>
+      </c>
+      <c r="U237" s="3"/>
+      <c r="V237" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W237" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X237" s="3"/>
+    </row>
+    <row r="238" ht="166" customHeight="1">
+      <c r="A238" s="3"/>
+      <c r="B238" s="4" t="str">
+        <v>airway-structure-case-q04</v>
+      </c>
+      <c r="C238" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D238" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F238" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G238" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H238" s="5" t="str">
+        <v>【生活情境】小孩吃花生時嗆到，吸入的花生較容易卡在哪裡？</v>
+      </c>
+      <c r="I238" s="5" t="str">
+        <v>左主支氣管，因其較寬</v>
+      </c>
+      <c r="J238" s="5" t="str">
+        <v>右主支氣管，因其較短、寬且垂直</v>
+      </c>
+      <c r="K238" s="5" t="str">
+        <v>氣管上段，因其最窄</v>
+      </c>
+      <c r="L238" s="5" t="str">
+        <v>食道，因其在氣管後方</v>
+      </c>
+      <c r="M238" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N238" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O238" s="5" t="str">
+        <v>右主支氣管較短、寬且垂直，因此吸入的異物較容易卡住右側。</v>
+      </c>
+      <c r="P238" s="5" t="str">
+        <v>沿吸入方向比較左右主支氣管的形狀。</v>
+      </c>
+      <c r="Q238" s="5" t="str">
+        <v>沿吸入方向比較左右主支氣管的形狀。 → 【生活情境】小孩吃花生時嗆到，吸入的花生較容易卡在哪裡？</v>
+      </c>
+      <c r="R238" s="5" t="str">
+        <v>選擇「右主支氣管，因其較短、寬且垂直」。右主支氣管較短、寬且垂直，因此吸入的異物較容易卡住右側。</v>
+      </c>
+      <c r="S238" s="5" t="str">
+        <v>右主支氣管較短、寬且垂直，因此吸入的異物較容易卡住右側。</v>
+      </c>
+      <c r="T238" s="3" t="str">
+        <v>right-left-main-bronchi、bronchial-tree、airway-histology；AB-05_13 p.10–11</v>
+      </c>
+      <c r="U238" s="3"/>
+      <c r="V238" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W238" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X238" s="3"/>
+    </row>
+    <row r="239" ht="166" customHeight="1">
+      <c r="A239" s="3"/>
+      <c r="B239" s="4" t="str">
+        <v>airway-structure-case-q05</v>
+      </c>
+      <c r="C239" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D239" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F239" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G239" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H239" s="5" t="str">
+        <v>【模型觀察】沿支氣管樹往下，軟骨與平滑肌的變化？</v>
+      </c>
+      <c r="I239" s="5" t="str">
+        <v>軟骨越來越多</v>
+      </c>
+      <c r="J239" s="5" t="str">
+        <v>兩者都不變</v>
+      </c>
+      <c r="K239" s="5" t="str">
+        <v>軟骨漸少、細支氣管已無軟骨且平滑肌較多</v>
+      </c>
+      <c r="L239" s="5" t="str">
+        <v>平滑肌消失只剩軟骨</v>
+      </c>
+      <c r="M239" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N239" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O239" s="5" t="str">
+        <v>越往下軟骨越少；細支氣管已無軟骨，但平滑肌較多。</v>
+      </c>
+      <c r="P239" s="5" t="str">
+        <v>依主支氣管到終末細支氣管的順序比較管壁。</v>
+      </c>
+      <c r="Q239" s="5" t="str">
+        <v>依主支氣管到終末細支氣管的順序比較管壁。 → 【模型觀察】沿支氣管樹往下，軟骨與平滑肌的變化？</v>
+      </c>
+      <c r="R239" s="5" t="str">
+        <v>選擇「軟骨漸少、細支氣管已無軟骨且平滑肌較多」。越往下軟骨越少；細支氣管已無軟骨，但平滑肌較多。</v>
+      </c>
+      <c r="S239" s="5" t="str">
+        <v>越往下軟骨越少；細支氣管已無軟骨，但平滑肌較多。</v>
+      </c>
+      <c r="T239" s="3" t="str">
+        <v>right-left-main-bronchi、bronchial-tree、airway-histology；AB-05_13 p.10–11</v>
+      </c>
+      <c r="U239" s="3"/>
+      <c r="V239" s="5" t="str">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="W239" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/airway-structure-v1/index.html</v>
+      </c>
+      <c r="X239" s="3"/>
+    </row>
+    <row r="240" ht="166" customHeight="1">
+      <c r="A240" s="3"/>
+      <c r="B240" s="4" t="str">
+        <v>lungs-pleura-foundation-q01</v>
+      </c>
+      <c r="C240" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D240" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G240" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H240" s="5" t="str">
+        <v>右肺的分葉？</v>
+      </c>
+      <c r="I240" s="5" t="str">
+        <v>兩葉，以斜裂分隔</v>
+      </c>
+      <c r="J240" s="5" t="str">
+        <v>三葉，只以水平裂分隔</v>
+      </c>
+      <c r="K240" s="5" t="str">
+        <v>兩葉，以水平裂分隔</v>
+      </c>
+      <c r="L240" s="5" t="str">
+        <v>三葉，以水平裂與斜裂分隔</v>
+      </c>
+      <c r="M240" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N240" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O240" s="5" t="str">
+        <v>右肺由水平裂與斜裂分成上、中、下三葉。</v>
+      </c>
+      <c r="P240" s="5" t="str">
+        <v>數右肺的裂線，再看分成幾個區域。</v>
+      </c>
+      <c r="Q240" s="5" t="str">
+        <v>數右肺的裂線，再看分成幾個區域。 → 右肺的分葉？</v>
+      </c>
+      <c r="R240" s="5" t="str">
+        <v>選擇「三葉，以水平裂與斜裂分隔」。右肺由水平裂與斜裂分成上、中、下三葉。</v>
+      </c>
+      <c r="S240" s="5" t="str">
+        <v>右肺由水平裂與斜裂分成上、中、下三葉。</v>
+      </c>
+      <c r="T240" s="3" t="str">
+        <v>lung-lobes；AB-05_13 p.7–8</v>
+      </c>
+      <c r="U240" s="3"/>
+      <c r="V240" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W240" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X240" s="3"/>
+    </row>
+    <row r="241" ht="166" customHeight="1">
+      <c r="A241" s="3"/>
+      <c r="B241" s="4" t="str">
+        <v>lungs-pleura-foundation-q02</v>
+      </c>
+      <c r="C241" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D241" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G241" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H241" s="5" t="str">
+        <v>心切跡位於？</v>
+      </c>
+      <c r="I241" s="5" t="str">
+        <v>左肺前緣</v>
+      </c>
+      <c r="J241" s="5" t="str">
+        <v>右肺前緣</v>
+      </c>
+      <c r="K241" s="5" t="str">
+        <v>右肺底</v>
+      </c>
+      <c r="L241" s="5" t="str">
+        <v>左肺尖</v>
+      </c>
+      <c r="M241" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" s="5" t="str">
+        <v>心切跡位於左肺前緣；左肺只有上、下兩葉。</v>
+      </c>
+      <c r="P241" s="5" t="str">
+        <v>從左右肺的前緣找凹口。</v>
+      </c>
+      <c r="Q241" s="5" t="str">
+        <v>從左右肺的前緣找凹口。 → 心切跡位於？</v>
+      </c>
+      <c r="R241" s="5" t="str">
+        <v>選擇「左肺前緣」。心切跡位於左肺前緣；左肺只有上、下兩葉。</v>
+      </c>
+      <c r="S241" s="5" t="str">
+        <v>心切跡位於左肺前緣；左肺只有上、下兩葉。</v>
+      </c>
+      <c r="T241" s="3" t="str">
+        <v>lung-lobes；AB-05_13 p.7–8</v>
+      </c>
+      <c r="U241" s="3"/>
+      <c r="V241" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W241" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X241" s="3"/>
+    </row>
+    <row r="242" ht="166" customHeight="1">
+      <c r="A242" s="3"/>
+      <c r="B242" s="4" t="str">
+        <v>lungs-pleura-foundation-q03</v>
+      </c>
+      <c r="C242" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D242" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F242" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G242" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H242" s="5" t="str">
+        <v>覆蓋在肺表面的胸膜？</v>
+      </c>
+      <c r="I242" s="5" t="str">
+        <v>壁層胸膜</v>
+      </c>
+      <c r="J242" s="5" t="str">
+        <v>臟層胸膜</v>
+      </c>
+      <c r="K242" s="5" t="str">
+        <v>縱膈</v>
+      </c>
+      <c r="L242" s="5" t="str">
+        <v>橫膈</v>
+      </c>
+      <c r="M242" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N242" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O242" s="5" t="str">
+        <v>臟層胸膜覆蓋肺表面，壁層胸膜貼胸腔壁。</v>
+      </c>
+      <c r="P242" s="5" t="str">
+        <v>分清貼肺表面與貼胸腔壁的兩層。</v>
+      </c>
+      <c r="Q242" s="5" t="str">
+        <v>分清貼肺表面與貼胸腔壁的兩層。 → 覆蓋在肺表面的胸膜？</v>
+      </c>
+      <c r="R242" s="5" t="str">
+        <v>選擇「臟層胸膜」。臟層胸膜覆蓋肺表面，壁層胸膜貼胸腔壁。</v>
+      </c>
+      <c r="S242" s="5" t="str">
+        <v>臟層胸膜覆蓋肺表面，壁層胸膜貼胸腔壁。</v>
+      </c>
+      <c r="T242" s="3" t="str">
+        <v>pleura；AB-05_13 p.8；CH06 p.6, 8–9</v>
+      </c>
+      <c r="U242" s="3"/>
+      <c r="V242" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W242" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X242" s="3"/>
+    </row>
+    <row r="243" ht="166" customHeight="1">
+      <c r="A243" s="3"/>
+      <c r="B243" s="4" t="str">
+        <v>lungs-pleura-foundation-q04</v>
+      </c>
+      <c r="C243" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D243" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F243" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G243" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H243" s="5" t="str">
+        <v>構成肺泡壁連續內襯、參與氣體交換的是？</v>
+      </c>
+      <c r="I243" s="5" t="str">
+        <v>第二型肺泡細胞</v>
+      </c>
+      <c r="J243" s="5" t="str">
+        <v>肺泡巨噬細胞</v>
+      </c>
+      <c r="K243" s="5" t="str">
+        <v>第一型肺泡細胞</v>
+      </c>
+      <c r="L243" s="5" t="str">
+        <v>杯狀細胞</v>
+      </c>
+      <c r="M243" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N243" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O243" s="5" t="str">
+        <v>第一型肺泡細胞是單層鱗狀上皮，構成連續內襯並參與氣體交換。</v>
+      </c>
+      <c r="P243" s="5" t="str">
+        <v>氣體交換需要薄而連續的肺泡內襯。</v>
+      </c>
+      <c r="Q243" s="5" t="str">
+        <v>氣體交換需要薄而連續的肺泡內襯。 → 構成肺泡壁連續內襯、參與氣體交換的是？</v>
+      </c>
+      <c r="R243" s="5" t="str">
+        <v>選擇「第一型肺泡細胞」。第一型肺泡細胞是單層鱗狀上皮，構成連續內襯並參與氣體交換。</v>
+      </c>
+      <c r="S243" s="5" t="str">
+        <v>第一型肺泡細胞是單層鱗狀上皮，構成連續內襯並參與氣體交換。</v>
+      </c>
+      <c r="T243" s="3" t="str">
+        <v>alveolar-cells；AB-05_13 p.11；CH06 p.19</v>
+      </c>
+      <c r="U243" s="3"/>
+      <c r="V243" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W243" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X243" s="3"/>
+    </row>
+    <row r="244" ht="166" customHeight="1">
+      <c r="A244" s="3"/>
+      <c r="B244" s="4" t="str">
+        <v>lungs-pleura-foundation-q05</v>
+      </c>
+      <c r="C244" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D244" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F244" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G244" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H244" s="5" t="str">
+        <v>分泌表面張力素的是？</v>
+      </c>
+      <c r="I244" s="5" t="str">
+        <v>第一型肺泡細胞</v>
+      </c>
+      <c r="J244" s="5" t="str">
+        <v>肺泡巨噬細胞</v>
+      </c>
+      <c r="K244" s="5" t="str">
+        <v>微血管內皮細胞</v>
+      </c>
+      <c r="L244" s="5" t="str">
+        <v>第二型肺泡細胞</v>
+      </c>
+      <c r="M244" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N244" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O244" s="5" t="str">
+        <v>第二型肺泡細胞分泌表面張力素；第一型參與交換，巨噬細胞負責清除。</v>
+      </c>
+      <c r="P244" s="5" t="str">
+        <v>將分泌功能與氣體交換、清除功能分開。</v>
+      </c>
+      <c r="Q244" s="5" t="str">
+        <v>將分泌功能與氣體交換、清除功能分開。 → 分泌表面張力素的是？</v>
+      </c>
+      <c r="R244" s="5" t="str">
+        <v>選擇「第二型肺泡細胞」。第二型肺泡細胞分泌表面張力素；第一型參與交換，巨噬細胞負責清除。</v>
+      </c>
+      <c r="S244" s="5" t="str">
+        <v>第二型肺泡細胞分泌表面張力素；第一型參與交換，巨噬細胞負責清除。</v>
+      </c>
+      <c r="T244" s="3" t="str">
+        <v>alveolar-cells；AB-05_13 p.11；CH06 p.19</v>
+      </c>
+      <c r="U244" s="3"/>
+      <c r="V244" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W244" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X244" s="3"/>
+    </row>
+    <row r="245" ht="166" customHeight="1">
+      <c r="A245" s="3"/>
+      <c r="B245" s="4" t="str">
+        <v>lungs-pleura-foundation-q06</v>
+      </c>
+      <c r="C245" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D245" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F245" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G245" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H245" s="5" t="str">
+        <v>呼吸膜不包括？</v>
+      </c>
+      <c r="I245" s="5" t="str">
+        <v>第二型肺泡細胞</v>
+      </c>
+      <c r="J245" s="5" t="str">
+        <v>第一型肺泡細胞</v>
+      </c>
+      <c r="K245" s="5" t="str">
+        <v>微血管內皮細胞</v>
+      </c>
+      <c r="L245" s="5" t="str">
+        <v>基底膜</v>
+      </c>
+      <c r="M245" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" s="5" t="str">
+        <v>呼吸膜包括第一型細胞、基底膜、間質與微血管內皮；第二型細胞不在這個薄層序列中。</v>
+      </c>
+      <c r="P245" s="5" t="str">
+        <v>沿肺泡到微血管列出薄層的順序。</v>
+      </c>
+      <c r="Q245" s="5" t="str">
+        <v>沿肺泡到微血管列出薄層的順序。 → 呼吸膜不包括？</v>
+      </c>
+      <c r="R245" s="5" t="str">
+        <v>選擇「第二型肺泡細胞」。呼吸膜包括第一型細胞、基底膜、間質與微血管內皮；第二型細胞不在這個薄層序列中。</v>
+      </c>
+      <c r="S245" s="5" t="str">
+        <v>呼吸膜包括第一型細胞、基底膜、間質與微血管內皮；第二型細胞不在這個薄層序列中。</v>
+      </c>
+      <c r="T245" s="3" t="str">
+        <v>respiratory-membrane；CH06 p.19–21</v>
+      </c>
+      <c r="U245" s="3"/>
+      <c r="V245" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W245" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X245" s="3"/>
+    </row>
+    <row r="246" ht="166" customHeight="1">
+      <c r="A246" s="3"/>
+      <c r="B246" s="4" t="str">
+        <v>lungs-pleura-case-q01</v>
+      </c>
+      <c r="C246" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D246" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F246" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G246" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H246" s="5" t="str">
+        <v>【模型觀察】依 P＝2T/r，表面張力相同時哪顆肺泡較易塌陷？</v>
+      </c>
+      <c r="I246" s="5" t="str">
+        <v>半徑較大的肺泡</v>
+      </c>
+      <c r="J246" s="5" t="str">
+        <v>半徑較小的肺泡</v>
+      </c>
+      <c r="K246" s="5" t="str">
+        <v>兩者一樣</v>
+      </c>
+      <c r="L246" s="5" t="str">
+        <v>與半徑無關</v>
+      </c>
+      <c r="M246" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N246" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O246" s="5" t="str">
+        <v>P＝2T/r；張力相同時半徑越小所需壓力越大，較易塌陷。</v>
+      </c>
+      <c r="P246" s="5" t="str">
+        <v>在張力固定時，看半徑在公式的分子還是分母。</v>
+      </c>
+      <c r="Q246" s="5" t="str">
+        <v>在張力固定時，看半徑在公式的分子還是分母。 → 【模型觀察】依 P＝2T/r，表面張力相同時哪顆肺泡較易塌陷？</v>
+      </c>
+      <c r="R246" s="5" t="str">
+        <v>選擇「半徑較小的肺泡」。P＝2T/r；張力相同時半徑越小所需壓力越大，較易塌陷。</v>
+      </c>
+      <c r="S246" s="5" t="str">
+        <v>P＝2T/r；張力相同時半徑越小所需壓力越大，較易塌陷。</v>
+      </c>
+      <c r="T246" s="3" t="str">
+        <v>surfactant、ards；CH06 p.19–20</v>
+      </c>
+      <c r="U246" s="3"/>
+      <c r="V246" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W246" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X246" s="3"/>
+    </row>
+    <row r="247" ht="166" customHeight="1">
+      <c r="A247" s="3"/>
+      <c r="B247" s="4" t="str">
+        <v>lungs-pleura-case-q02</v>
+      </c>
+      <c r="C247" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D247" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F247" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G247" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H247" s="5" t="str">
+        <v>【生理判讀】早產兒呼吸困難，最可能與哪種細胞分泌不足有關？</v>
+      </c>
+      <c r="I247" s="5" t="str">
+        <v>第一型肺泡細胞</v>
+      </c>
+      <c r="J247" s="5" t="str">
+        <v>肺泡巨噬細胞</v>
+      </c>
+      <c r="K247" s="5" t="str">
+        <v>第二型肺泡細胞</v>
+      </c>
+      <c r="L247" s="5" t="str">
+        <v>纖毛柱狀細胞</v>
+      </c>
+      <c r="M247" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N247" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O247" s="5" t="str">
+        <v>表面張力素降低張力，幫助肺泡擴張與維持；不足時塌陷傾向增加。</v>
+      </c>
+      <c r="P247" s="5" t="str">
+        <v>先想表面張力素不足會如何影響肺泡擴張。</v>
+      </c>
+      <c r="Q247" s="5" t="str">
+        <v>先想表面張力素不足會如何影響肺泡擴張。 → 【生理判讀】早產兒呼吸困難，最可能與哪種細胞分泌不足有關？</v>
+      </c>
+      <c r="R247" s="5" t="str">
+        <v>選擇「第二型肺泡細胞」。表面張力素降低張力，幫助肺泡擴張與維持；不足時塌陷傾向增加。</v>
+      </c>
+      <c r="S247" s="5" t="str">
+        <v>表面張力素降低張力，幫助肺泡擴張與維持；不足時塌陷傾向增加。</v>
+      </c>
+      <c r="T247" s="3" t="str">
+        <v>surfactant、ards；CH06 p.19–20</v>
+      </c>
+      <c r="U247" s="3"/>
+      <c r="V247" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W247" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X247" s="3"/>
+    </row>
+    <row r="248" ht="166" customHeight="1">
+      <c r="A248" s="3"/>
+      <c r="B248" s="4" t="str">
+        <v>lungs-pleura-case-q03</v>
+      </c>
+      <c r="C248" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D248" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F248" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G248" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H248" s="5" t="str">
+        <v>【生理判讀】肺纖維化使呼吸膜變厚，最直接的影響？</v>
+      </c>
+      <c r="I248" s="5" t="str">
+        <v>氣體擴散加快</v>
+      </c>
+      <c r="J248" s="5" t="str">
+        <v>肺葉數目減少</v>
+      </c>
+      <c r="K248" s="5" t="str">
+        <v>表面張力素增加</v>
+      </c>
+      <c r="L248" s="5" t="str">
+        <v>氣體擴散變慢</v>
+      </c>
+      <c r="M248" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N248" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O248" s="5" t="str">
+        <v>呼吸膜薄且面積廣利於擴散；膜變厚會使氣體擴散變慢。</v>
+      </c>
+      <c r="P248" s="5" t="str">
+        <v>比較薄膜與厚膜的擴散條件。</v>
+      </c>
+      <c r="Q248" s="5" t="str">
+        <v>比較薄膜與厚膜的擴散條件。 → 【生理判讀】肺纖維化使呼吸膜變厚，最直接的影響？</v>
+      </c>
+      <c r="R248" s="5" t="str">
+        <v>選擇「氣體擴散變慢」。呼吸膜薄且面積廣利於擴散；膜變厚會使氣體擴散變慢。</v>
+      </c>
+      <c r="S248" s="5" t="str">
+        <v>呼吸膜薄且面積廣利於擴散；膜變厚會使氣體擴散變慢。</v>
+      </c>
+      <c r="T248" s="3" t="str">
+        <v>respiratory-membrane；CH06 p.19–21</v>
+      </c>
+      <c r="U248" s="3"/>
+      <c r="V248" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W248" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X248" s="3"/>
+    </row>
+    <row r="249" ht="166" customHeight="1">
+      <c r="A249" s="3"/>
+      <c r="B249" s="4" t="str">
+        <v>lungs-pleura-case-q04</v>
+      </c>
+      <c r="C249" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D249" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F249" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G249" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H249" s="5" t="str">
+        <v>【模型觀察】吸入的灰塵到達肺泡後，主要由誰清除？</v>
+      </c>
+      <c r="I249" s="5" t="str">
+        <v>肺泡巨噬細胞</v>
+      </c>
+      <c r="J249" s="5" t="str">
+        <v>第二型肺泡細胞</v>
+      </c>
+      <c r="K249" s="5" t="str">
+        <v>第一型肺泡細胞</v>
+      </c>
+      <c r="L249" s="5" t="str">
+        <v>紅血球</v>
+      </c>
+      <c r="M249" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N249" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O249" s="5" t="str">
+        <v>肺泡巨噬細胞清除肺泡內的灰塵與碎片。</v>
+      </c>
+      <c r="P249" s="5" t="str">
+        <v>分清肺泡壁細胞與腔內清除細胞的功能。</v>
+      </c>
+      <c r="Q249" s="5" t="str">
+        <v>分清肺泡壁細胞與腔內清除細胞的功能。 → 【模型觀察】吸入的灰塵到達肺泡後，主要由誰清除？</v>
+      </c>
+      <c r="R249" s="5" t="str">
+        <v>選擇「肺泡巨噬細胞」。肺泡巨噬細胞清除肺泡內的灰塵與碎片。</v>
+      </c>
+      <c r="S249" s="5" t="str">
+        <v>肺泡巨噬細胞清除肺泡內的灰塵與碎片。</v>
+      </c>
+      <c r="T249" s="3" t="str">
+        <v>alveolar-cells；AB-05_13 p.11；CH06 p.19</v>
+      </c>
+      <c r="U249" s="3"/>
+      <c r="V249" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W249" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X249" s="3"/>
+    </row>
+    <row r="250" ht="166" customHeight="1">
+      <c r="A250" s="3"/>
+      <c r="B250" s="4" t="str">
+        <v>lungs-pleura-case-q05</v>
+      </c>
+      <c r="C250" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D250" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F250" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G250" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H250" s="5" t="str">
+        <v>【模型觀察】肺標本內側面，支氣管與肺血管進出的區域？</v>
+      </c>
+      <c r="I250" s="5" t="str">
+        <v>肺尖</v>
+      </c>
+      <c r="J250" s="5" t="str">
+        <v>肺門</v>
+      </c>
+      <c r="K250" s="5" t="str">
+        <v>肺底</v>
+      </c>
+      <c r="L250" s="5" t="str">
+        <v>心切跡</v>
+      </c>
+      <c r="M250" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N250" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" s="5" t="str">
+        <v>肺門是支氣管、肺血管、淋巴管與神經進出肺的區域；進出的構造合稱肺根。</v>
+      </c>
+      <c r="P250" s="5" t="str">
+        <v>找出肺內側面讓多種構造進出的區域。</v>
+      </c>
+      <c r="Q250" s="5" t="str">
+        <v>找出肺內側面讓多種構造進出的區域。 → 【模型觀察】肺標本內側面，支氣管與肺血管進出的區域？</v>
+      </c>
+      <c r="R250" s="5" t="str">
+        <v>選擇「肺門」。肺門是支氣管、肺血管、淋巴管與神經進出肺的區域；進出的構造合稱肺根。</v>
+      </c>
+      <c r="S250" s="5" t="str">
+        <v>肺門是支氣管、肺血管、淋巴管與神經進出肺的區域；進出的構造合稱肺根。</v>
+      </c>
+      <c r="T250" s="3" t="str">
+        <v>hilum-of-lung；p.7–8, 10</v>
+      </c>
+      <c r="U250" s="3"/>
+      <c r="V250" s="5" t="str">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="W250" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lungs-pleura-v1/index.html</v>
+      </c>
+      <c r="X250" s="3"/>
+    </row>
+    <row r="251" ht="166" customHeight="1">
+      <c r="A251" s="3"/>
+      <c r="B251" s="4" t="str">
+        <v>breathing-mechanics-foundation-q01</v>
+      </c>
+      <c r="C251" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D251" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G251" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H251" s="5" t="str">
+        <v>平靜吸氣主要由哪些肌肉收縮？</v>
+      </c>
+      <c r="I251" s="5" t="str">
+        <v>內肋間肌與腹直肌</v>
+      </c>
+      <c r="J251" s="5" t="str">
+        <v>胸鎖乳突肌與腹直肌</v>
+      </c>
+      <c r="K251" s="5" t="str">
+        <v>橫膈與外肋間肌</v>
+      </c>
+      <c r="L251" s="5" t="str">
+        <v>只有腹肌</v>
+      </c>
+      <c r="M251" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N251" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O251" s="5" t="str">
+        <v>平靜吸氣主要靠橫膈與外肋間肌收縮。</v>
+      </c>
+      <c r="P251" s="5" t="str">
+        <v>區分平靜吸氣肌與用力呼氣肌。</v>
+      </c>
+      <c r="Q251" s="5" t="str">
+        <v>區分平靜吸氣肌與用力呼氣肌。 → 平靜吸氣主要由哪些肌肉收縮？</v>
+      </c>
+      <c r="R251" s="5" t="str">
+        <v>選擇「橫膈與外肋間肌」。平靜吸氣主要靠橫膈與外肋間肌收縮。</v>
+      </c>
+      <c r="S251" s="5" t="str">
+        <v>平靜吸氣主要靠橫膈與外肋間肌收縮。</v>
+      </c>
+      <c r="T251" s="3" t="str">
+        <v>respiratory-muscles；CH06 p.3, 8, 10；AB-05_13 p.13</v>
+      </c>
+      <c r="U251" s="3"/>
+      <c r="V251" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W251" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X251" s="3"/>
+    </row>
+    <row r="252" ht="166" customHeight="1">
+      <c r="A252" s="3"/>
+      <c r="B252" s="4" t="str">
+        <v>breathing-mechanics-foundation-q02</v>
+      </c>
+      <c r="C252" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D252" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F252" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G252" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H252" s="5" t="str">
+        <v>平靜呼氣主要靠？</v>
+      </c>
+      <c r="I252" s="5" t="str">
+        <v>腹肌強力收縮</v>
+      </c>
+      <c r="J252" s="5" t="str">
+        <v>內肋間肌持續收縮</v>
+      </c>
+      <c r="K252" s="5" t="str">
+        <v>橫膈收縮下降</v>
+      </c>
+      <c r="L252" s="5" t="str">
+        <v>吸氣肌放鬆與肺的彈性回縮</v>
+      </c>
+      <c r="M252" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N252" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O252" s="5" t="str">
+        <v>平靜呼氣主要靠吸氣肌放鬆與肺的彈性回縮。</v>
+      </c>
+      <c r="P252" s="5" t="str">
+        <v>想想平靜呼氣是否需要額外呼氣肌收縮。</v>
+      </c>
+      <c r="Q252" s="5" t="str">
+        <v>想想平靜呼氣是否需要額外呼氣肌收縮。 → 平靜呼氣主要靠？</v>
+      </c>
+      <c r="R252" s="5" t="str">
+        <v>選擇「吸氣肌放鬆與肺的彈性回縮」。平靜呼氣主要靠吸氣肌放鬆與肺的彈性回縮。</v>
+      </c>
+      <c r="S252" s="5" t="str">
+        <v>平靜呼氣主要靠吸氣肌放鬆與肺的彈性回縮。</v>
+      </c>
+      <c r="T252" s="3" t="str">
+        <v>respiratory-muscles；CH06 p.3, 8, 10；AB-05_13 p.13</v>
+      </c>
+      <c r="U252" s="3"/>
+      <c r="V252" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W252" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X252" s="3"/>
+    </row>
+    <row r="253" ht="166" customHeight="1">
+      <c r="A253" s="3"/>
+      <c r="B253" s="4" t="str">
+        <v>breathing-mechanics-foundation-q03</v>
+      </c>
+      <c r="C253" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D253" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F253" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G253" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H253" s="5" t="str">
+        <v>肺間壓＝？</v>
+      </c>
+      <c r="I253" s="5" t="str">
+        <v>肺內壓－胸內壓</v>
+      </c>
+      <c r="J253" s="5" t="str">
+        <v>胸內壓－大氣壓</v>
+      </c>
+      <c r="K253" s="5" t="str">
+        <v>大氣壓－肺內壓</v>
+      </c>
+      <c r="L253" s="5" t="str">
+        <v>肺內壓＋胸內壓</v>
+      </c>
+      <c r="M253" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N253" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O253" s="5" t="str">
+        <v>肺間壓是肺內壓減去胸內壓。</v>
+      </c>
+      <c r="P253" s="5" t="str">
+        <v>確認肺內與胸膜腔之間的壓差如何定義。</v>
+      </c>
+      <c r="Q253" s="5" t="str">
+        <v>確認肺內與胸膜腔之間的壓差如何定義。 → 肺間壓＝？</v>
+      </c>
+      <c r="R253" s="5" t="str">
+        <v>選擇「肺內壓－胸內壓」。肺間壓是肺內壓減去胸內壓。</v>
+      </c>
+      <c r="S253" s="5" t="str">
+        <v>肺間壓是肺內壓減去胸內壓。</v>
+      </c>
+      <c r="T253" s="3" t="str">
+        <v>intrapleural-pressure；CH06 p.6–7</v>
+      </c>
+      <c r="U253" s="3"/>
+      <c r="V253" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W253" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X253" s="3"/>
+    </row>
+    <row r="254" ht="166" customHeight="1">
+      <c r="A254" s="3"/>
+      <c r="B254" s="4" t="str">
+        <v>breathing-mechanics-foundation-q04</v>
+      </c>
+      <c r="C254" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D254" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F254" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G254" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H254" s="5" t="str">
+        <v>平時胸內壓與大氣壓相比？</v>
+      </c>
+      <c r="I254" s="5" t="str">
+        <v>較高</v>
+      </c>
+      <c r="J254" s="5" t="str">
+        <v>較低</v>
+      </c>
+      <c r="K254" s="5" t="str">
+        <v>相等</v>
+      </c>
+      <c r="L254" s="5" t="str">
+        <v>隨機變動</v>
+      </c>
+      <c r="M254" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N254" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O254" s="5" t="str">
+        <v>胸內壓通常低於大氣壓；負壓是相對大氣壓，並非絕對壓力小於零。</v>
+      </c>
+      <c r="P254" s="5" t="str">
+        <v>負壓是相對哪個參考壓力而言？</v>
+      </c>
+      <c r="Q254" s="5" t="str">
+        <v>負壓是相對哪個參考壓力而言？ → 平時胸內壓與大氣壓相比？</v>
+      </c>
+      <c r="R254" s="5" t="str">
+        <v>選擇「較低」。胸內壓通常低於大氣壓；負壓是相對大氣壓，並非絕對壓力小於零。</v>
+      </c>
+      <c r="S254" s="5" t="str">
+        <v>胸內壓通常低於大氣壓；負壓是相對大氣壓，並非絕對壓力小於零。</v>
+      </c>
+      <c r="T254" s="3" t="str">
+        <v>intrapleural-pressure；CH06 p.6–7</v>
+      </c>
+      <c r="U254" s="3"/>
+      <c r="V254" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W254" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X254" s="3"/>
+    </row>
+    <row r="255" ht="166" customHeight="1">
+      <c r="A255" s="3"/>
+      <c r="B255" s="4" t="str">
+        <v>breathing-mechanics-foundation-q05</v>
+      </c>
+      <c r="C255" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D255" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F255" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G255" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H255" s="5" t="str">
+        <v>肺順應性的意義？</v>
+      </c>
+      <c r="I255" s="5" t="str">
+        <v>每分鐘換氣量</v>
+      </c>
+      <c r="J255" s="5" t="str">
+        <v>最大吸氣後能呼出的量</v>
+      </c>
+      <c r="K255" s="5" t="str">
+        <v>肺間壓改變時肺容積改變的多寡（ΔV/ΔP）</v>
+      </c>
+      <c r="L255" s="5" t="str">
+        <v>肺泡表面張力</v>
+      </c>
+      <c r="M255" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N255" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O255" s="5" t="str">
+        <v>順應性 C＝ΔV/ΔP，表示肺間壓改變時肺容積改變的多寡。</v>
+      </c>
+      <c r="P255" s="5" t="str">
+        <v>把容積變化放在分子、壓力變化放在分母。</v>
+      </c>
+      <c r="Q255" s="5" t="str">
+        <v>把容積變化放在分子、壓力變化放在分母。 → 肺順應性的意義？</v>
+      </c>
+      <c r="R255" s="5" t="str">
+        <v>選擇「肺間壓改變時肺容積改變的多寡（ΔV/ΔP）」。順應性 C＝ΔV/ΔP，表示肺間壓改變時肺容積改變的多寡。</v>
+      </c>
+      <c r="S255" s="5" t="str">
+        <v>順應性 C＝ΔV/ΔP，表示肺間壓改變時肺容積改變的多寡。</v>
+      </c>
+      <c r="T255" s="3" t="str">
+        <v>lung-compliance；CH06 p.9–10, 19–20</v>
+      </c>
+      <c r="U255" s="3"/>
+      <c r="V255" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W255" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X255" s="3"/>
+    </row>
+    <row r="256" ht="166" customHeight="1">
+      <c r="A256" s="3"/>
+      <c r="B256" s="4" t="str">
+        <v>breathing-mechanics-foundation-q06</v>
+      </c>
+      <c r="C256" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D256" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F256" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G256" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H256" s="5" t="str">
+        <v>肺氣腫的肺順應性？</v>
+      </c>
+      <c r="I256" s="5" t="str">
+        <v>減少</v>
+      </c>
+      <c r="J256" s="5" t="str">
+        <v>不變</v>
+      </c>
+      <c r="K256" s="5" t="str">
+        <v>變為零</v>
+      </c>
+      <c r="L256" s="5" t="str">
+        <v>增加</v>
+      </c>
+      <c r="M256" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N256" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O256" s="5" t="str">
+        <v>肺氣腫的順應性增加，但彈性回縮變差，容易有氣體滯留。</v>
+      </c>
+      <c r="P256" s="5" t="str">
+        <v>分清容易撐開與容易縮回兩件事。</v>
+      </c>
+      <c r="Q256" s="5" t="str">
+        <v>分清容易撐開與容易縮回兩件事。 → 肺氣腫的肺順應性？</v>
+      </c>
+      <c r="R256" s="5" t="str">
+        <v>選擇「增加」。肺氣腫的順應性增加，但彈性回縮變差，容易有氣體滯留。</v>
+      </c>
+      <c r="S256" s="5" t="str">
+        <v>肺氣腫的順應性增加，但彈性回縮變差，容易有氣體滯留。</v>
+      </c>
+      <c r="T256" s="3" t="str">
+        <v>lung-compliance、emphysema；CH06 p.9, 12, 15, 21</v>
+      </c>
+      <c r="U256" s="3"/>
+      <c r="V256" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W256" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X256" s="3"/>
+    </row>
+    <row r="257" ht="166" customHeight="1">
+      <c r="A257" s="3"/>
+      <c r="B257" s="4" t="str">
+        <v>breathing-mechanics-case-q01</v>
+      </c>
+      <c r="C257" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D257" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F257" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G257" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H257" s="5" t="str">
+        <v>【模型觀察】吸氣時胸內壓 758→754、肺內壓 760→758 mmHg，空氣為何流入？</v>
+      </c>
+      <c r="I257" s="5" t="str">
+        <v>肺內壓低於大氣壓</v>
+      </c>
+      <c r="J257" s="5" t="str">
+        <v>胸內壓高於肺內壓</v>
+      </c>
+      <c r="K257" s="5" t="str">
+        <v>肺內壓高於大氣壓</v>
+      </c>
+      <c r="L257" s="5" t="str">
+        <v>大氣壓下降</v>
+      </c>
+      <c r="M257" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N257" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" s="5" t="str">
+        <v>吸氣時肺內壓由 760 降到 758 mmHg，低於大氣壓而使空氣流入。</v>
+      </c>
+      <c r="P257" s="5" t="str">
+        <v>將吸氣時肺內壓與外界壓力比較。</v>
+      </c>
+      <c r="Q257" s="5" t="str">
+        <v>將吸氣時肺內壓與外界壓力比較。 → 【模型觀察】吸氣時胸內壓 758→754、肺內壓 760→758 mmHg，空氣為何流入？</v>
+      </c>
+      <c r="R257" s="5" t="str">
+        <v>選擇「肺內壓低於大氣壓」。吸氣時肺內壓由 760 降到 758 mmHg，低於大氣壓而使空氣流入。</v>
+      </c>
+      <c r="S257" s="5" t="str">
+        <v>吸氣時肺內壓由 760 降到 758 mmHg，低於大氣壓而使空氣流入。</v>
+      </c>
+      <c r="T257" s="3" t="str">
+        <v>intrapleural-pressure；CH06 p.8–9</v>
+      </c>
+      <c r="U257" s="3"/>
+      <c r="V257" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W257" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X257" s="3"/>
+    </row>
+    <row r="258" ht="166" customHeight="1">
+      <c r="A258" s="3"/>
+      <c r="B258" s="4" t="str">
+        <v>breathing-mechanics-case-q02</v>
+      </c>
+      <c r="C258" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D258" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F258" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G258" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H258" s="5" t="str">
+        <v>【生理判讀】吸氣過程中胸內壓的變化？</v>
+      </c>
+      <c r="I258" s="5" t="str">
+        <v>升高到高於大氣壓</v>
+      </c>
+      <c r="J258" s="5" t="str">
+        <v>變得更低（更負）</v>
+      </c>
+      <c r="K258" s="5" t="str">
+        <v>保持不變</v>
+      </c>
+      <c r="L258" s="5" t="str">
+        <v>變成等於肺內壓</v>
+      </c>
+      <c r="M258" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N258" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O258" s="5" t="str">
+        <v>吸氣時胸內壓下降，變得更低、更負。</v>
+      </c>
+      <c r="P258" s="5" t="str">
+        <v>依 758→754 的變化判讀相對大氣壓的方向。</v>
+      </c>
+      <c r="Q258" s="5" t="str">
+        <v>依 758→754 的變化判讀相對大氣壓的方向。 → 【生理判讀】吸氣過程中胸內壓的變化？</v>
+      </c>
+      <c r="R258" s="5" t="str">
+        <v>選擇「變得更低（更負）」。吸氣時胸內壓下降，變得更低、更負。</v>
+      </c>
+      <c r="S258" s="5" t="str">
+        <v>吸氣時胸內壓下降，變得更低、更負。</v>
+      </c>
+      <c r="T258" s="3" t="str">
+        <v>intrapleural-pressure；CH06 p.8–9</v>
+      </c>
+      <c r="U258" s="3"/>
+      <c r="V258" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W258" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X258" s="3"/>
+    </row>
+    <row r="259" ht="166" customHeight="1">
+      <c r="A259" s="3"/>
+      <c r="B259" s="4" t="str">
+        <v>breathing-mechanics-case-q03</v>
+      </c>
+      <c r="C259" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D259" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F259" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G259" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H259" s="5" t="str">
+        <v>【生理判讀】肺纖維化病人要吸入同樣空氣量，需要？</v>
+      </c>
+      <c r="I259" s="5" t="str">
+        <v>更小的壓力，因順應性增加</v>
+      </c>
+      <c r="J259" s="5" t="str">
+        <v>不需壓力變化</v>
+      </c>
+      <c r="K259" s="5" t="str">
+        <v>更大的壓力變化，因順應性降低</v>
+      </c>
+      <c r="L259" s="5" t="str">
+        <v>只靠肺內壓上升</v>
+      </c>
+      <c r="M259" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N259" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O259" s="5" t="str">
+        <v>纖維化使順應性降低，因此吸入相同容積需要更大的壓力變化。</v>
+      </c>
+      <c r="P259" s="5" t="str">
+        <v>用同樣容積變化需要多少壓差來判讀。</v>
+      </c>
+      <c r="Q259" s="5" t="str">
+        <v>用同樣容積變化需要多少壓差來判讀。 → 【生理判讀】肺纖維化病人要吸入同樣空氣量，需要？</v>
+      </c>
+      <c r="R259" s="5" t="str">
+        <v>選擇「更大的壓力變化，因順應性降低」。纖維化使順應性降低，因此吸入相同容積需要更大的壓力變化。</v>
+      </c>
+      <c r="S259" s="5" t="str">
+        <v>纖維化使順應性降低，因此吸入相同容積需要更大的壓力變化。</v>
+      </c>
+      <c r="T259" s="3" t="str">
+        <v>lung-compliance、emphysema；CH06 p.9, 12, 15, 21</v>
+      </c>
+      <c r="U259" s="3"/>
+      <c r="V259" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W259" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X259" s="3"/>
+    </row>
+    <row r="260" ht="166" customHeight="1">
+      <c r="A260" s="3"/>
+      <c r="B260" s="4" t="str">
+        <v>breathing-mechanics-case-q04</v>
+      </c>
+      <c r="C260" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D260" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F260" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G260" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H260" s="5" t="str">
+        <v>【生理判讀】肺氣腫病人容易吸進、不易呼出，最可能的結果？</v>
+      </c>
+      <c r="I260" s="5" t="str">
+        <v>肺餘容積減少</v>
+      </c>
+      <c r="J260" s="5" t="str">
+        <v>順應性降低</v>
+      </c>
+      <c r="K260" s="5" t="str">
+        <v>呼吸膜變厚</v>
+      </c>
+      <c r="L260" s="5" t="str">
+        <v>氣體滯留、肺餘容積增加</v>
+      </c>
+      <c r="M260" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N260" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O260" s="5" t="str">
+        <v>肺氣腫回縮變差，呼氣後氣體滯留，肺餘容積增加。</v>
+      </c>
+      <c r="P260" s="5" t="str">
+        <v>回縮變差時，盡力呼氣後會留下多少氣體？</v>
+      </c>
+      <c r="Q260" s="5" t="str">
+        <v>回縮變差時，盡力呼氣後會留下多少氣體？ → 【生理判讀】肺氣腫病人容易吸進、不易呼出，最可能的結果？</v>
+      </c>
+      <c r="R260" s="5" t="str">
+        <v>選擇「氣體滯留、肺餘容積增加」。肺氣腫回縮變差，呼氣後氣體滯留，肺餘容積增加。</v>
+      </c>
+      <c r="S260" s="5" t="str">
+        <v>肺氣腫回縮變差，呼氣後氣體滯留，肺餘容積增加。</v>
+      </c>
+      <c r="T260" s="3" t="str">
+        <v>lung-compliance、emphysema；CH06 p.9, 12, 15, 21</v>
+      </c>
+      <c r="U260" s="3"/>
+      <c r="V260" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W260" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X260" s="3"/>
+    </row>
+    <row r="261" ht="166" customHeight="1">
+      <c r="A261" s="3"/>
+      <c r="B261" s="4" t="str">
+        <v>breathing-mechanics-case-q05</v>
+      </c>
+      <c r="C261" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D261" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F261" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G261" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H261" s="5" t="str">
+        <v>【生活情境】跑完步用力把氣吐乾淨時，額外參與的肌肉？</v>
+      </c>
+      <c r="I261" s="5" t="str">
+        <v>內肋間肌與腹直肌</v>
+      </c>
+      <c r="J261" s="5" t="str">
+        <v>外肋間肌</v>
+      </c>
+      <c r="K261" s="5" t="str">
+        <v>胸鎖乳突肌</v>
+      </c>
+      <c r="L261" s="5" t="str">
+        <v>只有橫膈</v>
+      </c>
+      <c r="M261" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" s="5" t="str">
+        <v>用力呼氣可動用內肋間肌及腹直肌；平靜呼氣主要靠放鬆與回縮。</v>
+      </c>
+      <c r="P261" s="5" t="str">
+        <v>比較平靜呼氣與用力呼氣的肌肉參與。</v>
+      </c>
+      <c r="Q261" s="5" t="str">
+        <v>比較平靜呼氣與用力呼氣的肌肉參與。 → 【生活情境】跑完步用力把氣吐乾淨時，額外參與的肌肉？</v>
+      </c>
+      <c r="R261" s="5" t="str">
+        <v>選擇「內肋間肌與腹直肌」。用力呼氣可動用內肋間肌及腹直肌；平靜呼氣主要靠放鬆與回縮。</v>
+      </c>
+      <c r="S261" s="5" t="str">
+        <v>用力呼氣可動用內肋間肌及腹直肌；平靜呼氣主要靠放鬆與回縮。</v>
+      </c>
+      <c r="T261" s="3" t="str">
+        <v>respiratory-muscles；CH06 p.3, 8, 10；AB-05_13 p.13</v>
+      </c>
+      <c r="U261" s="3"/>
+      <c r="V261" s="5" t="str">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="W261" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/breathing-mechanics-v1/index.html</v>
+      </c>
+      <c r="X261" s="3"/>
+    </row>
+    <row r="262" ht="166" customHeight="1">
+      <c r="A262" s="3"/>
+      <c r="B262" s="4" t="str">
+        <v>lung-function-foundation-q01</v>
+      </c>
+      <c r="C262" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D262" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G262" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H262" s="5" t="str">
+        <v>平靜呼吸時一次吸入或呼出的量？</v>
+      </c>
+      <c r="I262" s="5" t="str">
+        <v>肺餘容積</v>
+      </c>
+      <c r="J262" s="5" t="str">
+        <v>潮氣容積</v>
+      </c>
+      <c r="K262" s="5" t="str">
+        <v>吸氣儲備容積</v>
+      </c>
+      <c r="L262" s="5" t="str">
+        <v>肺活量</v>
+      </c>
+      <c r="M262" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N262" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O262" s="5" t="str">
+        <v>潮氣容積是平靜呼吸時一次吸入或呼出的量，課本男性示例為 500 mL。</v>
+      </c>
+      <c r="P262" s="5" t="str">
+        <v>從平靜的一次呼吸量判斷容積名稱。</v>
+      </c>
+      <c r="Q262" s="5" t="str">
+        <v>從平靜的一次呼吸量判斷容積名稱。 → 平靜呼吸時一次吸入或呼出的量？</v>
+      </c>
+      <c r="R262" s="5" t="str">
+        <v>選擇「潮氣容積」。潮氣容積是平靜呼吸時一次吸入或呼出的量，課本男性示例為 500 mL。</v>
+      </c>
+      <c r="S262" s="5" t="str">
+        <v>潮氣容積是平靜呼吸時一次吸入或呼出的量，課本男性示例為 500 mL。</v>
+      </c>
+      <c r="T262" s="3" t="str">
+        <v>lung-volumes；CH06 p.11–12</v>
+      </c>
+      <c r="U262" s="3"/>
+      <c r="V262" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W262" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X262" s="3"/>
+    </row>
+    <row r="263" ht="166" customHeight="1">
+      <c r="A263" s="3"/>
+      <c r="B263" s="4" t="str">
+        <v>lung-function-foundation-q02</v>
+      </c>
+      <c r="C263" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D263" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F263" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G263" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H263" s="5" t="str">
+        <v>盡力呼氣後仍留在肺內的量？</v>
+      </c>
+      <c r="I263" s="5" t="str">
+        <v>功能肺餘量</v>
+      </c>
+      <c r="J263" s="5" t="str">
+        <v>呼氣儲備容積</v>
+      </c>
+      <c r="K263" s="5" t="str">
+        <v>肺餘容積</v>
+      </c>
+      <c r="L263" s="5" t="str">
+        <v>潮氣容積</v>
+      </c>
+      <c r="M263" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N263" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O263" s="5" t="str">
+        <v>肺餘容積是盡力呼氣後仍留在肺內的量，課本示例為 1200 mL。</v>
+      </c>
+      <c r="P263" s="5" t="str">
+        <v>盡力吐氣後仍存在的氣體屬於哪種容積？</v>
+      </c>
+      <c r="Q263" s="5" t="str">
+        <v>盡力吐氣後仍存在的氣體屬於哪種容積？ → 盡力呼氣後仍留在肺內的量？</v>
+      </c>
+      <c r="R263" s="5" t="str">
+        <v>選擇「肺餘容積」。肺餘容積是盡力呼氣後仍留在肺內的量，課本示例為 1200 mL。</v>
+      </c>
+      <c r="S263" s="5" t="str">
+        <v>肺餘容積是盡力呼氣後仍留在肺內的量，課本示例為 1200 mL。</v>
+      </c>
+      <c r="T263" s="3" t="str">
+        <v>lung-volumes；CH06 p.11–12</v>
+      </c>
+      <c r="U263" s="3"/>
+      <c r="V263" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W263" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X263" s="3"/>
+    </row>
+    <row r="264" ht="166" customHeight="1">
+      <c r="A264" s="3"/>
+      <c r="B264" s="4" t="str">
+        <v>lung-function-foundation-q03</v>
+      </c>
+      <c r="C264" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D264" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F264" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G264" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H264" s="5" t="str">
+        <v>肺活量（VC）＝？</v>
+      </c>
+      <c r="I264" s="5" t="str">
+        <v>IRV＋ERV</v>
+      </c>
+      <c r="J264" s="5" t="str">
+        <v>TV＋RV</v>
+      </c>
+      <c r="K264" s="5" t="str">
+        <v>ERV＋RV</v>
+      </c>
+      <c r="L264" s="5" t="str">
+        <v>IRV＋TV＋ERV</v>
+      </c>
+      <c r="M264" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N264" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O264" s="5" t="str">
+        <v>VC＝IRV＋TV＋ERV，不包含盡力呼氣後仍留下的 RV。</v>
+      </c>
+      <c r="P264" s="5" t="str">
+        <v>肺活量涵蓋能吸入與能呼出的哪些部分？</v>
+      </c>
+      <c r="Q264" s="5" t="str">
+        <v>肺活量涵蓋能吸入與能呼出的哪些部分？ → 肺活量（VC）＝？</v>
+      </c>
+      <c r="R264" s="5" t="str">
+        <v>選擇「IRV＋TV＋ERV」。VC＝IRV＋TV＋ERV，不包含盡力呼氣後仍留下的 RV。</v>
+      </c>
+      <c r="S264" s="5" t="str">
+        <v>VC＝IRV＋TV＋ERV，不包含盡力呼氣後仍留下的 RV。</v>
+      </c>
+      <c r="T264" s="3" t="str">
+        <v>lung-volumes；CH06 p.12</v>
+      </c>
+      <c r="U264" s="3"/>
+      <c r="V264" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W264" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X264" s="3"/>
+    </row>
+    <row r="265" ht="166" customHeight="1">
+      <c r="A265" s="3"/>
+      <c r="B265" s="4" t="str">
+        <v>lung-function-foundation-q04</v>
+      </c>
+      <c r="C265" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D265" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F265" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G265" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H265" s="5" t="str">
+        <v>功能肺餘量（FRC）＝？</v>
+      </c>
+      <c r="I265" s="5" t="str">
+        <v>ERV＋RV</v>
+      </c>
+      <c r="J265" s="5" t="str">
+        <v>TV＋IRV</v>
+      </c>
+      <c r="K265" s="5" t="str">
+        <v>IRV＋ERV</v>
+      </c>
+      <c r="L265" s="5" t="str">
+        <v>TV＋RV</v>
+      </c>
+      <c r="M265" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N265" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" s="5" t="str">
+        <v>FRC＝ERV＋RV，是平靜呼氣末的肺內氣體量。</v>
+      </c>
+      <c r="P265" s="5" t="str">
+        <v>平靜呼氣末還有哪些氣體留在肺內？</v>
+      </c>
+      <c r="Q265" s="5" t="str">
+        <v>平靜呼氣末還有哪些氣體留在肺內？ → 功能肺餘量（FRC）＝？</v>
+      </c>
+      <c r="R265" s="5" t="str">
+        <v>選擇「ERV＋RV」。FRC＝ERV＋RV，是平靜呼氣末的肺內氣體量。</v>
+      </c>
+      <c r="S265" s="5" t="str">
+        <v>FRC＝ERV＋RV，是平靜呼氣末的肺內氣體量。</v>
+      </c>
+      <c r="T265" s="3" t="str">
+        <v>lung-volumes；CH06 p.12</v>
+      </c>
+      <c r="U265" s="3"/>
+      <c r="V265" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W265" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X265" s="3"/>
+    </row>
+    <row r="266" ht="166" customHeight="1">
+      <c r="A266" s="3"/>
+      <c r="B266" s="4" t="str">
+        <v>lung-function-foundation-q05</v>
+      </c>
+      <c r="C266" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D266" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F266" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G266" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H266" s="5" t="str">
+        <v>傳導區的最後一段？</v>
+      </c>
+      <c r="I266" s="5" t="str">
+        <v>呼吸性細支氣管</v>
+      </c>
+      <c r="J266" s="5" t="str">
+        <v>終末細支氣管</v>
+      </c>
+      <c r="K266" s="5" t="str">
+        <v>肺泡管</v>
+      </c>
+      <c r="L266" s="5" t="str">
+        <v>主支氣管</v>
+      </c>
+      <c r="M266" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O266" s="5" t="str">
+        <v>終末細支氣管仍只傳送氣體；自呼吸性細支氣管起才是呼吸區。</v>
+      </c>
+      <c r="P266" s="5" t="str">
+        <v>找出呼吸區開始之前的最後一段。</v>
+      </c>
+      <c r="Q266" s="5" t="str">
+        <v>找出呼吸區開始之前的最後一段。 → 傳導區的最後一段？</v>
+      </c>
+      <c r="R266" s="5" t="str">
+        <v>選擇「終末細支氣管」。終末細支氣管仍只傳送氣體；自呼吸性細支氣管起才是呼吸區。</v>
+      </c>
+      <c r="S266" s="5" t="str">
+        <v>終末細支氣管仍只傳送氣體；自呼吸性細支氣管起才是呼吸區。</v>
+      </c>
+      <c r="T266" s="3" t="str">
+        <v>anatomic-dead-space、bronchial-tree；CH06 p.5, 13；AB-05_13 p.11</v>
+      </c>
+      <c r="U266" s="3"/>
+      <c r="V266" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W266" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X266" s="3"/>
+    </row>
+    <row r="267" ht="166" customHeight="1">
+      <c r="A267" s="3"/>
+      <c r="B267" s="4" t="str">
+        <v>lung-function-foundation-q06</v>
+      </c>
+      <c r="C267" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D267" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F267" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G267" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H267" s="5" t="str">
+        <v>肺泡通氣量的算法？</v>
+      </c>
+      <c r="I267" s="5" t="str">
+        <v>潮氣容積×呼吸頻率</v>
+      </c>
+      <c r="J267" s="5" t="str">
+        <v>（潮氣容積＋死腔）×呼吸頻率</v>
+      </c>
+      <c r="K267" s="5" t="str">
+        <v>（潮氣容積－死腔）×呼吸頻率</v>
+      </c>
+      <c r="L267" s="5" t="str">
+        <v>肺活量×呼吸頻率</v>
+      </c>
+      <c r="M267" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N267" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O267" s="5" t="str">
+        <v>肺泡通氣量 VA＝（TV－死腔）×呼吸頻率，不能直接使用總通氣量。</v>
+      </c>
+      <c r="P267" s="5" t="str">
+        <v>先扣掉每次未參與交換的量，再乘頻率。</v>
+      </c>
+      <c r="Q267" s="5" t="str">
+        <v>先扣掉每次未參與交換的量，再乘頻率。 → 肺泡通氣量的算法？</v>
+      </c>
+      <c r="R267" s="5" t="str">
+        <v>選擇「（潮氣容積－死腔）×呼吸頻率」。肺泡通氣量 VA＝（TV－死腔）×呼吸頻率，不能直接使用總通氣量。</v>
+      </c>
+      <c r="S267" s="5" t="str">
+        <v>肺泡通氣量 VA＝（TV－死腔）×呼吸頻率，不能直接使用總通氣量。</v>
+      </c>
+      <c r="T267" s="3" t="str">
+        <v>anatomic-dead-space、alveolar-ventilation；CH06 p.13–14</v>
+      </c>
+      <c r="U267" s="3"/>
+      <c r="V267" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W267" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X267" s="3"/>
+    </row>
+    <row r="268" ht="166" customHeight="1">
+      <c r="A268" s="3"/>
+      <c r="B268" s="4" t="str">
+        <v>lung-function-case-q01</v>
+      </c>
+      <c r="C268" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D268" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F268" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G268" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H268" s="5" t="str">
+        <v>【模型觀察】TV 450 mL、死腔 150 mL、每分鐘 12 次，肺泡通氣量？</v>
+      </c>
+      <c r="I268" s="5" t="str">
+        <v>5400 mL/min</v>
+      </c>
+      <c r="J268" s="5" t="str">
+        <v>1800 mL/min</v>
+      </c>
+      <c r="K268" s="5" t="str">
+        <v>4200 mL/min</v>
+      </c>
+      <c r="L268" s="5" t="str">
+        <v>3600 mL/min</v>
+      </c>
+      <c r="M268" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N268" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O268" s="5" t="str">
+        <v>VA＝（450－150）×12＝3600 mL/min。</v>
+      </c>
+      <c r="P268" s="5" t="str">
+        <v>先算 450－150，再乘每分鐘次數。</v>
+      </c>
+      <c r="Q268" s="5" t="str">
+        <v>先算 450－150，再乘每分鐘次數。 → 【模型觀察】TV 450 mL、死腔 150 mL、每分鐘 12 次，肺泡通氣量？</v>
+      </c>
+      <c r="R268" s="5" t="str">
+        <v>選擇「3600 mL/min」。VA＝（450－150）×12＝3600 mL/min。</v>
+      </c>
+      <c r="S268" s="5" t="str">
+        <v>VA＝（450－150）×12＝3600 mL/min。</v>
+      </c>
+      <c r="T268" s="3" t="str">
+        <v>anatomic-dead-space、alveolar-ventilation；CH06 p.13–14</v>
+      </c>
+      <c r="U268" s="3"/>
+      <c r="V268" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W268" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X268" s="3"/>
+    </row>
+    <row r="269" ht="166" customHeight="1">
+      <c r="A269" s="3"/>
+      <c r="B269" s="4" t="str">
+        <v>lung-function-case-q02</v>
+      </c>
+      <c r="C269" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D269" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F269" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G269" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H269" s="5" t="str">
+        <v>【模型觀察】每次 150 mL、每分鐘 40 次（總通氣 6000），肺泡通氣量？</v>
+      </c>
+      <c r="I269" s="5" t="str">
+        <v>0 mL/min</v>
+      </c>
+      <c r="J269" s="5" t="str">
+        <v>6000 mL/min</v>
+      </c>
+      <c r="K269" s="5" t="str">
+        <v>4200 mL/min</v>
+      </c>
+      <c r="L269" s="5" t="str">
+        <v>3000 mL/min</v>
+      </c>
+      <c r="M269" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" s="5" t="str">
+        <v>VA＝（150－150）×40＝0；總通氣雖有 6000，肺泡通氣仍為零。</v>
+      </c>
+      <c r="P269" s="5" t="str">
+        <v>比較每次呼吸量與 150 mL 死腔是否相等。</v>
+      </c>
+      <c r="Q269" s="5" t="str">
+        <v>比較每次呼吸量與 150 mL 死腔是否相等。 → 【模型觀察】每次 150 mL、每分鐘 40 次（總通氣 6000），肺泡通氣量？</v>
+      </c>
+      <c r="R269" s="5" t="str">
+        <v>選擇「0 mL/min」。VA＝（150－150）×40＝0；總通氣雖有 6000，肺泡通氣仍為零。</v>
+      </c>
+      <c r="S269" s="5" t="str">
+        <v>VA＝（150－150）×40＝0；總通氣雖有 6000，肺泡通氣仍為零。</v>
+      </c>
+      <c r="T269" s="3" t="str">
+        <v>alveolar-ventilation；CH06 p.13–14</v>
+      </c>
+      <c r="U269" s="3"/>
+      <c r="V269" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W269" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X269" s="3"/>
+    </row>
+    <row r="270" ht="166" customHeight="1">
+      <c r="A270" s="3"/>
+      <c r="B270" s="4" t="str">
+        <v>lung-function-case-q03</v>
+      </c>
+      <c r="C270" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D270" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F270" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G270" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H270" s="5" t="str">
+        <v>【生理判讀】長期吸菸使肺泡壁回彈變差，盡力呼氣後哪一項增加？</v>
+      </c>
+      <c r="I270" s="5" t="str">
+        <v>潮氣容積</v>
+      </c>
+      <c r="J270" s="5" t="str">
+        <v>肺餘容積</v>
+      </c>
+      <c r="K270" s="5" t="str">
+        <v>肺活量</v>
+      </c>
+      <c r="L270" s="5" t="str">
+        <v>吸氣儲備容積</v>
+      </c>
+      <c r="M270" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N270" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" s="5" t="str">
+        <v>盡力呼氣後仍留下的氣體稱肺餘容積，因此題目所述增加的是 RV。</v>
+      </c>
+      <c r="P270" s="5" t="str">
+        <v>找出盡力呼氣後留下的容積名稱。</v>
+      </c>
+      <c r="Q270" s="5" t="str">
+        <v>找出盡力呼氣後留下的容積名稱。 → 【生理判讀】長期吸菸使肺泡壁回彈變差，盡力呼氣後哪一項增加？</v>
+      </c>
+      <c r="R270" s="5" t="str">
+        <v>選擇「肺餘容積」。盡力呼氣後仍留下的氣體稱肺餘容積，因此題目所述增加的是 RV。</v>
+      </c>
+      <c r="S270" s="5" t="str">
+        <v>盡力呼氣後仍留下的氣體稱肺餘容積，因此題目所述增加的是 RV。</v>
+      </c>
+      <c r="T270" s="3" t="str">
+        <v>lung-volumes；CH06 p.11–12</v>
+      </c>
+      <c r="U270" s="3"/>
+      <c r="V270" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W270" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X270" s="3"/>
+    </row>
+    <row r="271" ht="166" customHeight="1">
+      <c r="A271" s="3"/>
+      <c r="B271" s="4" t="str">
+        <v>lung-function-case-q04</v>
+      </c>
+      <c r="C271" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D271" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F271" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G271" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H271" s="5" t="str">
+        <v>【生理判讀】FEV₁ 2.5 L、FVC 2.8 L（比值約 0.89），肺容量明顯減少，較符合？</v>
+      </c>
+      <c r="I271" s="5" t="str">
+        <v>阻塞性型態</v>
+      </c>
+      <c r="J271" s="5" t="str">
+        <v>完全正常</v>
+      </c>
+      <c r="K271" s="5" t="str">
+        <v>限制性型態</v>
+      </c>
+      <c r="L271" s="5" t="str">
+        <v>只有死腔增加</v>
+      </c>
+      <c r="M271" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N271" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O271" s="5" t="str">
+        <v>課本限制性示例為 2.5/2.8≈0.89；肺容量減少而比值可正常或增加。</v>
+      </c>
+      <c r="P271" s="5" t="str">
+        <v>同時比較肺容量與 FEV₁/FVC，勿只看比值。</v>
+      </c>
+      <c r="Q271" s="5" t="str">
+        <v>同時比較肺容量與 FEV₁/FVC，勿只看比值。 → 【生理判讀】FEV₁ 2.5 L、FVC 2.8 L（比值約 0.89），肺容量明顯減少，較符合？</v>
+      </c>
+      <c r="R271" s="5" t="str">
+        <v>選擇「限制性型態」。課本限制性示例為 2.5/2.8≈0.89；肺容量減少而比值可正常或增加。</v>
+      </c>
+      <c r="S271" s="5" t="str">
+        <v>課本限制性示例為 2.5/2.8≈0.89；肺容量減少而比值可正常或增加。</v>
+      </c>
+      <c r="T271" s="3" t="str">
+        <v>obstructive-restrictive；CH06 p.9, 12, 14–15</v>
+      </c>
+      <c r="U271" s="3"/>
+      <c r="V271" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W271" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X271" s="3"/>
+    </row>
+    <row r="272" ht="166" customHeight="1">
+      <c r="A272" s="3"/>
+      <c r="B272" s="4" t="str">
+        <v>lung-function-case-q05</v>
+      </c>
+      <c r="C272" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D272" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F272" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G272" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H272" s="5" t="str">
+        <v>【生理判讀】平靜吸氣結束時，肺內的氣體量？</v>
+      </c>
+      <c r="I272" s="5" t="str">
+        <v>肺活量</v>
+      </c>
+      <c r="J272" s="5" t="str">
+        <v>肺餘容積</v>
+      </c>
+      <c r="K272" s="5" t="str">
+        <v>總肺容量</v>
+      </c>
+      <c r="L272" s="5" t="str">
+        <v>功能肺餘量＋潮氣容積</v>
+      </c>
+      <c r="M272" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N272" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O272" s="5" t="str">
+        <v>平靜呼氣末為 FRC，平靜吸氣末則為 FRC＋TV。</v>
+      </c>
+      <c r="P272" s="5" t="str">
+        <v>從平靜呼氣末的量加上一次平靜吸氣量。</v>
+      </c>
+      <c r="Q272" s="5" t="str">
+        <v>從平靜呼氣末的量加上一次平靜吸氣量。 → 【生理判讀】平靜吸氣結束時，肺內的氣體量？</v>
+      </c>
+      <c r="R272" s="5" t="str">
+        <v>選擇「功能肺餘量＋潮氣容積」。平靜呼氣末為 FRC，平靜吸氣末則為 FRC＋TV。</v>
+      </c>
+      <c r="S272" s="5" t="str">
+        <v>平靜呼氣末為 FRC，平靜吸氣末則為 FRC＋TV。</v>
+      </c>
+      <c r="T272" s="3" t="str">
+        <v>lung-volumes；CH06 p.12</v>
+      </c>
+      <c r="U272" s="3"/>
+      <c r="V272" s="5" t="str">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="W272" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/lung-function-v1/index.html</v>
+      </c>
+      <c r="X272" s="3"/>
+    </row>
+    <row r="273" ht="166" customHeight="1">
+      <c r="A273" s="3"/>
+      <c r="B273" s="4" t="str">
+        <v>gas-exchange-foundation-q01</v>
+      </c>
+      <c r="C273" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D273" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F273" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G273" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H273" s="5" t="str">
+        <v>外呼吸發生在？</v>
+      </c>
+      <c r="I273" s="5" t="str">
+        <v>肺泡與肺微血管之間</v>
+      </c>
+      <c r="J273" s="5" t="str">
+        <v>組織細胞與微血管之間</v>
+      </c>
+      <c r="K273" s="5" t="str">
+        <v>鼻腔內</v>
+      </c>
+      <c r="L273" s="5" t="str">
+        <v>細胞粒線體內</v>
+      </c>
+      <c r="M273" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" s="5" t="str">
+        <v>外呼吸是肺泡與肺微血管之間的交換；內呼吸是血液與組織細胞間的交換。</v>
+      </c>
+      <c r="P273" s="5" t="str">
+        <v>先區分肺部交換與組織端交換。</v>
+      </c>
+      <c r="Q273" s="5" t="str">
+        <v>先區分肺部交換與組織端交換。 → 外呼吸發生在？</v>
+      </c>
+      <c r="R273" s="5" t="str">
+        <v>選擇「肺泡與肺微血管之間」。外呼吸是肺泡與肺微血管之間的交換；內呼吸是血液與組織細胞間的交換。</v>
+      </c>
+      <c r="S273" s="5" t="str">
+        <v>外呼吸是肺泡與肺微血管之間的交換；內呼吸是血液與組織細胞間的交換。</v>
+      </c>
+      <c r="T273" s="3" t="str">
+        <v>external-respiration；CH06 p.4, 17, 20, 23</v>
+      </c>
+      <c r="U273" s="3"/>
+      <c r="V273" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W273" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X273" s="3"/>
+    </row>
+    <row r="274" ht="166" customHeight="1">
+      <c r="A274" s="3"/>
+      <c r="B274" s="4" t="str">
+        <v>gas-exchange-foundation-q02</v>
+      </c>
+      <c r="C274" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D274" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F274" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G274" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H274" s="5" t="str">
+        <v>每種氣體的擴散方向由何決定？</v>
+      </c>
+      <c r="I274" s="5" t="str">
+        <v>混合氣體總壓</v>
+      </c>
+      <c r="J274" s="5" t="str">
+        <v>該氣體自己的分壓差</v>
+      </c>
+      <c r="K274" s="5" t="str">
+        <v>氣體分子量</v>
+      </c>
+      <c r="L274" s="5" t="str">
+        <v>血流速度</v>
+      </c>
+      <c r="M274" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N274" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O274" s="5" t="str">
+        <v>每種氣體依自己的分壓差擴散，氣體總壓不能取代氧分壓。</v>
+      </c>
+      <c r="P274" s="5" t="str">
+        <v>混合氣體中，各氣體是否共用同一個壓差？</v>
+      </c>
+      <c r="Q274" s="5" t="str">
+        <v>混合氣體中，各氣體是否共用同一個壓差？ → 每種氣體的擴散方向由何決定？</v>
+      </c>
+      <c r="R274" s="5" t="str">
+        <v>選擇「該氣體自己的分壓差」。每種氣體依自己的分壓差擴散，氣體總壓不能取代氧分壓。</v>
+      </c>
+      <c r="S274" s="5" t="str">
+        <v>每種氣體依自己的分壓差擴散，氣體總壓不能取代氧分壓。</v>
+      </c>
+      <c r="T274" s="3" t="str">
+        <v>gas-diffusion；CH06 p.16–17</v>
+      </c>
+      <c r="U274" s="3"/>
+      <c r="V274" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W274" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X274" s="3"/>
+    </row>
+    <row r="275" ht="166" customHeight="1">
+      <c r="A275" s="3"/>
+      <c r="B275" s="4" t="str">
+        <v>gas-exchange-foundation-q03</v>
+      </c>
+      <c r="C275" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D275" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F275" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G275" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H275" s="5" t="str">
+        <v>肺泡 PO₂ 約 100、入肺血約 40 mmHg，O₂ 如何移動？</v>
+      </c>
+      <c r="I275" s="5" t="str">
+        <v>由血液進入肺泡</v>
+      </c>
+      <c r="J275" s="5" t="str">
+        <v>不移動</v>
+      </c>
+      <c r="K275" s="5" t="str">
+        <v>由肺泡擴散進入血液</v>
+      </c>
+      <c r="L275" s="5" t="str">
+        <v>以主動運輸進入血液</v>
+      </c>
+      <c r="M275" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N275" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O275" s="5" t="str">
+        <v>肺泡 PO₂ 約 100，高於入肺血約 40 mmHg，因此氧由肺泡擴散入血。</v>
+      </c>
+      <c r="P275" s="5" t="str">
+        <v>比較肺泡與入肺血的氧分壓高低。</v>
+      </c>
+      <c r="Q275" s="5" t="str">
+        <v>比較肺泡與入肺血的氧分壓高低。 → 肺泡 PO₂ 約 100、入肺血約 40 mmHg，O₂ 如何移動？</v>
+      </c>
+      <c r="R275" s="5" t="str">
+        <v>選擇「由肺泡擴散進入血液」。肺泡 PO₂ 約 100，高於入肺血約 40 mmHg，因此氧由肺泡擴散入血。</v>
+      </c>
+      <c r="S275" s="5" t="str">
+        <v>肺泡 PO₂ 約 100，高於入肺血約 40 mmHg，因此氧由肺泡擴散入血。</v>
+      </c>
+      <c r="T275" s="3" t="str">
+        <v>external-respiration；CH06 p.17, 20</v>
+      </c>
+      <c r="U275" s="3"/>
+      <c r="V275" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W275" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X275" s="3"/>
+    </row>
+    <row r="276" ht="166" customHeight="1">
+      <c r="A276" s="3"/>
+      <c r="B276" s="4" t="str">
+        <v>gas-exchange-foundation-q04</v>
+      </c>
+      <c r="C276" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D276" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F276" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G276" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H276" s="5" t="str">
+        <v>哪個變化會使擴散增加？</v>
+      </c>
+      <c r="I276" s="5" t="str">
+        <v>呼吸膜變厚</v>
+      </c>
+      <c r="J276" s="5" t="str">
+        <v>分壓差變小</v>
+      </c>
+      <c r="K276" s="5" t="str">
+        <v>分子量增加</v>
+      </c>
+      <c r="L276" s="5" t="str">
+        <v>呼吸膜面積增加</v>
+      </c>
+      <c r="M276" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N276" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O276" s="5" t="str">
+        <v>呼吸膜面積增加會增加擴散；膜厚增加則減少擴散。</v>
+      </c>
+      <c r="P276" s="5" t="str">
+        <v>分清增加交換面積與增加膜厚的效果。</v>
+      </c>
+      <c r="Q276" s="5" t="str">
+        <v>分清增加交換面積與增加膜厚的效果。 → 哪個變化會使擴散增加？</v>
+      </c>
+      <c r="R276" s="5" t="str">
+        <v>選擇「呼吸膜面積增加」。呼吸膜面積增加會增加擴散；膜厚增加則減少擴散。</v>
+      </c>
+      <c r="S276" s="5" t="str">
+        <v>呼吸膜面積增加會增加擴散；膜厚增加則減少擴散。</v>
+      </c>
+      <c r="T276" s="3" t="str">
+        <v>gas-diffusion；CH06 p.16–17, 20–21</v>
+      </c>
+      <c r="U276" s="3"/>
+      <c r="V276" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W276" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X276" s="3"/>
+    </row>
+    <row r="277" ht="166" customHeight="1">
+      <c r="A277" s="3"/>
+      <c r="B277" s="4" t="str">
+        <v>gas-exchange-foundation-q05</v>
+      </c>
+      <c r="C277" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D277" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F277" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G277" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H277" s="5" t="str">
+        <v>站立時哪個部位 V/Q 較高？</v>
+      </c>
+      <c r="I277" s="5" t="str">
+        <v>肺尖</v>
+      </c>
+      <c r="J277" s="5" t="str">
+        <v>肺底</v>
+      </c>
+      <c r="K277" s="5" t="str">
+        <v>兩處相同</v>
+      </c>
+      <c r="L277" s="5" t="str">
+        <v>肺門</v>
+      </c>
+      <c r="M277" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N277" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" s="5" t="str">
+        <v>肺尖 V/Q 約 3.4，高於肺底約 0.63；血流的上下差異比通氣更大。</v>
+      </c>
+      <c r="P277" s="5" t="str">
+        <v>比較兩處通氣量除以血流量的結果。</v>
+      </c>
+      <c r="Q277" s="5" t="str">
+        <v>比較兩處通氣量除以血流量的結果。 → 站立時哪個部位 V/Q 較高？</v>
+      </c>
+      <c r="R277" s="5" t="str">
+        <v>選擇「肺尖」。肺尖 V/Q 約 3.4，高於肺底約 0.63；血流的上下差異比通氣更大。</v>
+      </c>
+      <c r="S277" s="5" t="str">
+        <v>肺尖 V/Q 約 3.4，高於肺底約 0.63；血流的上下差異比通氣更大。</v>
+      </c>
+      <c r="T277" s="3" t="str">
+        <v>ventilation-perfusion；CH06 p.21–22</v>
+      </c>
+      <c r="U277" s="3"/>
+      <c r="V277" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W277" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X277" s="3"/>
+    </row>
+    <row r="278" ht="166" customHeight="1">
+      <c r="A278" s="3"/>
+      <c r="B278" s="4" t="str">
+        <v>gas-exchange-foundation-q06</v>
+      </c>
+      <c r="C278" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D278" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F278" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G278" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H278" s="5" t="str">
+        <v>肺泡局部低氧時，該處肺小動脈？</v>
+      </c>
+      <c r="I278" s="5" t="str">
+        <v>舒張</v>
+      </c>
+      <c r="J278" s="5" t="str">
+        <v>收縮</v>
+      </c>
+      <c r="K278" s="5" t="str">
+        <v>不變</v>
+      </c>
+      <c r="L278" s="5" t="str">
+        <v>破裂</v>
+      </c>
+      <c r="M278" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N278" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O278" s="5" t="str">
+        <v>局部肺泡低氧使該處肺小動脈收縮，減少流向通氣不佳處的血流。</v>
+      </c>
+      <c r="P278" s="5" t="str">
+        <v>思考如何減少送往通氣不佳處的血流。</v>
+      </c>
+      <c r="Q278" s="5" t="str">
+        <v>思考如何減少送往通氣不佳處的血流。 → 肺泡局部低氧時，該處肺小動脈？</v>
+      </c>
+      <c r="R278" s="5" t="str">
+        <v>選擇「收縮」。局部肺泡低氧使該處肺小動脈收縮，減少流向通氣不佳處的血流。</v>
+      </c>
+      <c r="S278" s="5" t="str">
+        <v>局部肺泡低氧使該處肺小動脈收縮，減少流向通氣不佳處的血流。</v>
+      </c>
+      <c r="T278" s="3" t="str">
+        <v>ventilation-perfusion；CH06 p.22</v>
+      </c>
+      <c r="U278" s="3"/>
+      <c r="V278" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W278" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X278" s="3"/>
+    </row>
+    <row r="279" ht="166" customHeight="1">
+      <c r="A279" s="3"/>
+      <c r="B279" s="4" t="str">
+        <v>gas-exchange-case-q01</v>
+      </c>
+      <c r="C279" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D279" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F279" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G279" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H279" s="5" t="str">
+        <v>【生理判讀】CO₂ 分子量比 O₂ 大，卻容易擴散，主要因為？</v>
+      </c>
+      <c r="I279" s="5" t="str">
+        <v>CO₂ 以主動運輸通過</v>
+      </c>
+      <c r="J279" s="5" t="str">
+        <v>呼吸膜對 CO₂ 較薄</v>
+      </c>
+      <c r="K279" s="5" t="str">
+        <v>CO₂ 溶解度約為 O₂ 的 20 倍</v>
+      </c>
+      <c r="L279" s="5" t="str">
+        <v>CO₂ 不需要分壓差</v>
+      </c>
+      <c r="M279" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N279" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O279" s="5" t="str">
+        <v>CO₂ 的溶解度約為 O₂ 的 20 倍；較高溶解度有利於擴散。</v>
+      </c>
+      <c r="P279" s="5" t="str">
+        <v>分子量之外，還有哪個氣體性質影響擴散？</v>
+      </c>
+      <c r="Q279" s="5" t="str">
+        <v>分子量之外，還有哪個氣體性質影響擴散？ → 【生理判讀】CO₂ 分子量比 O₂ 大，卻容易擴散，主要因為？</v>
+      </c>
+      <c r="R279" s="5" t="str">
+        <v>選擇「CO₂ 溶解度約為 O₂ 的 20 倍」。CO₂ 的溶解度約為 O₂ 的 20 倍；較高溶解度有利於擴散。</v>
+      </c>
+      <c r="S279" s="5" t="str">
+        <v>CO₂ 的溶解度約為 O₂ 的 20 倍；較高溶解度有利於擴散。</v>
+      </c>
+      <c r="T279" s="3" t="str">
+        <v>gas-diffusion；CH06 p.16–17, 20–21</v>
+      </c>
+      <c r="U279" s="3"/>
+      <c r="V279" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W279" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X279" s="3"/>
+    </row>
+    <row r="280" ht="166" customHeight="1">
+      <c r="A280" s="3"/>
+      <c r="B280" s="4" t="str">
+        <v>gas-exchange-case-q02</v>
+      </c>
+      <c r="C280" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D280" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F280" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G280" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H280" s="5" t="str">
+        <v>【生理判讀】肺水腫使呼吸膜變厚，最可能妨礙？</v>
+      </c>
+      <c r="I280" s="5" t="str">
+        <v>肺葉的數目</v>
+      </c>
+      <c r="J280" s="5" t="str">
+        <v>表面張力素的分泌位置</v>
+      </c>
+      <c r="K280" s="5" t="str">
+        <v>血紅素的構造</v>
+      </c>
+      <c r="L280" s="5" t="str">
+        <v>氧的擴散</v>
+      </c>
+      <c r="M280" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N280" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O280" s="5" t="str">
+        <v>膜厚增加會減少擴散，因此呼吸膜變厚會妨礙氧的擴散。</v>
+      </c>
+      <c r="P280" s="5" t="str">
+        <v>膜厚增加對擴散的影響方向為何？</v>
+      </c>
+      <c r="Q280" s="5" t="str">
+        <v>膜厚增加對擴散的影響方向為何？ → 【生理判讀】肺水腫使呼吸膜變厚，最可能妨礙？</v>
+      </c>
+      <c r="R280" s="5" t="str">
+        <v>選擇「氧的擴散」。膜厚增加會減少擴散，因此呼吸膜變厚會妨礙氧的擴散。</v>
+      </c>
+      <c r="S280" s="5" t="str">
+        <v>膜厚增加會減少擴散，因此呼吸膜變厚會妨礙氧的擴散。</v>
+      </c>
+      <c r="T280" s="3" t="str">
+        <v>gas-diffusion；CH06 p.16–17, 20–21</v>
+      </c>
+      <c r="U280" s="3"/>
+      <c r="V280" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W280" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X280" s="3"/>
+    </row>
+    <row r="281" ht="166" customHeight="1">
+      <c r="A281" s="3"/>
+      <c r="B281" s="4" t="str">
+        <v>gas-exchange-case-q03</v>
+      </c>
+      <c r="C281" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D281" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E281" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F281" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G281" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H281" s="5" t="str">
+        <v>【模型觀察】一處肺泡被痰阻塞而無通氣，該處肺小動脈的反應與意義？</v>
+      </c>
+      <c r="I281" s="5" t="str">
+        <v>收縮，使血流轉向通氣良好的肺泡</v>
+      </c>
+      <c r="J281" s="5" t="str">
+        <v>舒張，增加流向該處的血流</v>
+      </c>
+      <c r="K281" s="5" t="str">
+        <v>不變</v>
+      </c>
+      <c r="L281" s="5" t="str">
+        <v>收縮，使全身血壓下降</v>
+      </c>
+      <c r="M281" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N281" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" s="5" t="str">
+        <v>低氧處肺小動脈收縮，減少通氣不佳處的血流，使通氣與灌流較能配合。</v>
+      </c>
+      <c r="P281" s="5" t="str">
+        <v>將局部血管反應與通氣、灌流配合連起來。</v>
+      </c>
+      <c r="Q281" s="5" t="str">
+        <v>將局部血管反應與通氣、灌流配合連起來。 → 【模型觀察】一處肺泡被痰阻塞而無通氣，該處肺小動脈的反應與意義？</v>
+      </c>
+      <c r="R281" s="5" t="str">
+        <v>選擇「收縮，使血流轉向通氣良好的肺泡」。低氧處肺小動脈收縮，減少通氣不佳處的血流，使通氣與灌流較能配合。</v>
+      </c>
+      <c r="S281" s="5" t="str">
+        <v>低氧處肺小動脈收縮，減少通氣不佳處的血流，使通氣與灌流較能配合。</v>
+      </c>
+      <c r="T281" s="3" t="str">
+        <v>ventilation-perfusion；CH06 p.22</v>
+      </c>
+      <c r="U281" s="3"/>
+      <c r="V281" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W281" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X281" s="3"/>
+    </row>
+    <row r="282" ht="166" customHeight="1">
+      <c r="A282" s="3"/>
+      <c r="B282" s="4" t="str">
+        <v>gas-exchange-case-q04</v>
+      </c>
+      <c r="C282" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D282" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F282" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G282" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H282" s="5" t="str">
+        <v>【模型觀察】肺尖 V/Q≈3.4、肺底≈0.63，何者正確？</v>
+      </c>
+      <c r="I282" s="5" t="str">
+        <v>肺尖血流比肺底多</v>
+      </c>
+      <c r="J282" s="5" t="str">
+        <v>肺尖通氣相對血流較多</v>
+      </c>
+      <c r="K282" s="5" t="str">
+        <v>肺底通氣多於血流</v>
+      </c>
+      <c r="L282" s="5" t="str">
+        <v>兩處配合完全相同</v>
+      </c>
+      <c r="M282" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N282" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O282" s="5" t="str">
+        <v>肺尖 V/Q≈3.4，表示通氣相對血流較多；不能據此說肺尖的絕對通氣量最多。</v>
+      </c>
+      <c r="P282" s="5" t="str">
+        <v>比值大於一，代表分子相對分母如何？</v>
+      </c>
+      <c r="Q282" s="5" t="str">
+        <v>比值大於一，代表分子相對分母如何？ → 【模型觀察】肺尖 V/Q≈3.4、肺底≈0.63，何者正確？</v>
+      </c>
+      <c r="R282" s="5" t="str">
+        <v>選擇「肺尖通氣相對血流較多」。肺尖 V/Q≈3.4，表示通氣相對血流較多；不能據此說肺尖的絕對通氣量最多。</v>
+      </c>
+      <c r="S282" s="5" t="str">
+        <v>肺尖 V/Q≈3.4，表示通氣相對血流較多；不能據此說肺尖的絕對通氣量最多。</v>
+      </c>
+      <c r="T282" s="3" t="str">
+        <v>ventilation-perfusion；CH06 p.21–22</v>
+      </c>
+      <c r="U282" s="3"/>
+      <c r="V282" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W282" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X282" s="3"/>
+    </row>
+    <row r="283" ht="166" customHeight="1">
+      <c r="A283" s="3"/>
+      <c r="B283" s="4" t="str">
+        <v>gas-exchange-case-q05</v>
+      </c>
+      <c r="C283" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D283" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F283" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G283" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H283" s="5" t="str">
+        <v>【模型觀察】運動中的肌肉，O₂ 與 CO₂ 的擴散方向？</v>
+      </c>
+      <c r="I283" s="5" t="str">
+        <v>兩者都由血液進入細胞</v>
+      </c>
+      <c r="J283" s="5" t="str">
+        <v>O₂ 由細胞進入血液</v>
+      </c>
+      <c r="K283" s="5" t="str">
+        <v>O₂ 由血液進入細胞、CO₂ 由細胞進入血液</v>
+      </c>
+      <c r="L283" s="5" t="str">
+        <v>兩者都不移動</v>
+      </c>
+      <c r="M283" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N283" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O283" s="5" t="str">
+        <v>內呼吸是血液與組織細胞的交換；氧由血液進入細胞，CO₂ 由細胞進入血液。</v>
+      </c>
+      <c r="P283" s="5" t="str">
+        <v>從內呼吸的交換雙方判斷兩種氣體方向。</v>
+      </c>
+      <c r="Q283" s="5" t="str">
+        <v>從內呼吸的交換雙方判斷兩種氣體方向。 → 【模型觀察】運動中的肌肉，O₂ 與 CO₂ 的擴散方向？</v>
+      </c>
+      <c r="R283" s="5" t="str">
+        <v>選擇「O₂ 由血液進入細胞、CO₂ 由細胞進入血液」。內呼吸是血液與組織細胞的交換；氧由血液進入細胞，CO₂ 由細胞進入血液。</v>
+      </c>
+      <c r="S283" s="5" t="str">
+        <v>內呼吸是血液與組織細胞的交換；氧由血液進入細胞，CO₂ 由細胞進入血液。</v>
+      </c>
+      <c r="T283" s="3" t="str">
+        <v>external-respiration；CH06 p.4, 17, 20, 23</v>
+      </c>
+      <c r="U283" s="3"/>
+      <c r="V283" s="5" t="str">
+        <v>氣體交換</v>
+      </c>
+      <c r="W283" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/gas-exchange-v1/index.html</v>
+      </c>
+      <c r="X283" s="3"/>
+    </row>
+    <row r="284" ht="166" customHeight="1">
+      <c r="A284" s="3"/>
+      <c r="B284" s="4" t="str">
+        <v>o2-co2-transport-foundation-q01</v>
+      </c>
+      <c r="C284" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D284" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F284" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G284" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H284" s="5" t="str">
+        <v>血液中的氧大部分以何種形式運送？</v>
+      </c>
+      <c r="I284" s="5" t="str">
+        <v>直接溶於血漿</v>
+      </c>
+      <c r="J284" s="5" t="str">
+        <v>形成碳酸氫根</v>
+      </c>
+      <c r="K284" s="5" t="str">
+        <v>與白蛋白結合</v>
+      </c>
+      <c r="L284" s="5" t="str">
+        <v>與血紅素結合</v>
+      </c>
+      <c r="M284" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N284" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O284" s="5" t="str">
+        <v>約 97% 的氧與血紅素結合，只有約 3% 直接溶於血漿。</v>
+      </c>
+      <c r="P284" s="5" t="str">
+        <v>比較與血紅素結合及直接溶解的比例。</v>
+      </c>
+      <c r="Q284" s="5" t="str">
+        <v>比較與血紅素結合及直接溶解的比例。 → 血液中的氧大部分以何種形式運送？</v>
+      </c>
+      <c r="R284" s="5" t="str">
+        <v>選擇「與血紅素結合」。約 97% 的氧與血紅素結合，只有約 3% 直接溶於血漿。</v>
+      </c>
+      <c r="S284" s="5" t="str">
+        <v>約 97% 的氧與血紅素結合，只有約 3% 直接溶於血漿。</v>
+      </c>
+      <c r="T284" s="3" t="str">
+        <v>oxygen-transport；CH06 p.23–25；AB-05_13 p.16</v>
+      </c>
+      <c r="U284" s="3"/>
+      <c r="V284" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W284" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X284" s="3"/>
+    </row>
+    <row r="285" ht="166" customHeight="1">
+      <c r="A285" s="3"/>
+      <c r="B285" s="4" t="str">
+        <v>o2-co2-transport-foundation-q02</v>
+      </c>
+      <c r="C285" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D285" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E285" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F285" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G285" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H285" s="5" t="str">
+        <v>血基質中與氧結合的鐵？</v>
+      </c>
+      <c r="I285" s="5" t="str">
+        <v>二價鐵（Fe²⁺）</v>
+      </c>
+      <c r="J285" s="5" t="str">
+        <v>三價鐵（Fe³⁺）</v>
+      </c>
+      <c r="K285" s="5" t="str">
+        <v>鈣離子</v>
+      </c>
+      <c r="L285" s="5" t="str">
+        <v>鎂離子</v>
+      </c>
+      <c r="M285" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N285" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" s="5" t="str">
+        <v>血基質中心是二價鐵 Fe²⁺，可與氧可逆結合。</v>
+      </c>
+      <c r="P285" s="5" t="str">
+        <v>注意血基質中心鐵的價數。</v>
+      </c>
+      <c r="Q285" s="5" t="str">
+        <v>注意血基質中心鐵的價數。 → 血基質中與氧結合的鐵？</v>
+      </c>
+      <c r="R285" s="5" t="str">
+        <v>選擇「二價鐵（Fe²⁺）」。血基質中心是二價鐵 Fe²⁺，可與氧可逆結合。</v>
+      </c>
+      <c r="S285" s="5" t="str">
+        <v>血基質中心是二價鐵 Fe²⁺，可與氧可逆結合。</v>
+      </c>
+      <c r="T285" s="3" t="str">
+        <v>hemoglobin-oxygen；CH06 p.23–25, 27</v>
+      </c>
+      <c r="U285" s="3"/>
+      <c r="V285" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W285" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X285" s="3"/>
+    </row>
+    <row r="286" ht="166" customHeight="1">
+      <c r="A286" s="3"/>
+      <c r="B286" s="4" t="str">
+        <v>o2-co2-transport-foundation-q03</v>
+      </c>
+      <c r="C286" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D286" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F286" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G286" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H286" s="5" t="str">
+        <v>一分子血紅素最多攜帶幾分子氧？</v>
+      </c>
+      <c r="I286" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="J286" s="5" t="str">
+        <v>4</v>
+      </c>
+      <c r="K286" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L286" s="5" t="str">
+        <v>8</v>
+      </c>
+      <c r="M286" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N286" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O286" s="5" t="str">
+        <v>一分子血紅素有四個血基質，可攜帶四分子氧。</v>
+      </c>
+      <c r="P286" s="5" t="str">
+        <v>由血基質的數目推算可結合的氧數目。</v>
+      </c>
+      <c r="Q286" s="5" t="str">
+        <v>由血基質的數目推算可結合的氧數目。 → 一分子血紅素最多攜帶幾分子氧？</v>
+      </c>
+      <c r="R286" s="5" t="str">
+        <v>選擇「4」。一分子血紅素有四個血基質，可攜帶四分子氧。</v>
+      </c>
+      <c r="S286" s="5" t="str">
+        <v>一分子血紅素有四個血基質，可攜帶四分子氧。</v>
+      </c>
+      <c r="T286" s="3" t="str">
+        <v>hemoglobin-oxygen；CH06 p.23–25, 27</v>
+      </c>
+      <c r="U286" s="3"/>
+      <c r="V286" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W286" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X286" s="3"/>
+    </row>
+    <row r="287" ht="166" customHeight="1">
+      <c r="A287" s="3"/>
+      <c r="B287" s="4" t="str">
+        <v>o2-co2-transport-foundation-q04</v>
+      </c>
+      <c r="C287" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D287" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E287" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F287" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G287" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H287" s="5" t="str">
+        <v>下列何者使解離曲線右移？</v>
+      </c>
+      <c r="I287" s="5" t="str">
+        <v>pH 升高</v>
+      </c>
+      <c r="J287" s="5" t="str">
+        <v>溫度降低</v>
+      </c>
+      <c r="K287" s="5" t="str">
+        <v>溫度升高</v>
+      </c>
+      <c r="L287" s="5" t="str">
+        <v>2,3-DPG 減少</v>
+      </c>
+      <c r="M287" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N287" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O287" s="5" t="str">
+        <v>溫度升高使親和力降低、曲線右移，有利於釋氧。</v>
+      </c>
+      <c r="P287" s="5" t="str">
+        <v>比較活動肌肉的溫度與釋氧需求。</v>
+      </c>
+      <c r="Q287" s="5" t="str">
+        <v>比較活動肌肉的溫度與釋氧需求。 → 下列何者使解離曲線右移？</v>
+      </c>
+      <c r="R287" s="5" t="str">
+        <v>選擇「溫度升高」。溫度升高使親和力降低、曲線右移，有利於釋氧。</v>
+      </c>
+      <c r="S287" s="5" t="str">
+        <v>溫度升高使親和力降低、曲線右移，有利於釋氧。</v>
+      </c>
+      <c r="T287" s="3" t="str">
+        <v>oxygen-dissociation-curve；CH06 p.25–27</v>
+      </c>
+      <c r="U287" s="3"/>
+      <c r="V287" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W287" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X287" s="3"/>
+    </row>
+    <row r="288" ht="166" customHeight="1">
+      <c r="A288" s="3"/>
+      <c r="B288" s="4" t="str">
+        <v>o2-co2-transport-foundation-q05</v>
+      </c>
+      <c r="C288" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D288" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E288" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F288" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G288" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H288" s="5" t="str">
+        <v>CO₂ 在血液中最主要的運送形式？</v>
+      </c>
+      <c r="I288" s="5" t="str">
+        <v>直接溶解</v>
+      </c>
+      <c r="J288" s="5" t="str">
+        <v>碳醯胺基血紅素</v>
+      </c>
+      <c r="K288" s="5" t="str">
+        <v>與血基質鐵結合</v>
+      </c>
+      <c r="L288" s="5" t="str">
+        <v>碳酸氫根</v>
+      </c>
+      <c r="M288" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N288" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O288" s="5" t="str">
+        <v>約 70% 的 CO₂ 以 HCO₃⁻ 在血漿運送，是最大宗的形式。</v>
+      </c>
+      <c r="P288" s="5" t="str">
+        <v>比較三種 CO₂ 運送形式的比例。</v>
+      </c>
+      <c r="Q288" s="5" t="str">
+        <v>比較三種 CO₂ 運送形式的比例。 → CO₂ 在血液中最主要的運送形式？</v>
+      </c>
+      <c r="R288" s="5" t="str">
+        <v>選擇「碳酸氫根」。約 70% 的 CO₂ 以 HCO₃⁻ 在血漿運送，是最大宗的形式。</v>
+      </c>
+      <c r="S288" s="5" t="str">
+        <v>約 70% 的 CO₂ 以 HCO₃⁻ 在血漿運送，是最大宗的形式。</v>
+      </c>
+      <c r="T288" s="3" t="str">
+        <v>co2-transport；CH06 p.27–28</v>
+      </c>
+      <c r="U288" s="3"/>
+      <c r="V288" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W288" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X288" s="3"/>
+    </row>
+    <row r="289" ht="166" customHeight="1">
+      <c r="A289" s="3"/>
+      <c r="B289" s="4" t="str">
+        <v>o2-co2-transport-foundation-q06</v>
+      </c>
+      <c r="C289" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D289" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E289" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F289" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G289" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H289" s="5" t="str">
+        <v>紅血球內催化 CO₂ 與水反應的酶？</v>
+      </c>
+      <c r="I289" s="5" t="str">
+        <v>碳酸酐酶</v>
+      </c>
+      <c r="J289" s="5" t="str">
+        <v>胃蛋白酶</v>
+      </c>
+      <c r="K289" s="5" t="str">
+        <v>澱粉酶</v>
+      </c>
+      <c r="L289" s="5" t="str">
+        <v>脂肪酶</v>
+      </c>
+      <c r="M289" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N289" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" s="5" t="str">
+        <v>碳酸酐酶催化 CO₂ 與水形成碳酸，接著解離為 H⁺ 與 HCO₃⁻。</v>
+      </c>
+      <c r="P289" s="5" t="str">
+        <v>找出紅血球內加速 CO₂ 與水反應的酶。</v>
+      </c>
+      <c r="Q289" s="5" t="str">
+        <v>找出紅血球內加速 CO₂ 與水反應的酶。 → 紅血球內催化 CO₂ 與水反應的酶？</v>
+      </c>
+      <c r="R289" s="5" t="str">
+        <v>選擇「碳酸酐酶」。碳酸酐酶催化 CO₂ 與水形成碳酸，接著解離為 H⁺ 與 HCO₃⁻。</v>
+      </c>
+      <c r="S289" s="5" t="str">
+        <v>碳酸酐酶催化 CO₂ 與水形成碳酸，接著解離為 H⁺ 與 HCO₃⁻。</v>
+      </c>
+      <c r="T289" s="3" t="str">
+        <v>co2-transport；CH06 p.28</v>
+      </c>
+      <c r="U289" s="3"/>
+      <c r="V289" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W289" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X289" s="3"/>
+    </row>
+    <row r="290" ht="166" customHeight="1">
+      <c r="A290" s="3"/>
+      <c r="B290" s="4" t="str">
+        <v>o2-co2-transport-case-q01</v>
+      </c>
+      <c r="C290" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D290" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F290" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G290" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H290" s="5" t="str">
+        <v>【生活情境】馬拉松跑者腿部肌肉溫度升高、酸增加，血紅素對氧的親和力？</v>
+      </c>
+      <c r="I290" s="5" t="str">
+        <v>上升，抓住氧不放</v>
+      </c>
+      <c r="J290" s="5" t="str">
+        <v>下降，釋出更多氧給肌肉</v>
+      </c>
+      <c r="K290" s="5" t="str">
+        <v>不變</v>
+      </c>
+      <c r="L290" s="5" t="str">
+        <v>血紅素改與 CO₂ 結合而完全不攜氧</v>
+      </c>
+      <c r="M290" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N290" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O290" s="5" t="str">
+        <v>H⁺增加與溫度升高使曲線右移、親和力降低，因此有利於釋氧給肌肉。</v>
+      </c>
+      <c r="P290" s="5" t="str">
+        <v>將酸與溫度變化連到曲線移動及釋氧。</v>
+      </c>
+      <c r="Q290" s="5" t="str">
+        <v>將酸與溫度變化連到曲線移動及釋氧。 → 【生活情境】馬拉松跑者腿部肌肉溫度升高、酸增加，血紅素對氧的親和力？</v>
+      </c>
+      <c r="R290" s="5" t="str">
+        <v>選擇「下降，釋出更多氧給肌肉」。H⁺增加與溫度升高使曲線右移、親和力降低，因此有利於釋氧給肌肉。</v>
+      </c>
+      <c r="S290" s="5" t="str">
+        <v>H⁺增加與溫度升高使曲線右移、親和力降低，因此有利於釋氧給肌肉。</v>
+      </c>
+      <c r="T290" s="3" t="str">
+        <v>oxygen-dissociation-curve；CH06 p.25–27</v>
+      </c>
+      <c r="U290" s="3"/>
+      <c r="V290" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W290" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X290" s="3"/>
+    </row>
+    <row r="291" ht="166" customHeight="1">
+      <c r="A291" s="3"/>
+      <c r="B291" s="4" t="str">
+        <v>o2-co2-transport-case-q02</v>
+      </c>
+      <c r="C291" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D291" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E291" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F291" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G291" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H291" s="5" t="str">
+        <v>【模型觀察】血液從肺部流到 PO₂ 約 40 mmHg 的組織，血紅素飽和度約為？</v>
+      </c>
+      <c r="I291" s="5" t="str">
+        <v>25%</v>
+      </c>
+      <c r="J291" s="5" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K291" s="5" t="str">
+        <v>75%</v>
+      </c>
+      <c r="L291" s="5" t="str">
+        <v>100%</v>
+      </c>
+      <c r="M291" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N291" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O291" s="5" t="str">
+        <v>課本指出 PO₂ 40 mmHg 時，血紅素氧飽和度約為 75%。</v>
+      </c>
+      <c r="P291" s="5" t="str">
+        <v>在 S 形曲線上找 PO₂ 40 的對應高度。</v>
+      </c>
+      <c r="Q291" s="5" t="str">
+        <v>在 S 形曲線上找 PO₂ 40 的對應高度。 → 【模型觀察】血液從肺部流到 PO₂ 約 40 mmHg 的組織，血紅素飽和度約為？</v>
+      </c>
+      <c r="R291" s="5" t="str">
+        <v>選擇「75%」。課本指出 PO₂ 40 mmHg 時，血紅素氧飽和度約為 75%。</v>
+      </c>
+      <c r="S291" s="5" t="str">
+        <v>課本指出 PO₂ 40 mmHg 時，血紅素氧飽和度約為 75%。</v>
+      </c>
+      <c r="T291" s="3" t="str">
+        <v>oxygen-dissociation-curve；CH06 p.25</v>
+      </c>
+      <c r="U291" s="3"/>
+      <c r="V291" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W291" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X291" s="3"/>
+    </row>
+    <row r="292" ht="166" customHeight="1">
+      <c r="A292" s="3"/>
+      <c r="B292" s="4" t="str">
+        <v>o2-co2-transport-case-q03</v>
+      </c>
+      <c r="C292" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D292" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E292" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F292" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G292" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H292" s="5" t="str">
+        <v>【生理判讀】過度換氣使血中 CO₂ 減少、pH 上升，解離曲線？</v>
+      </c>
+      <c r="I292" s="5" t="str">
+        <v>右移，親和力下降</v>
+      </c>
+      <c r="J292" s="5" t="str">
+        <v>不移動</v>
+      </c>
+      <c r="K292" s="5" t="str">
+        <v>變成直線</v>
+      </c>
+      <c r="L292" s="5" t="str">
+        <v>左移，親和力增加</v>
+      </c>
+      <c r="M292" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N292" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O292" s="5" t="str">
+        <v>CO₂ 減少、pH 上升是右移條件的相反方向，使曲線左移、親和力增加。</v>
+      </c>
+      <c r="P292" s="5" t="str">
+        <v>用右移條件的相反方向判斷。</v>
+      </c>
+      <c r="Q292" s="5" t="str">
+        <v>用右移條件的相反方向判斷。 → 【生理判讀】過度換氣使血中 CO₂ 減少、pH 上升，解離曲線？</v>
+      </c>
+      <c r="R292" s="5" t="str">
+        <v>選擇「左移，親和力增加」。CO₂ 減少、pH 上升是右移條件的相反方向，使曲線左移、親和力增加。</v>
+      </c>
+      <c r="S292" s="5" t="str">
+        <v>CO₂ 減少、pH 上升是右移條件的相反方向，使曲線左移、親和力增加。</v>
+      </c>
+      <c r="T292" s="3" t="str">
+        <v>oxygen-dissociation-curve；CH06 p.25–27</v>
+      </c>
+      <c r="U292" s="3"/>
+      <c r="V292" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W292" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X292" s="3"/>
+    </row>
+    <row r="293" ht="166" customHeight="1">
+      <c r="A293" s="3"/>
+      <c r="B293" s="4" t="str">
+        <v>o2-co2-transport-case-q04</v>
+      </c>
+      <c r="C293" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D293" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E293" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F293" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G293" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H293" s="5" t="str">
+        <v>【模型觀察】HCO₃⁻由紅血球移到血漿時，哪個離子同時進入紅血球？</v>
+      </c>
+      <c r="I293" s="5" t="str">
+        <v>Cl⁻</v>
+      </c>
+      <c r="J293" s="5" t="str">
+        <v>Na⁺</v>
+      </c>
+      <c r="K293" s="5" t="str">
+        <v>K⁺</v>
+      </c>
+      <c r="L293" s="5" t="str">
+        <v>Ca²⁺</v>
+      </c>
+      <c r="M293" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N293" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O293" s="5" t="str">
+        <v>HCO₃⁻移出紅血球時 Cl⁻進入，這個交換稱氯轉移。</v>
+      </c>
+      <c r="P293" s="5" t="str">
+        <v>思考碳酸氫根移出紅血球時的離子交換。</v>
+      </c>
+      <c r="Q293" s="5" t="str">
+        <v>思考碳酸氫根移出紅血球時的離子交換。 → 【模型觀察】HCO₃⁻由紅血球移到血漿時，哪個離子同時進入紅血球？</v>
+      </c>
+      <c r="R293" s="5" t="str">
+        <v>選擇「Cl⁻」。HCO₃⁻移出紅血球時 Cl⁻進入，這個交換稱氯轉移。</v>
+      </c>
+      <c r="S293" s="5" t="str">
+        <v>HCO₃⁻移出紅血球時 Cl⁻進入，這個交換稱氯轉移。</v>
+      </c>
+      <c r="T293" s="3" t="str">
+        <v>co2-transport；CH06 p.28</v>
+      </c>
+      <c r="U293" s="3"/>
+      <c r="V293" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W293" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X293" s="3"/>
+    </row>
+    <row r="294" ht="166" customHeight="1">
+      <c r="A294" s="3"/>
+      <c r="B294" s="4" t="str">
+        <v>o2-co2-transport-case-q05</v>
+      </c>
+      <c r="C294" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D294" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F294" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G294" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H294" s="5" t="str">
+        <v>【生理判讀】一氧化碳使氧運送下降的主要原因？</v>
+      </c>
+      <c r="I294" s="5" t="str">
+        <v>CO 使溶解氧大增</v>
+      </c>
+      <c r="J294" s="5" t="str">
+        <v>CO 與血紅素親和力約為氧的 250 倍，佔據結合位置</v>
+      </c>
+      <c r="K294" s="5" t="str">
+        <v>CO 使紅血球數目立刻減半</v>
+      </c>
+      <c r="L294" s="5" t="str">
+        <v>CO 只溶在血漿中</v>
+      </c>
+      <c r="M294" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N294" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O294" s="5" t="str">
+        <v>CO 與血紅素的親和力約為氧的 250 倍，佔據結合位置，使氧運送下降。</v>
+      </c>
+      <c r="P294" s="5" t="str">
+        <v>比較 CO 與氧對同一結合位置的競爭。</v>
+      </c>
+      <c r="Q294" s="5" t="str">
+        <v>比較 CO 與氧對同一結合位置的競爭。 → 【生理判讀】一氧化碳使氧運送下降的主要原因？</v>
+      </c>
+      <c r="R294" s="5" t="str">
+        <v>選擇「CO 與血紅素親和力約為氧的 250 倍，佔據結合位置」。CO 與血紅素的親和力約為氧的 250 倍，佔據結合位置，使氧運送下降。</v>
+      </c>
+      <c r="S294" s="5" t="str">
+        <v>CO 與血紅素的親和力約為氧的 250 倍，佔據結合位置，使氧運送下降。</v>
+      </c>
+      <c r="T294" s="3" t="str">
+        <v>hemoglobin-oxygen；CH06 p.23–25, 27</v>
+      </c>
+      <c r="U294" s="3"/>
+      <c r="V294" s="5" t="str">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="W294" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/o2-co2-transport-v1/index.html</v>
+      </c>
+      <c r="X294" s="3"/>
+    </row>
+    <row r="295" ht="166" customHeight="1">
+      <c r="A295" s="3"/>
+      <c r="B295" s="4" t="str">
+        <v>respiratory-control-foundation-q01</v>
+      </c>
+      <c r="C295" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D295" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E295" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G295" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H295" s="5" t="str">
+        <v>直接刺激中樞化學受器的是？</v>
+      </c>
+      <c r="I295" s="5" t="str">
+        <v>血液中的 O₂</v>
+      </c>
+      <c r="J295" s="5" t="str">
+        <v>血液中的 Na⁺</v>
+      </c>
+      <c r="K295" s="5" t="str">
+        <v>腦脊髓液中的 H⁺</v>
+      </c>
+      <c r="L295" s="5" t="str">
+        <v>腦脊髓液中的葡萄糖</v>
+      </c>
+      <c r="M295" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N295" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O295" s="5" t="str">
+        <v>中樞化學受器直接感受腦脊髓液中的 H⁺，不是血中 H⁺直接穿越血腦障壁。</v>
+      </c>
+      <c r="P295" s="5" t="str">
+        <v>區分血中物質與受器直接接觸的腦脊髓液物質。</v>
+      </c>
+      <c r="Q295" s="5" t="str">
+        <v>區分血中物質與受器直接接觸的腦脊髓液物質。 → 直接刺激中樞化學受器的是？</v>
+      </c>
+      <c r="R295" s="5" t="str">
+        <v>選擇「腦脊髓液中的 H⁺」。中樞化學受器直接感受腦脊髓液中的 H⁺，不是血中 H⁺直接穿越血腦障壁。</v>
+      </c>
+      <c r="S295" s="5" t="str">
+        <v>中樞化學受器直接感受腦脊髓液中的 H⁺，不是血中 H⁺直接穿越血腦障壁。</v>
+      </c>
+      <c r="T295" s="3" t="str">
+        <v>central-chemoreceptor、hypercapnia；CH06 p.31, 33</v>
+      </c>
+      <c r="U295" s="3"/>
+      <c r="V295" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W295" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X295" s="3"/>
+    </row>
+    <row r="296" ht="166" customHeight="1">
+      <c r="A296" s="3"/>
+      <c r="B296" s="4" t="str">
+        <v>respiratory-control-foundation-q02</v>
+      </c>
+      <c r="C296" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D296" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F296" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G296" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H296" s="5" t="str">
+        <v>能穿越血腦障壁、間接刺激中樞受器的是？</v>
+      </c>
+      <c r="I296" s="5" t="str">
+        <v>血中 H⁺</v>
+      </c>
+      <c r="J296" s="5" t="str">
+        <v>HCO₃⁻</v>
+      </c>
+      <c r="K296" s="5" t="str">
+        <v>白蛋白</v>
+      </c>
+      <c r="L296" s="5" t="str">
+        <v>CO₂</v>
+      </c>
+      <c r="M296" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N296" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O296" s="5" t="str">
+        <v>血中 CO₂ 能穿越血腦障壁，在腦脊髓液增加 H⁺，間接刺激中樞受器。</v>
+      </c>
+      <c r="P296" s="5" t="str">
+        <v>哪種氣體能先通過障壁，再使腦脊髓液酸增加？</v>
+      </c>
+      <c r="Q296" s="5" t="str">
+        <v>哪種氣體能先通過障壁，再使腦脊髓液酸增加？ → 能穿越血腦障壁、間接刺激中樞受器的是？</v>
+      </c>
+      <c r="R296" s="5" t="str">
+        <v>選擇「CO₂」。血中 CO₂ 能穿越血腦障壁，在腦脊髓液增加 H⁺，間接刺激中樞受器。</v>
+      </c>
+      <c r="S296" s="5" t="str">
+        <v>血中 CO₂ 能穿越血腦障壁，在腦脊髓液增加 H⁺，間接刺激中樞受器。</v>
+      </c>
+      <c r="T296" s="3" t="str">
+        <v>central-chemoreceptor、hypercapnia；CH06 p.31, 33</v>
+      </c>
+      <c r="U296" s="3"/>
+      <c r="V296" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W296" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X296" s="3"/>
+    </row>
+    <row r="297" ht="166" customHeight="1">
+      <c r="A297" s="3"/>
+      <c r="B297" s="4" t="str">
+        <v>respiratory-control-foundation-q03</v>
+      </c>
+      <c r="C297" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D297" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E297" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F297" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G297" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H297" s="5" t="str">
+        <v>周邊化學受器對低氧明顯反應約在？</v>
+      </c>
+      <c r="I297" s="5" t="str">
+        <v>PO₂ 低於約 60 mmHg</v>
+      </c>
+      <c r="J297" s="5" t="str">
+        <v>PO₂ 高於 100 mmHg</v>
+      </c>
+      <c r="K297" s="5" t="str">
+        <v>PO₂ 低於 95 mmHg</v>
+      </c>
+      <c r="L297" s="5" t="str">
+        <v>PCO₂ 低於 35 mmHg</v>
+      </c>
+      <c r="M297" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N297" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O297" s="5" t="str">
+        <v>PO₂ 低於約 60 mmHg 時，周邊化學受器的低氧刺激明顯。</v>
+      </c>
+      <c r="P297" s="5" t="str">
+        <v>留意低氧刺激開始明顯的分壓界線。</v>
+      </c>
+      <c r="Q297" s="5" t="str">
+        <v>留意低氧刺激開始明顯的分壓界線。 → 周邊化學受器對低氧明顯反應約在？</v>
+      </c>
+      <c r="R297" s="5" t="str">
+        <v>選擇「PO₂ 低於約 60 mmHg」。PO₂ 低於約 60 mmHg 時，周邊化學受器的低氧刺激明顯。</v>
+      </c>
+      <c r="S297" s="5" t="str">
+        <v>PO₂ 低於約 60 mmHg 時，周邊化學受器的低氧刺激明顯。</v>
+      </c>
+      <c r="T297" s="3" t="str">
+        <v>central-chemoreceptor；CH06 p.31</v>
+      </c>
+      <c r="U297" s="3"/>
+      <c r="V297" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W297" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X297" s="3"/>
+    </row>
+    <row r="298" ht="166" customHeight="1">
+      <c r="A298" s="3"/>
+      <c r="B298" s="4" t="str">
+        <v>respiratory-control-foundation-q04</v>
+      </c>
+      <c r="C298" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D298" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F298" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G298" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H298" s="5" t="str">
+        <v>赫鮑二氏反射的傳入神經？</v>
+      </c>
+      <c r="I298" s="5" t="str">
+        <v>膈神經</v>
+      </c>
+      <c r="J298" s="5" t="str">
+        <v>迷走神經</v>
+      </c>
+      <c r="K298" s="5" t="str">
+        <v>舌下神經</v>
+      </c>
+      <c r="L298" s="5" t="str">
+        <v>副神經</v>
+      </c>
+      <c r="M298" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N298" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O298" s="5" t="str">
+        <v>肺牽張受器的訊息經迷走神經傳入呼吸中樞，抑制吸氣。</v>
+      </c>
+      <c r="P298" s="5" t="str">
+        <v>沿肺牽張受器到延髓、橋腦追蹤傳入路徑。</v>
+      </c>
+      <c r="Q298" s="5" t="str">
+        <v>沿肺牽張受器到延髓、橋腦追蹤傳入路徑。 → 赫鮑二氏反射的傳入神經？</v>
+      </c>
+      <c r="R298" s="5" t="str">
+        <v>選擇「迷走神經」。肺牽張受器的訊息經迷走神經傳入呼吸中樞，抑制吸氣。</v>
+      </c>
+      <c r="S298" s="5" t="str">
+        <v>肺牽張受器的訊息經迷走神經傳入呼吸中樞，抑制吸氣。</v>
+      </c>
+      <c r="T298" s="3" t="str">
+        <v>hering-breuer-reflex；CH06 p.34；AB-05_13 p.17–18</v>
+      </c>
+      <c r="U298" s="3"/>
+      <c r="V298" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W298" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X298" s="3"/>
+    </row>
+    <row r="299" ht="166" customHeight="1">
+      <c r="A299" s="3"/>
+      <c r="B299" s="4" t="str">
+        <v>respiratory-control-foundation-q05</v>
+      </c>
+      <c r="C299" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D299" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F299" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G299" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H299" s="5" t="str">
+        <v>正常血液 pH？</v>
+      </c>
+      <c r="I299" s="5" t="str">
+        <v>6.8–7.0</v>
+      </c>
+      <c r="J299" s="5" t="str">
+        <v>7.6–7.8</v>
+      </c>
+      <c r="K299" s="5" t="str">
+        <v>7.35–7.45</v>
+      </c>
+      <c r="L299" s="5" t="str">
+        <v>7.0–7.2</v>
+      </c>
+      <c r="M299" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N299" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O299" s="5" t="str">
+        <v>正常血液 pH 約為 7.35–7.45。</v>
+      </c>
+      <c r="P299" s="5" t="str">
+        <v>分清正常範圍與酸、鹼方向。</v>
+      </c>
+      <c r="Q299" s="5" t="str">
+        <v>分清正常範圍與酸、鹼方向。 → 正常血液 pH？</v>
+      </c>
+      <c r="R299" s="5" t="str">
+        <v>選擇「7.35–7.45」。正常血液 pH 約為 7.35–7.45。</v>
+      </c>
+      <c r="S299" s="5" t="str">
+        <v>正常血液 pH 約為 7.35–7.45。</v>
+      </c>
+      <c r="T299" s="3" t="str">
+        <v>acid-base-balance、hypercapnia、respiratory-alkalosis；CH09 p.37–41, 44–45</v>
+      </c>
+      <c r="U299" s="3"/>
+      <c r="V299" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W299" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X299" s="3"/>
+    </row>
+    <row r="300" ht="166" customHeight="1">
+      <c r="A300" s="3"/>
+      <c r="B300" s="4" t="str">
+        <v>respiratory-control-foundation-q06</v>
+      </c>
+      <c r="C300" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D300" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F300" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G300" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H300" s="5" t="str">
+        <v>PCO₂ 低於 35 mmHg、pH 上升，屬於哪個方向？</v>
+      </c>
+      <c r="I300" s="5" t="str">
+        <v>呼吸性酸中毒</v>
+      </c>
+      <c r="J300" s="5" t="str">
+        <v>代謝性酸中毒</v>
+      </c>
+      <c r="K300" s="5" t="str">
+        <v>代謝性鹼中毒</v>
+      </c>
+      <c r="L300" s="5" t="str">
+        <v>呼吸性鹼中毒</v>
+      </c>
+      <c r="M300" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N300" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O300" s="5" t="str">
+        <v>PCO₂ 低於 35 mmHg 是呼吸性鹼中毒方向。</v>
+      </c>
+      <c r="P300" s="5" t="str">
+        <v>比較 CO₂ 降低與血液 pH 上升的方向。</v>
+      </c>
+      <c r="Q300" s="5" t="str">
+        <v>比較 CO₂ 降低與血液 pH 上升的方向。 → PCO₂ 低於 35 mmHg、pH 上升，屬於哪個方向？</v>
+      </c>
+      <c r="R300" s="5" t="str">
+        <v>選擇「呼吸性鹼中毒」。PCO₂ 低於 35 mmHg 是呼吸性鹼中毒方向。</v>
+      </c>
+      <c r="S300" s="5" t="str">
+        <v>PCO₂ 低於 35 mmHg 是呼吸性鹼中毒方向。</v>
+      </c>
+      <c r="T300" s="3" t="str">
+        <v>acid-base-balance、hypercapnia、respiratory-alkalosis；CH09 p.37–41, 44–45</v>
+      </c>
+      <c r="U300" s="3"/>
+      <c r="V300" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W300" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X300" s="3"/>
+    </row>
+    <row r="301" ht="166" customHeight="1">
+      <c r="A301" s="3"/>
+      <c r="B301" s="4" t="str">
+        <v>respiratory-control-case-q01</v>
+      </c>
+      <c r="C301" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D301" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E301" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F301" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G301" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H301" s="5" t="str">
+        <v>【生活情境】閉氣一段時間後忍不住吸氣，最主要的驅動？</v>
+      </c>
+      <c r="I301" s="5" t="str">
+        <v>CO₂ 累積使腦脊髓液 H⁺增加，刺激中樞化學受器</v>
+      </c>
+      <c r="J301" s="5" t="str">
+        <v>O₂ 增加刺激周邊受器</v>
+      </c>
+      <c r="K301" s="5" t="str">
+        <v>肺牽張受器興奮</v>
+      </c>
+      <c r="L301" s="5" t="str">
+        <v>血液 pH 上升</v>
+      </c>
+      <c r="M301" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N301" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O301" s="5" t="str">
+        <v>CO₂ 能穿越血腦障壁，使腦脊髓液 H⁺增加，刺激中樞化學受器並驅動呼吸。</v>
+      </c>
+      <c r="P301" s="5" t="str">
+        <v>把 CO₂ 累積連到腦脊髓液與中樞受器。</v>
+      </c>
+      <c r="Q301" s="5" t="str">
+        <v>把 CO₂ 累積連到腦脊髓液與中樞受器。 → 【生活情境】閉氣一段時間後忍不住吸氣，最主要的驅動？</v>
+      </c>
+      <c r="R301" s="5" t="str">
+        <v>選擇「CO₂ 累積使腦脊髓液 H⁺增加，刺激中樞化學受器」。CO₂ 能穿越血腦障壁，使腦脊髓液 H⁺增加，刺激中樞化學受器並驅動呼吸。</v>
+      </c>
+      <c r="S301" s="5" t="str">
+        <v>CO₂ 能穿越血腦障壁，使腦脊髓液 H⁺增加，刺激中樞化學受器並驅動呼吸。</v>
+      </c>
+      <c r="T301" s="3" t="str">
+        <v>central-chemoreceptor、hypercapnia；CH06 p.31, 33</v>
+      </c>
+      <c r="U301" s="3"/>
+      <c r="V301" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W301" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X301" s="3"/>
+    </row>
+    <row r="302" ht="166" customHeight="1">
+      <c r="A302" s="3"/>
+      <c r="B302" s="4" t="str">
+        <v>respiratory-control-case-q02</v>
+      </c>
+      <c r="C302" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D302" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F302" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G302" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H302" s="5" t="str">
+        <v>【生活情境】初登玉山呼吸加快，血液最可能的變化？</v>
+      </c>
+      <c r="I302" s="5" t="str">
+        <v>PCO₂ 上升、pH 下降</v>
+      </c>
+      <c r="J302" s="5" t="str">
+        <v>PCO₂ 下降、pH 上升</v>
+      </c>
+      <c r="K302" s="5" t="str">
+        <v>PCO₂ 與 pH 都下降</v>
+      </c>
+      <c r="L302" s="5" t="str">
+        <v>兩者都不變</v>
+      </c>
+      <c r="M302" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N302" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O302" s="5" t="str">
+        <v>高海拔低氧刺激周邊受器，使換氣與 CO₂ 排出增加，可使 PCO₂ 下降、pH 上升。</v>
+      </c>
+      <c r="P302" s="5" t="str">
+        <v>高山低氧促進換氣後，CO₂ 排出如何改變？</v>
+      </c>
+      <c r="Q302" s="5" t="str">
+        <v>高山低氧促進換氣後，CO₂ 排出如何改變？ → 【生活情境】初登玉山呼吸加快，血液最可能的變化？</v>
+      </c>
+      <c r="R302" s="5" t="str">
+        <v>選擇「PCO₂ 下降、pH 上升」。高海拔低氧刺激周邊受器，使換氣與 CO₂ 排出增加，可使 PCO₂ 下降、pH 上升。</v>
+      </c>
+      <c r="S302" s="5" t="str">
+        <v>高海拔低氧刺激周邊受器，使換氣與 CO₂ 排出增加，可使 PCO₂ 下降、pH 上升。</v>
+      </c>
+      <c r="T302" s="3" t="str">
+        <v>exercise-ventilation、high-altitude-adaptation、respiratory-alkalosis；CH06 p.31, 35；CH09 p.45</v>
+      </c>
+      <c r="U302" s="3"/>
+      <c r="V302" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W302" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X302" s="3"/>
+    </row>
+    <row r="303" ht="166" customHeight="1">
+      <c r="A303" s="3"/>
+      <c r="B303" s="4" t="str">
+        <v>respiratory-control-case-q03</v>
+      </c>
+      <c r="C303" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D303" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F303" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G303" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H303" s="5" t="str">
+        <v>【生理判讀】深吸氣使肺過度擴張時，哪個反射抑制吸氣？</v>
+      </c>
+      <c r="I303" s="5" t="str">
+        <v>壓力受器反射</v>
+      </c>
+      <c r="J303" s="5" t="str">
+        <v>膝反射</v>
+      </c>
+      <c r="K303" s="5" t="str">
+        <v>赫鮑二氏反射</v>
+      </c>
+      <c r="L303" s="5" t="str">
+        <v>咳嗽反射</v>
+      </c>
+      <c r="M303" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N303" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O303" s="5" t="str">
+        <v>肺牽張受器經迷走神經傳入中樞，抑制吸氣、避免肺過度擴張，形成赫鮑二氏反射。</v>
+      </c>
+      <c r="P303" s="5" t="str">
+        <v>肺牽張受器的訊息對吸氣是促進還是抑制？</v>
+      </c>
+      <c r="Q303" s="5" t="str">
+        <v>肺牽張受器的訊息對吸氣是促進還是抑制？ → 【生理判讀】深吸氣使肺過度擴張時，哪個反射抑制吸氣？</v>
+      </c>
+      <c r="R303" s="5" t="str">
+        <v>選擇「赫鮑二氏反射」。肺牽張受器經迷走神經傳入中樞，抑制吸氣、避免肺過度擴張，形成赫鮑二氏反射。</v>
+      </c>
+      <c r="S303" s="5" t="str">
+        <v>肺牽張受器經迷走神經傳入中樞，抑制吸氣、避免肺過度擴張，形成赫鮑二氏反射。</v>
+      </c>
+      <c r="T303" s="3" t="str">
+        <v>hering-breuer-reflex；CH06 p.34；AB-05_13 p.17–18</v>
+      </c>
+      <c r="U303" s="3"/>
+      <c r="V303" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W303" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X303" s="3"/>
+    </row>
+    <row r="304" ht="166" customHeight="1">
+      <c r="A304" s="3"/>
+      <c r="B304" s="4" t="str">
+        <v>respiratory-control-case-q04</v>
+      </c>
+      <c r="C304" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D304" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F304" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G304" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H304" s="5" t="str">
+        <v>【生理判讀】肺泡換氣不足使 PCO₂ 超過 45 mmHg，屬於？</v>
+      </c>
+      <c r="I304" s="5" t="str">
+        <v>呼吸性鹼中毒</v>
+      </c>
+      <c r="J304" s="5" t="str">
+        <v>代謝性鹼中毒</v>
+      </c>
+      <c r="K304" s="5" t="str">
+        <v>pH 不受影響</v>
+      </c>
+      <c r="L304" s="5" t="str">
+        <v>呼吸性酸中毒，腎臟排酸、保留 HCO₃⁻ 代償</v>
+      </c>
+      <c r="M304" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N304" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O304" s="5" t="str">
+        <v>PCO₂ 超過 45 mmHg 為呼吸性酸中毒方向；腎臟可排酸、保留 HCO₃⁻代償。</v>
+      </c>
+      <c r="P304" s="5" t="str">
+        <v>依 PCO₂ 的界線判方向，再看腎臟代償。</v>
+      </c>
+      <c r="Q304" s="5" t="str">
+        <v>依 PCO₂ 的界線判方向，再看腎臟代償。 → 【生理判讀】肺泡換氣不足使 PCO₂ 超過 45 mmHg，屬於？</v>
+      </c>
+      <c r="R304" s="5" t="str">
+        <v>選擇「呼吸性酸中毒，腎臟排酸、保留 HCO₃⁻ 代償」。PCO₂ 超過 45 mmHg 為呼吸性酸中毒方向；腎臟可排酸、保留 HCO₃⁻代償。</v>
+      </c>
+      <c r="S304" s="5" t="str">
+        <v>PCO₂ 超過 45 mmHg 為呼吸性酸中毒方向；腎臟可排酸、保留 HCO₃⁻代償。</v>
+      </c>
+      <c r="T304" s="3" t="str">
+        <v>acid-base-balance、hypercapnia、respiratory-alkalosis；CH09 p.37–41, 44–45</v>
+      </c>
+      <c r="U304" s="3"/>
+      <c r="V304" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W304" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X304" s="3"/>
+    </row>
+    <row r="305" ht="166" customHeight="1">
+      <c r="A305" s="3"/>
+      <c r="B305" s="4" t="str">
+        <v>respiratory-control-case-q05</v>
+      </c>
+      <c r="C305" s="5" t="str">
+        <v>呼吸系統</v>
+      </c>
+      <c r="D305" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="E305" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F305" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G305" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H305" s="5" t="str">
+        <v>【模型觀察】依 pH＝6.1＋log（HCO₃⁻/H₂CO₃），HCO₃⁻ 不變而 H₂CO₃ 增加，pH？</v>
+      </c>
+      <c r="I305" s="5" t="str">
+        <v>下降</v>
+      </c>
+      <c r="J305" s="5" t="str">
+        <v>上升</v>
+      </c>
+      <c r="K305" s="5" t="str">
+        <v>不變</v>
+      </c>
+      <c r="L305" s="5" t="str">
+        <v>固定為 6.1</v>
+      </c>
+      <c r="M305" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N305" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O305" s="5" t="str">
+        <v>H₂CO₃ 增加使 HCO₃⁻/H₂CO₃ 比值降低，因此依公式 pH 下降。</v>
+      </c>
+      <c r="P305" s="5" t="str">
+        <v>分母增加而分子固定，比值與對數如何變化？</v>
+      </c>
+      <c r="Q305" s="5" t="str">
+        <v>分母增加而分子固定，比值與對數如何變化？ → 【模型觀察】依 pH＝6.1＋log（HCO₃⁻/H₂CO₃），HCO₃⁻ 不變而 H₂CO₃ 增加，pH？</v>
+      </c>
+      <c r="R305" s="5" t="str">
+        <v>選擇「下降」。H₂CO₃ 增加使 HCO₃⁻/H₂CO₃ 比值降低，因此依公式 pH 下降。</v>
+      </c>
+      <c r="S305" s="5" t="str">
+        <v>H₂CO₃ 增加使 HCO₃⁻/H₂CO₃ 比值降低，因此依公式 pH 下降。</v>
+      </c>
+      <c r="T305" s="3" t="str">
+        <v>acid-base-balance、hypercapnia、respiratory-alkalosis；CH09 p.37–41, 44–45</v>
+      </c>
+      <c r="U305" s="3"/>
+      <c r="V305" s="5" t="str">
+        <v>呼吸調節</v>
+      </c>
+      <c r="W305" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/respiratory-control-v1/index.html</v>
+      </c>
+      <c r="X305" s="3"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="M2:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -23440,7 +28676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23709,10 +28945,8 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>227 題</t>
-        </is>
+      <c r="B23" t="str">
+        <v>304 題</v>
       </c>
     </row>
     <row r="24" ht="45" hidden="0" customHeight="1">
@@ -23845,6 +29079,62 @@
         <is>
           <t>11 題｜https://albertchang1008-alt.github.io/115-1-AP2/materials/lymphoid-organs-v1/index.html；單元：淋巴系統；6 先備＋5 情境</t>
         </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" t="str" s="5">
+        <v>呼吸道的構造</v>
+      </c>
+      <c r="B35" t="str" s="5">
+        <v>11 題｜public/materials/airway-structure-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" t="str" s="5">
+        <v>肺與胸膜</v>
+      </c>
+      <c r="B36" t="str" s="5">
+        <v>11 題｜public/materials/lungs-pleura-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" t="str" s="5">
+        <v>肺通氣與呼吸力學</v>
+      </c>
+      <c r="B37" t="str" s="5">
+        <v>11 題｜public/materials/breathing-mechanics-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" t="str" s="5">
+        <v>肺容積與肺功能</v>
+      </c>
+      <c r="B38" t="str" s="5">
+        <v>11 題｜public/materials/lung-function-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" t="str" s="5">
+        <v>氣體交換</v>
+      </c>
+      <c r="B39" t="str" s="5">
+        <v>11 題｜public/materials/gas-exchange-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" t="str" s="5">
+        <v>氧與二氧化碳的運輸</v>
+      </c>
+      <c r="B40" t="str" s="5">
+        <v>11 題｜public/materials/o2-co2-transport-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" t="str" s="5">
+        <v>呼吸調節</v>
+      </c>
+      <c r="B41" t="str" s="5">
+        <v>11 題｜public/materials/respiratory-control-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
       </c>
     </row>
   </sheetData>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -23471,8 +23471,10 @@
       <c r="P229" s="5" t="str">
         <v>比較鼻腔後方與口腔後方的分界。</v>
       </c>
-      <c r="Q229" s="5" t="str">
-        <v>比較鼻腔後方與口腔後方的分界。 → 鼻咽與口咽的分界參考構造？</v>
+      <c r="Q229" s="5" t="inlineStr">
+        <is>
+          <t>鼻咽位在鼻腔後方，口咽則對應口腔後方，兩者上下位置有何不同？→ 要分出這兩段，應找口腔後方的哪個腭部構造作為邊界？</t>
+        </is>
       </c>
       <c r="R229" s="5" t="str">
         <v>選擇「軟腭」。軟腭是區分鼻咽與口咽的參考邊界。</v>
@@ -23539,8 +23541,10 @@
       <c r="P230" s="5" t="str">
         <v>從鼓膜兩側的壓力平衡思考通路。</v>
       </c>
-      <c r="Q230" s="5" t="str">
-        <v>從鼓膜兩側的壓力平衡思考通路。 → 耳咽管連通哪兩處？</v>
+      <c r="Q230" s="5" t="inlineStr">
+        <is>
+          <t>耳咽管能讓鼓膜兩側的壓力較平衡，通路的一端應通往哪個耳部空間？→ 另一端在咽的哪一段開口，會是外耳道嗎？</t>
+        </is>
       </c>
       <c r="R230" s="5" t="str">
         <v>選擇「鼻咽與中耳」。耳咽管開口在鼻咽，連通中耳；它不連到外耳道。</v>
@@ -23607,8 +23611,10 @@
       <c r="P231" s="5" t="str">
         <v>找出構成頸前突出輪廓的單一軟骨。</v>
       </c>
-      <c r="Q231" s="5" t="str">
-        <v>找出構成頸前突出輪廓的單一軟骨。 → 喉結由哪塊軟骨形成？</v>
+      <c r="Q231" s="5" t="inlineStr">
+        <is>
+          <t>喉結是頸前可辨認的突出輪廓，應從喉的支撐構造還是腺體尋找？→ 喉的單一軟骨中，哪一塊形成這個輪廓而不是負責吞嚥保護？</t>
+        </is>
       </c>
       <c r="R231" s="5" t="str">
         <v>選擇「甲狀軟骨」。甲狀軟骨形成喉結；它屬於單一的喉軟骨。</v>
@@ -23675,8 +23681,10 @@
       <c r="P232" s="5" t="str">
         <v>區分發聲連接構造與吞嚥保護構造。</v>
       </c>
-      <c r="Q232" s="5" t="str">
-        <v>區分發聲連接構造與吞嚥保護構造。 → 與聲帶相連、參與發聲的成對軟骨？</v>
+      <c r="Q232" s="5" t="inlineStr">
+        <is>
+          <t>發聲時要找與聲帶連接的構造，和吞嚥時蓋住入口的構造會相同嗎？→ 在成對的喉軟骨中，哪一組與聲帶相連並參與發聲？</t>
+        </is>
       </c>
       <c r="R232" s="5" t="str">
         <v>選擇「杓狀軟骨」。杓狀軟骨與聲帶相連並參與發聲；會厭主要保護吞嚥時的喉入口。</v>
@@ -23743,8 +23751,10 @@
       <c r="P233" s="5" t="str">
         <v>想想黏液要靠什麼構造往外移動。</v>
       </c>
-      <c r="Q233" s="5" t="str">
-        <v>想想黏液要靠什麼構造往外移動。 → 氣管內襯的上皮？</v>
+      <c r="Q233" s="5" t="inlineStr">
+        <is>
+          <t>氣管要把黏液及附著物往外清除，內襯表面需要哪種可活動的構造？→ 配合分泌黏液的杯狀細胞，哪個上皮名稱同時符合纖毛與柱狀的特徵？</t>
+        </is>
       </c>
       <c r="R233" s="5" t="str">
         <v>選擇「偽複層纖毛柱狀上皮」。氣管內襯偽複層纖毛柱狀上皮；纖毛與杯狀細胞的黏液協同清潔空氣。</v>
@@ -23811,8 +23821,10 @@
       <c r="P234" s="5" t="str">
         <v>從管徑、長度與中線夾角比較兩側。</v>
       </c>
-      <c r="Q234" s="5" t="str">
-        <v>從管徑、長度與中線夾角比較兩側。 → 右主支氣管與左主支氣管相比？</v>
+      <c r="Q234" s="5" t="inlineStr">
+        <is>
+          <t>左右主支氣管分出後，兩側與中線的夾角會完全一樣嗎？→ 異物較容易沿哪一側進入，該側的長度、管徑和走向分別有何特徵？</t>
+        </is>
       </c>
       <c r="R234" s="5" t="str">
         <v>選擇「較短、較寬且較垂直」。右主支氣管較短、較寬且較垂直，與中線的夾角較小。</v>
@@ -23879,8 +23891,10 @@
       <c r="P235" s="5" t="str">
         <v>吞嚥後耳悶改善，先找連通中耳的通道。</v>
       </c>
-      <c r="Q235" s="5" t="str">
-        <v>吞嚥後耳悶改善，先找連通中耳的通道。 → 【生活情境】搭飛機下降時耳朵悶脹，吞口水後改善，是哪個構造平衡了中耳壓力？</v>
+      <c r="Q235" s="5" t="inlineStr">
+        <is>
+          <t>下降時耳悶在吞嚥後改善，表示哪個耳部空間的壓力得到調整？→ 從鼻咽通往這個空間、而非通往外耳道的通路叫什麼？</t>
+        </is>
       </c>
       <c r="R235" s="5" t="str">
         <v>選擇「耳咽管」。耳咽管連通鼻咽與中耳，使鼓膜兩側壓力較能平衡。</v>
@@ -23947,8 +23961,10 @@
       <c r="P236" s="5" t="str">
         <v>觀察吞嚥時喉的位置與入口如何改變。</v>
       </c>
-      <c r="Q236" s="5" t="str">
-        <v>觀察吞嚥時喉的位置與入口如何改變。 → 【生理判讀】吞嚥時食物沒有誤入氣管，主要因為？</v>
+      <c r="Q236" s="5" t="inlineStr">
+        <is>
+          <t>吞嚥時食物要避開呼吸道，喉入口應保持敞開還是受到遮蓋？→ 這時喉的位置如何移動，又由哪個構造負責蓋住入口？</t>
+        </is>
       </c>
       <c r="R236" s="5" t="str">
         <v>選擇「喉上提、會厭蓋住喉入口」。吞嚥時喉上提，會厭蓋住喉入口，防止食物誤入氣管。</v>
@@ -24015,8 +24031,10 @@
       <c r="P237" s="5" t="str">
         <v>先確認氣管與食道的前後位置。</v>
       </c>
-      <c r="Q237" s="5" t="str">
-        <v>先確認氣管與食道的前後位置。 → 【模型觀察】氣管 C 形軟骨環的缺口朝向？</v>
+      <c r="Q237" s="5" t="inlineStr">
+        <is>
+          <t>氣管與食道並列時，供空氣通過的管道位在前面還是後面？→ C 形軟骨環的開口朝向食道，換成前後方向應如何判斷？</t>
+        </is>
       </c>
       <c r="R237" s="5" t="str">
         <v>選擇「後方的食道」。氣管在食道前方，C 形軟骨環的缺口朝向後方食道。</v>
@@ -24083,8 +24101,10 @@
       <c r="P238" s="5" t="str">
         <v>沿吸入方向比較左右主支氣管的形狀。</v>
       </c>
-      <c r="Q238" s="5" t="str">
-        <v>沿吸入方向比較左右主支氣管的形狀。 → 【生活情境】小孩吃花生時嗆到，吸入的花生較容易卡在哪裡？</v>
+      <c r="Q238" s="5" t="inlineStr">
+        <is>
+          <t>花生進入氣管後，較容易沿哪一種支氣管走向繼續往下？→ 比較兩側的長度、寬度及與中線的夾角，哪一側較符合這條路徑？</t>
+        </is>
       </c>
       <c r="R238" s="5" t="str">
         <v>選擇「右主支氣管，因其較短、寬且垂直」。右主支氣管較短、寬且垂直，因此吸入的異物較容易卡住右側。</v>
@@ -24151,8 +24171,10 @@
       <c r="P239" s="5" t="str">
         <v>依主支氣管到終末細支氣管的順序比較管壁。</v>
       </c>
-      <c r="Q239" s="5" t="str">
-        <v>依主支氣管到終末細支氣管的順序比較管壁。 → 【模型觀察】沿支氣管樹往下，軟骨與平滑肌的變化？</v>
+      <c r="Q239" s="5" t="inlineStr">
+        <is>
+          <t>沿主支氣管走向終末細支氣管時，管壁的支撐組成會維持不變嗎？→ 到細支氣管時還有軟骨嗎，平滑肌的相對多寡又如何改變？</t>
+        </is>
       </c>
       <c r="R239" s="5" t="str">
         <v>選擇「軟骨漸少、細支氣管已無軟骨且平滑肌較多」。越往下軟骨越少；細支氣管已無軟骨，但平滑肌較多。</v>
@@ -24219,8 +24241,10 @@
       <c r="P240" s="5" t="str">
         <v>數右肺的裂線，再看分成幾個區域。</v>
       </c>
-      <c r="Q240" s="5" t="str">
-        <v>數右肺的裂線，再看分成幾個區域。 → 右肺的分葉？</v>
+      <c r="Q240" s="5" t="inlineStr">
+        <is>
+          <t>右肺表面可辨認一條水平走向與一條斜走的裂線，兩者會分出哪些區域？→ 依上、中、下的位置整理後，分葉數和分隔裂線應如何配對？</t>
+        </is>
       </c>
       <c r="R240" s="5" t="str">
         <v>選擇「三葉，以水平裂與斜裂分隔」。右肺由水平裂與斜裂分成上、中、下三葉。</v>
@@ -24287,8 +24311,10 @@
       <c r="P241" s="5" t="str">
         <v>從左右肺的前緣找凹口。</v>
       </c>
-      <c r="Q241" s="5" t="str">
-        <v>從左右肺的前緣找凹口。 → 心切跡位於？</v>
+      <c r="Q241" s="5" t="inlineStr">
+        <is>
+          <t>比較兩側肺的前緣時，哪一側可見向內凹入的缺口？→ 這一側只有上、下兩葉，凹口是在肺的前方邊緣還是肺尖？</t>
+        </is>
       </c>
       <c r="R241" s="5" t="str">
         <v>選擇「左肺前緣」。心切跡位於左肺前緣；左肺只有上、下兩葉。</v>
@@ -24355,8 +24381,10 @@
       <c r="P242" s="5" t="str">
         <v>分清貼肺表面與貼胸腔壁的兩層。</v>
       </c>
-      <c r="Q242" s="5" t="str">
-        <v>分清貼肺表面與貼胸腔壁的兩層。 → 覆蓋在肺表面的胸膜？</v>
+      <c r="Q242" s="5" t="inlineStr">
+        <is>
+          <t>胸膜一層隨肺表面貼附，另一層則貼胸腔壁，兩者覆蓋的對象有何不同？→ 要找直接包住肺的那一層，名稱中的層別應如何選擇？</t>
+        </is>
       </c>
       <c r="R242" s="5" t="str">
         <v>選擇「臟層胸膜」。臟層胸膜覆蓋肺表面，壁層胸膜貼胸腔壁。</v>
@@ -24423,8 +24451,10 @@
       <c r="P243" s="5" t="str">
         <v>氣體交換需要薄而連續的肺泡內襯。</v>
       </c>
-      <c r="Q243" s="5" t="str">
-        <v>氣體交換需要薄而連續的肺泡內襯。 → 構成肺泡壁連續內襯、參與氣體交換的是？</v>
+      <c r="Q243" s="5" t="inlineStr">
+        <is>
+          <t>肺泡要讓氣體通過，內襯適合薄而連續的細胞還是專門清除灰塵的細胞？→ 哪一型具有單層鱗狀的形態，能形成這層交換表面？</t>
+        </is>
       </c>
       <c r="R243" s="5" t="str">
         <v>選擇「第一型肺泡細胞」。第一型肺泡細胞是單層鱗狀上皮，構成連續內襯並參與氣體交換。</v>
@@ -24491,8 +24521,10 @@
       <c r="P244" s="5" t="str">
         <v>將分泌功能與氣體交換、清除功能分開。</v>
       </c>
-      <c r="Q244" s="5" t="str">
-        <v>將分泌功能與氣體交換、清除功能分開。 → 分泌表面張力素的是？</v>
+      <c r="Q244" s="5" t="inlineStr">
+        <is>
+          <t>肺泡內有交換、分泌和清除等不同工作，表面張力素應歸在哪一類功能？→ 排除形成薄壁與吞噬灰塵的細胞後，應選哪一型細胞？</t>
+        </is>
       </c>
       <c r="R244" s="5" t="str">
         <v>選擇「第二型肺泡細胞」。第二型肺泡細胞分泌表面張力素；第一型參與交換，巨噬細胞負責清除。</v>
@@ -24559,8 +24591,10 @@
       <c r="P245" s="5" t="str">
         <v>沿肺泡到微血管列出薄層的順序。</v>
       </c>
-      <c r="Q245" s="5" t="str">
-        <v>沿肺泡到微血管列出薄層的順序。 → 呼吸膜不包括？</v>
+      <c r="Q245" s="5" t="inlineStr">
+        <is>
+          <t>由肺泡氣體走到微血管血液，首先要穿過薄的交換內襯，接著還有哪些薄層？→ 專門分泌表面張力素的那一型，也在這個交換序列裡嗎？</t>
+        </is>
       </c>
       <c r="R245" s="5" t="str">
         <v>選擇「第二型肺泡細胞」。呼吸膜包括第一型細胞、基底膜、間質與微血管內皮；第二型細胞不在這個薄層序列中。</v>
@@ -24627,8 +24661,10 @@
       <c r="P246" s="5" t="str">
         <v>在張力固定時，看半徑在公式的分子還是分母。</v>
       </c>
-      <c r="Q246" s="5" t="str">
-        <v>在張力固定時，看半徑在公式的分子還是分母。 → 【模型觀察】依 P＝2T/r，表面張力相同時哪顆肺泡較易塌陷？</v>
+      <c r="Q246" s="5" t="inlineStr">
+        <is>
+          <t>表面張力固定時，P＝2T/r 中分母縮小會讓所需壓力往哪個方向改變？→ 維持張開所需壓力變大時，哪一種大小的肺泡較容易塌陷？</t>
+        </is>
       </c>
       <c r="R246" s="5" t="str">
         <v>選擇「半徑較小的肺泡」。P＝2T/r；張力相同時半徑越小所需壓力越大，較易塌陷。</v>
@@ -24695,8 +24731,10 @@
       <c r="P247" s="5" t="str">
         <v>先想表面張力素不足會如何影響肺泡擴張。</v>
       </c>
-      <c r="Q247" s="5" t="str">
-        <v>先想表面張力素不足會如何影響肺泡擴張。 → 【生理判讀】早產兒呼吸困難，最可能與哪種細胞分泌不足有關？</v>
+      <c r="Q247" s="5" t="inlineStr">
+        <is>
+          <t>早產兒若缺少讓肺泡容易擴張的分泌物，肺泡的塌陷傾向會如何改變？→ 這種分泌物負責降低什麼，又由哪一型細胞製造？</t>
+        </is>
       </c>
       <c r="R247" s="5" t="str">
         <v>選擇「第二型肺泡細胞」。表面張力素降低張力，幫助肺泡擴張與維持；不足時塌陷傾向增加。</v>
@@ -24763,8 +24801,10 @@
       <c r="P248" s="5" t="str">
         <v>比較薄膜與厚膜的擴散條件。</v>
       </c>
-      <c r="Q248" s="5" t="str">
-        <v>比較薄膜與厚膜的擴散條件。 → 【生理判讀】肺纖維化使呼吸膜變厚，最直接的影響？</v>
+      <c r="Q248" s="5" t="inlineStr">
+        <is>
+          <t>纖維化讓氣體穿越的膜層變厚，與薄膜相比是否仍同樣有利於通過？→ 肺泡與血液之間的交換速度，應朝較快還是較慢的方向變化？</t>
+        </is>
       </c>
       <c r="R248" s="5" t="str">
         <v>選擇「氣體擴散變慢」。呼吸膜薄且面積廣利於擴散；膜變厚會使氣體擴散變慢。</v>
@@ -24831,8 +24871,10 @@
       <c r="P249" s="5" t="str">
         <v>分清肺泡壁細胞與腔內清除細胞的功能。</v>
       </c>
-      <c r="Q249" s="5" t="str">
-        <v>分清肺泡壁細胞與腔內清除細胞的功能。 → 【模型觀察】吸入的灰塵到達肺泡後，主要由誰清除？</v>
+      <c r="Q249" s="5" t="inlineStr">
+        <is>
+          <t>灰塵已到肺泡腔內，接下來需要的是形成交換內襯還是吞噬清除的功能？→ 在肺泡細胞中，哪一種專門處理這些灰塵與碎片？</t>
+        </is>
       </c>
       <c r="R249" s="5" t="str">
         <v>選擇「肺泡巨噬細胞」。肺泡巨噬細胞清除肺泡內的灰塵與碎片。</v>
@@ -24899,8 +24941,10 @@
       <c r="P250" s="5" t="str">
         <v>找出肺內側面讓多種構造進出的區域。</v>
       </c>
-      <c r="Q250" s="5" t="str">
-        <v>找出肺內側面讓多種構造進出的區域。 → 【模型觀察】肺標本內側面，支氣管與肺血管進出的區域？</v>
+      <c r="Q250" s="5" t="inlineStr">
+        <is>
+          <t>支氣管與肺血管共同進出肺時，所在的是肺尖、肺底還是內側面？→ 這個進出區域和通過其中的整組構造，分別應稱為什麼？</t>
+        </is>
       </c>
       <c r="R250" s="5" t="str">
         <v>選擇「肺門」。肺門是支氣管、肺血管、淋巴管與神經進出肺的區域；進出的構造合稱肺根。</v>
@@ -24967,8 +25011,10 @@
       <c r="P251" s="5" t="str">
         <v>區分平靜吸氣肌與用力呼氣肌。</v>
       </c>
-      <c r="Q251" s="5" t="str">
-        <v>區分平靜吸氣肌與用力呼氣肌。 → 平靜吸氣主要由哪些肌肉收縮？</v>
+      <c r="Q251" s="5" t="inlineStr">
+        <is>
+          <t>平靜吸氣需要胸腔擴大，應先找吸氣肌的主動作用還是呼氣時的回縮？→ 主要參與的是哪兩種肌肉，和用力呼氣的肌群有何不同？</t>
+        </is>
       </c>
       <c r="R251" s="5" t="str">
         <v>選擇「橫膈與外肋間肌」。平靜吸氣主要靠橫膈與外肋間肌收縮。</v>
@@ -25035,8 +25081,10 @@
       <c r="P252" s="5" t="str">
         <v>想想平靜呼氣是否需要額外呼氣肌收縮。</v>
       </c>
-      <c r="Q252" s="5" t="str">
-        <v>想想平靜呼氣是否需要額外呼氣肌收縮。 → 平靜呼氣主要靠？</v>
+      <c r="Q252" s="5" t="inlineStr">
+        <is>
+          <t>平靜呼氣接在吸氣之後，原本工作的肌肉還要持續主動出力嗎？→ 當這些肌肉不再維持吸氣，肺本身的哪個特性可讓氣體呼出？</t>
+        </is>
       </c>
       <c r="R252" s="5" t="str">
         <v>選擇「吸氣肌放鬆與肺的彈性回縮」。平靜呼氣主要靠吸氣肌放鬆與肺的彈性回縮。</v>
@@ -25103,8 +25151,10 @@
       <c r="P253" s="5" t="str">
         <v>確認肺內與胸膜腔之間的壓差如何定義。</v>
       </c>
-      <c r="Q253" s="5" t="str">
-        <v>確認肺內與胸膜腔之間的壓差如何定義。 → 肺間壓＝？</v>
+      <c r="Q253" s="5" t="inlineStr">
+        <is>
+          <t>題目中的壓差比較的是肺內與胸膜腔這兩個位置，和外界氣流壓差相同嗎？→ 以肺內為起點作減法時，應扣除哪個位置的壓力？</t>
+        </is>
       </c>
       <c r="R253" s="5" t="str">
         <v>選擇「肺內壓－胸內壓」。肺間壓是肺內壓減去胸內壓。</v>
@@ -25171,8 +25221,10 @@
       <c r="P254" s="5" t="str">
         <v>負壓是相對哪個參考壓力而言？</v>
       </c>
-      <c r="Q254" s="5" t="str">
-        <v>負壓是相對哪個參考壓力而言？ → 平時胸內壓與大氣壓相比？</v>
+      <c r="Q254" s="5" t="inlineStr">
+        <is>
+          <t>胸內壓被稱為負壓時，是拿外界作參考，還是指絕對壓力小於零？→ 胸膜腔的壓力在這個參考值的哪一側，才符合通常的情況？</t>
+        </is>
       </c>
       <c r="R254" s="5" t="str">
         <v>選擇「較低」。胸內壓通常低於大氣壓；負壓是相對大氣壓，並非絕對壓力小於零。</v>
@@ -25239,8 +25291,10 @@
       <c r="P255" s="5" t="str">
         <v>把容積變化放在分子、壓力變化放在分母。</v>
       </c>
-      <c r="Q255" s="5" t="str">
-        <v>把容積變化放在分子、壓力變化放在分母。 → 肺順應性的意義？</v>
+      <c r="Q255" s="5" t="inlineStr">
+        <is>
+          <t>比較肺能否容易撐開時，只看壓力大小，還是要同時看容積的反應？→ 同樣肺間壓變化帶來更多容積改變，應如何用兩者的比值表達？</t>
+        </is>
       </c>
       <c r="R255" s="5" t="str">
         <v>選擇「肺間壓改變時肺容積改變的多寡（ΔV/ΔP）」。順應性 C＝ΔV/ΔP，表示肺間壓改變時肺容積改變的多寡。</v>
@@ -25307,8 +25361,10 @@
       <c r="P256" s="5" t="str">
         <v>分清容易撐開與容易縮回兩件事。</v>
       </c>
-      <c r="Q256" s="5" t="str">
-        <v>分清容易撐開與容易縮回兩件事。 → 肺氣腫的肺順應性？</v>
+      <c r="Q256" s="5" t="inlineStr">
+        <is>
+          <t>肺氣腫的肺回縮變差，同樣的肺間壓變化下，撐開的容積會變多還是變少？→ 依 C＝ΔV/ΔP，ΔV 變大時，順應性朝哪個方向改變？</t>
+        </is>
       </c>
       <c r="R256" s="5" t="str">
         <v>選擇「增加」。肺氣腫的順應性增加，但彈性回縮變差，容易有氣體滯留。</v>
@@ -25375,8 +25431,10 @@
       <c r="P257" s="5" t="str">
         <v>將吸氣時肺內壓與外界壓力比較。</v>
       </c>
-      <c r="Q257" s="5" t="str">
-        <v>將吸氣時肺內壓與外界壓力比較。 → 【模型觀察】吸氣時胸內壓 758→754、肺內壓 760→758 mmHg，空氣為何流入？</v>
+      <c r="Q257" s="5" t="inlineStr">
+        <is>
+          <t>吸氣時肺內的數值由 760 變成 758 mmHg，和外界相比哪一邊較高？→ 決定氣流方向要比較哪兩個壓力，空氣會沿壓差往哪裡走？</t>
+        </is>
       </c>
       <c r="R257" s="5" t="str">
         <v>選擇「肺內壓低於大氣壓」。吸氣時肺內壓由 760 降到 758 mmHg，低於大氣壓而使空氣流入。</v>
@@ -25443,8 +25501,10 @@
       <c r="P258" s="5" t="str">
         <v>依 758→754 的變化判讀相對大氣壓的方向。</v>
       </c>
-      <c r="Q258" s="5" t="str">
-        <v>依 758→754 的變化判讀相對大氣壓的方向。 → 【生理判讀】吸氣過程中胸內壓的變化？</v>
+      <c r="Q258" s="5" t="inlineStr">
+        <is>
+          <t>吸氣時胸腔擴大，胸膜腔壓力由 758 變成 754 mmHg，數值向哪個方向移動？→ 若以大氣壓作參考，這個變化代表負壓程度如何改變？</t>
+        </is>
       </c>
       <c r="R258" s="5" t="str">
         <v>選擇「變得更低（更負）」。吸氣時胸內壓下降，變得更低、更負。</v>
@@ -25511,8 +25571,10 @@
       <c r="P259" s="5" t="str">
         <v>用同樣容積變化需要多少壓差來判讀。</v>
       </c>
-      <c r="Q259" s="5" t="str">
-        <v>用同樣容積變化需要多少壓差來判讀。 → 【生理判讀】肺纖維化病人要吸入同樣空氣量，需要？</v>
+      <c r="Q259" s="5" t="inlineStr">
+        <is>
+          <t>纖維化使肺不容易撐開，同樣壓力改變能帶來的容積變化多還是少？→ 若仍想吸入相同氣量，壓力改變需要加大還是縮小？</t>
+        </is>
       </c>
       <c r="R259" s="5" t="str">
         <v>選擇「更大的壓力變化，因順應性降低」。纖維化使順應性降低，因此吸入相同容積需要更大的壓力變化。</v>
@@ -25579,8 +25641,10 @@
       <c r="P260" s="5" t="str">
         <v>回縮變差時，盡力呼氣後會留下多少氣體？</v>
       </c>
-      <c r="Q260" s="5" t="str">
-        <v>回縮變差時，盡力呼氣後會留下多少氣體？ → 【生理判讀】肺氣腫病人容易吸進、不易呼出，最可能的結果？</v>
+      <c r="Q260" s="5" t="inlineStr">
+        <is>
+          <t>肺氣腫使肺的回縮能力變差，已吸入的氣體是否容易完全呼出？→ 盡力吐氣後留下的量會變多還是變少，這個容積叫什麼？</t>
+        </is>
       </c>
       <c r="R260" s="5" t="str">
         <v>選擇「氣體滯留、肺餘容積增加」。肺氣腫回縮變差，呼氣後氣體滯留，肺餘容積增加。</v>
@@ -25647,8 +25711,10 @@
       <c r="P261" s="5" t="str">
         <v>比較平靜呼氣與用力呼氣的肌肉參與。</v>
       </c>
-      <c r="Q261" s="5" t="str">
-        <v>比較平靜呼氣與用力呼氣的肌肉參與。 → 【生活情境】跑完步用力把氣吐乾淨時，額外參與的肌肉？</v>
+      <c r="Q261" s="5" t="inlineStr">
+        <is>
+          <t>跑步後刻意用力吐氣，還只是平靜呼氣時的放鬆與回縮嗎？→ 需要額外動員時，應找呼氣用的哪一組肋間肌和哪一塊腹部肌肉？</t>
+        </is>
       </c>
       <c r="R261" s="5" t="str">
         <v>選擇「內肋間肌與腹直肌」。用力呼氣可動用內肋間肌及腹直肌；平靜呼氣主要靠放鬆與回縮。</v>
@@ -25715,8 +25781,10 @@
       <c r="P262" s="5" t="str">
         <v>從平靜的一次呼吸量判斷容積名稱。</v>
       </c>
-      <c r="Q262" s="5" t="str">
-        <v>從平靜的一次呼吸量判斷容積名稱。 → 平靜呼吸時一次吸入或呼出的量？</v>
+      <c r="Q262" s="5" t="inlineStr">
+        <is>
+          <t>題目只描述平靜的一次吸入或呼出，是否包含額外盡力吸進的部分？→ 在基本肺容積中，哪個名稱專指這一小段日常呼吸的氣量？</t>
+        </is>
       </c>
       <c r="R262" s="5" t="str">
         <v>選擇「潮氣容積」。潮氣容積是平靜呼吸時一次吸入或呼出的量，課本男性示例為 500 mL。</v>
@@ -25783,8 +25851,10 @@
       <c r="P263" s="5" t="str">
         <v>盡力吐氣後仍存在的氣體屬於哪種容積？</v>
       </c>
-      <c r="Q263" s="5" t="str">
-        <v>盡力吐氣後仍存在的氣體屬於哪種容積？ → 盡力呼氣後仍留在肺內的量？</v>
+      <c r="Q263" s="5" t="inlineStr">
+        <is>
+          <t>已經盡力吐氣，肺內是否仍會留有不能再呼出的氣體？→ 這部分和僅因平靜呼氣而保留的總量相同嗎，應選哪個基本容積？</t>
+        </is>
       </c>
       <c r="R263" s="5" t="str">
         <v>選擇「肺餘容積」。肺餘容積是盡力呼氣後仍留在肺內的量，課本示例為 1200 mL。</v>
@@ -25851,8 +25921,10 @@
       <c r="P264" s="5" t="str">
         <v>肺活量涵蓋能吸入與能呼出的哪些部分？</v>
       </c>
-      <c r="Q264" s="5" t="str">
-        <v>肺活量涵蓋能吸入與能呼出的哪些部分？ → 肺活量（VC）＝？</v>
+      <c r="Q264" s="5" t="inlineStr">
+        <is>
+          <t>肺活量要涵蓋能盡力吸進與呼出的範圍，應把哪些可移動的氣量合起來？→ 盡力呼氣仍留下的 RV 能算進去嗎，排除後應保留哪三項？</t>
+        </is>
       </c>
       <c r="R264" s="5" t="str">
         <v>選擇「IRV＋TV＋ERV」。VC＝IRV＋TV＋ERV，不包含盡力呼氣後仍留下的 RV。</v>
@@ -25919,8 +25991,10 @@
       <c r="P265" s="5" t="str">
         <v>平靜呼氣末還有哪些氣體留在肺內？</v>
       </c>
-      <c r="Q265" s="5" t="str">
-        <v>平靜呼氣末還有哪些氣體留在肺內？ → 功能肺餘量（FRC）＝？</v>
+      <c r="Q265" s="5" t="inlineStr">
+        <is>
+          <t>平靜呼氣剛結束時，肺裡仍有能繼續呼出的氣體和不能再呼出的氣體嗎？→ 把這兩部分各自換成容積名稱，應將哪兩個符號相加？</t>
+        </is>
       </c>
       <c r="R265" s="5" t="str">
         <v>選擇「ERV＋RV」。FRC＝ERV＋RV，是平靜呼氣末的肺內氣體量。</v>
@@ -25987,8 +26061,10 @@
       <c r="P266" s="5" t="str">
         <v>找出呼吸區開始之前的最後一段。</v>
       </c>
-      <c r="Q266" s="5" t="str">
-        <v>找出呼吸區開始之前的最後一段。 → 傳導區的最後一段？</v>
+      <c r="Q266" s="5" t="inlineStr">
+        <is>
+          <t>傳導區的工作是送氣，和開始參與交換的區域有何不同？→ 若呼吸性細支氣管是交換的起點，緊接在它之前的最後一段叫什麼？</t>
+        </is>
       </c>
       <c r="R266" s="5" t="str">
         <v>選擇「終末細支氣管」。終末細支氣管仍只傳送氣體；自呼吸性細支氣管起才是呼吸區。</v>
@@ -26055,8 +26131,10 @@
       <c r="P267" s="5" t="str">
         <v>先扣掉每次未參與交換的量，再乘頻率。</v>
       </c>
-      <c r="Q267" s="5" t="str">
-        <v>先扣掉每次未參與交換的量，再乘頻率。 → 肺泡通氣量的算法？</v>
+      <c r="Q267" s="5" t="inlineStr">
+        <is>
+          <t>每次吸入的氣體是否全都參與肺泡交換，還是有一部分留在死腔？→ 先算一次真正參與交換的量，再換成每分鐘時，應進行哪兩個運算？</t>
+        </is>
       </c>
       <c r="R267" s="5" t="str">
         <v>選擇「（潮氣容積－死腔）×呼吸頻率」。肺泡通氣量 VA＝（TV－死腔）×呼吸頻率，不能直接使用總通氣量。</v>
@@ -26123,8 +26201,10 @@
       <c r="P268" s="5" t="str">
         <v>先算 450－150，再乘每分鐘次數。</v>
       </c>
-      <c r="Q268" s="5" t="str">
-        <v>先算 450－150，再乘每分鐘次數。 → 【模型觀察】TV 450 mL、死腔 150 mL、每分鐘 12 次，肺泡通氣量？</v>
+      <c r="Q268" s="5" t="inlineStr">
+        <is>
+          <t>一次吸入 450 mL，其中 150 mL 未參與交換，一次有效氣量剩多少？→ 每分鐘有 12 次相同呼吸，應把哪個結果乘上次數得到每分鐘的量？</t>
+        </is>
       </c>
       <c r="R268" s="5" t="str">
         <v>選擇「3600 mL/min」。VA＝（450－150）×12＝3600 mL/min。</v>
@@ -26191,8 +26271,10 @@
       <c r="P269" s="5" t="str">
         <v>比較每次呼吸量與 150 mL 死腔是否相等。</v>
       </c>
-      <c r="Q269" s="5" t="str">
-        <v>比較每次呼吸量與 150 mL 死腔是否相等。 → 【模型觀察】每次 150 mL、每分鐘 40 次（總通氣 6000），肺泡通氣量？</v>
+      <c r="Q269" s="5" t="inlineStr">
+        <is>
+          <t>每次吸入 150 mL，而解剖死腔也占 150 mL，扣除後還有氣體可進行交換嗎？→ 即使每分鐘呼吸 40 次，乘上頻率能改變這個結果嗎？</t>
+        </is>
       </c>
       <c r="R269" s="5" t="str">
         <v>選擇「0 mL/min」。VA＝（150－150）×40＝0；總通氣雖有 6000，肺泡通氣仍為零。</v>
@@ -26259,8 +26341,10 @@
       <c r="P270" s="5" t="str">
         <v>找出盡力呼氣後留下的容積名稱。</v>
       </c>
-      <c r="Q270" s="5" t="str">
-        <v>找出盡力呼氣後留下的容積名稱。 → 【生理判讀】長期吸菸使肺泡壁回彈變差，盡力呼氣後哪一項增加？</v>
+      <c r="Q270" s="5" t="inlineStr">
+        <is>
+          <t>題目指出回彈變差，盡力呼氣是否仍能像原先一樣把氣體排出去？→ 留下的氣體變多時，應對照盡力呼氣後保留的哪個基本容積？</t>
+        </is>
       </c>
       <c r="R270" s="5" t="str">
         <v>選擇「肺餘容積」。盡力呼氣後仍留下的氣體稱肺餘容積，因此題目所述增加的是 RV。</v>
@@ -26327,8 +26411,10 @@
       <c r="P271" s="5" t="str">
         <v>同時比較肺容量與 FEV₁/FVC，勿只看比值。</v>
       </c>
-      <c r="Q271" s="5" t="str">
-        <v>同時比較肺容量與 FEV₁/FVC，勿只看比值。 → 【生理判讀】FEV₁ 2.5 L、FVC 2.8 L（比值約 0.89），肺容量明顯減少，較符合？</v>
+      <c r="Q271" s="5" t="inlineStr">
+        <is>
+          <t>肺容量明顯減少，FEV₁/FVC 卻約 0.89、沒有降低，這和阻塞性型態的比值特徵相符嗎？→ 對照課本兩種型態，哪一種是容量減少、比值卻可正常或增加？</t>
+        </is>
       </c>
       <c r="R271" s="5" t="str">
         <v>選擇「限制性型態」。課本限制性示例為 2.5/2.8≈0.89；肺容量減少而比值可正常或增加。</v>
@@ -26395,8 +26481,10 @@
       <c r="P272" s="5" t="str">
         <v>從平靜呼氣末的量加上一次平靜吸氣量。</v>
       </c>
-      <c r="Q272" s="5" t="str">
-        <v>從平靜呼氣末的量加上一次平靜吸氣量。 → 【生理判讀】平靜吸氣結束時，肺內的氣體量？</v>
+      <c r="Q272" s="5" t="inlineStr">
+        <is>
+          <t>平靜呼氣末肺裡已有一個保留量，接著一次平靜吸氣會帶來哪一段氣量？→ 吸氣結束時應將起始保留量加上什麼，而不是直接當作肺總量？</t>
+        </is>
       </c>
       <c r="R272" s="5" t="str">
         <v>選擇「功能肺餘量＋潮氣容積」。平靜呼氣末為 FRC，平靜吸氣末則為 FRC＋TV。</v>
@@ -26463,8 +26551,10 @@
       <c r="P273" s="5" t="str">
         <v>先區分肺部交換與組織端交換。</v>
       </c>
-      <c r="Q273" s="5" t="str">
-        <v>先區分肺部交換與組織端交換。 → 外呼吸發生在？</v>
+      <c r="Q273" s="5" t="inlineStr">
+        <is>
+          <t>外呼吸要先定位在肺部還是組織細胞端，兩種交換的場所相同嗎？→ 在肺部，交換的一側是肺泡氣體，另一側應是哪一種血管裡的血液？</t>
+        </is>
       </c>
       <c r="R273" s="5" t="str">
         <v>選擇「肺泡與肺微血管之間」。外呼吸是肺泡與肺微血管之間的交換；內呼吸是血液與組織細胞間的交換。</v>
@@ -26531,8 +26621,10 @@
       <c r="P274" s="5" t="str">
         <v>混合氣體中，各氣體是否共用同一個壓差？</v>
       </c>
-      <c r="Q274" s="5" t="str">
-        <v>混合氣體中，各氣體是否共用同一個壓差？ → 每種氣體的擴散方向由何決定？</v>
+      <c r="Q274" s="5" t="inlineStr">
+        <is>
+          <t>混合氣體裡各種氣體都有個別的壓力，總壓能直接代表其中一種嗎？→ 判斷某種氣體往哪裡擴散時，應比較兩側的哪一個壓力量？</t>
+        </is>
       </c>
       <c r="R274" s="5" t="str">
         <v>選擇「該氣體自己的分壓差」。每種氣體依自己的分壓差擴散，氣體總壓不能取代氧分壓。</v>
@@ -26599,8 +26691,10 @@
       <c r="P275" s="5" t="str">
         <v>比較肺泡與入肺血的氧分壓高低。</v>
       </c>
-      <c r="Q275" s="5" t="str">
-        <v>比較肺泡與入肺血的氧分壓高低。 → 肺泡 PO₂ 約 100、入肺血約 40 mmHg，O₂ 如何移動？</v>
+      <c r="Q275" s="5" t="inlineStr">
+        <is>
+          <t>肺泡的氧分壓是 100、入肺血是 40 mmHg，哪邊的數值較高？→ 氧依分壓差移動時，來源應是哪一側，目的地又是哪一側？</t>
+        </is>
       </c>
       <c r="R275" s="5" t="str">
         <v>選擇「由肺泡擴散進入血液」。肺泡 PO₂ 約 100，高於入肺血約 40 mmHg，因此氧由肺泡擴散入血。</v>
@@ -26667,8 +26761,10 @@
       <c r="P276" s="5" t="str">
         <v>分清增加交換面積與增加膜厚的效果。</v>
       </c>
-      <c r="Q276" s="5" t="str">
-        <v>分清增加交換面積與增加膜厚的效果。 → 哪個變化會使擴散增加？</v>
+      <c r="Q276" s="5" t="inlineStr">
+        <is>
+          <t>氣體穿越呼吸膜時，通過的面積和膜的厚度會有相同效果嗎？→ 若要讓更多氣體同時通過，應讓交換範圍變大，還是讓膜層變厚？</t>
+        </is>
       </c>
       <c r="R276" s="5" t="str">
         <v>選擇「呼吸膜面積增加」。呼吸膜面積增加會增加擴散；膜厚增加則減少擴散。</v>
@@ -26735,8 +26831,10 @@
       <c r="P277" s="5" t="str">
         <v>比較兩處通氣量除以血流量的結果。</v>
       </c>
-      <c r="Q277" s="5" t="str">
-        <v>比較兩處通氣量除以血流量的結果。 → 站立時哪個部位 V/Q 較高？</v>
+      <c r="Q277" s="5" t="inlineStr">
+        <is>
+          <t>站立時比較肺部上下兩端，應看絕對通氣量，還是通氣除以血流的比值？→ 課本的 3.4 和 0.63 哪個較大，分別對應較上方還是較下方？</t>
+        </is>
       </c>
       <c r="R277" s="5" t="str">
         <v>選擇「肺尖」。肺尖 V/Q 約 3.4，高於肺底約 0.63；血流的上下差異比通氣更大。</v>
@@ -26803,8 +26901,10 @@
       <c r="P278" s="5" t="str">
         <v>思考如何減少送往通氣不佳處的血流。</v>
       </c>
-      <c r="Q278" s="5" t="str">
-        <v>思考如何減少送往通氣不佳處的血流。 → 肺泡局部低氧時，該處肺小動脈？</v>
+      <c r="Q278" s="5" t="inlineStr">
+        <is>
+          <t>局部肺泡缺氧表示該區通氣不佳，血流還適合持續大量送到這裡嗎？→ 要減少進入這一區的血量，小動脈管徑應變窄還是變寬？</t>
+        </is>
       </c>
       <c r="R278" s="5" t="str">
         <v>選擇「收縮」。局部肺泡低氧使該處肺小動脈收縮，減少流向通氣不佳處的血流。</v>
@@ -26871,8 +26971,10 @@
       <c r="P279" s="5" t="str">
         <v>分子量之外，還有哪個氣體性質影響擴散？</v>
       </c>
-      <c r="Q279" s="5" t="str">
-        <v>分子量之外，還有哪個氣體性質影響擴散？ → 【生理判讀】CO₂ 分子量比 O₂ 大，卻容易擴散，主要因為？</v>
+      <c r="Q279" s="5" t="inlineStr">
+        <is>
+          <t>CO₂ 的分子量較大時，僅靠分子量能完整判斷它的通過能力嗎？→ 另一個有利擴散的氣體性質是哪一項，課本比較兩氣體的倍數是多少？</t>
+        </is>
       </c>
       <c r="R279" s="5" t="str">
         <v>選擇「CO₂ 溶解度約為 O₂ 的 20 倍」。CO₂ 的溶解度約為 O₂ 的 20 倍；較高溶解度有利於擴散。</v>
@@ -26939,8 +27041,10 @@
       <c r="P280" s="5" t="str">
         <v>膜厚增加對擴散的影響方向為何？</v>
       </c>
-      <c r="Q280" s="5" t="str">
-        <v>膜厚增加對擴散的影響方向為何？ → 【生理判讀】肺水腫使呼吸膜變厚，最可能妨礙？</v>
+      <c r="Q280" s="5" t="inlineStr">
+        <is>
+          <t>肺水腫把交換膜層加厚，氣體通過時遇到的條件比原先更有利嗎？→ 這會先改變氧跨膜移動的效率，還是改變肺葉的數目？</t>
+        </is>
       </c>
       <c r="R280" s="5" t="str">
         <v>選擇「氧的擴散」。膜厚增加會減少擴散，因此呼吸膜變厚會妨礙氧的擴散。</v>
@@ -27007,8 +27111,10 @@
       <c r="P281" s="5" t="str">
         <v>將局部血管反應與通氣、灌流配合連起來。</v>
       </c>
-      <c r="Q281" s="5" t="str">
-        <v>將局部血管反應與通氣、灌流配合連起來。 → 【模型觀察】一處肺泡被痰阻塞而無通氣，該處肺小動脈的反應與意義？</v>
+      <c r="Q281" s="5" t="inlineStr">
+        <is>
+          <t>痰讓局部肺泡沒有通氣時，這一區還能和送來的血液良好配合嗎？→ 若要把血流轉向通氣較好的區域，缺氧處的小動脈管徑應如何改變？</t>
+        </is>
       </c>
       <c r="R281" s="5" t="str">
         <v>選擇「收縮，使血流轉向通氣良好的肺泡」。低氧處肺小動脈收縮，減少通氣不佳處的血流，使通氣與灌流較能配合。</v>
@@ -27075,8 +27181,10 @@
       <c r="P282" s="5" t="str">
         <v>比值大於一，代表分子相對分母如何？</v>
       </c>
-      <c r="Q282" s="5" t="str">
-        <v>比值大於一，代表分子相對分母如何？ → 【模型觀察】肺尖 V/Q≈3.4、肺底≈0.63，何者正確？</v>
+      <c r="Q282" s="5" t="inlineStr">
+        <is>
+          <t>V/Q 中分子是通氣、分母是血流，比值大於一表示哪個相對較多？→ 3.4 能說明兩者的相對關係，但能直接推定該處絕對通氣量最多嗎？</t>
+        </is>
       </c>
       <c r="R282" s="5" t="str">
         <v>選擇「肺尖通氣相對血流較多」。肺尖 V/Q≈3.4，表示通氣相對血流較多；不能據此說肺尖的絕對通氣量最多。</v>
@@ -27143,8 +27251,10 @@
       <c r="P283" s="5" t="str">
         <v>從內呼吸的交換雙方判斷兩種氣體方向。</v>
       </c>
-      <c r="Q283" s="5" t="str">
-        <v>從內呼吸的交換雙方判斷兩種氣體方向。 → 【模型觀察】運動中的肌肉，O₂ 與 CO₂ 的擴散方向？</v>
+      <c r="Q283" s="5" t="inlineStr">
+        <is>
+          <t>運動肌肉的氣體交換發生在血液和組織細胞之間，屬於哪一類呼吸？→ 在這個交換中，氧送往哪一側，二氧化碳又沿哪個相反方向移動？</t>
+        </is>
       </c>
       <c r="R283" s="5" t="str">
         <v>選擇「O₂ 由血液進入細胞、CO₂ 由細胞進入血液」。內呼吸是血液與組織細胞的交換；氧由血液進入細胞，CO₂ 由細胞進入血液。</v>
@@ -27211,8 +27321,10 @@
       <c r="P284" s="5" t="str">
         <v>比較與血紅素結合及直接溶解的比例。</v>
       </c>
-      <c r="Q284" s="5" t="str">
-        <v>比較與血紅素結合及直接溶解的比例。 → 血液中的氧大部分以何種形式運送？</v>
+      <c r="Q284" s="5" t="inlineStr">
+        <is>
+          <t>血液運氧時，直接溶在血漿和附著於攜氧蛋白的比例會一樣多嗎？→ 對照課本 97% 與 3%，哪一種方式才是運送的大宗？</t>
+        </is>
       </c>
       <c r="R284" s="5" t="str">
         <v>選擇「與血紅素結合」。約 97% 的氧與血紅素結合，只有約 3% 直接溶於血漿。</v>
@@ -27279,8 +27391,10 @@
       <c r="P285" s="5" t="str">
         <v>注意血基質中心鐵的價數。</v>
       </c>
-      <c r="Q285" s="5" t="str">
-        <v>注意血基質中心鐵的價數。 → 血基質中與氧結合的鐵？</v>
+      <c r="Q285" s="5" t="inlineStr">
+        <is>
+          <t>血基質中心的鐵可和氧反覆結合與分離，題目要辨認的是哪個金屬特徵？→ 應看鐵的價數還是肽鏈數目，對應的離子符號該如何寫？</t>
+        </is>
       </c>
       <c r="R285" s="5" t="str">
         <v>選擇「二價鐵（Fe²⁺）」。血基質中心是二價鐵 Fe²⁺，可與氧可逆結合。</v>
@@ -27347,8 +27461,10 @@
       <c r="P286" s="5" t="str">
         <v>由血基質的數目推算可結合的氧數目。</v>
       </c>
-      <c r="Q286" s="5" t="str">
-        <v>由血基質的數目推算可結合的氧數目。 → 一分子血紅素最多攜帶幾分子氧？</v>
+      <c r="Q286" s="5" t="inlineStr">
+        <is>
+          <t>一分子血紅素含有幾個血基質，每個中心各有能結合氧的鐵嗎？→ 將這些結合位置加總，最多可以同時攜帶幾分子氧？</t>
+        </is>
       </c>
       <c r="R286" s="5" t="str">
         <v>選擇「4」。一分子血紅素有四個血基質，可攜帶四分子氧。</v>
@@ -27415,8 +27531,10 @@
       <c r="P287" s="5" t="str">
         <v>比較活動肌肉的溫度與釋氧需求。</v>
       </c>
-      <c r="Q287" s="5" t="str">
-        <v>比較活動肌肉的溫度與釋氧需求。 → 下列何者使解離曲線右移？</v>
+      <c r="Q287" s="5" t="inlineStr">
+        <is>
+          <t>曲線往右代表血紅素較容易放出氧，和活動肌肉的需要有何關聯？→ 肌肉變熱或變冷，哪一種情況較符合課本所列的右移條件？</t>
+        </is>
       </c>
       <c r="R287" s="5" t="str">
         <v>選擇「溫度升高」。溫度升高使親和力降低、曲線右移，有利於釋氧。</v>
@@ -27483,8 +27601,10 @@
       <c r="P288" s="5" t="str">
         <v>比較三種 CO₂ 運送形式的比例。</v>
       </c>
-      <c r="Q288" s="5" t="str">
-        <v>比較三種 CO₂ 運送形式的比例。 → CO₂ 在血液中最主要的運送形式？</v>
+      <c r="Q288" s="5" t="inlineStr">
+        <is>
+          <t>CO₂ 可直接溶解、結合蛋白或轉成離子，哪一類占的比例最多？→ 約占七成、主要在血漿中運送的那個離子，中文名稱是什麼？</t>
+        </is>
       </c>
       <c r="R288" s="5" t="str">
         <v>選擇「碳酸氫根」。約 70% 的 CO₂ 以 HCO₃⁻ 在血漿運送，是最大宗的形式。</v>
@@ -27551,8 +27671,10 @@
       <c r="P289" s="5" t="str">
         <v>找出紅血球內加速 CO₂ 與水反應的酶。</v>
       </c>
-      <c r="Q289" s="5" t="str">
-        <v>找出紅血球內加速 CO₂ 與水反應的酶。 → 紅血球內催化 CO₂ 與水反應的酶？</v>
+      <c r="Q289" s="5" t="inlineStr">
+        <is>
+          <t>紅血球要把 CO₂ 與水轉成碳酸，反應加速需要催化者還是攜氧位置？→ 這個催化者是酶還是血紅素，應選哪個與碳酸反應有關的名稱？</t>
+        </is>
       </c>
       <c r="R289" s="5" t="str">
         <v>選擇「碳酸酐酶」。碳酸酐酶催化 CO₂ 與水形成碳酸，接著解離為 H⁺ 與 HCO₃⁻。</v>
@@ -27619,8 +27741,10 @@
       <c r="P290" s="5" t="str">
         <v>將酸與溫度變化連到曲線移動及釋氧。</v>
       </c>
-      <c r="Q290" s="5" t="str">
-        <v>將酸與溫度變化連到曲線移動及釋氧。 → 【生活情境】馬拉松跑者腿部肌肉溫度升高、酸增加，血紅素對氧的親和力？</v>
+      <c r="Q290" s="5" t="inlineStr">
+        <is>
+          <t>跑步肌肉同時變熱、酸也變多，這與課本哪一組曲線移動條件相符？→ 曲線朝該方向移動時，血紅素會更抓緊氧，還是較容易把氧交給肌肉？</t>
+        </is>
       </c>
       <c r="R290" s="5" t="str">
         <v>選擇「下降，釋出更多氧給肌肉」。H⁺增加與溫度升高使曲線右移、親和力降低，因此有利於釋氧給肌肉。</v>
@@ -27687,8 +27811,10 @@
       <c r="P291" s="5" t="str">
         <v>在 S 形曲線上找 PO₂ 40 的對應高度。</v>
       </c>
-      <c r="Q291" s="5" t="str">
-        <v>在 S 形曲線上找 PO₂ 40 的對應高度。 → 【模型觀察】血液從肺部流到 PO₂ 約 40 mmHg 的組織，血紅素飽和度約為？</v>
+      <c r="Q291" s="5" t="inlineStr">
+        <is>
+          <t>血液到達氧分壓約 40 mmHg 的組織時，應沿同一條曲線讀值還是先移動曲線？→ 在這個橫軸位置往上找到曲線，縱軸的飽和度約是多少？</t>
+        </is>
       </c>
       <c r="R291" s="5" t="str">
         <v>選擇「75%」。課本指出 PO₂ 40 mmHg 時，血紅素氧飽和度約為 75%。</v>
@@ -27755,8 +27881,10 @@
       <c r="P292" s="5" t="str">
         <v>用右移條件的相反方向判斷。</v>
       </c>
-      <c r="Q292" s="5" t="str">
-        <v>用右移條件的相反方向判斷。 → 【生理判讀】過度換氣使血中 CO₂ 減少、pH 上升，解離曲線？</v>
+      <c r="Q292" s="5" t="inlineStr">
+        <is>
+          <t>過度換氣後二氧化碳變少、pH 變高，與酸增多的條件是同向還是反向？→ 對照右移條件的相反變化，曲線會往哪邊走，氧又會被抓得更緊嗎？</t>
+        </is>
       </c>
       <c r="R292" s="5" t="str">
         <v>選擇「左移，親和力增加」。CO₂ 減少、pH 上升是右移條件的相反方向，使曲線左移、親和力增加。</v>
@@ -27823,8 +27951,10 @@
       <c r="P293" s="5" t="str">
         <v>思考碳酸氫根移出紅血球時的離子交換。</v>
       </c>
-      <c r="Q293" s="5" t="str">
-        <v>思考碳酸氫根移出紅血球時的離子交換。 → 【模型觀察】HCO₃⁻由紅血球移到血漿時，哪個離子同時進入紅血球？</v>
+      <c r="Q293" s="5" t="inlineStr">
+        <is>
+          <t>碳酸氫根離開紅血球進入血漿時，是否還有另一種離子沿相反方向移動？→ 課本把這個交換稱為氯轉移，據此應選哪一個進入細胞的離子符號？</t>
+        </is>
       </c>
       <c r="R293" s="5" t="str">
         <v>選擇「Cl⁻」。HCO₃⁻移出紅血球時 Cl⁻進入，這個交換稱氯轉移。</v>
@@ -27891,8 +28021,10 @@
       <c r="P294" s="5" t="str">
         <v>比較 CO 與氧對同一結合位置的競爭。</v>
       </c>
-      <c r="Q294" s="5" t="str">
-        <v>比較 CO 與氧對同一結合位置的競爭。 → 【生理判讀】一氧化碳使氧運送下降的主要原因？</v>
+      <c r="Q294" s="5" t="inlineStr">
+        <is>
+          <t>一氧化碳和氧要競爭血紅素的位置時，兩者抓住血紅素的能力相同嗎？→ 若前者親和力遠高於後者，氧能使用的位置與運送量會如何改變？</t>
+        </is>
       </c>
       <c r="R294" s="5" t="str">
         <v>選擇「CO 與血紅素親和力約為氧的 250 倍，佔據結合位置」。CO 與血紅素的親和力約為氧的 250 倍，佔據結合位置，使氧運送下降。</v>
@@ -27959,8 +28091,10 @@
       <c r="P295" s="5" t="str">
         <v>區分血中物質與受器直接接觸的腦脊髓液物質。</v>
       </c>
-      <c r="Q295" s="5" t="str">
-        <v>區分血中物質與受器直接接觸的腦脊髓液物質。 → 直接刺激中樞化學受器的是？</v>
+      <c r="Q295" s="5" t="inlineStr">
+        <is>
+          <t>題目問受器直接接觸的刺激，血中氫離子能輕易越過血腦障壁嗎？→ 若血中的氣體先通過障壁，再使腦脊髓液變酸，受器實際感受到什麼？</t>
+        </is>
       </c>
       <c r="R295" s="5" t="str">
         <v>選擇「腦脊髓液中的 H⁺」。中樞化學受器直接感受腦脊髓液中的 H⁺，不是血中 H⁺直接穿越血腦障壁。</v>
@@ -28027,8 +28161,10 @@
       <c r="P296" s="5" t="str">
         <v>哪種氣體能先通過障壁，再使腦脊髓液酸增加？</v>
       </c>
-      <c r="Q296" s="5" t="str">
-        <v>哪種氣體能先通過障壁，再使腦脊髓液酸增加？ → 能穿越血腦障壁、間接刺激中樞受器的是？</v>
+      <c r="Q296" s="5" t="inlineStr">
+        <is>
+          <t>血腦障壁把血液與腦脊髓液分開，血中的氣體和氫離子都容易通過嗎？→ 哪種物質能先通過，再使液中的氫離子變多，形成間接刺激？</t>
+        </is>
       </c>
       <c r="R296" s="5" t="str">
         <v>選擇「CO₂」。血中 CO₂ 能穿越血腦障壁，在腦脊髓液增加 H⁺，間接刺激中樞受器。</v>
@@ -28095,8 +28231,10 @@
       <c r="P297" s="5" t="str">
         <v>留意低氧刺激開始明顯的分壓界線。</v>
       </c>
-      <c r="Q297" s="5" t="str">
-        <v>留意低氧刺激開始明顯的分壓界線。 → 周邊化學受器對低氧明顯反應約在？</v>
+      <c r="Q297" s="5" t="inlineStr">
+        <is>
+          <t>氧分壓偏低時，周邊受器的反應會一直同樣明顯，還是有課本所列的界線？→ 對照約 60 mmHg 的參考值，落在較高側或較低側時，刺激才會明顯？</t>
+        </is>
       </c>
       <c r="R297" s="5" t="str">
         <v>選擇「PO₂ 低於約 60 mmHg」。PO₂ 低於約 60 mmHg 時，周邊化學受器的低氧刺激明顯。</v>
@@ -28163,8 +28301,10 @@
       <c r="P298" s="5" t="str">
         <v>沿肺牽張受器到延髓、橋腦追蹤傳入路徑。</v>
       </c>
-      <c r="Q298" s="5" t="str">
-        <v>沿肺牽張受器到延髓、橋腦追蹤傳入路徑。 → 赫鮑二氏反射的傳入神經？</v>
+      <c r="Q298" s="5" t="inlineStr">
+        <is>
+          <t>肺被拉開後，牽張受器會把訊息送到延髓與橋腦，這是化學刺激嗎？→ 從肺到中樞的傳入路徑應找哪條神經，而不是把受器當成神經名稱？</t>
+        </is>
       </c>
       <c r="R298" s="5" t="str">
         <v>選擇「迷走神經」。肺牽張受器的訊息經迷走神經傳入呼吸中樞，抑制吸氣。</v>
@@ -28231,8 +28371,10 @@
       <c r="P299" s="5" t="str">
         <v>分清正常範圍與酸、鹼方向。</v>
       </c>
-      <c r="Q299" s="5" t="str">
-        <v>分清正常範圍與酸、鹼方向。 → 正常血液 pH？</v>
+      <c r="Q299" s="5" t="inlineStr">
+        <is>
+          <t>要判斷血液酸鹼是否偏離正常，應先知道一般值落在哪個區間嗎？→ 課本以約 7.4 為參考，正常範圍的下限與上限各是多少？</t>
+        </is>
       </c>
       <c r="R299" s="5" t="str">
         <v>選擇「7.35–7.45」。正常血液 pH 約為 7.35–7.45。</v>
@@ -28299,8 +28441,10 @@
       <c r="P300" s="5" t="str">
         <v>比較 CO₂ 降低與血液 pH 上升的方向。</v>
       </c>
-      <c r="Q300" s="5" t="str">
-        <v>比較 CO₂ 降低與血液 pH 上升的方向。 → PCO₂ 低於 35 mmHg、pH 上升，屬於哪個方向？</v>
+      <c r="Q300" s="5" t="inlineStr">
+        <is>
+          <t>題目中的 CO₂ 已減少而 pH 變高，應先從呼吸因素還是代謝因素判讀？→ pH 往高值偏移是偏酸還是偏鹼，兩個判斷合起來應如何命名？</t>
+        </is>
       </c>
       <c r="R300" s="5" t="str">
         <v>選擇「呼吸性鹼中毒」。PCO₂ 低於 35 mmHg 是呼吸性鹼中毒方向。</v>
@@ -28367,8 +28511,10 @@
       <c r="P301" s="5" t="str">
         <v>把 CO₂ 累積連到腦脊髓液與中樞受器。</v>
       </c>
-      <c r="Q301" s="5" t="str">
-        <v>把 CO₂ 累積連到腦脊髓液與中樞受器。 → 【生活情境】閉氣一段時間後忍不住吸氣，最主要的驅動？</v>
+      <c r="Q301" s="5" t="inlineStr">
+        <is>
+          <t>閉氣後二氧化碳累積，哪種物質能先通過血腦障壁影響腦脊髓液？→ 液中酸的變化接著由哪類受器感受，為何會促使人恢復呼吸？</t>
+        </is>
       </c>
       <c r="R301" s="5" t="str">
         <v>選擇「CO₂ 累積使腦脊髓液 H⁺增加，刺激中樞化學受器」。CO₂ 能穿越血腦障壁，使腦脊髓液 H⁺增加，刺激中樞化學受器並驅動呼吸。</v>
@@ -28435,8 +28581,10 @@
       <c r="P302" s="5" t="str">
         <v>高山低氧促進換氣後，CO₂ 排出如何改變？</v>
       </c>
-      <c r="Q302" s="5" t="str">
-        <v>高山低氧促進換氣後，CO₂ 排出如何改變？ → 【生活情境】初登玉山呼吸加快，血液最可能的變化？</v>
+      <c r="Q302" s="5" t="inlineStr">
+        <is>
+          <t>登高後吸入氧分壓降低，周邊受器的訊息會使換氣量如何改變？→ 換氣使二氧化碳排出變多後，血中分壓與 pH 各應往哪個方向走？</t>
+        </is>
       </c>
       <c r="R302" s="5" t="str">
         <v>選擇「PCO₂ 下降、pH 上升」。高海拔低氧刺激周邊受器，使換氣與 CO₂ 排出增加，可使 PCO₂ 下降、pH 上升。</v>
@@ -28503,8 +28651,10 @@
       <c r="P303" s="5" t="str">
         <v>肺牽張受器的訊息對吸氣是促進還是抑制？</v>
       </c>
-      <c r="Q303" s="5" t="str">
-        <v>肺牽張受器的訊息對吸氣是促進還是抑制？ → 【生理判讀】深吸氣使肺過度擴張時，哪個反射抑制吸氣？</v>
+      <c r="Q303" s="5" t="inlineStr">
+        <is>
+          <t>肺過度擴張時，最先受到牽拉的是哪一類受器，屬化學還是機械訊息？→ 訊息經神經送到中樞後抑制吸氣，這個保護性反射叫什麼？</t>
+        </is>
       </c>
       <c r="R303" s="5" t="str">
         <v>選擇「赫鮑二氏反射」。肺牽張受器經迷走神經傳入中樞，抑制吸氣、避免肺過度擴張，形成赫鮑二氏反射。</v>
@@ -28571,8 +28721,10 @@
       <c r="P304" s="5" t="str">
         <v>依 PCO₂ 的界線判方向，再看腎臟代償。</v>
       </c>
-      <c r="Q304" s="5" t="str">
-        <v>依 PCO₂ 的界線判方向，再看腎臟代償。 → 【生理判讀】肺泡換氣不足使 PCO₂ 超過 45 mmHg，屬於？</v>
+      <c r="Q304" s="5" t="inlineStr">
+        <is>
+          <t>換氣不足讓 CO₂ 累積，依課本界線會使酸鹼朝哪個方向偏移？→ 若腎臟要代償，應多排出酸還是留住酸，又該如何處理碳酸氫根？</t>
+        </is>
       </c>
       <c r="R304" s="5" t="str">
         <v>選擇「呼吸性酸中毒，腎臟排酸、保留 HCO₃⁻ 代償」。PCO₂ 超過 45 mmHg 為呼吸性酸中毒方向；腎臟可排酸、保留 HCO₃⁻代償。</v>
@@ -28639,8 +28791,10 @@
       <c r="P305" s="5" t="str">
         <v>分母增加而分子固定，比值與對數如何變化？</v>
       </c>
-      <c r="Q305" s="5" t="str">
-        <v>分母增加而分子固定，比值與對數如何變化？ → 【模型觀察】依 pH＝6.1＋log（HCO₃⁻/H₂CO₃），HCO₃⁻ 不變而 H₂CO₃ 增加，pH？</v>
+      <c r="Q305" s="5" t="inlineStr">
+        <is>
+          <t>公式中的 HCO₃⁻ 固定、H₂CO₃ 變多時，同一個分子除以較大分母，結果如何？→ 對數項會跟著變大還是變小，加上固定項後 pH 往哪個方向變？</t>
+        </is>
       </c>
       <c r="R305" s="5" t="str">
         <v>選擇「下降」。H₂CO₃ 增加使 HCO₃⁻/H₂CO₃ 比值降低，因此依公式 pH 下降。</v>

--- a/html/資訊圖表題庫_上傳用.xlsx
+++ b/html/資訊圖表題庫_上傳用.xlsx
@@ -48,7 +48,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -66,6 +66,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -361,7 +364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X305"/>
+  <dimension ref="A1:X415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28814,6 +28817,9358 @@
       </c>
       <c r="X305" s="3"/>
     </row>
+    <row r="306" ht="110" customHeight="1">
+      <c r="A306" s="3" t="str"/>
+      <c r="B306" s="7" t="str">
+        <v>kidney-anatomy-foundation-q01</v>
+      </c>
+      <c r="C306" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G306" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H306" s="5" t="inlineStr">
+        <is>
+          <t>腎臟在身體的哪個位置？</t>
+        </is>
+      </c>
+      <c r="I306" s="5" t="inlineStr">
+        <is>
+          <t>在腹膜後面靠背部，右腎通常比左腎低一點</t>
+        </is>
+      </c>
+      <c r="J306" s="5" t="inlineStr">
+        <is>
+          <t>在腹膜腔裡面，右腎通常比左腎高一點</t>
+        </is>
+      </c>
+      <c r="K306" s="5" t="inlineStr">
+        <is>
+          <t>在骨盆腔裡，左右腎臟一樣高</t>
+        </is>
+      </c>
+      <c r="L306" s="5" t="inlineStr">
+        <is>
+          <t>在胸腔裡，左腎通常比右腎低一點</t>
+        </is>
+      </c>
+      <c r="M306" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N306" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O306" s="5" t="inlineStr">
+        <is>
+          <t>因為腎臟在腹膜後面靠背部，所以叫後腹腔器官，右腎通常又比左腎低一點。選「在腹膜腔裡面，右腎通常比左腎高一點」的同學，把「腹膜後面」和「腹膜腔裡面」弄反了。</t>
+        </is>
+      </c>
+      <c r="P306" s="5" t="inlineStr">
+        <is>
+          <t>先想想：腎臟靠肚子前面，還是靠背後？</t>
+        </is>
+      </c>
+      <c r="Q306" s="5" t="str"/>
+      <c r="R306" s="5" t="inlineStr">
+        <is>
+          <t>答案是「在腹膜後面靠背部，右腎通常比左腎低一點」，因為腎臟在腹膜後面，右腎通常較低。</t>
+        </is>
+      </c>
+      <c r="S306" s="5" t="inlineStr">
+        <is>
+          <t>腎躲腹膜後，右腎低一點</t>
+        </is>
+      </c>
+      <c r="T306" s="3" t="str">
+        <v>kidney-position；anatomy/AB-05_15 p.2, anatomy/AB-05_15 p.3, physiology/CH09 p.2</v>
+      </c>
+      <c r="U306" s="3" t="str"/>
+      <c r="V306" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W306" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X306" s="3" t="str"/>
+    </row>
+    <row r="307" ht="110" customHeight="1">
+      <c r="A307" s="3" t="str"/>
+      <c r="B307" s="7" t="str">
+        <v>kidney-anatomy-foundation-q02</v>
+      </c>
+      <c r="C307" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F307" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G307" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H307" s="5" t="inlineStr">
+        <is>
+          <t>腎臟裡的「腎柱」是什麼？</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="inlineStr">
+        <is>
+          <t>腎錐體的尖端</t>
+        </is>
+      </c>
+      <c r="J307" s="5" t="inlineStr">
+        <is>
+          <t>伸進腎錐體之間的皮質</t>
+        </is>
+      </c>
+      <c r="K307" s="5" t="inlineStr">
+        <is>
+          <t>從腎盂接出去的輸尿管</t>
+        </is>
+      </c>
+      <c r="L307" s="5" t="inlineStr">
+        <is>
+          <t>包在腎臟外面的脂肪囊</t>
+        </is>
+      </c>
+      <c r="M307" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N307" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O307" s="5" t="inlineStr">
+        <is>
+          <t>因為腎臟外層的皮質會伸進錐體之間，所以這部分叫腎柱。選「腎錐體的尖端」的同學，說的是錐體尖端的腎乳頭。</t>
+        </is>
+      </c>
+      <c r="P307" s="5" t="inlineStr">
+        <is>
+          <t>先想想：腎柱在錐體之間，還是在尖端？</t>
+        </is>
+      </c>
+      <c r="Q307" s="5" t="str"/>
+      <c r="R307" s="5" t="inlineStr">
+        <is>
+          <t>答案是「伸進腎錐體之間的皮質」，因為腎柱是伸進錐體之間的皮質。</t>
+        </is>
+      </c>
+      <c r="S307" s="5" t="inlineStr">
+        <is>
+          <t>腎柱夾錐體，皮質伸進去</t>
+        </is>
+      </c>
+      <c r="T307" s="3" t="str">
+        <v>kidney-structure；anatomy/AB-05_15 p.3, anatomy/AB-05_15 p.4, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.3, physiology/CH09 p.4</v>
+      </c>
+      <c r="U307" s="3" t="str"/>
+      <c r="V307" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W307" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X307" s="3" t="str"/>
+    </row>
+    <row r="308" ht="110" customHeight="1">
+      <c r="A308" s="3" t="str"/>
+      <c r="B308" s="7" t="str">
+        <v>kidney-anatomy-foundation-q03</v>
+      </c>
+      <c r="C308" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F308" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G308" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H308" s="5" t="inlineStr">
+        <is>
+          <t>尿液從腎乳頭（腎錐體的尖端）流出後，先進入哪裡？</t>
+        </is>
+      </c>
+      <c r="I308" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球</t>
+        </is>
+      </c>
+      <c r="J308" s="5" t="inlineStr">
+        <is>
+          <t>大腎盞</t>
+        </is>
+      </c>
+      <c r="K308" s="5" t="inlineStr">
+        <is>
+          <t>小腎盞</t>
+        </is>
+      </c>
+      <c r="L308" s="5" t="inlineStr">
+        <is>
+          <t>腎門</t>
+        </is>
+      </c>
+      <c r="M308" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N308" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O308" s="5" t="inlineStr">
+        <is>
+          <t>因為小腎盞先接住乳頭流出的尿，所以答案是小腎盞。選「大腎盞」的同學，所選的大腎盞要等小腎盞的尿匯過來，才接得到。</t>
+        </is>
+      </c>
+      <c r="P308" s="5" t="inlineStr">
+        <is>
+          <t>先想想：乳頭流出的尿先進小腎盞，還是大腎盞？</t>
+        </is>
+      </c>
+      <c r="Q308" s="5" t="str"/>
+      <c r="R308" s="5" t="inlineStr">
+        <is>
+          <t>答案是「小腎盞」，因為小腎盞最先接住乳頭流出的尿。</t>
+        </is>
+      </c>
+      <c r="S308" s="5" t="inlineStr">
+        <is>
+          <t>乳頭接小盞，再流大盞</t>
+        </is>
+      </c>
+      <c r="T308" s="3" t="str">
+        <v>kidney-structure；anatomy/AB-05_15 p.3, anatomy/AB-05_15 p.4, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.3, physiology/CH09 p.4</v>
+      </c>
+      <c r="U308" s="3" t="str"/>
+      <c r="V308" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W308" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X308" s="3" t="str"/>
+    </row>
+    <row r="309" ht="110" customHeight="1">
+      <c r="A309" s="3" t="str"/>
+      <c r="B309" s="7" t="str">
+        <v>kidney-anatomy-foundation-q04</v>
+      </c>
+      <c r="C309" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F309" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G309" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H309" s="5" t="inlineStr">
+        <is>
+          <t>從貼著腎臟表面的位置往外數，三層保護構造的順序是什麼？</t>
+        </is>
+      </c>
+      <c r="I309" s="5" t="inlineStr">
+        <is>
+          <t>脂肪囊、腎筋膜、腎被膜</t>
+        </is>
+      </c>
+      <c r="J309" s="5" t="inlineStr">
+        <is>
+          <t>腎筋膜、腎被膜、脂肪囊</t>
+        </is>
+      </c>
+      <c r="K309" s="5" t="inlineStr">
+        <is>
+          <t>腎被膜、腎筋膜、脂肪囊</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="inlineStr">
+        <is>
+          <t>腎被膜、脂肪囊、腎筋膜</t>
+        </is>
+      </c>
+      <c r="M309" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N309" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O309" s="5" t="inlineStr">
+        <is>
+          <t>因為腎被膜貼著腎表面，外面再包脂肪囊與腎筋膜，所以選「腎被膜、脂肪囊、腎筋膜」。選「腎被膜、腎筋膜、脂肪囊」的同學，把脂肪囊與腎筋膜的位置交換了。</t>
+        </is>
+      </c>
+      <c r="P309" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪一層先貼住腎臟，外面才有脂肪？</t>
+        </is>
+      </c>
+      <c r="Q309" s="5" t="str"/>
+      <c r="R309" s="5" t="inlineStr">
+        <is>
+          <t>答案是「腎被膜、脂肪囊、腎筋膜」，因為由內往外是腎被膜、脂肪囊、腎筋膜。</t>
+        </is>
+      </c>
+      <c r="S309" s="5" t="inlineStr">
+        <is>
+          <t>被膜貼腎，脂肪外加筋膜</t>
+        </is>
+      </c>
+      <c r="T309" s="3" t="str">
+        <v>kidney-structure；anatomy/AB-05_15 p.3, anatomy/AB-05_15 p.4, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.3, physiology/CH09 p.4
+kidney-position；anatomy/AB-05_15 p.2–3</v>
+      </c>
+      <c r="U309" s="3" t="str"/>
+      <c r="V309" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W309" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X309" s="3" t="str"/>
+    </row>
+    <row r="310" ht="110" customHeight="1">
+      <c r="A310" s="3" t="str"/>
+      <c r="B310" s="7" t="str">
+        <v>kidney-anatomy-foundation-q05</v>
+      </c>
+      <c r="C310" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F310" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G310" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H310" s="5" t="inlineStr">
+        <is>
+          <t>腎臟與膀胱各做什麼工作？</t>
+        </is>
+      </c>
+      <c r="I310" s="5" t="inlineStr">
+        <is>
+          <t>腎臟製造尿液，膀胱暫存尿液</t>
+        </is>
+      </c>
+      <c r="J310" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管製造尿液，尿道暫存尿液</t>
+        </is>
+      </c>
+      <c r="K310" s="5" t="inlineStr">
+        <is>
+          <t>膀胱製造尿液，腎臟把尿排到體外</t>
+        </is>
+      </c>
+      <c r="L310" s="5" t="inlineStr">
+        <is>
+          <t>尿道把尿送到膀胱，輸尿管把尿排到體外</t>
+        </is>
+      </c>
+      <c r="M310" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N310" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O310" s="5" t="inlineStr">
+        <is>
+          <t>因為腎臟先形成尿液，尿再送到膀胱存放，所以選「腎臟製造尿液，膀胱暫存尿液」。選「尿道把尿送到膀胱，輸尿管把尿排到體外」的同學，把輸尿管的送尿工作和尿道的排尿工作交換了。</t>
+        </is>
+      </c>
+      <c r="P310" s="5" t="inlineStr">
+        <is>
+          <t>先想想：尿在哪裡形成，又在哪裡先存起來？</t>
+        </is>
+      </c>
+      <c r="Q310" s="5" t="str"/>
+      <c r="R310" s="5" t="inlineStr">
+        <is>
+          <t>答案是「腎臟製造尿液，膀胱暫存尿液」，因為腎臟形成尿液，膀胱負責儲尿。</t>
+        </is>
+      </c>
+      <c r="S310" s="5" t="inlineStr">
+        <is>
+          <t>腎造尿，膀胱先存尿</t>
+        </is>
+      </c>
+      <c r="T310" s="3" t="str">
+        <v>urinary-system-overview；physiology/CH09 p.9, physiology/CH09 p.10, anatomy/AB-05_15 p.2, anatomy/AB-05_15 p.9, anatomy/AB-05_15 p.10, anatomy/AB-05_15 p.11, anatomy/AB-05_15 p.14</v>
+      </c>
+      <c r="U310" s="3" t="str"/>
+      <c r="V310" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W310" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X310" s="3" t="str"/>
+    </row>
+    <row r="311" ht="110" customHeight="1">
+      <c r="A311" s="3" t="str"/>
+      <c r="B311" s="7" t="str">
+        <v>kidney-anatomy-foundation-q06</v>
+      </c>
+      <c r="C311" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F311" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G311" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H311" s="5" t="inlineStr">
+        <is>
+          <t>腎臟的紅血球生成素（腎紅血球生成因子）主要幫忙做什麼？</t>
+        </is>
+      </c>
+      <c r="I311" s="5" t="inlineStr">
+        <is>
+          <t>減少紅血球生成</t>
+        </is>
+      </c>
+      <c r="J311" s="5" t="inlineStr">
+        <is>
+          <t>增加紅血球生成</t>
+        </is>
+      </c>
+      <c r="K311" s="5" t="inlineStr">
+        <is>
+          <t>增加白血球生成</t>
+        </is>
+      </c>
+      <c r="L311" s="5" t="inlineStr">
+        <is>
+          <t>增加血小板生成</t>
+        </is>
+      </c>
+      <c r="M311" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N311" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O311" s="5" t="inlineStr">
+        <is>
+          <t>因為紅血球生成素會促進紅血球生成，所以選「增加紅血球生成」。選「增加白血球生成」的同學，把這個造血訊號的主要對象換成白血球了。</t>
+        </is>
+      </c>
+      <c r="P311" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這個訊號主要幫哪一種血球生成？</t>
+        </is>
+      </c>
+      <c r="Q311" s="5" t="str"/>
+      <c r="R311" s="5" t="inlineStr">
+        <is>
+          <t>答案是「增加紅血球生成」，因為紅血球生成素主要促進紅血球生成。</t>
+        </is>
+      </c>
+      <c r="S311" s="5" t="inlineStr">
+        <is>
+          <t>紅血球生成素，幫忙造紅血球</t>
+        </is>
+      </c>
+      <c r="T311" s="3" t="str">
+        <v>kidney-endocrine；physiology/CH09 p.9, anatomy/AB-05_15 p.9, physiology/CH09 p.6, physiology/CH09 p.7, physiology/CH09 p.35</v>
+      </c>
+      <c r="U311" s="3" t="str"/>
+      <c r="V311" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W311" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X311" s="3" t="str"/>
+    </row>
+    <row r="312" ht="110" customHeight="1">
+      <c r="A312" s="3" t="str"/>
+      <c r="B312" s="7" t="str">
+        <v>kidney-anatomy-case-q01</v>
+      </c>
+      <c r="C312" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F312" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G312" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H312" s="5" t="inlineStr">
+        <is>
+          <t>兩個腎錐體之間有一塊組織，和外層皮質連在一起，它叫什麼？</t>
+        </is>
+      </c>
+      <c r="I312" s="5" t="inlineStr">
+        <is>
+          <t>腎乳頭</t>
+        </is>
+      </c>
+      <c r="J312" s="5" t="inlineStr">
+        <is>
+          <t>腎盂</t>
+        </is>
+      </c>
+      <c r="K312" s="5" t="inlineStr">
+        <is>
+          <t>腎柱</t>
+        </is>
+      </c>
+      <c r="L312" s="5" t="inlineStr">
+        <is>
+          <t>腎被膜</t>
+        </is>
+      </c>
+      <c r="M312" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N312" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O312" s="5" t="inlineStr">
+        <is>
+          <t>因為皮質伸入錐體之間的部分叫腎柱，所以選「腎柱」。選「腎乳頭」的同學，所選的腎乳頭在錐體尖端，不在兩個錐體之間。</t>
+        </is>
+      </c>
+      <c r="P312" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這塊組織連著皮質，還是位在錐體尖端？</t>
+        </is>
+      </c>
+      <c r="Q312" s="5" t="str"/>
+      <c r="R312" s="5" t="inlineStr">
+        <is>
+          <t>答案是「腎柱」，因為深入兩個錐體之間的皮質叫腎柱。</t>
+        </is>
+      </c>
+      <c r="S312" s="5" t="inlineStr">
+        <is>
+          <t>兩錐體中間，找皮質腎柱</t>
+        </is>
+      </c>
+      <c r="T312" s="3" t="str">
+        <v>kidney-structure；anatomy/AB-05_15 p.3, anatomy/AB-05_15 p.4, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.3, physiology/CH09 p.4</v>
+      </c>
+      <c r="U312" s="3" t="str"/>
+      <c r="V312" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W312" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X312" s="3" t="str"/>
+    </row>
+    <row r="313" ht="110" customHeight="1">
+      <c r="A313" s="3" t="str"/>
+      <c r="B313" s="7" t="str">
+        <v>kidney-anatomy-case-q02</v>
+      </c>
+      <c r="C313" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F313" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G313" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H313" s="5" t="inlineStr">
+        <is>
+          <t>集尿管把尿送到腎乳頭後，尿接下來會依序流過哪三個地方？</t>
+        </is>
+      </c>
+      <c r="I313" s="5" t="inlineStr">
+        <is>
+          <t>大腎盞、小腎盞、腎盂</t>
+        </is>
+      </c>
+      <c r="J313" s="5" t="inlineStr">
+        <is>
+          <t>腎盂、大腎盞、小腎盞</t>
+        </is>
+      </c>
+      <c r="K313" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球、小腎盞、輸尿管</t>
+        </is>
+      </c>
+      <c r="L313" s="5" t="inlineStr">
+        <is>
+          <t>小腎盞、大腎盞、腎盂</t>
+        </is>
+      </c>
+      <c r="M313" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N313" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O313" s="5" t="inlineStr">
+        <is>
+          <t>因為小腎盞先接尿，再匯到大腎盞和腎盂，所以選「小腎盞、大腎盞、腎盂」。選「大腎盞、小腎盞、腎盂」的同學，把小腎盞和大腎盞的先後交換了。</t>
+        </is>
+      </c>
+      <c r="P313" s="5" t="inlineStr">
+        <is>
+          <t>先想想：尿要先被小盞接住，還是先進大盞？</t>
+        </is>
+      </c>
+      <c r="Q313" s="5" t="str"/>
+      <c r="R313" s="5" t="inlineStr">
+        <is>
+          <t>答案是「小腎盞、大腎盞、腎盂」，因為尿依序經小腎盞、大腎盞和腎盂。</t>
+        </is>
+      </c>
+      <c r="S313" s="5" t="inlineStr">
+        <is>
+          <t>小盞接尿，大盞再到腎盂</t>
+        </is>
+      </c>
+      <c r="T313" s="3" t="str">
+        <v>kidney-structure；anatomy/AB-05_15 p.3, anatomy/AB-05_15 p.4, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.3, physiology/CH09 p.4</v>
+      </c>
+      <c r="U313" s="3" t="str"/>
+      <c r="V313" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W313" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X313" s="3" t="str"/>
+    </row>
+    <row r="314" ht="110" customHeight="1">
+      <c r="A314" s="3" t="str"/>
+      <c r="B314" s="7" t="str">
+        <v>kidney-anatomy-case-q03</v>
+      </c>
+      <c r="C314" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F314" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G314" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H314" s="5" t="inlineStr">
+        <is>
+          <t>尿液離開腎盂後，先送到膀胱，再排到身體外面，這兩段各走哪條管？</t>
+        </is>
+      </c>
+      <c r="I314" s="5" t="inlineStr">
+        <is>
+          <t>先輸尿管，再尿道</t>
+        </is>
+      </c>
+      <c r="J314" s="5" t="inlineStr">
+        <is>
+          <t>先尿道，再輸尿管</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="inlineStr">
+        <is>
+          <t>先輸尿管，再腎小管</t>
+        </is>
+      </c>
+      <c r="L314" s="5" t="inlineStr">
+        <is>
+          <t>先腎小管，再尿道</t>
+        </is>
+      </c>
+      <c r="M314" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N314" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O314" s="5" t="inlineStr">
+        <is>
+          <t>因為輸尿管接腎臟與膀胱，尿道接膀胱與體外，所以選「先輸尿管，再尿道」。選「先尿道，再輸尿管」的同學，把這兩條管的先後與工作交換了。</t>
+        </is>
+      </c>
+      <c r="P314" s="5" t="inlineStr">
+        <is>
+          <t>先想想：腎臟到膀胱的管，和膀胱到體外的管一樣嗎？</t>
+        </is>
+      </c>
+      <c r="Q314" s="5" t="str"/>
+      <c r="R314" s="5" t="inlineStr">
+        <is>
+          <t>答案是「先輸尿管，再尿道」，因為輸尿管先送尿到膀胱，尿道再排出。</t>
+        </is>
+      </c>
+      <c r="S314" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管送進，尿道送出去</t>
+        </is>
+      </c>
+      <c r="T314" s="3" t="str">
+        <v>urinary-system-overview；physiology/CH09 p.9, physiology/CH09 p.10, anatomy/AB-05_15 p.2, anatomy/AB-05_15 p.9, anatomy/AB-05_15 p.10, anatomy/AB-05_15 p.11, anatomy/AB-05_15 p.14</v>
+      </c>
+      <c r="U314" s="3" t="str"/>
+      <c r="V314" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W314" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X314" s="3" t="str"/>
+    </row>
+    <row r="315" ht="110" customHeight="1">
+      <c r="A315" s="3" t="str"/>
+      <c r="B315" s="7" t="str">
+        <v>kidney-anatomy-case-q04</v>
+      </c>
+      <c r="C315" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F315" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G315" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H315" s="5" t="inlineStr">
+        <is>
+          <t>腎上腺與腎臟有什麼關係？</t>
+        </is>
+      </c>
+      <c r="I315" s="5" t="inlineStr">
+        <is>
+          <t>它是腎臟的腎錐體尖端</t>
+        </is>
+      </c>
+      <c r="J315" s="5" t="inlineStr">
+        <is>
+          <t>它靠近腎臟，但屬另一個器官</t>
+        </is>
+      </c>
+      <c r="K315" s="5" t="inlineStr">
+        <is>
+          <t>它是腎臟伸進髓質的腎柱</t>
+        </is>
+      </c>
+      <c r="L315" s="5" t="inlineStr">
+        <is>
+          <t>它是腎臟收集尿液的腎盂</t>
+        </is>
+      </c>
+      <c r="M315" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N315" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O315" s="5" t="inlineStr">
+        <is>
+          <t>因為腎上腺雖在腎臟附近，仍是另一個器官，所以選「它靠近腎臟，但屬另一個器官」。選「它是腎臟的腎錐體尖端」的同學，說的腎錐體尖端叫腎乳頭，並不是腎上腺。</t>
+        </is>
+      </c>
+      <c r="P315" s="5" t="inlineStr">
+        <is>
+          <t>先想想：住在附近，就表示是同一個器官嗎？</t>
+        </is>
+      </c>
+      <c r="Q315" s="5" t="str"/>
+      <c r="R315" s="5" t="inlineStr">
+        <is>
+          <t>答案是「它靠近腎臟，但屬另一個器官」，因為腎上腺鄰近腎臟，但兩者是不同器官。</t>
+        </is>
+      </c>
+      <c r="S315" s="5" t="inlineStr">
+        <is>
+          <t>腎上腺在旁邊，不是腎的一塊</t>
+        </is>
+      </c>
+      <c r="T315" s="3" t="str">
+        <v>kidney-structure；anatomy/AB-05_15 p.3, anatomy/AB-05_15 p.4, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.3, physiology/CH09 p.4
+kidney-position；anatomy/AB-05_15 p.2–3</v>
+      </c>
+      <c r="U315" s="3" t="str"/>
+      <c r="V315" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W315" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X315" s="3" t="str"/>
+    </row>
+    <row r="316" ht="110" customHeight="1">
+      <c r="A316" s="3" t="str"/>
+      <c r="B316" s="7" t="str">
+        <v>kidney-anatomy-case-q05</v>
+      </c>
+      <c r="C316" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>腎臟位置構造與功能</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F316" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G316" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H316" s="5" t="inlineStr">
+        <is>
+          <t>如果只用「尿有多少」介紹腎臟，還會漏掉哪一組工作？</t>
+        </is>
+      </c>
+      <c r="I316" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管送尿、尿道排尿</t>
+        </is>
+      </c>
+      <c r="J316" s="5" t="inlineStr">
+        <is>
+          <t>腎盞接尿、腎盂收集尿</t>
+        </is>
+      </c>
+      <c r="K316" s="5" t="inlineStr">
+        <is>
+          <t>發出造血訊號、活化維生素D</t>
+        </is>
+      </c>
+      <c r="L316" s="5" t="inlineStr">
+        <is>
+          <t>膀胱儲尿、括約肌管出口</t>
+        </is>
+      </c>
+      <c r="M316" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N316" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O316" s="5" t="inlineStr">
+        <is>
+          <t>因為腎臟也參與紅血球生成與維生素D活化，所以選「發出造血訊號、活化維生素D」。選「膀胱儲尿、括約肌管出口」的同學，說的是膀胱和排尿出口的工作。</t>
+        </is>
+      </c>
+      <c r="P316" s="5" t="inlineStr">
+        <is>
+          <t>先想想：除了製造尿液，腎臟還會發出什麼訊號？</t>
+        </is>
+      </c>
+      <c r="Q316" s="5" t="str"/>
+      <c r="R316" s="5" t="inlineStr">
+        <is>
+          <t>答案是「發出造血訊號、活化維生素D」，因為腎臟還有造血訊號與維生素D活化功能。</t>
+        </is>
+      </c>
+      <c r="S316" s="5" t="inlineStr">
+        <is>
+          <t>腎不只造尿，也管造血與鈣</t>
+        </is>
+      </c>
+      <c r="T316" s="3" t="str">
+        <v>kidney-endocrine；physiology/CH09 p.9, anatomy/AB-05_15 p.9, physiology/CH09 p.6, physiology/CH09 p.7, physiology/CH09 p.35</v>
+      </c>
+      <c r="U316" s="3" t="str"/>
+      <c r="V316" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="W316" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/kidney-anatomy-v1/index.html</v>
+      </c>
+      <c r="X316" s="3" t="str"/>
+    </row>
+    <row r="317" ht="110" customHeight="1">
+      <c r="A317" s="3" t="str"/>
+      <c r="B317" s="7" t="str">
+        <v>nephron-circulation-foundation-q01</v>
+      </c>
+      <c r="C317" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F317" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G317" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H317" s="5" t="inlineStr">
+        <is>
+          <t>腎元是腎臟裡處理液體的小單位，它由哪兩部分組成？</t>
+        </is>
+      </c>
+      <c r="I317" s="5" t="inlineStr">
+        <is>
+          <t>腎小體與腎小管</t>
+        </is>
+      </c>
+      <c r="J317" s="5" t="inlineStr">
+        <is>
+          <t>腎盂與輸尿管</t>
+        </is>
+      </c>
+      <c r="K317" s="5" t="inlineStr">
+        <is>
+          <t>膀胱與尿道</t>
+        </is>
+      </c>
+      <c r="L317" s="5" t="inlineStr">
+        <is>
+          <t>腎被膜與腎筋膜</t>
+        </is>
+      </c>
+      <c r="M317" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N317" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O317" s="5" t="inlineStr">
+        <is>
+          <t>因為腎元由先過濾的腎小體與接著處理液體的腎小管組成，所以選「腎小體與腎小管」。選「腎盂與輸尿管」的同學，所選的腎盂與輸尿管是後面的收尿和送尿通路。</t>
+        </is>
+      </c>
+      <c r="P317" s="5" t="inlineStr">
+        <is>
+          <t>先想想：腎元裡，哪一部分先過濾，哪一部分接著處理？</t>
+        </is>
+      </c>
+      <c r="Q317" s="5" t="str"/>
+      <c r="R317" s="5" t="inlineStr">
+        <is>
+          <t>答案是「腎小體與腎小管」，因為腎小體和腎小管一起構成腎元。</t>
+        </is>
+      </c>
+      <c r="S317" s="5" t="inlineStr">
+        <is>
+          <t>一個腎元，小體接小管</t>
+        </is>
+      </c>
+      <c r="T317" s="3" t="str">
+        <v>nephron-histology；physiology/CH09 p.6, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.4, physiology/CH09 p.7</v>
+      </c>
+      <c r="U317" s="3" t="str"/>
+      <c r="V317" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W317" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X317" s="3" t="str"/>
+    </row>
+    <row r="318" ht="110" customHeight="1">
+      <c r="A318" s="3" t="str"/>
+      <c r="B318" s="7" t="str">
+        <v>nephron-circulation-foundation-q02</v>
+      </c>
+      <c r="C318" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F318" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G318" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H318" s="5" t="inlineStr">
+        <is>
+          <t>皮質腎元和近髓質腎元是兩種腎元，它們的腎小體在哪裡？</t>
+        </is>
+      </c>
+      <c r="I318" s="5" t="inlineStr">
+        <is>
+          <t>近髓質型的腎小體在髓質深處</t>
+        </is>
+      </c>
+      <c r="J318" s="5" t="inlineStr">
+        <is>
+          <t>兩種的腎小體都在皮質</t>
+        </is>
+      </c>
+      <c r="K318" s="5" t="inlineStr">
+        <is>
+          <t>兩種的亨利氏環都只在皮質</t>
+        </is>
+      </c>
+      <c r="L318" s="5" t="inlineStr">
+        <is>
+          <t>皮質型的亨利氏環較長，伸到髓質深處</t>
+        </is>
+      </c>
+      <c r="M318" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N318" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O318" s="5" t="inlineStr">
+        <is>
+          <t>因為兩種腎元的腎小體都在腎臟外層皮質，所以選「兩種的腎小體都在皮質」。選「近髓質型的腎小體在髓質深處」的同學，把「靠近髓質交界」當成「已經在髓質裡」。</t>
+        </is>
+      </c>
+      <c r="P318" s="5" t="inlineStr">
+        <is>
+          <t>先想想：靠近髓質交界，和進到髓質裡一樣嗎？</t>
+        </is>
+      </c>
+      <c r="Q318" s="5" t="str"/>
+      <c r="R318" s="5" t="inlineStr">
+        <is>
+          <t>答案是「兩種的腎小體都在皮質」，因為兩型腎元的腎小體都位在皮質。</t>
+        </is>
+      </c>
+      <c r="S318" s="5" t="inlineStr">
+        <is>
+          <t>近髓質型，小體仍在皮質</t>
+        </is>
+      </c>
+      <c r="T318" s="3" t="str">
+        <v>nephron-types；physiology/CH09 p.4, anatomy/AB-05_15 p.6, anatomy/AB-05_15 p.8, physiology/CH09 p.20</v>
+      </c>
+      <c r="U318" s="3" t="str"/>
+      <c r="V318" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W318" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X318" s="3" t="str"/>
+    </row>
+    <row r="319" ht="110" customHeight="1">
+      <c r="A319" s="3" t="str"/>
+      <c r="B319" s="7" t="str">
+        <v>nephron-circulation-foundation-q03</v>
+      </c>
+      <c r="C319" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F319" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G319" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H319" s="5" t="inlineStr">
+        <is>
+          <t>某段腎小管的細胞像小方塊，內側有一圈細刷毛般的「刷狀緣」，最像哪一段？</t>
+        </is>
+      </c>
+      <c r="I319" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環薄段</t>
+        </is>
+      </c>
+      <c r="J319" s="5" t="inlineStr">
+        <is>
+          <t>遠曲小管</t>
+        </is>
+      </c>
+      <c r="K319" s="5" t="inlineStr">
+        <is>
+          <t>近曲小管</t>
+        </is>
+      </c>
+      <c r="L319" s="5" t="inlineStr">
+        <is>
+          <t>鮑氏囊腔</t>
+        </is>
+      </c>
+      <c r="M319" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N319" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O319" s="5" t="inlineStr">
+        <is>
+          <t>因為近曲小管有明顯刷狀緣，所以選「近曲小管」。選「遠曲小管」的同學，所選的遠曲小管雖也有立方上皮，卻沒有明顯的刷狀緣。</t>
+        </is>
+      </c>
+      <c r="P319" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪一段的小管細胞有明顯刷狀緣？</t>
+        </is>
+      </c>
+      <c r="Q319" s="5" t="str"/>
+      <c r="R319" s="5" t="inlineStr">
+        <is>
+          <t>答案是「近曲小管」，因為明顯刷狀緣是近曲小管的特徵。</t>
+        </is>
+      </c>
+      <c r="S319" s="5" t="inlineStr">
+        <is>
+          <t>近曲有刷毛，遠曲不明顯</t>
+        </is>
+      </c>
+      <c r="T319" s="3" t="str">
+        <v>nephron-histology；physiology/CH09 p.6, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.4, physiology/CH09 p.7</v>
+      </c>
+      <c r="U319" s="3" t="str"/>
+      <c r="V319" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W319" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X319" s="3" t="str"/>
+    </row>
+    <row r="320" ht="110" customHeight="1">
+      <c r="A320" s="3" t="str"/>
+      <c r="B320" s="7" t="str">
+        <v>nephron-circulation-foundation-q04</v>
+      </c>
+      <c r="C320" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F320" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G320" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H320" s="5" t="inlineStr">
+        <is>
+          <t>血液進出腎絲球時，先走進來和再走出去的血管各叫什麼？</t>
+        </is>
+      </c>
+      <c r="I320" s="5" t="inlineStr">
+        <is>
+          <t>入球小靜脈、出球小靜脈</t>
+        </is>
+      </c>
+      <c r="J320" s="5" t="inlineStr">
+        <is>
+          <t>腎靜脈、入球小動脈</t>
+        </is>
+      </c>
+      <c r="K320" s="5" t="inlineStr">
+        <is>
+          <t>管周微血管、腎動脈</t>
+        </is>
+      </c>
+      <c r="L320" s="5" t="inlineStr">
+        <is>
+          <t>入球小動脈、出球小動脈</t>
+        </is>
+      </c>
+      <c r="M320" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N320" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O320" s="5" t="inlineStr">
+        <is>
+          <t>因為血液從入球小動脈進來，再由出球小動脈出去，所以選「入球小動脈、出球小動脈」。選「入球小靜脈、出球小靜脈」的同學，把這兩條小動脈寫成小靜脈了。</t>
+        </is>
+      </c>
+      <c r="P320" s="5" t="inlineStr">
+        <is>
+          <t>先想想：名字裡的「入」和「出」各在說什麼方向？</t>
+        </is>
+      </c>
+      <c r="Q320" s="5" t="str"/>
+      <c r="R320" s="5" t="inlineStr">
+        <is>
+          <t>答案是「入球小動脈、出球小動脈」，因為腎絲球前後相接的是入球、出球小動脈。</t>
+        </is>
+      </c>
+      <c r="S320" s="5" t="inlineStr">
+        <is>
+          <t>入球進，出球出，都是小動脈</t>
+        </is>
+      </c>
+      <c r="T320" s="3" t="str">
+        <v>renal-blood-flow；physiology/CH09 p.8, physiology/CH09 p.13, physiology/CH09 p.27, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U320" s="3" t="str"/>
+      <c r="V320" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W320" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X320" s="3" t="str"/>
+    </row>
+    <row r="321" ht="110" customHeight="1">
+      <c r="A321" s="3" t="str"/>
+      <c r="B321" s="7" t="str">
+        <v>nephron-circulation-foundation-q05</v>
+      </c>
+      <c r="C321" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F321" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G321" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H321" s="5" t="inlineStr">
+        <is>
+          <t>近腎絲球器是小管與血管靠近的感測站，其中誰負責感受管液裡的鈉變化？</t>
+        </is>
+      </c>
+      <c r="I321" s="5" t="inlineStr">
+        <is>
+          <t>遠曲小管的緻密斑</t>
+        </is>
+      </c>
+      <c r="J321" s="5" t="inlineStr">
+        <is>
+          <t>入球血管壁的近腎絲球細胞</t>
+        </is>
+      </c>
+      <c r="K321" s="5" t="inlineStr">
+        <is>
+          <t>鮑氏囊外壁的細胞</t>
+        </is>
+      </c>
+      <c r="L321" s="5" t="inlineStr">
+        <is>
+          <t>腎盂內面的細胞</t>
+        </is>
+      </c>
+      <c r="M321" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N321" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O321" s="5" t="inlineStr">
+        <is>
+          <t>因為遠曲小管的緻密斑感受管液鈉的變化，所以選「遠曲小管的緻密斑」。選「入球血管壁的近腎絲球細胞」的同學，所選的近腎絲球細胞主要負責感受壓力並分泌腎素。</t>
+        </is>
+      </c>
+      <c r="P321" s="5" t="inlineStr">
+        <is>
+          <t>先想想：看管液裡的鈉，和分泌腎素，是同一種細胞嗎？</t>
+        </is>
+      </c>
+      <c r="Q321" s="5" t="str"/>
+      <c r="R321" s="5" t="inlineStr">
+        <is>
+          <t>答案是「遠曲小管的緻密斑」，因為緻密斑在遠曲小管，感受管液鈉變化。</t>
+        </is>
+      </c>
+      <c r="S321" s="5" t="inlineStr">
+        <is>
+          <t>緻密斑看鈉，入球壁分腎素</t>
+        </is>
+      </c>
+      <c r="T321" s="3" t="str">
+        <v>juxtaglomerular-apparatus；physiology/CH09 p.6, physiology/CH09 p.7, anatomy/AB-05_15 p.6, physiology/CH09 p.4</v>
+      </c>
+      <c r="U321" s="3" t="str"/>
+      <c r="V321" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W321" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X321" s="3" t="str"/>
+    </row>
+    <row r="322" ht="110" customHeight="1">
+      <c r="A322" s="3" t="str"/>
+      <c r="B322" s="7" t="str">
+        <v>nephron-circulation-foundation-q06</v>
+      </c>
+      <c r="C322" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F322" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G322" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H322" s="5" t="inlineStr">
+        <is>
+          <t>過濾分率（FF）是在問送到腎臟的血漿有多少比例被濾出去，應怎麼算？</t>
+        </is>
+      </c>
+      <c r="I322" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘濾出的量（GFR）除以腎血流量（RBF）</t>
+        </is>
+      </c>
+      <c r="J322" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘濾出的量（GFR）除以腎血漿流量（RPF）</t>
+        </is>
+      </c>
+      <c r="K322" s="5" t="inlineStr">
+        <is>
+          <t>腎血流量（RBF）除以每分鐘濾出的量（GFR）</t>
+        </is>
+      </c>
+      <c r="L322" s="5" t="inlineStr">
+        <is>
+          <t>腎血漿流量（RPF）除以每分鐘濾出的量（GFR）</t>
+        </is>
+      </c>
+      <c r="M322" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N322" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O322" s="5" t="inlineStr">
+        <is>
+          <t>因為這題要比較濾出量和送來的血漿量，所以用每分鐘濾出的量除以腎血漿流量。選「每分鐘濾出的量（GFR）除以腎血流量（RBF）」的同學，把包含血球的整份血流當成血漿了。</t>
+        </is>
+      </c>
+      <c r="P322" s="5" t="inlineStr">
+        <is>
+          <t>先想想：要算血漿被濾出的比例，應拿血漿還是整份血液來比？</t>
+        </is>
+      </c>
+      <c r="Q322" s="5" t="str"/>
+      <c r="R322" s="5" t="inlineStr">
+        <is>
+          <t>答案是「每分鐘濾出的量（GFR）除以腎血漿流量（RPF）」，因為FF是GFR除以RPF，兩者都以每分鐘體積表示。</t>
+        </is>
+      </c>
+      <c r="S322" s="5" t="inlineStr">
+        <is>
+          <t>過濾分率，濾出量除血漿量</t>
+        </is>
+      </c>
+      <c r="T322" s="3" t="str">
+        <v>renal-blood-flow；physiology/CH09 p.8, physiology/CH09 p.13, physiology/CH09 p.27, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U322" s="3" t="str"/>
+      <c r="V322" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W322" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X322" s="3" t="str"/>
+    </row>
+    <row r="323" ht="110" customHeight="1">
+      <c r="A323" s="3" t="str"/>
+      <c r="B323" s="7" t="str">
+        <v>nephron-circulation-case-q01</v>
+      </c>
+      <c r="C323" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F323" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G323" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H323" s="5" t="inlineStr">
+        <is>
+          <t>某腎元的亨利氏環很長，伸進髓質深處，腎小體靠近皮質與髓質交界，腎小體仍在哪一區？</t>
+        </is>
+      </c>
+      <c r="I323" s="5" t="inlineStr">
+        <is>
+          <t>髓質深處</t>
+        </is>
+      </c>
+      <c r="J323" s="5" t="inlineStr">
+        <is>
+          <t>腎盂</t>
+        </is>
+      </c>
+      <c r="K323" s="5" t="inlineStr">
+        <is>
+          <t>皮質</t>
+        </is>
+      </c>
+      <c r="L323" s="5" t="inlineStr">
+        <is>
+          <t>腎乳頭出口</t>
+        </is>
+      </c>
+      <c r="M323" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N323" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O323" s="5" t="inlineStr">
+        <is>
+          <t>因為伸進髓質深處的是長環，而腎小體仍在交界旁的皮質，所以選「皮質」。選「髓質深處」的同學，把長環的位置當成腎小體的位置了。</t>
+        </is>
+      </c>
+      <c r="P323" s="5" t="inlineStr">
+        <is>
+          <t>先想想：深入髓質的是小體，還是長環？</t>
+        </is>
+      </c>
+      <c r="Q323" s="5" t="str"/>
+      <c r="R323" s="5" t="inlineStr">
+        <is>
+          <t>答案是「皮質」，因為近髓質型腎元的腎小體仍在皮質。</t>
+        </is>
+      </c>
+      <c r="S323" s="5" t="inlineStr">
+        <is>
+          <t>長環入髓質，小體留皮質</t>
+        </is>
+      </c>
+      <c r="T323" s="3" t="str">
+        <v>nephron-types；physiology/CH09 p.4, anatomy/AB-05_15 p.6, anatomy/AB-05_15 p.8, physiology/CH09 p.20</v>
+      </c>
+      <c r="U323" s="3" t="str"/>
+      <c r="V323" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W323" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X323" s="3" t="str"/>
+    </row>
+    <row r="324" ht="110" customHeight="1">
+      <c r="A324" s="3" t="str"/>
+      <c r="B324" s="7" t="str">
+        <v>nephron-circulation-case-q02</v>
+      </c>
+      <c r="C324" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F324" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G324" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H324" s="5" t="inlineStr">
+        <is>
+          <t>血液剛離開出球小動脈，接下來會進入哪裡？</t>
+        </is>
+      </c>
+      <c r="I324" s="5" t="inlineStr">
+        <is>
+          <t>入球小動脈</t>
+        </is>
+      </c>
+      <c r="J324" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球微血管</t>
+        </is>
+      </c>
+      <c r="K324" s="5" t="inlineStr">
+        <is>
+          <t>腎靜脈</t>
+        </is>
+      </c>
+      <c r="L324" s="5" t="inlineStr">
+        <is>
+          <t>管周微血管或直血管</t>
+        </is>
+      </c>
+      <c r="M324" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N324" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O324" s="5" t="inlineStr">
+        <is>
+          <t>因為出球小動脈後還有一套微血管，所以接著進入管周微血管或直血管。選「腎靜脈」的同學，跳過了這段微血管。</t>
+        </is>
+      </c>
+      <c r="P324" s="5" t="inlineStr">
+        <is>
+          <t>先想想：血液離開腎絲球後，還要經過哪一套微血管？</t>
+        </is>
+      </c>
+      <c r="Q324" s="5" t="str"/>
+      <c r="R324" s="5" t="inlineStr">
+        <is>
+          <t>答案是「管周微血管或直血管」，因為出球小動脈後接管周微血管或直血管。</t>
+        </is>
+      </c>
+      <c r="S324" s="5" t="inlineStr">
+        <is>
+          <t>出球後，還有管周或直血管</t>
+        </is>
+      </c>
+      <c r="T324" s="3" t="str">
+        <v>renal-blood-flow；physiology/CH09 p.8, physiology/CH09 p.13, physiology/CH09 p.27, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U324" s="3" t="str"/>
+      <c r="V324" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W324" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X324" s="3" t="str"/>
+    </row>
+    <row r="325" ht="110" customHeight="1">
+      <c r="A325" s="3" t="str"/>
+      <c r="B325" s="7" t="str">
+        <v>nephron-circulation-case-q03</v>
+      </c>
+      <c r="C325" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F325" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G325" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H325" s="5" t="inlineStr">
+        <is>
+          <t>在腎髓質深處看到一段細管，管壁是很扁的「扁平上皮」，最像哪一段？</t>
+        </is>
+      </c>
+      <c r="I325" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環薄段</t>
+        </is>
+      </c>
+      <c r="J325" s="5" t="inlineStr">
+        <is>
+          <t>近曲小管</t>
+        </is>
+      </c>
+      <c r="K325" s="5" t="inlineStr">
+        <is>
+          <t>遠曲小管</t>
+        </is>
+      </c>
+      <c r="L325" s="5" t="inlineStr">
+        <is>
+          <t>集尿管</t>
+        </is>
+      </c>
+      <c r="M325" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N325" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O325" s="5" t="inlineStr">
+        <is>
+          <t>因為亨利氏環薄段的管壁是扁平上皮，所以選「亨利氏環薄段」。選「近曲小管」的同學，所選的近曲小管是有刷狀緣的立方上皮，樣子不同。</t>
+        </is>
+      </c>
+      <c r="P325" s="5" t="inlineStr">
+        <is>
+          <t>先想想：薄薄扁扁的管壁，和有刷狀緣的小方塊細胞一樣嗎？</t>
+        </is>
+      </c>
+      <c r="Q325" s="5" t="str"/>
+      <c r="R325" s="5" t="inlineStr">
+        <is>
+          <t>答案是「亨利氏環薄段」，因為扁平上皮符合亨利氏環薄段。</t>
+        </is>
+      </c>
+      <c r="S325" s="5" t="inlineStr">
+        <is>
+          <t>亨利薄段，細胞扁扁的</t>
+        </is>
+      </c>
+      <c r="T325" s="3" t="str">
+        <v>nephron-histology；physiology/CH09 p.6, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6, physiology/CH09 p.4, physiology/CH09 p.7</v>
+      </c>
+      <c r="U325" s="3" t="str"/>
+      <c r="V325" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W325" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X325" s="3" t="str"/>
+    </row>
+    <row r="326" ht="110" customHeight="1">
+      <c r="A326" s="3" t="str"/>
+      <c r="B326" s="7" t="str">
+        <v>nephron-circulation-case-q04</v>
+      </c>
+      <c r="C326" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F326" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G326" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H326" s="5" t="inlineStr">
+        <is>
+          <t>腎臟需要調節血流時，會由哪個位置的細胞分泌腎素？</t>
+        </is>
+      </c>
+      <c r="I326" s="5" t="inlineStr">
+        <is>
+          <t>遠曲小管的緻密斑</t>
+        </is>
+      </c>
+      <c r="J326" s="5" t="inlineStr">
+        <is>
+          <t>入球小動脈壁的近腎絲球細胞</t>
+        </is>
+      </c>
+      <c r="K326" s="5" t="inlineStr">
+        <is>
+          <t>腎盂內面</t>
+        </is>
+      </c>
+      <c r="L326" s="5" t="inlineStr">
+        <is>
+          <t>鮑氏囊外壁</t>
+        </is>
+      </c>
+      <c r="M326" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N326" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O326" s="5" t="inlineStr">
+        <is>
+          <t>因為入球小動脈壁的近腎絲球細胞會分泌腎素，所以選「入球小動脈壁的近腎絲球細胞」。選「遠曲小管的緻密斑」的同學，所選的緻密斑負責感受管液的鈉，和分泌腎素的細胞不同。</t>
+        </is>
+      </c>
+      <c r="P326" s="5" t="inlineStr">
+        <is>
+          <t>先想想：分泌腎素的細胞在血管壁，還是管液的感測點？</t>
+        </is>
+      </c>
+      <c r="Q326" s="5" t="str"/>
+      <c r="R326" s="5" t="inlineStr">
+        <is>
+          <t>答案是「入球小動脈壁的近腎絲球細胞」，因為腎素由入球小動脈壁的近腎絲球細胞分泌。</t>
+        </is>
+      </c>
+      <c r="S326" s="5" t="inlineStr">
+        <is>
+          <t>腎素的家，在入球血管壁</t>
+        </is>
+      </c>
+      <c r="T326" s="3" t="str">
+        <v>juxtaglomerular-apparatus；physiology/CH09 p.6, physiology/CH09 p.7, anatomy/AB-05_15 p.6, physiology/CH09 p.4</v>
+      </c>
+      <c r="U326" s="3" t="str"/>
+      <c r="V326" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W326" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X326" s="3" t="str"/>
+    </row>
+    <row r="327" ht="110" customHeight="1">
+      <c r="A327" s="3" t="str"/>
+      <c r="B327" s="7" t="str">
+        <v>nephron-circulation-case-q05</v>
+      </c>
+      <c r="C327" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>腎元腎血流與近腎絲球器</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F327" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G327" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H327" s="5" t="inlineStr">
+        <is>
+          <t>同學算過濾分率（FF）時，把每分鐘濾出的量（GFR）除以整份腎血流量，應改哪裡？</t>
+        </is>
+      </c>
+      <c r="I327" s="5" t="inlineStr">
+        <is>
+          <t>上面的數改成腎血流量</t>
+        </is>
+      </c>
+      <c r="J327" s="5" t="inlineStr">
+        <is>
+          <t>上面的數改成腎血漿流量</t>
+        </is>
+      </c>
+      <c r="K327" s="5" t="inlineStr">
+        <is>
+          <t>下面的數改成腎血漿流量</t>
+        </is>
+      </c>
+      <c r="L327" s="5" t="inlineStr">
+        <is>
+          <t>把上面和下面的數交換</t>
+        </is>
+      </c>
+      <c r="M327" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N327" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O327" s="5" t="inlineStr">
+        <is>
+          <t>因為FF比較的是送來血漿中有多少被濾出，所以下面的數要用腎血漿流量。選「上面的數改成腎血漿流量」的同學，改動了上面的濾出量，算的比例就不同了。</t>
+        </is>
+      </c>
+      <c r="P327" s="5" t="inlineStr">
+        <is>
+          <t>先想想：FF要比較血漿的哪一部分，下面應放什麼？</t>
+        </is>
+      </c>
+      <c r="Q327" s="5" t="str"/>
+      <c r="R327" s="5" t="inlineStr">
+        <is>
+          <t>答案是「下面的數改成腎血漿流量」，因為FF的下面要放腎血漿流量，GFR仍放上面。</t>
+        </is>
+      </c>
+      <c r="S327" s="5" t="inlineStr">
+        <is>
+          <t>算FF，下面放血漿流量</t>
+        </is>
+      </c>
+      <c r="T327" s="3" t="str">
+        <v>renal-blood-flow；physiology/CH09 p.8, physiology/CH09 p.13, physiology/CH09 p.27, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U327" s="3" t="str"/>
+      <c r="V327" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="W327" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/nephron-circulation-v1/index.html</v>
+      </c>
+      <c r="X327" s="3" t="str"/>
+    </row>
+    <row r="328" ht="110" customHeight="1">
+      <c r="A328" s="3" t="str"/>
+      <c r="B328" s="7" t="str">
+        <v>filtration-clearance-foundation-q01</v>
+      </c>
+      <c r="C328" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D328" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G328" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H328" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球先把血液裡的水和部分物質濾出來，它們會往哪裡走？</t>
+        </is>
+      </c>
+      <c r="I328" s="5" t="inlineStr">
+        <is>
+          <t>從腎絲球微血管進入鮑氏囊腔</t>
+        </is>
+      </c>
+      <c r="J328" s="5" t="inlineStr">
+        <is>
+          <t>從腎絲球微血管進入入球小動脈</t>
+        </is>
+      </c>
+      <c r="K328" s="5" t="inlineStr">
+        <is>
+          <t>從腎絲球微血管進入腎盂</t>
+        </is>
+      </c>
+      <c r="L328" s="5" t="inlineStr">
+        <is>
+          <t>從腎絲球微血管進入輸尿管</t>
+        </is>
+      </c>
+      <c r="M328" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N328" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O328" s="5" t="inlineStr">
+        <is>
+          <t>因為水和能通過的物質會從腎絲球血管進入鮑氏囊，所以選「從腎絲球微血管進入鮑氏囊腔」。選「從腎絲球微血管進入入球小動脈」的同學，把濾液的去處選成了血管，濾液應進入鮑氏囊。</t>
+        </is>
+      </c>
+      <c r="P328" s="5" t="inlineStr">
+        <is>
+          <t>先想想：水先在血管裡，過濾後進到哪個空間？</t>
+        </is>
+      </c>
+      <c r="Q328" s="5" t="str"/>
+      <c r="R328" s="5" t="inlineStr">
+        <is>
+          <t>答案是「從腎絲球微血管進入鮑氏囊腔」，因為過濾是從腎絲球微血管到鮑氏囊腔。</t>
+        </is>
+      </c>
+      <c r="S328" s="5" t="inlineStr">
+        <is>
+          <t>血管先濾水，鮑氏囊來接</t>
+        </is>
+      </c>
+      <c r="T328" s="3" t="str">
+        <v>glomerular-filtration；physiology/CH09 p.11, physiology/CH09 p.4, physiology/CH09 p.12, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6</v>
+      </c>
+      <c r="U328" s="3" t="str"/>
+      <c r="V328" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W328" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X328" s="3" t="str"/>
+    </row>
+    <row r="329" ht="110" customHeight="1">
+      <c r="A329" s="3" t="str"/>
+      <c r="B329" s="7" t="str">
+        <v>filtration-clearance-foundation-q02</v>
+      </c>
+      <c r="C329" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D329" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F329" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G329" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H329" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球有三層過濾膜，像連在一起的濾網，它們是哪三層？</t>
+        </is>
+      </c>
+      <c r="I329" s="5" t="inlineStr">
+        <is>
+          <t>微血管內皮、腎被膜、鮑氏囊壁層</t>
+        </is>
+      </c>
+      <c r="J329" s="5" t="inlineStr">
+        <is>
+          <t>微血管內皮、基底膜、足細胞</t>
+        </is>
+      </c>
+      <c r="K329" s="5" t="inlineStr">
+        <is>
+          <t>近曲小管、遠曲小管、集尿管</t>
+        </is>
+      </c>
+      <c r="L329" s="5" t="inlineStr">
+        <is>
+          <t>入球小動脈、出球小動脈、腎靜脈</t>
+        </is>
+      </c>
+      <c r="M329" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N329" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O329" s="5" t="inlineStr">
+        <is>
+          <t>因為過濾膜由微血管內皮、基底膜與鮑氏囊臟層的足細胞組成，所以選「微血管內皮、基底膜、足細胞」。選「微血管內皮、腎被膜、鮑氏囊壁層」的同學，把外面的腎被膜和鮑氏囊壁層當成了過濾膜。</t>
+        </is>
+      </c>
+      <c r="P329" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪三層真的在過濾，哪一些只是外面包住的構造？</t>
+        </is>
+      </c>
+      <c r="Q329" s="5" t="str"/>
+      <c r="R329" s="5" t="inlineStr">
+        <is>
+          <t>答案是「微血管內皮、基底膜、足細胞」，因為三層過濾膜是微血管內皮、基底膜與足細胞。</t>
+        </is>
+      </c>
+      <c r="S329" s="5" t="inlineStr">
+        <is>
+          <t>內皮、基底膜、足細胞來過濾</t>
+        </is>
+      </c>
+      <c r="T329" s="3" t="str">
+        <v>glomerular-filtration；physiology/CH09 p.11, physiology/CH09 p.4, physiology/CH09 p.12, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6</v>
+      </c>
+      <c r="U329" s="3" t="str"/>
+      <c r="V329" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W329" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X329" s="3" t="str"/>
+    </row>
+    <row r="330" ht="110" customHeight="1">
+      <c r="A330" s="3" t="str"/>
+      <c r="B330" s="7" t="str">
+        <v>filtration-clearance-foundation-q03</v>
+      </c>
+      <c r="C330" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D330" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F330" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G330" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H330" s="5" t="inlineStr">
+        <is>
+          <t>血漿是血液裡不含血球的液體，和剛濾進鮑氏囊的液體相比，哪種物質的量差別最明顯？</t>
+        </is>
+      </c>
+      <c r="I330" s="5" t="inlineStr">
+        <is>
+          <t>血漿裡的血球</t>
+        </is>
+      </c>
+      <c r="J330" s="5" t="inlineStr">
+        <is>
+          <t>兩邊的水</t>
+        </is>
+      </c>
+      <c r="K330" s="5" t="inlineStr">
+        <is>
+          <t>兩邊的白蛋白</t>
+        </is>
+      </c>
+      <c r="L330" s="5" t="inlineStr">
+        <is>
+          <t>兩邊的葡萄糖</t>
+        </is>
+      </c>
+      <c r="M330" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N330" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O330" s="5" t="inlineStr">
+        <is>
+          <t>因為白蛋白屬於受過濾膜限制的蛋白質，所以它的含量能顯出兩邊差別，選「兩邊的白蛋白」。選「血漿裡的血球」的同學，把血漿當成含血球的整份血液了。</t>
+        </is>
+      </c>
+      <c r="P330" s="5" t="inlineStr">
+        <is>
+          <t>先想想：水和小物質能過去，哪一種蛋白質比較難過去？</t>
+        </is>
+      </c>
+      <c r="Q330" s="5" t="str"/>
+      <c r="R330" s="5" t="inlineStr">
+        <is>
+          <t>答案是「兩邊的白蛋白」，因為白蛋白受到過濾膜限制，血漿與濾液含量不同。</t>
+        </is>
+      </c>
+      <c r="S330" s="5" t="inlineStr">
+        <is>
+          <t>血漿有蛋白，濾液少白蛋白</t>
+        </is>
+      </c>
+      <c r="T330" s="3" t="str">
+        <v>glomerular-filtration；physiology/CH09 p.11, physiology/CH09 p.4, physiology/CH09 p.12, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6</v>
+      </c>
+      <c r="U330" s="3" t="str"/>
+      <c r="V330" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W330" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X330" s="3" t="str"/>
+    </row>
+    <row r="331" ht="110" customHeight="1">
+      <c r="A331" s="3" t="str"/>
+      <c r="B331" s="7" t="str">
+        <v>filtration-clearance-foundation-q04</v>
+      </c>
+      <c r="C331" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D331" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F331" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G331" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H331" s="5" t="inlineStr">
+        <is>
+          <t>哪一種力量會把水從腎絲球血管推進鮑氏囊，幫忙過濾？</t>
+        </is>
+      </c>
+      <c r="I331" s="5" t="inlineStr">
+        <is>
+          <t>鮑氏囊裡的水往回頂的壓力</t>
+        </is>
+      </c>
+      <c r="J331" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球血管內蛋白質拉住水的力量（膠體滲透壓）</t>
+        </is>
+      </c>
+      <c r="K331" s="5" t="inlineStr">
+        <is>
+          <t>尿道外括約肌收緊的力量</t>
+        </is>
+      </c>
+      <c r="L331" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球血管裡的水往外推的壓力（靜水壓）</t>
+        </is>
+      </c>
+      <c r="M331" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N331" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O331" s="5" t="inlineStr">
+        <is>
+          <t>因為腎絲球血管內往外推的水壓會促進過濾，所以要選這股往囊裡推的力量。選「腎絲球血管內蛋白質拉住水的力量（膠體滲透壓）」的同學，選的是把水留在血管內的力量，方向相反。</t>
+        </is>
+      </c>
+      <c r="P331" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪股力往囊裡推，哪股力往血管拉？</t>
+        </is>
+      </c>
+      <c r="Q331" s="5" t="str"/>
+      <c r="R331" s="5" t="inlineStr">
+        <is>
+          <t>答案是「腎絲球血管裡的水往外推的壓力（靜水壓）」，因為腎絲球血管內的靜水壓把水往囊裡推。</t>
+        </is>
+      </c>
+      <c r="S331" s="5" t="inlineStr">
+        <is>
+          <t>血管水壓往外推，幫忙濾水</t>
+        </is>
+      </c>
+      <c r="T331" s="3" t="str">
+        <v>glomerular-filtration；physiology/CH09 p.11, physiology/CH09 p.4, physiology/CH09 p.12, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6
+gfr-regulation；physiology/CH09 p.12（教師核定計算例）</v>
+      </c>
+      <c r="U331" s="3" t="str"/>
+      <c r="V331" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W331" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X331" s="3" t="str"/>
+    </row>
+    <row r="332" ht="110" customHeight="1">
+      <c r="A332" s="3" t="str"/>
+      <c r="B332" s="7" t="str">
+        <v>filtration-clearance-foundation-q05</v>
+      </c>
+      <c r="C332" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D332" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F332" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G332" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H332" s="5" t="inlineStr">
+        <is>
+          <t>清除率的算式是「尿中物質有多濃 × 每分鐘尿量 ÷ 血漿中有多濃」（C＝U×V／P），算出的數字在說什麼？</t>
+        </is>
+      </c>
+      <c r="I332" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘相當清掉多少毫升血漿裡的那種物質</t>
+        </is>
+      </c>
+      <c r="J332" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘從血漿移到尿裡多少毫克的那種物質</t>
+        </is>
+      </c>
+      <c r="K332" s="5" t="inlineStr">
+        <is>
+          <t>每毫升尿裡裝了多少毫克的那種物質</t>
+        </is>
+      </c>
+      <c r="L332" s="5" t="inlineStr">
+        <is>
+          <t>一天從膀胱排掉多少毫升的尿</t>
+        </is>
+      </c>
+      <c r="M332" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N332" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O332" s="5" t="inlineStr">
+        <is>
+          <t>因為清除率是把尿裡排掉的物質換算回血漿體積，所以選「每分鐘相當清掉多少毫升血漿裡的那種物質」。選「每分鐘從血漿移到尿裡多少毫克的那種物質」的同學，在說每分鐘排掉的物質重量，和每分鐘相當多少血漿是不同的量。</t>
+        </is>
+      </c>
+      <c r="P332" s="5" t="inlineStr">
+        <is>
+          <t>先想想：算出來的單位是毫升／分鐘，還是毫克／分鐘？</t>
+        </is>
+      </c>
+      <c r="Q332" s="5" t="str"/>
+      <c r="R332" s="5" t="inlineStr">
+        <is>
+          <t>答案是「每分鐘相當清掉多少毫升血漿裡的那種物質」，因為清除率表示每分鐘相當被清除的血漿體積。</t>
+        </is>
+      </c>
+      <c r="S332" s="5" t="inlineStr">
+        <is>
+          <t>清除率算血漿，不是算尿量</t>
+        </is>
+      </c>
+      <c r="T332" s="3" t="str">
+        <v>renal-clearance；physiology/CH09 p.26, physiology/CH09 p.27, physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15</v>
+      </c>
+      <c r="U332" s="3" t="str"/>
+      <c r="V332" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W332" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X332" s="3" t="str"/>
+    </row>
+    <row r="333" ht="110" customHeight="1">
+      <c r="A333" s="3" t="str"/>
+      <c r="B333" s="7" t="str">
+        <v>filtration-clearance-foundation-q06</v>
+      </c>
+      <c r="C333" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D333" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F333" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G333" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H333" s="5" t="inlineStr">
+        <is>
+          <t>哪一種物質在腎臟只被濾出，不被小管收回、也不額外送進管液，清除率可代表腎絲球過濾率（GFR）？</t>
+        </is>
+      </c>
+      <c r="I333" s="5" t="inlineStr">
+        <is>
+          <t>PAH（對胺馬尿酸）</t>
+        </is>
+      </c>
+      <c r="J333" s="5" t="inlineStr">
+        <is>
+          <t>菊糖</t>
+        </is>
+      </c>
+      <c r="K333" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="L333" s="5" t="inlineStr">
+        <is>
+          <t>尿素</t>
+        </is>
+      </c>
+      <c r="M333" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N333" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O333" s="5" t="inlineStr">
+        <is>
+          <t>因為菊糖被濾出後不再吸收也不分泌，所以它的清除率等於GFR，選「菊糖」。選「葡萄糖」的同學，所選的葡萄糖正常會被收回，和菊糖的處理方式不同。</t>
+        </is>
+      </c>
+      <c r="P333" s="5" t="inlineStr">
+        <is>
+          <t>先想想：要用來看過濾量，這種物質後來還能被加進或收回嗎？</t>
+        </is>
+      </c>
+      <c r="Q333" s="5" t="str"/>
+      <c r="R333" s="5" t="inlineStr">
+        <is>
+          <t>答案是「菊糖」，因為菊糖只過濾，清除率可代表GFR。</t>
+        </is>
+      </c>
+      <c r="S333" s="5" t="inlineStr">
+        <is>
+          <t>菊糖不加不收，清除率看過濾</t>
+        </is>
+      </c>
+      <c r="T333" s="3" t="str">
+        <v>renal-clearance；physiology/CH09 p.26, physiology/CH09 p.27, physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15</v>
+      </c>
+      <c r="U333" s="3" t="str"/>
+      <c r="V333" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W333" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X333" s="3" t="str"/>
+    </row>
+    <row r="334" ht="110" customHeight="1">
+      <c r="A334" s="3" t="str"/>
+      <c r="B334" s="7" t="str">
+        <v>filtration-clearance-case-q01</v>
+      </c>
+      <c r="C334" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D334" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F334" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G334" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H334" s="5" t="inlineStr">
+        <is>
+          <t>收集了一小時的尿，要放進清除率公式中的「每分鐘尿量」，應先怎麼算？</t>
+        </is>
+      </c>
+      <c r="I334" s="5" t="inlineStr">
+        <is>
+          <t>把一小時尿量乘以60</t>
+        </is>
+      </c>
+      <c r="J334" s="5" t="inlineStr">
+        <is>
+          <t>把一小時尿量直接放進去</t>
+        </is>
+      </c>
+      <c r="K334" s="5" t="inlineStr">
+        <is>
+          <t>把一小時尿量除以60</t>
+        </is>
+      </c>
+      <c r="L334" s="5" t="inlineStr">
+        <is>
+          <t>把一小時尿量除以血漿有多濃</t>
+        </is>
+      </c>
+      <c r="M334" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N334" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O334" s="5" t="inlineStr">
+        <is>
+          <t>因為一小時有60分鐘，所以要把總尿量除以60，才得到每分鐘尿量，選「把一小時尿量除以60」。選「把一小時尿量直接放進去」的同學，會把一小時的量誤當成一分鐘的量。</t>
+        </is>
+      </c>
+      <c r="P334" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一小時的尿要平均分給幾分鐘？</t>
+        </is>
+      </c>
+      <c r="Q334" s="5" t="str"/>
+      <c r="R334" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把一小時尿量除以60」，因為一小時尿量除以60才是每分鐘尿量。</t>
+        </is>
+      </c>
+      <c r="S334" s="5" t="inlineStr">
+        <is>
+          <t>小時尿量，除60變每分鐘</t>
+        </is>
+      </c>
+      <c r="T334" s="3" t="str">
+        <v>renal-clearance；physiology/CH09 p.26, physiology/CH09 p.27, physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15</v>
+      </c>
+      <c r="U334" s="3" t="str"/>
+      <c r="V334" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W334" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X334" s="3" t="str"/>
+    </row>
+    <row r="335" ht="110" customHeight="1">
+      <c r="A335" s="3" t="str"/>
+      <c r="B335" s="7" t="str">
+        <v>filtration-clearance-case-q02</v>
+      </c>
+      <c r="C335" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D335" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F335" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G335" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H335" s="5" t="inlineStr">
+        <is>
+          <t>某物質的清除率算出是69毫升／分鐘（69 mL/min），這是在說什麼？</t>
+        </is>
+      </c>
+      <c r="I335" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘排出69毫克的這種物質</t>
+        </is>
+      </c>
+      <c r="J335" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘形成69毫升的最後尿液</t>
+        </is>
+      </c>
+      <c r="K335" s="5" t="inlineStr">
+        <is>
+          <t>每毫升尿裡有69毫克的這種物質</t>
+        </is>
+      </c>
+      <c r="L335" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘相當清掉69毫升血漿裡的這種物質</t>
+        </is>
+      </c>
+      <c r="M335" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N335" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O335" s="5" t="inlineStr">
+        <is>
+          <t>因為清除率的毫升指相當的血漿體積，所以選「每分鐘相當清掉69毫升血漿裡的這種物質」。選「每分鐘形成69毫升的最後尿液」的同學，把血漿體積誤當成最後形成的尿量了。</t>
+        </is>
+      </c>
+      <c r="P335" s="5" t="inlineStr">
+        <is>
+          <t>先想想：69毫升是在描述相當的血漿，還是實際尿量？</t>
+        </is>
+      </c>
+      <c r="Q335" s="5" t="str"/>
+      <c r="R335" s="5" t="inlineStr">
+        <is>
+          <t>答案是「每分鐘相當清掉69毫升血漿裡的這種物質」，因為69毫升／分鐘指相當被清除的血漿體積。</t>
+        </is>
+      </c>
+      <c r="S335" s="5" t="inlineStr">
+        <is>
+          <t>清除率的毫升，是相當血漿</t>
+        </is>
+      </c>
+      <c r="T335" s="3" t="str">
+        <v>renal-clearance；physiology/CH09 p.26, physiology/CH09 p.27, physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15</v>
+      </c>
+      <c r="U335" s="3" t="str"/>
+      <c r="V335" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W335" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X335" s="3" t="str"/>
+    </row>
+    <row r="336" ht="110" customHeight="1">
+      <c r="A336" s="3" t="str"/>
+      <c r="B336" s="7" t="str">
+        <v>filtration-clearance-case-q03</v>
+      </c>
+      <c r="C336" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D336" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F336" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G336" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H336" s="5" t="inlineStr">
+        <is>
+          <t>菊糖和肌酸酐都能幫忙了解每分鐘濾出多少液體（腎絲球過濾率，GFR），它們在腎小管裡有什麼不同？</t>
+        </is>
+      </c>
+      <c r="I336" s="5" t="inlineStr">
+        <is>
+          <t>肌酸酐會被少量分泌，菊糖不會</t>
+        </is>
+      </c>
+      <c r="J336" s="5" t="inlineStr">
+        <is>
+          <t>菊糖會被大量收回，肌酸酐不會被濾出</t>
+        </is>
+      </c>
+      <c r="K336" s="5" t="inlineStr">
+        <is>
+          <t>兩種都靠分泌才進入尿液</t>
+        </is>
+      </c>
+      <c r="L336" s="5" t="inlineStr">
+        <is>
+          <t>兩種都不會被腎小管分泌</t>
+        </is>
+      </c>
+      <c r="M336" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N336" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O336" s="5" t="inlineStr">
+        <is>
+          <t>因為肌酸酐還會由血液少量送進管液，而菊糖不會，所以選「肌酸酐會被少量分泌，菊糖不會」。選「兩種都不會被腎小管分泌」的同學，把肌酸酐也當成不分泌的菊糖了。</t>
+        </is>
+      </c>
+      <c r="P336" s="5" t="inlineStr">
+        <is>
+          <t>先想想：被濾出之後，哪一種還會從血液多送一點進管液？</t>
+        </is>
+      </c>
+      <c r="Q336" s="5" t="str"/>
+      <c r="R336" s="5" t="inlineStr">
+        <is>
+          <t>答案是「肌酸酐會被少量分泌，菊糖不會」，因為肌酸酐有少量分泌，菊糖沒有。</t>
+        </is>
+      </c>
+      <c r="S336" s="5" t="inlineStr">
+        <is>
+          <t>菊糖不分泌，肌酸酐多一點</t>
+        </is>
+      </c>
+      <c r="T336" s="3" t="str">
+        <v>renal-clearance；physiology/CH09 p.26, physiology/CH09 p.27, physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15</v>
+      </c>
+      <c r="U336" s="3" t="str"/>
+      <c r="V336" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W336" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X336" s="3" t="str"/>
+    </row>
+    <row r="337" ht="110" customHeight="1">
+      <c r="A337" s="3" t="str"/>
+      <c r="B337" s="7" t="str">
+        <v>filtration-clearance-case-q04</v>
+      </c>
+      <c r="C337" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D337" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F337" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G337" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H337" s="5" t="inlineStr">
+        <is>
+          <t>用PAH（對胺馬尿酸）的清除率估算腎臟流量時，為什麼不能直接把結果當成整份腎血流量？</t>
+        </is>
+      </c>
+      <c r="I337" s="5" t="inlineStr">
+        <is>
+          <t>它估算的是膀胱能裝多少尿</t>
+        </is>
+      </c>
+      <c r="J337" s="5" t="inlineStr">
+        <is>
+          <t>它估的是血漿流量，換成整份血流還要算血漿比例</t>
+        </is>
+      </c>
+      <c r="K337" s="5" t="inlineStr">
+        <is>
+          <t>它不會被濾出，也不會被分泌</t>
+        </is>
+      </c>
+      <c r="L337" s="5" t="inlineStr">
+        <is>
+          <t>血漿流量和整份血流量數字相同</t>
+        </is>
+      </c>
+      <c r="M337" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N337" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O337" s="5" t="inlineStr">
+        <is>
+          <t>因為PAH清除率估的是不含血球的血漿流量，所以還要用血漿比例換算整份血流，選「它估的是血漿流量，換成整份血流還要算血漿比例」。選「血漿流量和整份血流量數字相同」的同學，忽略了整份血液還包含血球。</t>
+        </is>
+      </c>
+      <c r="P337" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一份血液除了血漿，還有沒有血球？</t>
+        </is>
+      </c>
+      <c r="Q337" s="5" t="str"/>
+      <c r="R337" s="5" t="inlineStr">
+        <is>
+          <t>答案是「它估的是血漿流量，換成整份血流還要算血漿比例」，因為PAH先估血漿流量，換血流還需血漿比例。</t>
+        </is>
+      </c>
+      <c r="S337" s="5" t="inlineStr">
+        <is>
+          <t>PAH先算血漿，再換整份血流</t>
+        </is>
+      </c>
+      <c r="T337" s="3" t="str">
+        <v>renal-clearance；physiology/CH09 p.26, physiology/CH09 p.27, physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15</v>
+      </c>
+      <c r="U337" s="3" t="str"/>
+      <c r="V337" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W337" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X337" s="3" t="str"/>
+    </row>
+    <row r="338" ht="110" customHeight="1">
+      <c r="A338" s="3" t="str"/>
+      <c r="B338" s="7" t="str">
+        <v>filtration-clearance-case-q05</v>
+      </c>
+      <c r="C338" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D338" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F338" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G338" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H338" s="5" t="inlineStr">
+        <is>
+          <t>剛進鮑氏囊的濾液和血漿裡，葡萄糖一樣濃，最可能是為什麼？</t>
+        </is>
+      </c>
+      <c r="I338" s="5" t="inlineStr">
+        <is>
+          <t>鮑氏囊把葡萄糖分泌進去</t>
+        </is>
+      </c>
+      <c r="J338" s="5" t="inlineStr">
+        <is>
+          <t>濾液裡的血球把葡萄糖放出來</t>
+        </is>
+      </c>
+      <c r="K338" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖能通過過濾膜</t>
+        </is>
+      </c>
+      <c r="L338" s="5" t="inlineStr">
+        <is>
+          <t>白蛋白把葡萄糖一起帶過去</t>
+        </is>
+      </c>
+      <c r="M338" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N338" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O338" s="5" t="inlineStr">
+        <is>
+          <t>因為葡萄糖這種小物質可以通過過濾膜，所以剛形成的濾液可和血漿一樣濃，選「葡萄糖能通過過濾膜」。選「鮑氏囊把葡萄糖分泌進去」的同學，把過濾過程誤說成鮑氏囊分泌葡萄糖。</t>
+        </is>
+      </c>
+      <c r="P338" s="5" t="inlineStr">
+        <is>
+          <t>先想想：葡萄糖是過濾過去，還是鮑氏囊另外製造的？</t>
+        </is>
+      </c>
+      <c r="Q338" s="5" t="str"/>
+      <c r="R338" s="5" t="inlineStr">
+        <is>
+          <t>答案是「葡萄糖能通過過濾膜」，因為葡萄糖能通過過濾膜，初始濾液可與血漿相近。</t>
+        </is>
+      </c>
+      <c r="S338" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖能過濾，起初兩邊相近</t>
+        </is>
+      </c>
+      <c r="T338" s="3" t="str">
+        <v>glomerular-filtration；physiology/CH09 p.11, physiology/CH09 p.4, physiology/CH09 p.12, anatomy/AB-05_15 p.5, anatomy/AB-05_15 p.6</v>
+      </c>
+      <c r="U338" s="3" t="str"/>
+      <c r="V338" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="W338" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/filtration-clearance-v1/index.html</v>
+      </c>
+      <c r="X338" s="3" t="str"/>
+    </row>
+    <row r="339" ht="110" customHeight="1">
+      <c r="A339" s="3" t="str"/>
+      <c r="B339" s="7" t="str">
+        <v>tubular-handling-foundation-q01</v>
+      </c>
+      <c r="C339" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G339" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H339" s="5" t="inlineStr">
+        <is>
+          <t>小管裡原本被濾出的物質，又回到血液，這個動作叫什麼？</t>
+        </is>
+      </c>
+      <c r="I339" s="5" t="inlineStr">
+        <is>
+          <t>再吸收</t>
+        </is>
+      </c>
+      <c r="J339" s="5" t="inlineStr">
+        <is>
+          <t>分泌</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球過濾</t>
+        </is>
+      </c>
+      <c r="L339" s="5" t="inlineStr">
+        <is>
+          <t>排泄到體外</t>
+        </is>
+      </c>
+      <c r="M339" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N339" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O339" s="5" t="inlineStr">
+        <is>
+          <t>因為再吸收就是把管液中的物質收回血液，所以選「再吸收」。選「分泌」的同學，所選的分泌是從血液送進管液，方向相反。</t>
+        </is>
+      </c>
+      <c r="P339" s="5" t="inlineStr">
+        <is>
+          <t>先想想：物質這次是在回到血液，還是離開血液？</t>
+        </is>
+      </c>
+      <c r="Q339" s="5" t="str"/>
+      <c r="R339" s="5" t="inlineStr">
+        <is>
+          <t>答案是「再吸收」，因為管液中的物質回血液叫再吸收。</t>
+        </is>
+      </c>
+      <c r="S339" s="5" t="inlineStr">
+        <is>
+          <t>再吸收回到血，分泌送進管液</t>
+        </is>
+      </c>
+      <c r="T339" s="3" t="str">
+        <v>renal-handling；physiology/CH09 p.10, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.17, physiology/CH09 p.27</v>
+      </c>
+      <c r="U339" s="3" t="str"/>
+      <c r="V339" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W339" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X339" s="3" t="str"/>
+    </row>
+    <row r="340" ht="110" customHeight="1">
+      <c r="A340" s="3" t="str"/>
+      <c r="B340" s="7" t="str">
+        <v>tubular-handling-foundation-q02</v>
+      </c>
+      <c r="C340" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D340" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F340" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G340" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H340" s="5" t="inlineStr">
+        <is>
+          <t>想算同一種物質最後隨尿排出多少，哪一個加減算式正確？</t>
+        </is>
+      </c>
+      <c r="I340" s="5" t="inlineStr">
+        <is>
+          <t>先濾出＋收回血液－額外送進管液</t>
+        </is>
+      </c>
+      <c r="J340" s="5" t="inlineStr">
+        <is>
+          <t>先濾出－收回血液＋額外送進管液</t>
+        </is>
+      </c>
+      <c r="K340" s="5" t="inlineStr">
+        <is>
+          <t>收回血液－先濾出＋額外送進管液</t>
+        </is>
+      </c>
+      <c r="L340" s="5" t="inlineStr">
+        <is>
+          <t>先濾出＋收回血液＋額外送進管液</t>
+        </is>
+      </c>
+      <c r="M340" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N340" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O340" s="5" t="inlineStr">
+        <is>
+          <t>因為收回血液的部分不會再隨尿排出，而分泌是另外加進管液，所以選「先濾出－收回血液＋額外送進管液」。選「先濾出＋收回血液－額外送進管液」的同學，把再吸收和分泌的加減號交換了。</t>
+        </is>
+      </c>
+      <c r="P340" s="5" t="inlineStr">
+        <is>
+          <t>先想想：拿回身體的要減掉，另送進尿的要加上嗎？</t>
+        </is>
+      </c>
+      <c r="Q340" s="5" t="str"/>
+      <c r="R340" s="5" t="inlineStr">
+        <is>
+          <t>答案是「先濾出－收回血液＋額外送進管液」，因為排泄量等於過濾量減再吸收量再加分泌量。</t>
+        </is>
+      </c>
+      <c r="S340" s="5" t="inlineStr">
+        <is>
+          <t>先濾出，減回收，加分泌</t>
+        </is>
+      </c>
+      <c r="T340" s="3" t="str">
+        <v>renal-handling；physiology/CH09 p.10, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.17, physiology/CH09 p.27</v>
+      </c>
+      <c r="U340" s="3" t="str"/>
+      <c r="V340" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W340" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X340" s="3" t="str"/>
+    </row>
+    <row r="341" ht="110" customHeight="1">
+      <c r="A341" s="3" t="str"/>
+      <c r="B341" s="7" t="str">
+        <v>tubular-handling-foundation-q03</v>
+      </c>
+      <c r="C341" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F341" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G341" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H341" s="5" t="inlineStr">
+        <is>
+          <t>在近曲小管，葡萄糖和水各用什麼方式回到血液？</t>
+        </is>
+      </c>
+      <c r="I341" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖跟著水移動，水搭鈉離子的共同運輸</t>
+        </is>
+      </c>
+      <c r="J341" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖從血液送進管液，水靠滲透（隔著能通水、卻不通物質的膜，水往小粒子較多側移，叫做滲透）回收</t>
+        </is>
+      </c>
+      <c r="K341" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖搭鈉離子的共同運輸，水靠滲透（隔著能通水、卻不通物質的膜，水往小粒子較多側移，叫做滲透）回收</t>
+        </is>
+      </c>
+      <c r="L341" s="5" t="inlineStr">
+        <is>
+          <t>葡萄糖和鈉離子反向移動，水靠滲透（隔著能通水、卻不通物質的膜，水往小粒子較多側移，叫做滲透）回收</t>
+        </is>
+      </c>
+      <c r="M341" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N341" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O341" s="5" t="inlineStr">
+        <is>
+          <t>因為近曲小管讓葡萄糖和鈉離子同方向回收，水則靠滲透（隔著能通水、卻不通物質的膜，水往小粒子較多側移，叫做滲透）移動，所以選「葡萄糖搭鈉離子的共同運輸，水靠滲透回收」。選「葡萄糖和鈉離子反向移動，水靠滲透回收」的同學，把葡萄糖與鈉的共同運輸，錯寫成一進一出的交換。</t>
+        </is>
+      </c>
+      <c r="P341" s="5" t="inlineStr">
+        <is>
+          <t>先想想：葡萄糖和鈉是一起走，還是一個進、一個出？</t>
+        </is>
+      </c>
+      <c r="Q341" s="5" t="str"/>
+      <c r="R341" s="5" t="inlineStr">
+        <is>
+          <t>答案是「葡萄糖搭鈉離子的共同運輸，水靠滲透（隔著能通水、卻不通物質的膜，水往小粒子較多側移，叫做滲透）回收」，因為葡萄糖與鈉共同運輸，水依滲透（隔著能通水、卻不通物質的膜，水往小粒子較多側移，叫做滲透）作用回收。</t>
+        </is>
+      </c>
+      <c r="S341" s="5" t="inlineStr">
+        <is>
+          <t>糖搭鈉回收，水靠滲透跟上</t>
+        </is>
+      </c>
+      <c r="T341" s="3" t="str">
+        <v>tubular-reabsorption；physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.16, physiology/CH09 p.27, anatomy/AB-05_15 p.6, physiology/CH09 p.17</v>
+      </c>
+      <c r="U341" s="3" t="str"/>
+      <c r="V341" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W341" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X341" s="3" t="str"/>
+    </row>
+    <row r="342" ht="110" customHeight="1">
+      <c r="A342" s="3" t="str"/>
+      <c r="B342" s="7" t="str">
+        <v>tubular-handling-foundation-q04</v>
+      </c>
+      <c r="C342" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F342" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G342" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H342" s="5" t="inlineStr">
+        <is>
+          <t>腎小管回收葡萄糖也有速度上限，「葡萄糖最大轉運量」指的是什麼？</t>
+        </is>
+      </c>
+      <c r="I342" s="5" t="inlineStr">
+        <is>
+          <t>尿裡葡萄糖有多濃的固定數字</t>
+        </is>
+      </c>
+      <c r="J342" s="5" t="inlineStr">
+        <is>
+          <t>腎臟每分鐘血流量的上限</t>
+        </is>
+      </c>
+      <c r="K342" s="5" t="inlineStr">
+        <is>
+          <t>膀胱一天能存多少尿的上限</t>
+        </is>
+      </c>
+      <c r="L342" s="5" t="inlineStr">
+        <is>
+          <t>每分鐘能搬運多少葡萄糖的上限</t>
+        </is>
+      </c>
+      <c r="M342" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N342" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O342" s="5" t="inlineStr">
+        <is>
+          <t>因為小管每分鐘能搬運的葡萄糖有上限，所以這個上限叫最大轉運量，選「每分鐘能搬運多少葡萄糖的上限」。選「尿裡葡萄糖有多濃的固定數字」的同學，說的是尿有多濃，和每分鐘能搬多少不同。</t>
+        </is>
+      </c>
+      <c r="P342" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這個上限是在算每分鐘搬多少，還是液體多濃？</t>
+        </is>
+      </c>
+      <c r="Q342" s="5" t="str"/>
+      <c r="R342" s="5" t="inlineStr">
+        <is>
+          <t>答案是「每分鐘能搬運多少葡萄糖的上限」，因為最大轉運量是每分鐘能搬運的葡萄糖量上限。</t>
+        </is>
+      </c>
+      <c r="S342" s="5" t="inlineStr">
+        <is>
+          <t>最大轉運量，看每分鐘搬多少</t>
+        </is>
+      </c>
+      <c r="T342" s="3" t="str">
+        <v>tubular-reabsorption；physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.16, physiology/CH09 p.27, anatomy/AB-05_15 p.6, physiology/CH09 p.17</v>
+      </c>
+      <c r="U342" s="3" t="str"/>
+      <c r="V342" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W342" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X342" s="3" t="str"/>
+    </row>
+    <row r="343" ht="110" customHeight="1">
+      <c r="A343" s="3" t="str"/>
+      <c r="B343" s="7" t="str">
+        <v>tubular-handling-foundation-q05</v>
+      </c>
+      <c r="C343" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F343" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G343" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H343" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮是幫忙調整鈉與鉀的激素，它在腎小管後段會怎麼做？</t>
+        </is>
+      </c>
+      <c r="I343" s="5" t="inlineStr">
+        <is>
+          <t>把鈉收回血液，把鉀送進管液</t>
+        </is>
+      </c>
+      <c r="J343" s="5" t="inlineStr">
+        <is>
+          <t>把鈉送進管液，把鉀收回血液</t>
+        </is>
+      </c>
+      <c r="K343" s="5" t="inlineStr">
+        <is>
+          <t>把鈉和鉀都送進管液</t>
+        </is>
+      </c>
+      <c r="L343" s="5" t="inlineStr">
+        <is>
+          <t>讓鈉和鉀都停止移動</t>
+        </is>
+      </c>
+      <c r="M343" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N343" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O343" s="5" t="inlineStr">
+        <is>
+          <t>因為醛固酮增加鈉再吸收並增加鉀分泌，所以選「把鈉收回血液，把鉀送進管液」。選「把鈉送進管液，把鉀收回血液」的同學，把留下鈉與排出鉀的方向寫反了。</t>
+        </is>
+      </c>
+      <c r="P343" s="5" t="inlineStr">
+        <is>
+          <t>先想想：醛固酮要把哪一種留下，哪一種送進尿？</t>
+        </is>
+      </c>
+      <c r="Q343" s="5" t="str"/>
+      <c r="R343" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把鈉收回血液，把鉀送進管液」，因為醛固酮促鈉再吸收、促鉀分泌。</t>
+        </is>
+      </c>
+      <c r="S343" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮，留鈉又排鉀</t>
+        </is>
+      </c>
+      <c r="T343" s="3" t="str">
+        <v>potassium-secretion；physiology/CH09 p.18, physiology/CH09 p.17, physiology/CH09 p.34, physiology/CH09 p.14</v>
+      </c>
+      <c r="U343" s="3" t="str"/>
+      <c r="V343" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W343" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X343" s="3" t="str"/>
+    </row>
+    <row r="344" ht="110" customHeight="1">
+      <c r="A344" s="3" t="str"/>
+      <c r="B344" s="7" t="str">
+        <v>tubular-handling-foundation-q06</v>
+      </c>
+      <c r="C344" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F344" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G344" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H344" s="5" t="inlineStr">
+        <is>
+          <t>看到尿裡某種物質比較濃，就能說腎小管把更多這種物質分泌進尿裡嗎？</t>
+        </is>
+      </c>
+      <c r="I344" s="5" t="inlineStr">
+        <is>
+          <t>能，尿有多濃就是分泌的速度</t>
+        </is>
+      </c>
+      <c r="J344" s="5" t="inlineStr">
+        <is>
+          <t>不能，還要看收回多少水、每分鐘排多少尿</t>
+        </is>
+      </c>
+      <c r="K344" s="5" t="inlineStr">
+        <is>
+          <t>能，尿有多濃就是腎絲球過濾率</t>
+        </is>
+      </c>
+      <c r="L344" s="5" t="inlineStr">
+        <is>
+          <t>不能，尿變濃表示收回血液的物質更多</t>
+        </is>
+      </c>
+      <c r="M344" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N344" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O344" s="5" t="inlineStr">
+        <is>
+          <t>因為回收較多水也會讓剩下的尿變濃，所以單看濃淡還不夠，選「不能，還要看收回多少水、每分鐘排多少尿」。選「不能，尿變濃表示收回血液的物質更多」的同學，把尿比較濃直接當成物質回收量增加，少看了水的改變。</t>
+        </is>
+      </c>
+      <c r="P344" s="5" t="inlineStr">
+        <is>
+          <t>先想想：尿變濃，可能只是剩下的水變少嗎？</t>
+        </is>
+      </c>
+      <c r="Q344" s="5" t="str"/>
+      <c r="R344" s="5" t="inlineStr">
+        <is>
+          <t>答案是「不能，還要看收回多少水、每分鐘排多少尿」，因為水回收與尿流量都會影響尿濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）。</t>
+        </is>
+      </c>
+      <c r="S344" s="5" t="inlineStr">
+        <is>
+          <t>尿濃不等於分泌多，還要看水</t>
+        </is>
+      </c>
+      <c r="T344" s="3" t="str">
+        <v>renal-handling；physiology/CH09 p.10, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.17, physiology/CH09 p.27
+tubular-reabsorption；physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.16, physiology/CH09 p.27, anatomy/AB-05_15 p.6, physiology/CH09 p.17</v>
+      </c>
+      <c r="U344" s="3" t="str"/>
+      <c r="V344" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W344" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X344" s="3" t="str"/>
+    </row>
+    <row r="345" ht="110" customHeight="1">
+      <c r="A345" s="3" t="str"/>
+      <c r="B345" s="7" t="str">
+        <v>tubular-handling-case-q01</v>
+      </c>
+      <c r="C345" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F345" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G345" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H345" s="5" t="inlineStr">
+        <is>
+          <t>某種物質從小管旁的血液移進小管裡的液體，這個動作叫什麼？</t>
+        </is>
+      </c>
+      <c r="I345" s="5" t="inlineStr">
+        <is>
+          <t>再吸收</t>
+        </is>
+      </c>
+      <c r="J345" s="5" t="inlineStr">
+        <is>
+          <t>從膀胱排尿</t>
+        </is>
+      </c>
+      <c r="K345" s="5" t="inlineStr">
+        <is>
+          <t>分泌</t>
+        </is>
+      </c>
+      <c r="L345" s="5" t="inlineStr">
+        <is>
+          <t>腎絲球過濾</t>
+        </is>
+      </c>
+      <c r="M345" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N345" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O345" s="5" t="inlineStr">
+        <is>
+          <t>因為從血液額外送進管液叫分泌，所以選「分泌」。選「再吸收」的同學，所選的再吸收是把管液裡的物質拿回血液，方向相反。</t>
+        </is>
+      </c>
+      <c r="P345" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這一次是從血往管液，還是從管液往血？</t>
+        </is>
+      </c>
+      <c r="Q345" s="5" t="str"/>
+      <c r="R345" s="5" t="inlineStr">
+        <is>
+          <t>答案是「分泌」，因為血液中的物質進入小管管液叫分泌。</t>
+        </is>
+      </c>
+      <c r="S345" s="5" t="inlineStr">
+        <is>
+          <t>血送管液叫分泌，管液回血叫回收</t>
+        </is>
+      </c>
+      <c r="T345" s="3" t="str">
+        <v>renal-handling；physiology/CH09 p.10, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.17, physiology/CH09 p.27</v>
+      </c>
+      <c r="U345" s="3" t="str"/>
+      <c r="V345" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W345" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X345" s="3" t="str"/>
+    </row>
+    <row r="346" ht="110" customHeight="1">
+      <c r="A346" s="3" t="str"/>
+      <c r="B346" s="7" t="str">
+        <v>tubular-handling-case-q02</v>
+      </c>
+      <c r="C346" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D346" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F346" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G346" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H346" s="5" t="inlineStr">
+        <is>
+          <t>同一種物質，先濾出和額外送進管液的量都不變，但收回血液的量變多，最後隨尿排出的量會怎麼變？</t>
+        </is>
+      </c>
+      <c r="I346" s="5" t="inlineStr">
+        <is>
+          <t>變多</t>
+        </is>
+      </c>
+      <c r="J346" s="5" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="K346" s="5" t="inlineStr">
+        <is>
+          <t>還不能知道，要先知道每分鐘尿量</t>
+        </is>
+      </c>
+      <c r="L346" s="5" t="inlineStr">
+        <is>
+          <t>變少</t>
+        </is>
+      </c>
+      <c r="M346" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N346" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O346" s="5" t="inlineStr">
+        <is>
+          <t>因為先濾出的量要扣掉收回血液的量，再加上分泌量，所以回收變多就排出變少，選「變少」。選「還不能知道，要先知道每分鐘尿量」的同學，把計算物質排出量和計算尿有多濃混在一起，本題已固定其餘收支量。</t>
+        </is>
+      </c>
+      <c r="P346" s="5" t="inlineStr">
+        <is>
+          <t>先想想：原本要排掉的物質，多拿一些回身體，還會排得更多嗎？</t>
+        </is>
+      </c>
+      <c r="Q346" s="5" t="str"/>
+      <c r="R346" s="5" t="inlineStr">
+        <is>
+          <t>答案是「變少」，因為過濾與分泌不變時，再吸收增加會使排泄量減少。</t>
+        </is>
+      </c>
+      <c r="S346" s="5" t="inlineStr">
+        <is>
+          <t>其他量不變，多收回就少排出</t>
+        </is>
+      </c>
+      <c r="T346" s="3" t="str">
+        <v>renal-handling；physiology/CH09 p.10, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.17, physiology/CH09 p.27</v>
+      </c>
+      <c r="U346" s="3" t="str"/>
+      <c r="V346" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W346" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X346" s="3" t="str"/>
+    </row>
+    <row r="347" ht="110" customHeight="1">
+      <c r="A347" s="3" t="str"/>
+      <c r="B347" s="7" t="str">
+        <v>tubular-handling-case-q03</v>
+      </c>
+      <c r="C347" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F347" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G347" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H347" s="5" t="inlineStr">
+        <is>
+          <t>兩份尿裡的同一種物質一樣濃，甲每分鐘排出的尿比較多，哪個說法正確？</t>
+        </is>
+      </c>
+      <c r="I347" s="5" t="inlineStr">
+        <is>
+          <t>甲每分鐘排掉的這種物質比較多</t>
+        </is>
+      </c>
+      <c r="J347" s="5" t="inlineStr">
+        <is>
+          <t>甲乙每分鐘排掉的這種物質一樣多</t>
+        </is>
+      </c>
+      <c r="K347" s="5" t="inlineStr">
+        <is>
+          <t>甲每分鐘排掉的這種物質比較少</t>
+        </is>
+      </c>
+      <c r="L347" s="5" t="inlineStr">
+        <is>
+          <t>可以知道甲的小管分泌增加了</t>
+        </is>
+      </c>
+      <c r="M347" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N347" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O347" s="5" t="inlineStr">
+        <is>
+          <t>因為每分鐘排出量是尿中濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）乘以每分鐘尿量，所以一樣濃而尿較多的甲，排出物質也較多，選「甲每分鐘排掉的這種物質比較多」。選「甲乙每分鐘排掉的這種物質一樣多」的同學，忽略了兩份尿每分鐘的量不同。</t>
+        </is>
+      </c>
+      <c r="P347" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一樣濃的兩杯水，倒出去比較多會帶走比較多物質嗎？</t>
+        </is>
+      </c>
+      <c r="Q347" s="5" t="str"/>
+      <c r="R347" s="5" t="inlineStr">
+        <is>
+          <t>答案是「甲每分鐘排掉的這種物質比較多」，因為濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）相同而尿流量較大，物質排泄量就較多。</t>
+        </is>
+      </c>
+      <c r="S347" s="5" t="inlineStr">
+        <is>
+          <t>一樣濃，尿越多，排出的越多</t>
+        </is>
+      </c>
+      <c r="T347" s="3" t="str">
+        <v>renal-handling；physiology/CH09 p.10, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.17, physiology/CH09 p.27
+tubular-reabsorption；physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.16, physiology/CH09 p.27, anatomy/AB-05_15 p.6, physiology/CH09 p.17</v>
+      </c>
+      <c r="U347" s="3" t="str"/>
+      <c r="V347" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W347" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X347" s="3" t="str"/>
+    </row>
+    <row r="348" ht="110" customHeight="1">
+      <c r="A348" s="3" t="str"/>
+      <c r="B348" s="7" t="str">
+        <v>tubular-handling-case-q04</v>
+      </c>
+      <c r="C348" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F348" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G348" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H348" s="5" t="inlineStr">
+        <is>
+          <t>正常情況下，送進腎小管的葡萄糖沒有超過回收能力，搬運功能也正常，葡萄糖會怎樣？</t>
+        </is>
+      </c>
+      <c r="I348" s="5" t="inlineStr">
+        <is>
+          <t>被額外分泌進尿，才排得出去</t>
+        </is>
+      </c>
+      <c r="J348" s="5" t="inlineStr">
+        <is>
+          <t>能被小管收回血液</t>
+        </is>
+      </c>
+      <c r="K348" s="5" t="inlineStr">
+        <is>
+          <t>因搬運位置已滿，而留在尿裡</t>
+        </is>
+      </c>
+      <c r="L348" s="5" t="inlineStr">
+        <is>
+          <t>靠分泌從管液回到血液</t>
+        </is>
+      </c>
+      <c r="M348" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N348" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O348" s="5" t="inlineStr">
+        <is>
+          <t>因為正常小管有能力把這些葡萄糖收回，所以選「能被小管收回血液」。選「因搬運位置已滿，而留在尿裡」的同學，要在送來的糖超過回收能力時才可能發生，和題目的條件不同。</t>
+        </is>
+      </c>
+      <c r="P348" s="5" t="inlineStr">
+        <is>
+          <t>先想想：送來的糖沒超過回收能力，還會不會收不完？</t>
+        </is>
+      </c>
+      <c r="Q348" s="5" t="str"/>
+      <c r="R348" s="5" t="inlineStr">
+        <is>
+          <t>答案是「能被小管收回血液」，因為未超過正常回收能力時，葡萄糖可再吸收回血。</t>
+        </is>
+      </c>
+      <c r="S348" s="5" t="inlineStr">
+        <is>
+          <t>糖沒超過能力，小管能收回</t>
+        </is>
+      </c>
+      <c r="T348" s="3" t="str">
+        <v>tubular-reabsorption；physiology/CH09 p.13, physiology/CH09 p.14, physiology/CH09 p.15, physiology/CH09 p.16, physiology/CH09 p.27, anatomy/AB-05_15 p.6, physiology/CH09 p.17</v>
+      </c>
+      <c r="U348" s="3" t="str"/>
+      <c r="V348" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W348" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X348" s="3" t="str"/>
+    </row>
+    <row r="349" ht="110" customHeight="1">
+      <c r="A349" s="3" t="str"/>
+      <c r="B349" s="7" t="str">
+        <v>tubular-handling-case-q05</v>
+      </c>
+      <c r="C349" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>腎小管再吸收分泌與排泄</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F349" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G349" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H349" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮增加時，腎小管後段的鈉和鉀會往哪裡走？</t>
+        </is>
+      </c>
+      <c r="I349" s="5" t="inlineStr">
+        <is>
+          <t>鈉從血進管液，鉀從管液回血</t>
+        </is>
+      </c>
+      <c r="J349" s="5" t="inlineStr">
+        <is>
+          <t>鈉和鉀都從血進管液</t>
+        </is>
+      </c>
+      <c r="K349" s="5" t="inlineStr">
+        <is>
+          <t>鈉從管液回血，鉀從血進管液</t>
+        </is>
+      </c>
+      <c r="L349" s="5" t="inlineStr">
+        <is>
+          <t>鈉和鉀都從管液回血</t>
+        </is>
+      </c>
+      <c r="M349" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N349" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O349" s="5" t="inlineStr">
+        <is>
+          <t>因為醛固酮促進留鈉和排鉀，所以鈉回血、鉀進管液，選「鈉從管液回血，鉀從血進管液」。選「鈉和鉀都從管液回血」的同學，把鉀也當成要一起留回血液了。</t>
+        </is>
+      </c>
+      <c r="P349" s="5" t="inlineStr">
+        <is>
+          <t>先想想：鈉要留住、鉀要排掉，各要往哪裡移動？</t>
+        </is>
+      </c>
+      <c r="Q349" s="5" t="str"/>
+      <c r="R349" s="5" t="inlineStr">
+        <is>
+          <t>答案是「鈉從管液回血，鉀從血進管液」，因為醛固酮讓鈉再吸收回血，鉀分泌入管液。</t>
+        </is>
+      </c>
+      <c r="S349" s="5" t="inlineStr">
+        <is>
+          <t>鈉回血，鉀進尿，方向別顛倒</t>
+        </is>
+      </c>
+      <c r="T349" s="3" t="str">
+        <v>potassium-secretion；physiology/CH09 p.18, physiology/CH09 p.17, physiology/CH09 p.34, physiology/CH09 p.14</v>
+      </c>
+      <c r="U349" s="3" t="str"/>
+      <c r="V349" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="W349" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/tubular-handling-v1/index.html</v>
+      </c>
+      <c r="X349" s="3" t="str"/>
+    </row>
+    <row r="350" ht="110" customHeight="1">
+      <c r="A350" s="3" t="str"/>
+      <c r="B350" s="7" t="str">
+        <v>urine-concentration-foundation-q01</v>
+      </c>
+      <c r="C350" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D350" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E350" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F350" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G350" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H350" s="5" t="inlineStr">
+        <is>
+          <t>想讓最後的尿變濃，腎髓質周圍和集尿管要怎麼配合？</t>
+        </is>
+      </c>
+      <c r="I350" s="5" t="inlineStr">
+        <is>
+          <t>周圍物質較多，集尿管也能讓水通過</t>
+        </is>
+      </c>
+      <c r="J350" s="5" t="inlineStr">
+        <is>
+          <t>周圍物質較多，集尿管不讓水通過</t>
+        </is>
+      </c>
+      <c r="K350" s="5" t="inlineStr">
+        <is>
+          <t>周圍物質較少，集尿管能讓水通過</t>
+        </is>
+      </c>
+      <c r="L350" s="5" t="inlineStr">
+        <is>
+          <t>周圍物質較多，上升枝能讓水通過</t>
+        </is>
+      </c>
+      <c r="M350" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N350" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O350" s="5" t="inlineStr">
+        <is>
+          <t>因為周圍物質較多能吸引水移出，而集尿管也要能通水，所以選「周圍物質較多，集尿管也能讓水通過」。選「周圍物質較多，集尿管不讓水通過」的同學，只有外面的濃淡差，水卻過不了管壁，仍收不回同樣多的水。</t>
+        </is>
+      </c>
+      <c r="P350" s="5" t="inlineStr">
+        <is>
+          <t>先想想：外面能吸引水，裡面的管壁還要開門嗎？</t>
+        </is>
+      </c>
+      <c r="Q350" s="5" t="str"/>
+      <c r="R350" s="5" t="inlineStr">
+        <is>
+          <t>答案是「周圍物質較多，集尿管也能讓水通過」，因為髓質濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）差和可通水的集尿管要一起配合。</t>
+        </is>
+      </c>
+      <c r="S350" s="5" t="inlineStr">
+        <is>
+          <t>外面吸水，管壁也得通水</t>
+        </is>
+      </c>
+      <c r="T350" s="3" t="str">
+        <v>urine-concentration；physiology/CH09 p.22, physiology/CH09 p.19, physiology/CH09 p.20, physiology/CH09 p.21, physiology/CH09 p.16</v>
+      </c>
+      <c r="U350" s="3" t="str"/>
+      <c r="V350" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W350" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X350" s="3" t="str"/>
+    </row>
+    <row r="351" ht="110" customHeight="1">
+      <c r="A351" s="3" t="str"/>
+      <c r="B351" s="7" t="str">
+        <v>urine-concentration-foundation-q02</v>
+      </c>
+      <c r="C351" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D351" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E351" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F351" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G351" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H351" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環像一段彎下去再上來的小管，它的下降枝主要怎麼處理水？</t>
+        </is>
+      </c>
+      <c r="I351" s="5" t="inlineStr">
+        <is>
+          <t>不讓水通過，主動把鹽送出去</t>
+        </is>
+      </c>
+      <c r="J351" s="5" t="inlineStr">
+        <is>
+          <t>讓水通過，水往管外物質較多處移出</t>
+        </is>
+      </c>
+      <c r="K351" s="5" t="inlineStr">
+        <is>
+          <t>讓水通過，水往管內移入</t>
+        </is>
+      </c>
+      <c r="L351" s="5" t="inlineStr">
+        <is>
+          <t>讓水通過，水移出後管內變淡</t>
+        </is>
+      </c>
+      <c r="M351" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N351" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O351" s="5" t="inlineStr">
+        <is>
+          <t>因為下降枝能通水，水移出後剩下的管液較濃，所以選「讓水通過，水往管外物質較多處移出」。選「讓水通過，水移出後管內變淡」的同學，把水變少後的結果寫成變淡，方向相反。</t>
+        </is>
+      </c>
+      <c r="P351" s="5" t="inlineStr">
+        <is>
+          <t>先想想：同樣的物質留下，水變少後會更濃還是更淡？</t>
+        </is>
+      </c>
+      <c r="Q351" s="5" t="str"/>
+      <c r="R351" s="5" t="inlineStr">
+        <is>
+          <t>答案是「讓水通過，水往管外物質較多處移出」，因為下降枝能通水，水可沿濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）差移出。</t>
+        </is>
+      </c>
+      <c r="S351" s="5" t="inlineStr">
+        <is>
+          <t>下降枝讓水走，管內變濃</t>
+        </is>
+      </c>
+      <c r="T351" s="3" t="str">
+        <v>countercurrent-mechanism；physiology/CH09 p.20, physiology/CH09 p.19, physiology/CH09 p.21, physiology/CH09 p.22, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U351" s="3" t="str"/>
+      <c r="V351" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W351" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X351" s="3" t="str"/>
+    </row>
+    <row r="352" ht="110" customHeight="1">
+      <c r="A352" s="3" t="str"/>
+      <c r="B352" s="7" t="str">
+        <v>urine-concentration-foundation-q03</v>
+      </c>
+      <c r="C352" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D352" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E352" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F352" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G352" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H352" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環的上升枝把氯化鈉（NaCl，一種鹽）收回血液時，水能一起穿過它的管壁嗎？</t>
+        </is>
+      </c>
+      <c r="I352" s="5" t="inlineStr">
+        <is>
+          <t>水和鹽一起通過，比例相同</t>
+        </is>
+      </c>
+      <c r="J352" s="5" t="inlineStr">
+        <is>
+          <t>水能通過，鹽不能回收</t>
+        </is>
+      </c>
+      <c r="K352" s="5" t="inlineStr">
+        <is>
+          <t>水不能穿過管壁</t>
+        </is>
+      </c>
+      <c r="L352" s="5" t="inlineStr">
+        <is>
+          <t>水能不能通過，要看膀胱壓力</t>
+        </is>
+      </c>
+      <c r="M352" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N352" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O352" s="5" t="inlineStr">
+        <is>
+          <t>因為上升枝回收鹽卻不透水，所以選「水不能穿過管壁」。選「水和鹽一起通過，比例相同」的同學，把上升枝當成鹽和水會一起走，和這段管壁的特性不同。</t>
+        </is>
+      </c>
+      <c r="P352" s="5" t="inlineStr">
+        <is>
+          <t>先想想：鹽能走，就表示水也能一起走嗎？</t>
+        </is>
+      </c>
+      <c r="Q352" s="5" t="str"/>
+      <c r="R352" s="5" t="inlineStr">
+        <is>
+          <t>答案是「水不能穿過管壁」，因為上升枝回收鹽，但不透水。</t>
+        </is>
+      </c>
+      <c r="S352" s="5" t="inlineStr">
+        <is>
+          <t>上升枝送鹽，水不跟著走</t>
+        </is>
+      </c>
+      <c r="T352" s="3" t="str">
+        <v>countercurrent-mechanism；physiology/CH09 p.20, physiology/CH09 p.19, physiology/CH09 p.21, physiology/CH09 p.22, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U352" s="3" t="str"/>
+      <c r="V352" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W352" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X352" s="3" t="str"/>
+    </row>
+    <row r="353" ht="110" customHeight="1">
+      <c r="A353" s="3" t="str"/>
+      <c r="B353" s="7" t="str">
+        <v>urine-concentration-foundation-q04</v>
+      </c>
+      <c r="C353" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D353" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E353" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F353" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G353" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H353" s="5" t="inlineStr">
+        <is>
+          <t>腎髓質周圍有濃淡差，稱為滲透梯度，旁邊的直血管主要怎麼保住這個差別？</t>
+        </is>
+      </c>
+      <c r="I353" s="5" t="inlineStr">
+        <is>
+          <t>做逆流增強，建立髓質的濃淡差</t>
+        </is>
+      </c>
+      <c r="J353" s="5" t="inlineStr">
+        <is>
+          <t>加快血流，把髓質的鹽帶走</t>
+        </is>
+      </c>
+      <c r="K353" s="5" t="inlineStr">
+        <is>
+          <t>替集尿管開水通道，回收水</t>
+        </is>
+      </c>
+      <c r="L353" s="5" t="inlineStr">
+        <is>
+          <t>做逆流交換，減少髓質物質被帶走</t>
+        </is>
+      </c>
+      <c r="M353" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N353" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O353" s="5" t="inlineStr">
+        <is>
+          <t>因為直血管靠緩慢的逆流交換減少物質流失，所以選「做逆流交換，減少髓質物質被帶走」。選「做逆流增強，建立髓質的濃淡差」的同學，所選的逆流增強主要是亨利氏環建立濃淡差的工作。</t>
+        </is>
+      </c>
+      <c r="P353" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪一個先建立濃淡差，哪一個避免它被血流帶走？</t>
+        </is>
+      </c>
+      <c r="Q353" s="5" t="str"/>
+      <c r="R353" s="5" t="inlineStr">
+        <is>
+          <t>答案是「做逆流交換，減少髓質物質被帶走」，因為直血管以逆流交換減少髓質溶質（溶在水裡的物質，叫做溶質）流失。</t>
+        </is>
+      </c>
+      <c r="S353" s="5" t="inlineStr">
+        <is>
+          <t>亨利建差，直血管保住差</t>
+        </is>
+      </c>
+      <c r="T353" s="3" t="str">
+        <v>countercurrent-mechanism；physiology/CH09 p.20, physiology/CH09 p.19, physiology/CH09 p.21, physiology/CH09 p.22, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U353" s="3" t="str"/>
+      <c r="V353" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W353" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X353" s="3" t="str"/>
+    </row>
+    <row r="354" ht="110" customHeight="1">
+      <c r="A354" s="3" t="str"/>
+      <c r="B354" s="7" t="str">
+        <v>urine-concentration-foundation-q05</v>
+      </c>
+      <c r="C354" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D354" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E354" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F354" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G354" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H354" s="5" t="inlineStr">
+        <is>
+          <t>受器像接收激素訊號的接收站。抗利尿激素（ADH，叫腎臟把水留下來的訊號）會用哪個受器，幫集尿管多開水通道？</t>
+        </is>
+      </c>
+      <c r="I354" s="5" t="inlineStr">
+        <is>
+          <t>用V2受器，增加水通道，讓水更容易通過</t>
+        </is>
+      </c>
+      <c r="J354" s="5" t="inlineStr">
+        <is>
+          <t>用V2受器，減少水通道，讓水更難通過</t>
+        </is>
+      </c>
+      <c r="K354" s="5" t="inlineStr">
+        <is>
+          <t>用V2受器，增加鈉通道，讓鈉更容易通過</t>
+        </is>
+      </c>
+      <c r="L354" s="5" t="inlineStr">
+        <is>
+          <t>用醛固酮受器，增加水通道，讓水更容易通過</t>
+        </is>
+      </c>
+      <c r="M354" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N354" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O354" s="5" t="inlineStr">
+        <is>
+          <t>因為抗利尿激素會增加集尿管的水通道，讓水更容易回到血液，所以它幫身體留下水。選「用V2受器（受器像接收激素訊號的接收站），增加鈉通道，讓鈉更容易通過」的同學，把增加水通道誤當成增加鈉通道。</t>
+        </is>
+      </c>
+      <c r="P354" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這條訊號增加的是讓水通過，還是讓鈉通過的通道？</t>
+        </is>
+      </c>
+      <c r="Q354" s="5" t="str"/>
+      <c r="R354" s="5" t="inlineStr">
+        <is>
+          <t>答案是「用V2受器，增加水通道，讓水更容易通過」，因為ADH透過接收訊號的V2受器增加水通道，讓水更容易通過。</t>
+        </is>
+      </c>
+      <c r="S354" s="5" t="inlineStr">
+        <is>
+          <t>ADH接V2，水通道變多</t>
+        </is>
+      </c>
+      <c r="T354" s="3" t="str">
+        <v>adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U354" s="3" t="str"/>
+      <c r="V354" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W354" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X354" s="3" t="str"/>
+    </row>
+    <row r="355" ht="110" customHeight="1">
+      <c r="A355" s="3" t="str"/>
+      <c r="B355" s="7" t="str">
+        <v>urine-concentration-foundation-q06</v>
+      </c>
+      <c r="C355" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D355" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E355" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F355" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G355" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H355" s="5" t="inlineStr">
+        <is>
+          <t>抗利尿激素（ADH，幫腎臟留水的訊號）比較多，其他條件都相同時，尿會怎麼變？</t>
+        </is>
+      </c>
+      <c r="I355" s="5" t="inlineStr">
+        <is>
+          <t>尿變多，也變淡</t>
+        </is>
+      </c>
+      <c r="J355" s="5" t="inlineStr">
+        <is>
+          <t>尿變少，也變濃</t>
+        </is>
+      </c>
+      <c r="K355" s="5" t="inlineStr">
+        <is>
+          <t>尿變少，也變淡</t>
+        </is>
+      </c>
+      <c r="L355" s="5" t="inlineStr">
+        <is>
+          <t>尿變多，也變濃</t>
+        </is>
+      </c>
+      <c r="M355" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N355" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O355" s="5" t="inlineStr">
+        <is>
+          <t>因為ADH讓更多水回血液，留在尿裡的水較少，所以尿少又濃，選「尿變少，也變濃」。選「尿變少，也變淡」的同學，雖想到尿量少，卻把濃淡方向寫反了。</t>
+        </is>
+      </c>
+      <c r="P355" s="5" t="inlineStr">
+        <is>
+          <t>先想想：水被收回去，留在尿裡的水會更多還是更少？</t>
+        </is>
+      </c>
+      <c r="Q355" s="5" t="str"/>
+      <c r="R355" s="5" t="inlineStr">
+        <is>
+          <t>答案是「尿變少，也變濃」，因為ADH較多時水回收增加，尿少而濃。</t>
+        </is>
+      </c>
+      <c r="S355" s="5" t="inlineStr">
+        <is>
+          <t>ADH多，水留住，尿少又濃</t>
+        </is>
+      </c>
+      <c r="T355" s="3" t="str">
+        <v>urine-concentration；physiology/CH09 p.22, physiology/CH09 p.19, physiology/CH09 p.20, physiology/CH09 p.21, physiology/CH09 p.16
+adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U355" s="3" t="str"/>
+      <c r="V355" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W355" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X355" s="3" t="str"/>
+    </row>
+    <row r="356" ht="110" customHeight="1">
+      <c r="A356" s="3" t="str"/>
+      <c r="B356" s="7" t="str">
+        <v>urine-concentration-case-q01</v>
+      </c>
+      <c r="C356" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D356" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E356" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F356" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G356" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H356" s="5" t="inlineStr">
+        <is>
+          <t>某段小管會把氯化鈉（NaCl，一種鹽）收回，水卻穿不過管壁，最像哪一段？</t>
+        </is>
+      </c>
+      <c r="I356" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環下降枝</t>
+        </is>
+      </c>
+      <c r="J356" s="5" t="inlineStr">
+        <is>
+          <t>尿道</t>
+        </is>
+      </c>
+      <c r="K356" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環上升枝</t>
+        </is>
+      </c>
+      <c r="L356" s="5" t="inlineStr">
+        <is>
+          <t>膀胱</t>
+        </is>
+      </c>
+      <c r="M356" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N356" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O356" s="5" t="inlineStr">
+        <is>
+          <t>因為亨利氏環上升枝回收鹽又不透水，所以選「亨利氏環上升枝」。選「亨利氏環下降枝」的同學，所選的下降枝能讓水通過，性質不同。</t>
+        </is>
+      </c>
+      <c r="P356" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪一邊讓水走，哪一邊把鹽收回但水過不去？</t>
+        </is>
+      </c>
+      <c r="Q356" s="5" t="str"/>
+      <c r="R356" s="5" t="inlineStr">
+        <is>
+          <t>答案是「亨利氏環上升枝」，因為回收鹽而不透水的是亨利氏環上升枝。</t>
+        </is>
+      </c>
+      <c r="S356" s="5" t="inlineStr">
+        <is>
+          <t>收鹽不透水，找上升枝</t>
+        </is>
+      </c>
+      <c r="T356" s="3" t="str">
+        <v>countercurrent-mechanism；physiology/CH09 p.20, physiology/CH09 p.19, physiology/CH09 p.21, physiology/CH09 p.22, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U356" s="3" t="str"/>
+      <c r="V356" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W356" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X356" s="3" t="str"/>
+    </row>
+    <row r="357" ht="110" customHeight="1">
+      <c r="A357" s="3" t="str"/>
+      <c r="B357" s="7" t="str">
+        <v>urine-concentration-case-q02</v>
+      </c>
+      <c r="C357" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D357" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E357" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F357" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G357" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H357" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環是處理管液的小管，直血管是運血的血管，它們在逆流機制中各做什麼？</t>
+        </is>
+      </c>
+      <c r="I357" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環做逆流交換，直血管做逆流增強</t>
+        </is>
+      </c>
+      <c r="J357" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環做逆流增強，直血管也做逆流增強</t>
+        </is>
+      </c>
+      <c r="K357" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環做逆流交換，直血管也做逆流交換</t>
+        </is>
+      </c>
+      <c r="L357" s="5" t="inlineStr">
+        <is>
+          <t>亨利氏環做逆流增強，直血管做逆流交換</t>
+        </is>
+      </c>
+      <c r="M357" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N357" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O357" s="5" t="inlineStr">
+        <is>
+          <t>因為亨利氏環先建立髓質濃淡差，直血管再幫忙保住，所以選「亨利氏環做逆流增強，直血管做逆流交換」。選「亨利氏環做逆流交換，直血管做逆流增強」的同學，把兩個構造的工作名稱交換了。</t>
+        </is>
+      </c>
+      <c r="P357" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一個負責建立，一個負責保住，名字怎麼配？</t>
+        </is>
+      </c>
+      <c r="Q357" s="5" t="str"/>
+      <c r="R357" s="5" t="inlineStr">
+        <is>
+          <t>答案是「亨利氏環做逆流增強，直血管做逆流交換」，因為亨利氏環是逆流增強，直血管是逆流交換。</t>
+        </is>
+      </c>
+      <c r="S357" s="5" t="inlineStr">
+        <is>
+          <t>亨利增強，直血管交換</t>
+        </is>
+      </c>
+      <c r="T357" s="3" t="str">
+        <v>countercurrent-mechanism；physiology/CH09 p.20, physiology/CH09 p.19, physiology/CH09 p.21, physiology/CH09 p.22, anatomy/AB-05_15 p.8</v>
+      </c>
+      <c r="U357" s="3" t="str"/>
+      <c r="V357" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W357" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X357" s="3" t="str"/>
+    </row>
+    <row r="358" ht="110" customHeight="1">
+      <c r="A358" s="3" t="str"/>
+      <c r="B358" s="7" t="str">
+        <v>urine-concentration-case-q03</v>
+      </c>
+      <c r="C358" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D358" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E358" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F358" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G358" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H358" s="5" t="inlineStr">
+        <is>
+          <t>集尿管的水通道變多，水也更容易通過，最直接是哪個訊號在作用？</t>
+        </is>
+      </c>
+      <c r="I358" s="5" t="inlineStr">
+        <is>
+          <t>抗利尿激素ADH，透過V2受器（受器像接收激素訊號的接收站）</t>
+        </is>
+      </c>
+      <c r="J358" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮，直接增加水通道</t>
+        </is>
+      </c>
+      <c r="K358" s="5" t="inlineStr">
+        <is>
+          <t>抗利尿激素ADH，透過V2減少水通道</t>
+        </is>
+      </c>
+      <c r="L358" s="5" t="inlineStr">
+        <is>
+          <t>腎素，直接增加水通道</t>
+        </is>
+      </c>
+      <c r="M358" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N358" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O358" s="5" t="inlineStr">
+        <is>
+          <t>因為抗利尿激素ADH會透過V2受器（受器像接收激素訊號的接收站）增加水通道，所以選「抗利尿激素ADH，透過V2受器」。選「醛固酮，直接增加水通道」的同學，所選的醛固酮主要促進鈉回收，並不是這條直接增加水通道的訊號。</t>
+        </is>
+      </c>
+      <c r="P358" s="5" t="inlineStr">
+        <is>
+          <t>先想想：直接增加水通道，和先留住鈉，是同一個工作嗎？</t>
+        </is>
+      </c>
+      <c r="Q358" s="5" t="str"/>
+      <c r="R358" s="5" t="inlineStr">
+        <is>
+          <t>答案是「抗利尿激素ADH，透過V2受器（受器像接收激素訊號的接收站）」，因為ADH經V2受器（受器像接收激素訊號的接收站）直接增加集尿管水通透性（水穿過管壁有多容易，叫做水通透性）。</t>
+        </is>
+      </c>
+      <c r="S358" s="5" t="inlineStr">
+        <is>
+          <t>水通道增加，找ADH接V2</t>
+        </is>
+      </c>
+      <c r="T358" s="3" t="str">
+        <v>adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U358" s="3" t="str"/>
+      <c r="V358" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W358" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X358" s="3" t="str"/>
+    </row>
+    <row r="359" ht="110" customHeight="1">
+      <c r="A359" s="3" t="str"/>
+      <c r="B359" s="7" t="str">
+        <v>urine-concentration-case-q04</v>
+      </c>
+      <c r="C359" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D359" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E359" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F359" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G359" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H359" s="5" t="inlineStr">
+        <is>
+          <t>髓質周圍已經有濃淡差，能吸引水移出，但集尿管不太能通水，還能得到同樣濃的尿嗎？</t>
+        </is>
+      </c>
+      <c r="I359" s="5" t="inlineStr">
+        <is>
+          <t>能，集尿管外的濃淡差可以代替水通道</t>
+        </is>
+      </c>
+      <c r="J359" s="5" t="inlineStr">
+        <is>
+          <t>不能，集尿管也要能讓水通過</t>
+        </is>
+      </c>
+      <c r="K359" s="5" t="inlineStr">
+        <is>
+          <t>能，只要尿在膀胱裡存一樣久</t>
+        </is>
+      </c>
+      <c r="L359" s="5" t="inlineStr">
+        <is>
+          <t>不能，因為上升枝也要讓水通過</t>
+        </is>
+      </c>
+      <c r="M359" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N359" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O359" s="5" t="inlineStr">
+        <is>
+          <t>因為水還得穿過集尿管的管壁才能回血液，所以選「不能，集尿管也要能讓水通過」。選「能，集尿管外的濃淡差可以代替水通道」的同學，把外面的吸水條件當成已經替管壁開好了門。</t>
+        </is>
+      </c>
+      <c r="P359" s="5" t="inlineStr">
+        <is>
+          <t>先想想：門外能吸引水，門卻過不去，水能出去嗎？</t>
+        </is>
+      </c>
+      <c r="Q359" s="5" t="str"/>
+      <c r="R359" s="5" t="inlineStr">
+        <is>
+          <t>答案是「不能，集尿管也要能讓水通過」，因為集尿管水通透性（水穿過管壁有多容易，叫做水通透性）是濃縮尿液的必要條件。</t>
+        </is>
+      </c>
+      <c r="S359" s="5" t="inlineStr">
+        <is>
+          <t>濃淡差有了，水門也要開</t>
+        </is>
+      </c>
+      <c r="T359" s="3" t="str">
+        <v>urine-concentration；physiology/CH09 p.22, physiology/CH09 p.19, physiology/CH09 p.20, physiology/CH09 p.21, physiology/CH09 p.16</v>
+      </c>
+      <c r="U359" s="3" t="str"/>
+      <c r="V359" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W359" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X359" s="3" t="str"/>
+    </row>
+    <row r="360" ht="110" customHeight="1">
+      <c r="A360" s="3" t="str"/>
+      <c r="B360" s="7" t="str">
+        <v>urine-concentration-case-q05</v>
+      </c>
+      <c r="C360" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D360" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F360" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G360" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H360" s="5" t="inlineStr">
+        <is>
+          <t>抗利尿激素（ADH）是叫腎臟把水留下來的訊號，如果ADH變少，其他條件都一樣，水和尿會怎麼變？</t>
+        </is>
+      </c>
+      <c r="I360" s="5" t="inlineStr">
+        <is>
+          <t>留下的水變多，尿變少、變濃</t>
+        </is>
+      </c>
+      <c r="J360" s="5" t="inlineStr">
+        <is>
+          <t>留下的水不變，尿量與濃淡不變</t>
+        </is>
+      </c>
+      <c r="K360" s="5" t="inlineStr">
+        <is>
+          <t>留下的水變少，尿變多、變淡</t>
+        </is>
+      </c>
+      <c r="L360" s="5" t="inlineStr">
+        <is>
+          <t>留下的水變少，尿變少、變濃</t>
+        </is>
+      </c>
+      <c r="M360" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N360" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O360" s="5" t="inlineStr">
+        <is>
+          <t>因為ADH變少，集尿管水通道也變少，所以水留不住，尿就多又淡，選「留下的水變少，尿變多、變淡」。選「留下的水變少，尿變少、變濃」的同學，只想到水留不住，卻忘了這些水會跟著尿排掉。</t>
+        </is>
+      </c>
+      <c r="P360" s="5" t="inlineStr">
+        <is>
+          <t>先想想：水沒留回血液，是不是就跟著尿排出去了？</t>
+        </is>
+      </c>
+      <c r="Q360" s="5" t="str"/>
+      <c r="R360" s="5" t="inlineStr">
+        <is>
+          <t>答案是「留下的水變少，尿變多、變淡」，因為ADH少使水回收減少，尿量增加且較淡。</t>
+        </is>
+      </c>
+      <c r="S360" s="5" t="inlineStr">
+        <is>
+          <t>ADH少，水留不住，尿多又淡</t>
+        </is>
+      </c>
+      <c r="T360" s="3" t="str">
+        <v>urine-concentration；physiology/CH09 p.22, physiology/CH09 p.19, physiology/CH09 p.20, physiology/CH09 p.21, physiology/CH09 p.16
+adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U360" s="3" t="str"/>
+      <c r="V360" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="W360" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urine-concentration-v1/index.html</v>
+      </c>
+      <c r="X360" s="3" t="str"/>
+    </row>
+    <row r="361" ht="110" customHeight="1">
+      <c r="A361" s="3" t="str"/>
+      <c r="B361" s="7" t="str">
+        <v>urinary-route-micturition-foundation-q01</v>
+      </c>
+      <c r="C361" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D361" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E361" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F361" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G361" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H361" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管怎麼把尿送到膀胱，又怎麼幫忙防止尿倒流？</t>
+        </is>
+      </c>
+      <c r="I361" s="5" t="inlineStr">
+        <is>
+          <t>管壁一段段收縮送尿，斜穿膀胱壁幫忙防倒流</t>
+        </is>
+      </c>
+      <c r="J361" s="5" t="inlineStr">
+        <is>
+          <t>靠重力送尿，末端另有一片獨立瓣膜</t>
+        </is>
+      </c>
+      <c r="K361" s="5" t="inlineStr">
+        <is>
+          <t>先在膀胱製尿，再沿輸尿管送回腎盂</t>
+        </is>
+      </c>
+      <c r="L361" s="5" t="inlineStr">
+        <is>
+          <t>靠尿道收縮，代替輸尿管把尿送到膀胱</t>
+        </is>
+      </c>
+      <c r="M361" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N361" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O361" s="5" t="inlineStr">
+        <is>
+          <t>因為輸尿管靠蠕動送尿，斜穿膀胱壁的那段受壓時有助防倒流，所以選「管壁一段段收縮送尿，斜穿膀胱壁幫忙防倒流」。選「靠重力送尿，末端另有一片獨立瓣膜」的同學，把這種作用想成末端另有一片獨立的解剖瓣膜。</t>
+        </is>
+      </c>
+      <c r="P361" s="5" t="inlineStr">
+        <is>
+          <t>先想想：管壁自己會推尿，還是只能等尿往下掉？</t>
+        </is>
+      </c>
+      <c r="Q361" s="5" t="str"/>
+      <c r="R361" s="5" t="inlineStr">
+        <is>
+          <t>答案是「管壁一段段收縮送尿，斜穿膀胱壁幫忙防倒流」，因為輸尿管靠蠕動送尿，斜行穿壁有助防逆流。</t>
+        </is>
+      </c>
+      <c r="S361" s="5" t="inlineStr">
+        <is>
+          <t>管壁蠕動送尿，斜穿防倒流</t>
+        </is>
+      </c>
+      <c r="T361" s="3" t="str">
+        <v>ureter-constrictions；anatomy/AB-05_15 p.10, anatomy/AB-05_15 p.11</v>
+      </c>
+      <c r="U361" s="3" t="str"/>
+      <c r="V361" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W361" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X361" s="3" t="str"/>
+    </row>
+    <row r="362" ht="110" customHeight="1">
+      <c r="A362" s="3" t="str"/>
+      <c r="B362" s="7" t="str">
+        <v>urinary-route-micturition-foundation-q02</v>
+      </c>
+      <c r="C362" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D362" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E362" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F362" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G362" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H362" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管從腎盂通到膀胱，沿路有三個較窄的地方，中間那個在哪裡？</t>
+        </is>
+      </c>
+      <c r="I362" s="5" t="inlineStr">
+        <is>
+          <t>腎門和腎筋膜交界</t>
+        </is>
+      </c>
+      <c r="J362" s="5" t="inlineStr">
+        <is>
+          <t>與髂外動脈及靜脈交叉的地方</t>
+        </is>
+      </c>
+      <c r="K362" s="5" t="inlineStr">
+        <is>
+          <t>尿道通到體外的開口</t>
+        </is>
+      </c>
+      <c r="L362" s="5" t="inlineStr">
+        <is>
+          <t>膀胱出口的尿道內口</t>
+        </is>
+      </c>
+      <c r="M362" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N362" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O362" s="5" t="inlineStr">
+        <is>
+          <t>因為輸尿管中段在跨過髂外動脈及靜脈時較窄，所以選「與髂外動脈及靜脈交叉的地方」。選「膀胱出口的尿道內口」的同學，所選的尿道內口在膀胱出口，不是輸尿管中段。</t>
+        </is>
+      </c>
+      <c r="P362" s="5" t="inlineStr">
+        <is>
+          <t>先想想：尿還在輸尿管中途，還是已到了膀胱出口？</t>
+        </is>
+      </c>
+      <c r="Q362" s="5" t="str"/>
+      <c r="R362" s="5" t="inlineStr">
+        <is>
+          <t>答案是「與髂外動脈及靜脈交叉的地方」，因為中段狹窄位於髂外動脈及靜脈交叉處。</t>
+        </is>
+      </c>
+      <c r="S362" s="5" t="inlineStr">
+        <is>
+          <t>中段狹窄，記髂外血管交叉</t>
+        </is>
+      </c>
+      <c r="T362" s="3" t="str">
+        <v>ureter-constrictions；anatomy/AB-05_15 p.10, anatomy/AB-05_15 p.11, physiology/CH09 p.3, physiology/CH09 p.13</v>
+      </c>
+      <c r="U362" s="3" t="str"/>
+      <c r="V362" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W362" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X362" s="3" t="str"/>
+    </row>
+    <row r="363" ht="110" customHeight="1">
+      <c r="A363" s="3" t="str"/>
+      <c r="B363" s="7" t="str">
+        <v>urinary-route-micturition-foundation-q03</v>
+      </c>
+      <c r="C363" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D363" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F363" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G363" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H363" s="5" t="inlineStr">
+        <is>
+          <t>膀胱三角是膀胱內的一塊三角區域，它的三個角由哪三處界定？</t>
+        </is>
+      </c>
+      <c r="I363" s="5" t="inlineStr">
+        <is>
+          <t>左右輸尿管口和尿道外口</t>
+        </is>
+      </c>
+      <c r="J363" s="5" t="inlineStr">
+        <is>
+          <t>左右腎盂開口和尿道內口</t>
+        </is>
+      </c>
+      <c r="K363" s="5" t="inlineStr">
+        <is>
+          <t>左右輸尿管口和尿道內口</t>
+        </is>
+      </c>
+      <c r="L363" s="5" t="inlineStr">
+        <is>
+          <t>左右輸尿管口和膀胱頂</t>
+        </is>
+      </c>
+      <c r="M363" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N363" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O363" s="5" t="inlineStr">
+        <is>
+          <t>因為兩側輸尿管口讓尿進入，尿道內口讓尿流出，三處圍成膀胱三角，所以選「左右輸尿管口和尿道內口」。選「左右輸尿管口和尿道外口」的同學，把膀胱裡的尿道內口換成身體外的尿道外口。</t>
+        </is>
+      </c>
+      <c r="P363" s="5" t="inlineStr">
+        <is>
+          <t>先想想：三角要在膀胱裡找，還是到身體外面找？</t>
+        </is>
+      </c>
+      <c r="Q363" s="5" t="str"/>
+      <c r="R363" s="5" t="inlineStr">
+        <is>
+          <t>答案是「左右輸尿管口和尿道內口」，因為膀胱三角由兩輸尿管口與一尿道內口界定。</t>
+        </is>
+      </c>
+      <c r="S363" s="5" t="inlineStr">
+        <is>
+          <t>膀胱三角，兩進一出</t>
+        </is>
+      </c>
+      <c r="T363" s="3" t="str">
+        <v>urinary-bladder；anatomy/AB-05_15 p.11, anatomy/AB-05_15 p.12, physiology/CH09 p.24, physiology/CH09 p.25</v>
+      </c>
+      <c r="U363" s="3" t="str"/>
+      <c r="V363" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W363" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X363" s="3" t="str"/>
+    </row>
+    <row r="364" ht="110" customHeight="1">
+      <c r="A364" s="3" t="str"/>
+      <c r="B364" s="7" t="str">
+        <v>urinary-route-micturition-foundation-q04</v>
+      </c>
+      <c r="C364" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D364" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E364" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F364" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G364" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H364" s="5" t="inlineStr">
+        <is>
+          <t>哪一個尿道括約肌是骨骼肌，能讓我們用意識暫時管住排尿出口？</t>
+        </is>
+      </c>
+      <c r="I364" s="5" t="inlineStr">
+        <is>
+          <t>尿道內括約肌</t>
+        </is>
+      </c>
+      <c r="J364" s="5" t="inlineStr">
+        <is>
+          <t>膀胱壁的逼尿肌（迫尿肌）</t>
+        </is>
+      </c>
+      <c r="K364" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管壁的平滑肌</t>
+        </is>
+      </c>
+      <c r="L364" s="5" t="inlineStr">
+        <is>
+          <t>尿道外括約肌</t>
+        </is>
+      </c>
+      <c r="M364" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N364" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O364" s="5" t="inlineStr">
+        <is>
+          <t>因為尿道外括約肌是能隨意控制的骨骼肌，所以選「尿道外括約肌」。選「膀胱壁的逼尿肌（迫尿肌）」的同學，所選的逼尿肌是膀胱壁的平滑肌，和外括約肌不同。</t>
+        </is>
+      </c>
+      <c r="P364" s="5" t="inlineStr">
+        <is>
+          <t>先想想：能用意識管住的出口肌肉，在內側還是外側？</t>
+        </is>
+      </c>
+      <c r="Q364" s="5" t="str"/>
+      <c r="R364" s="5" t="inlineStr">
+        <is>
+          <t>答案是「尿道外括約肌」，因為外括約肌是骨骼肌，可受隨意控制。</t>
+        </is>
+      </c>
+      <c r="S364" s="5" t="inlineStr">
+        <is>
+          <t>外括約肌，意識能控制</t>
+        </is>
+      </c>
+      <c r="T364" s="3" t="str">
+        <v>urethra；anatomy/AB-05_15 p.14, anatomy/AB-05_15 p.15, anatomy/AB-05_15 p.12, physiology/CH09 p.25</v>
+      </c>
+      <c r="U364" s="3" t="str"/>
+      <c r="V364" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W364" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X364" s="3" t="str"/>
+    </row>
+    <row r="365" ht="110" customHeight="1">
+      <c r="A365" s="3" t="str"/>
+      <c r="B365" s="7" t="str">
+        <v>urinary-route-micturition-foundation-q05</v>
+      </c>
+      <c r="C365" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D365" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E365" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F365" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G365" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H365" s="5" t="inlineStr">
+        <is>
+          <t>排尿時，膀胱壁的逼尿肌（迫尿肌）和尿液出口要怎麼配合？</t>
+        </is>
+      </c>
+      <c r="I365" s="5" t="inlineStr">
+        <is>
+          <t>膀胱壁收縮，出口放鬆</t>
+        </is>
+      </c>
+      <c r="J365" s="5" t="inlineStr">
+        <is>
+          <t>膀胱壁放鬆，出口緊閉</t>
+        </is>
+      </c>
+      <c r="K365" s="5" t="inlineStr">
+        <is>
+          <t>膀胱壁收縮，出口也緊閉</t>
+        </is>
+      </c>
+      <c r="L365" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管停止蠕動，出口緊閉</t>
+        </is>
+      </c>
+      <c r="M365" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N365" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O365" s="5" t="inlineStr">
+        <is>
+          <t>因為排尿要把尿擠出、又要讓出口打開，所以膀胱壁要收縮，出口要放鬆。選「膀胱壁收縮，出口也緊閉」的同學，雖然擠了膀胱，出口卻還關著。</t>
+        </is>
+      </c>
+      <c r="P365" s="5" t="inlineStr">
+        <is>
+          <t>先想想：水袋要擠出水時，出口應打開還是關上？</t>
+        </is>
+      </c>
+      <c r="Q365" s="5" t="str"/>
+      <c r="R365" s="5" t="inlineStr">
+        <is>
+          <t>答案是「膀胱壁收縮，出口放鬆」，因為排尿需逼尿肌收縮並讓出口放鬆。</t>
+        </is>
+      </c>
+      <c r="S365" s="5" t="inlineStr">
+        <is>
+          <t>膀胱擠，出口鬆，尿才出得來</t>
+        </is>
+      </c>
+      <c r="T365" s="3" t="str">
+        <v>micturition-reflex；physiology/CH09 p.24, physiology/CH09 p.25, anatomy/AB-05_15 p.11, anatomy/AB-05_15 p.12, anatomy/AB-05_15 p.14</v>
+      </c>
+      <c r="U365" s="3" t="str"/>
+      <c r="V365" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W365" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X365" s="3" t="str"/>
+    </row>
+    <row r="366" ht="110" customHeight="1">
+      <c r="A366" s="3" t="str"/>
+      <c r="B366" s="7" t="str">
+        <v>urinary-route-micturition-foundation-q06</v>
+      </c>
+      <c r="C366" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D366" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F366" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G366" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H366" s="5" t="inlineStr">
+        <is>
+          <t>酸不酸的數字叫pH，數字越小越酸。記錄尿液時，每日尿量、尿比重和pH各是在說什麼？</t>
+        </is>
+      </c>
+      <c r="I366" s="5" t="inlineStr">
+        <is>
+          <t>尿量看酸鹼，比重看每日容量，pH看相對密度</t>
+        </is>
+      </c>
+      <c r="J366" s="5" t="inlineStr">
+        <is>
+          <t>尿量看每日容量，比重看相對密度，pH看酸鹼</t>
+        </is>
+      </c>
+      <c r="K366" s="5" t="inlineStr">
+        <is>
+          <t>尿量看相對密度，比重看酸鹼，pH看每日容量</t>
+        </is>
+      </c>
+      <c r="L366" s="5" t="inlineStr">
+        <is>
+          <t>尿量看每日容量，比重看酸鹼，pH看相對密度</t>
+        </is>
+      </c>
+      <c r="M366" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N366" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O366" s="5" t="inlineStr">
+        <is>
+          <t>因為每日尿量、比重與pH（酸不酸的數字，越小越酸）分別描述容量、相對密度與酸鹼，所以選「尿量看每日容量，比重看相對密度，pH看酸鹼」。選「尿量看相對密度，比重看酸鹼，pH看每日容量」的同學，把三個項目的意思錯配了。</t>
+        </is>
+      </c>
+      <c r="P366" s="5" t="inlineStr">
+        <is>
+          <t>先想想：容量、相對密度和酸不酸，能用同一個數字代替嗎？</t>
+        </is>
+      </c>
+      <c r="Q366" s="5" t="str"/>
+      <c r="R366" s="5" t="inlineStr">
+        <is>
+          <t>答案是「尿量看每日容量，比重看相對密度，pH看酸鹼」，因為尿量是每日容量，比重是相對密度，pH（酸不酸的數字叫pH，數字越小越酸）是酸鹼性。</t>
+        </is>
+      </c>
+      <c r="S366" s="5" t="inlineStr">
+        <is>
+          <t>尿量看多少，比重看密，pH看酸鹼</t>
+        </is>
+      </c>
+      <c r="T366" s="3" t="str">
+        <v>urine-physical-properties；physiology/CH09 p.22</v>
+      </c>
+      <c r="U366" s="3" t="str"/>
+      <c r="V366" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W366" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X366" s="3" t="str"/>
+    </row>
+    <row r="367" ht="110" customHeight="1">
+      <c r="A367" s="3" t="str"/>
+      <c r="B367" s="7" t="str">
+        <v>urinary-route-micturition-case-q01</v>
+      </c>
+      <c r="C367" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D367" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E367" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F367" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G367" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H367" s="5" t="inlineStr">
+        <is>
+          <t>輸尿管斜斜地穿過膀胱壁，膀胱內壓增加會把這段壓閉，這有什麼作用？</t>
+        </is>
+      </c>
+      <c r="I367" s="5" t="inlineStr">
+        <is>
+          <t>表示末端另有一片獨立瓣膜</t>
+        </is>
+      </c>
+      <c r="J367" s="5" t="inlineStr">
+        <is>
+          <t>像閥門一樣，有助防止尿倒流</t>
+        </is>
+      </c>
+      <c r="K367" s="5" t="inlineStr">
+        <is>
+          <t>讓尿從膀胱倒流回腎盂</t>
+        </is>
+      </c>
+      <c r="L367" s="5" t="inlineStr">
+        <is>
+          <t>讓輸尿管不必再蠕動送尿</t>
+        </is>
+      </c>
+      <c r="M367" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N367" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O367" s="5" t="inlineStr">
+        <is>
+          <t>因為斜穿膀胱壁的輸尿管受壓時能幫忙擋回流，所以選「像閥門一樣，有助防止尿倒流」的生理性瓣膜作用。選「表示末端另有一片獨立瓣膜」的同學，把這種關閉作用當成另外長了一片解剖瓣膜。</t>
+        </is>
+      </c>
+      <c r="P367" s="5" t="inlineStr">
+        <is>
+          <t>先想想：管壁被壓住像閥門，就表示另有一片瓣膜嗎？</t>
+        </is>
+      </c>
+      <c r="Q367" s="5" t="str"/>
+      <c r="R367" s="5" t="inlineStr">
+        <is>
+          <t>答案是「像閥門一樣，有助防止尿倒流」，因為斜穿膀胱壁受壓閉合可幫忙防逆流。</t>
+        </is>
+      </c>
+      <c r="S367" s="5" t="inlineStr">
+        <is>
+          <t>斜穿受壓像閥門，幫尿不倒流</t>
+        </is>
+      </c>
+      <c r="T367" s="3" t="str">
+        <v>ureter-constrictions；anatomy/AB-05_15 p.10, anatomy/AB-05_15 p.11</v>
+      </c>
+      <c r="U367" s="3" t="str"/>
+      <c r="V367" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W367" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X367" s="3" t="str"/>
+    </row>
+    <row r="368" ht="110" customHeight="1">
+      <c r="A368" s="3" t="str"/>
+      <c r="B368" s="7" t="str">
+        <v>urinary-route-micturition-case-q02</v>
+      </c>
+      <c r="C368" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D368" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E368" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F368" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G368" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H368" s="5" t="inlineStr">
+        <is>
+          <t>一滴尿從腎盂流向膀胱，會依序經過輸尿管哪三個較窄的地方？</t>
+        </is>
+      </c>
+      <c r="I368" s="5" t="inlineStr">
+        <is>
+          <t>先膀胱壁，再髂外血管交叉，最後腎盂交接</t>
+        </is>
+      </c>
+      <c r="J368" s="5" t="inlineStr">
+        <is>
+          <t>先髂外血管交叉，再腎盂交接，最後膀胱壁</t>
+        </is>
+      </c>
+      <c r="K368" s="5" t="inlineStr">
+        <is>
+          <t>先腎盂交接，再髂外血管交叉，最後膀胱壁</t>
+        </is>
+      </c>
+      <c r="L368" s="5" t="inlineStr">
+        <is>
+          <t>先腎盂交接，再尿道內口，最後膀胱壁</t>
+        </is>
+      </c>
+      <c r="M368" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N368" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O368" s="5" t="inlineStr">
+        <is>
+          <t>因為尿先從腎盂進輸尿管，中途跨過髂外動脈及靜脈，最後穿入膀胱壁，所以選「先腎盂交接，再髂外血管交叉，最後膀胱壁」。選「先腎盂交接，再尿道內口，最後膀胱壁」的同學，所選的尿道內口在膀胱出口，不在輸尿管上。</t>
+        </is>
+      </c>
+      <c r="P368" s="5" t="inlineStr">
+        <is>
+          <t>先想想：從腎到膀胱，是先過入口、交叉處，還是膀胱壁？</t>
+        </is>
+      </c>
+      <c r="Q368" s="5" t="str"/>
+      <c r="R368" s="5" t="inlineStr">
+        <is>
+          <t>答案是「先腎盂交接，再髂外血管交叉，最後膀胱壁」，因為三狹窄依序是腎盂交接、髂外血管交叉、膀胱壁。</t>
+        </is>
+      </c>
+      <c r="S368" s="5" t="inlineStr">
+        <is>
+          <t>腎盂出發，跨髂外，入膀胱</t>
+        </is>
+      </c>
+      <c r="T368" s="3" t="str">
+        <v>ureter-constrictions；anatomy/AB-05_15 p.10, anatomy/AB-05_15 p.11, physiology/CH09 p.3, physiology/CH09 p.13</v>
+      </c>
+      <c r="U368" s="3" t="str"/>
+      <c r="V368" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W368" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X368" s="3" t="str"/>
+    </row>
+    <row r="369" ht="110" customHeight="1">
+      <c r="A369" s="3" t="str"/>
+      <c r="B369" s="7" t="str">
+        <v>urinary-route-micturition-case-q03</v>
+      </c>
+      <c r="C369" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D369" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E369" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F369" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G369" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H369" s="5" t="inlineStr">
+        <is>
+          <t>要在膀胱裡找出膀胱三角，應找哪三處來定出範圍？</t>
+        </is>
+      </c>
+      <c r="I369" s="5" t="inlineStr">
+        <is>
+          <t>左右輸尿管口和尿道外口</t>
+        </is>
+      </c>
+      <c r="J369" s="5" t="inlineStr">
+        <is>
+          <t>左右腎盂開口和尿道內口</t>
+        </is>
+      </c>
+      <c r="K369" s="5" t="inlineStr">
+        <is>
+          <t>左右輸尿管口和膀胱頂</t>
+        </is>
+      </c>
+      <c r="L369" s="5" t="inlineStr">
+        <is>
+          <t>左右輸尿管口和尿道內口</t>
+        </is>
+      </c>
+      <c r="M369" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N369" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O369" s="5" t="inlineStr">
+        <is>
+          <t>因為膀胱三角由兩個進尿口和一個出尿口圍成，所以選「左右輸尿管口和尿道內口」。選「左右輸尿管口和膀胱頂」的同學，把出尿的尿道內口換成膀胱頂，位置就錯了。</t>
+        </is>
+      </c>
+      <c r="P369" s="5" t="inlineStr">
+        <is>
+          <t>先想想：兩個入口和一個出口，都能在膀胱裡找到嗎？</t>
+        </is>
+      </c>
+      <c r="Q369" s="5" t="str"/>
+      <c r="R369" s="5" t="inlineStr">
+        <is>
+          <t>答案是「左右輸尿管口和尿道內口」，因為兩輸尿管口與尿道內口界定膀胱三角。</t>
+        </is>
+      </c>
+      <c r="S369" s="5" t="inlineStr">
+        <is>
+          <t>膀胱三角，找兩進一出</t>
+        </is>
+      </c>
+      <c r="T369" s="3" t="str">
+        <v>urinary-bladder；anatomy/AB-05_15 p.11, anatomy/AB-05_15 p.12, physiology/CH09 p.24, physiology/CH09 p.25</v>
+      </c>
+      <c r="U369" s="3" t="str"/>
+      <c r="V369" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W369" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X369" s="3" t="str"/>
+    </row>
+    <row r="370" ht="110" customHeight="1">
+      <c r="A370" s="3" t="str"/>
+      <c r="B370" s="7" t="str">
+        <v>urinary-route-micturition-case-q04</v>
+      </c>
+      <c r="C370" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D370" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E370" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F370" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G370" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H370" s="5" t="inlineStr">
+        <is>
+          <t>想用意識暫時控制排尿出口，主要是哪一條神經和哪塊肌肉在配合？</t>
+        </is>
+      </c>
+      <c r="I370" s="5" t="inlineStr">
+        <is>
+          <t>陰神經與尿道外括約肌</t>
+        </is>
+      </c>
+      <c r="J370" s="5" t="inlineStr">
+        <is>
+          <t>副交感神經與尿道外括約肌</t>
+        </is>
+      </c>
+      <c r="K370" s="5" t="inlineStr">
+        <is>
+          <t>陰神經與尿道內括約肌</t>
+        </is>
+      </c>
+      <c r="L370" s="5" t="inlineStr">
+        <is>
+          <t>交感神經與尿道外括約肌</t>
+        </is>
+      </c>
+      <c r="M370" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N370" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O370" s="5" t="inlineStr">
+        <is>
+          <t>因為陰神經這條體神經控制尿道外括約肌，所以選「陰神經與尿道外括約肌」。選「陰神經與尿道內括約肌」的同學，把能隨意控制的外括約肌換成了平滑肌的內括約肌。</t>
+        </is>
+      </c>
+      <c r="P370" s="5" t="inlineStr">
+        <is>
+          <t>先想想：能隨意控制的肌肉，是內括約肌還是外括約肌？</t>
+        </is>
+      </c>
+      <c r="Q370" s="5" t="str"/>
+      <c r="R370" s="5" t="inlineStr">
+        <is>
+          <t>答案是「陰神經與尿道外括約肌」，因為陰神經控制外括約肌，讓排尿出口可受意識控制。</t>
+        </is>
+      </c>
+      <c r="S370" s="5" t="inlineStr">
+        <is>
+          <t>陰神經管外肌，意識能憋尿</t>
+        </is>
+      </c>
+      <c r="T370" s="3" t="str">
+        <v>micturition-reflex；physiology/CH09 p.24, physiology/CH09 p.25, anatomy/AB-05_15 p.11, anatomy/AB-05_15 p.12, anatomy/AB-05_15 p.14</v>
+      </c>
+      <c r="U370" s="3" t="str"/>
+      <c r="V370" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W370" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X370" s="3" t="str"/>
+    </row>
+    <row r="371" ht="110" customHeight="1">
+      <c r="A371" s="3" t="str"/>
+      <c r="B371" s="7" t="str">
+        <v>urinary-route-micturition-case-q05</v>
+      </c>
+      <c r="C371" s="5" t="str">
+        <v>泌尿系統</v>
+      </c>
+      <c r="D371" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="E371" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F371" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G371" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H371" s="5" t="inlineStr">
+        <is>
+          <t>尿液紀錄同時寫了每日尿量和尿比重，應怎麼看這兩個數字？</t>
+        </is>
+      </c>
+      <c r="I371" s="5" t="inlineStr">
+        <is>
+          <t>尿量一樣，比重就一樣</t>
+        </is>
+      </c>
+      <c r="J371" s="5" t="inlineStr">
+        <is>
+          <t>用比重直接換成每日尿量</t>
+        </is>
+      </c>
+      <c r="K371" s="5" t="inlineStr">
+        <is>
+          <t>一個看每日容量，一個看相對密度，分開來看</t>
+        </is>
+      </c>
+      <c r="L371" s="5" t="inlineStr">
+        <is>
+          <t>兩個都在說尿液酸不酸</t>
+        </is>
+      </c>
+      <c r="M371" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N371" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O371" s="5" t="inlineStr">
+        <is>
+          <t>因為尿量在說一天排出多少，尿比重是相對密度、在比較尿液有多「密」，所以要分開看，選「一個看每日容量，一個看相對密度，分開來看」。選「尿量一樣，比重就一樣」的同學，把尿量一樣當成比重也會一樣。</t>
+        </is>
+      </c>
+      <c r="P371" s="5" t="inlineStr">
+        <is>
+          <t>先想想：兩杯液體一樣多，就表示它們的相對密度也一樣嗎？</t>
+        </is>
+      </c>
+      <c r="Q371" s="5" t="str"/>
+      <c r="R371" s="5" t="inlineStr">
+        <is>
+          <t>答案是「一個看每日容量，一個看相對密度，分開來看」，因為每日容量與相對密度是不同的量，須分別閱讀。</t>
+        </is>
+      </c>
+      <c r="S371" s="5" t="inlineStr">
+        <is>
+          <t>尿量看多少，比重另看相對密度</t>
+        </is>
+      </c>
+      <c r="T371" s="3" t="str">
+        <v>urine-physical-properties；physiology/CH09 p.22</v>
+      </c>
+      <c r="U371" s="3" t="str"/>
+      <c r="V371" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="W371" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/urinary-route-micturition-v2/index.html</v>
+      </c>
+      <c r="X371" s="3" t="str"/>
+    </row>
+    <row r="372" ht="110" customHeight="1">
+      <c r="A372" s="3" t="str"/>
+      <c r="B372" s="7" t="str">
+        <v>fluid-compartments-foundation-q01</v>
+      </c>
+      <c r="C372" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D372" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E372" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F372" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G372" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H372" s="5" t="inlineStr">
+        <is>
+          <t>課本用「全身的水約占60%」作標準例子，這60%是在和什麼相比？</t>
+        </is>
+      </c>
+      <c r="I372" s="5" t="inlineStr">
+        <is>
+          <t>全身體重</t>
+        </is>
+      </c>
+      <c r="J372" s="5" t="inlineStr">
+        <is>
+          <t>細胞裡的水</t>
+        </is>
+      </c>
+      <c r="K372" s="5" t="inlineStr">
+        <is>
+          <t>血漿的量</t>
+        </is>
+      </c>
+      <c r="L372" s="5" t="inlineStr">
+        <is>
+          <t>細胞之間的水</t>
+        </is>
+      </c>
+      <c r="M372" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N372" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O372" s="5" t="inlineStr">
+        <is>
+          <t>因為這個60%說的是水占體重的比例，所以選「全身體重」。選「細胞裡的水」的同學，把全身體重換成細胞內的水，百分比的意思就變了。</t>
+        </is>
+      </c>
+      <c r="P372" s="5" t="inlineStr">
+        <is>
+          <t>先想想：說身體六成是水，是拿水和整個身體的什麼相比？</t>
+        </is>
+      </c>
+      <c r="Q372" s="5" t="str"/>
+      <c r="R372" s="5" t="inlineStr">
+        <is>
+          <t>答案是「全身體重」，因為標準總水量60%是以體重為基準。</t>
+        </is>
+      </c>
+      <c r="S372" s="5" t="inlineStr">
+        <is>
+          <t>身體六成水，是和體重比</t>
+        </is>
+      </c>
+      <c r="T372" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U372" s="3" t="str"/>
+      <c r="V372" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W372" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X372" s="3" t="str"/>
+    </row>
+    <row r="373" ht="110" customHeight="1">
+      <c r="A373" s="3" t="str"/>
+      <c r="B373" s="7" t="str">
+        <v>fluid-compartments-foundation-q02</v>
+      </c>
+      <c r="C373" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D373" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E373" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F373" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G373" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H373" s="5" t="inlineStr">
+        <is>
+          <t>先把全身的水當成一整份，細胞內液和細胞外液各分到多少？</t>
+        </is>
+      </c>
+      <c r="I373" s="5" t="inlineStr">
+        <is>
+          <t>細胞內一半，細胞外一半</t>
+        </is>
+      </c>
+      <c r="J373" s="5" t="inlineStr">
+        <is>
+          <t>細胞內三分之二，細胞外三分之一</t>
+        </is>
+      </c>
+      <c r="K373" s="5" t="inlineStr">
+        <is>
+          <t>細胞內三分之一，細胞外三分之二</t>
+        </is>
+      </c>
+      <c r="L373" s="5" t="inlineStr">
+        <is>
+          <t>細胞內五分之四，細胞外五分之一</t>
+        </is>
+      </c>
+      <c r="M373" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N373" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O373" s="5" t="inlineStr">
+        <is>
+          <t>因為全身總水量約三分之二在細胞裡、三分之一在外面，所以選「細胞內三分之二，細胞外三分之一」。選「細胞內三分之一，細胞外三分之二」的同學，把細胞內與細胞外的份量交換了。</t>
+        </is>
+      </c>
+      <c r="P373" s="5" t="inlineStr">
+        <is>
+          <t>先想想：全身的水分三份，細胞裡拿兩份還是一份？</t>
+        </is>
+      </c>
+      <c r="Q373" s="5" t="str"/>
+      <c r="R373" s="5" t="inlineStr">
+        <is>
+          <t>答案是「細胞內三分之二，細胞外三分之一」，因為細胞內液占總水量2/3，外液占1/3。</t>
+        </is>
+      </c>
+      <c r="S373" s="5" t="inlineStr">
+        <is>
+          <t>總水分三份，內二外一</t>
+        </is>
+      </c>
+      <c r="T373" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U373" s="3" t="str"/>
+      <c r="V373" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W373" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X373" s="3" t="str"/>
+    </row>
+    <row r="374" ht="110" customHeight="1">
+      <c r="A374" s="3" t="str"/>
+      <c r="B374" s="7" t="str">
+        <v>fluid-compartments-foundation-q03</v>
+      </c>
+      <c r="C374" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D374" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F374" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G374" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H374" s="5" t="inlineStr">
+        <is>
+          <t>血漿占20%、細胞之間的組織間液占80%，這兩個比例是在分哪一整份水？</t>
+        </is>
+      </c>
+      <c r="I374" s="5" t="inlineStr">
+        <is>
+          <t>全身總水量</t>
+        </is>
+      </c>
+      <c r="J374" s="5" t="inlineStr">
+        <is>
+          <t>細胞內液</t>
+        </is>
+      </c>
+      <c r="K374" s="5" t="inlineStr">
+        <is>
+          <t>細胞外液</t>
+        </is>
+      </c>
+      <c r="L374" s="5" t="inlineStr">
+        <is>
+          <t>全身體重</t>
+        </is>
+      </c>
+      <c r="M374" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N374" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O374" s="5" t="inlineStr">
+        <is>
+          <t>因為血漿和組織間液都是細胞外液的一部分，所以選「細胞外液」。選「全身體重」的同學，把「占細胞外液」誤當成「占體重」。</t>
+        </is>
+      </c>
+      <c r="P374" s="5" t="inlineStr">
+        <is>
+          <t>先想想：血管裡的血漿和細胞之間的水，都在細胞外嗎？</t>
+        </is>
+      </c>
+      <c r="Q374" s="5" t="str"/>
+      <c r="R374" s="5" t="inlineStr">
+        <is>
+          <t>答案是「細胞外液」，因為血漿20%與組織間液80%是在細分細胞外液。</t>
+        </is>
+      </c>
+      <c r="S374" s="5" t="inlineStr">
+        <is>
+          <t>外液分兩邊，血漿二、間液八</t>
+        </is>
+      </c>
+      <c r="T374" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U374" s="3" t="str"/>
+      <c r="V374" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W374" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X374" s="3" t="str"/>
+    </row>
+    <row r="375" ht="110" customHeight="1">
+      <c r="A375" s="3" t="str"/>
+      <c r="B375" s="7" t="str">
+        <v>fluid-compartments-foundation-q04</v>
+      </c>
+      <c r="C375" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D375" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F375" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G375" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H375" s="5" t="inlineStr">
+        <is>
+          <t>同一個標準例子說血漿占體重4%、組織間液占體重16%，把兩項合起來是什麼？</t>
+        </is>
+      </c>
+      <c r="I375" s="5" t="inlineStr">
+        <is>
+          <t>先加成20%，再多加一次外液20%</t>
+        </is>
+      </c>
+      <c r="J375" s="5" t="inlineStr">
+        <is>
+          <t>合起來就是細胞內液</t>
+        </is>
+      </c>
+      <c r="K375" s="5" t="inlineStr">
+        <is>
+          <t>兩項都改說成占血漿的比例</t>
+        </is>
+      </c>
+      <c r="L375" s="5" t="inlineStr">
+        <is>
+          <t>合起來是占體重20%的細胞外液</t>
+        </is>
+      </c>
+      <c r="M375" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N375" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O375" s="5" t="inlineStr">
+        <is>
+          <t>因為血漿和組織間液已經組成細胞外液，所以4%加16%就是外液20%，選「合起來是占體重20%的細胞外液」。選「先加成20%，再多加一次外液20%」的同學，又加一次外液20%，把同一份水重複算了。</t>
+        </is>
+      </c>
+      <c r="P375" s="5" t="inlineStr">
+        <is>
+          <t>先想想：小份加起來已是整份，還要把整份再加一次嗎？</t>
+        </is>
+      </c>
+      <c r="Q375" s="5" t="str"/>
+      <c r="R375" s="5" t="inlineStr">
+        <is>
+          <t>答案是「合起來是占體重20%的細胞外液」，因為4%加16%就是占體重20%的細胞外液。</t>
+        </is>
+      </c>
+      <c r="S375" s="5" t="inlineStr">
+        <is>
+          <t>血漿四加間液十六，外液二十</t>
+        </is>
+      </c>
+      <c r="T375" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U375" s="3" t="str"/>
+      <c r="V375" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W375" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X375" s="3" t="str"/>
+    </row>
+    <row r="376" ht="110" customHeight="1">
+      <c r="A376" s="3" t="str"/>
+      <c r="B376" s="7" t="str">
+        <v>fluid-compartments-foundation-q05</v>
+      </c>
+      <c r="C376" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D376" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E376" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F376" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G376" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H376" s="5" t="inlineStr">
+        <is>
+          <t>血漿在血管內，組織間液在細胞之間，兩邊的重要差別是什麼？</t>
+        </is>
+      </c>
+      <c r="I376" s="5" t="inlineStr">
+        <is>
+          <t>血漿的蛋白質比較多</t>
+        </is>
+      </c>
+      <c r="J376" s="5" t="inlineStr">
+        <is>
+          <t>組織間液沒有小離子</t>
+        </is>
+      </c>
+      <c r="K376" s="5" t="inlineStr">
+        <is>
+          <t>組織間液的蛋白質比較多</t>
+        </is>
+      </c>
+      <c r="L376" s="5" t="inlineStr">
+        <is>
+          <t>兩邊的蛋白質差不多</t>
+        </is>
+      </c>
+      <c r="M376" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N376" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O376" s="5" t="inlineStr">
+        <is>
+          <t>因為微血管壁讓蛋白質較多留在血漿，所以選「血漿的蛋白質比較多」。選「組織間液的蛋白質比較多」的同學，把蛋白質較多的一邊寫成了組織間液。</t>
+        </is>
+      </c>
+      <c r="P376" s="5" t="inlineStr">
+        <is>
+          <t>先想想：蛋白質比較容易留在血管裡，還是跑到細胞之間？</t>
+        </is>
+      </c>
+      <c r="Q376" s="5" t="str"/>
+      <c r="R376" s="5" t="inlineStr">
+        <is>
+          <t>答案是「血漿的蛋白質比較多」，因為血漿通常比組織間液含較多蛋白質。</t>
+        </is>
+      </c>
+      <c r="S376" s="5" t="inlineStr">
+        <is>
+          <t>血漿蛋白多，間液比較少</t>
+        </is>
+      </c>
+      <c r="T376" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37
+electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U376" s="3" t="str"/>
+      <c r="V376" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W376" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X376" s="3" t="str"/>
+    </row>
+    <row r="377" ht="110" customHeight="1">
+      <c r="A377" s="3" t="str"/>
+      <c r="B377" s="7" t="str">
+        <v>fluid-compartments-foundation-q06</v>
+      </c>
+      <c r="C377" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D377" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E377" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F377" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G377" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H377" s="5" t="inlineStr">
+        <is>
+          <t>課本說女性全身水量約占體重55%、男性約65%，使用這些比例時要注意什麼？</t>
+        </is>
+      </c>
+      <c r="I377" s="5" t="inlineStr">
+        <is>
+          <t>脂肪多少不會影響身體含水比例</t>
+        </is>
+      </c>
+      <c r="J377" s="5" t="inlineStr">
+        <is>
+          <t>男女的條件會影響身體含水比例</t>
+        </is>
+      </c>
+      <c r="K377" s="5" t="inlineStr">
+        <is>
+          <t>每個人都用標準60%就好</t>
+        </is>
+      </c>
+      <c r="L377" s="5" t="inlineStr">
+        <is>
+          <t>55%和65%是拿水和細胞外液相比</t>
+        </is>
+      </c>
+      <c r="M377" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N377" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O377" s="5" t="inlineStr">
+        <is>
+          <t>因為課本的男女含水比例不同，所以要把性別與脂肪差異算進去，選「男女的條件會影響身體含水比例」。選「每個人都用標準60%就好」的同學，把標準60%當成每個人的固定比例。</t>
+        </is>
+      </c>
+      <c r="P377" s="5" t="inlineStr">
+        <is>
+          <t>先想想：課本已給男女不同數字，還能用同一個60%嗎？</t>
+        </is>
+      </c>
+      <c r="Q377" s="5" t="str"/>
+      <c r="R377" s="5" t="inlineStr">
+        <is>
+          <t>答案是「男女的條件會影響身體含水比例」，因為男女條件會影響占體重的含水比例。</t>
+        </is>
+      </c>
+      <c r="S377" s="5" t="inlineStr">
+        <is>
+          <t>含水比例看條件，男女不硬套</t>
+        </is>
+      </c>
+      <c r="T377" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U377" s="3" t="str"/>
+      <c r="V377" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W377" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X377" s="3" t="str"/>
+    </row>
+    <row r="378" ht="110" customHeight="1">
+      <c r="A378" s="3" t="str"/>
+      <c r="B378" s="7" t="str">
+        <v>fluid-compartments-case-q01</v>
+      </c>
+      <c r="C378" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D378" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E378" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F378" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G378" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H378" s="5" t="inlineStr">
+        <is>
+          <t>知道一個人的體重，並採用「全身水約占體重60%」的例子，想分出細胞內外各有多少水，第一步要算什麼？</t>
+        </is>
+      </c>
+      <c r="I378" s="5" t="inlineStr">
+        <is>
+          <t>把整個體重當成細胞裡的水</t>
+        </is>
+      </c>
+      <c r="J378" s="5" t="inlineStr">
+        <is>
+          <t>把血漿比例當成全身水比例</t>
+        </is>
+      </c>
+      <c r="K378" s="5" t="inlineStr">
+        <is>
+          <t>先用體重算出全身共有多少水</t>
+        </is>
+      </c>
+      <c r="L378" s="5" t="inlineStr">
+        <is>
+          <t>直接把體重當成血漿的量</t>
+        </is>
+      </c>
+      <c r="M378" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N378" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O378" s="5" t="inlineStr">
+        <is>
+          <t>因為要先知道全身有多少水，才有一整份水能分配，所以先用體重乘60%，選「先用體重算出全身共有多少水」。選「把整個體重當成細胞裡的水」的同學，把整個體重都當成細胞內的水，少了先算總水量這一步。</t>
+        </is>
+      </c>
+      <c r="P378" s="5" t="inlineStr">
+        <is>
+          <t>先想想：要把水分成內外兩份，先要知道哪個總量？</t>
+        </is>
+      </c>
+      <c r="Q378" s="5" t="str"/>
+      <c r="R378" s="5" t="inlineStr">
+        <is>
+          <t>答案是「先用體重算出全身共有多少水」，因為先算出全身總水量，才能再分細胞內外。</t>
+        </is>
+      </c>
+      <c r="S378" s="5" t="inlineStr">
+        <is>
+          <t>先算總水量，再分內外</t>
+        </is>
+      </c>
+      <c r="T378" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U378" s="3" t="str"/>
+      <c r="V378" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W378" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X378" s="3" t="str"/>
+    </row>
+    <row r="379" ht="110" customHeight="1">
+      <c r="A379" s="3" t="str"/>
+      <c r="B379" s="7" t="str">
+        <v>fluid-compartments-case-q02</v>
+      </c>
+      <c r="C379" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D379" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E379" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F379" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G379" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H379" s="5" t="inlineStr">
+        <is>
+          <t>血漿雖然在血管裡，但以「在不在細胞裡」來分，它屬於哪一類？</t>
+        </is>
+      </c>
+      <c r="I379" s="5" t="inlineStr">
+        <is>
+          <t>細胞內液</t>
+        </is>
+      </c>
+      <c r="J379" s="5" t="inlineStr">
+        <is>
+          <t>腎小管內液</t>
+        </is>
+      </c>
+      <c r="K379" s="5" t="inlineStr">
+        <is>
+          <t>紅血球裡的液體</t>
+        </is>
+      </c>
+      <c r="L379" s="5" t="inlineStr">
+        <is>
+          <t>細胞外液</t>
+        </is>
+      </c>
+      <c r="M379" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N379" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O379" s="5" t="inlineStr">
+        <is>
+          <t>因為血漿在血管內、卻在細胞外面，所以屬於細胞外液，選「細胞外液」。選「細胞內液」的同學，把「血管裡面」當成「細胞裡面」了。</t>
+        </is>
+      </c>
+      <c r="P379" s="5" t="inlineStr">
+        <is>
+          <t>先想想：血管裡面，和細胞裡面，是同一個地方嗎？</t>
+        </is>
+      </c>
+      <c r="Q379" s="5" t="str"/>
+      <c r="R379" s="5" t="inlineStr">
+        <is>
+          <t>答案是「細胞外液」，因為血漿在細胞外，屬於細胞外液。</t>
+        </is>
+      </c>
+      <c r="S379" s="5" t="inlineStr">
+        <is>
+          <t>血管內的血漿，仍在細胞外</t>
+        </is>
+      </c>
+      <c r="T379" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U379" s="3" t="str"/>
+      <c r="V379" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W379" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X379" s="3" t="str"/>
+    </row>
+    <row r="380" ht="110" customHeight="1">
+      <c r="A380" s="3" t="str"/>
+      <c r="B380" s="7" t="str">
+        <v>fluid-compartments-case-q03</v>
+      </c>
+      <c r="C380" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D380" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E380" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F380" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G380" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H380" s="5" t="inlineStr">
+        <is>
+          <t>這個例子用全身水占體重60%、血漿占體重4%、組織間液占16%，另一份資料卻用不同數字，應怎麼整理？</t>
+        </is>
+      </c>
+      <c r="I380" s="5" t="inlineStr">
+        <is>
+          <t>保留本例的比較基準和比例，另一例另外列</t>
+        </is>
+      </c>
+      <c r="J380" s="5" t="inlineStr">
+        <is>
+          <t>把4%和16%改說成占細胞外液的比例</t>
+        </is>
+      </c>
+      <c r="K380" s="5" t="inlineStr">
+        <is>
+          <t>把4%和16%改說成細胞內液的兩部分</t>
+        </is>
+      </c>
+      <c r="L380" s="5" t="inlineStr">
+        <is>
+          <t>把4%改說成占全身總水量的比例</t>
+        </is>
+      </c>
+      <c r="M380" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N380" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O380" s="5" t="inlineStr">
+        <is>
+          <t>因為4%和16%都是本例占體重的比例，所以要和本例的60%一起使用，選「保留本例的比較基準和比例，另一例另外列」。選「把4%和16%改說成占細胞外液的比例」的同學，換了比較的整份水，數字就不再是同一個意思。</t>
+        </is>
+      </c>
+      <c r="P380" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這些百分比原本都是拿哪一個整體來比較？</t>
+        </is>
+      </c>
+      <c r="Q380" s="5" t="str"/>
+      <c r="R380" s="5" t="inlineStr">
+        <is>
+          <t>答案是「保留本例的比較基準和比例，另一例另外列」，因為保留同一例的基準與比例，別例另列才一致。</t>
+        </is>
+      </c>
+      <c r="S380" s="5" t="inlineStr">
+        <is>
+          <t>同一例用同一基準，別例另列</t>
+        </is>
+      </c>
+      <c r="T380" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U380" s="3" t="str"/>
+      <c r="V380" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W380" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X380" s="3" t="str"/>
+    </row>
+    <row r="381" ht="110" customHeight="1">
+      <c r="A381" s="3" t="str"/>
+      <c r="B381" s="7" t="str">
+        <v>fluid-compartments-case-q04</v>
+      </c>
+      <c r="C381" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D381" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E381" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F381" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G381" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H381" s="5" t="inlineStr">
+        <is>
+          <t>兩位成年男女體重一樣，要估算身體有多少水，還要把什麼差異算進去？</t>
+        </is>
+      </c>
+      <c r="I381" s="5" t="inlineStr">
+        <is>
+          <t>主要看年齡，男女差異可以省略</t>
+        </is>
+      </c>
+      <c r="J381" s="5" t="inlineStr">
+        <is>
+          <t>男女與脂肪比例的差異</t>
+        </is>
+      </c>
+      <c r="K381" s="5" t="inlineStr">
+        <is>
+          <t>男女都用60%，不再看其他條件</t>
+        </is>
+      </c>
+      <c r="L381" s="5" t="inlineStr">
+        <is>
+          <t>把女性的含水比例設得比男性高</t>
+        </is>
+      </c>
+      <c r="M381" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N381" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O381" s="5" t="inlineStr">
+        <is>
+          <t>因為含水比例會隨性別等條件改變，所以估算時要看男女與脂肪差異，選「男女與脂肪比例的差異」。選「主要看年齡，男女差異可以省略」的同學，雖想到年齡，卻把題目要比較的男女差異省略了。</t>
+        </is>
+      </c>
+      <c r="P381" s="5" t="inlineStr">
+        <is>
+          <t>先想想：體重相同，就表示男女的含水比例也相同嗎？</t>
+        </is>
+      </c>
+      <c r="Q381" s="5" t="str"/>
+      <c r="R381" s="5" t="inlineStr">
+        <is>
+          <t>答案是「男女與脂肪比例的差異」，因為性別與脂肪比例差異會影響含水比例。</t>
+        </is>
+      </c>
+      <c r="S381" s="5" t="inlineStr">
+        <is>
+          <t>同體重，含水還要看男女脂肪</t>
+        </is>
+      </c>
+      <c r="T381" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37</v>
+      </c>
+      <c r="U381" s="3" t="str"/>
+      <c r="V381" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W381" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X381" s="3" t="str"/>
+    </row>
+    <row r="382" ht="110" customHeight="1">
+      <c r="A382" s="3" t="str"/>
+      <c r="B382" s="7" t="str">
+        <v>fluid-compartments-case-q05</v>
+      </c>
+      <c r="C382" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D382" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="E382" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F382" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G382" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H382" s="5" t="inlineStr">
+        <is>
+          <t>正常血漿和組織間液都有小離子，為什麼血漿通常有比較多蛋白質？</t>
+        </is>
+      </c>
+      <c r="I382" s="5" t="inlineStr">
+        <is>
+          <t>微血管壁會主動把外面的蛋白質搬回血漿</t>
+        </is>
+      </c>
+      <c r="J382" s="5" t="inlineStr">
+        <is>
+          <t>微血管壁讓蛋白質自由通過，兩邊應一樣多</t>
+        </is>
+      </c>
+      <c r="K382" s="5" t="inlineStr">
+        <is>
+          <t>微血管壁不太讓蛋白質通過，較多留在血漿</t>
+        </is>
+      </c>
+      <c r="L382" s="5" t="inlineStr">
+        <is>
+          <t>微血管壁擋住小離子，卻讓蛋白質容易通過</t>
+        </is>
+      </c>
+      <c r="M382" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N382" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O382" s="5" t="inlineStr">
+        <is>
+          <t>因為微血管壁限制蛋白質通過，所以較多蛋白質保留在血漿，選「微血管壁不太讓蛋白質通過，較多留在血漿」。選「微血管壁擋住小離子，卻讓蛋白質容易通過」的同學，把蛋白質與小離子的通過情形交換了。</t>
+        </is>
+      </c>
+      <c r="P382" s="5" t="inlineStr">
+        <is>
+          <t>先想想：微血管壁比較容易擋住蛋白質，還是小離子？</t>
+        </is>
+      </c>
+      <c r="Q382" s="5" t="str"/>
+      <c r="R382" s="5" t="inlineStr">
+        <is>
+          <t>答案是「微血管壁不太讓蛋白質通過，較多留在血漿」，因為微血管壁不易讓蛋白質通過，蛋白質較多留在血漿。</t>
+        </is>
+      </c>
+      <c r="S382" s="5" t="inlineStr">
+        <is>
+          <t>微血管擋蛋白，血漿留得多</t>
+        </is>
+      </c>
+      <c r="T382" s="3" t="str">
+        <v>body-fluid-compartments；physiology/CH09 p.28, physiology/CH09 p.29, physiology/CH09 p.33, physiology/CH09 p.37
+electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U382" s="3" t="str"/>
+      <c r="V382" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="W382" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/fluid-compartments-v1/index.html</v>
+      </c>
+      <c r="X382" s="3" t="str"/>
+    </row>
+    <row r="383" ht="110" customHeight="1">
+      <c r="A383" s="3" t="str"/>
+      <c r="B383" s="7" t="str">
+        <v>water-sodium-regulation-foundation-q01</v>
+      </c>
+      <c r="C383" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D383" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E383" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F383" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G383" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H383" s="5" t="inlineStr">
+        <is>
+          <t>一天補進身體的水，應把哪三種來源算進去？</t>
+        </is>
+      </c>
+      <c r="I383" s="5" t="inlineStr">
+        <is>
+          <t>喝進的液體、食物裡的水、身體產生的代謝水</t>
+        </is>
+      </c>
+      <c r="J383" s="5" t="inlineStr">
+        <is>
+          <t>喝進的液體，不算食物和代謝水</t>
+        </is>
+      </c>
+      <c r="K383" s="5" t="inlineStr">
+        <is>
+          <t>尿液、呼氣與糞便帶走的水</t>
+        </is>
+      </c>
+      <c r="L383" s="5" t="inlineStr">
+        <is>
+          <t>流汗和皮膚慢慢散掉的水</t>
+        </is>
+      </c>
+      <c r="M383" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N383" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O383" s="5" t="inlineStr">
+        <is>
+          <t>因為身體會從喝水、食物和代謝產水得到水分，所以選「喝進的液體、食物裡的水、身體產生的代謝水」。選「喝進的液體，不算食物和代謝水」的同學，漏掉了食物裡的水與身體代謝產生的水。</t>
+        </is>
+      </c>
+      <c r="P383" s="5" t="inlineStr">
+        <is>
+          <t>先想想：除了喝水，吃東西和身體運作也會帶來水嗎？</t>
+        </is>
+      </c>
+      <c r="Q383" s="5" t="str"/>
+      <c r="R383" s="5" t="inlineStr">
+        <is>
+          <t>答案是「喝進的液體、食物裡的水、身體產生的代謝水」，因為每日水攝取包括液體、食物水與代謝水。</t>
+        </is>
+      </c>
+      <c r="S383" s="5" t="inlineStr">
+        <is>
+          <t>喝的、吃的、身體產的都算水</t>
+        </is>
+      </c>
+      <c r="T383" s="3" t="str">
+        <v>water-intake-output；physiology/CH09 p.30, physiology/CH09 p.29</v>
+      </c>
+      <c r="U383" s="3" t="str"/>
+      <c r="V383" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W383" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X383" s="3" t="str"/>
+    </row>
+    <row r="384" ht="110" customHeight="1">
+      <c r="A384" s="3" t="str"/>
+      <c r="B384" s="7" t="str">
+        <v>water-sodium-regulation-foundation-q02</v>
+      </c>
+      <c r="C384" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D384" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E384" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F384" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G384" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H384" s="5" t="inlineStr">
+        <is>
+          <t>沒有看到汗流出來時，皮膚還會失去水分嗎？</t>
+        </is>
+      </c>
+      <c r="I384" s="5" t="inlineStr">
+        <is>
+          <t>不會，而且呼氣也沒有水</t>
+        </is>
+      </c>
+      <c r="J384" s="5" t="inlineStr">
+        <is>
+          <t>會，仍有看不見的無知覺蒸散</t>
+        </is>
+      </c>
+      <c r="K384" s="5" t="inlineStr">
+        <is>
+          <t>不會，皮膚此時不會排水</t>
+        </is>
+      </c>
+      <c r="L384" s="5" t="inlineStr">
+        <is>
+          <t>不會，這些水都改從糞便排掉</t>
+        </is>
+      </c>
+      <c r="M384" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N384" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O384" s="5" t="inlineStr">
+        <is>
+          <t>因為皮膚即使沒明顯流汗，仍會慢慢散掉水，所以仍有看不見的無知覺蒸散。選「不會，皮膚此時不會排水」的同學，把沒有看見汗當成沒有皮膚失水。</t>
+        </is>
+      </c>
+      <c r="P384" s="5" t="inlineStr">
+        <is>
+          <t>先想想：沒看見汗，和沒有水離開皮膚，一樣嗎？</t>
+        </is>
+      </c>
+      <c r="Q384" s="5" t="str"/>
+      <c r="R384" s="5" t="inlineStr">
+        <is>
+          <t>答案是「會，仍有看不見的無知覺蒸散」，因為沒有明顯流汗仍可有無知覺蒸散。</t>
+        </is>
+      </c>
+      <c r="S384" s="5" t="inlineStr">
+        <is>
+          <t>沒流汗，皮膚仍會散水</t>
+        </is>
+      </c>
+      <c r="T384" s="3" t="str">
+        <v>water-intake-output；physiology/CH09 p.30, physiology/CH09 p.29</v>
+      </c>
+      <c r="U384" s="3" t="str"/>
+      <c r="V384" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W384" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X384" s="3" t="str"/>
+    </row>
+    <row r="385" ht="110" customHeight="1">
+      <c r="A385" s="3" t="str"/>
+      <c r="B385" s="7" t="str">
+        <v>water-sodium-regulation-foundation-q03</v>
+      </c>
+      <c r="C385" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D385" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E385" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F385" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G385" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H385" s="5" t="inlineStr">
+        <is>
+          <t>身體缺水時，口渴和抗利尿激素（ADH，叫腎臟留水的訊號）主要各做什麼？</t>
+        </is>
+      </c>
+      <c r="I385" s="5" t="inlineStr">
+        <is>
+          <t>口渴幫小管開水門，ADH讓人喝水</t>
+        </is>
+      </c>
+      <c r="J385" s="5" t="inlineStr">
+        <is>
+          <t>口渴讓人喝水，ADH讓小管更難通水</t>
+        </is>
+      </c>
+      <c r="K385" s="5" t="inlineStr">
+        <is>
+          <t>口渴讓人喝水，ADH讓小管更容易通水</t>
+        </is>
+      </c>
+      <c r="L385" s="5" t="inlineStr">
+        <is>
+          <t>口渴讓人喝水，ADH直接促鈉回收</t>
+        </is>
+      </c>
+      <c r="M385" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N385" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O385" s="5" t="inlineStr">
+        <is>
+          <t>因為口渴增加喝進的水，ADH增加腎小管的水回收，所以選「口渴讓人喝水，ADH讓小管更容易通水」。選「口渴幫小管開水門，ADH讓人喝水」的同學，把增加喝水和增加水通透性（水穿過管壁有多容易，叫做水通透性）的工作交換了。</t>
+        </is>
+      </c>
+      <c r="P385" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一個讓水進身體，一個讓水留身體，怎麼配？</t>
+        </is>
+      </c>
+      <c r="Q385" s="5" t="str"/>
+      <c r="R385" s="5" t="inlineStr">
+        <is>
+          <t>答案是「口渴讓人喝水，ADH讓小管更容易通水」，因為口渴促進飲水，ADH增加水通透性（水穿過管壁有多容易，叫做水通透性）。</t>
+        </is>
+      </c>
+      <c r="S385" s="5" t="inlineStr">
+        <is>
+          <t>口渴多喝水，ADH幫留水</t>
+        </is>
+      </c>
+      <c r="T385" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22
+adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U385" s="3" t="str"/>
+      <c r="V385" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W385" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X385" s="3" t="str"/>
+    </row>
+    <row r="386" ht="110" customHeight="1">
+      <c r="A386" s="3" t="str"/>
+      <c r="B386" s="7" t="str">
+        <v>water-sodium-regulation-foundation-q04</v>
+      </c>
+      <c r="C386" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D386" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E386" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F386" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G386" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H386" s="5" t="inlineStr">
+        <is>
+          <t>腎素—血管收縮素—醛固酮系統（RAAS）是一條調血壓的訊號鏈，哪個物質直接讓血管收縮？</t>
+        </is>
+      </c>
+      <c r="I386" s="5" t="inlineStr">
+        <is>
+          <t>腎素</t>
+        </is>
+      </c>
+      <c r="J386" s="5" t="inlineStr">
+        <is>
+          <t>血管收縮素原</t>
+        </is>
+      </c>
+      <c r="K386" s="5" t="inlineStr">
+        <is>
+          <t>尿裡的物質</t>
+        </is>
+      </c>
+      <c r="L386" s="5" t="inlineStr">
+        <is>
+          <t>血管收縮素II</t>
+        </is>
+      </c>
+      <c r="M386" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N386" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O386" s="5" t="inlineStr">
+        <is>
+          <t>因為血管收縮素II直接作用於小動脈，使血管縮緊，所以選「血管收縮素II」。選「腎素」的同學，所選的腎素是先啟動前面轉換的酵素（幫身體進行化學工作的幫手，叫做酵素），不是直接收縮血管的那個物質。</t>
+        </is>
+      </c>
+      <c r="P386" s="5" t="inlineStr">
+        <is>
+          <t>先想想：先啟動接力，和最後直接讓血管收縮，是同一棒嗎？</t>
+        </is>
+      </c>
+      <c r="Q386" s="5" t="str"/>
+      <c r="R386" s="5" t="inlineStr">
+        <is>
+          <t>答案是「血管收縮素II」，因為直接使血管收縮的是血管收縮素II。</t>
+        </is>
+      </c>
+      <c r="S386" s="5" t="inlineStr">
+        <is>
+          <t>腎素先啟動，II讓血管縮</t>
+        </is>
+      </c>
+      <c r="T386" s="3" t="str">
+        <v>renin-angiotensin-aldosterone；physiology/CH05 p.66, physiology/CH05 p.67
+juxtaglomerular-apparatus；physiology/CH09 p.6, physiology/CH09 p.7, anatomy/AB-05_15 p.6, physiology/CH09 p.4</v>
+      </c>
+      <c r="U386" s="3" t="str"/>
+      <c r="V386" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W386" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X386" s="3" t="str"/>
+    </row>
+    <row r="387" ht="110" customHeight="1">
+      <c r="A387" s="3" t="str"/>
+      <c r="B387" s="7" t="str">
+        <v>water-sodium-regulation-foundation-q05</v>
+      </c>
+      <c r="C387" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D387" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E387" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F387" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G387" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H387" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮和抗利尿激素（ADH）都會影響留水，它們最直接的工作怎麼配？</t>
+        </is>
+      </c>
+      <c r="I387" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮促鈉回收，ADH讓水更容易通過</t>
+        </is>
+      </c>
+      <c r="J387" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮直接開水通道，ADH不調整水通過</t>
+        </is>
+      </c>
+      <c r="K387" s="5" t="inlineStr">
+        <is>
+          <t>ADH主要促鈉回收，醛固酮不調整鈉</t>
+        </is>
+      </c>
+      <c r="L387" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮促鈉排出，ADH促水回收</t>
+        </is>
+      </c>
+      <c r="M387" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N387" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O387" s="5" t="inlineStr">
+        <is>
+          <t>因為醛固酮主要促鈉回收，ADH直接讓水更容易穿過管壁（水通透性增加），所以兩個訊號留水的方式不同。選「醛固酮直接開水通道，ADH不調整水通過」的同學，把直接開水通道的工作交給醛固酮了。</t>
+        </is>
+      </c>
+      <c r="P387" s="5" t="inlineStr">
+        <is>
+          <t>先想想：把鈉留下，和替水開門，是同一條直接作用嗎？</t>
+        </is>
+      </c>
+      <c r="Q387" s="5" t="str"/>
+      <c r="R387" s="5" t="inlineStr">
+        <is>
+          <t>答案是「醛固酮促鈉回收，ADH讓水更容易通過」，因為醛固酮促鈉回收，ADH直接增加水通透性（水穿過管壁有多容易，叫做水通透性）。</t>
+        </is>
+      </c>
+      <c r="S387" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮留鈉，ADH開水門</t>
+        </is>
+      </c>
+      <c r="T387" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22
+potassium-secretion；physiology/CH09 p.18, physiology/CH09 p.17, physiology/CH09 p.34, physiology/CH09 p.14
+adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U387" s="3" t="str"/>
+      <c r="V387" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W387" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X387" s="3" t="str"/>
+    </row>
+    <row r="388" ht="110" customHeight="1">
+      <c r="A388" s="3" t="str"/>
+      <c r="B388" s="7" t="str">
+        <v>water-sodium-regulation-foundation-q06</v>
+      </c>
+      <c r="C388" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D388" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E388" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F388" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G388" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H388" s="5" t="inlineStr">
+        <is>
+          <t>想知道鈉在體液裡有多濃，要一起看哪兩個量？</t>
+        </is>
+      </c>
+      <c r="I388" s="5" t="inlineStr">
+        <is>
+          <t>剛才喝水的動作和次數</t>
+        </is>
+      </c>
+      <c r="J388" s="5" t="inlineStr">
+        <is>
+          <t>鈉的量和水的量</t>
+        </is>
+      </c>
+      <c r="K388" s="5" t="inlineStr">
+        <is>
+          <t>鈉的總量，不看水有多少</t>
+        </is>
+      </c>
+      <c r="L388" s="5" t="inlineStr">
+        <is>
+          <t>鈉的總量和鉀的總量</t>
+        </is>
+      </c>
+      <c r="M388" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N388" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O388" s="5" t="inlineStr">
+        <is>
+          <t>因為濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）在比較物質量和水量，所以要把鈉量與水量一起看，選「鈉的量和水的量」。選「鈉的總量，不看水有多少」的同學，漏掉水量，一樣多的鈉配不同水量就可能不一樣濃。</t>
+        </is>
+      </c>
+      <c r="P388" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一樣多的鹽，放在一杯和兩杯水裡會一樣鹹嗎？</t>
+        </is>
+      </c>
+      <c r="Q388" s="5" t="str"/>
+      <c r="R388" s="5" t="inlineStr">
+        <is>
+          <t>答案是「鈉的量和水的量」，因為鈉濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）要由鈉量與水量共同決定。</t>
+        </is>
+      </c>
+      <c r="S388" s="5" t="inlineStr">
+        <is>
+          <t>鈉有多少、水有多少，一起看</t>
+        </is>
+      </c>
+      <c r="T388" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22</v>
+      </c>
+      <c r="U388" s="3" t="str"/>
+      <c r="V388" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W388" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X388" s="3" t="str"/>
+    </row>
+    <row r="389" ht="110" customHeight="1">
+      <c r="A389" s="3" t="str"/>
+      <c r="B389" s="7" t="str">
+        <v>water-sodium-regulation-case-q01</v>
+      </c>
+      <c r="C389" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D389" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E389" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F389" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G389" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H389" s="5" t="inlineStr">
+        <is>
+          <t>一天喝進1500毫升液體、從食物得到800毫升水，身體再產生200毫升代謝水，合計多少？</t>
+        </is>
+      </c>
+      <c r="I389" s="5" t="inlineStr">
+        <is>
+          <t>2300毫升／日</t>
+        </is>
+      </c>
+      <c r="J389" s="5" t="inlineStr">
+        <is>
+          <t>1700毫升／日</t>
+        </is>
+      </c>
+      <c r="K389" s="5" t="inlineStr">
+        <is>
+          <t>2500毫升／日</t>
+        </is>
+      </c>
+      <c r="L389" s="5" t="inlineStr">
+        <is>
+          <t>3300毫升／日</t>
+        </is>
+      </c>
+      <c r="M389" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N389" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O389" s="5" t="inlineStr">
+        <is>
+          <t>因為三種來源都算攝取，所以先算1500加800等於2300，再加200等於2500毫升，選「2500毫升／日」。選「3300毫升／日」的同學，又把800毫升食物水加了一次，變成3300毫升。</t>
+        </is>
+      </c>
+      <c r="P389" s="5" t="inlineStr">
+        <is>
+          <t>先想想：食物裡的800毫升水，應算一次還是兩次？</t>
+        </is>
+      </c>
+      <c r="Q389" s="5" t="str"/>
+      <c r="R389" s="5" t="inlineStr">
+        <is>
+          <t>答案是「2500毫升／日」，因為1500加800再加200等於2500毫升／日。</t>
+        </is>
+      </c>
+      <c r="S389" s="5" t="inlineStr">
+        <is>
+          <t>喝一千五、食八百、代謝兩百</t>
+        </is>
+      </c>
+      <c r="T389" s="3" t="str">
+        <v>water-intake-output；physiology/CH09 p.30, physiology/CH09 p.29</v>
+      </c>
+      <c r="U389" s="3" t="str"/>
+      <c r="V389" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W389" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X389" s="3" t="str"/>
+    </row>
+    <row r="390" ht="110" customHeight="1">
+      <c r="A390" s="3" t="str"/>
+      <c r="B390" s="7" t="str">
+        <v>water-sodium-regulation-case-q02</v>
+      </c>
+      <c r="C390" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D390" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E390" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F390" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G390" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H390" s="5" t="inlineStr">
+        <is>
+          <t>同學寫「沒有流汗，就沒有水從皮膚離開」，應怎麼改才對？</t>
+        </is>
+      </c>
+      <c r="I390" s="5" t="inlineStr">
+        <is>
+          <t>把呼氣帶走的水也刪掉</t>
+        </is>
+      </c>
+      <c r="J390" s="5" t="inlineStr">
+        <is>
+          <t>把糞便帶走的水改算皮膚失水</t>
+        </is>
+      </c>
+      <c r="K390" s="5" t="inlineStr">
+        <is>
+          <t>認為水都從尿排出</t>
+        </is>
+      </c>
+      <c r="L390" s="5" t="inlineStr">
+        <is>
+          <t>加上皮膚看不見的無知覺蒸散</t>
+        </is>
+      </c>
+      <c r="M390" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N390" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O390" s="5" t="inlineStr">
+        <is>
+          <t>因為沒明顯流汗時皮膚仍有看不見的水分散出，所以要保留無知覺蒸散，選「加上皮膚看不見的無知覺蒸散」。選「認為水都從尿排出」的同學，漏掉皮膚、呼氣與糞便等其他排水途徑。</t>
+        </is>
+      </c>
+      <c r="P390" s="5" t="inlineStr">
+        <is>
+          <t>先想想：身體排水，真的只有尿這一條路嗎？</t>
+        </is>
+      </c>
+      <c r="Q390" s="5" t="str"/>
+      <c r="R390" s="5" t="inlineStr">
+        <is>
+          <t>答案是「加上皮膚看不見的無知覺蒸散」，因為無知覺蒸散在沒有明顯流汗時仍可發生。</t>
+        </is>
+      </c>
+      <c r="S390" s="5" t="inlineStr">
+        <is>
+          <t>皮膚會散水，不必先見汗</t>
+        </is>
+      </c>
+      <c r="T390" s="3" t="str">
+        <v>water-intake-output；physiology/CH09 p.30, physiology/CH09 p.29</v>
+      </c>
+      <c r="U390" s="3" t="str"/>
+      <c r="V390" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W390" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X390" s="3" t="str"/>
+    </row>
+    <row r="391" ht="110" customHeight="1">
+      <c r="A391" s="3" t="str"/>
+      <c r="B391" s="7" t="str">
+        <v>water-sodium-regulation-case-q03</v>
+      </c>
+      <c r="C391" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D391" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E391" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F391" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G391" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H391" s="5" t="inlineStr">
+        <is>
+          <t>腎小管後段把更多鈉收回血液，也把更多鉀送進尿，最像哪種激素在作用？</t>
+        </is>
+      </c>
+      <c r="I391" s="5" t="inlineStr">
+        <is>
+          <t>醛固酮</t>
+        </is>
+      </c>
+      <c r="J391" s="5" t="inlineStr">
+        <is>
+          <t>抗利尿激素ADH</t>
+        </is>
+      </c>
+      <c r="K391" s="5" t="inlineStr">
+        <is>
+          <t>心房利鈉尿肽ANP</t>
+        </is>
+      </c>
+      <c r="L391" s="5" t="inlineStr">
+        <is>
+          <t>副甲狀腺素PTH</t>
+        </is>
+      </c>
+      <c r="M391" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N391" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O391" s="5" t="inlineStr">
+        <is>
+          <t>因為醛固酮會增加鈉再吸收與鉀分泌，所以選「醛固酮」。選「抗利尿激素ADH」的同學，所選的ADH主要直接增加水通透性（水穿過管壁有多容易，叫做水通透性），不是這個留鈉又排鉀的組合。</t>
+        </is>
+      </c>
+      <c r="P391" s="5" t="inlineStr">
+        <is>
+          <t>先想想：留鈉和排鉀同時出現，應找哪個訊號？</t>
+        </is>
+      </c>
+      <c r="Q391" s="5" t="str"/>
+      <c r="R391" s="5" t="inlineStr">
+        <is>
+          <t>答案是「醛固酮」，因為鈉回收與鉀分泌一起增加，符合醛固酮作用。</t>
+        </is>
+      </c>
+      <c r="S391" s="5" t="inlineStr">
+        <is>
+          <t>留鈉又排鉀，找醛固酮</t>
+        </is>
+      </c>
+      <c r="T391" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22
+potassium-secretion；physiology/CH09 p.18, physiology/CH09 p.17, physiology/CH09 p.34, physiology/CH09 p.14
+adh-water-reabsorption；physiology/CH09 p.22, physiology/CH09 p.16, physiology/CH09 p.19, physiology/CH09 p.30, physiology/CH09 p.37, physiology/CH09 p.21</v>
+      </c>
+      <c r="U391" s="3" t="str"/>
+      <c r="V391" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W391" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X391" s="3" t="str"/>
+    </row>
+    <row r="392" ht="110" customHeight="1">
+      <c r="A392" s="3" t="str"/>
+      <c r="B392" s="7" t="str">
+        <v>water-sodium-regulation-case-q04</v>
+      </c>
+      <c r="C392" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D392" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E392" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F392" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G392" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H392" s="5" t="inlineStr">
+        <is>
+          <t>腎素和接著轉換的幫手ACE會接力，血管收縮素原會依什麼順序變成血管收縮素II？</t>
+        </is>
+      </c>
+      <c r="I392" s="5" t="inlineStr">
+        <is>
+          <t>先由ACE變成I，再由腎素變成II</t>
+        </is>
+      </c>
+      <c r="J392" s="5" t="inlineStr">
+        <is>
+          <t>先變成I，再經轉換幫手ACE變成II</t>
+        </is>
+      </c>
+      <c r="K392" s="5" t="inlineStr">
+        <is>
+          <t>腎素本身直接變成II</t>
+        </is>
+      </c>
+      <c r="L392" s="5" t="inlineStr">
+        <is>
+          <t>I先變回原，再經ACE變成II</t>
+        </is>
+      </c>
+      <c r="M392" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N392" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O392" s="5" t="inlineStr">
+        <is>
+          <t>因為腎素先把血管收縮素原變成I，再由轉化酵素（幫身體進行化學工作的幫手）ACE把I變成II，所以要依這個順序接力。選「先由ACE變成I，再由腎素變成II」的同學，把兩個幫忙轉換的順序交換了。</t>
+        </is>
+      </c>
+      <c r="P392" s="5" t="inlineStr">
+        <is>
+          <t>先想想：先由腎素起步，再由哪個轉換幫手接手？</t>
+        </is>
+      </c>
+      <c r="Q392" s="5" t="str"/>
+      <c r="R392" s="5" t="inlineStr">
+        <is>
+          <t>答案是「先變成I，再經轉換幫手ACE變成II」，因為先由原變I，再經ACE形成II。</t>
+        </is>
+      </c>
+      <c r="S392" s="5" t="inlineStr">
+        <is>
+          <t>腎素先原變I，ACE再變II</t>
+        </is>
+      </c>
+      <c r="T392" s="3" t="str">
+        <v>renin-angiotensin-aldosterone；physiology/CH05 p.66, physiology/CH05 p.67
+juxtaglomerular-apparatus；physiology/CH09 p.6, physiology/CH09 p.7, anatomy/AB-05_15 p.6, physiology/CH09 p.4</v>
+      </c>
+      <c r="U392" s="3" t="str"/>
+      <c r="V392" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W392" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X392" s="3" t="str"/>
+    </row>
+    <row r="393" ht="110" customHeight="1">
+      <c r="A393" s="3" t="str"/>
+      <c r="B393" s="7" t="str">
+        <v>water-sodium-regulation-case-q05</v>
+      </c>
+      <c r="C393" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D393" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="E393" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F393" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G393" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H393" s="5" t="inlineStr">
+        <is>
+          <t>同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜。同樣多的鈉，現在配上更多水，能直接說它的濃度沒有變嗎？</t>
+        </is>
+      </c>
+      <c r="I393" s="5" t="inlineStr">
+        <is>
+          <t>能，水量不會影響濃度</t>
+        </is>
+      </c>
+      <c r="J393" s="5" t="inlineStr">
+        <is>
+          <t>能，鈉的總量會抵銷水增加的影響</t>
+        </is>
+      </c>
+      <c r="K393" s="5" t="inlineStr">
+        <is>
+          <t>不能，還要把水量的改變算進去</t>
+        </is>
+      </c>
+      <c r="L393" s="5" t="inlineStr">
+        <is>
+          <t>能，濃度只看鈉有幾顆</t>
+        </is>
+      </c>
+      <c r="M393" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N393" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O393" s="5" t="inlineStr">
+        <is>
+          <t>因為同樣的鈉分到更多水裡會比較淡，所以不能說濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）不變，選「不能，還要把水量的改變算進去」。選「能，鈉的總量會抵銷水增加的影響」的同學，把鈉總量沒變當成能抵銷水量增加，少看了鈉和水的比例。</t>
+        </is>
+      </c>
+      <c r="P393" s="5" t="inlineStr">
+        <is>
+          <t>先想想：同樣多的鹽，加更多水後會一樣鹹嗎？</t>
+        </is>
+      </c>
+      <c r="Q393" s="5" t="str"/>
+      <c r="R393" s="5" t="inlineStr">
+        <is>
+          <t>答案是「不能，還要把水量的改變算進去」，因為鈉量相同而水量增加時，濃度（同樣多的水裡裝了多少物質，叫做濃度，就像糖水有多甜）會改變。</t>
+        </is>
+      </c>
+      <c r="S393" s="5" t="inlineStr">
+        <is>
+          <t>鈉量相同，水變多就變淡</t>
+        </is>
+      </c>
+      <c r="T393" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22</v>
+      </c>
+      <c r="U393" s="3" t="str"/>
+      <c r="V393" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="W393" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/water-sodium-regulation-v1/index.html</v>
+      </c>
+      <c r="X393" s="3" t="str"/>
+    </row>
+    <row r="394" ht="110" customHeight="1">
+      <c r="A394" s="3" t="str"/>
+      <c r="B394" s="7" t="str">
+        <v>electrolyte-balance-foundation-q01</v>
+      </c>
+      <c r="C394" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F394" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G394" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H394" s="5" t="inlineStr">
+        <is>
+          <t>一顆氯化鎂（MgCl₂）放進水裡，拆成一顆鎂離子（Mg²⁺）和兩顆氯離子（Cl⁻），最後共幾顆小粒子？</t>
+        </is>
+      </c>
+      <c r="I394" s="5" t="inlineStr">
+        <is>
+          <t>3顆</t>
+        </is>
+      </c>
+      <c r="J394" s="5" t="inlineStr">
+        <is>
+          <t>1顆</t>
+        </is>
+      </c>
+      <c r="K394" s="5" t="inlineStr">
+        <is>
+          <t>2顆</t>
+        </is>
+      </c>
+      <c r="L394" s="5" t="inlineStr">
+        <is>
+          <t>4顆</t>
+        </is>
+      </c>
+      <c r="M394" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N394" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O394" s="5" t="inlineStr">
+        <is>
+          <t>因為一顆鎂離子加兩顆氯離子，所以1加2等於3顆。選「2顆」的同學，是把鎂帶的「2份電」當成了顆數。</t>
+        </is>
+      </c>
+      <c r="P394" s="5" t="inlineStr">
+        <is>
+          <t>先想想：要數拆開後有幾顆，還是只看鎂帶幾份電？</t>
+        </is>
+      </c>
+      <c r="Q394" s="5" t="str"/>
+      <c r="R394" s="5" t="inlineStr">
+        <is>
+          <t>答案是「3顆」，因為1顆鎂加2顆氯，共3顆粒子。</t>
+        </is>
+      </c>
+      <c r="S394" s="5" t="inlineStr">
+        <is>
+          <t>一鎂加兩氯，一加二等三</t>
+        </is>
+      </c>
+      <c r="T394" s="3" t="str">
+        <v>electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U394" s="3" t="str"/>
+      <c r="V394" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W394" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X394" s="3" t="str"/>
+    </row>
+    <row r="395" ht="110" customHeight="1">
+      <c r="A395" s="3" t="str"/>
+      <c r="B395" s="7" t="str">
+        <v>electrolyte-balance-foundation-q02</v>
+      </c>
+      <c r="C395" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F395" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G395" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H395" s="5" t="inlineStr">
+        <is>
+          <t>兩邊隔著一層只讓水通過、不讓裡面物質通過的膜，水整體會往哪一邊移？</t>
+        </is>
+      </c>
+      <c r="I395" s="5" t="inlineStr">
+        <is>
+          <t>不管膜能讓什麼通過，水方向都一樣</t>
+        </is>
+      </c>
+      <c r="J395" s="5" t="inlineStr">
+        <is>
+          <t>往小粒子比較多的那邊</t>
+        </is>
+      </c>
+      <c r="K395" s="5" t="inlineStr">
+        <is>
+          <t>往小粒子比較少的那邊</t>
+        </is>
+      </c>
+      <c r="L395" s="5" t="inlineStr">
+        <is>
+          <t>停在原處，不移動</t>
+        </is>
+      </c>
+      <c r="M395" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N395" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O395" s="5" t="inlineStr">
+        <is>
+          <t>因為這個模型只讓水過膜，而水會往小粒子較多的一邊移，所以選「往小粒子比較多的那邊」。選「往小粒子比較少的那邊」的同學，把水移動的方向寫反了。</t>
+        </is>
+      </c>
+      <c r="P395" s="5" t="inlineStr">
+        <is>
+          <t>先想想：像糖水一濃一淡，水會往物質多還是少的一邊跑？</t>
+        </is>
+      </c>
+      <c r="Q395" s="5" t="str"/>
+      <c r="R395" s="5" t="inlineStr">
+        <is>
+          <t>答案是「往小粒子比較多的那邊」，因為只通水的膜模型中，水淨移向粒子較多側。</t>
+        </is>
+      </c>
+      <c r="S395" s="5" t="inlineStr">
+        <is>
+          <t>只通水時，水往粒子多處移</t>
+        </is>
+      </c>
+      <c r="T395" s="3" t="str">
+        <v>electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U395" s="3" t="str"/>
+      <c r="V395" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W395" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X395" s="3" t="str"/>
+    </row>
+    <row r="396" ht="110" customHeight="1">
+      <c r="A396" s="3" t="str"/>
+      <c r="B396" s="7" t="str">
+        <v>electrolyte-balance-foundation-q03</v>
+      </c>
+      <c r="C396" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D396" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F396" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G396" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H396" s="5" t="inlineStr">
+        <is>
+          <t>mEq/L是每公升的毫當量，會把小粒子帶的電也算進去，它和「拆開後有幾顆粒子」有什麼不同？</t>
+        </is>
+      </c>
+      <c r="I396" s="5" t="inlineStr">
+        <is>
+          <t>算電看粒子顆數，算顆數看帶電份數</t>
+        </is>
+      </c>
+      <c r="J396" s="5" t="inlineStr">
+        <is>
+          <t>兩者都只數還沒拆開的整顆物質</t>
+        </is>
+      </c>
+      <c r="K396" s="5" t="inlineStr">
+        <is>
+          <t>算電的量要看帶幾份電，粒子顆數另外數</t>
+        </is>
+      </c>
+      <c r="L396" s="5" t="inlineStr">
+        <is>
+          <t>帶幾份電，就拆成幾顆粒子</t>
+        </is>
+      </c>
+      <c r="M396" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N396" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O396" s="5" t="inlineStr">
+        <is>
+          <t>因為毫當量要考慮每顆離子帶幾份電，而粒子數是在數顆數，所以選「算電的量要看帶幾份電，粒子顆數另外數」。選「帶幾份電，就拆成幾顆粒子」的同學，把帶電的份數直接當成拆開後的顆數。</t>
+        </is>
+      </c>
+      <c r="P396" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一顆帶兩份電，和拆成兩顆，是同一件事嗎？</t>
+        </is>
+      </c>
+      <c r="Q396" s="5" t="str"/>
+      <c r="R396" s="5" t="inlineStr">
+        <is>
+          <t>答案是「算電的量要看帶幾份電，粒子顆數另外數」，因為電荷當量涉及價數（一顆帶電小粒子帶幾份電，叫做價數），解離（一整顆物質放進水裡拆成幾顆帶電小粒子，叫做解離）後粒子顆數須另數。</t>
+        </is>
+      </c>
+      <c r="S396" s="5" t="inlineStr">
+        <is>
+          <t>電看幾份，粒子看幾顆</t>
+        </is>
+      </c>
+      <c r="T396" s="3" t="str">
+        <v>electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U396" s="3" t="str"/>
+      <c r="V396" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W396" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X396" s="3" t="str"/>
+    </row>
+    <row r="397" ht="110" customHeight="1">
+      <c r="A397" s="3" t="str"/>
+      <c r="B397" s="7" t="str">
+        <v>electrolyte-balance-foundation-q04</v>
+      </c>
+      <c r="C397" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F397" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G397" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H397" s="5" t="inlineStr">
+        <is>
+          <t>鈉離子（Na⁺）和鉀離子（K⁺）是體液中的帶電小粒子，哪一種在細胞外比較多，哪一種在細胞內比較多？</t>
+        </is>
+      </c>
+      <c r="I397" s="5" t="inlineStr">
+        <is>
+          <t>鈉和鉀都主要在細胞外</t>
+        </is>
+      </c>
+      <c r="J397" s="5" t="inlineStr">
+        <is>
+          <t>鈉和鉀都主要在細胞內</t>
+        </is>
+      </c>
+      <c r="K397" s="5" t="inlineStr">
+        <is>
+          <t>鈉主要在細胞內，鉀主要在細胞外</t>
+        </is>
+      </c>
+      <c r="L397" s="5" t="inlineStr">
+        <is>
+          <t>鈉主要在細胞外，鉀主要在細胞內</t>
+        </is>
+      </c>
+      <c r="M397" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N397" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O397" s="5" t="inlineStr">
+        <is>
+          <t>因為鈉是細胞外主要陽離子（帶正電的小粒子叫陽離子），鉀是細胞內主要陽離子，所以選「鈉主要在細胞外，鉀主要在細胞內」。選「鈉主要在細胞內，鉀主要在細胞外」的同學，把主要分布的位置交換了。</t>
+        </is>
+      </c>
+      <c r="P397" s="5" t="inlineStr">
+        <is>
+          <t>先想想：細胞外最多的正電小粒子是鈉，還是鉀？</t>
+        </is>
+      </c>
+      <c r="Q397" s="5" t="str"/>
+      <c r="R397" s="5" t="inlineStr">
+        <is>
+          <t>答案是「鈉主要在細胞外，鉀主要在細胞內」，因為鈉主要在細胞外，鉀主要在細胞內。</t>
+        </is>
+      </c>
+      <c r="S397" s="5" t="inlineStr">
+        <is>
+          <t>鈉在外，鉀在內</t>
+        </is>
+      </c>
+      <c r="T397" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22
+potassium-secretion；physiology/CH09 p.18, physiology/CH09 p.17, physiology/CH09 p.34, physiology/CH09 p.14
+electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U397" s="3" t="str"/>
+      <c r="V397" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W397" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X397" s="3" t="str"/>
+    </row>
+    <row r="398" ht="110" customHeight="1">
+      <c r="A398" s="3" t="str"/>
+      <c r="B398" s="7" t="str">
+        <v>electrolyte-balance-foundation-q05</v>
+      </c>
+      <c r="C398" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D398" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F398" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G398" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H398" s="5" t="inlineStr">
+        <is>
+          <t>副甲狀腺素（PTH，一種調整鈣磷的激素）在腎臟作用時，會把鈣和磷往哪裡送？</t>
+        </is>
+      </c>
+      <c r="I398" s="5" t="inlineStr">
+        <is>
+          <t>把更多鈣收回血液，把更多磷排進尿</t>
+        </is>
+      </c>
+      <c r="J398" s="5" t="inlineStr">
+        <is>
+          <t>把更多鈣和磷都收回血液</t>
+        </is>
+      </c>
+      <c r="K398" s="5" t="inlineStr">
+        <is>
+          <t>把更多鈣和磷都排進尿</t>
+        </is>
+      </c>
+      <c r="L398" s="5" t="inlineStr">
+        <is>
+          <t>把更多鈣排進尿，把更多磷收回血液</t>
+        </is>
+      </c>
+      <c r="M398" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N398" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O398" s="5" t="inlineStr">
+        <is>
+          <t>因為PTH在腎臟促進回收鈣、排出磷，所以選「把更多鈣收回血液，把更多磷排進尿」。選「把更多鈣和磷都收回血液」的同學，把腎臟對磷的作用也寫成回收，方向錯了。</t>
+        </is>
+      </c>
+      <c r="P398" s="5" t="inlineStr">
+        <is>
+          <t>先想想：這個訊號是把鈣和磷都留下，還是一留一排？</t>
+        </is>
+      </c>
+      <c r="Q398" s="5" t="str"/>
+      <c r="R398" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把更多鈣收回血液，把更多磷排進尿」，因為PTH在腎端增加鈣再吸收與磷排泄。</t>
+        </is>
+      </c>
+      <c r="S398" s="5" t="inlineStr">
+        <is>
+          <t>PTH在腎臟，留鈣排磷</t>
+        </is>
+      </c>
+      <c r="T398" s="3" t="str">
+        <v>chloride-balance；physiology/CH09 p.34, physiology/CH09 p.16
+calcium-phosphate-balance；physiology/CH09 p.35, physiology/CH09 p.16</v>
+      </c>
+      <c r="U398" s="3" t="str"/>
+      <c r="V398" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W398" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X398" s="3" t="str"/>
+    </row>
+    <row r="399" ht="110" customHeight="1">
+      <c r="A399" s="3" t="str"/>
+      <c r="B399" s="7" t="str">
+        <v>electrolyte-balance-foundation-q06</v>
+      </c>
+      <c r="C399" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D399" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F399" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G399" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H399" s="5" t="inlineStr">
+        <is>
+          <t>鎂離子（Mg²⁺）是一種帶電小粒子，它會幫身體做什麼？</t>
+        </is>
+      </c>
+      <c r="I399" s="5" t="inlineStr">
+        <is>
+          <t>是細胞外最多的正電粒子</t>
+        </is>
+      </c>
+      <c r="J399" s="5" t="inlineStr">
+        <is>
+          <t>參與酵素（幫身體進行化學工作的幫手，叫做酵素）工作與神經肌肉功能</t>
+        </is>
+      </c>
+      <c r="K399" s="5" t="inlineStr">
+        <is>
+          <t>降低幫忙代謝的酵素（幫身體進行化學工作的幫手，叫做酵素）活性</t>
+        </is>
+      </c>
+      <c r="L399" s="5" t="inlineStr">
+        <is>
+          <t>血鎂變低時，讓神經肌肉更不容易被刺激</t>
+        </is>
+      </c>
+      <c r="M399" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N399" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O399" s="5" t="inlineStr">
+        <is>
+          <t>因為鎂會幫忙活化酵素，也參與神經肌肉功能，所以選「參與酵素工作與神經肌肉功能」。選「血鎂變低時，讓神經肌肉更不容易被刺激」的同學，把低血鎂時比較容易被刺激（興奮性增加）的方向說反了。</t>
+        </is>
+      </c>
+      <c r="P399" s="5" t="inlineStr">
+        <is>
+          <t>先想想：鎂會幫細胞內的酵素工作，還是沒有作用？</t>
+        </is>
+      </c>
+      <c r="Q399" s="5" t="str"/>
+      <c r="R399" s="5" t="inlineStr">
+        <is>
+          <t>答案是「參與酵素（幫身體進行化學工作的幫手，叫做酵素）工作與神經肌肉功能」，因為鎂參與酵素（幫身體進行化學工作的幫手，叫做酵素）活性與神經肌肉功能。</t>
+        </is>
+      </c>
+      <c r="S399" s="5" t="inlineStr">
+        <is>
+          <t>鎂幫酵素，也關神經肌肉</t>
+        </is>
+      </c>
+      <c r="T399" s="3" t="str">
+        <v>magnesium-balance；physiology/CH09 p.35, physiology/CH09 p.36</v>
+      </c>
+      <c r="U399" s="3" t="str"/>
+      <c r="V399" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W399" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X399" s="3" t="str"/>
+    </row>
+    <row r="400" ht="110" customHeight="1">
+      <c r="A400" s="3" t="str"/>
+      <c r="B400" s="7" t="str">
+        <v>electrolyte-balance-case-q01</v>
+      </c>
+      <c r="C400" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D400" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F400" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G400" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H400" s="5" t="inlineStr">
+        <is>
+          <t>把同樣顆數的葡萄糖和氯化鈉（NaCl，一種鹽）放進水裡，想比較最後小粒子有幾顆，要先注意什麼？</t>
+        </is>
+      </c>
+      <c r="I400" s="5" t="inlineStr">
+        <is>
+          <t>只數鈉，不數拆出來的氯</t>
+        </is>
+      </c>
+      <c r="J400" s="5" t="inlineStr">
+        <is>
+          <t>把葡萄糖和氯化鈉都當成不會拆開</t>
+        </is>
+      </c>
+      <c r="K400" s="5" t="inlineStr">
+        <is>
+          <t>確認氯化鈉拆開，鈉和氯兩種都要數</t>
+        </is>
+      </c>
+      <c r="L400" s="5" t="inlineStr">
+        <is>
+          <t>只比較每種物質看起來有多大</t>
+        </is>
+      </c>
+      <c r="M400" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N400" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O400" s="5" t="inlineStr">
+        <is>
+          <t>因為葡萄糖不拆開，氯化鈉拆成鈉和氯兩種粒子，所以兩種都要數，選「確認氯化鈉拆開，鈉和氯兩種都要數」。選「只數鈉，不數拆出來的氯」的同學，少算了氯離子，會把兩顆當成一顆。</t>
+        </is>
+      </c>
+      <c r="P400" s="5" t="inlineStr">
+        <is>
+          <t>先想想：一份鹽拆出鈉和氯，兩種是不是都該算？</t>
+        </is>
+      </c>
+      <c r="Q400" s="5" t="str"/>
+      <c r="R400" s="5" t="inlineStr">
+        <is>
+          <t>答案是「確認氯化鈉拆開，鈉和氯兩種都要數」，因為氯化鈉拆開後，鈉與氯兩種粒子都要數。</t>
+        </is>
+      </c>
+      <c r="S400" s="5" t="inlineStr">
+        <is>
+          <t>糖一顆不拆，鹽拆鈉加氯</t>
+        </is>
+      </c>
+      <c r="T400" s="3" t="str">
+        <v>electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U400" s="3" t="str"/>
+      <c r="V400" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W400" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X400" s="3" t="str"/>
+    </row>
+    <row r="401" ht="110" customHeight="1">
+      <c r="A401" s="3" t="str"/>
+      <c r="B401" s="7" t="str">
+        <v>electrolyte-balance-case-q02</v>
+      </c>
+      <c r="C401" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F401" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G401" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H401" s="5" t="inlineStr">
+        <is>
+          <t>鎂離子（Mg²⁺）的「2+」表示帶兩份正電，同學因此說一顆氯化鎂（MgCl₂）拆開只有兩顆粒子，他錯在哪裡？</t>
+        </is>
+      </c>
+      <c r="I401" s="5" t="inlineStr">
+        <is>
+          <t>應該數鎂的兩份正電，就算兩顆</t>
+        </is>
+      </c>
+      <c r="J401" s="5" t="inlineStr">
+        <is>
+          <t>應該把氯離子省略不算</t>
+        </is>
+      </c>
+      <c r="K401" s="5" t="inlineStr">
+        <is>
+          <t>應該把氯化鎂當成沒拆開的一顆</t>
+        </is>
+      </c>
+      <c r="L401" s="5" t="inlineStr">
+        <is>
+          <t>把帶電的份數，當成拆開後的顆數</t>
+        </is>
+      </c>
+      <c r="M401" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N401" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O401" s="5" t="inlineStr">
+        <is>
+          <t>因為一顆MgCl₂拆成一顆鎂離子和兩顆氯離子，所以共三顆，「把帶電的份數，當成拆開後的顆數」才說中錯誤。選「應該數鎂的兩份正電，就算兩顆」的同學，仍在數電的份數，沒有把拆出的三顆粒子數清楚。</t>
+        </is>
+      </c>
+      <c r="P401" s="5" t="inlineStr">
+        <is>
+          <t>先想想：鎂上的2+是在說帶電，還是在數拆出幾顆？</t>
+        </is>
+      </c>
+      <c r="Q401" s="5" t="str"/>
+      <c r="R401" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把帶電的份數，當成拆開後的顆數」，因為價數（一顆帶電小粒子帶幾份電，叫做價數）是電荷份數，不是解離（一整顆物質放進水裡拆成幾顆帶電小粒子，叫做解離）後粒子總數。</t>
+        </is>
+      </c>
+      <c r="S401" s="5" t="inlineStr">
+        <is>
+          <t>鎂二價是帶電，拆鹽要數三顆</t>
+        </is>
+      </c>
+      <c r="T401" s="3" t="str">
+        <v>electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U401" s="3" t="str"/>
+      <c r="V401" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W401" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X401" s="3" t="str"/>
+    </row>
+    <row r="402" ht="110" customHeight="1">
+      <c r="A402" s="3" t="str"/>
+      <c r="B402" s="7" t="str">
+        <v>electrolyte-balance-case-q03</v>
+      </c>
+      <c r="C402" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D402" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F402" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G402" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H402" s="5" t="inlineStr">
+        <is>
+          <t>兩邊的物質多少不同，想用「水往物質較多側移動」來想水流方向，先要確定膜有什麼特性？</t>
+        </is>
+      </c>
+      <c r="I402" s="5" t="inlineStr">
+        <is>
+          <t>讓水通過，卻不讓溶質（溶在水裡的物質，叫做溶質）通過</t>
+        </is>
+      </c>
+      <c r="J402" s="5" t="inlineStr">
+        <is>
+          <t>讓溶質（溶在水裡的物質，叫做溶質）都能自由穿過</t>
+        </is>
+      </c>
+      <c r="K402" s="5" t="inlineStr">
+        <is>
+          <t>只要知道離子帶幾份電即可</t>
+        </is>
+      </c>
+      <c r="L402" s="5" t="inlineStr">
+        <is>
+          <t>不必知道膜能讓什麼通過</t>
+        </is>
+      </c>
+      <c r="M402" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N402" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O402" s="5" t="inlineStr">
+        <is>
+          <t>因為這個水移動模型先假定膜能通水、不能通溶質（溶在水裡的物質，叫做溶質），所以選「讓水通過，卻不讓溶質通過」。選「讓溶質都能自由穿過」的同學，把物質也能自由通過的情況帶進來，已經換了條件。</t>
+        </is>
+      </c>
+      <c r="P402" s="5" t="inlineStr">
+        <is>
+          <t>先想想：水能不能過、物質能不能過，要不要先分清楚？</t>
+        </is>
+      </c>
+      <c r="Q402" s="5" t="str"/>
+      <c r="R402" s="5" t="inlineStr">
+        <is>
+          <t>答案是「讓水通過，卻不讓溶質（溶在水裡的物質，叫做溶質）通過」，因為先確定膜可通水且不通溶質（溶在水裡的物質，叫做溶質），才能套用此模型。</t>
+        </is>
+      </c>
+      <c r="S402" s="5" t="inlineStr">
+        <is>
+          <t>先看膜讓誰過，再想水往哪移</t>
+        </is>
+      </c>
+      <c r="T402" s="3" t="str">
+        <v>electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U402" s="3" t="str"/>
+      <c r="V402" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W402" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X402" s="3" t="str"/>
+    </row>
+    <row r="403" ht="110" customHeight="1">
+      <c r="A403" s="3" t="str"/>
+      <c r="B403" s="7" t="str">
+        <v>electrolyte-balance-case-q04</v>
+      </c>
+      <c r="C403" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F403" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G403" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H403" s="5" t="inlineStr">
+        <is>
+          <t>鈉鉀在細胞內外的分布，和鉀從血液送進小管的「分泌」，應怎麼分清楚？</t>
+        </is>
+      </c>
+      <c r="I403" s="5" t="inlineStr">
+        <is>
+          <t>鉀分泌就是鉀從管液回到血液</t>
+        </is>
+      </c>
+      <c r="J403" s="5" t="inlineStr">
+        <is>
+          <t>先看是在比較細胞內外，還是在說血到管液</t>
+        </is>
+      </c>
+      <c r="K403" s="5" t="inlineStr">
+        <is>
+          <t>細胞外液就是腎小管裡的尿</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>細胞內液就是血管裡的血漿</t>
+        </is>
+      </c>
+      <c r="M403" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N403" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O403" s="5" t="inlineStr">
+        <is>
+          <t>因為細胞內外是按細胞膜分區，分泌則是從血送進管液，所以選「先看是在比較細胞內外，還是在說血到管液」。選「鉀分泌就是鉀從管液回到血液」的同學，把分泌寫成反方向的再吸收了。</t>
+        </is>
+      </c>
+      <c r="P403" s="5" t="inlineStr">
+        <is>
+          <t>先想想：細胞膜內外，和血液到小管，是同一組位置嗎？</t>
+        </is>
+      </c>
+      <c r="Q403" s="5" t="str"/>
+      <c r="R403" s="5" t="inlineStr">
+        <is>
+          <t>答案是「先看是在比較細胞內外，還是在說血到管液」，因為細胞內外分布與血液到管液的分泌方向要分開看。</t>
+        </is>
+      </c>
+      <c r="S403" s="5" t="inlineStr">
+        <is>
+          <t>先分細胞內外，再看血到管液</t>
+        </is>
+      </c>
+      <c r="T403" s="3" t="str">
+        <v>sodium-water-balance；physiology/CH09 p.37, physiology/CH09 p.34, physiology/CH09 p.30, physiology/CH09 p.16, physiology/CH09 p.22
+potassium-secretion；physiology/CH09 p.18, physiology/CH09 p.17, physiology/CH09 p.34, physiology/CH09 p.14
+electrolyte-osmolarity；physiology/CH09 p.32, physiology/CH09 p.31, physiology/CH09 p.33</v>
+      </c>
+      <c r="U403" s="3" t="str"/>
+      <c r="V403" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W403" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X403" s="3" t="str"/>
+    </row>
+    <row r="404" ht="110" customHeight="1">
+      <c r="A404" s="3" t="str"/>
+      <c r="B404" s="7" t="str">
+        <v>electrolyte-balance-case-q05</v>
+      </c>
+      <c r="C404" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D404" s="5" t="inlineStr">
+        <is>
+          <t>電解質滲透與離子平衡</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F404" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G404" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H404" s="5" t="inlineStr">
+        <is>
+          <t>已知氯離子（Cl⁻）是細胞外主要陰離子，也就是外液裡較多的負電小粒子，再配上副甲狀腺素（PTH，調整鈣與磷的激素）的腎臟作用，哪一組正確？</t>
+        </is>
+      </c>
+      <c r="I404" s="5" t="inlineStr">
+        <is>
+          <t>氯主要在細胞外；PTH留鈣、排磷</t>
+        </is>
+      </c>
+      <c r="J404" s="5" t="inlineStr">
+        <is>
+          <t>氯主要在細胞內；PTH留鈣、排磷</t>
+        </is>
+      </c>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>氯主要在細胞外；PTH排鈣、留磷</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="inlineStr">
+        <is>
+          <t>氯主要在細胞外；PTH留鈣、也留磷</t>
+        </is>
+      </c>
+      <c r="M404" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N404" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O404" s="5" t="inlineStr">
+        <is>
+          <t>因為副甲狀腺素PTH在腎臟幫忙回收鈣、排出磷，所以配上題目已給的氯分布，選「氯主要在細胞外；PTH留鈣、排磷」。選「氯主要在細胞內；PTH留鈣、排磷」的同學，把已知的細胞外改成細胞內了。</t>
+        </is>
+      </c>
+      <c r="P404" s="5" t="inlineStr">
+        <is>
+          <t>先想想：題目已說氯在外面，鈣和磷又各該留下還是排掉？</t>
+        </is>
+      </c>
+      <c r="Q404" s="5" t="str"/>
+      <c r="R404" s="5" t="inlineStr">
+        <is>
+          <t>答案是「氯主要在細胞外；PTH留鈣、排磷」，因為氯是細胞外主要陰離子（帶負電的小粒子叫陰離子），PTH在腎端回鈣排磷。</t>
+        </is>
+      </c>
+      <c r="S404" s="5" t="inlineStr">
+        <is>
+          <t>氯在外帶負電，腎端留鈣排磷</t>
+        </is>
+      </c>
+      <c r="T404" s="3" t="str">
+        <v>chloride-balance；physiology/CH09 p.34, physiology/CH09 p.16
+calcium-phosphate-balance；physiology/CH09 p.35, physiology/CH09 p.16</v>
+      </c>
+      <c r="U404" s="3" t="str"/>
+      <c r="V404" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="W404" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/electrolyte-balance-v1/index.html</v>
+      </c>
+      <c r="X404" s="3" t="str"/>
+    </row>
+    <row r="405" ht="110" customHeight="1">
+      <c r="A405" s="3" t="str"/>
+      <c r="B405" s="7" t="str">
+        <v>acid-base-homeostasis-foundation-q01</v>
+      </c>
+      <c r="C405" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D405" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E405" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F405" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G405" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H405" s="5" t="inlineStr">
+        <is>
+          <t>身體用哪三組工作一起讓血液不要太酸、也不要太鹼？</t>
+        </is>
+      </c>
+      <c r="I405" s="5" t="inlineStr">
+        <is>
+          <t>化學緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）、肺、腎</t>
+        </is>
+      </c>
+      <c r="J405" s="5" t="inlineStr">
+        <is>
+          <t>化學緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）這一組就夠</t>
+        </is>
+      </c>
+      <c r="K405" s="5" t="inlineStr">
+        <is>
+          <t>化學緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）、肺、膀胱</t>
+        </is>
+      </c>
+      <c r="L405" s="5" t="inlineStr">
+        <is>
+          <t>化學緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）、肝、腎</t>
+        </is>
+      </c>
+      <c r="M405" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N405" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O405" s="5" t="inlineStr">
+        <is>
+          <t>因為緩衝先接住酸，肺和腎再調整酸的去路，所以選「化學緩衝、肺、腎」。選「化學緩衝、肺、膀胱」的同學，把儲存尿的膀胱當成腎臟，換掉了真正調整排酸的角色。</t>
+        </is>
+      </c>
+      <c r="P405" s="5" t="inlineStr">
+        <is>
+          <t>先想想：先接住酸以後，還需要哪兩個器官接手？</t>
+        </is>
+      </c>
+      <c r="Q405" s="5" t="str"/>
+      <c r="R405" s="5" t="inlineStr">
+        <is>
+          <t>答案是「化學緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）、肺、腎」，因為三套酸鹼調節系統是化學緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）、肺與腎。</t>
+        </is>
+      </c>
+      <c r="S405" s="5" t="inlineStr">
+        <is>
+          <t>緩衝先接，肺腎再調整</t>
+        </is>
+      </c>
+      <c r="T405" s="3" t="str">
+        <v>acid-base-balance；physiology/CH09 p.37, physiology/CH09 p.38, physiology/CH09 p.40, physiology/CH09 p.41, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U405" s="3" t="str"/>
+      <c r="V405" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W405" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X405" s="3" t="str"/>
+    </row>
+    <row r="406" ht="110" customHeight="1">
+      <c r="A406" s="3" t="str"/>
+      <c r="B406" s="7" t="str">
+        <v>acid-base-homeostasis-foundation-q02</v>
+      </c>
+      <c r="C406" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D406" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E406" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F406" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G406" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H406" s="5" t="inlineStr">
+        <is>
+          <t>先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝。酸不酸的數字叫pH，數字越小越酸。在碳酸緩衝公式裡，會接酸的碳酸氫根（HCO₃⁻）當作鹼，碳酸（H₂CO₃）當作酸，算pH時，上面的分子與下面的分母要怎麼放？</t>
+        </is>
+      </c>
+      <c r="I406" s="5" t="inlineStr">
+        <is>
+          <t>上面放鹼加酸，下面放酸</t>
+        </is>
+      </c>
+      <c r="J406" s="5" t="inlineStr">
+        <is>
+          <t>上面放鹼，下面放酸</t>
+        </is>
+      </c>
+      <c r="K406" s="5" t="inlineStr">
+        <is>
+          <t>上面放酸，下面放鹼</t>
+        </is>
+      </c>
+      <c r="L406" s="5" t="inlineStr">
+        <is>
+          <t>上面放鹼減酸，下面放酸</t>
+        </is>
+      </c>
+      <c r="M406" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N406" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O406" s="5" t="inlineStr">
+        <is>
+          <t>因為公式用鹼的量除以酸的量，所以碳酸氫根放上面、碳酸放下面，選「上面放鹼，下面放酸」。選「上面放酸，下面放鹼」的同學，把除法的上下兩個量交換了。</t>
+        </is>
+      </c>
+      <c r="P406" s="5" t="inlineStr">
+        <is>
+          <t>先想想：公式是在算鹼除以酸，還是酸除以鹼？</t>
+        </is>
+      </c>
+      <c r="Q406" s="5" t="str"/>
+      <c r="R406" s="5" t="inlineStr">
+        <is>
+          <t>答案是「上面放鹼，下面放酸」，因為HCO₃⁻是上面的鹼，H₂CO₃是下面的酸。</t>
+        </is>
+      </c>
+      <c r="S406" s="5" t="inlineStr">
+        <is>
+          <t>上面放鹼，下面放酸</t>
+        </is>
+      </c>
+      <c r="T406" s="3" t="str">
+        <v>acid-base-balance；physiology/CH09 p.37, physiology/CH09 p.38, physiology/CH09 p.40, physiology/CH09 p.41, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U406" s="3" t="str"/>
+      <c r="V406" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W406" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X406" s="3" t="str"/>
+    </row>
+    <row r="407" ht="110" customHeight="1">
+      <c r="A407" s="3" t="str"/>
+      <c r="B407" s="7" t="str">
+        <v>acid-base-homeostasis-foundation-q03</v>
+      </c>
+      <c r="C407" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D407" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F407" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G407" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H407" s="5" t="inlineStr">
+        <is>
+          <t>能幫忙接住酸的血紅素，主要在哪裡工作？</t>
+        </is>
+      </c>
+      <c r="I407" s="5" t="inlineStr">
+        <is>
+          <t>尿液裡</t>
+        </is>
+      </c>
+      <c r="J407" s="5" t="inlineStr">
+        <is>
+          <t>呼出去的氣體裡</t>
+        </is>
+      </c>
+      <c r="K407" s="5" t="inlineStr">
+        <is>
+          <t>紅血球裡</t>
+        </is>
+      </c>
+      <c r="L407" s="5" t="inlineStr">
+        <is>
+          <t>血漿裡自由漂著</t>
+        </is>
+      </c>
+      <c r="M407" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N407" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O407" s="5" t="inlineStr">
+        <is>
+          <t>因為血紅素在紅血球裡參與緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝），所以選「紅血球裡」。選「血漿裡自由漂著」的同學，把血紅素的主要位置換成了血漿。</t>
+        </is>
+      </c>
+      <c r="P407" s="5" t="inlineStr">
+        <is>
+          <t>先想想：血紅素的名字和哪一種血球有關？</t>
+        </is>
+      </c>
+      <c r="Q407" s="5" t="str"/>
+      <c r="R407" s="5" t="inlineStr">
+        <is>
+          <t>答案是「紅血球裡」，因為血紅素緩衝（先接住多出來的酸，讓酸不酸的數字別亂跳，叫做緩衝）的主要位置在紅血球內。</t>
+        </is>
+      </c>
+      <c r="S407" s="5" t="inlineStr">
+        <is>
+          <t>血紅素在紅血球裡接酸</t>
+        </is>
+      </c>
+      <c r="T407" s="3" t="str">
+        <v>buffer-systems；physiology/CH09 p.38, physiology/CH09 p.39, physiology/CH09 p.40, physiology/CH09 p.42</v>
+      </c>
+      <c r="U407" s="3" t="str"/>
+      <c r="V407" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W407" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X407" s="3" t="str"/>
+    </row>
+    <row r="408" ht="110" customHeight="1">
+      <c r="A408" s="3" t="str"/>
+      <c r="B408" s="7" t="str">
+        <v>acid-base-homeostasis-foundation-q04</v>
+      </c>
+      <c r="C408" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D408" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F408" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G408" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H408" s="5" t="inlineStr">
+        <is>
+          <t>酸不酸的數字叫pH，數字越小越酸。其他條件先不變，呼吸加快、呼出更多二氧化碳（CO₂）時，血液的pH會往哪個方向變？</t>
+        </is>
+      </c>
+      <c r="I408" s="5" t="inlineStr">
+        <is>
+          <t>pH變小，血液更酸</t>
+        </is>
+      </c>
+      <c r="J408" s="5" t="inlineStr">
+        <is>
+          <t>pH不改變</t>
+        </is>
+      </c>
+      <c r="K408" s="5" t="inlineStr">
+        <is>
+          <t>pH變大，但血液的酸增加</t>
+        </is>
+      </c>
+      <c r="L408" s="5" t="inlineStr">
+        <is>
+          <t>pH變大，血液比較不酸</t>
+        </is>
+      </c>
+      <c r="M408" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N408" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O408" s="5" t="inlineStr">
+        <is>
+          <t>因為呼出更多二氧化碳有助減少酸的負擔，所以pH（酸不酸的數字叫pH，數字越小越酸）朝變大的方向走，選「pH變大，血液比較不酸」。選「pH變大，但血液的酸增加」的同學，雖寫pH變大，卻把酸的變化說反了。</t>
+        </is>
+      </c>
+      <c r="P408" s="5" t="inlineStr">
+        <is>
+          <t>先想想：讓酸減少後，表示酸不酸的pH會變大還是變小？</t>
+        </is>
+      </c>
+      <c r="Q408" s="5" t="str"/>
+      <c r="R408" s="5" t="inlineStr">
+        <is>
+          <t>答案是「pH變大，血液比較不酸」，因為排CO₂增加可減酸，使pH（酸不酸的數字叫pH，數字越小越酸）上升。</t>
+        </is>
+      </c>
+      <c r="S408" s="5" t="inlineStr">
+        <is>
+          <t>多呼CO₂，酸減少，pH升</t>
+        </is>
+      </c>
+      <c r="T408" s="3" t="str">
+        <v>acid-base-balance；physiology/CH09 p.37, physiology/CH09 p.38, physiology/CH09 p.40, physiology/CH09 p.41, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U408" s="3" t="str"/>
+      <c r="V408" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W408" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X408" s="3" t="str"/>
+    </row>
+    <row r="409" ht="110" customHeight="1">
+      <c r="A409" s="3" t="str"/>
+      <c r="B409" s="7" t="str">
+        <v>acid-base-homeostasis-foundation-q05</v>
+      </c>
+      <c r="C409" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D409" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F409" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G409" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H409" s="5" t="inlineStr">
+        <is>
+          <t>氫離子（H⁺）會讓液體變酸，碳酸氫根（HCO₃⁻）會幫忙接住酸，腎臟排酸留鹼時會怎麼做？</t>
+        </is>
+      </c>
+      <c r="I409" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子送進管液，碳酸氫根留回血液</t>
+        </is>
+      </c>
+      <c r="J409" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子和碳酸氫根都送進管液</t>
+        </is>
+      </c>
+      <c r="K409" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子留回血液，不讓它排出</t>
+        </is>
+      </c>
+      <c r="L409" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子留回血液，碳酸氫根送進管液</t>
+        </is>
+      </c>
+      <c r="M409" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N409" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O409" s="5" t="inlineStr">
+        <is>
+          <t>因為氫離子要送走，能接酸的碳酸氫根要留下，所以選「把氫離子送進管液，碳酸氫根留回血液」。選「把氫離子留回血液，碳酸氫根送進管液」的同學，把排酸和留鹼的兩個方向交換了。</t>
+        </is>
+      </c>
+      <c r="P409" s="5" t="inlineStr">
+        <is>
+          <t>先想想：讓血變酸的要送走，能幫忙接酸的要留下嗎？</t>
+        </is>
+      </c>
+      <c r="Q409" s="5" t="str"/>
+      <c r="R409" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把氫離子送進管液，碳酸氫根留回血液」，因為H⁺入管液而HCO₃⁻回血液，是排酸留鹼。</t>
+        </is>
+      </c>
+      <c r="S409" s="5" t="inlineStr">
+        <is>
+          <t>酸進管液，幫手留回血</t>
+        </is>
+      </c>
+      <c r="T409" s="3" t="str">
+        <v>renal-acid-base-compensation；physiology/CH09 p.42, physiology/CH09 p.41, physiology/CH09 p.17, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U409" s="3" t="str"/>
+      <c r="V409" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W409" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X409" s="3" t="str"/>
+    </row>
+    <row r="410" ht="110" customHeight="1">
+      <c r="A410" s="3" t="str"/>
+      <c r="B410" s="7" t="str">
+        <v>acid-base-homeostasis-foundation-q06</v>
+      </c>
+      <c r="C410" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D410" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F410" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G410" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H410" s="5" t="inlineStr">
+        <is>
+          <t>氨是能接住酸的物質（NH₃），它接住讓液體變酸的氫離子（H⁺）後會變成什麼？</t>
+        </is>
+      </c>
+      <c r="I410" s="5" t="inlineStr">
+        <is>
+          <t>紅血球裡的血紅素</t>
+        </is>
+      </c>
+      <c r="J410" s="5" t="inlineStr">
+        <is>
+          <t>帶正電的銨離子（NH₄⁺）</t>
+        </is>
+      </c>
+      <c r="K410" s="5" t="inlineStr">
+        <is>
+          <t>會接酸的碳酸氫根（HCO₃⁻）</t>
+        </is>
+      </c>
+      <c r="L410" s="5" t="inlineStr">
+        <is>
+          <t>能呼出的二氧化碳（CO₂）</t>
+        </is>
+      </c>
+      <c r="M410" s="3" t="str">
+        <v>B</v>
+      </c>
+      <c r="N410" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O410" s="5" t="inlineStr">
+        <is>
+          <t>因為一個NH₃接上氫離子會成為NH₄⁺，所以選「帶正電的銨離子（NH₄⁺）」，再隨尿帶走酸。選「會接酸的碳酸氫根（HCO₃⁻）」的同學，所選的碳酸氫根是要留回血液的幫手，不是這個結合的產物。</t>
+        </is>
+      </c>
+      <c r="P410" s="5" t="inlineStr">
+        <is>
+          <t>先想想：NH₃接住一個H⁺，名稱和符號會變成哪個？</t>
+        </is>
+      </c>
+      <c r="Q410" s="5" t="str"/>
+      <c r="R410" s="5" t="inlineStr">
+        <is>
+          <t>答案是「帶正電的銨離子（NH₄⁺）」，因為NH₃結合H⁺形成NH₄⁺。</t>
+        </is>
+      </c>
+      <c r="S410" s="5" t="inlineStr">
+        <is>
+          <t>氨接一個氫，變銨隨尿走</t>
+        </is>
+      </c>
+      <c r="T410" s="3" t="str">
+        <v>renal-acid-base-compensation；physiology/CH09 p.42, physiology/CH09 p.41, physiology/CH09 p.17, physiology/CH09 p.44, physiology/CH09 p.45
+buffer-systems；physiology/CH09 p.38, physiology/CH09 p.39, physiology/CH09 p.40, physiology/CH09 p.42</v>
+      </c>
+      <c r="U410" s="3" t="str"/>
+      <c r="V410" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W410" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X410" s="3" t="str"/>
+    </row>
+    <row r="411" ht="110" customHeight="1">
+      <c r="A411" s="3" t="str"/>
+      <c r="B411" s="7" t="str">
+        <v>acid-base-homeostasis-case-q01</v>
+      </c>
+      <c r="C411" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D411" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E411" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F411" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G411" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H411" s="5" t="inlineStr">
+        <is>
+          <t>用公式把酸和鹼的量相除，來算血液酸不酸的數字pH，除法上面叫分子、下面叫分母，代入數字前應先確認哪種放法？</t>
+        </is>
+      </c>
+      <c r="I411" s="5" t="inlineStr">
+        <is>
+          <t>把鹼加酸，代替鹼除以酸</t>
+        </is>
+      </c>
+      <c r="J411" s="5" t="inlineStr">
+        <is>
+          <t>把鹼減酸，代替鹼除以酸</t>
+        </is>
+      </c>
+      <c r="K411" s="5" t="inlineStr">
+        <is>
+          <t>把鹼放上面，酸放下面</t>
+        </is>
+      </c>
+      <c r="L411" s="5" t="inlineStr">
+        <is>
+          <t>把酸放上面，鹼放下面</t>
+        </is>
+      </c>
+      <c r="M411" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N411" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O411" s="5" t="inlineStr">
+        <is>
+          <t>因為公式用鹼的量除以酸的量，所以先確認鹼在上、酸在下，選「把鹼放上面，酸放下面」。選「把酸放上面，鹼放下面」的同學，交換上下的量，算出的比較結果就會不同。</t>
+        </is>
+      </c>
+      <c r="P411" s="5" t="inlineStr">
+        <is>
+          <t>先想想：在這個算式裡，要用哪一種量除以哪一種量？</t>
+        </is>
+      </c>
+      <c r="Q411" s="5" t="str"/>
+      <c r="R411" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把鹼放上面，酸放下面」，因為公式是鹼除以酸，鹼在上面、酸在下面。</t>
+        </is>
+      </c>
+      <c r="S411" s="5" t="inlineStr">
+        <is>
+          <t>先放對上下，再代入數字</t>
+        </is>
+      </c>
+      <c r="T411" s="3" t="str">
+        <v>acid-base-balance；physiology/CH09 p.37, physiology/CH09 p.38, physiology/CH09 p.40, physiology/CH09 p.41, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U411" s="3" t="str"/>
+      <c r="V411" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W411" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X411" s="3" t="str"/>
+    </row>
+    <row r="412" ht="110" customHeight="1">
+      <c r="A412" s="3" t="str"/>
+      <c r="B412" s="7" t="str">
+        <v>acid-base-homeostasis-case-q02</v>
+      </c>
+      <c r="C412" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D412" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F412" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G412" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H412" s="5" t="inlineStr">
+        <is>
+          <t>血液裡的緩衝物先接住氫離子（H⁺）後，就能說酸已經離開身體了嗎？</t>
+        </is>
+      </c>
+      <c r="I412" s="5" t="inlineStr">
+        <is>
+          <t>能，接住氫離子就是把它排出體外</t>
+        </is>
+      </c>
+      <c r="J412" s="5" t="inlineStr">
+        <is>
+          <t>能，pH（酸不酸的數字叫pH，數字越小越酸）變穩就表示酸已經排掉</t>
+        </is>
+      </c>
+      <c r="K412" s="5" t="inlineStr">
+        <is>
+          <t>能，沒被接住的氫離子減少，就表示總酸量減少</t>
+        </is>
+      </c>
+      <c r="L412" s="5" t="inlineStr">
+        <is>
+          <t>不能，暫時接住和真正排出是兩回事</t>
+        </is>
+      </c>
+      <c r="M412" s="3" t="str">
+        <v>D</v>
+      </c>
+      <c r="N412" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="O412" s="5" t="inlineStr">
+        <is>
+          <t>因為緩衝只是先接住酸，讓酸鹼變化不要太大，所以還要等肺和腎處理，選「不能，暫時接住和真正排出是兩回事」。選「能，接住氫離子就是把它排出體外」的同學，把在身體裡接住酸，當成已把酸送到體外了。</t>
+        </is>
+      </c>
+      <c r="P412" s="5" t="inlineStr">
+        <is>
+          <t>先想想：被接住的酸，現在還在身體裡嗎？</t>
+        </is>
+      </c>
+      <c r="Q412" s="5" t="str"/>
+      <c r="R412" s="5" t="inlineStr">
+        <is>
+          <t>答案是「不能，暫時接住和真正排出是兩回事」，因為化學緩衝與排出體外不同，接住不表示已離開。</t>
+        </is>
+      </c>
+      <c r="S412" s="5" t="inlineStr">
+        <is>
+          <t>先接住，不等於已排出去</t>
+        </is>
+      </c>
+      <c r="T412" s="3" t="str">
+        <v>acid-base-balance；physiology/CH09 p.37, physiology/CH09 p.38, physiology/CH09 p.40, physiology/CH09 p.41, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U412" s="3" t="str"/>
+      <c r="V412" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W412" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X412" s="3" t="str"/>
+    </row>
+    <row r="413" ht="110" customHeight="1">
+      <c r="A413" s="3" t="str"/>
+      <c r="B413" s="7" t="str">
+        <v>acid-base-homeostasis-case-q03</v>
+      </c>
+      <c r="C413" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D413" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F413" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G413" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H413" s="5" t="inlineStr">
+        <is>
+          <t>血液裡的二氧化碳（CO₂，一種氣體）要真正離開身體，主要會走哪條路？</t>
+        </is>
+      </c>
+      <c r="I413" s="5" t="inlineStr">
+        <is>
+          <t>血液送到肺，再跟著呼氣出去</t>
+        </is>
+      </c>
+      <c r="J413" s="5" t="inlineStr">
+        <is>
+          <t>血液送到腎，和碳酸氫根一起進尿</t>
+        </is>
+      </c>
+      <c r="K413" s="5" t="inlineStr">
+        <is>
+          <t>血液送到肺，變成碳酸氫根再呼出去</t>
+        </is>
+      </c>
+      <c r="L413" s="5" t="inlineStr">
+        <is>
+          <t>在細胞膜兩側重新分配水分</t>
+        </is>
+      </c>
+      <c r="M413" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N413" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O413" s="5" t="inlineStr">
+        <is>
+          <t>因為肺能把血液送來的二氧化碳呼出去，所以選「血液送到肺，再跟著呼氣出去」。選「血液送到肺，變成碳酸氫根再呼出去」的同學，把血液中運送用的碳酸氫根，誤當成最後被呼出去的形式。</t>
+        </is>
+      </c>
+      <c r="P413" s="5" t="inlineStr">
+        <is>
+          <t>先想想：最後從嘴鼻呼出去的，是二氧化碳還是碳酸氫根？</t>
+        </is>
+      </c>
+      <c r="Q413" s="5" t="str"/>
+      <c r="R413" s="5" t="inlineStr">
+        <is>
+          <t>答案是「血液送到肺，再跟著呼氣出去」，因為CO₂由血液到肺，再隨呼氣排出。</t>
+        </is>
+      </c>
+      <c r="S413" s="5" t="inlineStr">
+        <is>
+          <t>血送CO₂到肺，再呼出去</t>
+        </is>
+      </c>
+      <c r="T413" s="3" t="str">
+        <v>acid-base-balance；physiology/CH09 p.37, physiology/CH09 p.38, physiology/CH09 p.40, physiology/CH09 p.41, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U413" s="3" t="str"/>
+      <c r="V413" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W413" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X413" s="3" t="str"/>
+    </row>
+    <row r="414" ht="110" customHeight="1">
+      <c r="A414" s="3" t="str"/>
+      <c r="B414" s="7" t="str">
+        <v>acid-base-homeostasis-case-q04</v>
+      </c>
+      <c r="C414" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D414" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E414" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F414" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G414" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H414" s="5" t="inlineStr">
+        <is>
+          <t>氫離子（H⁺）會讓血液變酸，碳酸氫根（HCO₃⁻）是接住氫離子的幫手，血液太酸時腎臟會怎麼做？</t>
+        </is>
+      </c>
+      <c r="I414" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子送進管液排掉，把碳酸氫根留回血液</t>
+        </is>
+      </c>
+      <c r="J414" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子留回血液，把碳酸氫根送進管液</t>
+        </is>
+      </c>
+      <c r="K414" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子和碳酸氫根都送進管液</t>
+        </is>
+      </c>
+      <c r="L414" s="5" t="inlineStr">
+        <is>
+          <t>把氫離子和碳酸氫根都留回血液</t>
+        </is>
+      </c>
+      <c r="M414" s="3" t="str">
+        <v>A</v>
+      </c>
+      <c r="N414" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O414" s="5" t="inlineStr">
+        <is>
+          <t>因為酸要排掉、接酸的幫手要保留，所以腎臟把氫離子送進管液，讓碳酸氫根回血，選「把氫離子送進管液排掉，把碳酸氫根留回血液」。選「把氫離子和碳酸氫根都送進管液」的同學，把能接酸的幫手也一起送走了。</t>
+        </is>
+      </c>
+      <c r="P414" s="5" t="inlineStr">
+        <is>
+          <t>先想想：哪一樣讓血變酸，哪一樣是幫忙接酸的？</t>
+        </is>
+      </c>
+      <c r="Q414" s="5" t="str"/>
+      <c r="R414" s="5" t="inlineStr">
+        <is>
+          <t>答案是「把氫離子送進管液排掉，把碳酸氫根留回血液」，因為H⁺進管液，HCO₃⁻回血液。</t>
+        </is>
+      </c>
+      <c r="S414" s="5" t="inlineStr">
+        <is>
+          <t>酸丟尿裡，幫手留血裡</t>
+        </is>
+      </c>
+      <c r="T414" s="3" t="str">
+        <v>renal-acid-base-compensation；physiology/CH09 p.42, physiology/CH09 p.41, physiology/CH09 p.17, physiology/CH09 p.44, physiology/CH09 p.45</v>
+      </c>
+      <c r="U414" s="3" t="str"/>
+      <c r="V414" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W414" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X414" s="3" t="str"/>
+    </row>
+    <row r="415" ht="110" customHeight="1">
+      <c r="A415" s="3" t="str"/>
+      <c r="B415" s="7" t="str">
+        <v>acid-base-homeostasis-case-q05</v>
+      </c>
+      <c r="C415" s="5" t="str">
+        <v>體液電解質與酸鹼平衡</v>
+      </c>
+      <c r="D415" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="E415" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F415" s="3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G415" s="3" t="str">
+        <v>單選</v>
+      </c>
+      <c r="H415" s="5" t="inlineStr">
+        <is>
+          <t>尿液帶走更多氫離子（H⁺，讓液體變酸的小粒子）時，對血液有什麼幫助？</t>
+        </is>
+      </c>
+      <c r="I415" s="5" t="inlineStr">
+        <is>
+          <t>也排掉碳酸氫根，讓血裡接酸的幫手變少</t>
+        </is>
+      </c>
+      <c r="J415" s="5" t="inlineStr">
+        <is>
+          <t>氫離子留在血液裡，沒有排出去</t>
+        </is>
+      </c>
+      <c r="K415" s="5" t="inlineStr">
+        <is>
+          <t>幫忙減少血液裡酸的負擔</t>
+        </is>
+      </c>
+      <c r="L415" s="5" t="inlineStr">
+        <is>
+          <t>尿變酸，表示血液也跟著更酸</t>
+        </is>
+      </c>
+      <c r="M415" s="3" t="str">
+        <v>C</v>
+      </c>
+      <c r="N415" s="3" t="str">
+        <v>3</v>
+      </c>
+      <c r="O415" s="5" t="inlineStr">
+        <is>
+          <t>因為氫離子隨尿離開身體，所以能幫血液減少酸的負擔，選「幫忙減少血液裡酸的負擔」。選「尿變酸，表示血液也跟著更酸」的同學，把尿裡的酸增多，誤當成血液裡的酸也增多。</t>
+        </is>
+      </c>
+      <c r="P415" s="5" t="inlineStr">
+        <is>
+          <t>先想想：酸已經被尿帶走，是留在血裡還是離開血裡？</t>
+        </is>
+      </c>
+      <c r="Q415" s="5" t="str"/>
+      <c r="R415" s="5" t="inlineStr">
+        <is>
+          <t>答案是「幫忙減少血液裡酸的負擔」，因為H⁺排入尿液有助減少血中酸負荷。</t>
+        </is>
+      </c>
+      <c r="S415" s="5" t="inlineStr">
+        <is>
+          <t>酸隨尿走，血的負擔變少</t>
+        </is>
+      </c>
+      <c r="T415" s="3" t="str">
+        <v>renal-acid-base-compensation；physiology/CH09 p.42, physiology/CH09 p.41, physiology/CH09 p.17, physiology/CH09 p.44, physiology/CH09 p.45
+buffer-systems；physiology/CH09 p.38, physiology/CH09 p.39, physiology/CH09 p.40, physiology/CH09 p.42</v>
+      </c>
+      <c r="U415" s="3" t="str"/>
+      <c r="V415" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="W415" s="5" t="str">
+        <v>https://albertchang1008-alt.github.io/115-1-AP2/materials/acid-base-homeostasis-v1/index.html</v>
+      </c>
+      <c r="X415" s="3" t="str"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="M2:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -28830,7 +38185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29291,6 +38646,86 @@
         <v>11 題｜public/materials/respiratory-control-v1/index.html；單元：呼吸系統；6 先備＋5 情境</v>
       </c>
     </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="5" t="str">
+        <v>腎臟位置、構造與功能</v>
+      </c>
+      <c r="B42" s="5" t="str">
+        <v>11 題｜public/materials/kidney-anatomy-v1/index.html；單元：泌尿系統；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="5" t="str">
+        <v>腎元、腎血流與近腎絲球器</v>
+      </c>
+      <c r="B43" s="5" t="str">
+        <v>11 題｜public/materials/nephron-circulation-v1/index.html；單元：泌尿系統；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="5" t="str">
+        <v>腎絲球過濾與清除率</v>
+      </c>
+      <c r="B44" s="5" t="str">
+        <v>11 題｜public/materials/filtration-clearance-v1/index.html；單元：泌尿系統；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="5" t="str">
+        <v>腎小管再吸收、分泌與排泄</v>
+      </c>
+      <c r="B45" s="5" t="str">
+        <v>11 題｜public/materials/tubular-handling-v1/index.html；單元：泌尿系統；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="5" t="str">
+        <v>逆流機制與尿液濃縮</v>
+      </c>
+      <c r="B46" s="5" t="str">
+        <v>11 題｜public/materials/urine-concentration-v1/index.html；單元：泌尿系統；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="5" t="str">
+        <v>尿液通路與排尿控制</v>
+      </c>
+      <c r="B47" s="5" t="str">
+        <v>11 題｜public/materials/urinary-route-micturition-v2/index.html；單元：泌尿系統；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="5" t="str">
+        <v>體液分布與細胞內外液</v>
+      </c>
+      <c r="B48" s="5" t="str">
+        <v>11 題｜public/materials/fluid-compartments-v1/index.html；單元：體液電解質與酸鹼平衡；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="5" t="str">
+        <v>水分收支與鈉水調節</v>
+      </c>
+      <c r="B49" s="5" t="str">
+        <v>11 題｜public/materials/water-sodium-regulation-v1/index.html；單元：體液電解質與酸鹼平衡；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="5" t="str">
+        <v>電解質、滲透與離子平衡</v>
+      </c>
+      <c r="B50" s="5" t="str">
+        <v>11 題｜public/materials/electrolyte-balance-v1/index.html；單元：體液電解質與酸鹼平衡；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="5" t="str">
+        <v>酸鹼緩衝與肺腎調節</v>
+      </c>
+      <c r="B51" s="5" t="str">
+        <v>11 題｜public/materials/acid-base-homeostasis-v1/index.html；單元：體液電解質與酸鹼平衡；核可兩階段6＋5；不含節點小檢核與lab.predict</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
